--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518394470215</v>
+        <v>15.99518585205078</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073600044276</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008337506717</v>
+        <v>15.48008522099254</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073600044276</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869618523321</v>
+        <v>14.64869711259133</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291838990186</v>
+        <v>14.70291932069259</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572238922119</v>
+        <v>15.14572143554688</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186880124062</v>
+        <v>15.18186784529029</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195510316014</v>
+        <v>14.71195417679867</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113329386751</v>
+        <v>15.00113234929747</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.4981575012207</v>
+        <v>15.49815845489502</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52526860192735</v>
+        <v>15.52526955726993</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209568682876</v>
+        <v>14.99209660936272</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15475884379279</v>
+        <v>15.15475977633618</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399261474609</v>
+        <v>16.19399452209473</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317077728191</v>
+        <v>16.48317271869031</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977214018008</v>
+        <v>16.13977404114256</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702436878384</v>
+        <v>16.44702630593487</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -1052,16 +1052,16 @@
         <v>43818</v>
       </c>
       <c r="B32" t="n">
-        <v>16.40184211730957</v>
+        <v>16.40184020996094</v>
       </c>
       <c r="C32" t="n">
-        <v>16.59161639745967</v>
+        <v>16.59161446804244</v>
       </c>
       <c r="D32" t="n">
-        <v>16.33858459847224</v>
+        <v>16.33858269847974</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35665866775094</v>
+        <v>16.35665676565663</v>
       </c>
       <c r="F32" t="n">
         <v>961700</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436088562012</v>
+        <v>16.28436279296875</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51931856874445</v>
+        <v>16.51932050361312</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444551937144</v>
+        <v>15.81444737168</v>
       </c>
       <c r="E33" t="n">
-        <v>16.4018388653634</v>
+        <v>16.40184078647195</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1092,16 +1092,16 @@
         <v>43822</v>
       </c>
       <c r="B34" t="n">
-        <v>16.38376617431641</v>
+        <v>16.38376808166504</v>
       </c>
       <c r="C34" t="n">
-        <v>16.60968684354858</v>
+        <v>16.60968877719821</v>
       </c>
       <c r="D34" t="n">
-        <v>16.09458799348129</v>
+        <v>16.09458986716468</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31147162910763</v>
+        <v>16.31147352803995</v>
       </c>
       <c r="F34" t="n">
         <v>766700</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21206855773926</v>
+        <v>16.21206665039062</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620446892584</v>
+        <v>16.73620249991266</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21206855773926</v>
+        <v>16.21206665039062</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813040076541</v>
+        <v>16.71812843387864</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -33872,19 +33872,19 @@
         <v>46231</v>
       </c>
       <c r="B1673" t="n">
-        <v>9.73</v>
+        <v>9.68</v>
       </c>
       <c r="C1673" t="n">
         <v>10.03</v>
       </c>
       <c r="D1673" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E1673" t="n">
         <v>9.91</v>
       </c>
       <c r="F1673" t="n">
-        <v>839400</v>
+        <v>2646700</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -452,16 +452,16 @@
         <v>43774</v>
       </c>
       <c r="B2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04940511406312</v>
+        <v>16.04940323214578</v>
       </c>
       <c r="E2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="F2" t="n">
         <v>862100</v>
@@ -472,16 +472,16 @@
         <v>43775</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1307373046875</v>
+        <v>16.13073921203613</v>
       </c>
       <c r="C3" t="n">
-        <v>16.32050985334077</v>
+        <v>16.3205117831287</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94096303239619</v>
+        <v>15.94096491730532</v>
       </c>
       <c r="E3" t="n">
-        <v>16.26628937138813</v>
+        <v>16.26629129476486</v>
       </c>
       <c r="F3" t="n">
         <v>1352600</v>
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518394470215</v>
+        <v>15.99518585205078</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073600044276</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008337506717</v>
+        <v>15.48008522099254</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073600044276</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -532,16 +532,16 @@
         <v>43780</v>
       </c>
       <c r="B6" t="n">
-        <v>15.80541133880615</v>
+        <v>15.80540943145752</v>
       </c>
       <c r="C6" t="n">
-        <v>15.85963182203875</v>
+        <v>15.85962990814695</v>
       </c>
       <c r="D6" t="n">
-        <v>15.52527016452663</v>
+        <v>15.52526829098458</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65178519994872</v>
+        <v>15.65178331113922</v>
       </c>
       <c r="F6" t="n">
         <v>2507900</v>
@@ -552,16 +552,16 @@
         <v>43781</v>
       </c>
       <c r="B7" t="n">
-        <v>15.18186855316162</v>
+        <v>15.18186950683594</v>
       </c>
       <c r="C7" t="n">
-        <v>15.86866760668798</v>
+        <v>15.86866860350472</v>
       </c>
       <c r="D7" t="n">
-        <v>15.02824242640391</v>
+        <v>15.02824337042795</v>
       </c>
       <c r="E7" t="n">
-        <v>15.79637306019247</v>
+        <v>15.79637405246791</v>
       </c>
       <c r="F7" t="n">
         <v>2855600</v>
@@ -572,16 +572,16 @@
         <v>43782</v>
       </c>
       <c r="B8" t="n">
-        <v>13.55524063110352</v>
+        <v>13.55524158477783</v>
       </c>
       <c r="C8" t="n">
-        <v>14.91076469421387</v>
+        <v>14.91076574325561</v>
       </c>
       <c r="D8" t="n">
-        <v>13.3925774677482</v>
+        <v>13.3925784099784</v>
       </c>
       <c r="E8" t="n">
-        <v>14.73002746301063</v>
+        <v>14.73002849933667</v>
       </c>
       <c r="F8" t="n">
         <v>9002100</v>
@@ -592,16 +592,16 @@
         <v>43783</v>
       </c>
       <c r="B9" t="n">
-        <v>13.55524063110352</v>
+        <v>13.55524158477783</v>
       </c>
       <c r="C9" t="n">
-        <v>13.93478743771993</v>
+        <v>13.93478841809713</v>
       </c>
       <c r="D9" t="n">
-        <v>12.80518405179464</v>
+        <v>12.80518495269898</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60946197282829</v>
+        <v>13.60946293031733</v>
       </c>
       <c r="F9" t="n">
         <v>6889800</v>
@@ -612,16 +612,16 @@
         <v>43787</v>
       </c>
       <c r="B10" t="n">
-        <v>14.11552429199219</v>
+        <v>14.11552333831787</v>
       </c>
       <c r="C10" t="n">
-        <v>14.35048201117233</v>
+        <v>14.35048104162378</v>
       </c>
       <c r="D10" t="n">
-        <v>13.5733151652138</v>
+        <v>13.57331424817226</v>
       </c>
       <c r="E10" t="n">
-        <v>13.64560971545092</v>
+        <v>13.64560879352501</v>
       </c>
       <c r="F10" t="n">
         <v>4129300</v>
@@ -632,16 +632,16 @@
         <v>43788</v>
       </c>
       <c r="B11" t="n">
-        <v>13.91671371459961</v>
+        <v>13.91671276092529</v>
       </c>
       <c r="C11" t="n">
-        <v>14.40470235493443</v>
+        <v>14.40470136781958</v>
       </c>
       <c r="D11" t="n">
-        <v>13.79019868380626</v>
+        <v>13.79019773880167</v>
       </c>
       <c r="E11" t="n">
-        <v>14.27818732414107</v>
+        <v>14.27818634569596</v>
       </c>
       <c r="F11" t="n">
         <v>1475000</v>
@@ -652,16 +652,16 @@
         <v>43790</v>
       </c>
       <c r="B12" t="n">
-        <v>13.97093677520752</v>
+        <v>13.97093486785889</v>
       </c>
       <c r="C12" t="n">
-        <v>14.09745268337332</v>
+        <v>14.09745075875241</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66368447096136</v>
+        <v>13.66368260555961</v>
       </c>
       <c r="E12" t="n">
-        <v>13.92575246073265</v>
+        <v>13.9257505595527</v>
       </c>
       <c r="F12" t="n">
         <v>946900</v>
@@ -672,16 +672,16 @@
         <v>43791</v>
       </c>
       <c r="B13" t="n">
-        <v>14.31433486938477</v>
+        <v>14.31433391571045</v>
       </c>
       <c r="C13" t="n">
-        <v>14.36855535165813</v>
+        <v>14.36855439437145</v>
       </c>
       <c r="D13" t="n">
-        <v>13.77212487573694</v>
+        <v>13.77212395818667</v>
       </c>
       <c r="E13" t="n">
-        <v>13.79923597869265</v>
+        <v>13.79923505933614</v>
       </c>
       <c r="F13" t="n">
         <v>1005200</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869618523321</v>
+        <v>14.64869711259133</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291838990186</v>
+        <v>14.70291932069259</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572238922119</v>
+        <v>15.14572334289551</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186880124062</v>
+        <v>15.18186975719096</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195510316014</v>
+        <v>14.71195602952161</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113329386751</v>
+        <v>15.00113423843754</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.4981575012207</v>
+        <v>15.49815940856934</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52526860192735</v>
+        <v>15.52527051261252</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209568682876</v>
+        <v>14.99209753189668</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15475884379279</v>
+        <v>15.15476070887956</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -832,16 +832,16 @@
         <v>43803</v>
       </c>
       <c r="B21" t="n">
-        <v>16.10362434387207</v>
+        <v>16.1036262512207</v>
       </c>
       <c r="C21" t="n">
-        <v>16.19399295245853</v>
+        <v>16.19399487051062</v>
       </c>
       <c r="D21" t="n">
-        <v>15.74215163316408</v>
+        <v>15.74215349769909</v>
       </c>
       <c r="E21" t="n">
-        <v>16.0403668349529</v>
+        <v>16.04036873480918</v>
       </c>
       <c r="F21" t="n">
         <v>976000</v>
@@ -852,16 +852,16 @@
         <v>43804</v>
       </c>
       <c r="B22" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C22" t="n">
-        <v>16.4379889546035</v>
+        <v>16.43798702712168</v>
       </c>
       <c r="D22" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="E22" t="n">
-        <v>16.40184081890766</v>
+        <v>16.40183889566449</v>
       </c>
       <c r="F22" t="n">
         <v>1168600</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399261474609</v>
+        <v>16.19399452209473</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317077728191</v>
+        <v>16.48317271869031</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977214018008</v>
+        <v>16.13977404114256</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702436878384</v>
+        <v>16.44702630593487</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -892,16 +892,16 @@
         <v>43808</v>
       </c>
       <c r="B24" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C24" t="n">
-        <v>16.37473144077376</v>
+        <v>16.37472952070938</v>
       </c>
       <c r="D24" t="n">
-        <v>16.21206827741844</v>
+        <v>16.21206637642758</v>
       </c>
       <c r="E24" t="n">
-        <v>16.33858330507792</v>
+        <v>16.33858138925219</v>
       </c>
       <c r="F24" t="n">
         <v>474400</v>
@@ -932,16 +932,16 @@
         <v>43810</v>
       </c>
       <c r="B26" t="n">
-        <v>17.48626327514648</v>
+        <v>17.48626136779785</v>
       </c>
       <c r="C26" t="n">
-        <v>17.84773606593138</v>
+        <v>17.84773411915439</v>
       </c>
       <c r="D26" t="n">
-        <v>16.92597915670124</v>
+        <v>16.9259773104667</v>
       </c>
       <c r="E26" t="n">
-        <v>16.98020136804764</v>
+        <v>16.98019951589871</v>
       </c>
       <c r="F26" t="n">
         <v>2363200</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436088562012</v>
+        <v>16.28436279296875</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51931856874445</v>
+        <v>16.51932050361312</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444551937144</v>
+        <v>15.81444737168</v>
       </c>
       <c r="E33" t="n">
-        <v>16.4018388653634</v>
+        <v>16.40184078647195</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1092,16 +1092,16 @@
         <v>43822</v>
       </c>
       <c r="B34" t="n">
-        <v>16.38376808166504</v>
+        <v>16.38376617431641</v>
       </c>
       <c r="C34" t="n">
-        <v>16.60968877719821</v>
+        <v>16.60968684354858</v>
       </c>
       <c r="D34" t="n">
-        <v>16.09458986716468</v>
+        <v>16.09458799348129</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31147352803995</v>
+        <v>16.31147162910763</v>
       </c>
       <c r="F34" t="n">
         <v>766700</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739547729492</v>
+        <v>16.53739356994629</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872707174377</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821724087158</v>
+        <v>16.24821536687546</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872707174377</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -1192,16 +1192,16 @@
         <v>43833</v>
       </c>
       <c r="B39" t="n">
-        <v>16.49941062927246</v>
+        <v>16.49941253662109</v>
       </c>
       <c r="C39" t="n">
-        <v>16.673571564339</v>
+        <v>16.67357349182081</v>
       </c>
       <c r="D39" t="n">
-        <v>16.20608805337542</v>
+        <v>16.20608992681567</v>
       </c>
       <c r="E39" t="n">
-        <v>16.22442115145411</v>
+        <v>16.22442302701367</v>
       </c>
       <c r="F39" t="n">
         <v>1551100</v>
@@ -1212,16 +1212,16 @@
         <v>43836</v>
       </c>
       <c r="B40" t="n">
-        <v>16.32525062561035</v>
+        <v>16.32525253295898</v>
       </c>
       <c r="C40" t="n">
-        <v>16.58190876833361</v>
+        <v>16.5819107056687</v>
       </c>
       <c r="D40" t="n">
-        <v>16.31608407604803</v>
+        <v>16.3160859823257</v>
       </c>
       <c r="E40" t="n">
-        <v>16.49941157061329</v>
+        <v>16.49941349830989</v>
       </c>
       <c r="F40" t="n">
         <v>970100</v>
@@ -1272,16 +1272,16 @@
         <v>43839</v>
       </c>
       <c r="B43" t="n">
-        <v>14.4003210067749</v>
+        <v>14.40032005310059</v>
       </c>
       <c r="C43" t="n">
-        <v>15.28945628290185</v>
+        <v>15.28945527034375</v>
       </c>
       <c r="D43" t="n">
-        <v>14.30865725181199</v>
+        <v>14.30865630420819</v>
       </c>
       <c r="E43" t="n">
-        <v>15.09696222264567</v>
+        <v>15.09696122283566</v>
       </c>
       <c r="F43" t="n">
         <v>3315800</v>
@@ -1332,16 +1332,16 @@
         <v>43844</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72027206420898</v>
+        <v>15.7202730178833</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74777171241136</v>
+        <v>15.74777266775395</v>
       </c>
       <c r="D46" t="n">
-        <v>15.24362198541098</v>
+        <v>15.2436229101692</v>
       </c>
       <c r="E46" t="n">
-        <v>15.35361882987996</v>
+        <v>15.35361976131116</v>
       </c>
       <c r="F46" t="n">
         <v>2831800</v>
@@ -1352,16 +1352,16 @@
         <v>43845</v>
       </c>
       <c r="B47" t="n">
-        <v>15.76610565185547</v>
+        <v>15.76610469818115</v>
       </c>
       <c r="C47" t="n">
-        <v>15.76610565185547</v>
+        <v>15.76610469818115</v>
       </c>
       <c r="D47" t="n">
-        <v>15.35361964852889</v>
+        <v>15.3536187198054</v>
       </c>
       <c r="E47" t="n">
-        <v>15.72027290240772</v>
+        <v>15.72027195150578</v>
       </c>
       <c r="F47" t="n">
         <v>1838000</v>
@@ -1372,16 +1372,16 @@
         <v>43846</v>
       </c>
       <c r="B48" t="n">
-        <v>16.10525894165039</v>
+        <v>16.10525703430176</v>
       </c>
       <c r="C48" t="n">
-        <v>16.34358398910408</v>
+        <v>16.34358205353058</v>
       </c>
       <c r="D48" t="n">
-        <v>15.56444474710943</v>
+        <v>15.56444290380952</v>
       </c>
       <c r="E48" t="n">
-        <v>15.76610534406134</v>
+        <v>15.76610347687872</v>
       </c>
       <c r="F48" t="n">
         <v>3608000</v>
@@ -1392,16 +1392,16 @@
         <v>43847</v>
       </c>
       <c r="B49" t="n">
-        <v>16.31608390808105</v>
+        <v>16.31608581542969</v>
       </c>
       <c r="C49" t="n">
-        <v>16.31608390808105</v>
+        <v>16.31608581542969</v>
       </c>
       <c r="D49" t="n">
-        <v>15.93109757212972</v>
+        <v>15.93109943447349</v>
       </c>
       <c r="E49" t="n">
-        <v>16.2244219100826</v>
+        <v>16.22442380671596</v>
       </c>
       <c r="F49" t="n">
         <v>2719000</v>
@@ -1492,16 +1492,16 @@
         <v>43854</v>
       </c>
       <c r="B54" t="n">
-        <v>15.73860740661621</v>
+        <v>15.73860645294189</v>
       </c>
       <c r="C54" t="n">
-        <v>15.80277151322809</v>
+        <v>15.80277055566578</v>
       </c>
       <c r="D54" t="n">
-        <v>15.39945202380098</v>
+        <v>15.39945109067764</v>
       </c>
       <c r="E54" t="n">
-        <v>15.57361299056236</v>
+        <v>15.57361204688581</v>
       </c>
       <c r="F54" t="n">
         <v>887500</v>
@@ -1552,16 +1552,16 @@
         <v>43859</v>
       </c>
       <c r="B57" t="n">
-        <v>15.21612548828125</v>
+        <v>15.21612453460693</v>
       </c>
       <c r="C57" t="n">
-        <v>15.64694285979114</v>
+        <v>15.64694187911524</v>
       </c>
       <c r="D57" t="n">
-        <v>15.16112793514696</v>
+        <v>15.16112698491963</v>
       </c>
       <c r="E57" t="n">
-        <v>15.40861779842162</v>
+        <v>15.4086168326828</v>
       </c>
       <c r="F57" t="n">
         <v>686700</v>
@@ -1592,16 +1592,16 @@
         <v>43861</v>
       </c>
       <c r="B59" t="n">
-        <v>14.66614437103271</v>
+        <v>14.6661434173584</v>
       </c>
       <c r="C59" t="n">
-        <v>15.21612513461457</v>
+        <v>15.21612414517745</v>
       </c>
       <c r="D59" t="n">
-        <v>14.66614437103271</v>
+        <v>14.6661434173584</v>
       </c>
       <c r="E59" t="n">
-        <v>14.94113387865332</v>
+        <v>14.94113290709765</v>
       </c>
       <c r="F59" t="n">
         <v>897400</v>
@@ -1612,16 +1612,16 @@
         <v>43864</v>
       </c>
       <c r="B60" t="n">
-        <v>14.66614437103271</v>
+        <v>14.6661434173584</v>
       </c>
       <c r="C60" t="n">
-        <v>15.01446453057486</v>
+        <v>15.01446355425082</v>
       </c>
       <c r="D60" t="n">
-        <v>14.59281371911118</v>
+        <v>14.59281277020523</v>
       </c>
       <c r="E60" t="n">
-        <v>14.73030847292148</v>
+        <v>14.73030751507486</v>
       </c>
       <c r="F60" t="n">
         <v>1344600</v>
@@ -1632,16 +1632,16 @@
         <v>43865</v>
       </c>
       <c r="B61" t="n">
-        <v>14.92280292510986</v>
+        <v>14.92280197143555</v>
       </c>
       <c r="C61" t="n">
-        <v>15.03279803175682</v>
+        <v>15.03279707105302</v>
       </c>
       <c r="D61" t="n">
-        <v>14.68447786292053</v>
+        <v>14.6844769244769</v>
       </c>
       <c r="E61" t="n">
-        <v>14.92280292510986</v>
+        <v>14.92280197143555</v>
       </c>
       <c r="F61" t="n">
         <v>708300</v>
@@ -1752,16 +1752,16 @@
         <v>43873</v>
       </c>
       <c r="B67" t="n">
-        <v>14.66614437103271</v>
+        <v>14.6661434173584</v>
       </c>
       <c r="C67" t="n">
-        <v>14.7578081230198</v>
+        <v>14.757807163385</v>
       </c>
       <c r="D67" t="n">
-        <v>14.29949111142503</v>
+        <v>14.29949018159255</v>
       </c>
       <c r="E67" t="n">
-        <v>14.29949111142503</v>
+        <v>14.29949018159255</v>
       </c>
       <c r="F67" t="n">
         <v>2320900</v>
@@ -1832,16 +1832,16 @@
         <v>43879</v>
       </c>
       <c r="B71" t="n">
-        <v>15.48194789886475</v>
+        <v>15.48194694519043</v>
       </c>
       <c r="C71" t="n">
-        <v>15.57361164970714</v>
+        <v>15.57361069038642</v>
       </c>
       <c r="D71" t="n">
-        <v>14.4828175603683</v>
+        <v>14.48281666823953</v>
       </c>
       <c r="E71" t="n">
-        <v>14.64781108804616</v>
+        <v>14.64781018575394</v>
       </c>
       <c r="F71" t="n">
         <v>4553800</v>
@@ -1892,16 +1892,16 @@
         <v>43882</v>
       </c>
       <c r="B74" t="n">
-        <v>16.04109382629395</v>
+        <v>16.04109573364258</v>
       </c>
       <c r="C74" t="n">
-        <v>16.04109382629395</v>
+        <v>16.04109573364258</v>
       </c>
       <c r="D74" t="n">
-        <v>15.43611557042667</v>
+        <v>15.43611740584103</v>
       </c>
       <c r="E74" t="n">
-        <v>15.63777440626894</v>
+        <v>15.63777626566132</v>
       </c>
       <c r="F74" t="n">
         <v>1940300</v>
@@ -1932,16 +1932,16 @@
         <v>43888</v>
       </c>
       <c r="B76" t="n">
-        <v>14.47365093231201</v>
+        <v>14.47365188598633</v>
       </c>
       <c r="C76" t="n">
-        <v>14.88613606053529</v>
+        <v>14.88613704138841</v>
       </c>
       <c r="D76" t="n">
-        <v>14.09783112939368</v>
+        <v>14.09783205830509</v>
       </c>
       <c r="E76" t="n">
-        <v>14.56531468265955</v>
+        <v>14.56531564237362</v>
       </c>
       <c r="F76" t="n">
         <v>1056800</v>
@@ -2032,16 +2032,16 @@
         <v>43895</v>
       </c>
       <c r="B81" t="n">
-        <v>13.29119300842285</v>
+        <v>13.29119396209717</v>
       </c>
       <c r="C81" t="n">
-        <v>14.68447710890754</v>
+        <v>14.68447816255327</v>
       </c>
       <c r="D81" t="n">
-        <v>13.22702890811669</v>
+        <v>13.22702985718708</v>
       </c>
       <c r="E81" t="n">
-        <v>14.62031213443108</v>
+        <v>14.62031318347281</v>
       </c>
       <c r="F81" t="n">
         <v>2239700</v>
@@ -2172,16 +2172,16 @@
         <v>43906</v>
       </c>
       <c r="B88" t="n">
-        <v>7.562231063842773</v>
+        <v>7.562230587005615</v>
       </c>
       <c r="C88" t="n">
-        <v>8.918849065390972</v>
+        <v>8.918848503012144</v>
       </c>
       <c r="D88" t="n">
-        <v>7.562231063842773</v>
+        <v>7.562230587005615</v>
       </c>
       <c r="E88" t="n">
-        <v>8.918849065390972</v>
+        <v>8.918848503012144</v>
       </c>
       <c r="F88" t="n">
         <v>1319600</v>
@@ -2252,16 +2252,16 @@
         <v>43910</v>
       </c>
       <c r="B92" t="n">
-        <v>5.820625782012939</v>
+        <v>5.820626258850098</v>
       </c>
       <c r="C92" t="n">
-        <v>6.508101278402306</v>
+        <v>6.508101811558814</v>
       </c>
       <c r="D92" t="n">
-        <v>5.756461682084427</v>
+        <v>5.756462153665136</v>
       </c>
       <c r="E92" t="n">
-        <v>6.27894277960585</v>
+        <v>6.278943293989242</v>
       </c>
       <c r="F92" t="n">
         <v>2218000</v>
@@ -2332,16 +2332,16 @@
         <v>43916</v>
       </c>
       <c r="B96" t="n">
-        <v>6.874754905700684</v>
+        <v>6.874755382537842</v>
       </c>
       <c r="C96" t="n">
-        <v>7.653894144681544</v>
+        <v>7.653894675560271</v>
       </c>
       <c r="D96" t="n">
-        <v>6.297275388721391</v>
+        <v>6.29727582550422</v>
       </c>
       <c r="E96" t="n">
-        <v>6.471435898782693</v>
+        <v>6.471436347645401</v>
       </c>
       <c r="F96" t="n">
         <v>4787500</v>
@@ -2432,16 +2432,16 @@
         <v>43923</v>
       </c>
       <c r="B101" t="n">
-        <v>5.536468982696533</v>
+        <v>5.536469459533691</v>
       </c>
       <c r="C101" t="n">
-        <v>5.793126679144077</v>
+        <v>5.793127178086285</v>
       </c>
       <c r="D101" t="n">
-        <v>5.334809707483203</v>
+        <v>5.334810166952138</v>
       </c>
       <c r="E101" t="n">
-        <v>5.408140353015323</v>
+        <v>5.408140818799975</v>
       </c>
       <c r="F101" t="n">
         <v>2769000</v>
@@ -2452,16 +2452,16 @@
         <v>43924</v>
       </c>
       <c r="B102" t="n">
-        <v>5.582300662994385</v>
+        <v>5.582301139831543</v>
       </c>
       <c r="C102" t="n">
-        <v>5.710629288268649</v>
+        <v>5.71062977606757</v>
       </c>
       <c r="D102" t="n">
-        <v>5.068985724812216</v>
+        <v>5.068986157802285</v>
       </c>
       <c r="E102" t="n">
-        <v>5.609799435582029</v>
+        <v>5.609799914768118</v>
       </c>
       <c r="F102" t="n">
         <v>3057300</v>
@@ -2492,16 +2492,16 @@
         <v>43928</v>
       </c>
       <c r="B104" t="n">
-        <v>7.342238903045654</v>
+        <v>7.342238426208496</v>
       </c>
       <c r="C104" t="n">
-        <v>7.846387802134982</v>
+        <v>7.846387292556186</v>
       </c>
       <c r="D104" t="n">
-        <v>6.608931492931209</v>
+        <v>6.608931063718246</v>
       </c>
       <c r="E104" t="n">
-        <v>6.773925463518632</v>
+        <v>6.773925023590238</v>
       </c>
       <c r="F104" t="n">
         <v>4216400</v>
@@ -2532,16 +2532,16 @@
         <v>43930</v>
       </c>
       <c r="B106" t="n">
-        <v>7.883052825927734</v>
+        <v>7.883052349090576</v>
       </c>
       <c r="C106" t="n">
-        <v>8.653024659073285</v>
+        <v>8.653024135661383</v>
       </c>
       <c r="D106" t="n">
-        <v>7.718058424597103</v>
+        <v>7.718057957740275</v>
       </c>
       <c r="E106" t="n">
-        <v>8.12137700386382</v>
+        <v>8.121376512610697</v>
       </c>
       <c r="F106" t="n">
         <v>2853400</v>
@@ -2672,16 +2672,16 @@
         <v>43943</v>
       </c>
       <c r="B113" t="n">
-        <v>8.983013153076172</v>
+        <v>8.983012199401855</v>
       </c>
       <c r="C113" t="n">
-        <v>9.285502295675192</v>
+        <v>9.28550130988736</v>
       </c>
       <c r="D113" t="n">
-        <v>8.570528038092988</v>
+        <v>8.57052712820982</v>
       </c>
       <c r="E113" t="n">
-        <v>8.57969371349729</v>
+        <v>8.579692802641055</v>
       </c>
       <c r="F113" t="n">
         <v>2037400</v>
@@ -2732,16 +2732,16 @@
         <v>43948</v>
       </c>
       <c r="B116" t="n">
-        <v>7.333072185516357</v>
+        <v>7.333071708679199</v>
       </c>
       <c r="C116" t="n">
-        <v>7.947217050986978</v>
+        <v>7.947216534214704</v>
       </c>
       <c r="D116" t="n">
-        <v>7.296406859555589</v>
+        <v>7.296406385102614</v>
       </c>
       <c r="E116" t="n">
-        <v>7.928883950921431</v>
+        <v>7.928883435341277</v>
       </c>
       <c r="F116" t="n">
         <v>2360400</v>
@@ -2772,16 +2772,16 @@
         <v>43950</v>
       </c>
       <c r="B118" t="n">
-        <v>9.12050724029541</v>
+        <v>9.120508193969727</v>
       </c>
       <c r="C118" t="n">
-        <v>9.166339110682868</v>
+        <v>9.166340069149538</v>
       </c>
       <c r="D118" t="n">
-        <v>8.258871748526117</v>
+        <v>8.258872612104607</v>
       </c>
       <c r="E118" t="n">
-        <v>8.442198355905731</v>
+        <v>8.442199238653536</v>
       </c>
       <c r="F118" t="n">
         <v>3867700</v>
@@ -2852,16 +2852,16 @@
         <v>43957</v>
       </c>
       <c r="B122" t="n">
-        <v>7.828054428100586</v>
+        <v>7.828054904937744</v>
       </c>
       <c r="C122" t="n">
-        <v>8.148876681992785</v>
+        <v>8.148877178372471</v>
       </c>
       <c r="D122" t="n">
-        <v>7.553064049645888</v>
+        <v>7.553064509732316</v>
       </c>
       <c r="E122" t="n">
-        <v>7.928883854726839</v>
+        <v>7.928884337705908</v>
       </c>
       <c r="F122" t="n">
         <v>2058000</v>
@@ -2912,16 +2912,16 @@
         <v>43962</v>
       </c>
       <c r="B125" t="n">
-        <v>6.718927383422852</v>
+        <v>6.718926906585693</v>
       </c>
       <c r="C125" t="n">
-        <v>7.058081870301661</v>
+        <v>7.058081369394968</v>
       </c>
       <c r="D125" t="n">
-        <v>6.700594720269542</v>
+        <v>6.700594244733439</v>
       </c>
       <c r="E125" t="n">
-        <v>7.058081870301661</v>
+        <v>7.058081369394968</v>
       </c>
       <c r="F125" t="n">
         <v>2505400</v>
@@ -2972,16 +2972,16 @@
         <v>43965</v>
       </c>
       <c r="B128" t="n">
-        <v>6.08644962310791</v>
+        <v>6.086450099945068</v>
       </c>
       <c r="C128" t="n">
-        <v>6.187279485251405</v>
+        <v>6.187279969987983</v>
       </c>
       <c r="D128" t="n">
-        <v>5.701463274091976</v>
+        <v>5.701463720767742</v>
       </c>
       <c r="E128" t="n">
-        <v>5.893956448599943</v>
+        <v>5.893956910356406</v>
       </c>
       <c r="F128" t="n">
         <v>4161800</v>
@@ -2992,16 +2992,16 @@
         <v>43966</v>
       </c>
       <c r="B129" t="n">
-        <v>6.049784660339355</v>
+        <v>6.049784183502197</v>
       </c>
       <c r="C129" t="n">
-        <v>6.645596882005126</v>
+        <v>6.645596358206725</v>
       </c>
       <c r="D129" t="n">
-        <v>5.857291474307565</v>
+        <v>5.857291012642501</v>
       </c>
       <c r="E129" t="n">
-        <v>6.049784660339355</v>
+        <v>6.049784183502197</v>
       </c>
       <c r="F129" t="n">
         <v>4143200</v>
@@ -3012,16 +3012,16 @@
         <v>43969</v>
       </c>
       <c r="B130" t="n">
-        <v>6.783092021942139</v>
+        <v>6.78309154510498</v>
       </c>
       <c r="C130" t="n">
-        <v>6.856422675624999</v>
+        <v>6.856422193632849</v>
       </c>
       <c r="D130" t="n">
-        <v>6.260610458824003</v>
+        <v>6.260610018716203</v>
       </c>
       <c r="E130" t="n">
-        <v>6.46227019353704</v>
+        <v>6.462269739252984</v>
       </c>
       <c r="F130" t="n">
         <v>4121800</v>
@@ -3032,16 +3032,16 @@
         <v>43970</v>
       </c>
       <c r="B131" t="n">
-        <v>7.333072185516357</v>
+        <v>7.333071708679199</v>
       </c>
       <c r="C131" t="n">
-        <v>7.55306414128097</v>
+        <v>7.553063650138711</v>
       </c>
       <c r="D131" t="n">
-        <v>6.709761207098126</v>
+        <v>6.709760770792116</v>
       </c>
       <c r="E131" t="n">
-        <v>6.828923297928043</v>
+        <v>6.828922853873451</v>
       </c>
       <c r="F131" t="n">
         <v>3759800</v>
@@ -3072,16 +3072,16 @@
         <v>43972</v>
       </c>
       <c r="B133" t="n">
-        <v>7.727224826812744</v>
+        <v>7.727224349975586</v>
       </c>
       <c r="C133" t="n">
-        <v>7.873886125561454</v>
+        <v>7.873885639674015</v>
       </c>
       <c r="D133" t="n">
-        <v>7.461401004288134</v>
+        <v>7.461400543854623</v>
       </c>
       <c r="E133" t="n">
-        <v>7.55306387892093</v>
+        <v>7.55306341283102</v>
       </c>
       <c r="F133" t="n">
         <v>2073000</v>
@@ -3112,16 +3112,16 @@
         <v>43976</v>
       </c>
       <c r="B135" t="n">
-        <v>7.754724025726318</v>
+        <v>7.75472354888916</v>
       </c>
       <c r="C135" t="n">
-        <v>7.828054679109565</v>
+        <v>7.828054197763313</v>
       </c>
       <c r="D135" t="n">
-        <v>7.39723643485523</v>
+        <v>7.397235979999946</v>
       </c>
       <c r="E135" t="n">
-        <v>7.39723643485523</v>
+        <v>7.397235979999946</v>
       </c>
       <c r="F135" t="n">
         <v>2073000</v>
@@ -3132,16 +3132,16 @@
         <v>43977</v>
       </c>
       <c r="B136" t="n">
-        <v>7.626394748687744</v>
+        <v>7.626394271850586</v>
       </c>
       <c r="C136" t="n">
-        <v>8.286371486299668</v>
+        <v>8.286370968197739</v>
       </c>
       <c r="D136" t="n">
-        <v>7.608062522899527</v>
+        <v>7.608062047208583</v>
       </c>
       <c r="E136" t="n">
-        <v>7.974715780367084</v>
+        <v>7.974715281751298</v>
       </c>
       <c r="F136" t="n">
         <v>2630000</v>
@@ -3152,16 +3152,16 @@
         <v>43978</v>
       </c>
       <c r="B137" t="n">
-        <v>8.158041954040527</v>
+        <v>8.158042907714844</v>
       </c>
       <c r="C137" t="n">
-        <v>8.158041954040527</v>
+        <v>8.158042907714844</v>
       </c>
       <c r="D137" t="n">
-        <v>7.653893971686885</v>
+        <v>7.653894866426351</v>
       </c>
       <c r="E137" t="n">
-        <v>7.745556843855605</v>
+        <v>7.745557749310453</v>
       </c>
       <c r="F137" t="n">
         <v>2323900</v>
@@ -3212,16 +3212,16 @@
         <v>43983</v>
       </c>
       <c r="B140" t="n">
-        <v>8.955514907836914</v>
+        <v>8.955513954162598</v>
       </c>
       <c r="C140" t="n">
-        <v>9.065510886722372</v>
+        <v>9.065509921334565</v>
       </c>
       <c r="D140" t="n">
-        <v>8.561361994536275</v>
+        <v>8.56136108283537</v>
       </c>
       <c r="E140" t="n">
-        <v>8.662191423305361</v>
+        <v>8.662190500867112</v>
       </c>
       <c r="F140" t="n">
         <v>3007600</v>
@@ -3332,16 +3332,16 @@
         <v>43991</v>
       </c>
       <c r="B146" t="n">
-        <v>11.93457412719727</v>
+        <v>11.93457508087158</v>
       </c>
       <c r="C146" t="n">
-        <v>12.34705921875477</v>
+        <v>12.34706020539017</v>
       </c>
       <c r="D146" t="n">
-        <v>11.05460552392848</v>
+        <v>11.0546064072858</v>
       </c>
       <c r="E146" t="n">
-        <v>11.27459745620312</v>
+        <v>11.27459835713967</v>
       </c>
       <c r="F146" t="n">
         <v>3964300</v>
@@ -3612,16 +3612,16 @@
         <v>44012</v>
       </c>
       <c r="B160" t="n">
-        <v>9.450496673583984</v>
+        <v>9.450497627258301</v>
       </c>
       <c r="C160" t="n">
-        <v>9.633823293879882</v>
+        <v>9.633824266054166</v>
       </c>
       <c r="D160" t="n">
-        <v>9.120507882881091</v>
+        <v>9.120508803255376</v>
       </c>
       <c r="E160" t="n">
-        <v>9.532992997089428</v>
+        <v>9.532993959088664</v>
       </c>
       <c r="F160" t="n">
         <v>4221600</v>
@@ -3732,16 +3732,16 @@
         <v>44020</v>
       </c>
       <c r="B166" t="n">
-        <v>10.19297027587891</v>
+        <v>10.19297122955322</v>
       </c>
       <c r="C166" t="n">
-        <v>10.94460989832417</v>
+        <v>10.94461092232337</v>
       </c>
       <c r="D166" t="n">
-        <v>10.14713839969241</v>
+        <v>10.14713934907861</v>
       </c>
       <c r="E166" t="n">
-        <v>10.7704498178199</v>
+        <v>10.77045082552434</v>
       </c>
       <c r="F166" t="n">
         <v>5151100</v>
@@ -3792,16 +3792,16 @@
         <v>44025</v>
       </c>
       <c r="B169" t="n">
-        <v>10.50462532043457</v>
+        <v>10.50462627410889</v>
       </c>
       <c r="C169" t="n">
-        <v>11.09127137533651</v>
+        <v>11.09127238227016</v>
       </c>
       <c r="D169" t="n">
-        <v>10.32129870145592</v>
+        <v>10.32129963848672</v>
       </c>
       <c r="E169" t="n">
-        <v>10.88961165737486</v>
+        <v>10.8896126460006</v>
       </c>
       <c r="F169" t="n">
         <v>4409000</v>
@@ -3932,16 +3932,16 @@
         <v>44034</v>
       </c>
       <c r="B176" t="n">
-        <v>9.936311721801758</v>
+        <v>9.936312675476074</v>
       </c>
       <c r="C176" t="n">
-        <v>10.00047581575137</v>
+        <v>10.00047677558407</v>
       </c>
       <c r="D176" t="n">
-        <v>9.679654471833102</v>
+        <v>9.67965540087379</v>
       </c>
       <c r="E176" t="n">
-        <v>9.881313302580509</v>
+        <v>9.881314250976148</v>
       </c>
       <c r="F176" t="n">
         <v>2365200</v>
@@ -3952,16 +3952,16 @@
         <v>44035</v>
       </c>
       <c r="B177" t="n">
-        <v>9.771318435668945</v>
+        <v>9.771317481994629</v>
       </c>
       <c r="C177" t="n">
-        <v>10.10130723971515</v>
+        <v>10.10130625383415</v>
       </c>
       <c r="D177" t="n">
-        <v>9.670489008971668</v>
+        <v>9.670488065138237</v>
       </c>
       <c r="E177" t="n">
-        <v>9.982144713161835</v>
+        <v>9.982143738911011</v>
       </c>
       <c r="F177" t="n">
         <v>2784800</v>
@@ -3972,16 +3972,16 @@
         <v>44036</v>
       </c>
       <c r="B178" t="n">
-        <v>9.578824996948242</v>
+        <v>9.578825950622559</v>
       </c>
       <c r="C178" t="n">
-        <v>9.725486295117854</v>
+        <v>9.72548726339387</v>
       </c>
       <c r="D178" t="n">
-        <v>9.193838652167866</v>
+        <v>9.193839567512681</v>
       </c>
       <c r="E178" t="n">
-        <v>9.652155646033048</v>
+        <v>9.652156607008214</v>
       </c>
       <c r="F178" t="n">
         <v>3085100</v>
@@ -4312,16 +4312,16 @@
         <v>44061</v>
       </c>
       <c r="B195" t="n">
-        <v>9.532993316650391</v>
+        <v>9.532992362976074</v>
       </c>
       <c r="C195" t="n">
-        <v>9.73465304282097</v>
+        <v>9.734652068972748</v>
       </c>
       <c r="D195" t="n">
-        <v>9.248837264208962</v>
+        <v>9.248836338961429</v>
       </c>
       <c r="E195" t="n">
-        <v>9.313001364920838</v>
+        <v>9.31300043325437</v>
       </c>
       <c r="F195" t="n">
         <v>3391400</v>
@@ -4352,16 +4352,16 @@
         <v>44063</v>
       </c>
       <c r="B197" t="n">
-        <v>9.853816032409668</v>
+        <v>9.853815078735352</v>
       </c>
       <c r="C197" t="n">
-        <v>9.945479787030456</v>
+        <v>9.945478824484717</v>
       </c>
       <c r="D197" t="n">
-        <v>9.010512636911677</v>
+        <v>9.010511764854147</v>
       </c>
       <c r="E197" t="n">
-        <v>9.074676740644019</v>
+        <v>9.074675862376543</v>
       </c>
       <c r="F197" t="n">
         <v>3999100</v>
@@ -4372,16 +4372,16 @@
         <v>44064</v>
       </c>
       <c r="B198" t="n">
-        <v>10.38546371459961</v>
+        <v>10.38546276092529</v>
       </c>
       <c r="C198" t="n">
-        <v>10.54129157300373</v>
+        <v>10.54129060502008</v>
       </c>
       <c r="D198" t="n">
-        <v>9.65215629990441</v>
+        <v>9.652155413568103</v>
       </c>
       <c r="E198" t="n">
-        <v>9.853816035633919</v>
+        <v>9.85381513077964</v>
       </c>
       <c r="F198" t="n">
         <v>4055100</v>
@@ -4392,16 +4392,16 @@
         <v>44067</v>
       </c>
       <c r="B199" t="n">
-        <v>10.22046852111816</v>
+        <v>10.22046947479248</v>
       </c>
       <c r="C199" t="n">
-        <v>10.7429504838363</v>
+        <v>10.74295148626354</v>
       </c>
       <c r="D199" t="n">
-        <v>10.16547097188696</v>
+        <v>10.16547192042944</v>
       </c>
       <c r="E199" t="n">
-        <v>10.54129076359123</v>
+        <v>10.54129174720154</v>
       </c>
       <c r="F199" t="n">
         <v>2579200</v>
@@ -4472,16 +4472,16 @@
         <v>44071</v>
       </c>
       <c r="B203" t="n">
-        <v>11.07293796539307</v>
+        <v>11.07293891906738</v>
       </c>
       <c r="C203" t="n">
-        <v>11.12793638662728</v>
+        <v>11.12793734503842</v>
       </c>
       <c r="D203" t="n">
-        <v>10.35796373436977</v>
+        <v>10.3579646264658</v>
       </c>
       <c r="E203" t="n">
-        <v>10.51379157466809</v>
+        <v>10.51379248018504</v>
       </c>
       <c r="F203" t="n">
         <v>2710200</v>
@@ -4512,16 +4512,16 @@
         <v>44075</v>
       </c>
       <c r="B205" t="n">
-        <v>11.7237491607666</v>
+        <v>11.72374820709229</v>
       </c>
       <c r="C205" t="n">
-        <v>11.7237491607666</v>
+        <v>11.72374820709229</v>
       </c>
       <c r="D205" t="n">
-        <v>10.96294298891299</v>
+        <v>10.96294209712684</v>
       </c>
       <c r="E205" t="n">
-        <v>11.14626961932886</v>
+        <v>11.14626871262991</v>
       </c>
       <c r="F205" t="n">
         <v>3676800</v>
@@ -4652,16 +4652,16 @@
         <v>44085</v>
       </c>
       <c r="B212" t="n">
-        <v>10.83461284637451</v>
+        <v>10.83461380004883</v>
       </c>
       <c r="C212" t="n">
-        <v>11.54958794602793</v>
+        <v>11.54958896263513</v>
       </c>
       <c r="D212" t="n">
-        <v>10.66961933229085</v>
+        <v>10.66962027144226</v>
       </c>
       <c r="E212" t="n">
-        <v>11.43959110441184</v>
+        <v>11.43959211133699</v>
       </c>
       <c r="F212" t="n">
         <v>2696500</v>
@@ -4692,16 +4692,16 @@
         <v>44089</v>
       </c>
       <c r="B214" t="n">
-        <v>11.8245792388916</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="C214" t="n">
-        <v>12.09956963671544</v>
+        <v>12.09956866086264</v>
       </c>
       <c r="D214" t="n">
-        <v>11.62292037143511</v>
+        <v>11.62291943402496</v>
       </c>
       <c r="E214" t="n">
-        <v>12.01707242995125</v>
+        <v>12.017071460752</v>
       </c>
       <c r="F214" t="n">
         <v>2177400</v>
@@ -4772,16 +4772,16 @@
         <v>44095</v>
       </c>
       <c r="B218" t="n">
-        <v>11.32042980194092</v>
+        <v>11.32043075561523</v>
       </c>
       <c r="C218" t="n">
-        <v>11.73291491079292</v>
+        <v>11.73291589921649</v>
       </c>
       <c r="D218" t="n">
-        <v>11.00877411439977</v>
+        <v>11.00877504181907</v>
       </c>
       <c r="E218" t="n">
-        <v>11.70541613664819</v>
+        <v>11.70541712275516</v>
       </c>
       <c r="F218" t="n">
         <v>2982400</v>
@@ -4872,16 +4872,16 @@
         <v>44102</v>
       </c>
       <c r="B223" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C223" t="n">
-        <v>11.44875814201422</v>
+        <v>11.44875714774106</v>
       </c>
       <c r="D223" t="n">
-        <v>10.8621129572749</v>
+        <v>10.86211201394924</v>
       </c>
       <c r="E223" t="n">
-        <v>11.39376059303005</v>
+        <v>11.39375960353318</v>
       </c>
       <c r="F223" t="n">
         <v>1430300</v>
@@ -4932,16 +4932,16 @@
         <v>44105</v>
       </c>
       <c r="B226" t="n">
-        <v>11.01794052124023</v>
+        <v>11.01794147491455</v>
       </c>
       <c r="C226" t="n">
-        <v>11.18293403814347</v>
+        <v>11.18293500609905</v>
       </c>
       <c r="D226" t="n">
-        <v>10.58712231908736</v>
+        <v>10.58712323547157</v>
       </c>
       <c r="E226" t="n">
-        <v>10.61462109287619</v>
+        <v>10.61462201164059</v>
       </c>
       <c r="F226" t="n">
         <v>1825000</v>
@@ -4992,16 +4992,16 @@
         <v>44110</v>
       </c>
       <c r="B229" t="n">
-        <v>11.03627300262451</v>
+        <v>11.03627395629883</v>
       </c>
       <c r="C229" t="n">
-        <v>11.35709524292028</v>
+        <v>11.35709622431771</v>
       </c>
       <c r="D229" t="n">
-        <v>10.99960767866245</v>
+        <v>10.99960862916841</v>
       </c>
       <c r="E229" t="n">
-        <v>11.35709524292028</v>
+        <v>11.35709622431771</v>
       </c>
       <c r="F229" t="n">
         <v>1315200</v>
@@ -5012,16 +5012,16 @@
         <v>44111</v>
       </c>
       <c r="B230" t="n">
-        <v>10.95377635955811</v>
+        <v>10.95377540588379</v>
       </c>
       <c r="C230" t="n">
-        <v>11.23793329027351</v>
+        <v>11.23793231185949</v>
       </c>
       <c r="D230" t="n">
-        <v>10.81628160628407</v>
+        <v>10.81628066458053</v>
       </c>
       <c r="E230" t="n">
-        <v>11.10043766282916</v>
+        <v>11.10043669638599</v>
       </c>
       <c r="F230" t="n">
         <v>1553900</v>
@@ -5032,16 +5032,16 @@
         <v>44112</v>
       </c>
       <c r="B231" t="n">
-        <v>11.03627300262451</v>
+        <v>11.03627395629883</v>
       </c>
       <c r="C231" t="n">
-        <v>11.09127142565275</v>
+        <v>11.09127238407963</v>
       </c>
       <c r="D231" t="n">
-        <v>10.83461328374802</v>
+        <v>10.83461421999638</v>
       </c>
       <c r="E231" t="n">
-        <v>10.99960767866245</v>
+        <v>10.99960862916841</v>
       </c>
       <c r="F231" t="n">
         <v>1563000</v>
@@ -5112,16 +5112,16 @@
         <v>44119</v>
       </c>
       <c r="B235" t="n">
-        <v>11.57708740234375</v>
+        <v>11.57708835601807</v>
       </c>
       <c r="C235" t="n">
-        <v>11.62291927669263</v>
+        <v>11.62292023414239</v>
       </c>
       <c r="D235" t="n">
-        <v>10.92627723426651</v>
+        <v>10.92627813432967</v>
       </c>
       <c r="E235" t="n">
-        <v>10.99960788355659</v>
+        <v>10.99960878966045</v>
       </c>
       <c r="F235" t="n">
         <v>4442200</v>
@@ -5232,16 +5232,16 @@
         <v>44127</v>
       </c>
       <c r="B241" t="n">
-        <v>11.8245792388916</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="C241" t="n">
-        <v>11.8245792388916</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="D241" t="n">
-        <v>11.31126464551279</v>
+        <v>11.31126373323825</v>
       </c>
       <c r="E241" t="n">
-        <v>11.49459128600522</v>
+        <v>11.49459035894505</v>
       </c>
       <c r="F241" t="n">
         <v>1343300</v>
@@ -5272,16 +5272,16 @@
         <v>44131</v>
       </c>
       <c r="B243" t="n">
-        <v>11.90707492828369</v>
+        <v>11.90707588195801</v>
       </c>
       <c r="C243" t="n">
-        <v>12.45705565384485</v>
+        <v>12.45705665156882</v>
       </c>
       <c r="D243" t="n">
-        <v>11.77874673337762</v>
+        <v>11.77874767677373</v>
       </c>
       <c r="E243" t="n">
-        <v>12.20956406509125</v>
+        <v>12.20956504299285</v>
       </c>
       <c r="F243" t="n">
         <v>2061500</v>
@@ -5352,16 +5352,16 @@
         <v>44138</v>
       </c>
       <c r="B247" t="n">
-        <v>10.8712797164917</v>
+        <v>10.87127876281738</v>
       </c>
       <c r="C247" t="n">
-        <v>11.17376888857272</v>
+        <v>11.17376790836278</v>
       </c>
       <c r="D247" t="n">
-        <v>10.66962085121793</v>
+        <v>10.66961991523398</v>
       </c>
       <c r="E247" t="n">
-        <v>10.99960880053258</v>
+        <v>10.9996078356007</v>
       </c>
       <c r="F247" t="n">
         <v>2487500</v>
@@ -5492,16 +5492,16 @@
         <v>44147</v>
       </c>
       <c r="B254" t="n">
-        <v>11.64125156402588</v>
+        <v>11.6412525177002</v>
       </c>
       <c r="C254" t="n">
-        <v>12.54871900945897</v>
+        <v>12.54872003747481</v>
       </c>
       <c r="D254" t="n">
-        <v>11.62291933869072</v>
+        <v>11.62292029086322</v>
       </c>
       <c r="E254" t="n">
-        <v>12.54871900945897</v>
+        <v>12.54872003747481</v>
       </c>
       <c r="F254" t="n">
         <v>2275500</v>
@@ -5512,16 +5512,16 @@
         <v>44148</v>
       </c>
       <c r="B255" t="n">
-        <v>11.86124324798584</v>
+        <v>11.86124420166016</v>
       </c>
       <c r="C255" t="n">
-        <v>12.0537364176397</v>
+        <v>12.05373738679096</v>
       </c>
       <c r="D255" t="n">
-        <v>11.47625778284841</v>
+        <v>11.47625870556891</v>
       </c>
       <c r="E255" t="n">
-        <v>11.60458597983746</v>
+        <v>11.60458691287587</v>
       </c>
       <c r="F255" t="n">
         <v>1796700</v>
@@ -5572,16 +5572,16 @@
         <v>44153</v>
       </c>
       <c r="B258" t="n">
-        <v>12.64038372039795</v>
+        <v>12.64038276672363</v>
       </c>
       <c r="C258" t="n">
-        <v>12.76871280418928</v>
+        <v>12.76871184083297</v>
       </c>
       <c r="D258" t="n">
-        <v>12.31956144800481</v>
+        <v>12.31956051853545</v>
       </c>
       <c r="E258" t="n">
-        <v>12.57621961558747</v>
+        <v>12.57621866675412</v>
       </c>
       <c r="F258" t="n">
         <v>1757300</v>
@@ -5712,16 +5712,16 @@
         <v>44165</v>
       </c>
       <c r="B265" t="n">
-        <v>12.20956516265869</v>
+        <v>12.20956420898438</v>
       </c>
       <c r="C265" t="n">
-        <v>12.85120969155017</v>
+        <v>12.85120868775777</v>
       </c>
       <c r="D265" t="n">
-        <v>11.97124097605051</v>
+        <v>11.9712400409914</v>
       </c>
       <c r="E265" t="n">
-        <v>12.69538183443885</v>
+        <v>12.69538084281798</v>
       </c>
       <c r="F265" t="n">
         <v>1362800</v>
@@ -5732,16 +5732,16 @@
         <v>44166</v>
       </c>
       <c r="B266" t="n">
-        <v>12.13623332977295</v>
+        <v>12.13623428344727</v>
       </c>
       <c r="C266" t="n">
-        <v>12.38372491672248</v>
+        <v>12.38372588984487</v>
       </c>
       <c r="D266" t="n">
-        <v>12.05373613412311</v>
+        <v>12.05373708131473</v>
       </c>
       <c r="E266" t="n">
-        <v>12.32872649489916</v>
+        <v>12.32872746369974</v>
       </c>
       <c r="F266" t="n">
         <v>1296100</v>
@@ -5752,16 +5752,16 @@
         <v>44167</v>
       </c>
       <c r="B267" t="n">
-        <v>12.38372611999512</v>
+        <v>12.3837251663208</v>
       </c>
       <c r="C267" t="n">
-        <v>12.67704873376632</v>
+        <v>12.67704775750314</v>
       </c>
       <c r="D267" t="n">
-        <v>12.22789826288658</v>
+        <v>12.22789732121261</v>
       </c>
       <c r="E267" t="n">
-        <v>12.25539703938504</v>
+        <v>12.25539609559339</v>
       </c>
       <c r="F267" t="n">
         <v>1547700</v>
@@ -5852,16 +5852,16 @@
         <v>44174</v>
       </c>
       <c r="B272" t="n">
-        <v>12.05373764038086</v>
+        <v>12.05373668670654</v>
       </c>
       <c r="C272" t="n">
-        <v>12.30122925825741</v>
+        <v>12.30122828500191</v>
       </c>
       <c r="D272" t="n">
-        <v>11.87041100167807</v>
+        <v>11.87041006250829</v>
       </c>
       <c r="E272" t="n">
-        <v>12.27373048099458</v>
+        <v>12.27372950991475</v>
       </c>
       <c r="F272" t="n">
         <v>927800</v>
@@ -5892,16 +5892,16 @@
         <v>44176</v>
       </c>
       <c r="B274" t="n">
-        <v>12.05373764038086</v>
+        <v>12.05373668670654</v>
       </c>
       <c r="C274" t="n">
-        <v>12.35622681278306</v>
+        <v>12.35622583517624</v>
       </c>
       <c r="D274" t="n">
-        <v>11.96207475811465</v>
+        <v>11.96207381169257</v>
       </c>
       <c r="E274" t="n">
-        <v>12.15456794729517</v>
+        <v>12.15456698564331</v>
       </c>
       <c r="F274" t="n">
         <v>1470700</v>
@@ -5952,16 +5952,16 @@
         <v>44181</v>
       </c>
       <c r="B277" t="n">
-        <v>12.4753885269165</v>
+        <v>12.47538948059082</v>
       </c>
       <c r="C277" t="n">
-        <v>12.91537330506894</v>
+        <v>12.91537429237765</v>
       </c>
       <c r="D277" t="n">
-        <v>12.38372565067205</v>
+        <v>12.38372659733925</v>
       </c>
       <c r="E277" t="n">
-        <v>12.55788572745573</v>
+        <v>12.5578866874365</v>
       </c>
       <c r="F277" t="n">
         <v>1004500</v>
@@ -5992,16 +5992,16 @@
         <v>44183</v>
       </c>
       <c r="B279" t="n">
-        <v>12.19123268127441</v>
+        <v>12.19123363494873</v>
       </c>
       <c r="C279" t="n">
-        <v>12.51205406483644</v>
+        <v>12.51205504360741</v>
       </c>
       <c r="D279" t="n">
-        <v>12.08123670340998</v>
+        <v>12.08123764847972</v>
       </c>
       <c r="E279" t="n">
-        <v>12.31956088503109</v>
+        <v>12.31956184874404</v>
       </c>
       <c r="F279" t="n">
         <v>677600</v>
@@ -6112,16 +6112,16 @@
         <v>44195</v>
       </c>
       <c r="B285" t="n">
-        <v>11.8154125213623</v>
+        <v>11.81541156768799</v>
       </c>
       <c r="C285" t="n">
-        <v>12.05373669591699</v>
+        <v>12.05373572300648</v>
       </c>
       <c r="D285" t="n">
-        <v>11.77874719649464</v>
+        <v>11.77874624577974</v>
       </c>
       <c r="E285" t="n">
-        <v>11.91624194620582</v>
+        <v>11.91624098439311</v>
       </c>
       <c r="F285" t="n">
         <v>1061200</v>
@@ -6132,16 +6132,16 @@
         <v>44200</v>
       </c>
       <c r="B286" t="n">
-        <v>11.7237491607666</v>
+        <v>11.72374820709229</v>
       </c>
       <c r="C286" t="n">
-        <v>11.8979092411191</v>
+        <v>11.89790827327764</v>
       </c>
       <c r="D286" t="n">
-        <v>11.42126000203783</v>
+        <v>11.42125907296965</v>
       </c>
       <c r="E286" t="n">
-        <v>11.8979092411191</v>
+        <v>11.89790827327764</v>
       </c>
       <c r="F286" t="n">
         <v>1030900</v>
@@ -6152,16 +6152,16 @@
         <v>44201</v>
       </c>
       <c r="B287" t="n">
-        <v>11.26543235778809</v>
+        <v>11.26543140411377</v>
       </c>
       <c r="C287" t="n">
-        <v>11.73291592969678</v>
+        <v>11.73291493644768</v>
       </c>
       <c r="D287" t="n">
-        <v>11.16460292772106</v>
+        <v>11.16460198258245</v>
       </c>
       <c r="E287" t="n">
-        <v>11.73291592969678</v>
+        <v>11.73291493644768</v>
       </c>
       <c r="F287" t="n">
         <v>2157200</v>
@@ -6172,16 +6172,16 @@
         <v>44202</v>
       </c>
       <c r="B288" t="n">
-        <v>11.07293796539307</v>
+        <v>11.07293891906738</v>
       </c>
       <c r="C288" t="n">
-        <v>11.36626054752155</v>
+        <v>11.36626152645873</v>
       </c>
       <c r="D288" t="n">
-        <v>10.91711012509475</v>
+        <v>10.91711106534815</v>
       </c>
       <c r="E288" t="n">
-        <v>11.2837642269256</v>
+        <v>11.28376519875766</v>
       </c>
       <c r="F288" t="n">
         <v>1263500</v>
@@ -6232,16 +6232,16 @@
         <v>44207</v>
       </c>
       <c r="B291" t="n">
-        <v>10.95377635955811</v>
+        <v>10.95377540588379</v>
       </c>
       <c r="C291" t="n">
-        <v>11.13710298864692</v>
+        <v>11.13710201901154</v>
       </c>
       <c r="D291" t="n">
-        <v>10.83461383210779</v>
+        <v>10.83461288880819</v>
       </c>
       <c r="E291" t="n">
-        <v>11.04544011118768</v>
+        <v>11.04543914953279</v>
       </c>
       <c r="F291" t="n">
         <v>926700</v>
@@ -6272,16 +6272,16 @@
         <v>44209</v>
       </c>
       <c r="B293" t="n">
-        <v>10.90794467926025</v>
+        <v>10.90794372558594</v>
       </c>
       <c r="C293" t="n">
-        <v>10.98127533221018</v>
+        <v>10.98127437212461</v>
       </c>
       <c r="D293" t="n">
-        <v>10.67878617024915</v>
+        <v>10.67878523661001</v>
       </c>
       <c r="E293" t="n">
-        <v>10.87127935278529</v>
+        <v>10.8712784023166</v>
       </c>
       <c r="F293" t="n">
         <v>2157000</v>
@@ -6332,16 +6332,16 @@
         <v>44214</v>
       </c>
       <c r="B296" t="n">
-        <v>11.29293060302734</v>
+        <v>11.29293155670166</v>
       </c>
       <c r="C296" t="n">
-        <v>11.44875845299908</v>
+        <v>11.44875941983287</v>
       </c>
       <c r="D296" t="n">
-        <v>11.04543987753537</v>
+        <v>11.0454408103094</v>
       </c>
       <c r="E296" t="n">
-        <v>11.40292657815381</v>
+        <v>11.40292754111715</v>
       </c>
       <c r="F296" t="n">
         <v>2481600</v>
@@ -6412,16 +6412,16 @@
         <v>44218</v>
       </c>
       <c r="B300" t="n">
-        <v>11.00877571105957</v>
+        <v>11.00877475738525</v>
       </c>
       <c r="C300" t="n">
-        <v>11.19210235556369</v>
+        <v>11.19210138600805</v>
       </c>
       <c r="D300" t="n">
-        <v>10.82544906655545</v>
+        <v>10.82544812876246</v>
       </c>
       <c r="E300" t="n">
-        <v>11.09127291962902</v>
+        <v>11.09127195880809</v>
       </c>
       <c r="F300" t="n">
         <v>3052400</v>
@@ -6612,16 +6612,16 @@
         <v>44235</v>
       </c>
       <c r="B310" t="n">
-        <v>11.01794052124023</v>
+        <v>11.01794147491455</v>
       </c>
       <c r="C310" t="n">
-        <v>11.33876187989727</v>
+        <v>11.33876286134076</v>
       </c>
       <c r="D310" t="n">
-        <v>10.91711022706409</v>
+        <v>10.91711117201089</v>
       </c>
       <c r="E310" t="n">
-        <v>11.27459778299992</v>
+        <v>11.27459875888959</v>
       </c>
       <c r="F310" t="n">
         <v>1845700</v>
@@ -6792,16 +6792,16 @@
         <v>44250</v>
       </c>
       <c r="B319" t="n">
-        <v>10.90794467926025</v>
+        <v>10.90794372558594</v>
       </c>
       <c r="C319" t="n">
-        <v>10.99960843253283</v>
+        <v>10.99960747084441</v>
       </c>
       <c r="D319" t="n">
-        <v>10.55045796467195</v>
+        <v>10.55045704225246</v>
       </c>
       <c r="E319" t="n">
-        <v>10.67878617024915</v>
+        <v>10.67878523661001</v>
       </c>
       <c r="F319" t="n">
         <v>1964300</v>
@@ -6852,16 +6852,16 @@
         <v>44253</v>
       </c>
       <c r="B322" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C322" t="n">
-        <v>10.651287786344</v>
+        <v>10.65128678074554</v>
       </c>
       <c r="D322" t="n">
-        <v>9.945480007155426</v>
+        <v>9.945479068192968</v>
       </c>
       <c r="E322" t="n">
-        <v>10.6054559080192</v>
+        <v>10.60545490674777</v>
       </c>
       <c r="F322" t="n">
         <v>2794300</v>
@@ -6912,16 +6912,16 @@
         <v>44258</v>
       </c>
       <c r="B325" t="n">
-        <v>9.752986907958984</v>
+        <v>9.752985954284668</v>
       </c>
       <c r="C325" t="n">
-        <v>9.817151013706422</v>
+        <v>9.81715005375796</v>
       </c>
       <c r="D325" t="n">
-        <v>9.184673884304942</v>
+        <v>9.184672986201862</v>
       </c>
       <c r="E325" t="n">
-        <v>9.578825943543972</v>
+        <v>9.578825006899601</v>
       </c>
       <c r="F325" t="n">
         <v>2305100</v>
@@ -7032,16 +7032,16 @@
         <v>44266</v>
       </c>
       <c r="B331" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C331" t="n">
-        <v>10.24796918026058</v>
+        <v>10.24796821273983</v>
       </c>
       <c r="D331" t="n">
-        <v>9.32216855994705</v>
+        <v>9.322167679832035</v>
       </c>
       <c r="E331" t="n">
-        <v>9.404665766097615</v>
+        <v>9.404664878193957</v>
       </c>
       <c r="F331" t="n">
         <v>2921600</v>
@@ -7092,16 +7092,16 @@
         <v>44271</v>
       </c>
       <c r="B334" t="n">
-        <v>9.771318435668945</v>
+        <v>9.771317481994629</v>
       </c>
       <c r="C334" t="n">
-        <v>10.3487979685795</v>
+        <v>10.34879695854355</v>
       </c>
       <c r="D334" t="n">
-        <v>9.734653110127178</v>
+        <v>9.734652160031374</v>
       </c>
       <c r="E334" t="n">
-        <v>10.31213264303773</v>
+        <v>10.3121316365803</v>
       </c>
       <c r="F334" t="n">
         <v>1474300</v>
@@ -7152,16 +7152,16 @@
         <v>44274</v>
       </c>
       <c r="B337" t="n">
-        <v>9.972977638244629</v>
+        <v>9.972978591918945</v>
       </c>
       <c r="C337" t="n">
-        <v>10.10130670797058</v>
+        <v>10.10130767391647</v>
       </c>
       <c r="D337" t="n">
-        <v>9.679655049351345</v>
+        <v>9.679655974976443</v>
       </c>
       <c r="E337" t="n">
-        <v>9.826316343797988</v>
+        <v>9.826317283447693</v>
       </c>
       <c r="F337" t="n">
         <v>1607200</v>
@@ -7212,16 +7212,16 @@
         <v>44279</v>
       </c>
       <c r="B340" t="n">
-        <v>10.38546371459961</v>
+        <v>10.38546276092529</v>
       </c>
       <c r="C340" t="n">
-        <v>10.60545567675706</v>
+        <v>10.60545470288137</v>
       </c>
       <c r="D340" t="n">
-        <v>10.21130362976755</v>
+        <v>10.21130269208597</v>
       </c>
       <c r="E340" t="n">
-        <v>10.56879034973082</v>
+        <v>10.56878937922202</v>
       </c>
       <c r="F340" t="n">
         <v>3104200</v>
@@ -7272,16 +7272,16 @@
         <v>44284</v>
       </c>
       <c r="B343" t="n">
-        <v>9.853816032409668</v>
+        <v>9.853815078735352</v>
       </c>
       <c r="C343" t="n">
-        <v>10.06464144419899</v>
+        <v>10.06464047012052</v>
       </c>
       <c r="D343" t="n">
-        <v>9.734653501070783</v>
+        <v>9.734652558929284</v>
       </c>
       <c r="E343" t="n">
-        <v>10.04630921777704</v>
+        <v>10.04630824547281</v>
       </c>
       <c r="F343" t="n">
         <v>1233600</v>
@@ -7452,16 +7452,16 @@
         <v>44298</v>
       </c>
       <c r="B352" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C352" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="D352" t="n">
-        <v>10.69711856198182</v>
+        <v>10.69711763298518</v>
       </c>
       <c r="E352" t="n">
-        <v>10.87127863265874</v>
+        <v>10.87127768853708</v>
       </c>
       <c r="F352" t="n">
         <v>1341200</v>
@@ -7532,16 +7532,16 @@
         <v>44302</v>
       </c>
       <c r="B356" t="n">
-        <v>12.53955364227295</v>
+        <v>12.53955268859863</v>
       </c>
       <c r="C356" t="n">
-        <v>13.63951428871419</v>
+        <v>13.63951325138424</v>
       </c>
       <c r="D356" t="n">
-        <v>11.47625832157408</v>
+        <v>11.47625744876687</v>
       </c>
       <c r="E356" t="n">
-        <v>11.61375307456536</v>
+        <v>11.61375219130122</v>
       </c>
       <c r="F356" t="n">
         <v>14691000</v>
@@ -7592,16 +7592,16 @@
         <v>44308</v>
       </c>
       <c r="B359" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C359" t="n">
-        <v>11.41209281796801</v>
+        <v>11.41209182687907</v>
       </c>
       <c r="D359" t="n">
-        <v>10.91711050625907</v>
+        <v>10.91710955815712</v>
       </c>
       <c r="E359" t="n">
-        <v>11.26543152178318</v>
+        <v>11.26543054343111</v>
       </c>
       <c r="F359" t="n">
         <v>4817400</v>
@@ -7612,16 +7612,16 @@
         <v>44309</v>
       </c>
       <c r="B360" t="n">
-        <v>11.02710628509521</v>
+        <v>11.02710723876953</v>
       </c>
       <c r="C360" t="n">
-        <v>11.18293412810254</v>
+        <v>11.18293509525356</v>
       </c>
       <c r="D360" t="n">
-        <v>10.70628492385739</v>
+        <v>10.70628584978561</v>
       </c>
       <c r="E360" t="n">
-        <v>11.14626880469907</v>
+        <v>11.1462697686791</v>
       </c>
       <c r="F360" t="n">
         <v>3824500</v>
@@ -7672,16 +7672,16 @@
         <v>44314</v>
       </c>
       <c r="B363" t="n">
-        <v>11.20126819610596</v>
+        <v>11.20126724243164</v>
       </c>
       <c r="C363" t="n">
-        <v>11.30209762564745</v>
+        <v>11.30209666338853</v>
       </c>
       <c r="D363" t="n">
-        <v>10.92627780970057</v>
+        <v>10.9262768794389</v>
       </c>
       <c r="E363" t="n">
-        <v>11.18293509573277</v>
+        <v>11.18293414361933</v>
       </c>
       <c r="F363" t="n">
         <v>1629600</v>
@@ -7692,16 +7692,16 @@
         <v>44315</v>
       </c>
       <c r="B364" t="n">
-        <v>11.4212589263916</v>
+        <v>11.42125988006592</v>
       </c>
       <c r="C364" t="n">
-        <v>11.59541899034182</v>
+        <v>11.59541995855849</v>
       </c>
       <c r="D364" t="n">
-        <v>11.08210447352099</v>
+        <v>11.08210539887593</v>
       </c>
       <c r="E364" t="n">
-        <v>11.21959921484115</v>
+        <v>11.2196001516769</v>
       </c>
       <c r="F364" t="n">
         <v>1614300</v>
@@ -7892,16 +7892,16 @@
         <v>44329</v>
       </c>
       <c r="B374" t="n">
-        <v>11.16460132598877</v>
+        <v>11.16460227966309</v>
       </c>
       <c r="C374" t="n">
-        <v>11.43042512545659</v>
+        <v>11.43042610183743</v>
       </c>
       <c r="D374" t="n">
-        <v>11.10043635772397</v>
+        <v>11.10043730591735</v>
       </c>
       <c r="E374" t="n">
-        <v>11.13710167923091</v>
+        <v>11.13710263055622</v>
       </c>
       <c r="F374" t="n">
         <v>1639700</v>
@@ -7952,16 +7952,16 @@
         <v>44334</v>
       </c>
       <c r="B377" t="n">
-        <v>12.26456260681152</v>
+        <v>12.26456356048584</v>
       </c>
       <c r="C377" t="n">
-        <v>12.5945505208612</v>
+        <v>12.59455150019489</v>
       </c>
       <c r="D377" t="n">
-        <v>12.18206540975654</v>
+        <v>12.18206635701599</v>
       </c>
       <c r="E377" t="n">
-        <v>12.35622547918463</v>
+        <v>12.35622643998652</v>
       </c>
       <c r="F377" t="n">
         <v>1445400</v>
@@ -7992,16 +7992,16 @@
         <v>44336</v>
       </c>
       <c r="B379" t="n">
-        <v>12.5945520401001</v>
+        <v>12.59455108642578</v>
       </c>
       <c r="C379" t="n">
-        <v>12.5945520401001</v>
+        <v>12.59455108642578</v>
       </c>
       <c r="D379" t="n">
-        <v>11.86124460180745</v>
+        <v>11.86124370366004</v>
       </c>
       <c r="E379" t="n">
-        <v>12.05373779343214</v>
+        <v>12.05373688070891</v>
       </c>
       <c r="F379" t="n">
         <v>2196400</v>
@@ -8012,16 +8012,16 @@
         <v>44337</v>
       </c>
       <c r="B380" t="n">
-        <v>12.5945520401001</v>
+        <v>12.59455108642578</v>
       </c>
       <c r="C380" t="n">
-        <v>12.79621178231891</v>
+        <v>12.79621081337468</v>
       </c>
       <c r="D380" t="n">
-        <v>12.42955850025778</v>
+        <v>12.42955755907697</v>
       </c>
       <c r="E380" t="n">
-        <v>12.53038793428199</v>
+        <v>12.53038698546626</v>
       </c>
       <c r="F380" t="n">
         <v>1466000</v>
@@ -8052,16 +8052,16 @@
         <v>44341</v>
       </c>
       <c r="B382" t="n">
-        <v>12.53955364227295</v>
+        <v>12.53955268859863</v>
       </c>
       <c r="C382" t="n">
-        <v>12.75037904674896</v>
+        <v>12.75037807704068</v>
       </c>
       <c r="D382" t="n">
-        <v>12.40205801511135</v>
+        <v>12.40205707189402</v>
       </c>
       <c r="E382" t="n">
-        <v>12.62205084373585</v>
+        <v>12.62204988378735</v>
       </c>
       <c r="F382" t="n">
         <v>1256400</v>
@@ -8252,16 +8252,16 @@
         <v>44356</v>
       </c>
       <c r="B392" t="n">
-        <v>13.5386848449707</v>
+        <v>13.53868389129639</v>
       </c>
       <c r="C392" t="n">
-        <v>13.84117400051925</v>
+        <v>13.84117302553739</v>
       </c>
       <c r="D392" t="n">
-        <v>13.38285699221293</v>
+        <v>13.38285604951523</v>
       </c>
       <c r="E392" t="n">
-        <v>13.78617557488755</v>
+        <v>13.78617460377982</v>
       </c>
       <c r="F392" t="n">
         <v>1247900</v>
@@ -8272,16 +8272,16 @@
         <v>44357</v>
       </c>
       <c r="B393" t="n">
-        <v>13.62118053436279</v>
+        <v>13.62118148803711</v>
       </c>
       <c r="C393" t="n">
-        <v>13.77700837982407</v>
+        <v>13.77700934440852</v>
       </c>
       <c r="D393" t="n">
-        <v>13.32785794251582</v>
+        <v>13.32785887565343</v>
       </c>
       <c r="E393" t="n">
-        <v>13.56618298547662</v>
+        <v>13.56618393530034</v>
       </c>
       <c r="F393" t="n">
         <v>1127800</v>
@@ -8312,16 +8312,16 @@
         <v>44361</v>
       </c>
       <c r="B395" t="n">
-        <v>13.50201892852783</v>
+        <v>13.50201797485352</v>
       </c>
       <c r="C395" t="n">
-        <v>13.65784678455664</v>
+        <v>13.6578458198759</v>
       </c>
       <c r="D395" t="n">
-        <v>13.30036007004259</v>
+        <v>13.30035913061184</v>
       </c>
       <c r="E395" t="n">
-        <v>13.3186922961911</v>
+        <v>13.3186913554655</v>
       </c>
       <c r="F395" t="n">
         <v>1118700</v>
@@ -8392,16 +8392,16 @@
         <v>44365</v>
       </c>
       <c r="B399" t="n">
-        <v>13.74034404754639</v>
+        <v>13.74034309387207</v>
       </c>
       <c r="C399" t="n">
-        <v>13.75867714794514</v>
+        <v>13.75867619299839</v>
       </c>
       <c r="D399" t="n">
-        <v>13.34619200484684</v>
+        <v>13.34619107852938</v>
       </c>
       <c r="E399" t="n">
-        <v>13.40118955770243</v>
+        <v>13.40118862756777</v>
       </c>
       <c r="F399" t="n">
         <v>1818300</v>
@@ -8412,16 +8412,16 @@
         <v>44368</v>
       </c>
       <c r="B400" t="n">
-        <v>14.03366661071777</v>
+        <v>14.03366756439209</v>
       </c>
       <c r="C400" t="n">
-        <v>14.28115733061313</v>
+        <v>14.28115830110597</v>
       </c>
       <c r="D400" t="n">
-        <v>13.86867221467401</v>
+        <v>13.86867315713594</v>
       </c>
       <c r="E400" t="n">
-        <v>13.99700128650475</v>
+        <v>13.99700223768743</v>
       </c>
       <c r="F400" t="n">
         <v>2278000</v>
@@ -8432,16 +8432,16 @@
         <v>44369</v>
       </c>
       <c r="B401" t="n">
-        <v>13.5386848449707</v>
+        <v>13.53868389129639</v>
       </c>
       <c r="C401" t="n">
-        <v>13.98783530331003</v>
+        <v>13.98783431799724</v>
       </c>
       <c r="D401" t="n">
-        <v>13.41952231791062</v>
+        <v>13.41952137263019</v>
       </c>
       <c r="E401" t="n">
-        <v>13.95116997761234</v>
+        <v>13.95116899488228</v>
       </c>
       <c r="F401" t="n">
         <v>2062700</v>
@@ -8492,16 +8492,16 @@
         <v>44372</v>
       </c>
       <c r="B404" t="n">
-        <v>13.4378547668457</v>
+        <v>13.43785381317139</v>
       </c>
       <c r="C404" t="n">
-        <v>13.56618384600404</v>
+        <v>13.5661828832223</v>
       </c>
       <c r="D404" t="n">
-        <v>12.83287644570132</v>
+        <v>12.83287553496186</v>
       </c>
       <c r="E404" t="n">
-        <v>13.53868506981665</v>
+        <v>13.53868410898649</v>
       </c>
       <c r="F404" t="n">
         <v>1465200</v>
@@ -8532,16 +8532,16 @@
         <v>44376</v>
       </c>
       <c r="B406" t="n">
-        <v>13.15369892120361</v>
+        <v>13.1536979675293</v>
       </c>
       <c r="C406" t="n">
-        <v>13.30036022882386</v>
+        <v>13.30035926451625</v>
       </c>
       <c r="D406" t="n">
-        <v>12.89704075869783</v>
+        <v>12.89703982363184</v>
       </c>
       <c r="E406" t="n">
-        <v>13.2636949019188</v>
+        <v>13.26369394026951</v>
       </c>
       <c r="F406" t="n">
         <v>967400</v>
@@ -8672,16 +8672,16 @@
         <v>44385</v>
       </c>
       <c r="B413" t="n">
-        <v>12.45705604553223</v>
+        <v>12.45705699920654</v>
       </c>
       <c r="C413" t="n">
-        <v>12.57621856895631</v>
+        <v>12.57621953175335</v>
       </c>
       <c r="D413" t="n">
-        <v>12.17289912441782</v>
+        <v>12.17290005633794</v>
       </c>
       <c r="E413" t="n">
-        <v>12.31956042273353</v>
+        <v>12.3195613658816</v>
       </c>
       <c r="F413" t="n">
         <v>1082500</v>
@@ -8812,16 +8812,16 @@
         <v>44397</v>
       </c>
       <c r="B420" t="n">
-        <v>11.48542404174805</v>
+        <v>11.48542308807373</v>
       </c>
       <c r="C420" t="n">
-        <v>11.68708377119518</v>
+        <v>11.68708280077636</v>
       </c>
       <c r="D420" t="n">
-        <v>11.37542806409606</v>
+        <v>11.37542711955509</v>
       </c>
       <c r="E420" t="n">
-        <v>11.5770877935432</v>
+        <v>11.57708683225772</v>
       </c>
       <c r="F420" t="n">
         <v>1744400</v>
@@ -8832,16 +8832,16 @@
         <v>44398</v>
       </c>
       <c r="B421" t="n">
-        <v>11.48542404174805</v>
+        <v>11.48542308807373</v>
       </c>
       <c r="C421" t="n">
-        <v>11.66875067116803</v>
+        <v>11.66874970227147</v>
       </c>
       <c r="D421" t="n">
-        <v>11.22876676056008</v>
+        <v>11.2287658281969</v>
       </c>
       <c r="E421" t="n">
-        <v>11.5404224676592</v>
+        <v>11.54042150941818</v>
       </c>
       <c r="F421" t="n">
         <v>2115800</v>
@@ -8872,16 +8872,16 @@
         <v>44400</v>
       </c>
       <c r="B423" t="n">
-        <v>11.68708324432373</v>
+        <v>11.68708419799805</v>
       </c>
       <c r="C423" t="n">
-        <v>11.71458201895446</v>
+        <v>11.7145829748727</v>
       </c>
       <c r="D423" t="n">
-        <v>11.43959165013631</v>
+        <v>11.43959258361514</v>
       </c>
       <c r="E423" t="n">
-        <v>11.62291914546194</v>
+        <v>11.62292009390042</v>
       </c>
       <c r="F423" t="n">
         <v>1513600</v>
@@ -8912,16 +8912,16 @@
         <v>44404</v>
       </c>
       <c r="B425" t="n">
-        <v>11.4395923614502</v>
+        <v>11.43959140777588</v>
       </c>
       <c r="C425" t="n">
-        <v>11.61375331800481</v>
+        <v>11.61375234981137</v>
       </c>
       <c r="D425" t="n">
-        <v>11.19210162604409</v>
+        <v>11.19210069300211</v>
       </c>
       <c r="E425" t="n">
-        <v>11.3937613589393</v>
+        <v>11.39376040908574</v>
       </c>
       <c r="F425" t="n">
         <v>1727000</v>
@@ -8952,16 +8952,16 @@
         <v>44406</v>
       </c>
       <c r="B427" t="n">
-        <v>11.25626564025879</v>
+        <v>11.25626468658447</v>
       </c>
       <c r="C427" t="n">
-        <v>11.36626161892538</v>
+        <v>11.36626065593178</v>
       </c>
       <c r="D427" t="n">
-        <v>11.15543621169033</v>
+        <v>11.15543526655867</v>
       </c>
       <c r="E427" t="n">
-        <v>11.36626161892538</v>
+        <v>11.36626065593178</v>
       </c>
       <c r="F427" t="n">
         <v>743300</v>
@@ -8992,16 +8992,16 @@
         <v>44410</v>
       </c>
       <c r="B429" t="n">
-        <v>10.90794467926025</v>
+        <v>10.90794372558594</v>
       </c>
       <c r="C429" t="n">
-        <v>11.20126816523029</v>
+        <v>11.2012671859109</v>
       </c>
       <c r="D429" t="n">
-        <v>10.8621136767943</v>
+        <v>10.86211272712696</v>
       </c>
       <c r="E429" t="n">
-        <v>10.96294310605787</v>
+        <v>10.96294214757507</v>
       </c>
       <c r="F429" t="n">
         <v>1959100</v>
@@ -9132,16 +9132,16 @@
         <v>44419</v>
       </c>
       <c r="B436" t="n">
-        <v>9.890480995178223</v>
+        <v>9.890481948852539</v>
       </c>
       <c r="C436" t="n">
-        <v>10.51379240563549</v>
+        <v>10.51379341941164</v>
       </c>
       <c r="D436" t="n">
-        <v>9.74381969252247</v>
+        <v>9.743820632055199</v>
       </c>
       <c r="E436" t="n">
-        <v>10.51379240563549</v>
+        <v>10.51379341941164</v>
       </c>
       <c r="F436" t="n">
         <v>4618100</v>
@@ -9172,16 +9172,16 @@
         <v>44421</v>
       </c>
       <c r="B438" t="n">
-        <v>9.817150115966797</v>
+        <v>9.81714916229248</v>
       </c>
       <c r="C438" t="n">
-        <v>10.00964328977675</v>
+        <v>10.00964231740293</v>
       </c>
       <c r="D438" t="n">
-        <v>9.688821042036732</v>
+        <v>9.688820100828776</v>
       </c>
       <c r="E438" t="n">
-        <v>9.90881386508403</v>
+        <v>9.908812902505156</v>
       </c>
       <c r="F438" t="n">
         <v>1360000</v>
@@ -9212,16 +9212,16 @@
         <v>44425</v>
       </c>
       <c r="B440" t="n">
-        <v>8.323037147521973</v>
+        <v>8.323036193847656</v>
       </c>
       <c r="C440" t="n">
-        <v>9.29466963022994</v>
+        <v>9.294668565223555</v>
       </c>
       <c r="D440" t="n">
-        <v>8.30470492099484</v>
+        <v>8.304703969421075</v>
       </c>
       <c r="E440" t="n">
-        <v>9.285503079881195</v>
+        <v>9.285502015925136</v>
       </c>
       <c r="F440" t="n">
         <v>6613600</v>
@@ -9272,16 +9272,16 @@
         <v>44428</v>
       </c>
       <c r="B443" t="n">
-        <v>8.625526428222656</v>
+        <v>8.62552547454834</v>
       </c>
       <c r="C443" t="n">
-        <v>8.689690533160434</v>
+        <v>8.689689572391865</v>
       </c>
       <c r="D443" t="n">
-        <v>8.414701012472607</v>
+        <v>8.414700082108032</v>
       </c>
       <c r="E443" t="n">
-        <v>8.515530445113452</v>
+        <v>8.515529503600753</v>
       </c>
       <c r="F443" t="n">
         <v>1662000</v>
@@ -9332,16 +9332,16 @@
         <v>44433</v>
       </c>
       <c r="B446" t="n">
-        <v>8.955514907836914</v>
+        <v>8.955513954162598</v>
       </c>
       <c r="C446" t="n">
-        <v>9.322168170788439</v>
+        <v>9.322167178069154</v>
       </c>
       <c r="D446" t="n">
-        <v>8.744688626012037</v>
+        <v>8.744687694788647</v>
       </c>
       <c r="E446" t="n">
-        <v>9.175506865607829</v>
+        <v>9.175505888506532</v>
       </c>
       <c r="F446" t="n">
         <v>3539500</v>
@@ -9352,16 +9352,16 @@
         <v>44434</v>
       </c>
       <c r="B447" t="n">
-        <v>8.488030433654785</v>
+        <v>8.488031387329102</v>
       </c>
       <c r="C447" t="n">
-        <v>9.093008689872168</v>
+        <v>9.093009711518935</v>
       </c>
       <c r="D447" t="n">
-        <v>8.451365111283133</v>
+        <v>8.451366060837909</v>
       </c>
       <c r="E447" t="n">
-        <v>8.928014302114612</v>
+        <v>8.928015305223402</v>
       </c>
       <c r="F447" t="n">
         <v>2819100</v>
@@ -9412,16 +9412,16 @@
         <v>44439</v>
       </c>
       <c r="B450" t="n">
-        <v>8.148876190185547</v>
+        <v>8.148877143859863</v>
       </c>
       <c r="C450" t="n">
-        <v>8.478864099913311</v>
+        <v>8.478865092206572</v>
       </c>
       <c r="D450" t="n">
-        <v>8.075545543579377</v>
+        <v>8.075546488671705</v>
       </c>
       <c r="E450" t="n">
-        <v>8.35970158063572</v>
+        <v>8.359702558983225</v>
       </c>
       <c r="F450" t="n">
         <v>2719700</v>
@@ -9472,16 +9472,16 @@
         <v>44442</v>
       </c>
       <c r="B453" t="n">
-        <v>8.020546913146973</v>
+        <v>8.020547866821289</v>
       </c>
       <c r="C453" t="n">
-        <v>8.048045686367239</v>
+        <v>8.048046643311267</v>
       </c>
       <c r="D453" t="n">
-        <v>7.818887203134468</v>
+        <v>7.818888132830658</v>
       </c>
       <c r="E453" t="n">
-        <v>7.965548492536203</v>
+        <v>7.965549439670992</v>
       </c>
       <c r="F453" t="n">
         <v>2243900</v>
@@ -9532,16 +9532,16 @@
         <v>44448</v>
       </c>
       <c r="B456" t="n">
-        <v>7.956383228302002</v>
+        <v>7.95638370513916</v>
       </c>
       <c r="C456" t="n">
-        <v>8.075545750634898</v>
+        <v>8.075546234613633</v>
       </c>
       <c r="D456" t="n">
-        <v>7.626394435943123</v>
+        <v>7.626394893003591</v>
       </c>
       <c r="E456" t="n">
-        <v>7.883052579815647</v>
+        <v>7.883053052257997</v>
       </c>
       <c r="F456" t="n">
         <v>3062500</v>
@@ -9672,16 +9672,16 @@
         <v>44459</v>
       </c>
       <c r="B463" t="n">
-        <v>7.333072185516357</v>
+        <v>7.333071708679199</v>
       </c>
       <c r="C463" t="n">
-        <v>7.415569387470669</v>
+        <v>7.415568905269083</v>
       </c>
       <c r="D463" t="n">
-        <v>7.14057900567974</v>
+        <v>7.140578541359559</v>
       </c>
       <c r="E463" t="n">
-        <v>7.213909657601278</v>
+        <v>7.21390918851273</v>
       </c>
       <c r="F463" t="n">
         <v>2478700</v>
@@ -9692,16 +9692,16 @@
         <v>44460</v>
       </c>
       <c r="B464" t="n">
-        <v>7.562231063842773</v>
+        <v>7.562230587005615</v>
       </c>
       <c r="C464" t="n">
-        <v>7.63556171937671</v>
+        <v>7.635561237915681</v>
       </c>
       <c r="D464" t="n">
-        <v>7.21391001297139</v>
+        <v>7.213909558097646</v>
       </c>
       <c r="E464" t="n">
-        <v>7.488900408308837</v>
+        <v>7.488899936095549</v>
       </c>
       <c r="F464" t="n">
         <v>2716900</v>
@@ -9712,16 +9712,16 @@
         <v>44461</v>
       </c>
       <c r="B465" t="n">
-        <v>7.653893947601318</v>
+        <v>7.653894424438477</v>
       </c>
       <c r="C465" t="n">
-        <v>7.773055593628645</v>
+        <v>7.773056077889568</v>
       </c>
       <c r="D465" t="n">
-        <v>7.443067681353181</v>
+        <v>7.443068145055875</v>
       </c>
       <c r="E465" t="n">
-        <v>7.708891495895427</v>
+        <v>7.708891976158931</v>
       </c>
       <c r="F465" t="n">
         <v>2341500</v>
@@ -9732,16 +9732,16 @@
         <v>44462</v>
       </c>
       <c r="B466" t="n">
-        <v>7.635561466217041</v>
+        <v>7.635560989379883</v>
       </c>
       <c r="C466" t="n">
-        <v>7.809722422963551</v>
+        <v>7.809721935250124</v>
       </c>
       <c r="D466" t="n">
-        <v>7.553064262933993</v>
+        <v>7.553063791248745</v>
       </c>
       <c r="E466" t="n">
-        <v>7.663060242587944</v>
+        <v>7.6630597640335</v>
       </c>
       <c r="F466" t="n">
         <v>1813900</v>
@@ -9852,16 +9852,16 @@
         <v>44470</v>
       </c>
       <c r="B472" t="n">
-        <v>7.05808162689209</v>
+        <v>7.058081150054932</v>
       </c>
       <c r="C472" t="n">
-        <v>7.05808162689209</v>
+        <v>7.058081150054932</v>
       </c>
       <c r="D472" t="n">
-        <v>6.590598514062039</v>
+        <v>6.590598068807588</v>
       </c>
       <c r="E472" t="n">
-        <v>6.627263839104194</v>
+        <v>6.627263391372669</v>
       </c>
       <c r="F472" t="n">
         <v>1964300</v>
@@ -9872,16 +9872,16 @@
         <v>44473</v>
       </c>
       <c r="B473" t="n">
-        <v>6.88392162322998</v>
+        <v>6.883921146392822</v>
       </c>
       <c r="C473" t="n">
-        <v>7.05808170045277</v>
+        <v>7.058081211551849</v>
       </c>
       <c r="D473" t="n">
-        <v>6.792257872584105</v>
+        <v>6.792257402096333</v>
       </c>
       <c r="E473" t="n">
-        <v>6.911420398755618</v>
+        <v>6.911419920013668</v>
       </c>
       <c r="F473" t="n">
         <v>2556200</v>
@@ -9972,16 +9972,16 @@
         <v>44480</v>
       </c>
       <c r="B478" t="n">
-        <v>6.645596504211426</v>
+        <v>6.645596981048584</v>
       </c>
       <c r="C478" t="n">
-        <v>6.792257804437119</v>
+        <v>6.79225829179757</v>
       </c>
       <c r="D478" t="n">
-        <v>6.526433979235474</v>
+        <v>6.526434447522441</v>
       </c>
       <c r="E478" t="n">
-        <v>6.783091691715589</v>
+        <v>6.783092178418349</v>
       </c>
       <c r="F478" t="n">
         <v>1719800</v>
@@ -9992,16 +9992,16 @@
         <v>44482</v>
       </c>
       <c r="B479" t="n">
-        <v>6.810590267181396</v>
+        <v>6.810590744018555</v>
       </c>
       <c r="C479" t="n">
-        <v>6.893087464680927</v>
+        <v>6.89308794729405</v>
       </c>
       <c r="D479" t="n">
-        <v>6.58143177375838</v>
+        <v>6.581432234551219</v>
       </c>
       <c r="E479" t="n">
-        <v>6.645596309267474</v>
+        <v>6.645596774552734</v>
       </c>
       <c r="F479" t="n">
         <v>1797400</v>
@@ -10032,16 +10032,16 @@
         <v>44484</v>
       </c>
       <c r="B481" t="n">
-        <v>6.801424026489258</v>
+        <v>6.801424503326416</v>
       </c>
       <c r="C481" t="n">
-        <v>6.810590138769081</v>
+        <v>6.810590616248861</v>
       </c>
       <c r="D481" t="n">
-        <v>6.581431649666802</v>
+        <v>6.58143211108064</v>
       </c>
       <c r="E481" t="n">
-        <v>6.654762733331041</v>
+        <v>6.654763199886006</v>
       </c>
       <c r="F481" t="n">
         <v>1272200</v>
@@ -10112,16 +10112,16 @@
         <v>44490</v>
       </c>
       <c r="B485" t="n">
-        <v>5.967287063598633</v>
+        <v>5.967287540435791</v>
       </c>
       <c r="C485" t="n">
-        <v>6.29727496201059</v>
+        <v>6.297275465216598</v>
       </c>
       <c r="D485" t="n">
-        <v>5.89395598242197</v>
+        <v>5.89395645339935</v>
       </c>
       <c r="E485" t="n">
-        <v>6.29727496201059</v>
+        <v>6.297275465216598</v>
       </c>
       <c r="F485" t="n">
         <v>2712900</v>
@@ -10172,16 +10172,16 @@
         <v>44495</v>
       </c>
       <c r="B488" t="n">
-        <v>5.600634098052979</v>
+        <v>5.60063362121582</v>
       </c>
       <c r="C488" t="n">
-        <v>5.994786577287869</v>
+        <v>5.994786066892628</v>
       </c>
       <c r="D488" t="n">
-        <v>5.600634098052979</v>
+        <v>5.60063362121582</v>
       </c>
       <c r="E488" t="n">
-        <v>5.930622037237235</v>
+        <v>5.930621532304952</v>
       </c>
       <c r="F488" t="n">
         <v>1746800</v>
@@ -10232,16 +10232,16 @@
         <v>44498</v>
       </c>
       <c r="B491" t="n">
-        <v>5.554802417755127</v>
+        <v>5.554801940917969</v>
       </c>
       <c r="C491" t="n">
-        <v>5.838958927312109</v>
+        <v>5.838958426082296</v>
       </c>
       <c r="D491" t="n">
-        <v>5.545636304329514</v>
+        <v>5.545635828279196</v>
       </c>
       <c r="E491" t="n">
-        <v>5.701463729246425</v>
+        <v>5.701463239819518</v>
       </c>
       <c r="F491" t="n">
         <v>2502600</v>
@@ -10312,16 +10312,16 @@
         <v>44505</v>
       </c>
       <c r="B495" t="n">
-        <v>6.810590267181396</v>
+        <v>6.810590744018555</v>
       </c>
       <c r="C495" t="n">
-        <v>6.948085450652234</v>
+        <v>6.94808593711599</v>
       </c>
       <c r="D495" t="n">
-        <v>6.398105153854022</v>
+        <v>6.398105601811419</v>
       </c>
       <c r="E495" t="n">
-        <v>6.398105153854022</v>
+        <v>6.398105601811419</v>
       </c>
       <c r="F495" t="n">
         <v>3968000</v>
@@ -10372,16 +10372,16 @@
         <v>44510</v>
       </c>
       <c r="B498" t="n">
-        <v>7.177244663238525</v>
+        <v>7.177244186401367</v>
       </c>
       <c r="C498" t="n">
-        <v>7.333072524313823</v>
+        <v>7.333072037123874</v>
       </c>
       <c r="D498" t="n">
-        <v>6.874755491544209</v>
+        <v>6.874755034803632</v>
       </c>
       <c r="E498" t="n">
-        <v>6.874755491544209</v>
+        <v>6.874755034803632</v>
       </c>
       <c r="F498" t="n">
         <v>8294800</v>
@@ -10432,16 +10432,16 @@
         <v>44516</v>
       </c>
       <c r="B501" t="n">
-        <v>6.783092021942139</v>
+        <v>6.78309154510498</v>
       </c>
       <c r="C501" t="n">
-        <v>7.177244504030098</v>
+        <v>7.177243999484845</v>
       </c>
       <c r="D501" t="n">
-        <v>6.691428704838564</v>
+        <v>6.691428234445144</v>
       </c>
       <c r="E501" t="n">
-        <v>7.131413064020896</v>
+        <v>7.131412562697498</v>
       </c>
       <c r="F501" t="n">
         <v>3605600</v>
@@ -10492,16 +10492,16 @@
         <v>44519</v>
       </c>
       <c r="B504" t="n">
-        <v>7.232241630554199</v>
+        <v>7.232242107391357</v>
       </c>
       <c r="C504" t="n">
-        <v>7.305572275479267</v>
+        <v>7.305572757151272</v>
       </c>
       <c r="D504" t="n">
-        <v>6.544766178754005</v>
+        <v>6.544766610264437</v>
       </c>
       <c r="E504" t="n">
-        <v>6.645596034068535</v>
+        <v>6.645596472226894</v>
       </c>
       <c r="F504" t="n">
         <v>4026100</v>
@@ -10512,16 +10512,16 @@
         <v>44522</v>
       </c>
       <c r="B505" t="n">
-        <v>6.783092021942139</v>
+        <v>6.78309154510498</v>
       </c>
       <c r="C505" t="n">
-        <v>7.296407034807332</v>
+        <v>7.296406521885203</v>
       </c>
       <c r="D505" t="n">
-        <v>6.57226617406133</v>
+        <v>6.572265712044786</v>
       </c>
       <c r="E505" t="n">
-        <v>7.278074371386616</v>
+        <v>7.278073859753236</v>
       </c>
       <c r="F505" t="n">
         <v>4188800</v>
@@ -10752,16 +10752,16 @@
         <v>44538</v>
       </c>
       <c r="B517" t="n">
-        <v>6.269776821136475</v>
+        <v>6.269776344299316</v>
       </c>
       <c r="C517" t="n">
-        <v>6.398105461234748</v>
+        <v>6.398104974637775</v>
       </c>
       <c r="D517" t="n">
-        <v>5.912289239520686</v>
+        <v>5.912288789871634</v>
       </c>
       <c r="E517" t="n">
-        <v>6.22394494541594</v>
+        <v>6.223944472064447</v>
       </c>
       <c r="F517" t="n">
         <v>2255900</v>
@@ -10772,16 +10772,16 @@
         <v>44539</v>
       </c>
       <c r="B518" t="n">
-        <v>6.08644962310791</v>
+        <v>6.086450099945068</v>
       </c>
       <c r="C518" t="n">
-        <v>6.269776684922006</v>
+        <v>6.26977717612175</v>
       </c>
       <c r="D518" t="n">
-        <v>5.994786310743438</v>
+        <v>5.994786780399321</v>
       </c>
       <c r="E518" t="n">
-        <v>6.2056121477243</v>
+        <v>6.205612633897133</v>
       </c>
       <c r="F518" t="n">
         <v>1370200</v>
@@ -10792,16 +10792,16 @@
         <v>44540</v>
       </c>
       <c r="B519" t="n">
-        <v>6.132281303405762</v>
+        <v>6.13228178024292</v>
       </c>
       <c r="C519" t="n">
-        <v>6.242277274755653</v>
+        <v>6.242277760145935</v>
       </c>
       <c r="D519" t="n">
-        <v>6.077283317730816</v>
+        <v>6.077283790291412</v>
       </c>
       <c r="E519" t="n">
-        <v>6.233111162352396</v>
+        <v>6.233111647029936</v>
       </c>
       <c r="F519" t="n">
         <v>1440000</v>
@@ -10812,16 +10812,16 @@
         <v>44543</v>
       </c>
       <c r="B520" t="n">
-        <v>5.93062162399292</v>
+        <v>5.930622100830078</v>
       </c>
       <c r="C520" t="n">
-        <v>6.233111202795508</v>
+        <v>6.233111703953602</v>
       </c>
       <c r="D520" t="n">
-        <v>5.93062162399292</v>
+        <v>5.930622100830078</v>
       </c>
       <c r="E520" t="n">
-        <v>6.123114793646776</v>
+        <v>6.123115285960878</v>
       </c>
       <c r="F520" t="n">
         <v>1532500</v>
@@ -10852,16 +10852,16 @@
         <v>44545</v>
       </c>
       <c r="B522" t="n">
-        <v>5.783960819244385</v>
+        <v>5.783960342407227</v>
       </c>
       <c r="C522" t="n">
-        <v>5.848125360274703</v>
+        <v>5.848124878147738</v>
       </c>
       <c r="D522" t="n">
-        <v>5.527303529293464</v>
+        <v>5.527303073615463</v>
       </c>
       <c r="E522" t="n">
-        <v>5.68313095107822</v>
+        <v>5.683130482553606</v>
       </c>
       <c r="F522" t="n">
         <v>1794200</v>
@@ -10912,16 +10912,16 @@
         <v>44550</v>
       </c>
       <c r="B525" t="n">
-        <v>5.701463222503662</v>
+        <v>5.70146369934082</v>
       </c>
       <c r="C525" t="n">
-        <v>5.756461646509856</v>
+        <v>5.756462127946762</v>
       </c>
       <c r="D525" t="n">
-        <v>5.582301136050633</v>
+        <v>5.582301602921769</v>
       </c>
       <c r="E525" t="n">
-        <v>5.710629772199743</v>
+        <v>5.710630249803538</v>
       </c>
       <c r="F525" t="n">
         <v>2934100</v>
@@ -10952,16 +10952,16 @@
         <v>44552</v>
       </c>
       <c r="B527" t="n">
-        <v>5.453972339630127</v>
+        <v>5.453971862792969</v>
       </c>
       <c r="C527" t="n">
-        <v>5.646465522166265</v>
+        <v>5.646465028499557</v>
       </c>
       <c r="D527" t="n">
-        <v>5.426473563316489</v>
+        <v>5.42647308888353</v>
       </c>
       <c r="E527" t="n">
-        <v>5.618966745852627</v>
+        <v>5.618966254590118</v>
       </c>
       <c r="F527" t="n">
         <v>3033600</v>
@@ -10972,16 +10972,16 @@
         <v>44553</v>
       </c>
       <c r="B528" t="n">
-        <v>5.453972339630127</v>
+        <v>5.453971862792969</v>
       </c>
       <c r="C528" t="n">
-        <v>5.481471553028933</v>
+        <v>5.481471073787537</v>
       </c>
       <c r="D528" t="n">
-        <v>5.325643696967758</v>
+        <v>5.325643231350287</v>
       </c>
       <c r="E528" t="n">
-        <v>5.444806226553971</v>
+        <v>5.444805750518199</v>
       </c>
       <c r="F528" t="n">
         <v>2899900</v>
@@ -11012,16 +11012,16 @@
         <v>44558</v>
       </c>
       <c r="B530" t="n">
-        <v>5.719796180725098</v>
+        <v>5.719795703887939</v>
       </c>
       <c r="C530" t="n">
-        <v>5.756461944321184</v>
+        <v>5.756461464427344</v>
       </c>
       <c r="D530" t="n">
-        <v>5.527303435085368</v>
+        <v>5.527302974295581</v>
       </c>
       <c r="E530" t="n">
-        <v>5.563968761596285</v>
+        <v>5.563968297749852</v>
       </c>
       <c r="F530" t="n">
         <v>2551400</v>
@@ -11072,16 +11072,16 @@
         <v>44564</v>
       </c>
       <c r="B533" t="n">
-        <v>5.417306423187256</v>
+        <v>5.417306900024414</v>
       </c>
       <c r="C533" t="n">
-        <v>5.774793973013967</v>
+        <v>5.774794481317564</v>
       </c>
       <c r="D533" t="n">
-        <v>5.371474988627377</v>
+        <v>5.371475461430403</v>
       </c>
       <c r="E533" t="n">
-        <v>5.655631456405064</v>
+        <v>5.655631954219848</v>
       </c>
       <c r="F533" t="n">
         <v>2044700</v>
@@ -11112,16 +11112,16 @@
         <v>44566</v>
       </c>
       <c r="B535" t="n">
-        <v>4.885659217834473</v>
+        <v>4.885658740997314</v>
       </c>
       <c r="C535" t="n">
-        <v>5.06898628262846</v>
+        <v>5.0689857878987</v>
       </c>
       <c r="D535" t="n">
-        <v>4.839827779449844</v>
+        <v>4.839827307085804</v>
       </c>
       <c r="E535" t="n">
-        <v>5.023154407158674</v>
+        <v>5.023153916902075</v>
       </c>
       <c r="F535" t="n">
         <v>2302400</v>
@@ -11172,16 +11172,16 @@
         <v>44571</v>
       </c>
       <c r="B538" t="n">
-        <v>4.79399585723877</v>
+        <v>4.793996334075928</v>
       </c>
       <c r="C538" t="n">
-        <v>4.894825720038117</v>
+        <v>4.894826206904368</v>
       </c>
       <c r="D538" t="n">
-        <v>4.629001893909508</v>
+        <v>4.62900235433546</v>
       </c>
       <c r="E538" t="n">
-        <v>4.720665206870209</v>
+        <v>4.720665676413498</v>
       </c>
       <c r="F538" t="n">
         <v>3868800</v>
@@ -11192,16 +11192,16 @@
         <v>44572</v>
       </c>
       <c r="B539" t="n">
-        <v>5.004822254180908</v>
+        <v>5.00482177734375</v>
       </c>
       <c r="C539" t="n">
-        <v>5.059820248095674</v>
+        <v>5.059819766018552</v>
       </c>
       <c r="D539" t="n">
-        <v>4.766497176798388</v>
+        <v>4.766496722667781</v>
       </c>
       <c r="E539" t="n">
-        <v>4.775663727660117</v>
+        <v>4.775663272656161</v>
       </c>
       <c r="F539" t="n">
         <v>2192500</v>
@@ -11212,16 +11212,16 @@
         <v>44573</v>
       </c>
       <c r="B540" t="n">
-        <v>5.169816017150879</v>
+        <v>5.169815540313721</v>
       </c>
       <c r="C540" t="n">
-        <v>5.270645886937004</v>
+        <v>5.270645400799818</v>
       </c>
       <c r="D540" t="n">
-        <v>4.995655491914913</v>
+        <v>4.995655031141423</v>
       </c>
       <c r="E540" t="n">
-        <v>5.032320819639834</v>
+        <v>5.032320355484523</v>
       </c>
       <c r="F540" t="n">
         <v>2344800</v>
@@ -11272,16 +11272,16 @@
         <v>44578</v>
       </c>
       <c r="B543" t="n">
-        <v>4.903992176055908</v>
+        <v>4.90399169921875</v>
       </c>
       <c r="C543" t="n">
-        <v>5.105651915770163</v>
+        <v>5.105651419324723</v>
       </c>
       <c r="D543" t="n">
-        <v>4.821495407159335</v>
+        <v>4.821494938343708</v>
       </c>
       <c r="E543" t="n">
-        <v>5.041487373663776</v>
+        <v>5.041486883457342</v>
       </c>
       <c r="F543" t="n">
         <v>1383000</v>
@@ -11292,16 +11292,16 @@
         <v>44579</v>
       </c>
       <c r="B544" t="n">
-        <v>4.80316162109375</v>
+        <v>4.803162097930908</v>
       </c>
       <c r="C544" t="n">
-        <v>4.977322121610753</v>
+        <v>4.977322615737815</v>
       </c>
       <c r="D544" t="n">
-        <v>4.748163637312347</v>
+        <v>4.748164108689543</v>
       </c>
       <c r="E544" t="n">
-        <v>4.913158025741677</v>
+        <v>4.913158513498805</v>
       </c>
       <c r="F544" t="n">
         <v>2424100</v>
@@ -11312,16 +11312,16 @@
         <v>44580</v>
       </c>
       <c r="B545" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C545" t="n">
-        <v>5.050653052647643</v>
+        <v>5.050653537402776</v>
       </c>
       <c r="D545" t="n">
-        <v>4.812328026305926</v>
+        <v>4.812328488186932</v>
       </c>
       <c r="E545" t="n">
-        <v>4.839827235916551</v>
+        <v>4.839827700436895</v>
       </c>
       <c r="F545" t="n">
         <v>2176700</v>
@@ -11552,16 +11552,16 @@
         <v>44596</v>
       </c>
       <c r="B557" t="n">
-        <v>5.490637302398682</v>
+        <v>5.490636825561523</v>
       </c>
       <c r="C557" t="n">
-        <v>5.637299035668652</v>
+        <v>5.637298546094581</v>
       </c>
       <c r="D557" t="n">
-        <v>5.371475217791077</v>
+        <v>5.37147475130261</v>
       </c>
       <c r="E557" t="n">
-        <v>5.628132486114529</v>
+        <v>5.628131997336533</v>
       </c>
       <c r="F557" t="n">
         <v>2310300</v>
@@ -11812,16 +11812,16 @@
         <v>44615</v>
       </c>
       <c r="B570" t="n">
-        <v>4.867326259613037</v>
+        <v>4.867326736450195</v>
       </c>
       <c r="C570" t="n">
-        <v>5.013987552877644</v>
+        <v>5.013988044082764</v>
       </c>
       <c r="D570" t="n">
-        <v>4.803161725267206</v>
+        <v>4.803162195818359</v>
       </c>
       <c r="E570" t="n">
-        <v>4.949823455616944</v>
+        <v>4.949823940536103</v>
       </c>
       <c r="F570" t="n">
         <v>3505100</v>
@@ -11872,16 +11872,16 @@
         <v>44622</v>
       </c>
       <c r="B573" t="n">
-        <v>4.647335052490234</v>
+        <v>4.647334575653076</v>
       </c>
       <c r="C573" t="n">
-        <v>4.738998375233738</v>
+        <v>4.738997888991517</v>
       </c>
       <c r="D573" t="n">
-        <v>4.583170508027182</v>
+        <v>4.58317003777359</v>
       </c>
       <c r="E573" t="n">
-        <v>4.665667717038935</v>
+        <v>4.665667238320764</v>
       </c>
       <c r="F573" t="n">
         <v>2274100</v>
@@ -11932,16 +11932,16 @@
         <v>44627</v>
       </c>
       <c r="B576" t="n">
-        <v>4.079020977020264</v>
+        <v>4.079021453857422</v>
       </c>
       <c r="C576" t="n">
-        <v>4.464007312971596</v>
+        <v>4.46400783481362</v>
       </c>
       <c r="D576" t="n">
-        <v>4.079020977020264</v>
+        <v>4.079021453857422</v>
       </c>
       <c r="E576" t="n">
-        <v>4.464007312971596</v>
+        <v>4.46400783481362</v>
       </c>
       <c r="F576" t="n">
         <v>3496200</v>
@@ -11952,16 +11952,16 @@
         <v>44628</v>
       </c>
       <c r="B577" t="n">
-        <v>4.124852657318115</v>
+        <v>4.124853134155273</v>
       </c>
       <c r="C577" t="n">
-        <v>4.207349850331715</v>
+        <v>4.207350336705632</v>
       </c>
       <c r="D577" t="n">
-        <v>3.969024820330257</v>
+        <v>3.969025279153559</v>
       </c>
       <c r="E577" t="n">
-        <v>4.134019206357456</v>
+        <v>4.134019684254276</v>
       </c>
       <c r="F577" t="n">
         <v>4412200</v>
@@ -11972,16 +11972,16 @@
         <v>44629</v>
       </c>
       <c r="B578" t="n">
-        <v>4.335679054260254</v>
+        <v>4.335678577423096</v>
       </c>
       <c r="C578" t="n">
-        <v>4.418176258252227</v>
+        <v>4.418175772342043</v>
       </c>
       <c r="D578" t="n">
-        <v>4.161518533102296</v>
+        <v>4.161518075419278</v>
       </c>
       <c r="E578" t="n">
-        <v>4.17068508336148</v>
+        <v>4.170684624670328</v>
       </c>
       <c r="F578" t="n">
         <v>3479000</v>
@@ -12172,16 +12172,16 @@
         <v>44643</v>
       </c>
       <c r="B588" t="n">
-        <v>4.79399585723877</v>
+        <v>4.793996334075928</v>
       </c>
       <c r="C588" t="n">
-        <v>4.839827732261697</v>
+        <v>4.839828213657545</v>
       </c>
       <c r="D588" t="n">
-        <v>4.574003469047934</v>
+        <v>4.574003924003441</v>
       </c>
       <c r="E588" t="n">
-        <v>4.656500669255141</v>
+        <v>4.656501132416273</v>
       </c>
       <c r="F588" t="n">
         <v>5289000</v>
@@ -12212,16 +12212,16 @@
         <v>44645</v>
       </c>
       <c r="B590" t="n">
-        <v>4.986488819122314</v>
+        <v>4.986489295959473</v>
       </c>
       <c r="C590" t="n">
-        <v>5.270645295655251</v>
+        <v>5.270645799665109</v>
       </c>
       <c r="D590" t="n">
-        <v>4.958989607871001</v>
+        <v>4.958990082078524</v>
       </c>
       <c r="E590" t="n">
-        <v>5.078152128151466</v>
+        <v>5.078152613754004</v>
       </c>
       <c r="F590" t="n">
         <v>4172200</v>
@@ -12232,16 +12232,16 @@
         <v>44648</v>
       </c>
       <c r="B591" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C591" t="n">
-        <v>5.142317254043173</v>
+        <v>5.142316768551991</v>
       </c>
       <c r="D591" t="n">
-        <v>4.885659522177632</v>
+        <v>4.885659060917757</v>
       </c>
       <c r="E591" t="n">
-        <v>5.01398816956781</v>
+        <v>5.013987696192302</v>
       </c>
       <c r="F591" t="n">
         <v>3528600</v>
@@ -12252,16 +12252,16 @@
         <v>44649</v>
       </c>
       <c r="B592" t="n">
-        <v>5.334810256958008</v>
+        <v>5.33480978012085</v>
       </c>
       <c r="C592" t="n">
-        <v>5.362309033322309</v>
+        <v>5.362308554027249</v>
       </c>
       <c r="D592" t="n">
-        <v>5.142317074067217</v>
+        <v>5.142316614435527</v>
       </c>
       <c r="E592" t="n">
-        <v>5.160649737338475</v>
+        <v>5.16064927606817</v>
       </c>
       <c r="F592" t="n">
         <v>3923800</v>
@@ -12292,16 +12292,16 @@
         <v>44651</v>
       </c>
       <c r="B594" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C594" t="n">
-        <v>5.224814023108552</v>
+        <v>5.224813529828769</v>
       </c>
       <c r="D594" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="E594" t="n">
-        <v>5.178982581868937</v>
+        <v>5.178982092916146</v>
       </c>
       <c r="F594" t="n">
         <v>1926600</v>
@@ -12452,16 +12452,16 @@
         <v>44663</v>
       </c>
       <c r="B602" t="n">
-        <v>4.372344017028809</v>
+        <v>4.372344493865967</v>
       </c>
       <c r="C602" t="n">
-        <v>4.519005312281472</v>
+        <v>4.519005805113152</v>
       </c>
       <c r="D602" t="n">
-        <v>4.363177904618086</v>
+        <v>4.36317838045561</v>
       </c>
       <c r="E602" t="n">
-        <v>4.464007326561723</v>
+        <v>4.464007813395457</v>
       </c>
       <c r="F602" t="n">
         <v>2977800</v>
@@ -12472,16 +12472,16 @@
         <v>44664</v>
       </c>
       <c r="B603" t="n">
-        <v>4.482339859008789</v>
+        <v>4.482340335845947</v>
       </c>
       <c r="C603" t="n">
-        <v>4.500672520385886</v>
+        <v>4.500672999173296</v>
       </c>
       <c r="D603" t="n">
-        <v>4.344844680138003</v>
+        <v>4.344845142348245</v>
       </c>
       <c r="E603" t="n">
-        <v>4.4273418748775</v>
+        <v>4.427342345863901</v>
       </c>
       <c r="F603" t="n">
         <v>2309600</v>
@@ -12512,16 +12512,16 @@
         <v>44669</v>
       </c>
       <c r="B605" t="n">
-        <v>4.537337779998779</v>
+        <v>4.537338256835938</v>
       </c>
       <c r="C605" t="n">
-        <v>4.537337779998779</v>
+        <v>4.537338256835938</v>
       </c>
       <c r="D605" t="n">
-        <v>4.372343829900955</v>
+        <v>4.372344289398597</v>
       </c>
       <c r="E605" t="n">
-        <v>4.454841023492427</v>
+        <v>4.45484149165985</v>
       </c>
       <c r="F605" t="n">
         <v>2710700</v>
@@ -12552,16 +12552,16 @@
         <v>44671</v>
       </c>
       <c r="B607" t="n">
-        <v>4.354012012481689</v>
+        <v>4.354011535644531</v>
       </c>
       <c r="C607" t="n">
-        <v>4.509839880756772</v>
+        <v>4.509839386853855</v>
       </c>
       <c r="D607" t="n">
-        <v>4.354012012481689</v>
+        <v>4.354011535644531</v>
       </c>
       <c r="E607" t="n">
-        <v>4.418176557384724</v>
+        <v>4.418176073520475</v>
       </c>
       <c r="F607" t="n">
         <v>2075500</v>
@@ -12572,16 +12572,16 @@
         <v>44673</v>
       </c>
       <c r="B608" t="n">
-        <v>4.097354412078857</v>
+        <v>4.097353935241699</v>
       </c>
       <c r="C608" t="n">
-        <v>4.308180281690042</v>
+        <v>4.308179780317636</v>
       </c>
       <c r="D608" t="n">
-        <v>4.079021746768547</v>
+        <v>4.079021272064886</v>
       </c>
       <c r="E608" t="n">
-        <v>4.308180281690042</v>
+        <v>4.308179780317636</v>
       </c>
       <c r="F608" t="n">
         <v>4745700</v>
@@ -12612,16 +12612,16 @@
         <v>44677</v>
       </c>
       <c r="B610" t="n">
-        <v>4.079020977020264</v>
+        <v>4.079021453857422</v>
       </c>
       <c r="C610" t="n">
-        <v>4.189017385210027</v>
+        <v>4.189017874905755</v>
       </c>
       <c r="D610" t="n">
-        <v>4.02402299146795</v>
+        <v>4.024023461875849</v>
       </c>
       <c r="E610" t="n">
-        <v>4.042355653318721</v>
+        <v>4.042356125869706</v>
       </c>
       <c r="F610" t="n">
         <v>5064800</v>
@@ -12632,16 +12632,16 @@
         <v>44678</v>
       </c>
       <c r="B611" t="n">
-        <v>3.978191614151001</v>
+        <v>3.97819185256958</v>
       </c>
       <c r="C611" t="n">
-        <v>4.170684784970252</v>
+        <v>4.170685034925215</v>
       </c>
       <c r="D611" t="n">
-        <v>3.941526289907824</v>
+        <v>3.941526526128999</v>
       </c>
       <c r="E611" t="n">
-        <v>4.170684784970252</v>
+        <v>4.170685034925215</v>
       </c>
       <c r="F611" t="n">
         <v>4173400</v>
@@ -12812,16 +12812,16 @@
         <v>44691</v>
       </c>
       <c r="B620" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C620" t="n">
-        <v>2.887397154408436</v>
+        <v>2.887397395893507</v>
       </c>
       <c r="D620" t="n">
-        <v>2.694903981642197</v>
+        <v>2.694904207028261</v>
       </c>
       <c r="E620" t="n">
-        <v>2.8140662866378</v>
+        <v>2.814066521989905</v>
       </c>
       <c r="F620" t="n">
         <v>7309900</v>
@@ -12852,16 +12852,16 @@
         <v>44693</v>
       </c>
       <c r="B622" t="n">
-        <v>2.942395210266113</v>
+        <v>2.942394971847534</v>
       </c>
       <c r="C622" t="n">
-        <v>3.024892192580485</v>
+        <v>3.02489194747728</v>
       </c>
       <c r="D622" t="n">
-        <v>2.814066352567845</v>
+        <v>2.814066124547592</v>
       </c>
       <c r="E622" t="n">
-        <v>2.869064559320005</v>
+        <v>2.869064326843316</v>
       </c>
       <c r="F622" t="n">
         <v>3382300</v>
@@ -12872,16 +12872,16 @@
         <v>44694</v>
       </c>
       <c r="B623" t="n">
-        <v>3.043224811553955</v>
+        <v>3.043225049972534</v>
       </c>
       <c r="C623" t="n">
-        <v>3.107389348751661</v>
+        <v>3.10738959219715</v>
       </c>
       <c r="D623" t="n">
-        <v>2.942395167953036</v>
+        <v>2.942395398472212</v>
       </c>
       <c r="E623" t="n">
-        <v>2.969894161662377</v>
+        <v>2.969894394335936</v>
       </c>
       <c r="F623" t="n">
         <v>4357400</v>
@@ -12932,16 +12932,16 @@
         <v>44699</v>
       </c>
       <c r="B626" t="n">
-        <v>2.859898090362549</v>
+        <v>2.85989785194397</v>
       </c>
       <c r="C626" t="n">
-        <v>3.089056599598365</v>
+        <v>3.089056342075733</v>
       </c>
       <c r="D626" t="n">
-        <v>2.85073175873482</v>
+        <v>2.850731521080402</v>
       </c>
       <c r="E626" t="n">
-        <v>3.079890267970636</v>
+        <v>3.079890011212165</v>
       </c>
       <c r="F626" t="n">
         <v>5243400</v>
@@ -13112,16 +13112,16 @@
         <v>44712</v>
       </c>
       <c r="B635" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C635" t="n">
-        <v>3.015725790557546</v>
+        <v>3.015726042775277</v>
       </c>
       <c r="D635" t="n">
-        <v>2.804899955484291</v>
+        <v>2.804900190069778</v>
       </c>
       <c r="E635" t="n">
-        <v>2.988226797097023</v>
+        <v>2.988227047014898</v>
       </c>
       <c r="F635" t="n">
         <v>7519800</v>
@@ -13192,16 +13192,16 @@
         <v>44718</v>
       </c>
       <c r="B639" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="C639" t="n">
-        <v>2.859897899145521</v>
+        <v>2.859898153024676</v>
       </c>
       <c r="D639" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="E639" t="n">
-        <v>2.814066244071248</v>
+        <v>2.81406649388183</v>
       </c>
       <c r="F639" t="n">
         <v>3115900</v>
@@ -13212,16 +13212,16 @@
         <v>44719</v>
       </c>
       <c r="B640" t="n">
-        <v>2.667405128479004</v>
+        <v>2.667404890060425</v>
       </c>
       <c r="C640" t="n">
-        <v>2.713236786657148</v>
+        <v>2.713236544142034</v>
       </c>
       <c r="D640" t="n">
-        <v>2.584907925215759</v>
+        <v>2.584907694170964</v>
       </c>
       <c r="E640" t="n">
-        <v>2.658238796843375</v>
+        <v>2.658238559244103</v>
       </c>
       <c r="F640" t="n">
         <v>2825300</v>
@@ -13232,16 +13232,16 @@
         <v>44720</v>
       </c>
       <c r="B641" t="n">
-        <v>2.667405128479004</v>
+        <v>2.667404890060425</v>
       </c>
       <c r="C641" t="n">
-        <v>2.722403118292777</v>
+        <v>2.722402874958356</v>
       </c>
       <c r="D641" t="n">
-        <v>2.639906133572117</v>
+        <v>2.63990589761146</v>
       </c>
       <c r="E641" t="n">
-        <v>2.649072465207746</v>
+        <v>2.649072228427781</v>
       </c>
       <c r="F641" t="n">
         <v>3025200</v>
@@ -13272,16 +13272,16 @@
         <v>44722</v>
       </c>
       <c r="B643" t="n">
-        <v>2.502411127090454</v>
+        <v>2.502410888671875</v>
       </c>
       <c r="C643" t="n">
-        <v>2.630739779558241</v>
+        <v>2.63073952891308</v>
       </c>
       <c r="D643" t="n">
-        <v>2.493244794771327</v>
+        <v>2.493244557226074</v>
       </c>
       <c r="E643" t="n">
-        <v>2.594074450281731</v>
+        <v>2.594074203129878</v>
       </c>
       <c r="F643" t="n">
         <v>4379600</v>
@@ -13292,16 +13292,16 @@
         <v>44725</v>
       </c>
       <c r="B644" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C644" t="n">
-        <v>2.429080238828605</v>
+        <v>2.42907999298842</v>
       </c>
       <c r="D644" t="n">
-        <v>2.282418717049181</v>
+        <v>2.282418486052185</v>
       </c>
       <c r="E644" t="n">
-        <v>2.429080238828605</v>
+        <v>2.42907999298842</v>
       </c>
       <c r="F644" t="n">
         <v>5369000</v>
@@ -13312,16 +13312,16 @@
         <v>44726</v>
       </c>
       <c r="B645" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C645" t="n">
-        <v>2.401580915813275</v>
+        <v>2.401580660851382</v>
       </c>
       <c r="D645" t="n">
-        <v>2.236586957237029</v>
+        <v>2.236586719791586</v>
       </c>
       <c r="E645" t="n">
-        <v>2.374081922717234</v>
+        <v>2.374081670674749</v>
       </c>
       <c r="F645" t="n">
         <v>2610500</v>
@@ -13392,16 +13392,16 @@
         <v>44733</v>
       </c>
       <c r="B649" t="n">
-        <v>2.254919528961182</v>
+        <v>2.254919767379761</v>
       </c>
       <c r="C649" t="n">
-        <v>2.328250174279411</v>
+        <v>2.328250420451433</v>
       </c>
       <c r="D649" t="n">
-        <v>2.236586867631624</v>
+        <v>2.236587104111843</v>
       </c>
       <c r="E649" t="n">
-        <v>2.254919528961182</v>
+        <v>2.254919767379761</v>
       </c>
       <c r="F649" t="n">
         <v>3435200</v>
@@ -13412,16 +13412,16 @@
         <v>44734</v>
       </c>
       <c r="B650" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C650" t="n">
-        <v>2.300751274461124</v>
+        <v>2.300751030203729</v>
       </c>
       <c r="D650" t="n">
-        <v>2.190755302076961</v>
+        <v>2.190755069497199</v>
       </c>
       <c r="E650" t="n">
-        <v>2.236586957237029</v>
+        <v>2.236586719791586</v>
       </c>
       <c r="F650" t="n">
         <v>3144500</v>
@@ -13452,16 +13452,16 @@
         <v>44736</v>
       </c>
       <c r="B652" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C652" t="n">
-        <v>2.355749260653206</v>
+        <v>2.355749010556994</v>
       </c>
       <c r="D652" t="n">
-        <v>2.209087964140989</v>
+        <v>2.209087729614954</v>
       </c>
       <c r="E652" t="n">
-        <v>2.337416598589179</v>
+        <v>2.337416350439239</v>
       </c>
       <c r="F652" t="n">
         <v>3887000</v>
@@ -13472,16 +13472,16 @@
         <v>44739</v>
       </c>
       <c r="B653" t="n">
-        <v>2.163256168365479</v>
+        <v>2.163255929946899</v>
       </c>
       <c r="C653" t="n">
-        <v>2.291585025979039</v>
+        <v>2.291584773416974</v>
       </c>
       <c r="D653" t="n">
-        <v>2.154089837003265</v>
+        <v>2.154089599594934</v>
       </c>
       <c r="E653" t="n">
-        <v>2.273252363254613</v>
+        <v>2.273252112713042</v>
       </c>
       <c r="F653" t="n">
         <v>3063200</v>
@@ -13512,16 +13512,16 @@
         <v>44741</v>
       </c>
       <c r="B655" t="n">
-        <v>2.126590728759766</v>
+        <v>2.126590967178345</v>
       </c>
       <c r="C655" t="n">
-        <v>2.126590728759766</v>
+        <v>2.126590967178345</v>
       </c>
       <c r="D655" t="n">
-        <v>2.016594758317869</v>
+        <v>2.016594984404464</v>
       </c>
       <c r="E655" t="n">
-        <v>2.089925405279133</v>
+        <v>2.089925639587051</v>
       </c>
       <c r="F655" t="n">
         <v>5733700</v>
@@ -13632,16 +13632,16 @@
         <v>44749</v>
       </c>
       <c r="B661" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C661" t="n">
-        <v>2.392414694476813</v>
+        <v>2.392414452347443</v>
       </c>
       <c r="D661" t="n">
-        <v>2.300751379953786</v>
+        <v>2.300751147101395</v>
       </c>
       <c r="E661" t="n">
-        <v>2.337416705762997</v>
+        <v>2.337416469199814</v>
       </c>
       <c r="F661" t="n">
         <v>2762300</v>
@@ -13652,16 +13652,16 @@
         <v>44750</v>
       </c>
       <c r="B662" t="n">
-        <v>2.401580810546875</v>
+        <v>2.401581048965454</v>
       </c>
       <c r="C662" t="n">
-        <v>2.401580810546875</v>
+        <v>2.401581048965454</v>
       </c>
       <c r="D662" t="n">
-        <v>2.300751173614302</v>
+        <v>2.300751402022951</v>
       </c>
       <c r="E662" t="n">
-        <v>2.337416496135238</v>
+        <v>2.337416728183861</v>
       </c>
       <c r="F662" t="n">
         <v>2746100</v>
@@ -13672,16 +13672,16 @@
         <v>44753</v>
       </c>
       <c r="B663" t="n">
-        <v>2.337416410446167</v>
+        <v>2.337416648864746</v>
       </c>
       <c r="C663" t="n">
-        <v>2.38324806191716</v>
+        <v>2.383248305010609</v>
       </c>
       <c r="D663" t="n">
-        <v>2.273252098386777</v>
+        <v>2.273252330260538</v>
       </c>
       <c r="E663" t="n">
-        <v>2.346582740740366</v>
+        <v>2.346582980093919</v>
       </c>
       <c r="F663" t="n">
         <v>1807800</v>
@@ -13692,16 +13692,16 @@
         <v>44754</v>
       </c>
       <c r="B664" t="n">
-        <v>2.401580810546875</v>
+        <v>2.401581048965454</v>
       </c>
       <c r="C664" t="n">
-        <v>2.447412682240605</v>
+        <v>2.447412925209175</v>
       </c>
       <c r="D664" t="n">
-        <v>2.254919520463134</v>
+        <v>2.254919744321813</v>
       </c>
       <c r="E664" t="n">
-        <v>2.355749157395706</v>
+        <v>2.355749391264316</v>
       </c>
       <c r="F664" t="n">
         <v>5712200</v>
@@ -13752,16 +13752,16 @@
         <v>44757</v>
       </c>
       <c r="B667" t="n">
-        <v>2.163256168365479</v>
+        <v>2.163255929946899</v>
       </c>
       <c r="C667" t="n">
-        <v>2.245753369167974</v>
+        <v>2.245753121657145</v>
       </c>
       <c r="D667" t="n">
-        <v>2.135757174278839</v>
+        <v>2.135756938891002</v>
       </c>
       <c r="E667" t="n">
-        <v>2.227420706443548</v>
+        <v>2.227420460953214</v>
       </c>
       <c r="F667" t="n">
         <v>2806200</v>
@@ -13772,16 +13772,16 @@
         <v>44760</v>
       </c>
       <c r="B668" t="n">
-        <v>2.254919528961182</v>
+        <v>2.254919767379761</v>
       </c>
       <c r="C668" t="n">
-        <v>2.346582835608969</v>
+        <v>2.346583083719351</v>
       </c>
       <c r="D668" t="n">
-        <v>2.19992154497251</v>
+        <v>2.199921777576007</v>
       </c>
       <c r="E668" t="n">
-        <v>2.19992154497251</v>
+        <v>2.199921777576007</v>
       </c>
       <c r="F668" t="n">
         <v>4381400</v>
@@ -13832,16 +13832,16 @@
         <v>44763</v>
       </c>
       <c r="B671" t="n">
-        <v>2.383248329162598</v>
+        <v>2.383248090744019</v>
       </c>
       <c r="C671" t="n">
-        <v>2.474911860925822</v>
+        <v>2.474911613337284</v>
       </c>
       <c r="D671" t="n">
-        <v>2.346583003874339</v>
+        <v>2.346582769123735</v>
       </c>
       <c r="E671" t="n">
-        <v>2.364915666518468</v>
+        <v>2.364915429933876</v>
       </c>
       <c r="F671" t="n">
         <v>3831200</v>
@@ -13872,16 +13872,16 @@
         <v>44767</v>
       </c>
       <c r="B673" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C673" t="n">
-        <v>2.392414694476813</v>
+        <v>2.392414452347443</v>
       </c>
       <c r="D673" t="n">
-        <v>2.254919722692273</v>
+        <v>2.25491949447837</v>
       </c>
       <c r="E673" t="n">
-        <v>2.300751379953786</v>
+        <v>2.300751147101395</v>
       </c>
       <c r="F673" t="n">
         <v>3311300</v>
@@ -13892,16 +13892,16 @@
         <v>44768</v>
       </c>
       <c r="B674" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C674" t="n">
-        <v>2.520743251874533</v>
+        <v>2.520743493812202</v>
       </c>
       <c r="D674" t="n">
-        <v>2.300751104787417</v>
+        <v>2.300751325610525</v>
       </c>
       <c r="E674" t="n">
-        <v>2.374081747635604</v>
+        <v>2.374081975496892</v>
       </c>
       <c r="F674" t="n">
         <v>4848400</v>
@@ -13912,16 +13912,16 @@
         <v>44769</v>
       </c>
       <c r="B675" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242807388306</v>
       </c>
       <c r="C675" t="n">
-        <v>2.603240558142417</v>
+        <v>2.603240801706716</v>
       </c>
       <c r="D675" t="n">
-        <v>2.419913927566782</v>
+        <v>2.419914153978682</v>
       </c>
       <c r="E675" t="n">
-        <v>2.502410911325818</v>
+        <v>2.502411145456297</v>
       </c>
       <c r="F675" t="n">
         <v>5961800</v>
@@ -13952,16 +13952,16 @@
         <v>44771</v>
       </c>
       <c r="B677" t="n">
-        <v>2.575741291046143</v>
+        <v>2.575741529464722</v>
       </c>
       <c r="C677" t="n">
-        <v>2.603240282723132</v>
+        <v>2.603240523687103</v>
       </c>
       <c r="D677" t="n">
-        <v>2.493244316015175</v>
+        <v>2.493244546797579</v>
       </c>
       <c r="E677" t="n">
-        <v>2.566574960487146</v>
+        <v>2.566575198057261</v>
       </c>
       <c r="F677" t="n">
         <v>2895400</v>
@@ -13972,16 +13972,16 @@
         <v>44774</v>
       </c>
       <c r="B678" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="C678" t="n">
-        <v>2.749901926967264</v>
+        <v>2.749902171081845</v>
       </c>
       <c r="D678" t="n">
-        <v>2.520743433053326</v>
+        <v>2.520743656825025</v>
       </c>
       <c r="E678" t="n">
-        <v>2.575741419142454</v>
+        <v>2.57574164779644</v>
       </c>
       <c r="F678" t="n">
         <v>6003000</v>
@@ -13992,16 +13992,16 @@
         <v>44775</v>
       </c>
       <c r="B679" t="n">
-        <v>2.575741291046143</v>
+        <v>2.575741529464722</v>
       </c>
       <c r="C679" t="n">
-        <v>2.740735459650637</v>
+        <v>2.740735713341587</v>
       </c>
       <c r="D679" t="n">
-        <v>2.548242299369153</v>
+        <v>2.548242535242341</v>
       </c>
       <c r="E679" t="n">
-        <v>2.676571145737662</v>
+        <v>2.676571393489365</v>
       </c>
       <c r="F679" t="n">
         <v>4865400</v>
@@ -14032,16 +14032,16 @@
         <v>44777</v>
       </c>
       <c r="B681" t="n">
-        <v>2.859898090362549</v>
+        <v>2.85989785194397</v>
       </c>
       <c r="C681" t="n">
-        <v>2.878230972160592</v>
+        <v>2.878230732213672</v>
       </c>
       <c r="D681" t="n">
-        <v>2.704070452691151</v>
+        <v>2.704070227263316</v>
       </c>
       <c r="E681" t="n">
-        <v>2.72240311594661</v>
+        <v>2.722402888990452</v>
       </c>
       <c r="F681" t="n">
         <v>7566500</v>
@@ -14052,16 +14052,16 @@
         <v>44778</v>
       </c>
       <c r="B682" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232889175415</v>
       </c>
       <c r="C682" t="n">
-        <v>2.969894169468031</v>
+        <v>2.969894420271998</v>
       </c>
       <c r="D682" t="n">
-        <v>2.731569338151449</v>
+        <v>2.731569568829172</v>
       </c>
       <c r="E682" t="n">
-        <v>2.869064525602105</v>
+        <v>2.869064767891131</v>
       </c>
       <c r="F682" t="n">
         <v>6497600</v>
@@ -14072,16 +14072,16 @@
         <v>44781</v>
       </c>
       <c r="B683" t="n">
-        <v>2.759068250656128</v>
+        <v>2.759068489074707</v>
       </c>
       <c r="C683" t="n">
-        <v>2.924062427027984</v>
+        <v>2.924062679704158</v>
       </c>
       <c r="D683" t="n">
-        <v>2.759068250656128</v>
+        <v>2.759068489074707</v>
       </c>
       <c r="E683" t="n">
-        <v>2.850731560561287</v>
+        <v>2.850731806900742</v>
       </c>
       <c r="F683" t="n">
         <v>8446700</v>
@@ -14132,16 +14132,16 @@
         <v>44784</v>
       </c>
       <c r="B686" t="n">
-        <v>3.034058332443237</v>
+        <v>3.034058570861816</v>
       </c>
       <c r="C686" t="n">
-        <v>3.15322085125187</v>
+        <v>3.153221099034329</v>
       </c>
       <c r="D686" t="n">
-        <v>2.887397039808076</v>
+        <v>2.887397266701901</v>
       </c>
       <c r="E686" t="n">
-        <v>2.896563370597774</v>
+        <v>2.896563598211896</v>
       </c>
       <c r="F686" t="n">
         <v>13306300</v>
@@ -14232,16 +14232,16 @@
         <v>44791</v>
       </c>
       <c r="B691" t="n">
-        <v>3.024892330169678</v>
+        <v>3.024892091751099</v>
       </c>
       <c r="C691" t="n">
-        <v>3.272383506912668</v>
+        <v>3.272383248987116</v>
       </c>
       <c r="D691" t="n">
-        <v>3.024892330169678</v>
+        <v>3.024892091751099</v>
       </c>
       <c r="E691" t="n">
-        <v>3.263217175127469</v>
+        <v>3.263216917924395</v>
       </c>
       <c r="F691" t="n">
         <v>6872400</v>
@@ -14392,16 +14392,16 @@
         <v>44803</v>
       </c>
       <c r="B699" t="n">
-        <v>3.024892330169678</v>
+        <v>3.024892091751099</v>
       </c>
       <c r="C699" t="n">
-        <v>3.162387525490268</v>
+        <v>3.162387276234473</v>
       </c>
       <c r="D699" t="n">
-        <v>2.951561675888077</v>
+        <v>2.951561443249337</v>
       </c>
       <c r="E699" t="n">
-        <v>3.079890320880878</v>
+        <v>3.07989007812742</v>
       </c>
       <c r="F699" t="n">
         <v>4644000</v>
@@ -14432,16 +14432,16 @@
         <v>44805</v>
       </c>
       <c r="B701" t="n">
-        <v>3.12572193145752</v>
+        <v>3.125722169876099</v>
       </c>
       <c r="C701" t="n">
-        <v>3.134888262460046</v>
+        <v>3.134888501577799</v>
       </c>
       <c r="D701" t="n">
-        <v>2.94239509286442</v>
+        <v>2.942395317299501</v>
       </c>
       <c r="E701" t="n">
-        <v>2.951561423866946</v>
+        <v>2.951561649001202</v>
       </c>
       <c r="F701" t="n">
         <v>5408300</v>
@@ -14552,16 +14552,16 @@
         <v>44816</v>
       </c>
       <c r="B707" t="n">
-        <v>3.391546010971069</v>
+        <v>3.39154577255249</v>
       </c>
       <c r="C707" t="n">
-        <v>3.437377669522857</v>
+        <v>3.437377427882408</v>
       </c>
       <c r="D707" t="n">
-        <v>3.327381688998567</v>
+        <v>3.327381455090605</v>
       </c>
       <c r="E707" t="n">
-        <v>3.327381688998567</v>
+        <v>3.327381455090605</v>
       </c>
       <c r="F707" t="n">
         <v>4227100</v>
@@ -14732,16 +14732,16 @@
         <v>44827</v>
       </c>
       <c r="B716" t="n">
-        <v>3.134888410568237</v>
+        <v>3.134888172149658</v>
       </c>
       <c r="C716" t="n">
-        <v>3.25405071923092</v>
+        <v>3.254050471749655</v>
       </c>
       <c r="D716" t="n">
-        <v>3.098223084825873</v>
+        <v>3.098222849195813</v>
       </c>
       <c r="E716" t="n">
-        <v>3.098223084825873</v>
+        <v>3.098222849195813</v>
       </c>
       <c r="F716" t="n">
         <v>4782400</v>
@@ -14792,16 +14792,16 @@
         <v>44832</v>
       </c>
       <c r="B719" t="n">
-        <v>2.942395210266113</v>
+        <v>2.942394971847534</v>
       </c>
       <c r="C719" t="n">
-        <v>2.96072787300264</v>
+        <v>2.960727633098589</v>
       </c>
       <c r="D719" t="n">
-        <v>2.841565346672636</v>
+        <v>2.841565116424174</v>
       </c>
       <c r="E719" t="n">
-        <v>2.896563553424795</v>
+        <v>2.896563318719898</v>
       </c>
       <c r="F719" t="n">
         <v>3561500</v>
@@ -14812,16 +14812,16 @@
         <v>44833</v>
       </c>
       <c r="B720" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232889175415</v>
       </c>
       <c r="C720" t="n">
-        <v>2.90572985064426</v>
+        <v>2.905730096029628</v>
       </c>
       <c r="D720" t="n">
-        <v>2.79573365697522</v>
+        <v>2.795733893071542</v>
       </c>
       <c r="E720" t="n">
-        <v>2.896563519383722</v>
+        <v>2.896563763995004</v>
       </c>
       <c r="F720" t="n">
         <v>3966200</v>
@@ -14932,16 +14932,16 @@
         <v>44841</v>
       </c>
       <c r="B726" t="n">
-        <v>3.44654393196106</v>
+        <v>3.44654369354248</v>
       </c>
       <c r="C726" t="n">
-        <v>3.602371786447736</v>
+        <v>3.602371537249589</v>
       </c>
       <c r="D726" t="n">
-        <v>3.41904493738269</v>
+        <v>3.419044700866385</v>
       </c>
       <c r="E726" t="n">
-        <v>3.464876595013306</v>
+        <v>3.464876355326544</v>
       </c>
       <c r="F726" t="n">
         <v>4739800</v>
@@ -15012,16 +15012,16 @@
         <v>44848</v>
       </c>
       <c r="B730" t="n">
-        <v>3.052391290664673</v>
+        <v>3.052391052246094</v>
       </c>
       <c r="C730" t="n">
-        <v>3.199052816095478</v>
+        <v>3.199052566221344</v>
       </c>
       <c r="D730" t="n">
-        <v>2.997393300581591</v>
+        <v>2.997393066458838</v>
       </c>
       <c r="E730" t="n">
-        <v>3.153221157692909</v>
+        <v>3.153220911398631</v>
       </c>
       <c r="F730" t="n">
         <v>2652600</v>
@@ -15032,16 +15032,16 @@
         <v>44851</v>
       </c>
       <c r="B731" t="n">
-        <v>3.034058332443237</v>
+        <v>3.034058570861816</v>
       </c>
       <c r="C731" t="n">
-        <v>3.11655552809308</v>
+        <v>3.116555772994351</v>
       </c>
       <c r="D731" t="n">
-        <v>3.02489200165354</v>
+        <v>3.024892239351822</v>
       </c>
       <c r="E731" t="n">
-        <v>3.079889986391725</v>
+        <v>3.07989022841179</v>
       </c>
       <c r="F731" t="n">
         <v>3944900</v>
@@ -15092,16 +15092,16 @@
         <v>44854</v>
       </c>
       <c r="B734" t="n">
-        <v>2.814066410064697</v>
+        <v>2.814066171646118</v>
       </c>
       <c r="C734" t="n">
-        <v>2.951561601940523</v>
+        <v>2.95156135187282</v>
       </c>
       <c r="D734" t="n">
-        <v>2.795733746953598</v>
+        <v>2.795733510088233</v>
       </c>
       <c r="E734" t="n">
-        <v>2.942395270384973</v>
+        <v>2.942395021093878</v>
       </c>
       <c r="F734" t="n">
         <v>4518300</v>
@@ -15112,16 +15112,16 @@
         <v>44855</v>
       </c>
       <c r="B735" t="n">
-        <v>2.814066410064697</v>
+        <v>2.814066171646118</v>
       </c>
       <c r="C735" t="n">
-        <v>2.869064617940577</v>
+        <v>2.869064374862337</v>
       </c>
       <c r="D735" t="n">
-        <v>2.685737768287004</v>
+        <v>2.685737540740923</v>
       </c>
       <c r="E735" t="n">
-        <v>2.804900078509148</v>
+        <v>2.804899840867176</v>
       </c>
       <c r="F735" t="n">
         <v>6831600</v>
@@ -15132,16 +15132,16 @@
         <v>44858</v>
       </c>
       <c r="B736" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="C736" t="n">
-        <v>2.814066144805841</v>
+        <v>2.814066387171744</v>
       </c>
       <c r="D736" t="n">
-        <v>2.704070176507662</v>
+        <v>2.704070409399987</v>
       </c>
       <c r="E736" t="n">
-        <v>2.795733483422811</v>
+        <v>2.795733724209785</v>
       </c>
       <c r="F736" t="n">
         <v>4201100</v>
@@ -15172,16 +15172,16 @@
         <v>44860</v>
       </c>
       <c r="B738" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C738" t="n">
-        <v>2.749901729317672</v>
+        <v>2.749901993249675</v>
       </c>
       <c r="D738" t="n">
-        <v>2.438246278670322</v>
+        <v>2.438246512690039</v>
       </c>
       <c r="E738" t="n">
-        <v>2.749901729317672</v>
+        <v>2.749901993249675</v>
       </c>
       <c r="F738" t="n">
         <v>9447400</v>
@@ -15232,16 +15232,16 @@
         <v>44865</v>
       </c>
       <c r="B741" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="C741" t="n">
-        <v>2.832398806188871</v>
+        <v>2.832399050133704</v>
       </c>
       <c r="D741" t="n">
-        <v>2.55740866690086</v>
+        <v>2.557408887161731</v>
       </c>
       <c r="E741" t="n">
-        <v>2.59407398966692</v>
+        <v>2.59407421308565</v>
       </c>
       <c r="F741" t="n">
         <v>6603200</v>
@@ -15292,16 +15292,16 @@
         <v>44869</v>
       </c>
       <c r="B744" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="C744" t="n">
-        <v>2.933228662338098</v>
+        <v>2.933228914967061</v>
       </c>
       <c r="D744" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="E744" t="n">
-        <v>2.924062331646583</v>
+        <v>2.924062583486082</v>
       </c>
       <c r="F744" t="n">
         <v>7869400</v>
@@ -15392,16 +15392,16 @@
         <v>44876</v>
       </c>
       <c r="B749" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C749" t="n">
-        <v>2.429080127451886</v>
+        <v>2.429079869570562</v>
       </c>
       <c r="D749" t="n">
-        <v>2.227420626205016</v>
+        <v>2.227420389732709</v>
       </c>
       <c r="E749" t="n">
-        <v>2.319083936525152</v>
+        <v>2.319083690321484</v>
       </c>
       <c r="F749" t="n">
         <v>8256600</v>
@@ -15512,16 +15512,16 @@
         <v>44887</v>
       </c>
       <c r="B755" t="n">
-        <v>2.144923686981201</v>
+        <v>2.144923448562622</v>
       </c>
       <c r="C755" t="n">
-        <v>2.209088230483989</v>
+        <v>2.209087984933213</v>
       </c>
       <c r="D755" t="n">
-        <v>2.10825835843252</v>
+        <v>2.108258124089469</v>
       </c>
       <c r="E755" t="n">
-        <v>2.181589234072479</v>
+        <v>2.181588991578348</v>
       </c>
       <c r="F755" t="n">
         <v>3236000</v>
@@ -15572,16 +15572,16 @@
         <v>44890</v>
       </c>
       <c r="B758" t="n">
-        <v>2.144923686981201</v>
+        <v>2.144923448562622</v>
       </c>
       <c r="C758" t="n">
-        <v>2.25491989116984</v>
+        <v>2.254919640524655</v>
       </c>
       <c r="D758" t="n">
-        <v>2.117424690569691</v>
+        <v>2.117424455207757</v>
       </c>
       <c r="E758" t="n">
-        <v>2.22742089475833</v>
+        <v>2.22742064716979</v>
       </c>
       <c r="F758" t="n">
         <v>2578200</v>
@@ -15592,16 +15592,16 @@
         <v>44893</v>
       </c>
       <c r="B759" t="n">
-        <v>2.04409384727478</v>
+        <v>2.044094085693359</v>
       </c>
       <c r="C759" t="n">
-        <v>2.144923491599029</v>
+        <v>2.144923741778154</v>
       </c>
       <c r="D759" t="n">
-        <v>2.034927515972576</v>
+        <v>2.034927753322014</v>
       </c>
       <c r="E759" t="n">
-        <v>2.135757160296825</v>
+        <v>2.135757409406809</v>
       </c>
       <c r="F759" t="n">
         <v>2781000</v>
@@ -15672,16 +15672,16 @@
         <v>44897</v>
       </c>
       <c r="B763" t="n">
-        <v>2.181588888168335</v>
+        <v>2.181589126586914</v>
       </c>
       <c r="C763" t="n">
-        <v>2.199921549535921</v>
+        <v>2.199921789958015</v>
       </c>
       <c r="D763" t="n">
-        <v>2.099091693471637</v>
+        <v>2.099091922874372</v>
       </c>
       <c r="E763" t="n">
-        <v>2.154089677574394</v>
+        <v>2.154089912987676</v>
       </c>
       <c r="F763" t="n">
         <v>2941200</v>
@@ -15772,16 +15772,16 @@
         <v>44904</v>
       </c>
       <c r="B768" t="n">
-        <v>2.126590728759766</v>
+        <v>2.126590967178345</v>
       </c>
       <c r="C768" t="n">
-        <v>2.172422383110556</v>
+        <v>2.172422626667462</v>
       </c>
       <c r="D768" t="n">
-        <v>2.071592743538817</v>
+        <v>2.071592975791404</v>
       </c>
       <c r="E768" t="n">
-        <v>2.135757059629924</v>
+        <v>2.135757299076168</v>
       </c>
       <c r="F768" t="n">
         <v>2468100</v>
@@ -15792,16 +15792,16 @@
         <v>44907</v>
       </c>
       <c r="B769" t="n">
-        <v>2.126590728759766</v>
+        <v>2.126590967178345</v>
       </c>
       <c r="C769" t="n">
-        <v>2.135757059629924</v>
+        <v>2.135757299076168</v>
       </c>
       <c r="D769" t="n">
-        <v>2.034927420058185</v>
+        <v>2.034927648200111</v>
       </c>
       <c r="E769" t="n">
-        <v>2.126590728759766</v>
+        <v>2.126590967178345</v>
       </c>
       <c r="F769" t="n">
         <v>2948100</v>
@@ -15812,16 +15812,16 @@
         <v>44908</v>
       </c>
       <c r="B770" t="n">
-        <v>1.998262286186218</v>
+        <v>1.998262166976929</v>
       </c>
       <c r="C770" t="n">
-        <v>2.190755471267162</v>
+        <v>2.190755340574407</v>
       </c>
       <c r="D770" t="n">
-        <v>1.989095954446297</v>
+        <v>1.989095835783838</v>
       </c>
       <c r="E770" t="n">
-        <v>2.144923594024966</v>
+        <v>2.144923466066379</v>
       </c>
       <c r="F770" t="n">
         <v>3298100</v>
@@ -15832,16 +15832,16 @@
         <v>44909</v>
       </c>
       <c r="B771" t="n">
-        <v>1.979929685592651</v>
+        <v>1.979929566383362</v>
       </c>
       <c r="C771" t="n">
-        <v>2.007428681685836</v>
+        <v>2.007428560820864</v>
       </c>
       <c r="D771" t="n">
-        <v>1.888266146739441</v>
+        <v>1.888266033049108</v>
       </c>
       <c r="E771" t="n">
-        <v>1.97076335356159</v>
+        <v>1.970763234904195</v>
       </c>
       <c r="F771" t="n">
         <v>6743600</v>
@@ -15852,16 +15852,16 @@
         <v>44910</v>
       </c>
       <c r="B772" t="n">
-        <v>1.906598687171936</v>
+        <v>1.906598567962646</v>
       </c>
       <c r="C772" t="n">
-        <v>2.04409387726485</v>
+        <v>2.044093749458731</v>
       </c>
       <c r="D772" t="n">
-        <v>1.897432355735247</v>
+        <v>1.897432237099079</v>
       </c>
       <c r="E772" t="n">
-        <v>1.952430562897961</v>
+        <v>1.952430440823052</v>
       </c>
       <c r="F772" t="n">
         <v>3868500</v>
@@ -15912,16 +15912,16 @@
         <v>44915</v>
       </c>
       <c r="B775" t="n">
-        <v>2.062426328659058</v>
+        <v>2.062426567077637</v>
       </c>
       <c r="C775" t="n">
-        <v>2.10825798114297</v>
+        <v>2.108258224859735</v>
       </c>
       <c r="D775" t="n">
-        <v>1.879099500180852</v>
+        <v>1.879099717406664</v>
       </c>
       <c r="E775" t="n">
-        <v>1.924931152664764</v>
+        <v>1.924931375188761</v>
       </c>
       <c r="F775" t="n">
         <v>8464700</v>
@@ -15932,16 +15932,16 @@
         <v>44916</v>
       </c>
       <c r="B776" t="n">
-        <v>1.970763206481934</v>
+        <v>1.970763087272644</v>
       </c>
       <c r="C776" t="n">
-        <v>2.108258176686496</v>
+        <v>2.108258049160288</v>
       </c>
       <c r="D776" t="n">
-        <v>1.961596875134963</v>
+        <v>1.961596756480134</v>
       </c>
       <c r="E776" t="n">
-        <v>2.053260188604671</v>
+        <v>2.05326006440523</v>
       </c>
       <c r="F776" t="n">
         <v>5125400</v>
@@ -15952,16 +15952,16 @@
         <v>44917</v>
       </c>
       <c r="B777" t="n">
-        <v>1.906598687171936</v>
+        <v>1.906598567962646</v>
       </c>
       <c r="C777" t="n">
-        <v>1.989095888644717</v>
+        <v>1.989095764277324</v>
       </c>
       <c r="D777" t="n">
-        <v>1.869933361425181</v>
+        <v>1.869933244508375</v>
       </c>
       <c r="E777" t="n">
-        <v>1.952430562897961</v>
+        <v>1.952430440823052</v>
       </c>
       <c r="F777" t="n">
         <v>5426000</v>
@@ -15972,16 +15972,16 @@
         <v>44918</v>
       </c>
       <c r="B778" t="n">
-        <v>1.9890958070755</v>
+        <v>1.98909592628479</v>
       </c>
       <c r="C778" t="n">
-        <v>2.016594800257883</v>
+        <v>2.016594921115226</v>
       </c>
       <c r="D778" t="n">
-        <v>1.906598608985781</v>
+        <v>1.906598723250898</v>
       </c>
       <c r="E778" t="n">
-        <v>1.915764940046575</v>
+        <v>1.915765054861043</v>
       </c>
       <c r="F778" t="n">
         <v>4257800</v>
@@ -15992,16 +15992,16 @@
         <v>44921</v>
       </c>
       <c r="B779" t="n">
-        <v>1.998262286186218</v>
+        <v>1.998262166976929</v>
       </c>
       <c r="C779" t="n">
-        <v>2.044093944885827</v>
+        <v>2.044093822942382</v>
       </c>
       <c r="D779" t="n">
-        <v>1.95243062748661</v>
+        <v>1.952430511011476</v>
       </c>
       <c r="E779" t="n">
-        <v>1.989095954446297</v>
+        <v>1.989095835783838</v>
       </c>
       <c r="F779" t="n">
         <v>2247800</v>
@@ -16012,16 +16012,16 @@
         <v>44922</v>
       </c>
       <c r="B780" t="n">
-        <v>1.970763206481934</v>
+        <v>1.970763087272644</v>
       </c>
       <c r="C780" t="n">
-        <v>2.062426519951642</v>
+        <v>2.06242639519774</v>
       </c>
       <c r="D780" t="n">
-        <v>1.934097662551472</v>
+        <v>1.934097545560041</v>
       </c>
       <c r="E780" t="n">
-        <v>2.007428531869817</v>
+        <v>2.007428410442682</v>
       </c>
       <c r="F780" t="n">
         <v>3370000</v>
@@ -16032,16 +16032,16 @@
         <v>44923</v>
       </c>
       <c r="B781" t="n">
-        <v>2.144923686981201</v>
+        <v>2.144923448562622</v>
       </c>
       <c r="C781" t="n">
-        <v>2.144923686981201</v>
+        <v>2.144923448562622</v>
       </c>
       <c r="D781" t="n">
-        <v>1.952430712100627</v>
+        <v>1.952430495078567</v>
       </c>
       <c r="E781" t="n">
-        <v>1.970763376374967</v>
+        <v>1.970763157315144</v>
       </c>
       <c r="F781" t="n">
         <v>4579800</v>
@@ -16112,16 +16112,16 @@
         <v>44930</v>
       </c>
       <c r="B785" t="n">
-        <v>2.062426328659058</v>
+        <v>2.062426567077637</v>
       </c>
       <c r="C785" t="n">
-        <v>2.062426328659058</v>
+        <v>2.062426567077637</v>
       </c>
       <c r="D785" t="n">
-        <v>1.952430362697669</v>
+        <v>1.952430588400603</v>
       </c>
       <c r="E785" t="n">
-        <v>1.961596693194451</v>
+        <v>1.961596919957022</v>
       </c>
       <c r="F785" t="n">
         <v>2931500</v>
@@ -16172,16 +16172,16 @@
         <v>44935</v>
       </c>
       <c r="B788" t="n">
-        <v>2.163256168365479</v>
+        <v>2.163255929946899</v>
       </c>
       <c r="C788" t="n">
-        <v>2.190755380994696</v>
+        <v>2.190755139545351</v>
       </c>
       <c r="D788" t="n">
-        <v>2.071592854743348</v>
+        <v>2.071592626427242</v>
       </c>
       <c r="E788" t="n">
-        <v>2.135757174278839</v>
+        <v>2.135756938891002</v>
       </c>
       <c r="F788" t="n">
         <v>5355300</v>
@@ -16232,16 +16232,16 @@
         <v>44938</v>
       </c>
       <c r="B791" t="n">
-        <v>2.337416410446167</v>
+        <v>2.337416648864746</v>
       </c>
       <c r="C791" t="n">
-        <v>2.410747271342309</v>
+        <v>2.410747517240701</v>
       </c>
       <c r="D791" t="n">
-        <v>2.19075512573899</v>
+        <v>2.190755349197985</v>
       </c>
       <c r="E791" t="n">
-        <v>2.282418428680975</v>
+        <v>2.282418661489711</v>
       </c>
       <c r="F791" t="n">
         <v>7447800</v>
@@ -16252,16 +16252,16 @@
         <v>44939</v>
       </c>
       <c r="B792" t="n">
-        <v>2.227420806884766</v>
+        <v>2.227420568466187</v>
       </c>
       <c r="C792" t="n">
-        <v>2.392414778844683</v>
+        <v>2.392414522765486</v>
       </c>
       <c r="D792" t="n">
-        <v>2.199921811558113</v>
+        <v>2.19992157608297</v>
       </c>
       <c r="E792" t="n">
-        <v>2.319084124640275</v>
+        <v>2.319083876410242</v>
       </c>
       <c r="F792" t="n">
         <v>4284200</v>
@@ -16272,16 +16272,16 @@
         <v>44942</v>
       </c>
       <c r="B793" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C793" t="n">
-        <v>2.869064242488531</v>
+        <v>2.869064517857597</v>
       </c>
       <c r="D793" t="n">
-        <v>2.291584774431394</v>
+        <v>2.29158499437473</v>
       </c>
       <c r="E793" t="n">
-        <v>2.749901729317672</v>
+        <v>2.749901993249675</v>
       </c>
       <c r="F793" t="n">
         <v>29414600</v>
@@ -16312,16 +16312,16 @@
         <v>44944</v>
       </c>
       <c r="B795" t="n">
-        <v>2.337416410446167</v>
+        <v>2.337416648864746</v>
       </c>
       <c r="C795" t="n">
-        <v>2.493244243990096</v>
+        <v>2.493244498303254</v>
       </c>
       <c r="D795" t="n">
-        <v>2.31908374985777</v>
+        <v>2.319083986406401</v>
       </c>
       <c r="E795" t="n">
-        <v>2.429079931930706</v>
+        <v>2.429080179699046</v>
       </c>
       <c r="F795" t="n">
         <v>5215700</v>
@@ -16352,16 +16352,16 @@
         <v>44946</v>
       </c>
       <c r="B797" t="n">
-        <v>2.814066410064697</v>
+        <v>2.814066171646118</v>
       </c>
       <c r="C797" t="n">
-        <v>2.823232741620247</v>
+        <v>2.823232502425061</v>
       </c>
       <c r="D797" t="n">
-        <v>2.291585074313209</v>
+        <v>2.291584880161267</v>
       </c>
       <c r="E797" t="n">
-        <v>2.300751405868758</v>
+        <v>2.30075121094021</v>
       </c>
       <c r="F797" t="n">
         <v>16674600</v>
@@ -16392,16 +16392,16 @@
         <v>44950</v>
       </c>
       <c r="B799" t="n">
-        <v>2.584908008575439</v>
+        <v>2.58490777015686</v>
       </c>
       <c r="C799" t="n">
-        <v>2.704070542224025</v>
+        <v>2.704070292814508</v>
       </c>
       <c r="D799" t="n">
-        <v>2.548242680850518</v>
+        <v>2.54824244581376</v>
       </c>
       <c r="E799" t="n">
-        <v>2.575741676644209</v>
+        <v>2.575741439071086</v>
       </c>
       <c r="F799" t="n">
         <v>6059800</v>
@@ -16452,16 +16452,16 @@
         <v>44953</v>
       </c>
       <c r="B802" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C802" t="n">
-        <v>2.933228810175975</v>
+        <v>2.933229055494139</v>
       </c>
       <c r="D802" t="n">
-        <v>2.704070312795705</v>
+        <v>2.704070538948388</v>
       </c>
       <c r="E802" t="n">
-        <v>2.731569306256229</v>
+        <v>2.731569534708767</v>
       </c>
       <c r="F802" t="n">
         <v>5877300</v>
@@ -16572,16 +16572,16 @@
         <v>44963</v>
       </c>
       <c r="B808" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C808" t="n">
-        <v>2.676571086469485</v>
+        <v>2.676571343363308</v>
       </c>
       <c r="D808" t="n">
-        <v>2.465745269738393</v>
+        <v>2.465745506397427</v>
       </c>
       <c r="E808" t="n">
-        <v>2.658238425757438</v>
+        <v>2.658238680891716</v>
       </c>
       <c r="F808" t="n">
         <v>3450900</v>
@@ -16692,16 +16692,16 @@
         <v>44971</v>
       </c>
       <c r="B814" t="n">
-        <v>2.034927606582642</v>
+        <v>2.034927368164062</v>
       </c>
       <c r="C814" t="n">
-        <v>2.172422582238004</v>
+        <v>2.172422327710077</v>
       </c>
       <c r="D814" t="n">
-        <v>2.007428611451569</v>
+        <v>2.00742837625486</v>
       </c>
       <c r="E814" t="n">
-        <v>2.099091928555144</v>
+        <v>2.099091682618869</v>
       </c>
       <c r="F814" t="n">
         <v>2996200</v>
@@ -16732,16 +16732,16 @@
         <v>44973</v>
       </c>
       <c r="B816" t="n">
-        <v>2.062426328659058</v>
+        <v>2.062426567077637</v>
       </c>
       <c r="C816" t="n">
-        <v>2.144923303130099</v>
+        <v>2.144923551085412</v>
       </c>
       <c r="D816" t="n">
-        <v>2.044093667665493</v>
+        <v>2.044093903964798</v>
       </c>
       <c r="E816" t="n">
-        <v>2.099091650646187</v>
+        <v>2.099091893303315</v>
       </c>
       <c r="F816" t="n">
         <v>2969500</v>
@@ -16752,16 +16752,16 @@
         <v>44974</v>
       </c>
       <c r="B817" t="n">
-        <v>1.961596965789795</v>
+        <v>1.961597084999084</v>
       </c>
       <c r="C817" t="n">
-        <v>2.099091942348662</v>
+        <v>2.099092069913735</v>
       </c>
       <c r="D817" t="n">
-        <v>1.961596965789795</v>
+        <v>1.961597084999084</v>
       </c>
       <c r="E817" t="n">
-        <v>2.053260283495706</v>
+        <v>2.053260408275518</v>
       </c>
       <c r="F817" t="n">
         <v>5027900</v>
@@ -16832,16 +16832,16 @@
         <v>44984</v>
       </c>
       <c r="B821" t="n">
-        <v>1.860767006874084</v>
+        <v>1.860766887664795</v>
       </c>
       <c r="C821" t="n">
-        <v>1.897432332165384</v>
+        <v>1.897432210607146</v>
       </c>
       <c r="D821" t="n">
-        <v>1.81493535025996</v>
+        <v>1.814935233986857</v>
       </c>
       <c r="E821" t="n">
-        <v>1.824101681582785</v>
+        <v>1.824101564722445</v>
       </c>
       <c r="F821" t="n">
         <v>2628700</v>
@@ -16892,16 +16892,16 @@
         <v>44987</v>
       </c>
       <c r="B824" t="n">
-        <v>1.998262286186218</v>
+        <v>1.998262166976929</v>
       </c>
       <c r="C824" t="n">
-        <v>2.144923594024966</v>
+        <v>2.144923466066379</v>
       </c>
       <c r="D824" t="n">
-        <v>1.970763290966453</v>
+        <v>1.970763173397657</v>
       </c>
       <c r="E824" t="n">
-        <v>2.126590930545122</v>
+        <v>2.126590803680198</v>
       </c>
       <c r="F824" t="n">
         <v>10060700</v>
@@ -16912,16 +16912,16 @@
         <v>44988</v>
       </c>
       <c r="B825" t="n">
-        <v>2.493244409561157</v>
+        <v>2.493244647979736</v>
       </c>
       <c r="C825" t="n">
-        <v>2.566575056784478</v>
+        <v>2.566575302215361</v>
       </c>
       <c r="D825" t="n">
-        <v>1.998262103718605</v>
+        <v>1.998262294804088</v>
       </c>
       <c r="E825" t="n">
-        <v>2.025761096427351</v>
+        <v>2.025761290142448</v>
       </c>
       <c r="F825" t="n">
         <v>20771000</v>
@@ -16972,16 +16972,16 @@
         <v>44993</v>
       </c>
       <c r="B828" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C828" t="n">
-        <v>2.905729816715452</v>
+        <v>2.90573005973376</v>
       </c>
       <c r="D828" t="n">
-        <v>2.694903981642197</v>
+        <v>2.694904207028261</v>
       </c>
       <c r="E828" t="n">
-        <v>2.704070312795705</v>
+        <v>2.704070538948388</v>
       </c>
       <c r="F828" t="n">
         <v>7104000</v>
@@ -17132,16 +17132,16 @@
         <v>45005</v>
       </c>
       <c r="B836" t="n">
-        <v>2.502411127090454</v>
+        <v>2.502410888671875</v>
       </c>
       <c r="C836" t="n">
-        <v>2.621573447239113</v>
+        <v>2.621573197467279</v>
       </c>
       <c r="D836" t="n">
-        <v>2.484078462452199</v>
+        <v>2.484078225780274</v>
       </c>
       <c r="E836" t="n">
-        <v>2.584908117962603</v>
+        <v>2.584907871684078</v>
       </c>
       <c r="F836" t="n">
         <v>2571800</v>
@@ -17152,16 +17152,16 @@
         <v>45006</v>
       </c>
       <c r="B837" t="n">
-        <v>2.502411127090454</v>
+        <v>2.502410888671875</v>
       </c>
       <c r="C837" t="n">
-        <v>2.539076456366965</v>
+        <v>2.539076214455076</v>
       </c>
       <c r="D837" t="n">
-        <v>2.474912130133071</v>
+        <v>2.474911894334474</v>
       </c>
       <c r="E837" t="n">
-        <v>2.52074379172871</v>
+        <v>2.520743551563476</v>
       </c>
       <c r="F837" t="n">
         <v>2400000</v>
@@ -17172,16 +17172,16 @@
         <v>45007</v>
       </c>
       <c r="B838" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C838" t="n">
-        <v>2.621572885790791</v>
+        <v>2.621573137405957</v>
       </c>
       <c r="D838" t="n">
-        <v>2.419913617958275</v>
+        <v>2.419913850218447</v>
       </c>
       <c r="E838" t="n">
-        <v>2.493244260806463</v>
+        <v>2.493244500104815</v>
       </c>
       <c r="F838" t="n">
         <v>4450900</v>
@@ -17192,16 +17192,16 @@
         <v>45008</v>
       </c>
       <c r="B839" t="n">
-        <v>2.383248329162598</v>
+        <v>2.383248090744019</v>
       </c>
       <c r="C839" t="n">
-        <v>2.493244523569952</v>
+        <v>2.493244274147426</v>
       </c>
       <c r="D839" t="n">
-        <v>2.300751347264015</v>
+        <v>2.300751117098379</v>
       </c>
       <c r="E839" t="n">
-        <v>2.484078192247887</v>
+        <v>2.484077943742355</v>
       </c>
       <c r="F839" t="n">
         <v>5291300</v>
@@ -17212,16 +17212,16 @@
         <v>45009</v>
       </c>
       <c r="B840" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C840" t="n">
-        <v>2.429080238828605</v>
+        <v>2.42907999298842</v>
       </c>
       <c r="D840" t="n">
-        <v>2.209088065430759</v>
+        <v>2.209087841855346</v>
       </c>
       <c r="E840" t="n">
-        <v>2.38324836302451</v>
+        <v>2.383248121822838</v>
       </c>
       <c r="F840" t="n">
         <v>8035300</v>
@@ -17232,16 +17232,16 @@
         <v>45012</v>
       </c>
       <c r="B841" t="n">
-        <v>2.502411127090454</v>
+        <v>2.502410888671875</v>
       </c>
       <c r="C841" t="n">
-        <v>2.55740912100522</v>
+        <v>2.557408877346677</v>
       </c>
       <c r="D841" t="n">
-        <v>2.364915923760939</v>
+        <v>2.36491569844229</v>
       </c>
       <c r="E841" t="n">
-        <v>2.364915923760939</v>
+        <v>2.36491569844229</v>
       </c>
       <c r="F841" t="n">
         <v>3948600</v>
@@ -17272,16 +17272,16 @@
         <v>45014</v>
       </c>
       <c r="B843" t="n">
-        <v>2.575741291046143</v>
+        <v>2.575741529464722</v>
       </c>
       <c r="C843" t="n">
-        <v>2.676571145737662</v>
+        <v>2.676571393489365</v>
       </c>
       <c r="D843" t="n">
-        <v>2.511576977133168</v>
+        <v>2.511577209612499</v>
       </c>
       <c r="E843" t="n">
-        <v>2.658238484619669</v>
+        <v>2.658238730674444</v>
       </c>
       <c r="F843" t="n">
         <v>3021100</v>
@@ -17472,16 +17472,16 @@
         <v>45029</v>
       </c>
       <c r="B853" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C853" t="n">
-        <v>2.960727803636499</v>
+        <v>2.960728051254518</v>
       </c>
       <c r="D853" t="n">
-        <v>2.740735637409736</v>
+        <v>2.740735866628893</v>
       </c>
       <c r="E853" t="n">
-        <v>2.804899955484291</v>
+        <v>2.804900190069778</v>
       </c>
       <c r="F853" t="n">
         <v>4826100</v>
@@ -17512,16 +17512,16 @@
         <v>45033</v>
       </c>
       <c r="B855" t="n">
-        <v>2.759068250656128</v>
+        <v>2.759068489074707</v>
       </c>
       <c r="C855" t="n">
-        <v>2.841565229570771</v>
+        <v>2.841565475118138</v>
       </c>
       <c r="D855" t="n">
-        <v>2.759068250656128</v>
+        <v>2.759068489074707</v>
       </c>
       <c r="E855" t="n">
-        <v>2.77740091263716</v>
+        <v>2.777401152639914</v>
       </c>
       <c r="F855" t="n">
         <v>2017100</v>
@@ -17532,16 +17532,16 @@
         <v>45034</v>
       </c>
       <c r="B856" t="n">
-        <v>2.667405128479004</v>
+        <v>2.667404890060425</v>
       </c>
       <c r="C856" t="n">
-        <v>2.823232766284694</v>
+        <v>2.823232513937895</v>
       </c>
       <c r="D856" t="n">
-        <v>2.612406920122646</v>
+        <v>2.612406686619929</v>
       </c>
       <c r="E856" t="n">
-        <v>2.804900103013436</v>
+        <v>2.804899852305252</v>
       </c>
       <c r="F856" t="n">
         <v>3770500</v>
@@ -17572,16 +17572,16 @@
         <v>45036</v>
       </c>
       <c r="B858" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242807388306</v>
       </c>
       <c r="C858" t="n">
-        <v>2.603240558142417</v>
+        <v>2.603240801706716</v>
       </c>
       <c r="D858" t="n">
-        <v>2.419913927566782</v>
+        <v>2.419914153978682</v>
       </c>
       <c r="E858" t="n">
-        <v>2.484078248268254</v>
+        <v>2.484078480683494</v>
       </c>
       <c r="F858" t="n">
         <v>4312900</v>
@@ -17672,16 +17672,16 @@
         <v>45044</v>
       </c>
       <c r="B863" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242807388306</v>
       </c>
       <c r="C863" t="n">
-        <v>2.62157322119998</v>
+        <v>2.62157346647952</v>
       </c>
       <c r="D863" t="n">
-        <v>2.438246590624346</v>
+        <v>2.438246818751485</v>
       </c>
       <c r="E863" t="n">
-        <v>2.465745585210691</v>
+        <v>2.46574581591069</v>
       </c>
       <c r="F863" t="n">
         <v>4247000</v>
@@ -17692,16 +17692,16 @@
         <v>45048</v>
       </c>
       <c r="B864" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="C864" t="n">
-        <v>2.749901926967264</v>
+        <v>2.749902171081845</v>
       </c>
       <c r="D864" t="n">
-        <v>2.419913791889924</v>
+        <v>2.419914006710763</v>
       </c>
       <c r="E864" t="n">
-        <v>2.54824242609789</v>
+        <v>2.548242652310732</v>
       </c>
       <c r="F864" t="n">
         <v>8626200</v>
@@ -17732,16 +17732,16 @@
         <v>45050</v>
       </c>
       <c r="B866" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232889175415</v>
       </c>
       <c r="C866" t="n">
-        <v>2.869064525602105</v>
+        <v>2.869064767891131</v>
       </c>
       <c r="D866" t="n">
-        <v>2.704070344369832</v>
+        <v>2.704070572725299</v>
       </c>
       <c r="E866" t="n">
-        <v>2.72240300689091</v>
+        <v>2.722403236794548</v>
       </c>
       <c r="F866" t="n">
         <v>5400200</v>
@@ -17772,16 +17772,16 @@
         <v>45054</v>
       </c>
       <c r="B868" t="n">
-        <v>3.12572193145752</v>
+        <v>3.125722169876099</v>
       </c>
       <c r="C868" t="n">
-        <v>3.199052579477732</v>
+        <v>3.199052823489703</v>
       </c>
       <c r="D868" t="n">
-        <v>3.015725740884632</v>
+        <v>3.015725970913106</v>
       </c>
       <c r="E868" t="n">
-        <v>3.024892071887158</v>
+        <v>3.024892302614806</v>
       </c>
       <c r="F868" t="n">
         <v>6228600</v>
@@ -17892,16 +17892,16 @@
         <v>45062</v>
       </c>
       <c r="B874" t="n">
-        <v>3.60237193107605</v>
+        <v>3.602371692657471</v>
       </c>
       <c r="C874" t="n">
-        <v>3.675702804771711</v>
+        <v>3.675702561499818</v>
       </c>
       <c r="D874" t="n">
-        <v>3.529041057380388</v>
+        <v>3.529040823815123</v>
       </c>
       <c r="E874" t="n">
-        <v>3.657369922440853</v>
+        <v>3.657369680382299</v>
       </c>
       <c r="F874" t="n">
         <v>5715400</v>
@@ -17912,16 +17912,16 @@
         <v>45063</v>
       </c>
       <c r="B875" t="n">
-        <v>3.92319393157959</v>
+        <v>3.923194169998169</v>
       </c>
       <c r="C875" t="n">
-        <v>3.92319393157959</v>
+        <v>3.923194169998169</v>
       </c>
       <c r="D875" t="n">
-        <v>3.629870877835498</v>
+        <v>3.62987109842838</v>
       </c>
       <c r="E875" t="n">
-        <v>3.64820354137668</v>
+        <v>3.648203763083666</v>
       </c>
       <c r="F875" t="n">
         <v>6160500</v>
@@ -17972,16 +17972,16 @@
         <v>45068</v>
       </c>
       <c r="B878" t="n">
-        <v>3.92319393157959</v>
+        <v>3.923194169998169</v>
       </c>
       <c r="C878" t="n">
-        <v>3.996524585744319</v>
+        <v>3.996524828619315</v>
       </c>
       <c r="D878" t="n">
-        <v>3.859029390642864</v>
+        <v>3.859029625162064</v>
       </c>
       <c r="E878" t="n">
-        <v>3.904861268038407</v>
+        <v>3.904861505342882</v>
       </c>
       <c r="F878" t="n">
         <v>3483600</v>
@@ -17992,16 +17992,16 @@
         <v>45069</v>
       </c>
       <c r="B879" t="n">
-        <v>3.941526412963867</v>
+        <v>3.941526174545288</v>
       </c>
       <c r="C879" t="n">
-        <v>4.134019589792833</v>
+        <v>4.134019339730554</v>
       </c>
       <c r="D879" t="n">
-        <v>3.877361874992493</v>
+        <v>3.877361640455157</v>
       </c>
       <c r="E879" t="n">
-        <v>3.886527987796886</v>
+        <v>3.886527752705101</v>
       </c>
       <c r="F879" t="n">
         <v>4348000</v>
@@ -18092,16 +18092,16 @@
         <v>45076</v>
       </c>
       <c r="B884" t="n">
-        <v>3.996524572372437</v>
+        <v>3.996524333953857</v>
       </c>
       <c r="C884" t="n">
-        <v>4.24401574789291</v>
+        <v>4.244015494709879</v>
       </c>
       <c r="D884" t="n">
-        <v>3.969025358610084</v>
+        <v>3.969025121832011</v>
       </c>
       <c r="E884" t="n">
-        <v>4.225683084413067</v>
+        <v>4.225682832323698</v>
       </c>
       <c r="F884" t="n">
         <v>3937000</v>
@@ -18172,16 +18172,16 @@
         <v>45082</v>
       </c>
       <c r="B888" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="C888" t="n">
-        <v>4.72066469090588</v>
+        <v>4.72066517241793</v>
       </c>
       <c r="D888" t="n">
-        <v>4.399842912066377</v>
+        <v>4.399843360854316</v>
       </c>
       <c r="E888" t="n">
-        <v>4.647334048552291</v>
+        <v>4.64733452258455</v>
       </c>
       <c r="F888" t="n">
         <v>6247400</v>
@@ -18232,16 +18232,16 @@
         <v>45086</v>
       </c>
       <c r="B891" t="n">
-        <v>4.354012012481689</v>
+        <v>4.354011535644531</v>
       </c>
       <c r="C891" t="n">
-        <v>4.500673329876966</v>
+        <v>4.500672836977939</v>
       </c>
       <c r="D891" t="n">
-        <v>4.289847467578654</v>
+        <v>4.289846997768588</v>
       </c>
       <c r="E891" t="n">
-        <v>4.454841886733544</v>
+        <v>4.454841398853827</v>
       </c>
       <c r="F891" t="n">
         <v>5651200</v>
@@ -18252,16 +18252,16 @@
         <v>45089</v>
       </c>
       <c r="B892" t="n">
-        <v>4.491506576538086</v>
+        <v>4.491506099700928</v>
       </c>
       <c r="C892" t="n">
-        <v>4.647334422624888</v>
+        <v>4.647333929244392</v>
       </c>
       <c r="D892" t="n">
-        <v>4.271514194684618</v>
+        <v>4.271513741202773</v>
       </c>
       <c r="E892" t="n">
-        <v>4.363177942089895</v>
+        <v>4.363177478876643</v>
       </c>
       <c r="F892" t="n">
         <v>6649300</v>
@@ -18272,16 +18272,16 @@
         <v>45090</v>
       </c>
       <c r="B893" t="n">
-        <v>4.289847373962402</v>
+        <v>4.289846897125244</v>
       </c>
       <c r="C893" t="n">
-        <v>4.592336990116809</v>
+        <v>4.592336479656477</v>
       </c>
       <c r="D893" t="n">
-        <v>4.234849381139381</v>
+        <v>4.234848910415514</v>
       </c>
       <c r="E893" t="n">
-        <v>4.537338560208595</v>
+        <v>4.537338055861602</v>
       </c>
       <c r="F893" t="n">
         <v>4358900</v>
@@ -18392,16 +18392,16 @@
         <v>45098</v>
       </c>
       <c r="B899" t="n">
-        <v>4.903992176055908</v>
+        <v>4.90399169921875</v>
       </c>
       <c r="C899" t="n">
-        <v>4.986489382037665</v>
+        <v>4.986488897178933</v>
       </c>
       <c r="D899" t="n">
-        <v>4.748164314572671</v>
+        <v>4.748163852887355</v>
       </c>
       <c r="E899" t="n">
-        <v>4.821495407159335</v>
+        <v>4.821494938343708</v>
       </c>
       <c r="F899" t="n">
         <v>4163100</v>
@@ -18412,16 +18412,16 @@
         <v>45099</v>
       </c>
       <c r="B900" t="n">
-        <v>4.766496658325195</v>
+        <v>4.766496181488037</v>
       </c>
       <c r="C900" t="n">
-        <v>4.858160408630997</v>
+        <v>4.858159922623858</v>
       </c>
       <c r="D900" t="n">
-        <v>4.592336581748543</v>
+        <v>4.592336122334244</v>
       </c>
       <c r="E900" t="n">
-        <v>4.757330545545708</v>
+        <v>4.757330069625522</v>
       </c>
       <c r="F900" t="n">
         <v>4737400</v>
@@ -18572,16 +18572,16 @@
         <v>45111</v>
       </c>
       <c r="B908" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C908" t="n">
-        <v>5.087319262304525</v>
+        <v>5.087318782005757</v>
       </c>
       <c r="D908" t="n">
-        <v>4.876493408763784</v>
+        <v>4.87649294836929</v>
       </c>
       <c r="E908" t="n">
-        <v>4.94065751391628</v>
+        <v>4.940657047463991</v>
       </c>
       <c r="F908" t="n">
         <v>2828200</v>
@@ -18612,16 +18612,16 @@
         <v>45113</v>
       </c>
       <c r="B910" t="n">
-        <v>5.087318897247314</v>
+        <v>5.087319374084473</v>
       </c>
       <c r="C910" t="n">
-        <v>5.224813648184956</v>
+        <v>5.22481413790957</v>
       </c>
       <c r="D910" t="n">
-        <v>5.041487022211331</v>
+        <v>5.041487494752643</v>
       </c>
       <c r="E910" t="n">
-        <v>5.206480985587593</v>
+        <v>5.206481473593878</v>
       </c>
       <c r="F910" t="n">
         <v>3192100</v>
@@ -18672,16 +18672,16 @@
         <v>45118</v>
       </c>
       <c r="B913" t="n">
-        <v>5.096485137939453</v>
+        <v>5.096485614776611</v>
       </c>
       <c r="C913" t="n">
-        <v>5.114817800997017</v>
+        <v>5.114818279549415</v>
       </c>
       <c r="D913" t="n">
-        <v>4.858160518191128</v>
+        <v>4.858160972730167</v>
       </c>
       <c r="E913" t="n">
-        <v>5.105651688010817</v>
+        <v>5.105652165705616</v>
       </c>
       <c r="F913" t="n">
         <v>3857700</v>
@@ -18692,16 +18692,16 @@
         <v>45119</v>
       </c>
       <c r="B914" t="n">
-        <v>5.325643539428711</v>
+        <v>5.325643062591553</v>
       </c>
       <c r="C914" t="n">
-        <v>5.573134704356201</v>
+        <v>5.573134205359659</v>
       </c>
       <c r="D914" t="n">
-        <v>5.178982237867281</v>
+        <v>5.178981774161598</v>
       </c>
       <c r="E914" t="n">
-        <v>5.178982237867281</v>
+        <v>5.178981774161598</v>
       </c>
       <c r="F914" t="n">
         <v>7685700</v>
@@ -18712,16 +18712,16 @@
         <v>45120</v>
       </c>
       <c r="B915" t="n">
-        <v>5.096485137939453</v>
+        <v>5.096485614776611</v>
       </c>
       <c r="C915" t="n">
-        <v>5.453972286104523</v>
+        <v>5.453972796388881</v>
       </c>
       <c r="D915" t="n">
-        <v>4.995655272580271</v>
+        <v>4.99565573998359</v>
       </c>
       <c r="E915" t="n">
-        <v>5.334810194772943</v>
+        <v>5.334810693908262</v>
       </c>
       <c r="F915" t="n">
         <v>4692200</v>
@@ -18732,16 +18732,16 @@
         <v>45121</v>
       </c>
       <c r="B916" t="n">
-        <v>4.482339859008789</v>
+        <v>4.482340335845947</v>
       </c>
       <c r="C916" t="n">
-        <v>4.903991507767135</v>
+        <v>4.903992029460144</v>
       </c>
       <c r="D916" t="n">
-        <v>4.381510439977321</v>
+        <v>4.381510906088113</v>
       </c>
       <c r="E916" t="n">
-        <v>4.858160072866955</v>
+        <v>4.858160589684357</v>
       </c>
       <c r="F916" t="n">
         <v>15771400</v>
@@ -18772,16 +18772,16 @@
         <v>45125</v>
       </c>
       <c r="B918" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C918" t="n">
-        <v>5.041486503749065</v>
+        <v>5.041486987624404</v>
       </c>
       <c r="D918" t="n">
-        <v>4.711498173847115</v>
+        <v>4.711498626050601</v>
       </c>
       <c r="E918" t="n">
-        <v>4.720664722745693</v>
+        <v>4.720665175828972</v>
       </c>
       <c r="F918" t="n">
         <v>5384000</v>
@@ -18812,16 +18812,16 @@
         <v>45127</v>
       </c>
       <c r="B920" t="n">
-        <v>4.876493453979492</v>
+        <v>4.876492977142334</v>
       </c>
       <c r="C920" t="n">
-        <v>5.004822102559555</v>
+        <v>5.004821613174064</v>
       </c>
       <c r="D920" t="n">
-        <v>4.784829696479972</v>
+        <v>4.784829228605952</v>
       </c>
       <c r="E920" t="n">
-        <v>4.958990223809796</v>
+        <v>4.958989738905873</v>
       </c>
       <c r="F920" t="n">
         <v>2200400</v>
@@ -18832,16 +18832,16 @@
         <v>45128</v>
       </c>
       <c r="B921" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C921" t="n">
-        <v>5.169815198316529</v>
+        <v>5.169815688182035</v>
       </c>
       <c r="D921" t="n">
-        <v>4.85815996201701</v>
+        <v>4.858160422351643</v>
       </c>
       <c r="E921" t="n">
-        <v>4.85815996201701</v>
+        <v>4.858160422351643</v>
       </c>
       <c r="F921" t="n">
         <v>3946200</v>
@@ -18852,16 +18852,16 @@
         <v>45131</v>
       </c>
       <c r="B922" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C922" t="n">
-        <v>5.105651103503303</v>
+        <v>5.105651587288944</v>
       </c>
       <c r="D922" t="n">
-        <v>4.885658734912646</v>
+        <v>4.885659197852923</v>
       </c>
       <c r="E922" t="n">
-        <v>5.068985781585712</v>
+        <v>5.068986261897133</v>
       </c>
       <c r="F922" t="n">
         <v>2320000</v>
@@ -18872,16 +18872,16 @@
         <v>45132</v>
       </c>
       <c r="B923" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C923" t="n">
-        <v>5.270645052132461</v>
+        <v>5.270645551552092</v>
       </c>
       <c r="D923" t="n">
-        <v>4.995654700665417</v>
+        <v>4.995655174028355</v>
       </c>
       <c r="E923" t="n">
-        <v>5.096484554481348</v>
+        <v>5.096485037398413</v>
       </c>
       <c r="F923" t="n">
         <v>3865600</v>
@@ -18952,16 +18952,16 @@
         <v>45138</v>
       </c>
       <c r="B927" t="n">
-        <v>5.224813461303711</v>
+        <v>5.224813938140869</v>
       </c>
       <c r="C927" t="n">
-        <v>5.389807855863602</v>
+        <v>5.389808347758803</v>
       </c>
       <c r="D927" t="n">
-        <v>5.087318715283986</v>
+        <v>5.087319179572829</v>
       </c>
       <c r="E927" t="n">
-        <v>5.087318715283986</v>
+        <v>5.087319179572829</v>
       </c>
       <c r="F927" t="n">
         <v>3571100</v>
@@ -18972,16 +18972,16 @@
         <v>45139</v>
       </c>
       <c r="B928" t="n">
-        <v>5.417306423187256</v>
+        <v>5.417306900024414</v>
       </c>
       <c r="C928" t="n">
-        <v>5.426472972350305</v>
+        <v>5.426473449994312</v>
       </c>
       <c r="D928" t="n">
-        <v>4.99565477755969</v>
+        <v>4.995655217282615</v>
       </c>
       <c r="E928" t="n">
-        <v>5.17898182705457</v>
+        <v>5.17898228291414</v>
       </c>
       <c r="F928" t="n">
         <v>5677300</v>
@@ -18992,16 +18992,16 @@
         <v>45140</v>
       </c>
       <c r="B929" t="n">
-        <v>5.334810256958008</v>
+        <v>5.33480978012085</v>
       </c>
       <c r="C929" t="n">
-        <v>5.518136889670584</v>
+        <v>5.518136396447286</v>
       </c>
       <c r="D929" t="n">
-        <v>5.215647727152248</v>
+        <v>5.215647260966101</v>
       </c>
       <c r="E929" t="n">
-        <v>5.472305012949855</v>
+        <v>5.472304523823111</v>
       </c>
       <c r="F929" t="n">
         <v>6874400</v>
@@ -19032,16 +19032,16 @@
         <v>45142</v>
       </c>
       <c r="B931" t="n">
-        <v>5.628132820129395</v>
+        <v>5.628132343292236</v>
       </c>
       <c r="C931" t="n">
-        <v>5.655632033338626</v>
+        <v>5.655631554171628</v>
       </c>
       <c r="D931" t="n">
-        <v>5.31647754724071</v>
+        <v>5.316477096808192</v>
       </c>
       <c r="E931" t="n">
-        <v>5.325643660253677</v>
+        <v>5.32564320904457</v>
       </c>
       <c r="F931" t="n">
         <v>4666200</v>
@@ -19092,16 +19092,16 @@
         <v>45147</v>
       </c>
       <c r="B934" t="n">
-        <v>5.224813461303711</v>
+        <v>5.224813938140869</v>
       </c>
       <c r="C934" t="n">
-        <v>5.453971954116771</v>
+        <v>5.45397245186784</v>
       </c>
       <c r="D934" t="n">
-        <v>5.197314686933821</v>
+        <v>5.197315161261333</v>
       </c>
       <c r="E934" t="n">
-        <v>5.26147878518699</v>
+        <v>5.261479265370371</v>
       </c>
       <c r="F934" t="n">
         <v>3345000</v>
@@ -19152,16 +19152,16 @@
         <v>45152</v>
       </c>
       <c r="B937" t="n">
-        <v>6.068116664886475</v>
+        <v>6.068117141723633</v>
       </c>
       <c r="C937" t="n">
-        <v>6.288109040924345</v>
+        <v>6.28810953504867</v>
       </c>
       <c r="D937" t="n">
-        <v>5.985619906321761</v>
+        <v>5.985620376676263</v>
       </c>
       <c r="E937" t="n">
-        <v>6.141447311204055</v>
+        <v>6.14144779380359</v>
       </c>
       <c r="F937" t="n">
         <v>5683800</v>
@@ -19232,16 +19232,16 @@
         <v>45156</v>
       </c>
       <c r="B941" t="n">
-        <v>5.710629463195801</v>
+        <v>5.710629940032959</v>
       </c>
       <c r="C941" t="n">
-        <v>5.838958092401009</v>
+        <v>5.838958579953599</v>
       </c>
       <c r="D941" t="n">
-        <v>5.33480968769513</v>
+        <v>5.334810133151363</v>
       </c>
       <c r="E941" t="n">
-        <v>5.609799607420576</v>
+        <v>5.609800075838448</v>
       </c>
       <c r="F941" t="n">
         <v>5405200</v>
@@ -19252,16 +19252,16 @@
         <v>45159</v>
       </c>
       <c r="B942" t="n">
-        <v>5.490637302398682</v>
+        <v>5.490636825561523</v>
       </c>
       <c r="C942" t="n">
-        <v>5.701463134206945</v>
+        <v>5.701462639060511</v>
       </c>
       <c r="D942" t="n">
-        <v>5.463138527906596</v>
+        <v>5.463138053457582</v>
       </c>
       <c r="E942" t="n">
-        <v>5.673964359714859</v>
+        <v>5.67396386695657</v>
       </c>
       <c r="F942" t="n">
         <v>3510600</v>
@@ -19272,16 +19272,16 @@
         <v>45160</v>
       </c>
       <c r="B943" t="n">
-        <v>5.628132820129395</v>
+        <v>5.628132343292236</v>
       </c>
       <c r="C943" t="n">
-        <v>5.646465483240493</v>
+        <v>5.646465004850121</v>
       </c>
       <c r="D943" t="n">
-        <v>5.408140862796206</v>
+        <v>5.408140404597616</v>
       </c>
       <c r="E943" t="n">
-        <v>5.563968717783131</v>
+        <v>5.563968246382204</v>
       </c>
       <c r="F943" t="n">
         <v>4158800</v>
@@ -19412,16 +19412,16 @@
         <v>45169</v>
       </c>
       <c r="B950" t="n">
-        <v>4.903992176055908</v>
+        <v>4.90399169921875</v>
       </c>
       <c r="C950" t="n">
-        <v>5.032320823183499</v>
+        <v>5.03232033386837</v>
       </c>
       <c r="D950" t="n">
-        <v>4.858160734910076</v>
+        <v>4.858160262529314</v>
       </c>
       <c r="E950" t="n">
-        <v>5.032320823183499</v>
+        <v>5.03232033386837</v>
       </c>
       <c r="F950" t="n">
         <v>3681000</v>
@@ -19432,16 +19432,16 @@
         <v>45170</v>
       </c>
       <c r="B951" t="n">
-        <v>5.151482582092285</v>
+        <v>5.151483058929443</v>
       </c>
       <c r="C951" t="n">
-        <v>5.169815243210278</v>
+        <v>5.169815721744364</v>
       </c>
       <c r="D951" t="n">
-        <v>4.876492665322393</v>
+        <v>4.876493116705634</v>
       </c>
       <c r="E951" t="n">
-        <v>4.949823309794364</v>
+        <v>4.949823767965317</v>
       </c>
       <c r="F951" t="n">
         <v>4962000</v>
@@ -19472,16 +19472,16 @@
         <v>45174</v>
       </c>
       <c r="B953" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C953" t="n">
-        <v>5.032319954850488</v>
+        <v>5.032320437846034</v>
       </c>
       <c r="D953" t="n">
-        <v>4.858159896628598</v>
+        <v>4.858160362908486</v>
       </c>
       <c r="E953" t="n">
-        <v>4.995654633426395</v>
+        <v>4.99565511290285</v>
       </c>
       <c r="F953" t="n">
         <v>3096400</v>
@@ -19492,16 +19492,16 @@
         <v>45175</v>
       </c>
       <c r="B954" t="n">
-        <v>4.986488819122314</v>
+        <v>4.986489295959473</v>
       </c>
       <c r="C954" t="n">
-        <v>5.105651339402779</v>
+        <v>5.105651827634952</v>
       </c>
       <c r="D954" t="n">
-        <v>4.949823495510654</v>
+        <v>4.94982396884166</v>
       </c>
       <c r="E954" t="n">
-        <v>4.949823495510654</v>
+        <v>4.94982396884166</v>
       </c>
       <c r="F954" t="n">
         <v>4361600</v>
@@ -19512,16 +19512,16 @@
         <v>45177</v>
       </c>
       <c r="B955" t="n">
-        <v>4.876493453979492</v>
+        <v>4.876492977142334</v>
       </c>
       <c r="C955" t="n">
-        <v>5.004822102559555</v>
+        <v>5.004821613174064</v>
       </c>
       <c r="D955" t="n">
-        <v>4.867326903395464</v>
+        <v>4.867326427454637</v>
       </c>
       <c r="E955" t="n">
-        <v>4.977322887892662</v>
+        <v>4.97732240119612</v>
       </c>
       <c r="F955" t="n">
         <v>2168000</v>
@@ -19552,16 +19552,16 @@
         <v>45181</v>
       </c>
       <c r="B957" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C957" t="n">
-        <v>5.105651926217408</v>
+        <v>5.105651444187835</v>
       </c>
       <c r="D957" t="n">
-        <v>4.913158736589549</v>
+        <v>4.913158272733446</v>
       </c>
       <c r="E957" t="n">
-        <v>4.913158736589549</v>
+        <v>4.913158272733446</v>
       </c>
       <c r="F957" t="n">
         <v>2356100</v>
@@ -19672,16 +19672,16 @@
         <v>45189</v>
       </c>
       <c r="B963" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C963" t="n">
-        <v>5.114817146597253</v>
+        <v>5.114817637510772</v>
       </c>
       <c r="D963" t="n">
-        <v>4.711498173847115</v>
+        <v>4.711498626050601</v>
       </c>
       <c r="E963" t="n">
-        <v>4.720664722745693</v>
+        <v>4.720665175828972</v>
       </c>
       <c r="F963" t="n">
         <v>5388800</v>
@@ -19712,16 +19712,16 @@
         <v>45191</v>
       </c>
       <c r="B965" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="C965" t="n">
-        <v>4.867325975613057</v>
+        <v>4.86732647208469</v>
       </c>
       <c r="D965" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="E965" t="n">
-        <v>4.812327993847866</v>
+        <v>4.812328484709655</v>
       </c>
       <c r="F965" t="n">
         <v>2426200</v>
@@ -19752,16 +19752,16 @@
         <v>45195</v>
       </c>
       <c r="B967" t="n">
-        <v>4.491506576538086</v>
+        <v>4.491506099700928</v>
       </c>
       <c r="C967" t="n">
-        <v>4.784829169562522</v>
+        <v>4.784828661585008</v>
       </c>
       <c r="D967" t="n">
-        <v>4.418175928281977</v>
+        <v>4.418175459229907</v>
       </c>
       <c r="E967" t="n">
-        <v>4.574003337283638</v>
+        <v>4.574002851688278</v>
       </c>
       <c r="F967" t="n">
         <v>4192900</v>
@@ -19852,16 +19852,16 @@
         <v>45202</v>
       </c>
       <c r="B972" t="n">
-        <v>4.31734561920166</v>
+        <v>4.317346096038818</v>
       </c>
       <c r="C972" t="n">
-        <v>4.674832710799063</v>
+        <v>4.674833227119539</v>
       </c>
       <c r="D972" t="n">
-        <v>4.308179070580783</v>
+        <v>4.308179546405524</v>
       </c>
       <c r="E972" t="n">
-        <v>4.619834730329086</v>
+        <v>4.619835240575209</v>
       </c>
       <c r="F972" t="n">
         <v>3808300</v>
@@ -19892,16 +19892,16 @@
         <v>45204</v>
       </c>
       <c r="B974" t="n">
-        <v>4.537337779998779</v>
+        <v>4.537338256835938</v>
       </c>
       <c r="C974" t="n">
-        <v>4.793995472791623</v>
+        <v>4.79399597660141</v>
       </c>
       <c r="D974" t="n">
-        <v>4.528171667980348</v>
+        <v>4.528172143854223</v>
       </c>
       <c r="E974" t="n">
-        <v>4.674832956956192</v>
+        <v>4.67483344824297</v>
       </c>
       <c r="F974" t="n">
         <v>3401000</v>
@@ -20032,16 +20032,16 @@
         <v>45216</v>
       </c>
       <c r="B981" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="C981" t="n">
-        <v>4.812327993847866</v>
+        <v>4.812328484709655</v>
       </c>
       <c r="D981" t="n">
-        <v>4.601502178538746</v>
+        <v>4.601502647896112</v>
       </c>
       <c r="E981" t="n">
-        <v>4.656500160303938</v>
+        <v>4.656500635271147</v>
       </c>
       <c r="F981" t="n">
         <v>2762000</v>
@@ -20052,16 +20052,16 @@
         <v>45217</v>
       </c>
       <c r="B982" t="n">
-        <v>4.509839057922363</v>
+        <v>4.509839534759521</v>
       </c>
       <c r="C982" t="n">
-        <v>4.67483300988838</v>
+        <v>4.674833504170784</v>
       </c>
       <c r="D982" t="n">
-        <v>4.418175751274577</v>
+        <v>4.418176218419932</v>
       </c>
       <c r="E982" t="n">
-        <v>4.647334236436606</v>
+        <v>4.647334727811492</v>
       </c>
       <c r="F982" t="n">
         <v>3515800</v>
@@ -20132,16 +20132,16 @@
         <v>45223</v>
       </c>
       <c r="B986" t="n">
-        <v>4.711498737335205</v>
+        <v>4.711498260498047</v>
       </c>
       <c r="C986" t="n">
-        <v>4.79399593894851</v>
+        <v>4.793995453762048</v>
       </c>
       <c r="D986" t="n">
-        <v>4.619835422812178</v>
+        <v>4.619834955251998</v>
       </c>
       <c r="E986" t="n">
-        <v>4.683999961520877</v>
+        <v>4.683999487466791</v>
       </c>
       <c r="F986" t="n">
         <v>2628000</v>
@@ -20172,16 +20172,16 @@
         <v>45225</v>
       </c>
       <c r="B988" t="n">
-        <v>4.79399585723877</v>
+        <v>4.793996334075928</v>
       </c>
       <c r="C988" t="n">
-        <v>4.858160394853837</v>
+        <v>4.858160878073153</v>
       </c>
       <c r="D988" t="n">
-        <v>4.601502681478721</v>
+        <v>4.60150313916945</v>
       </c>
       <c r="E988" t="n">
-        <v>4.601502681478721</v>
+        <v>4.60150313916945</v>
       </c>
       <c r="F988" t="n">
         <v>4908400</v>
@@ -20192,16 +20192,16 @@
         <v>45226</v>
       </c>
       <c r="B989" t="n">
-        <v>4.766496658325195</v>
+        <v>4.766496181488037</v>
       </c>
       <c r="C989" t="n">
-        <v>4.977322497275261</v>
+        <v>4.977321999347226</v>
       </c>
       <c r="D989" t="n">
-        <v>4.720665220257449</v>
+        <v>4.720664748005237</v>
       </c>
       <c r="E989" t="n">
-        <v>4.803161983613454</v>
+        <v>4.803161503108321</v>
       </c>
       <c r="F989" t="n">
         <v>2912800</v>
@@ -20252,16 +20252,16 @@
         <v>45231</v>
       </c>
       <c r="B992" t="n">
-        <v>4.80316162109375</v>
+        <v>4.803162097930908</v>
       </c>
       <c r="C992" t="n">
-        <v>4.848993492787479</v>
+        <v>4.848993974174629</v>
       </c>
       <c r="D992" t="n">
-        <v>4.656500331010008</v>
+        <v>4.656500793287267</v>
       </c>
       <c r="E992" t="n">
-        <v>4.729830976051879</v>
+        <v>4.729831445609087</v>
       </c>
       <c r="F992" t="n">
         <v>2720700</v>
@@ -20332,16 +20332,16 @@
         <v>45238</v>
       </c>
       <c r="B996" t="n">
-        <v>5.518136501312256</v>
+        <v>5.518136978149414</v>
       </c>
       <c r="C996" t="n">
-        <v>5.573134487255351</v>
+        <v>5.573134968845035</v>
       </c>
       <c r="D996" t="n">
-        <v>5.316477219520905</v>
+        <v>5.316477678932137</v>
       </c>
       <c r="E996" t="n">
-        <v>5.316477219520905</v>
+        <v>5.316477678932137</v>
       </c>
       <c r="F996" t="n">
         <v>4022900</v>
@@ -20352,16 +20352,16 @@
         <v>45239</v>
       </c>
       <c r="B997" t="n">
-        <v>5.618966579437256</v>
+        <v>5.618966102600098</v>
       </c>
       <c r="C997" t="n">
-        <v>5.728962555604424</v>
+        <v>5.728962069432778</v>
       </c>
       <c r="D997" t="n">
-        <v>5.417306852712293</v>
+        <v>5.417306392988397</v>
       </c>
       <c r="E997" t="n">
-        <v>5.5823012540482</v>
+        <v>5.582300780322537</v>
       </c>
       <c r="F997" t="n">
         <v>3100500</v>
@@ -20392,16 +20392,16 @@
         <v>45243</v>
       </c>
       <c r="B999" t="n">
-        <v>6.810590267181396</v>
+        <v>6.810590744018555</v>
       </c>
       <c r="C999" t="n">
-        <v>7.140578620094379</v>
+        <v>7.140579120035365</v>
       </c>
       <c r="D999" t="n">
-        <v>6.544766449777509</v>
+        <v>6.544766908003258</v>
       </c>
       <c r="E999" t="n">
-        <v>6.608930985286603</v>
+        <v>6.608931448004774</v>
       </c>
       <c r="F999" t="n">
         <v>8835300</v>
@@ -20432,16 +20432,16 @@
         <v>45246</v>
       </c>
       <c r="B1001" t="n">
-        <v>7.360570430755615</v>
+        <v>7.360570907592773</v>
       </c>
       <c r="C1001" t="n">
-        <v>7.562230146085571</v>
+        <v>7.562230635986777</v>
       </c>
       <c r="D1001" t="n">
-        <v>6.627263527325669</v>
+        <v>6.627263956657273</v>
       </c>
       <c r="E1001" t="n">
-        <v>6.783091369966508</v>
+        <v>6.78309180939305</v>
       </c>
       <c r="F1001" t="n">
         <v>9976600</v>
@@ -20452,16 +20452,16 @@
         <v>45247</v>
       </c>
       <c r="B1002" t="n">
-        <v>7.635561466217041</v>
+        <v>7.635560989379883</v>
       </c>
       <c r="C1002" t="n">
-        <v>7.699725569139261</v>
+        <v>7.699725088295085</v>
       </c>
       <c r="D1002" t="n">
-        <v>7.333072303626092</v>
+        <v>7.333071845679237</v>
       </c>
       <c r="E1002" t="n">
-        <v>7.41556950690914</v>
+        <v>7.415569043810375</v>
       </c>
       <c r="F1002" t="n">
         <v>5823800</v>
@@ -20492,16 +20492,16 @@
         <v>45251</v>
       </c>
       <c r="B1004" t="n">
-        <v>7.424735546112061</v>
+        <v>7.424736022949219</v>
       </c>
       <c r="C1004" t="n">
-        <v>7.543897193575265</v>
+        <v>7.543897678065316</v>
       </c>
       <c r="D1004" t="n">
-        <v>7.287239925379449</v>
+        <v>7.287240393386257</v>
       </c>
       <c r="E1004" t="n">
-        <v>7.543897193575265</v>
+        <v>7.543897678065316</v>
       </c>
       <c r="F1004" t="n">
         <v>4025000</v>
@@ -20532,16 +20532,16 @@
         <v>45253</v>
       </c>
       <c r="B1006" t="n">
-        <v>7.094747066497803</v>
+        <v>7.094747543334961</v>
       </c>
       <c r="C1006" t="n">
-        <v>7.32390557025422</v>
+        <v>7.323906062493096</v>
       </c>
       <c r="D1006" t="n">
-        <v>7.094747066497803</v>
+        <v>7.094747543334961</v>
       </c>
       <c r="E1006" t="n">
-        <v>7.314739457388246</v>
+        <v>7.314739949011068</v>
       </c>
       <c r="F1006" t="n">
         <v>2414400</v>
@@ -20612,16 +20612,16 @@
         <v>45259</v>
       </c>
       <c r="B1010" t="n">
-        <v>7.443068027496338</v>
+        <v>7.44306755065918</v>
       </c>
       <c r="C1010" t="n">
-        <v>7.763890279422943</v>
+        <v>7.763889782032437</v>
       </c>
       <c r="D1010" t="n">
-        <v>7.16807808781159</v>
+        <v>7.168077628591552</v>
       </c>
       <c r="E1010" t="n">
-        <v>7.213909525883136</v>
+        <v>7.213909063726926</v>
       </c>
       <c r="F1010" t="n">
         <v>6571400</v>
@@ -20752,16 +20752,16 @@
         <v>45268</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.718058109283447</v>
+        <v>7.718058586120605</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.800555306578421</v>
+        <v>7.800555788512423</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.580563363238674</v>
+        <v>7.580563831581132</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.69972501025333</v>
+        <v>7.699725485957833</v>
       </c>
       <c r="F1017" t="n">
         <v>1787800</v>
@@ -20772,16 +20772,16 @@
         <v>45271</v>
       </c>
       <c r="B1018" t="n">
-        <v>7.672226428985596</v>
+        <v>7.672226905822754</v>
       </c>
       <c r="C1018" t="n">
-        <v>7.892218377862459</v>
+        <v>7.892218868372355</v>
       </c>
       <c r="D1018" t="n">
-        <v>7.626394554427008</v>
+        <v>7.626395028415665</v>
       </c>
       <c r="E1018" t="n">
-        <v>7.699725204052629</v>
+        <v>7.699725682598865</v>
       </c>
       <c r="F1018" t="n">
         <v>2800600</v>
@@ -20872,16 +20872,16 @@
         <v>45278</v>
       </c>
       <c r="B1023" t="n">
-        <v>7.443068027496338</v>
+        <v>7.44306755065918</v>
       </c>
       <c r="C1023" t="n">
-        <v>7.681393078974941</v>
+        <v>7.681392586869585</v>
       </c>
       <c r="D1023" t="n">
-        <v>7.415569252070441</v>
+        <v>7.415568776994981</v>
       </c>
       <c r="E1023" t="n">
-        <v>7.516398678078938</v>
+        <v>7.516398196543881</v>
       </c>
       <c r="F1023" t="n">
         <v>2448800</v>
@@ -20932,16 +20932,16 @@
         <v>45281</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.498066425323486</v>
+        <v>7.498065948486328</v>
       </c>
       <c r="C1026" t="n">
-        <v>7.653894275788911</v>
+        <v>7.653893789041931</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.40640267534254</v>
+        <v>7.406402204334709</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.461401100165169</v>
+        <v>7.461400625659731</v>
       </c>
       <c r="F1026" t="n">
         <v>2110700</v>
@@ -20972,16 +20972,16 @@
         <v>45286</v>
       </c>
       <c r="B1028" t="n">
-        <v>7.177244663238525</v>
+        <v>7.177244186401367</v>
       </c>
       <c r="C1028" t="n">
-        <v>7.433901956821806</v>
+        <v>7.433901462933017</v>
       </c>
       <c r="D1028" t="n">
-        <v>7.168078549867428</v>
+        <v>7.168078073639243</v>
       </c>
       <c r="E1028" t="n">
-        <v>7.378904402424857</v>
+        <v>7.37890391218996</v>
       </c>
       <c r="F1028" t="n">
         <v>1748700</v>
@@ -20992,16 +20992,16 @@
         <v>45287</v>
       </c>
       <c r="B1029" t="n">
-        <v>7.232241630554199</v>
+        <v>7.232242107391357</v>
       </c>
       <c r="C1029" t="n">
-        <v>7.333071485868728</v>
+        <v>7.333071969353814</v>
       </c>
       <c r="D1029" t="n">
-        <v>7.140578324397864</v>
+        <v>7.140578795191465</v>
       </c>
       <c r="E1029" t="n">
-        <v>7.195576308091665</v>
+        <v>7.195576782511401</v>
       </c>
       <c r="F1029" t="n">
         <v>1937700</v>
@@ -21012,16 +21012,16 @@
         <v>45288</v>
       </c>
       <c r="B1030" t="n">
-        <v>7.177244663238525</v>
+        <v>7.177244186401367</v>
       </c>
       <c r="C1030" t="n">
-        <v>7.314739860486446</v>
+        <v>7.31473937451447</v>
       </c>
       <c r="D1030" t="n">
-        <v>7.103914007929016</v>
+        <v>7.103913535963753</v>
       </c>
       <c r="E1030" t="n">
-        <v>7.22307654134956</v>
+        <v>7.223076061467453</v>
       </c>
       <c r="F1030" t="n">
         <v>1438100</v>
@@ -21032,16 +21032,16 @@
         <v>45293</v>
       </c>
       <c r="B1031" t="n">
-        <v>6.893087863922119</v>
+        <v>6.893087387084961</v>
       </c>
       <c r="C1031" t="n">
-        <v>7.204743572895473</v>
+        <v>7.204743074499178</v>
       </c>
       <c r="D1031" t="n">
-        <v>6.828923324696675</v>
+        <v>6.828922852298171</v>
       </c>
       <c r="E1031" t="n">
-        <v>7.195577022826767</v>
+        <v>7.195576525064578</v>
       </c>
       <c r="F1031" t="n">
         <v>2422400</v>
@@ -21052,16 +21052,16 @@
         <v>45294</v>
       </c>
       <c r="B1032" t="n">
-        <v>6.893087863922119</v>
+        <v>6.893087387084961</v>
       </c>
       <c r="C1032" t="n">
-        <v>7.039749168340091</v>
+        <v>7.03974868135747</v>
       </c>
       <c r="D1032" t="n">
-        <v>6.764759222556394</v>
+        <v>6.764758754596515</v>
       </c>
       <c r="E1032" t="n">
-        <v>6.874755200869873</v>
+        <v>6.874754725300897</v>
       </c>
       <c r="F1032" t="n">
         <v>2218000</v>
@@ -21172,16 +21172,16 @@
         <v>45302</v>
       </c>
       <c r="B1038" t="n">
-        <v>6.847256183624268</v>
+        <v>6.847255706787109</v>
       </c>
       <c r="C1038" t="n">
-        <v>7.213909892243003</v>
+        <v>7.213909389872389</v>
       </c>
       <c r="D1038" t="n">
-        <v>6.819757406801839</v>
+        <v>6.819756931879673</v>
       </c>
       <c r="E1038" t="n">
-        <v>6.993917929322868</v>
+        <v>6.993917442272309</v>
       </c>
       <c r="F1038" t="n">
         <v>2188900</v>
@@ -21192,16 +21192,16 @@
         <v>45303</v>
       </c>
       <c r="B1039" t="n">
-        <v>6.810590267181396</v>
+        <v>6.810590744018555</v>
       </c>
       <c r="C1039" t="n">
-        <v>7.085580634123072</v>
+        <v>7.085581130213425</v>
       </c>
       <c r="D1039" t="n">
-        <v>6.792257605190961</v>
+        <v>6.792258080744574</v>
       </c>
       <c r="E1039" t="n">
-        <v>6.83808947870962</v>
+        <v>6.83808995747211</v>
       </c>
       <c r="F1039" t="n">
         <v>1935400</v>
@@ -21212,16 +21212,16 @@
         <v>45306</v>
       </c>
       <c r="B1040" t="n">
-        <v>6.929752826690674</v>
+        <v>6.929753303527832</v>
       </c>
       <c r="C1040" t="n">
-        <v>7.003083475054838</v>
+        <v>7.003083956937887</v>
       </c>
       <c r="D1040" t="n">
-        <v>6.700594332010089</v>
+        <v>6.700594793078822</v>
       </c>
       <c r="E1040" t="n">
-        <v>6.746426205780263</v>
+        <v>6.746426670002693</v>
       </c>
       <c r="F1040" t="n">
         <v>1399400</v>
@@ -21232,16 +21232,16 @@
         <v>45307</v>
       </c>
       <c r="B1041" t="n">
-        <v>6.718927383422852</v>
+        <v>6.718926906585693</v>
       </c>
       <c r="C1041" t="n">
-        <v>6.911420565075185</v>
+        <v>6.911420074576932</v>
       </c>
       <c r="D1041" t="n">
-        <v>6.654763280928852</v>
+        <v>6.654762808645371</v>
       </c>
       <c r="E1041" t="n">
-        <v>6.911420565075185</v>
+        <v>6.911420074576932</v>
       </c>
       <c r="F1041" t="n">
         <v>2256200</v>
@@ -21332,16 +21332,16 @@
         <v>45314</v>
       </c>
       <c r="B1046" t="n">
-        <v>6.718927383422852</v>
+        <v>6.718926906585693</v>
       </c>
       <c r="C1046" t="n">
-        <v>6.801424586155328</v>
+        <v>6.801424103463406</v>
       </c>
       <c r="D1046" t="n">
-        <v>6.526434201770518</v>
+        <v>6.526433738594455</v>
       </c>
       <c r="E1046" t="n">
-        <v>6.608931404502994</v>
+        <v>6.608930935472167</v>
       </c>
       <c r="F1046" t="n">
         <v>2038100</v>
@@ -21352,16 +21352,16 @@
         <v>45315</v>
       </c>
       <c r="B1047" t="n">
-        <v>6.874754905700684</v>
+        <v>6.874755382537842</v>
       </c>
       <c r="C1047" t="n">
-        <v>6.957252104436338</v>
+        <v>6.957252586995552</v>
       </c>
       <c r="D1047" t="n">
-        <v>6.75559238243477</v>
+        <v>6.755592851006743</v>
       </c>
       <c r="E1047" t="n">
-        <v>6.801424256640167</v>
+        <v>6.801424728391066</v>
       </c>
       <c r="F1047" t="n">
         <v>1933800</v>
@@ -21372,16 +21372,16 @@
         <v>45316</v>
       </c>
       <c r="B1048" t="n">
-        <v>6.893087863922119</v>
+        <v>6.893087387084961</v>
       </c>
       <c r="C1048" t="n">
-        <v>7.149745583738733</v>
+        <v>7.149745089146987</v>
       </c>
       <c r="D1048" t="n">
-        <v>6.83808987476538</v>
+        <v>6.83808940173277</v>
       </c>
       <c r="E1048" t="n">
-        <v>6.883921750938578</v>
+        <v>6.883921274735496</v>
       </c>
       <c r="F1048" t="n">
         <v>2213100</v>
@@ -21392,16 +21392,16 @@
         <v>45317</v>
       </c>
       <c r="B1049" t="n">
-        <v>7.094747066497803</v>
+        <v>7.094747543334961</v>
       </c>
       <c r="C1049" t="n">
-        <v>7.177244267717364</v>
+        <v>7.17724475009915</v>
       </c>
       <c r="D1049" t="n">
-        <v>6.718927260204529</v>
+        <v>6.718927711782881</v>
       </c>
       <c r="E1049" t="n">
-        <v>6.957252313912079</v>
+        <v>6.957252781508231</v>
       </c>
       <c r="F1049" t="n">
         <v>2582000</v>
@@ -21572,16 +21572,16 @@
         <v>45330</v>
       </c>
       <c r="B1058" t="n">
-        <v>7.424735546112061</v>
+        <v>7.424736022949219</v>
       </c>
       <c r="C1058" t="n">
-        <v>7.617228715801493</v>
+        <v>7.617229205001097</v>
       </c>
       <c r="D1058" t="n">
-        <v>7.103913305239581</v>
+        <v>7.103913761472643</v>
       </c>
       <c r="E1058" t="n">
-        <v>7.13141251680313</v>
+        <v>7.131412974802268</v>
       </c>
       <c r="F1058" t="n">
         <v>7472200</v>
@@ -21652,16 +21652,16 @@
         <v>45338</v>
       </c>
       <c r="B1062" t="n">
-        <v>7.424735546112061</v>
+        <v>7.424736022949219</v>
       </c>
       <c r="C1062" t="n">
-        <v>7.443067771040908</v>
+        <v>7.443068249055412</v>
       </c>
       <c r="D1062" t="n">
-        <v>7.158911291281541</v>
+        <v>7.158911751046727</v>
       </c>
       <c r="E1062" t="n">
-        <v>7.333071798956986</v>
+        <v>7.333072269907244</v>
       </c>
       <c r="F1062" t="n">
         <v>2565400</v>
@@ -21692,16 +21692,16 @@
         <v>45342</v>
       </c>
       <c r="B1064" t="n">
-        <v>7.2047438621521</v>
+        <v>7.204743385314941</v>
       </c>
       <c r="C1064" t="n">
-        <v>7.314739844881705</v>
+        <v>7.314739360764598</v>
       </c>
       <c r="D1064" t="n">
-        <v>6.92058735489136</v>
+        <v>6.920586896860753</v>
       </c>
       <c r="E1064" t="n">
-        <v>7.241409189728635</v>
+        <v>7.241408710464827</v>
       </c>
       <c r="F1064" t="n">
         <v>5572100</v>
@@ -21752,16 +21752,16 @@
         <v>45345</v>
       </c>
       <c r="B1067" t="n">
-        <v>7.910551071166992</v>
+        <v>7.91055154800415</v>
       </c>
       <c r="C1067" t="n">
-        <v>8.249705526813331</v>
+        <v>8.249706024094255</v>
       </c>
       <c r="D1067" t="n">
-        <v>7.754723230171342</v>
+        <v>7.754723697615412</v>
       </c>
       <c r="E1067" t="n">
-        <v>8.07554546143774</v>
+        <v>8.075545948220533</v>
       </c>
       <c r="F1067" t="n">
         <v>3191100</v>
@@ -21772,16 +21772,16 @@
         <v>45348</v>
       </c>
       <c r="B1068" t="n">
-        <v>8.084712028503418</v>
+        <v>8.084711074829102</v>
       </c>
       <c r="C1068" t="n">
-        <v>8.112211679362662</v>
+        <v>8.11221072244448</v>
       </c>
       <c r="D1068" t="n">
-        <v>7.828054739676261</v>
+        <v>7.828053816277292</v>
       </c>
       <c r="E1068" t="n">
-        <v>7.910551943913292</v>
+        <v>7.910551010782934</v>
       </c>
       <c r="F1068" t="n">
         <v>1473000</v>
@@ -21892,16 +21892,16 @@
         <v>45356</v>
       </c>
       <c r="B1074" t="n">
-        <v>8.790519714355469</v>
+        <v>8.790520668029785</v>
       </c>
       <c r="C1074" t="n">
-        <v>8.909682232674404</v>
+        <v>8.90968319927654</v>
       </c>
       <c r="D1074" t="n">
-        <v>8.616358774439233</v>
+        <v>8.61635970921901</v>
       </c>
       <c r="E1074" t="n">
-        <v>8.763020940641946</v>
+        <v>8.763021891332949</v>
       </c>
       <c r="F1074" t="n">
         <v>2317900</v>
@@ -22112,16 +22112,16 @@
         <v>45371</v>
       </c>
       <c r="B1085" t="n">
-        <v>9.12050724029541</v>
+        <v>9.120508193969727</v>
       </c>
       <c r="C1085" t="n">
-        <v>9.193837883247255</v>
+        <v>9.193838844589299</v>
       </c>
       <c r="D1085" t="n">
-        <v>8.341368940389497</v>
+        <v>8.341369812594202</v>
       </c>
       <c r="E1085" t="n">
-        <v>8.387199936606738</v>
+        <v>8.387200813603702</v>
       </c>
       <c r="F1085" t="n">
         <v>3946300</v>
@@ -22172,16 +22172,16 @@
         <v>45376</v>
       </c>
       <c r="B1088" t="n">
-        <v>8.506362915039062</v>
+        <v>8.506363868713379</v>
       </c>
       <c r="C1088" t="n">
-        <v>8.634691984306407</v>
+        <v>8.634692952368088</v>
       </c>
       <c r="D1088" t="n">
-        <v>8.378034719941983</v>
+        <v>8.378035659229033</v>
       </c>
       <c r="E1088" t="n">
-        <v>8.433032268077797</v>
+        <v>8.433033213530791</v>
       </c>
       <c r="F1088" t="n">
         <v>2424700</v>
@@ -22232,16 +22232,16 @@
         <v>45379</v>
       </c>
       <c r="B1091" t="n">
-        <v>9.752986907958984</v>
+        <v>9.752985954284668</v>
       </c>
       <c r="C1091" t="n">
-        <v>9.881315119453859</v>
+        <v>9.881314153231251</v>
       </c>
       <c r="D1091" t="n">
-        <v>9.340500873381522</v>
+        <v>9.340499960041242</v>
       </c>
       <c r="E1091" t="n">
-        <v>9.386332752131281</v>
+        <v>9.386331834309434</v>
       </c>
       <c r="F1091" t="n">
         <v>5263200</v>
@@ -22312,16 +22312,16 @@
         <v>45386</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C1095" t="n">
-        <v>11.18293432413664</v>
+        <v>11.18293335294909</v>
       </c>
       <c r="D1095" t="n">
-        <v>10.43129474410425</v>
+        <v>10.43129383819321</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.43129474410425</v>
+        <v>10.43129383819321</v>
       </c>
       <c r="F1095" t="n">
         <v>7684100</v>
@@ -22372,16 +22372,16 @@
         <v>45391</v>
       </c>
       <c r="B1098" t="n">
-        <v>11.40292644500732</v>
+        <v>11.40292739868164</v>
       </c>
       <c r="C1098" t="n">
-        <v>11.7329152407039</v>
+        <v>11.73291622197656</v>
       </c>
       <c r="D1098" t="n">
-        <v>11.28376479563944</v>
+        <v>11.28376573934777</v>
       </c>
       <c r="E1098" t="n">
-        <v>11.29293047116523</v>
+        <v>11.29293141564012</v>
       </c>
       <c r="F1098" t="n">
         <v>4003300</v>
@@ -22392,16 +22392,16 @@
         <v>45392</v>
       </c>
       <c r="B1099" t="n">
-        <v>10.58712291717529</v>
+        <v>10.58712196350098</v>
       </c>
       <c r="C1099" t="n">
-        <v>11.36626129578913</v>
+        <v>11.36626027193104</v>
       </c>
       <c r="D1099" t="n">
-        <v>10.44962729212322</v>
+        <v>10.44962635083433</v>
       </c>
       <c r="E1099" t="n">
-        <v>11.36626129578913</v>
+        <v>11.36626027193104</v>
       </c>
       <c r="F1099" t="n">
         <v>6473200</v>
@@ -22412,16 +22412,16 @@
         <v>45393</v>
       </c>
       <c r="B1100" t="n">
-        <v>10.50462532043457</v>
+        <v>10.50462627410889</v>
       </c>
       <c r="C1100" t="n">
-        <v>10.94460920598332</v>
+        <v>10.94461019960207</v>
       </c>
       <c r="D1100" t="n">
-        <v>10.31213215196442</v>
+        <v>10.31213308816303</v>
       </c>
       <c r="E1100" t="n">
-        <v>10.66045316510899</v>
+        <v>10.66045413293031</v>
       </c>
       <c r="F1100" t="n">
         <v>3334800</v>
@@ -22492,16 +22492,16 @@
         <v>45399</v>
       </c>
       <c r="B1104" t="n">
-        <v>9.193840026855469</v>
+        <v>9.193839073181152</v>
       </c>
       <c r="C1104" t="n">
-        <v>9.707155521371709</v>
+        <v>9.707154514451329</v>
       </c>
       <c r="D1104" t="n">
-        <v>9.129675917854847</v>
+        <v>9.129674970836255</v>
       </c>
       <c r="E1104" t="n">
-        <v>9.395499779076538</v>
+        <v>9.395498804484115</v>
       </c>
       <c r="F1104" t="n">
         <v>2870900</v>
@@ -22612,16 +22612,16 @@
         <v>45407</v>
       </c>
       <c r="B1110" t="n">
-        <v>9.936311721801758</v>
+        <v>9.936312675476074</v>
       </c>
       <c r="C1110" t="n">
-        <v>10.00964236464995</v>
+        <v>10.00964332536244</v>
       </c>
       <c r="D1110" t="n">
-        <v>9.505493539440995</v>
+        <v>9.505494451765941</v>
       </c>
       <c r="E1110" t="n">
-        <v>9.670487922934525</v>
+        <v>9.670488851095419</v>
       </c>
       <c r="F1110" t="n">
         <v>2344600</v>
@@ -22672,16 +22672,16 @@
         <v>45412</v>
       </c>
       <c r="B1113" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C1113" t="n">
-        <v>10.89877940479569</v>
+        <v>10.89877837583131</v>
       </c>
       <c r="D1113" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="E1113" t="n">
-        <v>10.86211407696992</v>
+        <v>10.86211305146715</v>
       </c>
       <c r="F1113" t="n">
         <v>3726700</v>
@@ -22712,16 +22712,16 @@
         <v>45415</v>
       </c>
       <c r="B1115" t="n">
-        <v>11.01794052124023</v>
+        <v>11.01794147491455</v>
       </c>
       <c r="C1115" t="n">
-        <v>11.01794052124023</v>
+        <v>11.01794147491455</v>
       </c>
       <c r="D1115" t="n">
-        <v>10.41296137869417</v>
+        <v>10.41296228000361</v>
       </c>
       <c r="E1115" t="n">
-        <v>10.48629202491122</v>
+        <v>10.48629293256791</v>
       </c>
       <c r="F1115" t="n">
         <v>3177300</v>
@@ -22792,16 +22792,16 @@
         <v>45421</v>
       </c>
       <c r="B1119" t="n">
-        <v>11.23793315887451</v>
+        <v>11.2379322052002</v>
       </c>
       <c r="C1119" t="n">
-        <v>11.33876258515184</v>
+        <v>11.33876162292093</v>
       </c>
       <c r="D1119" t="n">
-        <v>10.56878987781135</v>
+        <v>10.56878898092192</v>
       </c>
       <c r="E1119" t="n">
-        <v>11.30209725976278</v>
+        <v>11.30209630064337</v>
       </c>
       <c r="F1119" t="n">
         <v>4225100</v>
@@ -22832,16 +22832,16 @@
         <v>45425</v>
       </c>
       <c r="B1121" t="n">
-        <v>9.303833961486816</v>
+        <v>9.303834915161133</v>
       </c>
       <c r="C1121" t="n">
-        <v>9.569657763981576</v>
+        <v>9.569658744903728</v>
       </c>
       <c r="D1121" t="n">
-        <v>9.184672320860052</v>
+        <v>9.184673262319901</v>
       </c>
       <c r="E1121" t="n">
-        <v>9.395497703383034</v>
+        <v>9.395498666453195</v>
       </c>
       <c r="F1121" t="n">
         <v>4893500</v>
@@ -22872,16 +22872,16 @@
         <v>45427</v>
       </c>
       <c r="B1123" t="n">
-        <v>9.523828506469727</v>
+        <v>9.52382755279541</v>
       </c>
       <c r="C1123" t="n">
-        <v>9.835483362657577</v>
+        <v>9.835482377775513</v>
       </c>
       <c r="D1123" t="n">
-        <v>9.395499419213278</v>
+        <v>9.395498478389273</v>
       </c>
       <c r="E1123" t="n">
-        <v>9.597159163710444</v>
+        <v>9.597158202693118</v>
       </c>
       <c r="F1123" t="n">
         <v>4359100</v>
@@ -23012,16 +23012,16 @@
         <v>45436</v>
       </c>
       <c r="B1130" t="n">
-        <v>8.708024024963379</v>
+        <v>8.708023071289062</v>
       </c>
       <c r="C1130" t="n">
-        <v>9.083843869331375</v>
+        <v>9.083842874498499</v>
       </c>
       <c r="D1130" t="n">
-        <v>8.671358695614559</v>
+        <v>8.67135774595571</v>
       </c>
       <c r="E1130" t="n">
-        <v>8.882184120827667</v>
+        <v>8.882183148079907</v>
       </c>
       <c r="F1130" t="n">
         <v>2233000</v>
@@ -23032,16 +23032,16 @@
         <v>45439</v>
       </c>
       <c r="B1131" t="n">
-        <v>8.808853149414062</v>
+        <v>8.808852195739746</v>
       </c>
       <c r="C1131" t="n">
-        <v>8.836352801077238</v>
+        <v>8.836351844425723</v>
       </c>
       <c r="D1131" t="n">
-        <v>8.625526509178098</v>
+        <v>8.625525575351304</v>
       </c>
       <c r="E1131" t="n">
-        <v>8.680524938334075</v>
+        <v>8.680523998552976</v>
       </c>
       <c r="F1131" t="n">
         <v>1394600</v>
@@ -23092,16 +23092,16 @@
         <v>45443</v>
       </c>
       <c r="B1134" t="n">
-        <v>8.808853149414062</v>
+        <v>8.808852195739746</v>
       </c>
       <c r="C1134" t="n">
-        <v>9.395499272339524</v>
+        <v>9.395498255153042</v>
       </c>
       <c r="D1134" t="n">
-        <v>8.717190266381268</v>
+        <v>8.717189322630665</v>
       </c>
       <c r="E1134" t="n">
-        <v>9.074676996298805</v>
+        <v>9.074676013845558</v>
       </c>
       <c r="F1134" t="n">
         <v>8270300</v>
@@ -23172,16 +23172,16 @@
         <v>45449</v>
       </c>
       <c r="B1138" t="n">
-        <v>9.074675559997559</v>
+        <v>9.074676513671875</v>
       </c>
       <c r="C1138" t="n">
-        <v>9.2396699471805</v>
+        <v>9.239670918194381</v>
       </c>
       <c r="D1138" t="n">
-        <v>8.772186432942322</v>
+        <v>8.772187354827501</v>
       </c>
       <c r="E1138" t="n">
-        <v>8.937180820125265</v>
+        <v>8.937181759350008</v>
       </c>
       <c r="F1138" t="n">
         <v>3356600</v>
@@ -23252,16 +23252,16 @@
         <v>45455</v>
       </c>
       <c r="B1142" t="n">
-        <v>8.909683227539062</v>
+        <v>8.909682273864746</v>
       </c>
       <c r="C1142" t="n">
-        <v>9.661322870219418</v>
+        <v>9.661321836091128</v>
       </c>
       <c r="D1142" t="n">
-        <v>8.882183576584646</v>
+        <v>8.882182625853835</v>
       </c>
       <c r="E1142" t="n">
-        <v>9.395499030185853</v>
+        <v>9.395498024510802</v>
       </c>
       <c r="F1142" t="n">
         <v>3064700</v>
@@ -23272,16 +23272,16 @@
         <v>45456</v>
       </c>
       <c r="B1143" t="n">
-        <v>8.625526428222656</v>
+        <v>8.62552547454834</v>
       </c>
       <c r="C1143" t="n">
-        <v>8.891350272612492</v>
+        <v>8.891349289547579</v>
       </c>
       <c r="D1143" t="n">
-        <v>8.598027650987946</v>
+        <v>8.59802670035401</v>
       </c>
       <c r="E1143" t="n">
-        <v>8.891350272612492</v>
+        <v>8.891349289547579</v>
       </c>
       <c r="F1143" t="n">
         <v>2367500</v>
@@ -23452,16 +23452,16 @@
         <v>45469</v>
       </c>
       <c r="B1152" t="n">
-        <v>8.73552131652832</v>
+        <v>8.735522270202637</v>
       </c>
       <c r="C1152" t="n">
-        <v>9.019678226242117</v>
+        <v>9.01967921093841</v>
       </c>
       <c r="D1152" t="n">
-        <v>8.73552131652832</v>
+        <v>8.735522270202637</v>
       </c>
       <c r="E1152" t="n">
-        <v>9.019678226242117</v>
+        <v>9.01967921093841</v>
       </c>
       <c r="F1152" t="n">
         <v>1529900</v>
@@ -23512,16 +23512,16 @@
         <v>45474</v>
       </c>
       <c r="B1155" t="n">
-        <v>8.579694747924805</v>
+        <v>8.579693794250488</v>
       </c>
       <c r="C1155" t="n">
-        <v>8.689690733570847</v>
+        <v>8.689689767669948</v>
       </c>
       <c r="D1155" t="n">
-        <v>8.414701206540935</v>
+        <v>8.414700271206444</v>
       </c>
       <c r="E1155" t="n">
-        <v>8.579694747924805</v>
+        <v>8.579693794250488</v>
       </c>
       <c r="F1155" t="n">
         <v>1954600</v>
@@ -23532,16 +23532,16 @@
         <v>45475</v>
       </c>
       <c r="B1156" t="n">
-        <v>8.414700508117676</v>
+        <v>8.414699554443359</v>
       </c>
       <c r="C1156" t="n">
-        <v>8.836352188515454</v>
+        <v>8.836351187053534</v>
       </c>
       <c r="D1156" t="n">
-        <v>8.387200858360856</v>
+        <v>8.387199907803193</v>
       </c>
       <c r="E1156" t="n">
-        <v>8.588860585725962</v>
+        <v>8.588859612313334</v>
       </c>
       <c r="F1156" t="n">
         <v>3229800</v>
@@ -23732,16 +23732,16 @@
         <v>45489</v>
       </c>
       <c r="B1166" t="n">
-        <v>9.303833961486816</v>
+        <v>9.303834915161133</v>
       </c>
       <c r="C1166" t="n">
-        <v>9.789650569698455</v>
+        <v>9.789651573170611</v>
       </c>
       <c r="D1166" t="n">
-        <v>9.258002964708936</v>
+        <v>9.258003913685421</v>
       </c>
       <c r="E1166" t="n">
-        <v>9.743818698750346</v>
+        <v>9.743819697524581</v>
       </c>
       <c r="F1166" t="n">
         <v>1952400</v>
@@ -23832,16 +23832,16 @@
         <v>45496</v>
       </c>
       <c r="B1171" t="n">
-        <v>8.176375389099121</v>
+        <v>8.176376342773438</v>
       </c>
       <c r="C1171" t="n">
-        <v>8.607193615930459</v>
+        <v>8.607194619854459</v>
       </c>
       <c r="D1171" t="n">
-        <v>8.176375389099121</v>
+        <v>8.176376342773438</v>
       </c>
       <c r="E1171" t="n">
-        <v>8.607193615930459</v>
+        <v>8.607194619854459</v>
       </c>
       <c r="F1171" t="n">
         <v>3005900</v>
@@ -23892,16 +23892,16 @@
         <v>45499</v>
       </c>
       <c r="B1174" t="n">
-        <v>7.818887710571289</v>
+        <v>7.818887233734131</v>
       </c>
       <c r="C1174" t="n">
-        <v>7.883052684476461</v>
+        <v>7.883052203726183</v>
       </c>
       <c r="D1174" t="n">
-        <v>7.653894186371567</v>
+        <v>7.653893719596588</v>
       </c>
       <c r="E1174" t="n">
-        <v>7.718058286106443</v>
+        <v>7.718057815418397</v>
       </c>
       <c r="F1174" t="n">
         <v>2119900</v>
@@ -23952,16 +23952,16 @@
         <v>45504</v>
       </c>
       <c r="B1177" t="n">
-        <v>7.736390590667725</v>
+        <v>7.736391067504883</v>
       </c>
       <c r="C1177" t="n">
-        <v>7.873886215441875</v>
+        <v>7.873886700753659</v>
       </c>
       <c r="D1177" t="n">
-        <v>7.617228939701889</v>
+        <v>7.617229409194445</v>
       </c>
       <c r="E1177" t="n">
-        <v>7.718058365200021</v>
+        <v>7.718058840907261</v>
       </c>
       <c r="F1177" t="n">
         <v>1863600</v>
@@ -23972,16 +23972,16 @@
         <v>45505</v>
       </c>
       <c r="B1178" t="n">
-        <v>7.727224826812744</v>
+        <v>7.727224349975586</v>
       </c>
       <c r="C1178" t="n">
-        <v>7.965549000194251</v>
+        <v>7.965548508650412</v>
       </c>
       <c r="D1178" t="n">
-        <v>7.663059852982463</v>
+        <v>7.663059380104842</v>
       </c>
       <c r="E1178" t="n">
-        <v>7.828054251159909</v>
+        <v>7.828053768100695</v>
       </c>
       <c r="F1178" t="n">
         <v>2732500</v>
@@ -24032,16 +24032,16 @@
         <v>45510</v>
       </c>
       <c r="B1181" t="n">
-        <v>7.956383228302002</v>
+        <v>7.95638370513916</v>
       </c>
       <c r="C1181" t="n">
-        <v>8.176375173761064</v>
+        <v>8.176375663782647</v>
       </c>
       <c r="D1181" t="n">
-        <v>7.782222282519196</v>
+        <v>7.782222748918646</v>
       </c>
       <c r="E1181" t="n">
-        <v>7.993048552545178</v>
+        <v>7.993049031579741</v>
       </c>
       <c r="F1181" t="n">
         <v>1835500</v>
@@ -24052,16 +24052,16 @@
         <v>45511</v>
       </c>
       <c r="B1182" t="n">
-        <v>8.506362915039062</v>
+        <v>8.506363868713379</v>
       </c>
       <c r="C1182" t="n">
-        <v>8.543028238519694</v>
+        <v>8.543029196304673</v>
       </c>
       <c r="D1182" t="n">
-        <v>8.020547160378118</v>
+        <v>8.020548059586147</v>
       </c>
       <c r="E1182" t="n">
-        <v>8.158041904887924</v>
+        <v>8.158042819510907</v>
       </c>
       <c r="F1182" t="n">
         <v>2816900</v>
@@ -24092,16 +24092,16 @@
         <v>45513</v>
       </c>
       <c r="B1184" t="n">
-        <v>7.84638786315918</v>
+        <v>7.846388339996338</v>
       </c>
       <c r="C1184" t="n">
-        <v>8.103045152735731</v>
+        <v>8.103045645170351</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.653894677434178</v>
+        <v>7.653895142573226</v>
       </c>
       <c r="E1184" t="n">
-        <v>8.103045152735731</v>
+        <v>8.103045645170351</v>
       </c>
       <c r="F1184" t="n">
         <v>6458600</v>
@@ -24132,16 +24132,16 @@
         <v>45517</v>
       </c>
       <c r="B1186" t="n">
-        <v>8.176375389099121</v>
+        <v>8.176376342773438</v>
       </c>
       <c r="C1186" t="n">
-        <v>8.497197640304007</v>
+        <v>8.497198631398319</v>
       </c>
       <c r="D1186" t="n">
-        <v>8.103044738681486</v>
+        <v>8.103045683802677</v>
       </c>
       <c r="E1186" t="n">
-        <v>8.497197640304007</v>
+        <v>8.497198631398319</v>
       </c>
       <c r="F1186" t="n">
         <v>4500900</v>
@@ -24192,16 +24192,16 @@
         <v>45520</v>
       </c>
       <c r="B1189" t="n">
-        <v>8.506362915039062</v>
+        <v>8.506363868713379</v>
       </c>
       <c r="C1189" t="n">
-        <v>8.598026660825775</v>
+        <v>8.598027624776794</v>
       </c>
       <c r="D1189" t="n">
-        <v>8.304704072980718</v>
+        <v>8.304705004046447</v>
       </c>
       <c r="E1189" t="n">
-        <v>8.387200395184442</v>
+        <v>8.387201335499084</v>
       </c>
       <c r="F1189" t="n">
         <v>3088500</v>
@@ -24212,16 +24212,16 @@
         <v>45523</v>
       </c>
       <c r="B1190" t="n">
-        <v>8.744688034057617</v>
+        <v>8.744688987731934</v>
       </c>
       <c r="C1190" t="n">
-        <v>8.82718523117981</v>
+        <v>8.827186193851068</v>
       </c>
       <c r="D1190" t="n">
-        <v>8.442198894056432</v>
+        <v>8.442199814742022</v>
       </c>
       <c r="E1190" t="n">
-        <v>8.478864217869598</v>
+        <v>8.478865142553818</v>
       </c>
       <c r="F1190" t="n">
         <v>2333900</v>
@@ -24272,16 +24272,16 @@
         <v>45526</v>
       </c>
       <c r="B1193" t="n">
-        <v>8.653024673461914</v>
+        <v>8.653023719787598</v>
       </c>
       <c r="C1193" t="n">
-        <v>9.093009453018452</v>
+        <v>9.093008450852169</v>
       </c>
       <c r="D1193" t="n">
-        <v>8.616359348013061</v>
+        <v>8.616358398379734</v>
       </c>
       <c r="E1193" t="n">
-        <v>9.038011027760017</v>
+        <v>9.038010031655267</v>
       </c>
       <c r="F1193" t="n">
         <v>2148900</v>
@@ -24412,16 +24412,16 @@
         <v>45537</v>
       </c>
       <c r="B1200" t="n">
-        <v>8.937182426452637</v>
+        <v>8.93718147277832</v>
       </c>
       <c r="C1200" t="n">
-        <v>9.248838158626967</v>
+        <v>9.2488371716963</v>
       </c>
       <c r="D1200" t="n">
-        <v>8.918849324950433</v>
+        <v>8.918848373232414</v>
       </c>
       <c r="E1200" t="n">
-        <v>9.120509070622715</v>
+        <v>9.120508097385867</v>
       </c>
       <c r="F1200" t="n">
         <v>2102800</v>
@@ -24452,16 +24452,16 @@
         <v>45539</v>
       </c>
       <c r="B1202" t="n">
-        <v>9.294670104980469</v>
+        <v>9.294669151306152</v>
       </c>
       <c r="C1202" t="n">
-        <v>9.468830199650526</v>
+        <v>9.468829228106612</v>
       </c>
       <c r="D1202" t="n">
-        <v>9.184674117688264</v>
+        <v>9.184673175300023</v>
       </c>
       <c r="E1202" t="n">
-        <v>9.212172895968715</v>
+        <v>9.212171950758979</v>
       </c>
       <c r="F1202" t="n">
         <v>2019900</v>
@@ -24572,16 +24572,16 @@
         <v>45547</v>
       </c>
       <c r="B1208" t="n">
-        <v>9.12050724029541</v>
+        <v>9.120508193969727</v>
       </c>
       <c r="C1208" t="n">
-        <v>9.212170981070326</v>
+        <v>9.212171944329347</v>
       </c>
       <c r="D1208" t="n">
-        <v>8.955513730738867</v>
+        <v>8.955514667160847</v>
       </c>
       <c r="E1208" t="n">
-        <v>9.175505659594403</v>
+        <v>9.175506619019561</v>
       </c>
       <c r="F1208" t="n">
         <v>1127400</v>
@@ -24612,16 +24612,16 @@
         <v>45551</v>
       </c>
       <c r="B1210" t="n">
-        <v>9.936311721801758</v>
+        <v>9.936312675476074</v>
       </c>
       <c r="C1210" t="n">
-        <v>10.17463674814347</v>
+        <v>10.17463772469192</v>
       </c>
       <c r="D1210" t="n">
-        <v>9.569657633390603</v>
+        <v>9.569658551873937</v>
       </c>
       <c r="E1210" t="n">
-        <v>9.707153244358619</v>
+        <v>9.707154176038602</v>
       </c>
       <c r="F1210" t="n">
         <v>2756600</v>
@@ -24652,16 +24652,16 @@
         <v>45553</v>
       </c>
       <c r="B1212" t="n">
-        <v>9.890480995178223</v>
+        <v>9.890481948852539</v>
       </c>
       <c r="C1212" t="n">
-        <v>10.26630080177617</v>
+        <v>10.26630179168833</v>
       </c>
       <c r="D1212" t="n">
-        <v>9.606324065654963</v>
+        <v>9.606324991929888</v>
       </c>
       <c r="E1212" t="n">
-        <v>9.697987816899968</v>
+        <v>9.697988752013428</v>
       </c>
       <c r="F1212" t="n">
         <v>2495300</v>
@@ -24672,16 +24672,16 @@
         <v>45554</v>
       </c>
       <c r="B1213" t="n">
-        <v>9.853816032409668</v>
+        <v>9.853815078735352</v>
       </c>
       <c r="C1213" t="n">
-        <v>10.15630519881978</v>
+        <v>10.15630421586989</v>
       </c>
       <c r="D1213" t="n">
-        <v>9.798817604803125</v>
+        <v>9.798816656451679</v>
       </c>
       <c r="E1213" t="n">
-        <v>10.00047734046665</v>
+        <v>10.00047637259812</v>
       </c>
       <c r="F1213" t="n">
         <v>3128500</v>
@@ -24732,16 +24732,16 @@
         <v>45559</v>
       </c>
       <c r="B1216" t="n">
-        <v>9.487162590026855</v>
+        <v>9.487161636352539</v>
       </c>
       <c r="C1216" t="n">
-        <v>9.615490795161728</v>
+        <v>9.615489828587524</v>
       </c>
       <c r="D1216" t="n">
-        <v>9.285502858024484</v>
+        <v>9.28550192462153</v>
       </c>
       <c r="E1216" t="n">
-        <v>9.51466136624571</v>
+        <v>9.514660409807144</v>
       </c>
       <c r="F1216" t="n">
         <v>1652000</v>
@@ -24772,16 +24772,16 @@
         <v>45561</v>
       </c>
       <c r="B1218" t="n">
-        <v>9.551326751708984</v>
+        <v>9.551325798034668</v>
       </c>
       <c r="C1218" t="n">
-        <v>9.78965181153497</v>
+        <v>9.789650834064538</v>
       </c>
       <c r="D1218" t="n">
-        <v>9.450497322168916</v>
+        <v>9.450496378562148</v>
       </c>
       <c r="E1218" t="n">
-        <v>9.450497322168916</v>
+        <v>9.450496378562148</v>
       </c>
       <c r="F1218" t="n">
         <v>1643400</v>
@@ -24792,16 +24792,16 @@
         <v>45562</v>
       </c>
       <c r="B1219" t="n">
-        <v>9.587991714477539</v>
+        <v>9.587992668151855</v>
       </c>
       <c r="C1219" t="n">
-        <v>9.752986114891955</v>
+        <v>9.752987084977519</v>
       </c>
       <c r="D1219" t="n">
-        <v>9.450496963579065</v>
+        <v>9.450497903577398</v>
       </c>
       <c r="E1219" t="n">
-        <v>9.532993289615966</v>
+        <v>9.532994237819837</v>
       </c>
       <c r="F1219" t="n">
         <v>1380700</v>
@@ -24892,16 +24892,16 @@
         <v>45569</v>
       </c>
       <c r="B1224" t="n">
-        <v>9.12050724029541</v>
+        <v>9.120508193969727</v>
       </c>
       <c r="C1224" t="n">
-        <v>9.258002851457784</v>
+        <v>9.258003819509156</v>
       </c>
       <c r="D1224" t="n">
-        <v>9.03801004843203</v>
+        <v>9.038010993480132</v>
       </c>
       <c r="E1224" t="n">
-        <v>9.166339110682868</v>
+        <v>9.166340069149538</v>
       </c>
       <c r="F1224" t="n">
         <v>1258700</v>
@@ -24972,16 +24972,16 @@
         <v>45575</v>
       </c>
       <c r="B1228" t="n">
-        <v>9.42299747467041</v>
+        <v>9.422996520996094</v>
       </c>
       <c r="C1228" t="n">
-        <v>9.441330574660176</v>
+        <v>9.441329619130419</v>
       </c>
       <c r="D1228" t="n">
-        <v>8.946348239150669</v>
+        <v>8.946347333716643</v>
       </c>
       <c r="E1228" t="n">
-        <v>9.065510766573185</v>
+        <v>9.065509849079064</v>
       </c>
       <c r="F1228" t="n">
         <v>2116800</v>
@@ -24992,16 +24992,16 @@
         <v>45576</v>
       </c>
       <c r="B1229" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C1229" t="n">
-        <v>10.36713171423691</v>
+        <v>10.3671307354659</v>
       </c>
       <c r="D1229" t="n">
-        <v>9.432164543424346</v>
+        <v>9.432163652924501</v>
       </c>
       <c r="E1229" t="n">
-        <v>9.432164543424346</v>
+        <v>9.432163652924501</v>
       </c>
       <c r="F1229" t="n">
         <v>6482800</v>
@@ -25112,16 +25112,16 @@
         <v>45586</v>
       </c>
       <c r="B1235" t="n">
-        <v>10.95377635955811</v>
+        <v>10.95377540588379</v>
       </c>
       <c r="C1235" t="n">
-        <v>11.26543206609426</v>
+        <v>11.2654310852861</v>
       </c>
       <c r="D1235" t="n">
-        <v>10.89877880791662</v>
+        <v>10.89877785903058</v>
       </c>
       <c r="E1235" t="n">
-        <v>11.07293888700842</v>
+        <v>11.07293792295939</v>
       </c>
       <c r="F1235" t="n">
         <v>2389000</v>
@@ -25132,16 +25132,16 @@
         <v>45587</v>
       </c>
       <c r="B1236" t="n">
-        <v>10.65128707885742</v>
+        <v>10.65128612518311</v>
       </c>
       <c r="C1236" t="n">
-        <v>11.00877465704114</v>
+        <v>11.00877367135879</v>
       </c>
       <c r="D1236" t="n">
-        <v>10.62378830335723</v>
+        <v>10.62378735214505</v>
       </c>
       <c r="E1236" t="n">
-        <v>10.86211335547971</v>
+        <v>10.86211238292884</v>
       </c>
       <c r="F1236" t="n">
         <v>2418100</v>
@@ -25232,16 +25232,16 @@
         <v>45594</v>
       </c>
       <c r="B1241" t="n">
-        <v>11.4212589263916</v>
+        <v>11.42125988006592</v>
       </c>
       <c r="C1241" t="n">
-        <v>11.62291863794205</v>
+        <v>11.62291960845494</v>
       </c>
       <c r="D1241" t="n">
-        <v>11.25626453747121</v>
+        <v>11.25626547736851</v>
       </c>
       <c r="E1241" t="n">
-        <v>11.47625734742181</v>
+        <v>11.47625830568849</v>
       </c>
       <c r="F1241" t="n">
         <v>2046100</v>
@@ -25252,16 +25252,16 @@
         <v>45595</v>
       </c>
       <c r="B1242" t="n">
-        <v>12.09956932067871</v>
+        <v>12.09956836700439</v>
       </c>
       <c r="C1242" t="n">
-        <v>12.35622661066431</v>
+        <v>12.35622563676056</v>
       </c>
       <c r="D1242" t="n">
-        <v>11.32043090039411</v>
+        <v>11.3204300081306</v>
       </c>
       <c r="E1242" t="n">
-        <v>11.32043090039411</v>
+        <v>11.3204300081306</v>
       </c>
       <c r="F1242" t="n">
         <v>5623200</v>
@@ -25412,16 +25412,16 @@
         <v>45607</v>
       </c>
       <c r="B1250" t="n">
-        <v>12.33789443969727</v>
+        <v>12.33789348602295</v>
       </c>
       <c r="C1250" t="n">
-        <v>12.47538919855138</v>
+        <v>12.47538823424922</v>
       </c>
       <c r="D1250" t="n">
-        <v>11.64125234671695</v>
+        <v>11.64125144689053</v>
       </c>
       <c r="E1250" t="n">
-        <v>11.69625077476081</v>
+        <v>11.69624987068321</v>
       </c>
       <c r="F1250" t="n">
         <v>4291300</v>
@@ -25432,16 +25432,16 @@
         <v>45608</v>
       </c>
       <c r="B1251" t="n">
-        <v>11.86124324798584</v>
+        <v>11.86124420166016</v>
       </c>
       <c r="C1251" t="n">
-        <v>12.37455865845288</v>
+        <v>12.37455965339907</v>
       </c>
       <c r="D1251" t="n">
-        <v>11.77874692456585</v>
+        <v>11.77874787160726</v>
       </c>
       <c r="E1251" t="n">
-        <v>12.28289491131475</v>
+        <v>12.28289589889094</v>
       </c>
       <c r="F1251" t="n">
         <v>1595200</v>
@@ -25472,16 +25472,16 @@
         <v>45610</v>
       </c>
       <c r="B1253" t="n">
-        <v>10.58712291717529</v>
+        <v>10.58712196350098</v>
       </c>
       <c r="C1253" t="n">
-        <v>10.99960804399089</v>
+        <v>10.99960705316045</v>
       </c>
       <c r="D1253" t="n">
-        <v>10.40379629127617</v>
+        <v>10.40379535411568</v>
       </c>
       <c r="E1253" t="n">
-        <v>10.559624141833</v>
+        <v>10.55962319063574</v>
       </c>
       <c r="F1253" t="n">
         <v>63226600</v>
@@ -25512,16 +25512,16 @@
         <v>45615</v>
       </c>
       <c r="B1255" t="n">
-        <v>11.35709571838379</v>
+        <v>11.35709667205811</v>
       </c>
       <c r="C1255" t="n">
-        <v>11.46709169487495</v>
+        <v>11.46709265778581</v>
       </c>
       <c r="D1255" t="n">
-        <v>10.91711093824883</v>
+        <v>10.91711185497689</v>
       </c>
       <c r="E1255" t="n">
-        <v>11.00877468907663</v>
+        <v>11.00877561350184</v>
       </c>
       <c r="F1255" t="n">
         <v>7243900</v>
@@ -25532,16 +25532,16 @@
         <v>45617</v>
       </c>
       <c r="B1256" t="n">
-        <v>11.23793315887451</v>
+        <v>11.2379322052002</v>
       </c>
       <c r="C1256" t="n">
-        <v>11.329596035262</v>
+        <v>11.32959507380898</v>
       </c>
       <c r="D1256" t="n">
-        <v>10.94460968159175</v>
+        <v>10.94460875280948</v>
       </c>
       <c r="E1256" t="n">
-        <v>11.30209725976278</v>
+        <v>11.30209630064337</v>
       </c>
       <c r="F1256" t="n">
         <v>3263500</v>
@@ -25592,16 +25592,16 @@
         <v>45622</v>
       </c>
       <c r="B1259" t="n">
-        <v>11.57708740234375</v>
+        <v>11.57708835601807</v>
       </c>
       <c r="C1259" t="n">
-        <v>11.66875027687121</v>
+        <v>11.66875123809635</v>
       </c>
       <c r="D1259" t="n">
-        <v>11.31126358012461</v>
+        <v>11.31126451190142</v>
       </c>
       <c r="E1259" t="n">
-        <v>11.63208495222617</v>
+        <v>11.63208591043096</v>
       </c>
       <c r="F1259" t="n">
         <v>7231300</v>
@@ -25652,16 +25652,16 @@
         <v>45625</v>
       </c>
       <c r="B1262" t="n">
-        <v>9.688820838928223</v>
+        <v>9.688821792602539</v>
       </c>
       <c r="C1262" t="n">
-        <v>9.697987388481845</v>
+        <v>9.697988343058428</v>
       </c>
       <c r="D1262" t="n">
-        <v>9.00134535747155</v>
+        <v>9.001346243477393</v>
       </c>
       <c r="E1262" t="n">
-        <v>9.532992993197755</v>
+        <v>9.532993931533877</v>
       </c>
       <c r="F1262" t="n">
         <v>14865400</v>
@@ -25732,16 +25732,16 @@
         <v>45631</v>
       </c>
       <c r="B1266" t="n">
-        <v>9.404664993286133</v>
+        <v>9.404665946960449</v>
       </c>
       <c r="C1266" t="n">
-        <v>9.835482341294636</v>
+        <v>9.835483338655724</v>
       </c>
       <c r="D1266" t="n">
-        <v>9.294669018847561</v>
+        <v>9.294669961367802</v>
       </c>
       <c r="E1266" t="n">
-        <v>9.624656942163279</v>
+        <v>9.624657918145745</v>
       </c>
       <c r="F1266" t="n">
         <v>7256000</v>
@@ -25952,16 +25952,16 @@
         <v>45646</v>
       </c>
       <c r="B1277" t="n">
-        <v>8.937182426452637</v>
+        <v>8.93718147277832</v>
       </c>
       <c r="C1277" t="n">
-        <v>9.138842172124919</v>
+        <v>9.138841196931772</v>
       </c>
       <c r="D1277" t="n">
-        <v>8.588861365444293</v>
+        <v>8.588860448938831</v>
       </c>
       <c r="E1277" t="n">
-        <v>8.799687661867678</v>
+        <v>8.799686722865236</v>
       </c>
       <c r="F1277" t="n">
         <v>5127000</v>
@@ -26032,16 +26032,16 @@
         <v>45656</v>
       </c>
       <c r="B1281" t="n">
-        <v>7.378903865814209</v>
+        <v>7.378904342651367</v>
       </c>
       <c r="C1281" t="n">
-        <v>7.86471964045267</v>
+        <v>7.86472014868406</v>
       </c>
       <c r="D1281" t="n">
-        <v>7.314739328541989</v>
+        <v>7.314739801232726</v>
       </c>
       <c r="E1281" t="n">
-        <v>7.809722090055269</v>
+        <v>7.809722594732624</v>
       </c>
       <c r="F1281" t="n">
         <v>5347400</v>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1680"/>
+  <dimension ref="A1:F1682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33929,102 +33929,142 @@
     </row>
     <row r="1676">
       <c r="A1676" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B1676" t="n">
-        <v>9.779999732971191</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="C1676" t="n">
-        <v>9.800000190734863</v>
+        <v>9.609999656677246</v>
       </c>
       <c r="D1676" t="n">
-        <v>9.470000267028809</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="E1676" t="n">
-        <v>9.569999694824219</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="F1676" t="n">
-        <v>7262200</v>
+        <v>4879600</v>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1677" t="n">
-        <v>9.720000267028809</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="C1677" t="n">
-        <v>10.01000022888184</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="D1677" t="n">
-        <v>9.600000381469727</v>
+        <v>9.470000267028809</v>
       </c>
       <c r="E1677" t="n">
-        <v>9.899999618530273</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="F1677" t="n">
-        <v>8354200</v>
+        <v>7262200</v>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1678" t="n">
-        <v>9.340000152587891</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="C1678" t="n">
-        <v>9.930000305175781</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="D1678" t="n">
-        <v>8.979999542236328</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="E1678" t="n">
-        <v>9.850000381469727</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="F1678" t="n">
-        <v>20128500</v>
+        <v>8354200</v>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1679" t="n">
-        <v>9.439999580383301</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="C1679" t="n">
-        <v>9.600000381469727</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="D1679" t="n">
-        <v>9.170000076293945</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="E1679" t="n">
-        <v>9.300000190734863</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="F1679" t="n">
-        <v>10508100</v>
+        <v>20128500</v>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1680" t="n">
+        <v>9.439999580383301</v>
+      </c>
+      <c r="C1680" t="n">
+        <v>9.600000381469727</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>9.170000076293945</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>9.300000190734863</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>10508100</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="B1680" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="C1680" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="D1680" t="n">
+      <c r="B1681" t="n">
+        <v>9.180000305175781</v>
+      </c>
+      <c r="C1681" t="n">
+        <v>9.510000228881836</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>8.880000114440918</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>9.479999542236328</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>13169100</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1682" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="C1682" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="D1682" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="E1680" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="F1680" t="n">
-        <v>13169100</v>
+      <c r="E1682" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>7898200</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1683"/>
+  <dimension ref="A1:F1682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43774</v>
       </c>
       <c r="B2" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="C2" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04940323214578</v>
+        <v>16.04940511406312</v>
       </c>
       <c r="E2" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="F2" t="n">
         <v>862100</v>
@@ -472,16 +472,16 @@
         <v>43775</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13073921203613</v>
+        <v>16.1307373046875</v>
       </c>
       <c r="C3" t="n">
-        <v>16.3205117831287</v>
+        <v>16.32050985334077</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94096491730532</v>
+        <v>15.94096303239619</v>
       </c>
       <c r="E3" t="n">
-        <v>16.26629129476486</v>
+        <v>16.26628937138813</v>
       </c>
       <c r="F3" t="n">
         <v>1352600</v>
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518585205078</v>
+        <v>15.99518394470215</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073792395533</v>
+        <v>16.13073600044276</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008522099254</v>
+        <v>15.48008337506717</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073792395533</v>
+        <v>16.13073600044276</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -512,16 +512,16 @@
         <v>43777</v>
       </c>
       <c r="B5" t="n">
-        <v>15.81444931030273</v>
+        <v>15.8144474029541</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12170160622253</v>
+        <v>16.12169966181682</v>
       </c>
       <c r="D5" t="n">
-        <v>15.57949157085594</v>
+        <v>15.57948969184508</v>
       </c>
       <c r="E5" t="n">
-        <v>15.95000138823483</v>
+        <v>15.94999946453754</v>
       </c>
       <c r="F5" t="n">
         <v>463500</v>
@@ -572,16 +572,16 @@
         <v>43782</v>
       </c>
       <c r="B8" t="n">
-        <v>13.55524158477783</v>
+        <v>13.55524063110352</v>
       </c>
       <c r="C8" t="n">
-        <v>14.91076574325561</v>
+        <v>14.91076469421387</v>
       </c>
       <c r="D8" t="n">
-        <v>13.3925784099784</v>
+        <v>13.3925774677482</v>
       </c>
       <c r="E8" t="n">
-        <v>14.73002849933667</v>
+        <v>14.73002746301063</v>
       </c>
       <c r="F8" t="n">
         <v>9002100</v>
@@ -592,16 +592,16 @@
         <v>43783</v>
       </c>
       <c r="B9" t="n">
-        <v>13.55524158477783</v>
+        <v>13.55524063110352</v>
       </c>
       <c r="C9" t="n">
-        <v>13.93478841809713</v>
+        <v>13.93478743771993</v>
       </c>
       <c r="D9" t="n">
-        <v>12.80518495269898</v>
+        <v>12.80518405179464</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60946293031733</v>
+        <v>13.60946197282829</v>
       </c>
       <c r="F9" t="n">
         <v>6889800</v>
@@ -612,16 +612,16 @@
         <v>43787</v>
       </c>
       <c r="B10" t="n">
-        <v>14.11552333831787</v>
+        <v>14.11552429199219</v>
       </c>
       <c r="C10" t="n">
-        <v>14.35048104162378</v>
+        <v>14.35048201117233</v>
       </c>
       <c r="D10" t="n">
-        <v>13.57331424817226</v>
+        <v>13.5733151652138</v>
       </c>
       <c r="E10" t="n">
-        <v>13.64560879352501</v>
+        <v>13.64560971545092</v>
       </c>
       <c r="F10" t="n">
         <v>4129300</v>
@@ -632,16 +632,16 @@
         <v>43788</v>
       </c>
       <c r="B11" t="n">
-        <v>13.91671276092529</v>
+        <v>13.91671371459961</v>
       </c>
       <c r="C11" t="n">
-        <v>14.40470136781958</v>
+        <v>14.40470235493443</v>
       </c>
       <c r="D11" t="n">
-        <v>13.79019773880167</v>
+        <v>13.79019868380626</v>
       </c>
       <c r="E11" t="n">
-        <v>14.27818634569596</v>
+        <v>14.27818732414107</v>
       </c>
       <c r="F11" t="n">
         <v>1475000</v>
@@ -652,16 +652,16 @@
         <v>43790</v>
       </c>
       <c r="B12" t="n">
-        <v>13.9709358215332</v>
+        <v>13.97093677520752</v>
       </c>
       <c r="C12" t="n">
-        <v>14.09745172106287</v>
+        <v>14.09745268337332</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66368353826049</v>
+        <v>13.66368447096136</v>
       </c>
       <c r="E12" t="n">
-        <v>13.92575151014267</v>
+        <v>13.92575246073265</v>
       </c>
       <c r="F12" t="n">
         <v>946900</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439208984375</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439208984375</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869711259133</v>
+        <v>14.64869618523321</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291932069259</v>
+        <v>14.70291838990186</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -812,16 +812,16 @@
         <v>43802</v>
       </c>
       <c r="B20" t="n">
-        <v>15.81444931030273</v>
+        <v>15.8144474029541</v>
       </c>
       <c r="C20" t="n">
-        <v>15.92289200683133</v>
+        <v>15.92289008640364</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29935037997784</v>
+        <v>15.29934853475424</v>
       </c>
       <c r="E20" t="n">
-        <v>15.48912294435515</v>
+        <v>15.48912107624346</v>
       </c>
       <c r="F20" t="n">
         <v>976200</v>
@@ -832,16 +832,16 @@
         <v>43803</v>
       </c>
       <c r="B21" t="n">
-        <v>16.1036262512207</v>
+        <v>16.10362434387207</v>
       </c>
       <c r="C21" t="n">
-        <v>16.19399487051062</v>
+        <v>16.19399295245853</v>
       </c>
       <c r="D21" t="n">
-        <v>15.74215349769909</v>
+        <v>15.74215163316408</v>
       </c>
       <c r="E21" t="n">
-        <v>16.04036873480918</v>
+        <v>16.0403668349529</v>
       </c>
       <c r="F21" t="n">
         <v>976000</v>
@@ -852,16 +852,16 @@
         <v>43804</v>
       </c>
       <c r="B22" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="C22" t="n">
-        <v>16.43798702712168</v>
+        <v>16.4379889546035</v>
       </c>
       <c r="D22" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="E22" t="n">
-        <v>16.40183889566449</v>
+        <v>16.40184081890766</v>
       </c>
       <c r="F22" t="n">
         <v>1168600</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399452209473</v>
+        <v>16.19399261474609</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317271869031</v>
+        <v>16.48317077728191</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977404114256</v>
+        <v>16.13977214018008</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702630593487</v>
+        <v>16.44702436878384</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -892,16 +892,16 @@
         <v>43808</v>
       </c>
       <c r="B24" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="C24" t="n">
-        <v>16.37472952070938</v>
+        <v>16.37473144077376</v>
       </c>
       <c r="D24" t="n">
-        <v>16.21206637642758</v>
+        <v>16.21206827741844</v>
       </c>
       <c r="E24" t="n">
-        <v>16.33858138925219</v>
+        <v>16.33858330507792</v>
       </c>
       <c r="F24" t="n">
         <v>474400</v>
@@ -912,16 +912,16 @@
         <v>43809</v>
       </c>
       <c r="B25" t="n">
-        <v>16.71813011169434</v>
+        <v>16.71813201904297</v>
       </c>
       <c r="C25" t="n">
-        <v>16.97116189065127</v>
+        <v>16.97116382686796</v>
       </c>
       <c r="D25" t="n">
-        <v>16.21206827741844</v>
+        <v>16.21207012703117</v>
       </c>
       <c r="E25" t="n">
-        <v>16.35665737292584</v>
+        <v>16.35665923903454</v>
       </c>
       <c r="F25" t="n">
         <v>1162400</v>
@@ -932,16 +932,16 @@
         <v>43810</v>
       </c>
       <c r="B26" t="n">
-        <v>17.48626136779785</v>
+        <v>17.48626327514648</v>
       </c>
       <c r="C26" t="n">
-        <v>17.84773411915439</v>
+        <v>17.84773606593138</v>
       </c>
       <c r="D26" t="n">
-        <v>16.9259773104667</v>
+        <v>16.92597915670124</v>
       </c>
       <c r="E26" t="n">
-        <v>16.98019951589871</v>
+        <v>16.98020136804764</v>
       </c>
       <c r="F26" t="n">
         <v>2363200</v>
@@ -972,16 +972,16 @@
         <v>43812</v>
       </c>
       <c r="B28" t="n">
-        <v>16.71813011169434</v>
+        <v>16.71813201904297</v>
       </c>
       <c r="C28" t="n">
-        <v>17.50433482669905</v>
+        <v>17.50433682374471</v>
       </c>
       <c r="D28" t="n">
-        <v>16.28436282517214</v>
+        <v>16.28436468303286</v>
       </c>
       <c r="E28" t="n">
-        <v>17.50433482669905</v>
+        <v>17.50433682374471</v>
       </c>
       <c r="F28" t="n">
         <v>3257200</v>
@@ -1012,16 +1012,16 @@
         <v>43816</v>
       </c>
       <c r="B30" t="n">
-        <v>16.71813011169434</v>
+        <v>16.71813201904297</v>
       </c>
       <c r="C30" t="n">
-        <v>16.89886734289757</v>
+        <v>16.89886927086627</v>
       </c>
       <c r="D30" t="n">
-        <v>16.51932053628116</v>
+        <v>16.51932242094788</v>
       </c>
       <c r="E30" t="n">
-        <v>16.85368217327778</v>
+        <v>16.85368409609136</v>
       </c>
       <c r="F30" t="n">
         <v>664900</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436279296875</v>
+        <v>16.28436088562012</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51932050361312</v>
+        <v>16.51931856874445</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444737168</v>
+        <v>15.81444551937144</v>
       </c>
       <c r="E33" t="n">
-        <v>16.40184078647195</v>
+        <v>16.4018388653634</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1112,16 +1112,16 @@
         <v>43825</v>
       </c>
       <c r="B35" t="n">
-        <v>16.51931953430176</v>
+        <v>16.51932144165039</v>
       </c>
       <c r="C35" t="n">
-        <v>16.59161407767043</v>
+        <v>16.59161599336631</v>
       </c>
       <c r="D35" t="n">
-        <v>16.37473044756441</v>
+        <v>16.37473233821854</v>
       </c>
       <c r="E35" t="n">
-        <v>16.59161407767043</v>
+        <v>16.59161599336631</v>
       </c>
       <c r="F35" t="n">
         <v>1111500</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739356994629</v>
+        <v>16.53739547729492</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872515501472</v>
+        <v>16.61872707174377</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821536687546</v>
+        <v>16.24821724087158</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872515501472</v>
+        <v>16.61872707174377</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -1192,16 +1192,16 @@
         <v>43833</v>
       </c>
       <c r="B39" t="n">
-        <v>16.49941253662109</v>
+        <v>16.49941062927246</v>
       </c>
       <c r="C39" t="n">
-        <v>16.67357349182081</v>
+        <v>16.673571564339</v>
       </c>
       <c r="D39" t="n">
-        <v>16.20608992681567</v>
+        <v>16.20608805337542</v>
       </c>
       <c r="E39" t="n">
-        <v>16.22442302701367</v>
+        <v>16.22442115145411</v>
       </c>
       <c r="F39" t="n">
         <v>1551100</v>
@@ -1212,16 +1212,16 @@
         <v>43836</v>
       </c>
       <c r="B40" t="n">
-        <v>16.32525253295898</v>
+        <v>16.32525062561035</v>
       </c>
       <c r="C40" t="n">
-        <v>16.5819107056687</v>
+        <v>16.58190876833361</v>
       </c>
       <c r="D40" t="n">
-        <v>16.3160859823257</v>
+        <v>16.31608407604803</v>
       </c>
       <c r="E40" t="n">
-        <v>16.49941349830989</v>
+        <v>16.49941157061329</v>
       </c>
       <c r="F40" t="n">
         <v>970100</v>
@@ -1272,16 +1272,16 @@
         <v>43839</v>
       </c>
       <c r="B43" t="n">
-        <v>14.40032005310059</v>
+        <v>14.4003210067749</v>
       </c>
       <c r="C43" t="n">
-        <v>15.28945527034375</v>
+        <v>15.28945628290185</v>
       </c>
       <c r="D43" t="n">
-        <v>14.30865630420819</v>
+        <v>14.30865725181199</v>
       </c>
       <c r="E43" t="n">
-        <v>15.09696122283566</v>
+        <v>15.09696222264567</v>
       </c>
       <c r="F43" t="n">
         <v>3315800</v>
@@ -1332,16 +1332,16 @@
         <v>43844</v>
       </c>
       <c r="B46" t="n">
-        <v>15.7202730178833</v>
+        <v>15.72027206420898</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74777266775395</v>
+        <v>15.74777171241136</v>
       </c>
       <c r="D46" t="n">
-        <v>15.2436229101692</v>
+        <v>15.24362198541098</v>
       </c>
       <c r="E46" t="n">
-        <v>15.35361976131116</v>
+        <v>15.35361882987996</v>
       </c>
       <c r="F46" t="n">
         <v>2831800</v>
@@ -1352,16 +1352,16 @@
         <v>43845</v>
       </c>
       <c r="B47" t="n">
-        <v>15.76610469818115</v>
+        <v>15.76610565185547</v>
       </c>
       <c r="C47" t="n">
-        <v>15.76610469818115</v>
+        <v>15.76610565185547</v>
       </c>
       <c r="D47" t="n">
-        <v>15.3536187198054</v>
+        <v>15.35361964852889</v>
       </c>
       <c r="E47" t="n">
-        <v>15.72027195150578</v>
+        <v>15.72027290240772</v>
       </c>
       <c r="F47" t="n">
         <v>1838000</v>
@@ -1372,16 +1372,16 @@
         <v>43846</v>
       </c>
       <c r="B48" t="n">
-        <v>16.10525703430176</v>
+        <v>16.10525894165039</v>
       </c>
       <c r="C48" t="n">
-        <v>16.34358205353058</v>
+        <v>16.34358398910408</v>
       </c>
       <c r="D48" t="n">
-        <v>15.56444290380952</v>
+        <v>15.56444474710943</v>
       </c>
       <c r="E48" t="n">
-        <v>15.76610347687872</v>
+        <v>15.76610534406134</v>
       </c>
       <c r="F48" t="n">
         <v>3608000</v>
@@ -1392,16 +1392,16 @@
         <v>43847</v>
       </c>
       <c r="B49" t="n">
-        <v>16.31608581542969</v>
+        <v>16.31608390808105</v>
       </c>
       <c r="C49" t="n">
-        <v>16.31608581542969</v>
+        <v>16.31608390808105</v>
       </c>
       <c r="D49" t="n">
-        <v>15.93109943447349</v>
+        <v>15.93109757212972</v>
       </c>
       <c r="E49" t="n">
-        <v>16.22442380671596</v>
+        <v>16.2244219100826</v>
       </c>
       <c r="F49" t="n">
         <v>2719000</v>
@@ -1492,16 +1492,16 @@
         <v>43854</v>
       </c>
       <c r="B54" t="n">
-        <v>15.73860645294189</v>
+        <v>15.73860740661621</v>
       </c>
       <c r="C54" t="n">
-        <v>15.80277055566578</v>
+        <v>15.80277151322809</v>
       </c>
       <c r="D54" t="n">
-        <v>15.39945109067764</v>
+        <v>15.39945202380098</v>
       </c>
       <c r="E54" t="n">
-        <v>15.57361204688581</v>
+        <v>15.57361299056236</v>
       </c>
       <c r="F54" t="n">
         <v>887500</v>
@@ -1552,16 +1552,16 @@
         <v>43859</v>
       </c>
       <c r="B57" t="n">
-        <v>15.21612453460693</v>
+        <v>15.21612548828125</v>
       </c>
       <c r="C57" t="n">
-        <v>15.64694187911524</v>
+        <v>15.64694285979114</v>
       </c>
       <c r="D57" t="n">
-        <v>15.16112698491963</v>
+        <v>15.16112793514696</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4086168326828</v>
+        <v>15.40861779842162</v>
       </c>
       <c r="F57" t="n">
         <v>686700</v>
@@ -1592,16 +1592,16 @@
         <v>43861</v>
       </c>
       <c r="B59" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C59" t="n">
-        <v>15.21612414517745</v>
+        <v>15.21612513461457</v>
       </c>
       <c r="D59" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="E59" t="n">
-        <v>14.94113290709765</v>
+        <v>14.94113387865332</v>
       </c>
       <c r="F59" t="n">
         <v>897400</v>
@@ -1612,16 +1612,16 @@
         <v>43864</v>
       </c>
       <c r="B60" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C60" t="n">
-        <v>15.01446355425082</v>
+        <v>15.01446453057486</v>
       </c>
       <c r="D60" t="n">
-        <v>14.59281277020523</v>
+        <v>14.59281371911118</v>
       </c>
       <c r="E60" t="n">
-        <v>14.73030751507486</v>
+        <v>14.73030847292148</v>
       </c>
       <c r="F60" t="n">
         <v>1344600</v>
@@ -1632,16 +1632,16 @@
         <v>43865</v>
       </c>
       <c r="B61" t="n">
-        <v>14.92280197143555</v>
+        <v>14.92280292510986</v>
       </c>
       <c r="C61" t="n">
-        <v>15.03279707105302</v>
+        <v>15.03279803175682</v>
       </c>
       <c r="D61" t="n">
-        <v>14.6844769244769</v>
+        <v>14.68447786292053</v>
       </c>
       <c r="E61" t="n">
-        <v>14.92280197143555</v>
+        <v>14.92280292510986</v>
       </c>
       <c r="F61" t="n">
         <v>708300</v>
@@ -1752,16 +1752,16 @@
         <v>43873</v>
       </c>
       <c r="B67" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C67" t="n">
-        <v>14.757807163385</v>
+        <v>14.7578081230198</v>
       </c>
       <c r="D67" t="n">
-        <v>14.29949018159255</v>
+        <v>14.29949111142503</v>
       </c>
       <c r="E67" t="n">
-        <v>14.29949018159255</v>
+        <v>14.29949111142503</v>
       </c>
       <c r="F67" t="n">
         <v>2320900</v>
@@ -1832,16 +1832,16 @@
         <v>43879</v>
       </c>
       <c r="B71" t="n">
-        <v>15.48194694519043</v>
+        <v>15.48194789886475</v>
       </c>
       <c r="C71" t="n">
-        <v>15.57361069038642</v>
+        <v>15.57361164970714</v>
       </c>
       <c r="D71" t="n">
-        <v>14.48281666823953</v>
+        <v>14.4828175603683</v>
       </c>
       <c r="E71" t="n">
-        <v>14.64781018575394</v>
+        <v>14.64781108804616</v>
       </c>
       <c r="F71" t="n">
         <v>4553800</v>
@@ -1892,16 +1892,16 @@
         <v>43882</v>
       </c>
       <c r="B74" t="n">
-        <v>16.04109573364258</v>
+        <v>16.04109382629395</v>
       </c>
       <c r="C74" t="n">
-        <v>16.04109573364258</v>
+        <v>16.04109382629395</v>
       </c>
       <c r="D74" t="n">
-        <v>15.43611740584103</v>
+        <v>15.43611557042667</v>
       </c>
       <c r="E74" t="n">
-        <v>15.63777626566132</v>
+        <v>15.63777440626894</v>
       </c>
       <c r="F74" t="n">
         <v>1940300</v>
@@ -1932,16 +1932,16 @@
         <v>43888</v>
       </c>
       <c r="B76" t="n">
-        <v>14.47365188598633</v>
+        <v>14.47365093231201</v>
       </c>
       <c r="C76" t="n">
-        <v>14.88613704138841</v>
+        <v>14.88613606053529</v>
       </c>
       <c r="D76" t="n">
-        <v>14.09783205830509</v>
+        <v>14.09783112939368</v>
       </c>
       <c r="E76" t="n">
-        <v>14.56531564237362</v>
+        <v>14.56531468265955</v>
       </c>
       <c r="F76" t="n">
         <v>1056800</v>
@@ -2032,16 +2032,16 @@
         <v>43895</v>
       </c>
       <c r="B81" t="n">
-        <v>13.29119396209717</v>
+        <v>13.29119300842285</v>
       </c>
       <c r="C81" t="n">
-        <v>14.68447816255327</v>
+        <v>14.68447710890754</v>
       </c>
       <c r="D81" t="n">
-        <v>13.22702985718708</v>
+        <v>13.22702890811669</v>
       </c>
       <c r="E81" t="n">
-        <v>14.62031318347281</v>
+        <v>14.62031213443108</v>
       </c>
       <c r="F81" t="n">
         <v>2239700</v>
@@ -2172,16 +2172,16 @@
         <v>43906</v>
       </c>
       <c r="B88" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="C88" t="n">
-        <v>8.918848503012144</v>
+        <v>8.918849065390972</v>
       </c>
       <c r="D88" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="E88" t="n">
-        <v>8.918848503012144</v>
+        <v>8.918849065390972</v>
       </c>
       <c r="F88" t="n">
         <v>1319600</v>
@@ -2252,16 +2252,16 @@
         <v>43910</v>
       </c>
       <c r="B92" t="n">
-        <v>5.820626258850098</v>
+        <v>5.820625782012939</v>
       </c>
       <c r="C92" t="n">
-        <v>6.508101811558814</v>
+        <v>6.508101278402306</v>
       </c>
       <c r="D92" t="n">
-        <v>5.756462153665136</v>
+        <v>5.756461682084427</v>
       </c>
       <c r="E92" t="n">
-        <v>6.278943293989242</v>
+        <v>6.27894277960585</v>
       </c>
       <c r="F92" t="n">
         <v>2218000</v>
@@ -2332,16 +2332,16 @@
         <v>43916</v>
       </c>
       <c r="B96" t="n">
-        <v>6.874755382537842</v>
+        <v>6.874754905700684</v>
       </c>
       <c r="C96" t="n">
-        <v>7.653894675560271</v>
+        <v>7.653894144681544</v>
       </c>
       <c r="D96" t="n">
-        <v>6.29727582550422</v>
+        <v>6.297275388721391</v>
       </c>
       <c r="E96" t="n">
-        <v>6.471436347645401</v>
+        <v>6.471435898782693</v>
       </c>
       <c r="F96" t="n">
         <v>4787500</v>
@@ -2432,16 +2432,16 @@
         <v>43923</v>
       </c>
       <c r="B101" t="n">
-        <v>5.536469459533691</v>
+        <v>5.536468982696533</v>
       </c>
       <c r="C101" t="n">
-        <v>5.793127178086285</v>
+        <v>5.793126679144077</v>
       </c>
       <c r="D101" t="n">
-        <v>5.334810166952138</v>
+        <v>5.334809707483203</v>
       </c>
       <c r="E101" t="n">
-        <v>5.408140818799975</v>
+        <v>5.408140353015323</v>
       </c>
       <c r="F101" t="n">
         <v>2769000</v>
@@ -2452,16 +2452,16 @@
         <v>43924</v>
       </c>
       <c r="B102" t="n">
-        <v>5.582301139831543</v>
+        <v>5.582300662994385</v>
       </c>
       <c r="C102" t="n">
-        <v>5.71062977606757</v>
+        <v>5.710629288268649</v>
       </c>
       <c r="D102" t="n">
-        <v>5.068986157802285</v>
+        <v>5.068985724812216</v>
       </c>
       <c r="E102" t="n">
-        <v>5.609799914768118</v>
+        <v>5.609799435582029</v>
       </c>
       <c r="F102" t="n">
         <v>3057300</v>
@@ -2492,16 +2492,16 @@
         <v>43928</v>
       </c>
       <c r="B104" t="n">
-        <v>7.342238426208496</v>
+        <v>7.342238903045654</v>
       </c>
       <c r="C104" t="n">
-        <v>7.846387292556186</v>
+        <v>7.846387802134982</v>
       </c>
       <c r="D104" t="n">
-        <v>6.608931063718246</v>
+        <v>6.608931492931209</v>
       </c>
       <c r="E104" t="n">
-        <v>6.773925023590238</v>
+        <v>6.773925463518632</v>
       </c>
       <c r="F104" t="n">
         <v>4216400</v>
@@ -2532,16 +2532,16 @@
         <v>43930</v>
       </c>
       <c r="B106" t="n">
-        <v>7.883052349090576</v>
+        <v>7.883052825927734</v>
       </c>
       <c r="C106" t="n">
-        <v>8.653024135661383</v>
+        <v>8.653024659073285</v>
       </c>
       <c r="D106" t="n">
-        <v>7.718057957740275</v>
+        <v>7.718058424597103</v>
       </c>
       <c r="E106" t="n">
-        <v>8.121376512610697</v>
+        <v>8.12137700386382</v>
       </c>
       <c r="F106" t="n">
         <v>2853400</v>
@@ -2672,16 +2672,16 @@
         <v>43943</v>
       </c>
       <c r="B113" t="n">
-        <v>8.983012199401855</v>
+        <v>8.983013153076172</v>
       </c>
       <c r="C113" t="n">
-        <v>9.28550130988736</v>
+        <v>9.285502295675192</v>
       </c>
       <c r="D113" t="n">
-        <v>8.57052712820982</v>
+        <v>8.570528038092988</v>
       </c>
       <c r="E113" t="n">
-        <v>8.579692802641055</v>
+        <v>8.57969371349729</v>
       </c>
       <c r="F113" t="n">
         <v>2037400</v>
@@ -2732,16 +2732,16 @@
         <v>43948</v>
       </c>
       <c r="B116" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C116" t="n">
-        <v>7.947216534214704</v>
+        <v>7.947217050986978</v>
       </c>
       <c r="D116" t="n">
-        <v>7.296406385102614</v>
+        <v>7.296406859555589</v>
       </c>
       <c r="E116" t="n">
-        <v>7.928883435341277</v>
+        <v>7.928883950921431</v>
       </c>
       <c r="F116" t="n">
         <v>2360400</v>
@@ -2772,16 +2772,16 @@
         <v>43950</v>
       </c>
       <c r="B118" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C118" t="n">
-        <v>9.166340069149538</v>
+        <v>9.166339110682868</v>
       </c>
       <c r="D118" t="n">
-        <v>8.258872612104607</v>
+        <v>8.258871748526117</v>
       </c>
       <c r="E118" t="n">
-        <v>8.442199238653536</v>
+        <v>8.442198355905731</v>
       </c>
       <c r="F118" t="n">
         <v>3867700</v>
@@ -2852,16 +2852,16 @@
         <v>43957</v>
       </c>
       <c r="B122" t="n">
-        <v>7.828054904937744</v>
+        <v>7.828054428100586</v>
       </c>
       <c r="C122" t="n">
-        <v>8.148877178372471</v>
+        <v>8.148876681992785</v>
       </c>
       <c r="D122" t="n">
-        <v>7.553064509732316</v>
+        <v>7.553064049645888</v>
       </c>
       <c r="E122" t="n">
-        <v>7.928884337705908</v>
+        <v>7.928883854726839</v>
       </c>
       <c r="F122" t="n">
         <v>2058000</v>
@@ -2912,16 +2912,16 @@
         <v>43962</v>
       </c>
       <c r="B125" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C125" t="n">
-        <v>7.058081369394968</v>
+        <v>7.058081870301661</v>
       </c>
       <c r="D125" t="n">
-        <v>6.700594244733439</v>
+        <v>6.700594720269542</v>
       </c>
       <c r="E125" t="n">
-        <v>7.058081369394968</v>
+        <v>7.058081870301661</v>
       </c>
       <c r="F125" t="n">
         <v>2505400</v>
@@ -2972,16 +2972,16 @@
         <v>43965</v>
       </c>
       <c r="B128" t="n">
-        <v>6.086450099945068</v>
+        <v>6.08644962310791</v>
       </c>
       <c r="C128" t="n">
-        <v>6.187279969987983</v>
+        <v>6.187279485251405</v>
       </c>
       <c r="D128" t="n">
-        <v>5.701463720767742</v>
+        <v>5.701463274091976</v>
       </c>
       <c r="E128" t="n">
-        <v>5.893956910356406</v>
+        <v>5.893956448599943</v>
       </c>
       <c r="F128" t="n">
         <v>4161800</v>
@@ -2992,16 +2992,16 @@
         <v>43966</v>
       </c>
       <c r="B129" t="n">
-        <v>6.049784183502197</v>
+        <v>6.049784660339355</v>
       </c>
       <c r="C129" t="n">
-        <v>6.645596358206725</v>
+        <v>6.645596882005126</v>
       </c>
       <c r="D129" t="n">
-        <v>5.857291012642501</v>
+        <v>5.857291474307565</v>
       </c>
       <c r="E129" t="n">
-        <v>6.049784183502197</v>
+        <v>6.049784660339355</v>
       </c>
       <c r="F129" t="n">
         <v>4143200</v>
@@ -3012,16 +3012,16 @@
         <v>43969</v>
       </c>
       <c r="B130" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C130" t="n">
-        <v>6.856422193632849</v>
+        <v>6.856422675624999</v>
       </c>
       <c r="D130" t="n">
-        <v>6.260610018716203</v>
+        <v>6.260610458824003</v>
       </c>
       <c r="E130" t="n">
-        <v>6.462269739252984</v>
+        <v>6.46227019353704</v>
       </c>
       <c r="F130" t="n">
         <v>4121800</v>
@@ -3032,16 +3032,16 @@
         <v>43970</v>
       </c>
       <c r="B131" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C131" t="n">
-        <v>7.553063650138711</v>
+        <v>7.55306414128097</v>
       </c>
       <c r="D131" t="n">
-        <v>6.709760770792116</v>
+        <v>6.709761207098126</v>
       </c>
       <c r="E131" t="n">
-        <v>6.828922853873451</v>
+        <v>6.828923297928043</v>
       </c>
       <c r="F131" t="n">
         <v>3759800</v>
@@ -3072,16 +3072,16 @@
         <v>43972</v>
       </c>
       <c r="B133" t="n">
-        <v>7.727224349975586</v>
+        <v>7.727224826812744</v>
       </c>
       <c r="C133" t="n">
-        <v>7.873885639674015</v>
+        <v>7.873886125561454</v>
       </c>
       <c r="D133" t="n">
-        <v>7.461400543854623</v>
+        <v>7.461401004288134</v>
       </c>
       <c r="E133" t="n">
-        <v>7.55306341283102</v>
+        <v>7.55306387892093</v>
       </c>
       <c r="F133" t="n">
         <v>2073000</v>
@@ -3112,16 +3112,16 @@
         <v>43976</v>
       </c>
       <c r="B135" t="n">
-        <v>7.75472354888916</v>
+        <v>7.754724025726318</v>
       </c>
       <c r="C135" t="n">
-        <v>7.828054197763313</v>
+        <v>7.828054679109565</v>
       </c>
       <c r="D135" t="n">
-        <v>7.397235979999946</v>
+        <v>7.39723643485523</v>
       </c>
       <c r="E135" t="n">
-        <v>7.397235979999946</v>
+        <v>7.39723643485523</v>
       </c>
       <c r="F135" t="n">
         <v>2073000</v>
@@ -3132,16 +3132,16 @@
         <v>43977</v>
       </c>
       <c r="B136" t="n">
-        <v>7.626394271850586</v>
+        <v>7.626394748687744</v>
       </c>
       <c r="C136" t="n">
-        <v>8.286370968197739</v>
+        <v>8.286371486299668</v>
       </c>
       <c r="D136" t="n">
-        <v>7.608062047208583</v>
+        <v>7.608062522899527</v>
       </c>
       <c r="E136" t="n">
-        <v>7.974715281751298</v>
+        <v>7.974715780367084</v>
       </c>
       <c r="F136" t="n">
         <v>2630000</v>
@@ -3152,16 +3152,16 @@
         <v>43978</v>
       </c>
       <c r="B137" t="n">
-        <v>8.158042907714844</v>
+        <v>8.158041954040527</v>
       </c>
       <c r="C137" t="n">
-        <v>8.158042907714844</v>
+        <v>8.158041954040527</v>
       </c>
       <c r="D137" t="n">
-        <v>7.653894866426351</v>
+        <v>7.653893971686885</v>
       </c>
       <c r="E137" t="n">
-        <v>7.745557749310453</v>
+        <v>7.745556843855605</v>
       </c>
       <c r="F137" t="n">
         <v>2323900</v>
@@ -3212,16 +3212,16 @@
         <v>43983</v>
       </c>
       <c r="B140" t="n">
-        <v>8.955513954162598</v>
+        <v>8.955514907836914</v>
       </c>
       <c r="C140" t="n">
-        <v>9.065509921334565</v>
+        <v>9.065510886722372</v>
       </c>
       <c r="D140" t="n">
-        <v>8.56136108283537</v>
+        <v>8.561361994536275</v>
       </c>
       <c r="E140" t="n">
-        <v>8.662190500867112</v>
+        <v>8.662191423305361</v>
       </c>
       <c r="F140" t="n">
         <v>3007600</v>
@@ -3332,16 +3332,16 @@
         <v>43991</v>
       </c>
       <c r="B146" t="n">
-        <v>11.93457508087158</v>
+        <v>11.93457412719727</v>
       </c>
       <c r="C146" t="n">
-        <v>12.34706020539017</v>
+        <v>12.34705921875477</v>
       </c>
       <c r="D146" t="n">
-        <v>11.0546064072858</v>
+        <v>11.05460552392848</v>
       </c>
       <c r="E146" t="n">
-        <v>11.27459835713967</v>
+        <v>11.27459745620312</v>
       </c>
       <c r="F146" t="n">
         <v>3964300</v>
@@ -3612,16 +3612,16 @@
         <v>44012</v>
       </c>
       <c r="B160" t="n">
-        <v>9.450497627258301</v>
+        <v>9.450496673583984</v>
       </c>
       <c r="C160" t="n">
-        <v>9.633824266054166</v>
+        <v>9.633823293879882</v>
       </c>
       <c r="D160" t="n">
-        <v>9.120508803255376</v>
+        <v>9.120507882881091</v>
       </c>
       <c r="E160" t="n">
-        <v>9.532993959088664</v>
+        <v>9.532992997089428</v>
       </c>
       <c r="F160" t="n">
         <v>4221600</v>
@@ -3732,16 +3732,16 @@
         <v>44020</v>
       </c>
       <c r="B166" t="n">
-        <v>10.19297122955322</v>
+        <v>10.19297027587891</v>
       </c>
       <c r="C166" t="n">
-        <v>10.94461092232337</v>
+        <v>10.94460989832417</v>
       </c>
       <c r="D166" t="n">
-        <v>10.14713934907861</v>
+        <v>10.14713839969241</v>
       </c>
       <c r="E166" t="n">
-        <v>10.77045082552434</v>
+        <v>10.7704498178199</v>
       </c>
       <c r="F166" t="n">
         <v>5151100</v>
@@ -3792,16 +3792,16 @@
         <v>44025</v>
       </c>
       <c r="B169" t="n">
-        <v>10.50462627410889</v>
+        <v>10.50462532043457</v>
       </c>
       <c r="C169" t="n">
-        <v>11.09127238227016</v>
+        <v>11.09127137533651</v>
       </c>
       <c r="D169" t="n">
-        <v>10.32129963848672</v>
+        <v>10.32129870145592</v>
       </c>
       <c r="E169" t="n">
-        <v>10.8896126460006</v>
+        <v>10.88961165737486</v>
       </c>
       <c r="F169" t="n">
         <v>4409000</v>
@@ -3932,16 +3932,16 @@
         <v>44034</v>
       </c>
       <c r="B176" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C176" t="n">
-        <v>10.00047677558407</v>
+        <v>10.00047581575137</v>
       </c>
       <c r="D176" t="n">
-        <v>9.67965540087379</v>
+        <v>9.679654471833102</v>
       </c>
       <c r="E176" t="n">
-        <v>9.881314250976148</v>
+        <v>9.881313302580509</v>
       </c>
       <c r="F176" t="n">
         <v>2365200</v>
@@ -3952,16 +3952,16 @@
         <v>44035</v>
       </c>
       <c r="B177" t="n">
-        <v>9.771317481994629</v>
+        <v>9.771318435668945</v>
       </c>
       <c r="C177" t="n">
-        <v>10.10130625383415</v>
+        <v>10.10130723971515</v>
       </c>
       <c r="D177" t="n">
-        <v>9.670488065138237</v>
+        <v>9.670489008971668</v>
       </c>
       <c r="E177" t="n">
-        <v>9.982143738911011</v>
+        <v>9.982144713161835</v>
       </c>
       <c r="F177" t="n">
         <v>2784800</v>
@@ -3972,16 +3972,16 @@
         <v>44036</v>
       </c>
       <c r="B178" t="n">
-        <v>9.578825950622559</v>
+        <v>9.578824996948242</v>
       </c>
       <c r="C178" t="n">
-        <v>9.72548726339387</v>
+        <v>9.725486295117854</v>
       </c>
       <c r="D178" t="n">
-        <v>9.193839567512681</v>
+        <v>9.193838652167866</v>
       </c>
       <c r="E178" t="n">
-        <v>9.652156607008214</v>
+        <v>9.652155646033048</v>
       </c>
       <c r="F178" t="n">
         <v>3085100</v>
@@ -4312,16 +4312,16 @@
         <v>44061</v>
       </c>
       <c r="B195" t="n">
-        <v>9.532992362976074</v>
+        <v>9.532993316650391</v>
       </c>
       <c r="C195" t="n">
-        <v>9.734652068972748</v>
+        <v>9.73465304282097</v>
       </c>
       <c r="D195" t="n">
-        <v>9.248836338961429</v>
+        <v>9.248837264208962</v>
       </c>
       <c r="E195" t="n">
-        <v>9.31300043325437</v>
+        <v>9.313001364920838</v>
       </c>
       <c r="F195" t="n">
         <v>3391400</v>
@@ -4352,16 +4352,16 @@
         <v>44063</v>
       </c>
       <c r="B197" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C197" t="n">
-        <v>9.945478824484717</v>
+        <v>9.945479787030456</v>
       </c>
       <c r="D197" t="n">
-        <v>9.010511764854147</v>
+        <v>9.010512636911677</v>
       </c>
       <c r="E197" t="n">
-        <v>9.074675862376543</v>
+        <v>9.074676740644019</v>
       </c>
       <c r="F197" t="n">
         <v>3999100</v>
@@ -4372,16 +4372,16 @@
         <v>44064</v>
       </c>
       <c r="B198" t="n">
-        <v>10.38546276092529</v>
+        <v>10.38546371459961</v>
       </c>
       <c r="C198" t="n">
-        <v>10.54129060502008</v>
+        <v>10.54129157300373</v>
       </c>
       <c r="D198" t="n">
-        <v>9.652155413568103</v>
+        <v>9.65215629990441</v>
       </c>
       <c r="E198" t="n">
-        <v>9.85381513077964</v>
+        <v>9.853816035633919</v>
       </c>
       <c r="F198" t="n">
         <v>4055100</v>
@@ -4392,16 +4392,16 @@
         <v>44067</v>
       </c>
       <c r="B199" t="n">
-        <v>10.22046947479248</v>
+        <v>10.22046852111816</v>
       </c>
       <c r="C199" t="n">
-        <v>10.74295148626354</v>
+        <v>10.7429504838363</v>
       </c>
       <c r="D199" t="n">
-        <v>10.16547192042944</v>
+        <v>10.16547097188696</v>
       </c>
       <c r="E199" t="n">
-        <v>10.54129174720154</v>
+        <v>10.54129076359123</v>
       </c>
       <c r="F199" t="n">
         <v>2579200</v>
@@ -4472,16 +4472,16 @@
         <v>44071</v>
       </c>
       <c r="B203" t="n">
-        <v>11.07293891906738</v>
+        <v>11.07293796539307</v>
       </c>
       <c r="C203" t="n">
-        <v>11.12793734503842</v>
+        <v>11.12793638662728</v>
       </c>
       <c r="D203" t="n">
-        <v>10.3579646264658</v>
+        <v>10.35796373436977</v>
       </c>
       <c r="E203" t="n">
-        <v>10.51379248018504</v>
+        <v>10.51379157466809</v>
       </c>
       <c r="F203" t="n">
         <v>2710200</v>
@@ -4512,16 +4512,16 @@
         <v>44075</v>
       </c>
       <c r="B205" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="C205" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="D205" t="n">
-        <v>10.96294209712684</v>
+        <v>10.96294298891299</v>
       </c>
       <c r="E205" t="n">
-        <v>11.14626871262991</v>
+        <v>11.14626961932886</v>
       </c>
       <c r="F205" t="n">
         <v>3676800</v>
@@ -4652,16 +4652,16 @@
         <v>44085</v>
       </c>
       <c r="B212" t="n">
-        <v>10.83461380004883</v>
+        <v>10.83461284637451</v>
       </c>
       <c r="C212" t="n">
-        <v>11.54958896263513</v>
+        <v>11.54958794602793</v>
       </c>
       <c r="D212" t="n">
-        <v>10.66962027144226</v>
+        <v>10.66961933229085</v>
       </c>
       <c r="E212" t="n">
-        <v>11.43959211133699</v>
+        <v>11.43959110441184</v>
       </c>
       <c r="F212" t="n">
         <v>2696500</v>
@@ -4692,16 +4692,16 @@
         <v>44089</v>
       </c>
       <c r="B214" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="C214" t="n">
-        <v>12.09956866086264</v>
+        <v>12.09956963671544</v>
       </c>
       <c r="D214" t="n">
-        <v>11.62291943402496</v>
+        <v>11.62292037143511</v>
       </c>
       <c r="E214" t="n">
-        <v>12.017071460752</v>
+        <v>12.01707242995125</v>
       </c>
       <c r="F214" t="n">
         <v>2177400</v>
@@ -4772,16 +4772,16 @@
         <v>44095</v>
       </c>
       <c r="B218" t="n">
-        <v>11.32043075561523</v>
+        <v>11.32042980194092</v>
       </c>
       <c r="C218" t="n">
-        <v>11.73291589921649</v>
+        <v>11.73291491079292</v>
       </c>
       <c r="D218" t="n">
-        <v>11.00877504181907</v>
+        <v>11.00877411439977</v>
       </c>
       <c r="E218" t="n">
-        <v>11.70541712275516</v>
+        <v>11.70541613664819</v>
       </c>
       <c r="F218" t="n">
         <v>2982400</v>
@@ -4872,16 +4872,16 @@
         <v>44102</v>
       </c>
       <c r="B223" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C223" t="n">
-        <v>11.44875714774106</v>
+        <v>11.44875814201422</v>
       </c>
       <c r="D223" t="n">
-        <v>10.86211201394924</v>
+        <v>10.8621129572749</v>
       </c>
       <c r="E223" t="n">
-        <v>11.39375960353318</v>
+        <v>11.39376059303005</v>
       </c>
       <c r="F223" t="n">
         <v>1430300</v>
@@ -4932,16 +4932,16 @@
         <v>44105</v>
       </c>
       <c r="B226" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C226" t="n">
-        <v>11.18293500609905</v>
+        <v>11.18293403814347</v>
       </c>
       <c r="D226" t="n">
-        <v>10.58712323547157</v>
+        <v>10.58712231908736</v>
       </c>
       <c r="E226" t="n">
-        <v>10.61462201164059</v>
+        <v>10.61462109287619</v>
       </c>
       <c r="F226" t="n">
         <v>1825000</v>
@@ -4992,16 +4992,16 @@
         <v>44110</v>
       </c>
       <c r="B229" t="n">
-        <v>11.03627395629883</v>
+        <v>11.03627300262451</v>
       </c>
       <c r="C229" t="n">
-        <v>11.35709622431771</v>
+        <v>11.35709524292028</v>
       </c>
       <c r="D229" t="n">
-        <v>10.99960862916841</v>
+        <v>10.99960767866245</v>
       </c>
       <c r="E229" t="n">
-        <v>11.35709622431771</v>
+        <v>11.35709524292028</v>
       </c>
       <c r="F229" t="n">
         <v>1315200</v>
@@ -5012,16 +5012,16 @@
         <v>44111</v>
       </c>
       <c r="B230" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C230" t="n">
-        <v>11.23793231185949</v>
+        <v>11.23793329027351</v>
       </c>
       <c r="D230" t="n">
-        <v>10.81628066458053</v>
+        <v>10.81628160628407</v>
       </c>
       <c r="E230" t="n">
-        <v>11.10043669638599</v>
+        <v>11.10043766282916</v>
       </c>
       <c r="F230" t="n">
         <v>1553900</v>
@@ -5032,16 +5032,16 @@
         <v>44112</v>
       </c>
       <c r="B231" t="n">
-        <v>11.03627395629883</v>
+        <v>11.03627300262451</v>
       </c>
       <c r="C231" t="n">
-        <v>11.09127238407963</v>
+        <v>11.09127142565275</v>
       </c>
       <c r="D231" t="n">
-        <v>10.83461421999638</v>
+        <v>10.83461328374802</v>
       </c>
       <c r="E231" t="n">
-        <v>10.99960862916841</v>
+        <v>10.99960767866245</v>
       </c>
       <c r="F231" t="n">
         <v>1563000</v>
@@ -5112,16 +5112,16 @@
         <v>44119</v>
       </c>
       <c r="B235" t="n">
-        <v>11.57708835601807</v>
+        <v>11.57708740234375</v>
       </c>
       <c r="C235" t="n">
-        <v>11.62292023414239</v>
+        <v>11.62291927669263</v>
       </c>
       <c r="D235" t="n">
-        <v>10.92627813432967</v>
+        <v>10.92627723426651</v>
       </c>
       <c r="E235" t="n">
-        <v>10.99960878966045</v>
+        <v>10.99960788355659</v>
       </c>
       <c r="F235" t="n">
         <v>4442200</v>
@@ -5232,16 +5232,16 @@
         <v>44127</v>
       </c>
       <c r="B241" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="C241" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="D241" t="n">
-        <v>11.31126373323825</v>
+        <v>11.31126464551279</v>
       </c>
       <c r="E241" t="n">
-        <v>11.49459035894505</v>
+        <v>11.49459128600522</v>
       </c>
       <c r="F241" t="n">
         <v>1343300</v>
@@ -5272,16 +5272,16 @@
         <v>44131</v>
       </c>
       <c r="B243" t="n">
-        <v>11.90707588195801</v>
+        <v>11.90707492828369</v>
       </c>
       <c r="C243" t="n">
-        <v>12.45705665156882</v>
+        <v>12.45705565384485</v>
       </c>
       <c r="D243" t="n">
-        <v>11.77874767677373</v>
+        <v>11.77874673337762</v>
       </c>
       <c r="E243" t="n">
-        <v>12.20956504299285</v>
+        <v>12.20956406509125</v>
       </c>
       <c r="F243" t="n">
         <v>2061500</v>
@@ -5352,16 +5352,16 @@
         <v>44138</v>
       </c>
       <c r="B247" t="n">
-        <v>10.87127876281738</v>
+        <v>10.8712797164917</v>
       </c>
       <c r="C247" t="n">
-        <v>11.17376790836278</v>
+        <v>11.17376888857272</v>
       </c>
       <c r="D247" t="n">
-        <v>10.66961991523398</v>
+        <v>10.66962085121793</v>
       </c>
       <c r="E247" t="n">
-        <v>10.9996078356007</v>
+        <v>10.99960880053258</v>
       </c>
       <c r="F247" t="n">
         <v>2487500</v>
@@ -5492,16 +5492,16 @@
         <v>44147</v>
       </c>
       <c r="B254" t="n">
-        <v>11.6412525177002</v>
+        <v>11.64125156402588</v>
       </c>
       <c r="C254" t="n">
-        <v>12.54872003747481</v>
+        <v>12.54871900945897</v>
       </c>
       <c r="D254" t="n">
-        <v>11.62292029086322</v>
+        <v>11.62291933869072</v>
       </c>
       <c r="E254" t="n">
-        <v>12.54872003747481</v>
+        <v>12.54871900945897</v>
       </c>
       <c r="F254" t="n">
         <v>2275500</v>
@@ -5512,16 +5512,16 @@
         <v>44148</v>
       </c>
       <c r="B255" t="n">
-        <v>11.86124420166016</v>
+        <v>11.86124324798584</v>
       </c>
       <c r="C255" t="n">
-        <v>12.05373738679096</v>
+        <v>12.0537364176397</v>
       </c>
       <c r="D255" t="n">
-        <v>11.47625870556891</v>
+        <v>11.47625778284841</v>
       </c>
       <c r="E255" t="n">
-        <v>11.60458691287587</v>
+        <v>11.60458597983746</v>
       </c>
       <c r="F255" t="n">
         <v>1796700</v>
@@ -5572,16 +5572,16 @@
         <v>44153</v>
       </c>
       <c r="B258" t="n">
-        <v>12.64038276672363</v>
+        <v>12.64038372039795</v>
       </c>
       <c r="C258" t="n">
-        <v>12.76871184083297</v>
+        <v>12.76871280418928</v>
       </c>
       <c r="D258" t="n">
-        <v>12.31956051853545</v>
+        <v>12.31956144800481</v>
       </c>
       <c r="E258" t="n">
-        <v>12.57621866675412</v>
+        <v>12.57621961558747</v>
       </c>
       <c r="F258" t="n">
         <v>1757300</v>
@@ -5712,16 +5712,16 @@
         <v>44165</v>
       </c>
       <c r="B265" t="n">
-        <v>12.20956420898438</v>
+        <v>12.20956516265869</v>
       </c>
       <c r="C265" t="n">
-        <v>12.85120868775777</v>
+        <v>12.85120969155017</v>
       </c>
       <c r="D265" t="n">
-        <v>11.9712400409914</v>
+        <v>11.97124097605051</v>
       </c>
       <c r="E265" t="n">
-        <v>12.69538084281798</v>
+        <v>12.69538183443885</v>
       </c>
       <c r="F265" t="n">
         <v>1362800</v>
@@ -5732,16 +5732,16 @@
         <v>44166</v>
       </c>
       <c r="B266" t="n">
-        <v>12.13623428344727</v>
+        <v>12.13623332977295</v>
       </c>
       <c r="C266" t="n">
-        <v>12.38372588984487</v>
+        <v>12.38372491672248</v>
       </c>
       <c r="D266" t="n">
-        <v>12.05373708131473</v>
+        <v>12.05373613412311</v>
       </c>
       <c r="E266" t="n">
-        <v>12.32872746369974</v>
+        <v>12.32872649489916</v>
       </c>
       <c r="F266" t="n">
         <v>1296100</v>
@@ -5752,16 +5752,16 @@
         <v>44167</v>
       </c>
       <c r="B267" t="n">
-        <v>12.3837251663208</v>
+        <v>12.38372611999512</v>
       </c>
       <c r="C267" t="n">
-        <v>12.67704775750314</v>
+        <v>12.67704873376632</v>
       </c>
       <c r="D267" t="n">
-        <v>12.22789732121261</v>
+        <v>12.22789826288658</v>
       </c>
       <c r="E267" t="n">
-        <v>12.25539609559339</v>
+        <v>12.25539703938504</v>
       </c>
       <c r="F267" t="n">
         <v>1547700</v>
@@ -5852,16 +5852,16 @@
         <v>44174</v>
       </c>
       <c r="B272" t="n">
-        <v>12.05373668670654</v>
+        <v>12.05373764038086</v>
       </c>
       <c r="C272" t="n">
-        <v>12.30122828500191</v>
+        <v>12.30122925825741</v>
       </c>
       <c r="D272" t="n">
-        <v>11.87041006250829</v>
+        <v>11.87041100167807</v>
       </c>
       <c r="E272" t="n">
-        <v>12.27372950991475</v>
+        <v>12.27373048099458</v>
       </c>
       <c r="F272" t="n">
         <v>927800</v>
@@ -5892,16 +5892,16 @@
         <v>44176</v>
       </c>
       <c r="B274" t="n">
-        <v>12.05373668670654</v>
+        <v>12.05373764038086</v>
       </c>
       <c r="C274" t="n">
-        <v>12.35622583517624</v>
+        <v>12.35622681278306</v>
       </c>
       <c r="D274" t="n">
-        <v>11.96207381169257</v>
+        <v>11.96207475811465</v>
       </c>
       <c r="E274" t="n">
-        <v>12.15456698564331</v>
+        <v>12.15456794729517</v>
       </c>
       <c r="F274" t="n">
         <v>1470700</v>
@@ -5952,16 +5952,16 @@
         <v>44181</v>
       </c>
       <c r="B277" t="n">
-        <v>12.47538948059082</v>
+        <v>12.4753885269165</v>
       </c>
       <c r="C277" t="n">
-        <v>12.91537429237765</v>
+        <v>12.91537330506894</v>
       </c>
       <c r="D277" t="n">
-        <v>12.38372659733925</v>
+        <v>12.38372565067205</v>
       </c>
       <c r="E277" t="n">
-        <v>12.5578866874365</v>
+        <v>12.55788572745573</v>
       </c>
       <c r="F277" t="n">
         <v>1004500</v>
@@ -5992,16 +5992,16 @@
         <v>44183</v>
       </c>
       <c r="B279" t="n">
-        <v>12.19123363494873</v>
+        <v>12.19123268127441</v>
       </c>
       <c r="C279" t="n">
-        <v>12.51205504360741</v>
+        <v>12.51205406483644</v>
       </c>
       <c r="D279" t="n">
-        <v>12.08123764847972</v>
+        <v>12.08123670340998</v>
       </c>
       <c r="E279" t="n">
-        <v>12.31956184874404</v>
+        <v>12.31956088503109</v>
       </c>
       <c r="F279" t="n">
         <v>677600</v>
@@ -6112,16 +6112,16 @@
         <v>44195</v>
       </c>
       <c r="B285" t="n">
-        <v>11.81541156768799</v>
+        <v>11.8154125213623</v>
       </c>
       <c r="C285" t="n">
-        <v>12.05373572300648</v>
+        <v>12.05373669591699</v>
       </c>
       <c r="D285" t="n">
-        <v>11.77874624577974</v>
+        <v>11.77874719649464</v>
       </c>
       <c r="E285" t="n">
-        <v>11.91624098439311</v>
+        <v>11.91624194620582</v>
       </c>
       <c r="F285" t="n">
         <v>1061200</v>
@@ -6132,16 +6132,16 @@
         <v>44200</v>
       </c>
       <c r="B286" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="C286" t="n">
-        <v>11.89790827327764</v>
+        <v>11.8979092411191</v>
       </c>
       <c r="D286" t="n">
-        <v>11.42125907296965</v>
+        <v>11.42126000203783</v>
       </c>
       <c r="E286" t="n">
-        <v>11.89790827327764</v>
+        <v>11.8979092411191</v>
       </c>
       <c r="F286" t="n">
         <v>1030900</v>
@@ -6152,16 +6152,16 @@
         <v>44201</v>
       </c>
       <c r="B287" t="n">
-        <v>11.26543140411377</v>
+        <v>11.26543235778809</v>
       </c>
       <c r="C287" t="n">
-        <v>11.73291493644768</v>
+        <v>11.73291592969678</v>
       </c>
       <c r="D287" t="n">
-        <v>11.16460198258245</v>
+        <v>11.16460292772106</v>
       </c>
       <c r="E287" t="n">
-        <v>11.73291493644768</v>
+        <v>11.73291592969678</v>
       </c>
       <c r="F287" t="n">
         <v>2157200</v>
@@ -6172,16 +6172,16 @@
         <v>44202</v>
       </c>
       <c r="B288" t="n">
-        <v>11.07293891906738</v>
+        <v>11.07293796539307</v>
       </c>
       <c r="C288" t="n">
-        <v>11.36626152645873</v>
+        <v>11.36626054752155</v>
       </c>
       <c r="D288" t="n">
-        <v>10.91711106534815</v>
+        <v>10.91711012509475</v>
       </c>
       <c r="E288" t="n">
-        <v>11.28376519875766</v>
+        <v>11.2837642269256</v>
       </c>
       <c r="F288" t="n">
         <v>1263500</v>
@@ -6232,16 +6232,16 @@
         <v>44207</v>
       </c>
       <c r="B291" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C291" t="n">
-        <v>11.13710201901154</v>
+        <v>11.13710298864692</v>
       </c>
       <c r="D291" t="n">
-        <v>10.83461288880819</v>
+        <v>10.83461383210779</v>
       </c>
       <c r="E291" t="n">
-        <v>11.04543914953279</v>
+        <v>11.04544011118768</v>
       </c>
       <c r="F291" t="n">
         <v>926700</v>
@@ -6272,16 +6272,16 @@
         <v>44209</v>
       </c>
       <c r="B293" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C293" t="n">
-        <v>10.98127437212461</v>
+        <v>10.98127533221018</v>
       </c>
       <c r="D293" t="n">
-        <v>10.67878523661001</v>
+        <v>10.67878617024915</v>
       </c>
       <c r="E293" t="n">
-        <v>10.8712784023166</v>
+        <v>10.87127935278529</v>
       </c>
       <c r="F293" t="n">
         <v>2157000</v>
@@ -6332,16 +6332,16 @@
         <v>44214</v>
       </c>
       <c r="B296" t="n">
-        <v>11.29293155670166</v>
+        <v>11.29293060302734</v>
       </c>
       <c r="C296" t="n">
-        <v>11.44875941983287</v>
+        <v>11.44875845299908</v>
       </c>
       <c r="D296" t="n">
-        <v>11.0454408103094</v>
+        <v>11.04543987753537</v>
       </c>
       <c r="E296" t="n">
-        <v>11.40292754111715</v>
+        <v>11.40292657815381</v>
       </c>
       <c r="F296" t="n">
         <v>2481600</v>
@@ -6412,16 +6412,16 @@
         <v>44218</v>
       </c>
       <c r="B300" t="n">
-        <v>11.00877475738525</v>
+        <v>11.00877571105957</v>
       </c>
       <c r="C300" t="n">
-        <v>11.19210138600805</v>
+        <v>11.19210235556369</v>
       </c>
       <c r="D300" t="n">
-        <v>10.82544812876246</v>
+        <v>10.82544906655545</v>
       </c>
       <c r="E300" t="n">
-        <v>11.09127195880809</v>
+        <v>11.09127291962902</v>
       </c>
       <c r="F300" t="n">
         <v>3052400</v>
@@ -6612,16 +6612,16 @@
         <v>44235</v>
       </c>
       <c r="B310" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C310" t="n">
-        <v>11.33876286134076</v>
+        <v>11.33876187989727</v>
       </c>
       <c r="D310" t="n">
-        <v>10.91711117201089</v>
+        <v>10.91711022706409</v>
       </c>
       <c r="E310" t="n">
-        <v>11.27459875888959</v>
+        <v>11.27459778299992</v>
       </c>
       <c r="F310" t="n">
         <v>1845700</v>
@@ -6792,16 +6792,16 @@
         <v>44250</v>
       </c>
       <c r="B319" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C319" t="n">
-        <v>10.99960747084441</v>
+        <v>10.99960843253283</v>
       </c>
       <c r="D319" t="n">
-        <v>10.55045704225246</v>
+        <v>10.55045796467195</v>
       </c>
       <c r="E319" t="n">
-        <v>10.67878523661001</v>
+        <v>10.67878617024915</v>
       </c>
       <c r="F319" t="n">
         <v>1964300</v>
@@ -6852,16 +6852,16 @@
         <v>44253</v>
       </c>
       <c r="B322" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C322" t="n">
-        <v>10.65128678074554</v>
+        <v>10.651287786344</v>
       </c>
       <c r="D322" t="n">
-        <v>9.945479068192968</v>
+        <v>9.945480007155426</v>
       </c>
       <c r="E322" t="n">
-        <v>10.60545490674777</v>
+        <v>10.6054559080192</v>
       </c>
       <c r="F322" t="n">
         <v>2794300</v>
@@ -6912,16 +6912,16 @@
         <v>44258</v>
       </c>
       <c r="B325" t="n">
-        <v>9.752985954284668</v>
+        <v>9.752986907958984</v>
       </c>
       <c r="C325" t="n">
-        <v>9.81715005375796</v>
+        <v>9.817151013706422</v>
       </c>
       <c r="D325" t="n">
-        <v>9.184672986201862</v>
+        <v>9.184673884304942</v>
       </c>
       <c r="E325" t="n">
-        <v>9.578825006899601</v>
+        <v>9.578825943543972</v>
       </c>
       <c r="F325" t="n">
         <v>2305100</v>
@@ -7032,16 +7032,16 @@
         <v>44266</v>
       </c>
       <c r="B331" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C331" t="n">
-        <v>10.24796821273983</v>
+        <v>10.24796918026058</v>
       </c>
       <c r="D331" t="n">
-        <v>9.322167679832035</v>
+        <v>9.32216855994705</v>
       </c>
       <c r="E331" t="n">
-        <v>9.404664878193957</v>
+        <v>9.404665766097615</v>
       </c>
       <c r="F331" t="n">
         <v>2921600</v>
@@ -7092,16 +7092,16 @@
         <v>44271</v>
       </c>
       <c r="B334" t="n">
-        <v>9.771317481994629</v>
+        <v>9.771318435668945</v>
       </c>
       <c r="C334" t="n">
-        <v>10.34879695854355</v>
+        <v>10.3487979685795</v>
       </c>
       <c r="D334" t="n">
-        <v>9.734652160031374</v>
+        <v>9.734653110127178</v>
       </c>
       <c r="E334" t="n">
-        <v>10.3121316365803</v>
+        <v>10.31213264303773</v>
       </c>
       <c r="F334" t="n">
         <v>1474300</v>
@@ -7152,16 +7152,16 @@
         <v>44274</v>
       </c>
       <c r="B337" t="n">
-        <v>9.972978591918945</v>
+        <v>9.972977638244629</v>
       </c>
       <c r="C337" t="n">
-        <v>10.10130767391647</v>
+        <v>10.10130670797058</v>
       </c>
       <c r="D337" t="n">
-        <v>9.679655974976443</v>
+        <v>9.679655049351345</v>
       </c>
       <c r="E337" t="n">
-        <v>9.826317283447693</v>
+        <v>9.826316343797988</v>
       </c>
       <c r="F337" t="n">
         <v>1607200</v>
@@ -7212,16 +7212,16 @@
         <v>44279</v>
       </c>
       <c r="B340" t="n">
-        <v>10.38546276092529</v>
+        <v>10.38546371459961</v>
       </c>
       <c r="C340" t="n">
-        <v>10.60545470288137</v>
+        <v>10.60545567675706</v>
       </c>
       <c r="D340" t="n">
-        <v>10.21130269208597</v>
+        <v>10.21130362976755</v>
       </c>
       <c r="E340" t="n">
-        <v>10.56878937922202</v>
+        <v>10.56879034973082</v>
       </c>
       <c r="F340" t="n">
         <v>3104200</v>
@@ -7272,16 +7272,16 @@
         <v>44284</v>
       </c>
       <c r="B343" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C343" t="n">
-        <v>10.06464047012052</v>
+        <v>10.06464144419899</v>
       </c>
       <c r="D343" t="n">
-        <v>9.734652558929284</v>
+        <v>9.734653501070783</v>
       </c>
       <c r="E343" t="n">
-        <v>10.04630824547281</v>
+        <v>10.04630921777704</v>
       </c>
       <c r="F343" t="n">
         <v>1233600</v>
@@ -7452,16 +7452,16 @@
         <v>44298</v>
       </c>
       <c r="B352" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C352" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="D352" t="n">
-        <v>10.69711763298518</v>
+        <v>10.69711856198182</v>
       </c>
       <c r="E352" t="n">
-        <v>10.87127768853708</v>
+        <v>10.87127863265874</v>
       </c>
       <c r="F352" t="n">
         <v>1341200</v>
@@ -7532,16 +7532,16 @@
         <v>44302</v>
       </c>
       <c r="B356" t="n">
-        <v>12.53955268859863</v>
+        <v>12.53955364227295</v>
       </c>
       <c r="C356" t="n">
-        <v>13.63951325138424</v>
+        <v>13.63951428871419</v>
       </c>
       <c r="D356" t="n">
-        <v>11.47625744876687</v>
+        <v>11.47625832157408</v>
       </c>
       <c r="E356" t="n">
-        <v>11.61375219130122</v>
+        <v>11.61375307456536</v>
       </c>
       <c r="F356" t="n">
         <v>14691000</v>
@@ -7592,16 +7592,16 @@
         <v>44308</v>
       </c>
       <c r="B359" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C359" t="n">
-        <v>11.41209182687907</v>
+        <v>11.41209281796801</v>
       </c>
       <c r="D359" t="n">
-        <v>10.91710955815712</v>
+        <v>10.91711050625907</v>
       </c>
       <c r="E359" t="n">
-        <v>11.26543054343111</v>
+        <v>11.26543152178318</v>
       </c>
       <c r="F359" t="n">
         <v>4817400</v>
@@ -7612,16 +7612,16 @@
         <v>44309</v>
       </c>
       <c r="B360" t="n">
-        <v>11.02710723876953</v>
+        <v>11.02710628509521</v>
       </c>
       <c r="C360" t="n">
-        <v>11.18293509525356</v>
+        <v>11.18293412810254</v>
       </c>
       <c r="D360" t="n">
-        <v>10.70628584978561</v>
+        <v>10.70628492385739</v>
       </c>
       <c r="E360" t="n">
-        <v>11.1462697686791</v>
+        <v>11.14626880469907</v>
       </c>
       <c r="F360" t="n">
         <v>3824500</v>
@@ -7672,16 +7672,16 @@
         <v>44314</v>
       </c>
       <c r="B363" t="n">
-        <v>11.20126724243164</v>
+        <v>11.20126819610596</v>
       </c>
       <c r="C363" t="n">
-        <v>11.30209666338853</v>
+        <v>11.30209762564745</v>
       </c>
       <c r="D363" t="n">
-        <v>10.9262768794389</v>
+        <v>10.92627780970057</v>
       </c>
       <c r="E363" t="n">
-        <v>11.18293414361933</v>
+        <v>11.18293509573277</v>
       </c>
       <c r="F363" t="n">
         <v>1629600</v>
@@ -7692,16 +7692,16 @@
         <v>44315</v>
       </c>
       <c r="B364" t="n">
-        <v>11.42125988006592</v>
+        <v>11.4212589263916</v>
       </c>
       <c r="C364" t="n">
-        <v>11.59541995855849</v>
+        <v>11.59541899034182</v>
       </c>
       <c r="D364" t="n">
-        <v>11.08210539887593</v>
+        <v>11.08210447352099</v>
       </c>
       <c r="E364" t="n">
-        <v>11.2196001516769</v>
+        <v>11.21959921484115</v>
       </c>
       <c r="F364" t="n">
         <v>1614300</v>
@@ -7892,16 +7892,16 @@
         <v>44329</v>
       </c>
       <c r="B374" t="n">
-        <v>11.16460227966309</v>
+        <v>11.16460132598877</v>
       </c>
       <c r="C374" t="n">
-        <v>11.43042610183743</v>
+        <v>11.43042512545659</v>
       </c>
       <c r="D374" t="n">
-        <v>11.10043730591735</v>
+        <v>11.10043635772397</v>
       </c>
       <c r="E374" t="n">
-        <v>11.13710263055622</v>
+        <v>11.13710167923091</v>
       </c>
       <c r="F374" t="n">
         <v>1639700</v>
@@ -7952,16 +7952,16 @@
         <v>44334</v>
       </c>
       <c r="B377" t="n">
-        <v>12.26456356048584</v>
+        <v>12.26456260681152</v>
       </c>
       <c r="C377" t="n">
-        <v>12.59455150019489</v>
+        <v>12.5945505208612</v>
       </c>
       <c r="D377" t="n">
-        <v>12.18206635701599</v>
+        <v>12.18206540975654</v>
       </c>
       <c r="E377" t="n">
-        <v>12.35622643998652</v>
+        <v>12.35622547918463</v>
       </c>
       <c r="F377" t="n">
         <v>1445400</v>
@@ -7992,16 +7992,16 @@
         <v>44336</v>
       </c>
       <c r="B379" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="C379" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="D379" t="n">
-        <v>11.86124370366004</v>
+        <v>11.86124460180745</v>
       </c>
       <c r="E379" t="n">
-        <v>12.05373688070891</v>
+        <v>12.05373779343214</v>
       </c>
       <c r="F379" t="n">
         <v>2196400</v>
@@ -8012,16 +8012,16 @@
         <v>44337</v>
       </c>
       <c r="B380" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="C380" t="n">
-        <v>12.79621081337468</v>
+        <v>12.79621178231891</v>
       </c>
       <c r="D380" t="n">
-        <v>12.42955755907697</v>
+        <v>12.42955850025778</v>
       </c>
       <c r="E380" t="n">
-        <v>12.53038698546626</v>
+        <v>12.53038793428199</v>
       </c>
       <c r="F380" t="n">
         <v>1466000</v>
@@ -8052,16 +8052,16 @@
         <v>44341</v>
       </c>
       <c r="B382" t="n">
-        <v>12.53955268859863</v>
+        <v>12.53955364227295</v>
       </c>
       <c r="C382" t="n">
-        <v>12.75037807704068</v>
+        <v>12.75037904674896</v>
       </c>
       <c r="D382" t="n">
-        <v>12.40205707189402</v>
+        <v>12.40205801511135</v>
       </c>
       <c r="E382" t="n">
-        <v>12.62204988378735</v>
+        <v>12.62205084373585</v>
       </c>
       <c r="F382" t="n">
         <v>1256400</v>
@@ -8252,16 +8252,16 @@
         <v>44356</v>
       </c>
       <c r="B392" t="n">
-        <v>13.53868389129639</v>
+        <v>13.5386848449707</v>
       </c>
       <c r="C392" t="n">
-        <v>13.84117302553739</v>
+        <v>13.84117400051925</v>
       </c>
       <c r="D392" t="n">
-        <v>13.38285604951523</v>
+        <v>13.38285699221293</v>
       </c>
       <c r="E392" t="n">
-        <v>13.78617460377982</v>
+        <v>13.78617557488755</v>
       </c>
       <c r="F392" t="n">
         <v>1247900</v>
@@ -8272,16 +8272,16 @@
         <v>44357</v>
       </c>
       <c r="B393" t="n">
-        <v>13.62118148803711</v>
+        <v>13.62118053436279</v>
       </c>
       <c r="C393" t="n">
-        <v>13.77700934440852</v>
+        <v>13.77700837982407</v>
       </c>
       <c r="D393" t="n">
-        <v>13.32785887565343</v>
+        <v>13.32785794251582</v>
       </c>
       <c r="E393" t="n">
-        <v>13.56618393530034</v>
+        <v>13.56618298547662</v>
       </c>
       <c r="F393" t="n">
         <v>1127800</v>
@@ -8312,16 +8312,16 @@
         <v>44361</v>
       </c>
       <c r="B395" t="n">
-        <v>13.50201797485352</v>
+        <v>13.50201892852783</v>
       </c>
       <c r="C395" t="n">
-        <v>13.6578458198759</v>
+        <v>13.65784678455664</v>
       </c>
       <c r="D395" t="n">
-        <v>13.30035913061184</v>
+        <v>13.30036007004259</v>
       </c>
       <c r="E395" t="n">
-        <v>13.3186913554655</v>
+        <v>13.3186922961911</v>
       </c>
       <c r="F395" t="n">
         <v>1118700</v>
@@ -8392,16 +8392,16 @@
         <v>44365</v>
       </c>
       <c r="B399" t="n">
-        <v>13.74034309387207</v>
+        <v>13.74034404754639</v>
       </c>
       <c r="C399" t="n">
-        <v>13.75867619299839</v>
+        <v>13.75867714794514</v>
       </c>
       <c r="D399" t="n">
-        <v>13.34619107852938</v>
+        <v>13.34619200484684</v>
       </c>
       <c r="E399" t="n">
-        <v>13.40118862756777</v>
+        <v>13.40118955770243</v>
       </c>
       <c r="F399" t="n">
         <v>1818300</v>
@@ -8412,16 +8412,16 @@
         <v>44368</v>
       </c>
       <c r="B400" t="n">
-        <v>14.03366756439209</v>
+        <v>14.03366661071777</v>
       </c>
       <c r="C400" t="n">
-        <v>14.28115830110597</v>
+        <v>14.28115733061313</v>
       </c>
       <c r="D400" t="n">
-        <v>13.86867315713594</v>
+        <v>13.86867221467401</v>
       </c>
       <c r="E400" t="n">
-        <v>13.99700223768743</v>
+        <v>13.99700128650475</v>
       </c>
       <c r="F400" t="n">
         <v>2278000</v>
@@ -8432,16 +8432,16 @@
         <v>44369</v>
       </c>
       <c r="B401" t="n">
-        <v>13.53868389129639</v>
+        <v>13.5386848449707</v>
       </c>
       <c r="C401" t="n">
-        <v>13.98783431799724</v>
+        <v>13.98783530331003</v>
       </c>
       <c r="D401" t="n">
-        <v>13.41952137263019</v>
+        <v>13.41952231791062</v>
       </c>
       <c r="E401" t="n">
-        <v>13.95116899488228</v>
+        <v>13.95116997761234</v>
       </c>
       <c r="F401" t="n">
         <v>2062700</v>
@@ -8492,16 +8492,16 @@
         <v>44372</v>
       </c>
       <c r="B404" t="n">
-        <v>13.43785381317139</v>
+        <v>13.4378547668457</v>
       </c>
       <c r="C404" t="n">
-        <v>13.5661828832223</v>
+        <v>13.56618384600404</v>
       </c>
       <c r="D404" t="n">
-        <v>12.83287553496186</v>
+        <v>12.83287644570132</v>
       </c>
       <c r="E404" t="n">
-        <v>13.53868410898649</v>
+        <v>13.53868506981665</v>
       </c>
       <c r="F404" t="n">
         <v>1465200</v>
@@ -8532,16 +8532,16 @@
         <v>44376</v>
       </c>
       <c r="B406" t="n">
-        <v>13.1536979675293</v>
+        <v>13.15369892120361</v>
       </c>
       <c r="C406" t="n">
-        <v>13.30035926451625</v>
+        <v>13.30036022882386</v>
       </c>
       <c r="D406" t="n">
-        <v>12.89703982363184</v>
+        <v>12.89704075869783</v>
       </c>
       <c r="E406" t="n">
-        <v>13.26369394026951</v>
+        <v>13.2636949019188</v>
       </c>
       <c r="F406" t="n">
         <v>967400</v>
@@ -8672,16 +8672,16 @@
         <v>44385</v>
       </c>
       <c r="B413" t="n">
-        <v>12.45705699920654</v>
+        <v>12.45705604553223</v>
       </c>
       <c r="C413" t="n">
-        <v>12.57621953175335</v>
+        <v>12.57621856895631</v>
       </c>
       <c r="D413" t="n">
-        <v>12.17290005633794</v>
+        <v>12.17289912441782</v>
       </c>
       <c r="E413" t="n">
-        <v>12.3195613658816</v>
+        <v>12.31956042273353</v>
       </c>
       <c r="F413" t="n">
         <v>1082500</v>
@@ -8812,16 +8812,16 @@
         <v>44397</v>
       </c>
       <c r="B420" t="n">
-        <v>11.48542308807373</v>
+        <v>11.48542404174805</v>
       </c>
       <c r="C420" t="n">
-        <v>11.68708280077636</v>
+        <v>11.68708377119518</v>
       </c>
       <c r="D420" t="n">
-        <v>11.37542711955509</v>
+        <v>11.37542806409606</v>
       </c>
       <c r="E420" t="n">
-        <v>11.57708683225772</v>
+        <v>11.5770877935432</v>
       </c>
       <c r="F420" t="n">
         <v>1744400</v>
@@ -8832,16 +8832,16 @@
         <v>44398</v>
       </c>
       <c r="B421" t="n">
-        <v>11.48542308807373</v>
+        <v>11.48542404174805</v>
       </c>
       <c r="C421" t="n">
-        <v>11.66874970227147</v>
+        <v>11.66875067116803</v>
       </c>
       <c r="D421" t="n">
-        <v>11.2287658281969</v>
+        <v>11.22876676056008</v>
       </c>
       <c r="E421" t="n">
-        <v>11.54042150941818</v>
+        <v>11.5404224676592</v>
       </c>
       <c r="F421" t="n">
         <v>2115800</v>
@@ -8872,16 +8872,16 @@
         <v>44400</v>
       </c>
       <c r="B423" t="n">
-        <v>11.68708419799805</v>
+        <v>11.68708324432373</v>
       </c>
       <c r="C423" t="n">
-        <v>11.7145829748727</v>
+        <v>11.71458201895446</v>
       </c>
       <c r="D423" t="n">
-        <v>11.43959258361514</v>
+        <v>11.43959165013631</v>
       </c>
       <c r="E423" t="n">
-        <v>11.62292009390042</v>
+        <v>11.62291914546194</v>
       </c>
       <c r="F423" t="n">
         <v>1513600</v>
@@ -8912,16 +8912,16 @@
         <v>44404</v>
       </c>
       <c r="B425" t="n">
-        <v>11.43959140777588</v>
+        <v>11.4395923614502</v>
       </c>
       <c r="C425" t="n">
-        <v>11.61375234981137</v>
+        <v>11.61375331800481</v>
       </c>
       <c r="D425" t="n">
-        <v>11.19210069300211</v>
+        <v>11.19210162604409</v>
       </c>
       <c r="E425" t="n">
-        <v>11.39376040908574</v>
+        <v>11.3937613589393</v>
       </c>
       <c r="F425" t="n">
         <v>1727000</v>
@@ -8952,16 +8952,16 @@
         <v>44406</v>
       </c>
       <c r="B427" t="n">
-        <v>11.25626468658447</v>
+        <v>11.25626564025879</v>
       </c>
       <c r="C427" t="n">
-        <v>11.36626065593178</v>
+        <v>11.36626161892538</v>
       </c>
       <c r="D427" t="n">
-        <v>11.15543526655867</v>
+        <v>11.15543621169033</v>
       </c>
       <c r="E427" t="n">
-        <v>11.36626065593178</v>
+        <v>11.36626161892538</v>
       </c>
       <c r="F427" t="n">
         <v>743300</v>
@@ -8992,16 +8992,16 @@
         <v>44410</v>
       </c>
       <c r="B429" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C429" t="n">
-        <v>11.2012671859109</v>
+        <v>11.20126816523029</v>
       </c>
       <c r="D429" t="n">
-        <v>10.86211272712696</v>
+        <v>10.8621136767943</v>
       </c>
       <c r="E429" t="n">
-        <v>10.96294214757507</v>
+        <v>10.96294310605787</v>
       </c>
       <c r="F429" t="n">
         <v>1959100</v>
@@ -9132,16 +9132,16 @@
         <v>44419</v>
       </c>
       <c r="B436" t="n">
-        <v>9.890481948852539</v>
+        <v>9.890480995178223</v>
       </c>
       <c r="C436" t="n">
-        <v>10.51379341941164</v>
+        <v>10.51379240563549</v>
       </c>
       <c r="D436" t="n">
-        <v>9.743820632055199</v>
+        <v>9.74381969252247</v>
       </c>
       <c r="E436" t="n">
-        <v>10.51379341941164</v>
+        <v>10.51379240563549</v>
       </c>
       <c r="F436" t="n">
         <v>4618100</v>
@@ -9172,16 +9172,16 @@
         <v>44421</v>
       </c>
       <c r="B438" t="n">
-        <v>9.81714916229248</v>
+        <v>9.817150115966797</v>
       </c>
       <c r="C438" t="n">
-        <v>10.00964231740293</v>
+        <v>10.00964328977675</v>
       </c>
       <c r="D438" t="n">
-        <v>9.688820100828776</v>
+        <v>9.688821042036732</v>
       </c>
       <c r="E438" t="n">
-        <v>9.908812902505156</v>
+        <v>9.90881386508403</v>
       </c>
       <c r="F438" t="n">
         <v>1360000</v>
@@ -9212,16 +9212,16 @@
         <v>44425</v>
       </c>
       <c r="B440" t="n">
-        <v>8.323036193847656</v>
+        <v>8.323037147521973</v>
       </c>
       <c r="C440" t="n">
-        <v>9.294668565223555</v>
+        <v>9.29466963022994</v>
       </c>
       <c r="D440" t="n">
-        <v>8.304703969421075</v>
+        <v>8.30470492099484</v>
       </c>
       <c r="E440" t="n">
-        <v>9.285502015925136</v>
+        <v>9.285503079881195</v>
       </c>
       <c r="F440" t="n">
         <v>6613600</v>
@@ -9272,16 +9272,16 @@
         <v>44428</v>
       </c>
       <c r="B443" t="n">
-        <v>8.62552547454834</v>
+        <v>8.625526428222656</v>
       </c>
       <c r="C443" t="n">
-        <v>8.689689572391865</v>
+        <v>8.689690533160434</v>
       </c>
       <c r="D443" t="n">
-        <v>8.414700082108032</v>
+        <v>8.414701012472607</v>
       </c>
       <c r="E443" t="n">
-        <v>8.515529503600753</v>
+        <v>8.515530445113452</v>
       </c>
       <c r="F443" t="n">
         <v>1662000</v>
@@ -9332,16 +9332,16 @@
         <v>44433</v>
       </c>
       <c r="B446" t="n">
-        <v>8.955513954162598</v>
+        <v>8.955514907836914</v>
       </c>
       <c r="C446" t="n">
-        <v>9.322167178069154</v>
+        <v>9.322168170788439</v>
       </c>
       <c r="D446" t="n">
-        <v>8.744687694788647</v>
+        <v>8.744688626012037</v>
       </c>
       <c r="E446" t="n">
-        <v>9.175505888506532</v>
+        <v>9.175506865607829</v>
       </c>
       <c r="F446" t="n">
         <v>3539500</v>
@@ -9352,16 +9352,16 @@
         <v>44434</v>
       </c>
       <c r="B447" t="n">
-        <v>8.488031387329102</v>
+        <v>8.488030433654785</v>
       </c>
       <c r="C447" t="n">
-        <v>9.093009711518935</v>
+        <v>9.093008689872168</v>
       </c>
       <c r="D447" t="n">
-        <v>8.451366060837909</v>
+        <v>8.451365111283133</v>
       </c>
       <c r="E447" t="n">
-        <v>8.928015305223402</v>
+        <v>8.928014302114612</v>
       </c>
       <c r="F447" t="n">
         <v>2819100</v>
@@ -9412,16 +9412,16 @@
         <v>44439</v>
       </c>
       <c r="B450" t="n">
-        <v>8.148877143859863</v>
+        <v>8.148876190185547</v>
       </c>
       <c r="C450" t="n">
-        <v>8.478865092206572</v>
+        <v>8.478864099913311</v>
       </c>
       <c r="D450" t="n">
-        <v>8.075546488671705</v>
+        <v>8.075545543579377</v>
       </c>
       <c r="E450" t="n">
-        <v>8.359702558983225</v>
+        <v>8.35970158063572</v>
       </c>
       <c r="F450" t="n">
         <v>2719700</v>
@@ -9472,16 +9472,16 @@
         <v>44442</v>
       </c>
       <c r="B453" t="n">
-        <v>8.020547866821289</v>
+        <v>8.020546913146973</v>
       </c>
       <c r="C453" t="n">
-        <v>8.048046643311267</v>
+        <v>8.048045686367239</v>
       </c>
       <c r="D453" t="n">
-        <v>7.818888132830658</v>
+        <v>7.818887203134468</v>
       </c>
       <c r="E453" t="n">
-        <v>7.965549439670992</v>
+        <v>7.965548492536203</v>
       </c>
       <c r="F453" t="n">
         <v>2243900</v>
@@ -9532,16 +9532,16 @@
         <v>44448</v>
       </c>
       <c r="B456" t="n">
-        <v>7.95638370513916</v>
+        <v>7.956383228302002</v>
       </c>
       <c r="C456" t="n">
-        <v>8.075546234613633</v>
+        <v>8.075545750634898</v>
       </c>
       <c r="D456" t="n">
-        <v>7.626394893003591</v>
+        <v>7.626394435943123</v>
       </c>
       <c r="E456" t="n">
-        <v>7.883053052257997</v>
+        <v>7.883052579815647</v>
       </c>
       <c r="F456" t="n">
         <v>3062500</v>
@@ -9672,16 +9672,16 @@
         <v>44459</v>
       </c>
       <c r="B463" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C463" t="n">
-        <v>7.415568905269083</v>
+        <v>7.415569387470669</v>
       </c>
       <c r="D463" t="n">
-        <v>7.140578541359559</v>
+        <v>7.14057900567974</v>
       </c>
       <c r="E463" t="n">
-        <v>7.21390918851273</v>
+        <v>7.213909657601278</v>
       </c>
       <c r="F463" t="n">
         <v>2478700</v>
@@ -9692,16 +9692,16 @@
         <v>44460</v>
       </c>
       <c r="B464" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="C464" t="n">
-        <v>7.635561237915681</v>
+        <v>7.63556171937671</v>
       </c>
       <c r="D464" t="n">
-        <v>7.213909558097646</v>
+        <v>7.21391001297139</v>
       </c>
       <c r="E464" t="n">
-        <v>7.488899936095549</v>
+        <v>7.488900408308837</v>
       </c>
       <c r="F464" t="n">
         <v>2716900</v>
@@ -9712,16 +9712,16 @@
         <v>44461</v>
       </c>
       <c r="B465" t="n">
-        <v>7.653894424438477</v>
+        <v>7.653893947601318</v>
       </c>
       <c r="C465" t="n">
-        <v>7.773056077889568</v>
+        <v>7.773055593628645</v>
       </c>
       <c r="D465" t="n">
-        <v>7.443068145055875</v>
+        <v>7.443067681353181</v>
       </c>
       <c r="E465" t="n">
-        <v>7.708891976158931</v>
+        <v>7.708891495895427</v>
       </c>
       <c r="F465" t="n">
         <v>2341500</v>
@@ -9732,16 +9732,16 @@
         <v>44462</v>
       </c>
       <c r="B466" t="n">
-        <v>7.635560989379883</v>
+        <v>7.635561466217041</v>
       </c>
       <c r="C466" t="n">
-        <v>7.809721935250124</v>
+        <v>7.809722422963551</v>
       </c>
       <c r="D466" t="n">
-        <v>7.553063791248745</v>
+        <v>7.553064262933993</v>
       </c>
       <c r="E466" t="n">
-        <v>7.6630597640335</v>
+        <v>7.663060242587944</v>
       </c>
       <c r="F466" t="n">
         <v>1813900</v>
@@ -9852,16 +9852,16 @@
         <v>44470</v>
       </c>
       <c r="B472" t="n">
-        <v>7.058081150054932</v>
+        <v>7.05808162689209</v>
       </c>
       <c r="C472" t="n">
-        <v>7.058081150054932</v>
+        <v>7.05808162689209</v>
       </c>
       <c r="D472" t="n">
-        <v>6.590598068807588</v>
+        <v>6.590598514062039</v>
       </c>
       <c r="E472" t="n">
-        <v>6.627263391372669</v>
+        <v>6.627263839104194</v>
       </c>
       <c r="F472" t="n">
         <v>1964300</v>
@@ -9872,16 +9872,16 @@
         <v>44473</v>
       </c>
       <c r="B473" t="n">
-        <v>6.883921146392822</v>
+        <v>6.88392162322998</v>
       </c>
       <c r="C473" t="n">
-        <v>7.058081211551849</v>
+        <v>7.05808170045277</v>
       </c>
       <c r="D473" t="n">
-        <v>6.792257402096333</v>
+        <v>6.792257872584105</v>
       </c>
       <c r="E473" t="n">
-        <v>6.911419920013668</v>
+        <v>6.911420398755618</v>
       </c>
       <c r="F473" t="n">
         <v>2556200</v>
@@ -9972,16 +9972,16 @@
         <v>44480</v>
       </c>
       <c r="B478" t="n">
-        <v>6.645596981048584</v>
+        <v>6.645596504211426</v>
       </c>
       <c r="C478" t="n">
-        <v>6.79225829179757</v>
+        <v>6.792257804437119</v>
       </c>
       <c r="D478" t="n">
-        <v>6.526434447522441</v>
+        <v>6.526433979235474</v>
       </c>
       <c r="E478" t="n">
-        <v>6.783092178418349</v>
+        <v>6.783091691715589</v>
       </c>
       <c r="F478" t="n">
         <v>1719800</v>
@@ -9992,16 +9992,16 @@
         <v>44482</v>
       </c>
       <c r="B479" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C479" t="n">
-        <v>6.89308794729405</v>
+        <v>6.893087464680927</v>
       </c>
       <c r="D479" t="n">
-        <v>6.581432234551219</v>
+        <v>6.58143177375838</v>
       </c>
       <c r="E479" t="n">
-        <v>6.645596774552734</v>
+        <v>6.645596309267474</v>
       </c>
       <c r="F479" t="n">
         <v>1797400</v>
@@ -10032,16 +10032,16 @@
         <v>44484</v>
       </c>
       <c r="B481" t="n">
-        <v>6.801424503326416</v>
+        <v>6.801424026489258</v>
       </c>
       <c r="C481" t="n">
-        <v>6.810590616248861</v>
+        <v>6.810590138769081</v>
       </c>
       <c r="D481" t="n">
-        <v>6.58143211108064</v>
+        <v>6.581431649666802</v>
       </c>
       <c r="E481" t="n">
-        <v>6.654763199886006</v>
+        <v>6.654762733331041</v>
       </c>
       <c r="F481" t="n">
         <v>1272200</v>
@@ -10112,16 +10112,16 @@
         <v>44490</v>
       </c>
       <c r="B485" t="n">
-        <v>5.967287540435791</v>
+        <v>5.967287063598633</v>
       </c>
       <c r="C485" t="n">
-        <v>6.297275465216598</v>
+        <v>6.29727496201059</v>
       </c>
       <c r="D485" t="n">
-        <v>5.89395645339935</v>
+        <v>5.89395598242197</v>
       </c>
       <c r="E485" t="n">
-        <v>6.297275465216598</v>
+        <v>6.29727496201059</v>
       </c>
       <c r="F485" t="n">
         <v>2712900</v>
@@ -10172,16 +10172,16 @@
         <v>44495</v>
       </c>
       <c r="B488" t="n">
-        <v>5.60063362121582</v>
+        <v>5.600634098052979</v>
       </c>
       <c r="C488" t="n">
-        <v>5.994786066892628</v>
+        <v>5.994786577287869</v>
       </c>
       <c r="D488" t="n">
-        <v>5.60063362121582</v>
+        <v>5.600634098052979</v>
       </c>
       <c r="E488" t="n">
-        <v>5.930621532304952</v>
+        <v>5.930622037237235</v>
       </c>
       <c r="F488" t="n">
         <v>1746800</v>
@@ -10232,16 +10232,16 @@
         <v>44498</v>
       </c>
       <c r="B491" t="n">
-        <v>5.554801940917969</v>
+        <v>5.554802417755127</v>
       </c>
       <c r="C491" t="n">
-        <v>5.838958426082296</v>
+        <v>5.838958927312109</v>
       </c>
       <c r="D491" t="n">
-        <v>5.545635828279196</v>
+        <v>5.545636304329514</v>
       </c>
       <c r="E491" t="n">
-        <v>5.701463239819518</v>
+        <v>5.701463729246425</v>
       </c>
       <c r="F491" t="n">
         <v>2502600</v>
@@ -10312,16 +10312,16 @@
         <v>44505</v>
       </c>
       <c r="B495" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C495" t="n">
-        <v>6.94808593711599</v>
+        <v>6.948085450652234</v>
       </c>
       <c r="D495" t="n">
-        <v>6.398105601811419</v>
+        <v>6.398105153854022</v>
       </c>
       <c r="E495" t="n">
-        <v>6.398105601811419</v>
+        <v>6.398105153854022</v>
       </c>
       <c r="F495" t="n">
         <v>3968000</v>
@@ -10372,16 +10372,16 @@
         <v>44510</v>
       </c>
       <c r="B498" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C498" t="n">
-        <v>7.333072037123874</v>
+        <v>7.333072524313823</v>
       </c>
       <c r="D498" t="n">
-        <v>6.874755034803632</v>
+        <v>6.874755491544209</v>
       </c>
       <c r="E498" t="n">
-        <v>6.874755034803632</v>
+        <v>6.874755491544209</v>
       </c>
       <c r="F498" t="n">
         <v>8294800</v>
@@ -10432,16 +10432,16 @@
         <v>44516</v>
       </c>
       <c r="B501" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C501" t="n">
-        <v>7.177243999484845</v>
+        <v>7.177244504030098</v>
       </c>
       <c r="D501" t="n">
-        <v>6.691428234445144</v>
+        <v>6.691428704838564</v>
       </c>
       <c r="E501" t="n">
-        <v>7.131412562697498</v>
+        <v>7.131413064020896</v>
       </c>
       <c r="F501" t="n">
         <v>3605600</v>
@@ -10492,16 +10492,16 @@
         <v>44519</v>
       </c>
       <c r="B504" t="n">
-        <v>7.232242107391357</v>
+        <v>7.232241630554199</v>
       </c>
       <c r="C504" t="n">
-        <v>7.305572757151272</v>
+        <v>7.305572275479267</v>
       </c>
       <c r="D504" t="n">
-        <v>6.544766610264437</v>
+        <v>6.544766178754005</v>
       </c>
       <c r="E504" t="n">
-        <v>6.645596472226894</v>
+        <v>6.645596034068535</v>
       </c>
       <c r="F504" t="n">
         <v>4026100</v>
@@ -10512,16 +10512,16 @@
         <v>44522</v>
       </c>
       <c r="B505" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C505" t="n">
-        <v>7.296406521885203</v>
+        <v>7.296407034807332</v>
       </c>
       <c r="D505" t="n">
-        <v>6.572265712044786</v>
+        <v>6.57226617406133</v>
       </c>
       <c r="E505" t="n">
-        <v>7.278073859753236</v>
+        <v>7.278074371386616</v>
       </c>
       <c r="F505" t="n">
         <v>4188800</v>
@@ -10752,16 +10752,16 @@
         <v>44538</v>
       </c>
       <c r="B517" t="n">
-        <v>6.269776344299316</v>
+        <v>6.269776821136475</v>
       </c>
       <c r="C517" t="n">
-        <v>6.398104974637775</v>
+        <v>6.398105461234748</v>
       </c>
       <c r="D517" t="n">
-        <v>5.912288789871634</v>
+        <v>5.912289239520686</v>
       </c>
       <c r="E517" t="n">
-        <v>6.223944472064447</v>
+        <v>6.22394494541594</v>
       </c>
       <c r="F517" t="n">
         <v>2255900</v>
@@ -10772,16 +10772,16 @@
         <v>44539</v>
       </c>
       <c r="B518" t="n">
-        <v>6.086450099945068</v>
+        <v>6.08644962310791</v>
       </c>
       <c r="C518" t="n">
-        <v>6.26977717612175</v>
+        <v>6.269776684922006</v>
       </c>
       <c r="D518" t="n">
-        <v>5.994786780399321</v>
+        <v>5.994786310743438</v>
       </c>
       <c r="E518" t="n">
-        <v>6.205612633897133</v>
+        <v>6.2056121477243</v>
       </c>
       <c r="F518" t="n">
         <v>1370200</v>
@@ -10792,16 +10792,16 @@
         <v>44540</v>
       </c>
       <c r="B519" t="n">
-        <v>6.13228178024292</v>
+        <v>6.132281303405762</v>
       </c>
       <c r="C519" t="n">
-        <v>6.242277760145935</v>
+        <v>6.242277274755653</v>
       </c>
       <c r="D519" t="n">
-        <v>6.077283790291412</v>
+        <v>6.077283317730816</v>
       </c>
       <c r="E519" t="n">
-        <v>6.233111647029936</v>
+        <v>6.233111162352396</v>
       </c>
       <c r="F519" t="n">
         <v>1440000</v>
@@ -10812,16 +10812,16 @@
         <v>44543</v>
       </c>
       <c r="B520" t="n">
-        <v>5.930622100830078</v>
+        <v>5.93062162399292</v>
       </c>
       <c r="C520" t="n">
-        <v>6.233111703953602</v>
+        <v>6.233111202795508</v>
       </c>
       <c r="D520" t="n">
-        <v>5.930622100830078</v>
+        <v>5.93062162399292</v>
       </c>
       <c r="E520" t="n">
-        <v>6.123115285960878</v>
+        <v>6.123114793646776</v>
       </c>
       <c r="F520" t="n">
         <v>1532500</v>
@@ -10852,16 +10852,16 @@
         <v>44545</v>
       </c>
       <c r="B522" t="n">
-        <v>5.783960342407227</v>
+        <v>5.783960819244385</v>
       </c>
       <c r="C522" t="n">
-        <v>5.848124878147738</v>
+        <v>5.848125360274703</v>
       </c>
       <c r="D522" t="n">
-        <v>5.527303073615463</v>
+        <v>5.527303529293464</v>
       </c>
       <c r="E522" t="n">
-        <v>5.683130482553606</v>
+        <v>5.68313095107822</v>
       </c>
       <c r="F522" t="n">
         <v>1794200</v>
@@ -10912,16 +10912,16 @@
         <v>44550</v>
       </c>
       <c r="B525" t="n">
-        <v>5.70146369934082</v>
+        <v>5.701463222503662</v>
       </c>
       <c r="C525" t="n">
-        <v>5.756462127946762</v>
+        <v>5.756461646509856</v>
       </c>
       <c r="D525" t="n">
-        <v>5.582301602921769</v>
+        <v>5.582301136050633</v>
       </c>
       <c r="E525" t="n">
-        <v>5.710630249803538</v>
+        <v>5.710629772199743</v>
       </c>
       <c r="F525" t="n">
         <v>2934100</v>
@@ -10952,16 +10952,16 @@
         <v>44552</v>
       </c>
       <c r="B527" t="n">
-        <v>5.453971862792969</v>
+        <v>5.453972339630127</v>
       </c>
       <c r="C527" t="n">
-        <v>5.646465028499557</v>
+        <v>5.646465522166265</v>
       </c>
       <c r="D527" t="n">
-        <v>5.42647308888353</v>
+        <v>5.426473563316489</v>
       </c>
       <c r="E527" t="n">
-        <v>5.618966254590118</v>
+        <v>5.618966745852627</v>
       </c>
       <c r="F527" t="n">
         <v>3033600</v>
@@ -10972,16 +10972,16 @@
         <v>44553</v>
       </c>
       <c r="B528" t="n">
-        <v>5.453971862792969</v>
+        <v>5.453972339630127</v>
       </c>
       <c r="C528" t="n">
-        <v>5.481471073787537</v>
+        <v>5.481471553028933</v>
       </c>
       <c r="D528" t="n">
-        <v>5.325643231350287</v>
+        <v>5.325643696967758</v>
       </c>
       <c r="E528" t="n">
-        <v>5.444805750518199</v>
+        <v>5.444806226553971</v>
       </c>
       <c r="F528" t="n">
         <v>2899900</v>
@@ -11012,16 +11012,16 @@
         <v>44558</v>
       </c>
       <c r="B530" t="n">
-        <v>5.719795703887939</v>
+        <v>5.719796180725098</v>
       </c>
       <c r="C530" t="n">
-        <v>5.756461464427344</v>
+        <v>5.756461944321184</v>
       </c>
       <c r="D530" t="n">
-        <v>5.527302974295581</v>
+        <v>5.527303435085368</v>
       </c>
       <c r="E530" t="n">
-        <v>5.563968297749852</v>
+        <v>5.563968761596285</v>
       </c>
       <c r="F530" t="n">
         <v>2551400</v>
@@ -11072,16 +11072,16 @@
         <v>44564</v>
       </c>
       <c r="B533" t="n">
-        <v>5.417306900024414</v>
+        <v>5.417306423187256</v>
       </c>
       <c r="C533" t="n">
-        <v>5.774794481317564</v>
+        <v>5.774793973013967</v>
       </c>
       <c r="D533" t="n">
-        <v>5.371475461430403</v>
+        <v>5.371474988627377</v>
       </c>
       <c r="E533" t="n">
-        <v>5.655631954219848</v>
+        <v>5.655631456405064</v>
       </c>
       <c r="F533" t="n">
         <v>2044700</v>
@@ -11112,16 +11112,16 @@
         <v>44566</v>
       </c>
       <c r="B535" t="n">
-        <v>4.885658740997314</v>
+        <v>4.885659217834473</v>
       </c>
       <c r="C535" t="n">
-        <v>5.0689857878987</v>
+        <v>5.06898628262846</v>
       </c>
       <c r="D535" t="n">
-        <v>4.839827307085804</v>
+        <v>4.839827779449844</v>
       </c>
       <c r="E535" t="n">
-        <v>5.023153916902075</v>
+        <v>5.023154407158674</v>
       </c>
       <c r="F535" t="n">
         <v>2302400</v>
@@ -11172,16 +11172,16 @@
         <v>44571</v>
       </c>
       <c r="B538" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C538" t="n">
-        <v>4.894826206904368</v>
+        <v>4.894825720038117</v>
       </c>
       <c r="D538" t="n">
-        <v>4.62900235433546</v>
+        <v>4.629001893909508</v>
       </c>
       <c r="E538" t="n">
-        <v>4.720665676413498</v>
+        <v>4.720665206870209</v>
       </c>
       <c r="F538" t="n">
         <v>3868800</v>
@@ -11192,16 +11192,16 @@
         <v>44572</v>
       </c>
       <c r="B539" t="n">
-        <v>5.00482177734375</v>
+        <v>5.004822254180908</v>
       </c>
       <c r="C539" t="n">
-        <v>5.059819766018552</v>
+        <v>5.059820248095674</v>
       </c>
       <c r="D539" t="n">
-        <v>4.766496722667781</v>
+        <v>4.766497176798388</v>
       </c>
       <c r="E539" t="n">
-        <v>4.775663272656161</v>
+        <v>4.775663727660117</v>
       </c>
       <c r="F539" t="n">
         <v>2192500</v>
@@ -11212,16 +11212,16 @@
         <v>44573</v>
       </c>
       <c r="B540" t="n">
-        <v>5.169815540313721</v>
+        <v>5.169816017150879</v>
       </c>
       <c r="C540" t="n">
-        <v>5.270645400799818</v>
+        <v>5.270645886937004</v>
       </c>
       <c r="D540" t="n">
-        <v>4.995655031141423</v>
+        <v>4.995655491914913</v>
       </c>
       <c r="E540" t="n">
-        <v>5.032320355484523</v>
+        <v>5.032320819639834</v>
       </c>
       <c r="F540" t="n">
         <v>2344800</v>
@@ -11272,16 +11272,16 @@
         <v>44578</v>
       </c>
       <c r="B543" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C543" t="n">
-        <v>5.105651419324723</v>
+        <v>5.105651915770163</v>
       </c>
       <c r="D543" t="n">
-        <v>4.821494938343708</v>
+        <v>4.821495407159335</v>
       </c>
       <c r="E543" t="n">
-        <v>5.041486883457342</v>
+        <v>5.041487373663776</v>
       </c>
       <c r="F543" t="n">
         <v>1383000</v>
@@ -11292,16 +11292,16 @@
         <v>44579</v>
       </c>
       <c r="B544" t="n">
-        <v>4.803162097930908</v>
+        <v>4.80316162109375</v>
       </c>
       <c r="C544" t="n">
-        <v>4.977322615737815</v>
+        <v>4.977322121610753</v>
       </c>
       <c r="D544" t="n">
-        <v>4.748164108689543</v>
+        <v>4.748163637312347</v>
       </c>
       <c r="E544" t="n">
-        <v>4.913158513498805</v>
+        <v>4.913158025741677</v>
       </c>
       <c r="F544" t="n">
         <v>2424100</v>
@@ -11312,16 +11312,16 @@
         <v>44580</v>
       </c>
       <c r="B545" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C545" t="n">
-        <v>5.050653537402776</v>
+        <v>5.050653052647643</v>
       </c>
       <c r="D545" t="n">
-        <v>4.812328488186932</v>
+        <v>4.812328026305926</v>
       </c>
       <c r="E545" t="n">
-        <v>4.839827700436895</v>
+        <v>4.839827235916551</v>
       </c>
       <c r="F545" t="n">
         <v>2176700</v>
@@ -11552,16 +11552,16 @@
         <v>44596</v>
       </c>
       <c r="B557" t="n">
-        <v>5.490636825561523</v>
+        <v>5.490637302398682</v>
       </c>
       <c r="C557" t="n">
-        <v>5.637298546094581</v>
+        <v>5.637299035668652</v>
       </c>
       <c r="D557" t="n">
-        <v>5.37147475130261</v>
+        <v>5.371475217791077</v>
       </c>
       <c r="E557" t="n">
-        <v>5.628131997336533</v>
+        <v>5.628132486114529</v>
       </c>
       <c r="F557" t="n">
         <v>2310300</v>
@@ -11812,16 +11812,16 @@
         <v>44615</v>
       </c>
       <c r="B570" t="n">
-        <v>4.867326736450195</v>
+        <v>4.867326259613037</v>
       </c>
       <c r="C570" t="n">
-        <v>5.013988044082764</v>
+        <v>5.013987552877644</v>
       </c>
       <c r="D570" t="n">
-        <v>4.803162195818359</v>
+        <v>4.803161725267206</v>
       </c>
       <c r="E570" t="n">
-        <v>4.949823940536103</v>
+        <v>4.949823455616944</v>
       </c>
       <c r="F570" t="n">
         <v>3505100</v>
@@ -11872,16 +11872,16 @@
         <v>44622</v>
       </c>
       <c r="B573" t="n">
-        <v>4.647334575653076</v>
+        <v>4.647335052490234</v>
       </c>
       <c r="C573" t="n">
-        <v>4.738997888991517</v>
+        <v>4.738998375233738</v>
       </c>
       <c r="D573" t="n">
-        <v>4.58317003777359</v>
+        <v>4.583170508027182</v>
       </c>
       <c r="E573" t="n">
-        <v>4.665667238320764</v>
+        <v>4.665667717038935</v>
       </c>
       <c r="F573" t="n">
         <v>2274100</v>
@@ -11932,16 +11932,16 @@
         <v>44627</v>
       </c>
       <c r="B576" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="C576" t="n">
-        <v>4.46400783481362</v>
+        <v>4.464007312971596</v>
       </c>
       <c r="D576" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="E576" t="n">
-        <v>4.46400783481362</v>
+        <v>4.464007312971596</v>
       </c>
       <c r="F576" t="n">
         <v>3496200</v>
@@ -11952,16 +11952,16 @@
         <v>44628</v>
       </c>
       <c r="B577" t="n">
-        <v>4.124853134155273</v>
+        <v>4.124852657318115</v>
       </c>
       <c r="C577" t="n">
-        <v>4.207350336705632</v>
+        <v>4.207349850331715</v>
       </c>
       <c r="D577" t="n">
-        <v>3.969025279153559</v>
+        <v>3.969024820330257</v>
       </c>
       <c r="E577" t="n">
-        <v>4.134019684254276</v>
+        <v>4.134019206357456</v>
       </c>
       <c r="F577" t="n">
         <v>4412200</v>
@@ -11972,16 +11972,16 @@
         <v>44629</v>
       </c>
       <c r="B578" t="n">
-        <v>4.335678577423096</v>
+        <v>4.335679054260254</v>
       </c>
       <c r="C578" t="n">
-        <v>4.418175772342043</v>
+        <v>4.418176258252227</v>
       </c>
       <c r="D578" t="n">
-        <v>4.161518075419278</v>
+        <v>4.161518533102296</v>
       </c>
       <c r="E578" t="n">
-        <v>4.170684624670328</v>
+        <v>4.17068508336148</v>
       </c>
       <c r="F578" t="n">
         <v>3479000</v>
@@ -12172,16 +12172,16 @@
         <v>44643</v>
       </c>
       <c r="B588" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C588" t="n">
-        <v>4.839828213657545</v>
+        <v>4.839827732261697</v>
       </c>
       <c r="D588" t="n">
-        <v>4.574003924003441</v>
+        <v>4.574003469047934</v>
       </c>
       <c r="E588" t="n">
-        <v>4.656501132416273</v>
+        <v>4.656500669255141</v>
       </c>
       <c r="F588" t="n">
         <v>5289000</v>
@@ -12212,16 +12212,16 @@
         <v>44645</v>
       </c>
       <c r="B590" t="n">
-        <v>4.986489295959473</v>
+        <v>4.986488819122314</v>
       </c>
       <c r="C590" t="n">
-        <v>5.270645799665109</v>
+        <v>5.270645295655251</v>
       </c>
       <c r="D590" t="n">
-        <v>4.958990082078524</v>
+        <v>4.958989607871001</v>
       </c>
       <c r="E590" t="n">
-        <v>5.078152613754004</v>
+        <v>5.078152128151466</v>
       </c>
       <c r="F590" t="n">
         <v>4172200</v>
@@ -12232,16 +12232,16 @@
         <v>44648</v>
       </c>
       <c r="B591" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C591" t="n">
-        <v>5.142316768551991</v>
+        <v>5.142317254043173</v>
       </c>
       <c r="D591" t="n">
-        <v>4.885659060917757</v>
+        <v>4.885659522177632</v>
       </c>
       <c r="E591" t="n">
-        <v>5.013987696192302</v>
+        <v>5.01398816956781</v>
       </c>
       <c r="F591" t="n">
         <v>3528600</v>
@@ -12252,16 +12252,16 @@
         <v>44649</v>
       </c>
       <c r="B592" t="n">
-        <v>5.33480978012085</v>
+        <v>5.334810256958008</v>
       </c>
       <c r="C592" t="n">
-        <v>5.362308554027249</v>
+        <v>5.362309033322309</v>
       </c>
       <c r="D592" t="n">
-        <v>5.142316614435527</v>
+        <v>5.142317074067217</v>
       </c>
       <c r="E592" t="n">
-        <v>5.16064927606817</v>
+        <v>5.160649737338475</v>
       </c>
       <c r="F592" t="n">
         <v>3923800</v>
@@ -12292,16 +12292,16 @@
         <v>44651</v>
       </c>
       <c r="B594" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C594" t="n">
-        <v>5.224813529828769</v>
+        <v>5.224814023108552</v>
       </c>
       <c r="D594" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="E594" t="n">
-        <v>5.178982092916146</v>
+        <v>5.178982581868937</v>
       </c>
       <c r="F594" t="n">
         <v>1926600</v>
@@ -12452,16 +12452,16 @@
         <v>44663</v>
       </c>
       <c r="B602" t="n">
-        <v>4.372344493865967</v>
+        <v>4.372344017028809</v>
       </c>
       <c r="C602" t="n">
-        <v>4.519005805113152</v>
+        <v>4.519005312281472</v>
       </c>
       <c r="D602" t="n">
-        <v>4.36317838045561</v>
+        <v>4.363177904618086</v>
       </c>
       <c r="E602" t="n">
-        <v>4.464007813395457</v>
+        <v>4.464007326561723</v>
       </c>
       <c r="F602" t="n">
         <v>2977800</v>
@@ -12472,16 +12472,16 @@
         <v>44664</v>
       </c>
       <c r="B603" t="n">
-        <v>4.482340335845947</v>
+        <v>4.482339859008789</v>
       </c>
       <c r="C603" t="n">
-        <v>4.500672999173296</v>
+        <v>4.500672520385886</v>
       </c>
       <c r="D603" t="n">
-        <v>4.344845142348245</v>
+        <v>4.344844680138003</v>
       </c>
       <c r="E603" t="n">
-        <v>4.427342345863901</v>
+        <v>4.4273418748775</v>
       </c>
       <c r="F603" t="n">
         <v>2309600</v>
@@ -12512,16 +12512,16 @@
         <v>44669</v>
       </c>
       <c r="B605" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="C605" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="D605" t="n">
-        <v>4.372344289398597</v>
+        <v>4.372343829900955</v>
       </c>
       <c r="E605" t="n">
-        <v>4.45484149165985</v>
+        <v>4.454841023492427</v>
       </c>
       <c r="F605" t="n">
         <v>2710700</v>
@@ -12552,16 +12552,16 @@
         <v>44671</v>
       </c>
       <c r="B607" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="C607" t="n">
-        <v>4.509839386853855</v>
+        <v>4.509839880756772</v>
       </c>
       <c r="D607" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="E607" t="n">
-        <v>4.418176073520475</v>
+        <v>4.418176557384724</v>
       </c>
       <c r="F607" t="n">
         <v>2075500</v>
@@ -12572,16 +12572,16 @@
         <v>44673</v>
       </c>
       <c r="B608" t="n">
-        <v>4.097353935241699</v>
+        <v>4.097354412078857</v>
       </c>
       <c r="C608" t="n">
-        <v>4.308179780317636</v>
+        <v>4.308180281690042</v>
       </c>
       <c r="D608" t="n">
-        <v>4.079021272064886</v>
+        <v>4.079021746768547</v>
       </c>
       <c r="E608" t="n">
-        <v>4.308179780317636</v>
+        <v>4.308180281690042</v>
       </c>
       <c r="F608" t="n">
         <v>4745700</v>
@@ -12612,16 +12612,16 @@
         <v>44677</v>
       </c>
       <c r="B610" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="C610" t="n">
-        <v>4.189017874905755</v>
+        <v>4.189017385210027</v>
       </c>
       <c r="D610" t="n">
-        <v>4.024023461875849</v>
+        <v>4.02402299146795</v>
       </c>
       <c r="E610" t="n">
-        <v>4.042356125869706</v>
+        <v>4.042355653318721</v>
       </c>
       <c r="F610" t="n">
         <v>5064800</v>
@@ -12632,16 +12632,16 @@
         <v>44678</v>
       </c>
       <c r="B611" t="n">
-        <v>3.97819185256958</v>
+        <v>3.978191614151001</v>
       </c>
       <c r="C611" t="n">
-        <v>4.170685034925215</v>
+        <v>4.170684784970252</v>
       </c>
       <c r="D611" t="n">
-        <v>3.941526526128999</v>
+        <v>3.941526289907824</v>
       </c>
       <c r="E611" t="n">
-        <v>4.170685034925215</v>
+        <v>4.170684784970252</v>
       </c>
       <c r="F611" t="n">
         <v>4173400</v>
@@ -12812,16 +12812,16 @@
         <v>44691</v>
       </c>
       <c r="B620" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C620" t="n">
-        <v>2.887397395893507</v>
+        <v>2.887397154408436</v>
       </c>
       <c r="D620" t="n">
-        <v>2.694904207028261</v>
+        <v>2.694903981642197</v>
       </c>
       <c r="E620" t="n">
-        <v>2.814066521989905</v>
+        <v>2.8140662866378</v>
       </c>
       <c r="F620" t="n">
         <v>7309900</v>
@@ -12852,16 +12852,16 @@
         <v>44693</v>
       </c>
       <c r="B622" t="n">
-        <v>2.942394971847534</v>
+        <v>2.942395210266113</v>
       </c>
       <c r="C622" t="n">
-        <v>3.02489194747728</v>
+        <v>3.024892192580485</v>
       </c>
       <c r="D622" t="n">
-        <v>2.814066124547592</v>
+        <v>2.814066352567845</v>
       </c>
       <c r="E622" t="n">
-        <v>2.869064326843316</v>
+        <v>2.869064559320005</v>
       </c>
       <c r="F622" t="n">
         <v>3382300</v>
@@ -12872,16 +12872,16 @@
         <v>44694</v>
       </c>
       <c r="B623" t="n">
-        <v>3.043225049972534</v>
+        <v>3.043224811553955</v>
       </c>
       <c r="C623" t="n">
-        <v>3.10738959219715</v>
+        <v>3.107389348751661</v>
       </c>
       <c r="D623" t="n">
-        <v>2.942395398472212</v>
+        <v>2.942395167953036</v>
       </c>
       <c r="E623" t="n">
-        <v>2.969894394335936</v>
+        <v>2.969894161662377</v>
       </c>
       <c r="F623" t="n">
         <v>4357400</v>
@@ -12932,16 +12932,16 @@
         <v>44699</v>
       </c>
       <c r="B626" t="n">
-        <v>2.85989785194397</v>
+        <v>2.859898090362549</v>
       </c>
       <c r="C626" t="n">
-        <v>3.089056342075733</v>
+        <v>3.089056599598365</v>
       </c>
       <c r="D626" t="n">
-        <v>2.850731521080402</v>
+        <v>2.85073175873482</v>
       </c>
       <c r="E626" t="n">
-        <v>3.079890011212165</v>
+        <v>3.079890267970636</v>
       </c>
       <c r="F626" t="n">
         <v>5243400</v>
@@ -13112,16 +13112,16 @@
         <v>44712</v>
       </c>
       <c r="B635" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C635" t="n">
-        <v>3.015726042775277</v>
+        <v>3.015725790557546</v>
       </c>
       <c r="D635" t="n">
-        <v>2.804900190069778</v>
+        <v>2.804899955484291</v>
       </c>
       <c r="E635" t="n">
-        <v>2.988227047014898</v>
+        <v>2.988226797097023</v>
       </c>
       <c r="F635" t="n">
         <v>7519800</v>
@@ -13192,16 +13192,16 @@
         <v>44718</v>
       </c>
       <c r="B639" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C639" t="n">
-        <v>2.859898153024676</v>
+        <v>2.859897899145521</v>
       </c>
       <c r="D639" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="E639" t="n">
-        <v>2.81406649388183</v>
+        <v>2.814066244071248</v>
       </c>
       <c r="F639" t="n">
         <v>3115900</v>
@@ -13212,16 +13212,16 @@
         <v>44719</v>
       </c>
       <c r="B640" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C640" t="n">
-        <v>2.713236544142034</v>
+        <v>2.713236786657148</v>
       </c>
       <c r="D640" t="n">
-        <v>2.584907694170964</v>
+        <v>2.584907925215759</v>
       </c>
       <c r="E640" t="n">
-        <v>2.658238559244103</v>
+        <v>2.658238796843375</v>
       </c>
       <c r="F640" t="n">
         <v>2825300</v>
@@ -13232,16 +13232,16 @@
         <v>44720</v>
       </c>
       <c r="B641" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C641" t="n">
-        <v>2.722402874958356</v>
+        <v>2.722403118292777</v>
       </c>
       <c r="D641" t="n">
-        <v>2.63990589761146</v>
+        <v>2.639906133572117</v>
       </c>
       <c r="E641" t="n">
-        <v>2.649072228427781</v>
+        <v>2.649072465207746</v>
       </c>
       <c r="F641" t="n">
         <v>3025200</v>
@@ -13272,16 +13272,16 @@
         <v>44722</v>
       </c>
       <c r="B643" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C643" t="n">
-        <v>2.63073952891308</v>
+        <v>2.630739779558241</v>
       </c>
       <c r="D643" t="n">
-        <v>2.493244557226074</v>
+        <v>2.493244794771327</v>
       </c>
       <c r="E643" t="n">
-        <v>2.594074203129878</v>
+        <v>2.594074450281731</v>
       </c>
       <c r="F643" t="n">
         <v>4379600</v>
@@ -13292,16 +13292,16 @@
         <v>44725</v>
       </c>
       <c r="B644" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C644" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="D644" t="n">
-        <v>2.282418486052185</v>
+        <v>2.282418717049181</v>
       </c>
       <c r="E644" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="F644" t="n">
         <v>5369000</v>
@@ -13312,16 +13312,16 @@
         <v>44726</v>
       </c>
       <c r="B645" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C645" t="n">
-        <v>2.401580660851382</v>
+        <v>2.401580915813275</v>
       </c>
       <c r="D645" t="n">
-        <v>2.236586719791586</v>
+        <v>2.236586957237029</v>
       </c>
       <c r="E645" t="n">
-        <v>2.374081670674749</v>
+        <v>2.374081922717234</v>
       </c>
       <c r="F645" t="n">
         <v>2610500</v>
@@ -13392,16 +13392,16 @@
         <v>44733</v>
       </c>
       <c r="B649" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="C649" t="n">
-        <v>2.328250420451433</v>
+        <v>2.328250174279411</v>
       </c>
       <c r="D649" t="n">
-        <v>2.236587104111843</v>
+        <v>2.236586867631624</v>
       </c>
       <c r="E649" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="F649" t="n">
         <v>3435200</v>
@@ -13412,16 +13412,16 @@
         <v>44734</v>
       </c>
       <c r="B650" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C650" t="n">
-        <v>2.300751030203729</v>
+        <v>2.300751274461124</v>
       </c>
       <c r="D650" t="n">
-        <v>2.190755069497199</v>
+        <v>2.190755302076961</v>
       </c>
       <c r="E650" t="n">
-        <v>2.236586719791586</v>
+        <v>2.236586957237029</v>
       </c>
       <c r="F650" t="n">
         <v>3144500</v>
@@ -13452,16 +13452,16 @@
         <v>44736</v>
       </c>
       <c r="B652" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C652" t="n">
-        <v>2.355749010556994</v>
+        <v>2.355749260653206</v>
       </c>
       <c r="D652" t="n">
-        <v>2.209087729614954</v>
+        <v>2.209087964140989</v>
       </c>
       <c r="E652" t="n">
-        <v>2.337416350439239</v>
+        <v>2.337416598589179</v>
       </c>
       <c r="F652" t="n">
         <v>3887000</v>
@@ -13472,16 +13472,16 @@
         <v>44739</v>
       </c>
       <c r="B653" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C653" t="n">
-        <v>2.291584773416974</v>
+        <v>2.291585025979039</v>
       </c>
       <c r="D653" t="n">
-        <v>2.154089599594934</v>
+        <v>2.154089837003265</v>
       </c>
       <c r="E653" t="n">
-        <v>2.273252112713042</v>
+        <v>2.273252363254613</v>
       </c>
       <c r="F653" t="n">
         <v>3063200</v>
@@ -13512,16 +13512,16 @@
         <v>44741</v>
       </c>
       <c r="B655" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C655" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="D655" t="n">
-        <v>2.016594984404464</v>
+        <v>2.016594758317869</v>
       </c>
       <c r="E655" t="n">
-        <v>2.089925639587051</v>
+        <v>2.089925405279133</v>
       </c>
       <c r="F655" t="n">
         <v>5733700</v>
@@ -13632,16 +13632,16 @@
         <v>44749</v>
       </c>
       <c r="B661" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C661" t="n">
-        <v>2.392414452347443</v>
+        <v>2.392414694476813</v>
       </c>
       <c r="D661" t="n">
-        <v>2.300751147101395</v>
+        <v>2.300751379953786</v>
       </c>
       <c r="E661" t="n">
-        <v>2.337416469199814</v>
+        <v>2.337416705762997</v>
       </c>
       <c r="F661" t="n">
         <v>2762300</v>
@@ -13652,16 +13652,16 @@
         <v>44750</v>
       </c>
       <c r="B662" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="C662" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="D662" t="n">
-        <v>2.300751402022951</v>
+        <v>2.300751173614302</v>
       </c>
       <c r="E662" t="n">
-        <v>2.337416728183861</v>
+        <v>2.337416496135238</v>
       </c>
       <c r="F662" t="n">
         <v>2746100</v>
@@ -13672,16 +13672,16 @@
         <v>44753</v>
       </c>
       <c r="B663" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C663" t="n">
-        <v>2.383248305010609</v>
+        <v>2.38324806191716</v>
       </c>
       <c r="D663" t="n">
-        <v>2.273252330260538</v>
+        <v>2.273252098386777</v>
       </c>
       <c r="E663" t="n">
-        <v>2.346582980093919</v>
+        <v>2.346582740740366</v>
       </c>
       <c r="F663" t="n">
         <v>1807800</v>
@@ -13692,16 +13692,16 @@
         <v>44754</v>
       </c>
       <c r="B664" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="C664" t="n">
-        <v>2.447412925209175</v>
+        <v>2.447412682240605</v>
       </c>
       <c r="D664" t="n">
-        <v>2.254919744321813</v>
+        <v>2.254919520463134</v>
       </c>
       <c r="E664" t="n">
-        <v>2.355749391264316</v>
+        <v>2.355749157395706</v>
       </c>
       <c r="F664" t="n">
         <v>5712200</v>
@@ -13752,16 +13752,16 @@
         <v>44757</v>
       </c>
       <c r="B667" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C667" t="n">
-        <v>2.245753121657145</v>
+        <v>2.245753369167974</v>
       </c>
       <c r="D667" t="n">
-        <v>2.135756938891002</v>
+        <v>2.135757174278839</v>
       </c>
       <c r="E667" t="n">
-        <v>2.227420460953214</v>
+        <v>2.227420706443548</v>
       </c>
       <c r="F667" t="n">
         <v>2806200</v>
@@ -13772,16 +13772,16 @@
         <v>44760</v>
       </c>
       <c r="B668" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="C668" t="n">
-        <v>2.346583083719351</v>
+        <v>2.346582835608969</v>
       </c>
       <c r="D668" t="n">
-        <v>2.199921777576007</v>
+        <v>2.19992154497251</v>
       </c>
       <c r="E668" t="n">
-        <v>2.199921777576007</v>
+        <v>2.19992154497251</v>
       </c>
       <c r="F668" t="n">
         <v>4381400</v>
@@ -13832,16 +13832,16 @@
         <v>44763</v>
       </c>
       <c r="B671" t="n">
-        <v>2.383248090744019</v>
+        <v>2.383248329162598</v>
       </c>
       <c r="C671" t="n">
-        <v>2.474911613337284</v>
+        <v>2.474911860925822</v>
       </c>
       <c r="D671" t="n">
-        <v>2.346582769123735</v>
+        <v>2.346583003874339</v>
       </c>
       <c r="E671" t="n">
-        <v>2.364915429933876</v>
+        <v>2.364915666518468</v>
       </c>
       <c r="F671" t="n">
         <v>3831200</v>
@@ -13872,16 +13872,16 @@
         <v>44767</v>
       </c>
       <c r="B673" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C673" t="n">
-        <v>2.392414452347443</v>
+        <v>2.392414694476813</v>
       </c>
       <c r="D673" t="n">
-        <v>2.25491949447837</v>
+        <v>2.254919722692273</v>
       </c>
       <c r="E673" t="n">
-        <v>2.300751147101395</v>
+        <v>2.300751379953786</v>
       </c>
       <c r="F673" t="n">
         <v>3311300</v>
@@ -13892,16 +13892,16 @@
         <v>44768</v>
       </c>
       <c r="B674" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C674" t="n">
-        <v>2.520743493812202</v>
+        <v>2.520743251874533</v>
       </c>
       <c r="D674" t="n">
-        <v>2.300751325610525</v>
+        <v>2.300751104787417</v>
       </c>
       <c r="E674" t="n">
-        <v>2.374081975496892</v>
+        <v>2.374081747635604</v>
       </c>
       <c r="F674" t="n">
         <v>4848400</v>
@@ -13912,16 +13912,16 @@
         <v>44769</v>
       </c>
       <c r="B675" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C675" t="n">
-        <v>2.603240801706716</v>
+        <v>2.603240558142417</v>
       </c>
       <c r="D675" t="n">
-        <v>2.419914153978682</v>
+        <v>2.419913927566782</v>
       </c>
       <c r="E675" t="n">
-        <v>2.502411145456297</v>
+        <v>2.502410911325818</v>
       </c>
       <c r="F675" t="n">
         <v>5961800</v>
@@ -13952,16 +13952,16 @@
         <v>44771</v>
       </c>
       <c r="B677" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C677" t="n">
-        <v>2.603240523687103</v>
+        <v>2.603240282723132</v>
       </c>
       <c r="D677" t="n">
-        <v>2.493244546797579</v>
+        <v>2.493244316015175</v>
       </c>
       <c r="E677" t="n">
-        <v>2.566575198057261</v>
+        <v>2.566574960487146</v>
       </c>
       <c r="F677" t="n">
         <v>2895400</v>
@@ -13972,16 +13972,16 @@
         <v>44774</v>
       </c>
       <c r="B678" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C678" t="n">
-        <v>2.749902171081845</v>
+        <v>2.749901926967264</v>
       </c>
       <c r="D678" t="n">
-        <v>2.520743656825025</v>
+        <v>2.520743433053326</v>
       </c>
       <c r="E678" t="n">
-        <v>2.57574164779644</v>
+        <v>2.575741419142454</v>
       </c>
       <c r="F678" t="n">
         <v>6003000</v>
@@ -13992,16 +13992,16 @@
         <v>44775</v>
       </c>
       <c r="B679" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C679" t="n">
-        <v>2.740735713341587</v>
+        <v>2.740735459650637</v>
       </c>
       <c r="D679" t="n">
-        <v>2.548242535242341</v>
+        <v>2.548242299369153</v>
       </c>
       <c r="E679" t="n">
-        <v>2.676571393489365</v>
+        <v>2.676571145737662</v>
       </c>
       <c r="F679" t="n">
         <v>4865400</v>
@@ -14032,16 +14032,16 @@
         <v>44777</v>
       </c>
       <c r="B681" t="n">
-        <v>2.85989785194397</v>
+        <v>2.859898090362549</v>
       </c>
       <c r="C681" t="n">
-        <v>2.878230732213672</v>
+        <v>2.878230972160592</v>
       </c>
       <c r="D681" t="n">
-        <v>2.704070227263316</v>
+        <v>2.704070452691151</v>
       </c>
       <c r="E681" t="n">
-        <v>2.722402888990452</v>
+        <v>2.72240311594661</v>
       </c>
       <c r="F681" t="n">
         <v>7566500</v>
@@ -14052,16 +14052,16 @@
         <v>44778</v>
       </c>
       <c r="B682" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C682" t="n">
-        <v>2.969894420271998</v>
+        <v>2.969894169468031</v>
       </c>
       <c r="D682" t="n">
-        <v>2.731569568829172</v>
+        <v>2.731569338151449</v>
       </c>
       <c r="E682" t="n">
-        <v>2.869064767891131</v>
+        <v>2.869064525602105</v>
       </c>
       <c r="F682" t="n">
         <v>6497600</v>
@@ -14072,16 +14072,16 @@
         <v>44781</v>
       </c>
       <c r="B683" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="C683" t="n">
-        <v>2.924062679704158</v>
+        <v>2.924062427027984</v>
       </c>
       <c r="D683" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="E683" t="n">
-        <v>2.850731806900742</v>
+        <v>2.850731560561287</v>
       </c>
       <c r="F683" t="n">
         <v>8446700</v>
@@ -14132,16 +14132,16 @@
         <v>44784</v>
       </c>
       <c r="B686" t="n">
-        <v>3.034058570861816</v>
+        <v>3.034058332443237</v>
       </c>
       <c r="C686" t="n">
-        <v>3.153221099034329</v>
+        <v>3.15322085125187</v>
       </c>
       <c r="D686" t="n">
-        <v>2.887397266701901</v>
+        <v>2.887397039808076</v>
       </c>
       <c r="E686" t="n">
-        <v>2.896563598211896</v>
+        <v>2.896563370597774</v>
       </c>
       <c r="F686" t="n">
         <v>13306300</v>
@@ -14232,16 +14232,16 @@
         <v>44791</v>
       </c>
       <c r="B691" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="C691" t="n">
-        <v>3.272383248987116</v>
+        <v>3.272383506912668</v>
       </c>
       <c r="D691" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="E691" t="n">
-        <v>3.263216917924395</v>
+        <v>3.263217175127469</v>
       </c>
       <c r="F691" t="n">
         <v>6872400</v>
@@ -14392,16 +14392,16 @@
         <v>44803</v>
       </c>
       <c r="B699" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="C699" t="n">
-        <v>3.162387276234473</v>
+        <v>3.162387525490268</v>
       </c>
       <c r="D699" t="n">
-        <v>2.951561443249337</v>
+        <v>2.951561675888077</v>
       </c>
       <c r="E699" t="n">
-        <v>3.07989007812742</v>
+        <v>3.079890320880878</v>
       </c>
       <c r="F699" t="n">
         <v>4644000</v>
@@ -14432,16 +14432,16 @@
         <v>44805</v>
       </c>
       <c r="B701" t="n">
-        <v>3.125722169876099</v>
+        <v>3.12572193145752</v>
       </c>
       <c r="C701" t="n">
-        <v>3.134888501577799</v>
+        <v>3.134888262460046</v>
       </c>
       <c r="D701" t="n">
-        <v>2.942395317299501</v>
+        <v>2.94239509286442</v>
       </c>
       <c r="E701" t="n">
-        <v>2.951561649001202</v>
+        <v>2.951561423866946</v>
       </c>
       <c r="F701" t="n">
         <v>5408300</v>
@@ -14552,16 +14552,16 @@
         <v>44816</v>
       </c>
       <c r="B707" t="n">
-        <v>3.39154577255249</v>
+        <v>3.391546010971069</v>
       </c>
       <c r="C707" t="n">
-        <v>3.437377427882408</v>
+        <v>3.437377669522857</v>
       </c>
       <c r="D707" t="n">
-        <v>3.327381455090605</v>
+        <v>3.327381688998567</v>
       </c>
       <c r="E707" t="n">
-        <v>3.327381455090605</v>
+        <v>3.327381688998567</v>
       </c>
       <c r="F707" t="n">
         <v>4227100</v>
@@ -14732,16 +14732,16 @@
         <v>44827</v>
       </c>
       <c r="B716" t="n">
-        <v>3.134888172149658</v>
+        <v>3.134888410568237</v>
       </c>
       <c r="C716" t="n">
-        <v>3.254050471749655</v>
+        <v>3.25405071923092</v>
       </c>
       <c r="D716" t="n">
-        <v>3.098222849195813</v>
+        <v>3.098223084825873</v>
       </c>
       <c r="E716" t="n">
-        <v>3.098222849195813</v>
+        <v>3.098223084825873</v>
       </c>
       <c r="F716" t="n">
         <v>4782400</v>
@@ -14792,16 +14792,16 @@
         <v>44832</v>
       </c>
       <c r="B719" t="n">
-        <v>2.942394971847534</v>
+        <v>2.942395210266113</v>
       </c>
       <c r="C719" t="n">
-        <v>2.960727633098589</v>
+        <v>2.96072787300264</v>
       </c>
       <c r="D719" t="n">
-        <v>2.841565116424174</v>
+        <v>2.841565346672636</v>
       </c>
       <c r="E719" t="n">
-        <v>2.896563318719898</v>
+        <v>2.896563553424795</v>
       </c>
       <c r="F719" t="n">
         <v>3561500</v>
@@ -14812,16 +14812,16 @@
         <v>44833</v>
       </c>
       <c r="B720" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C720" t="n">
-        <v>2.905730096029628</v>
+        <v>2.90572985064426</v>
       </c>
       <c r="D720" t="n">
-        <v>2.795733893071542</v>
+        <v>2.79573365697522</v>
       </c>
       <c r="E720" t="n">
-        <v>2.896563763995004</v>
+        <v>2.896563519383722</v>
       </c>
       <c r="F720" t="n">
         <v>3966200</v>
@@ -14932,16 +14932,16 @@
         <v>44841</v>
       </c>
       <c r="B726" t="n">
-        <v>3.44654369354248</v>
+        <v>3.44654393196106</v>
       </c>
       <c r="C726" t="n">
-        <v>3.602371537249589</v>
+        <v>3.602371786447736</v>
       </c>
       <c r="D726" t="n">
-        <v>3.419044700866385</v>
+        <v>3.41904493738269</v>
       </c>
       <c r="E726" t="n">
-        <v>3.464876355326544</v>
+        <v>3.464876595013306</v>
       </c>
       <c r="F726" t="n">
         <v>4739800</v>
@@ -15012,16 +15012,16 @@
         <v>44848</v>
       </c>
       <c r="B730" t="n">
-        <v>3.052391052246094</v>
+        <v>3.052391290664673</v>
       </c>
       <c r="C730" t="n">
-        <v>3.199052566221344</v>
+        <v>3.199052816095478</v>
       </c>
       <c r="D730" t="n">
-        <v>2.997393066458838</v>
+        <v>2.997393300581591</v>
       </c>
       <c r="E730" t="n">
-        <v>3.153220911398631</v>
+        <v>3.153221157692909</v>
       </c>
       <c r="F730" t="n">
         <v>2652600</v>
@@ -15032,16 +15032,16 @@
         <v>44851</v>
       </c>
       <c r="B731" t="n">
-        <v>3.034058570861816</v>
+        <v>3.034058332443237</v>
       </c>
       <c r="C731" t="n">
-        <v>3.116555772994351</v>
+        <v>3.11655552809308</v>
       </c>
       <c r="D731" t="n">
-        <v>3.024892239351822</v>
+        <v>3.02489200165354</v>
       </c>
       <c r="E731" t="n">
-        <v>3.07989022841179</v>
+        <v>3.079889986391725</v>
       </c>
       <c r="F731" t="n">
         <v>3944900</v>
@@ -15092,16 +15092,16 @@
         <v>44854</v>
       </c>
       <c r="B734" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C734" t="n">
-        <v>2.95156135187282</v>
+        <v>2.951561601940523</v>
       </c>
       <c r="D734" t="n">
-        <v>2.795733510088233</v>
+        <v>2.795733746953598</v>
       </c>
       <c r="E734" t="n">
-        <v>2.942395021093878</v>
+        <v>2.942395270384973</v>
       </c>
       <c r="F734" t="n">
         <v>4518300</v>
@@ -15112,16 +15112,16 @@
         <v>44855</v>
       </c>
       <c r="B735" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C735" t="n">
-        <v>2.869064374862337</v>
+        <v>2.869064617940577</v>
       </c>
       <c r="D735" t="n">
-        <v>2.685737540740923</v>
+        <v>2.685737768287004</v>
       </c>
       <c r="E735" t="n">
-        <v>2.804899840867176</v>
+        <v>2.804900078509148</v>
       </c>
       <c r="F735" t="n">
         <v>6831600</v>
@@ -15132,16 +15132,16 @@
         <v>44858</v>
       </c>
       <c r="B736" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C736" t="n">
-        <v>2.814066387171744</v>
+        <v>2.814066144805841</v>
       </c>
       <c r="D736" t="n">
-        <v>2.704070409399987</v>
+        <v>2.704070176507662</v>
       </c>
       <c r="E736" t="n">
-        <v>2.795733724209785</v>
+        <v>2.795733483422811</v>
       </c>
       <c r="F736" t="n">
         <v>4201100</v>
@@ -15172,16 +15172,16 @@
         <v>44860</v>
       </c>
       <c r="B738" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C738" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="D738" t="n">
-        <v>2.438246512690039</v>
+        <v>2.438246278670322</v>
       </c>
       <c r="E738" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="F738" t="n">
         <v>9447400</v>
@@ -15232,16 +15232,16 @@
         <v>44865</v>
       </c>
       <c r="B741" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C741" t="n">
-        <v>2.832399050133704</v>
+        <v>2.832398806188871</v>
       </c>
       <c r="D741" t="n">
-        <v>2.557408887161731</v>
+        <v>2.55740866690086</v>
       </c>
       <c r="E741" t="n">
-        <v>2.59407421308565</v>
+        <v>2.59407398966692</v>
       </c>
       <c r="F741" t="n">
         <v>6603200</v>
@@ -15292,16 +15292,16 @@
         <v>44869</v>
       </c>
       <c r="B744" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C744" t="n">
-        <v>2.933228914967061</v>
+        <v>2.933228662338098</v>
       </c>
       <c r="D744" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="E744" t="n">
-        <v>2.924062583486082</v>
+        <v>2.924062331646583</v>
       </c>
       <c r="F744" t="n">
         <v>7869400</v>
@@ -15392,16 +15392,16 @@
         <v>44876</v>
       </c>
       <c r="B749" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C749" t="n">
-        <v>2.429079869570562</v>
+        <v>2.429080127451886</v>
       </c>
       <c r="D749" t="n">
-        <v>2.227420389732709</v>
+        <v>2.227420626205016</v>
       </c>
       <c r="E749" t="n">
-        <v>2.319083690321484</v>
+        <v>2.319083936525152</v>
       </c>
       <c r="F749" t="n">
         <v>8256600</v>
@@ -15512,16 +15512,16 @@
         <v>44887</v>
       </c>
       <c r="B755" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C755" t="n">
-        <v>2.209087984933213</v>
+        <v>2.209088230483989</v>
       </c>
       <c r="D755" t="n">
-        <v>2.108258124089469</v>
+        <v>2.10825835843252</v>
       </c>
       <c r="E755" t="n">
-        <v>2.181588991578348</v>
+        <v>2.181589234072479</v>
       </c>
       <c r="F755" t="n">
         <v>3236000</v>
@@ -15572,16 +15572,16 @@
         <v>44890</v>
       </c>
       <c r="B758" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C758" t="n">
-        <v>2.254919640524655</v>
+        <v>2.25491989116984</v>
       </c>
       <c r="D758" t="n">
-        <v>2.117424455207757</v>
+        <v>2.117424690569691</v>
       </c>
       <c r="E758" t="n">
-        <v>2.22742064716979</v>
+        <v>2.22742089475833</v>
       </c>
       <c r="F758" t="n">
         <v>2578200</v>
@@ -15592,16 +15592,16 @@
         <v>44893</v>
       </c>
       <c r="B759" t="n">
-        <v>2.044094085693359</v>
+        <v>2.04409384727478</v>
       </c>
       <c r="C759" t="n">
-        <v>2.144923741778154</v>
+        <v>2.144923491599029</v>
       </c>
       <c r="D759" t="n">
-        <v>2.034927753322014</v>
+        <v>2.034927515972576</v>
       </c>
       <c r="E759" t="n">
-        <v>2.135757409406809</v>
+        <v>2.135757160296825</v>
       </c>
       <c r="F759" t="n">
         <v>2781000</v>
@@ -15672,16 +15672,16 @@
         <v>44897</v>
       </c>
       <c r="B763" t="n">
-        <v>2.181589126586914</v>
+        <v>2.181588888168335</v>
       </c>
       <c r="C763" t="n">
-        <v>2.199921789958015</v>
+        <v>2.199921549535921</v>
       </c>
       <c r="D763" t="n">
-        <v>2.099091922874372</v>
+        <v>2.099091693471637</v>
       </c>
       <c r="E763" t="n">
-        <v>2.154089912987676</v>
+        <v>2.154089677574394</v>
       </c>
       <c r="F763" t="n">
         <v>2941200</v>
@@ -15772,16 +15772,16 @@
         <v>44904</v>
       </c>
       <c r="B768" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C768" t="n">
-        <v>2.172422626667462</v>
+        <v>2.172422383110556</v>
       </c>
       <c r="D768" t="n">
-        <v>2.071592975791404</v>
+        <v>2.071592743538817</v>
       </c>
       <c r="E768" t="n">
-        <v>2.135757299076168</v>
+        <v>2.135757059629924</v>
       </c>
       <c r="F768" t="n">
         <v>2468100</v>
@@ -15792,16 +15792,16 @@
         <v>44907</v>
       </c>
       <c r="B769" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C769" t="n">
-        <v>2.135757299076168</v>
+        <v>2.135757059629924</v>
       </c>
       <c r="D769" t="n">
-        <v>2.034927648200111</v>
+        <v>2.034927420058185</v>
       </c>
       <c r="E769" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="F769" t="n">
         <v>2948100</v>
@@ -15812,16 +15812,16 @@
         <v>44908</v>
       </c>
       <c r="B770" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C770" t="n">
-        <v>2.190755340574407</v>
+        <v>2.190755471267162</v>
       </c>
       <c r="D770" t="n">
-        <v>1.989095835783838</v>
+        <v>1.989095954446297</v>
       </c>
       <c r="E770" t="n">
-        <v>2.144923466066379</v>
+        <v>2.144923594024966</v>
       </c>
       <c r="F770" t="n">
         <v>3298100</v>
@@ -15832,16 +15832,16 @@
         <v>44909</v>
       </c>
       <c r="B771" t="n">
-        <v>1.979929566383362</v>
+        <v>1.979929685592651</v>
       </c>
       <c r="C771" t="n">
-        <v>2.007428560820864</v>
+        <v>2.007428681685836</v>
       </c>
       <c r="D771" t="n">
-        <v>1.888266033049108</v>
+        <v>1.888266146739441</v>
       </c>
       <c r="E771" t="n">
-        <v>1.970763234904195</v>
+        <v>1.97076335356159</v>
       </c>
       <c r="F771" t="n">
         <v>6743600</v>
@@ -15852,16 +15852,16 @@
         <v>44910</v>
       </c>
       <c r="B772" t="n">
-        <v>1.906598567962646</v>
+        <v>1.906598687171936</v>
       </c>
       <c r="C772" t="n">
-        <v>2.044093749458731</v>
+        <v>2.04409387726485</v>
       </c>
       <c r="D772" t="n">
-        <v>1.897432237099079</v>
+        <v>1.897432355735247</v>
       </c>
       <c r="E772" t="n">
-        <v>1.952430440823052</v>
+        <v>1.952430562897961</v>
       </c>
       <c r="F772" t="n">
         <v>3868500</v>
@@ -15912,16 +15912,16 @@
         <v>44915</v>
       </c>
       <c r="B775" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C775" t="n">
-        <v>2.108258224859735</v>
+        <v>2.10825798114297</v>
       </c>
       <c r="D775" t="n">
-        <v>1.879099717406664</v>
+        <v>1.879099500180852</v>
       </c>
       <c r="E775" t="n">
-        <v>1.924931375188761</v>
+        <v>1.924931152664764</v>
       </c>
       <c r="F775" t="n">
         <v>8464700</v>
@@ -15932,16 +15932,16 @@
         <v>44916</v>
       </c>
       <c r="B776" t="n">
-        <v>1.970763087272644</v>
+        <v>1.970763206481934</v>
       </c>
       <c r="C776" t="n">
-        <v>2.108258049160288</v>
+        <v>2.108258176686496</v>
       </c>
       <c r="D776" t="n">
-        <v>1.961596756480134</v>
+        <v>1.961596875134963</v>
       </c>
       <c r="E776" t="n">
-        <v>2.05326006440523</v>
+        <v>2.053260188604671</v>
       </c>
       <c r="F776" t="n">
         <v>5125400</v>
@@ -15952,16 +15952,16 @@
         <v>44917</v>
       </c>
       <c r="B777" t="n">
-        <v>1.906598567962646</v>
+        <v>1.906598687171936</v>
       </c>
       <c r="C777" t="n">
-        <v>1.989095764277324</v>
+        <v>1.989095888644717</v>
       </c>
       <c r="D777" t="n">
-        <v>1.869933244508375</v>
+        <v>1.869933361425181</v>
       </c>
       <c r="E777" t="n">
-        <v>1.952430440823052</v>
+        <v>1.952430562897961</v>
       </c>
       <c r="F777" t="n">
         <v>5426000</v>
@@ -15972,16 +15972,16 @@
         <v>44918</v>
       </c>
       <c r="B778" t="n">
-        <v>1.98909592628479</v>
+        <v>1.9890958070755</v>
       </c>
       <c r="C778" t="n">
-        <v>2.016594921115226</v>
+        <v>2.016594800257883</v>
       </c>
       <c r="D778" t="n">
-        <v>1.906598723250898</v>
+        <v>1.906598608985781</v>
       </c>
       <c r="E778" t="n">
-        <v>1.915765054861043</v>
+        <v>1.915764940046575</v>
       </c>
       <c r="F778" t="n">
         <v>4257800</v>
@@ -15992,16 +15992,16 @@
         <v>44921</v>
       </c>
       <c r="B779" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C779" t="n">
-        <v>2.044093822942382</v>
+        <v>2.044093944885827</v>
       </c>
       <c r="D779" t="n">
-        <v>1.952430511011476</v>
+        <v>1.95243062748661</v>
       </c>
       <c r="E779" t="n">
-        <v>1.989095835783838</v>
+        <v>1.989095954446297</v>
       </c>
       <c r="F779" t="n">
         <v>2247800</v>
@@ -16012,16 +16012,16 @@
         <v>44922</v>
       </c>
       <c r="B780" t="n">
-        <v>1.970763087272644</v>
+        <v>1.970763206481934</v>
       </c>
       <c r="C780" t="n">
-        <v>2.06242639519774</v>
+        <v>2.062426519951642</v>
       </c>
       <c r="D780" t="n">
-        <v>1.934097545560041</v>
+        <v>1.934097662551472</v>
       </c>
       <c r="E780" t="n">
-        <v>2.007428410442682</v>
+        <v>2.007428531869817</v>
       </c>
       <c r="F780" t="n">
         <v>3370000</v>
@@ -16032,16 +16032,16 @@
         <v>44923</v>
       </c>
       <c r="B781" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C781" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="D781" t="n">
-        <v>1.952430495078567</v>
+        <v>1.952430712100627</v>
       </c>
       <c r="E781" t="n">
-        <v>1.970763157315144</v>
+        <v>1.970763376374967</v>
       </c>
       <c r="F781" t="n">
         <v>4579800</v>
@@ -16112,16 +16112,16 @@
         <v>44930</v>
       </c>
       <c r="B785" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C785" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="D785" t="n">
-        <v>1.952430588400603</v>
+        <v>1.952430362697669</v>
       </c>
       <c r="E785" t="n">
-        <v>1.961596919957022</v>
+        <v>1.961596693194451</v>
       </c>
       <c r="F785" t="n">
         <v>2931500</v>
@@ -16172,16 +16172,16 @@
         <v>44935</v>
       </c>
       <c r="B788" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C788" t="n">
-        <v>2.190755139545351</v>
+        <v>2.190755380994696</v>
       </c>
       <c r="D788" t="n">
-        <v>2.071592626427242</v>
+        <v>2.071592854743348</v>
       </c>
       <c r="E788" t="n">
-        <v>2.135756938891002</v>
+        <v>2.135757174278839</v>
       </c>
       <c r="F788" t="n">
         <v>5355300</v>
@@ -16232,16 +16232,16 @@
         <v>44938</v>
       </c>
       <c r="B791" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C791" t="n">
-        <v>2.410747517240701</v>
+        <v>2.410747271342309</v>
       </c>
       <c r="D791" t="n">
-        <v>2.190755349197985</v>
+        <v>2.19075512573899</v>
       </c>
       <c r="E791" t="n">
-        <v>2.282418661489711</v>
+        <v>2.282418428680975</v>
       </c>
       <c r="F791" t="n">
         <v>7447800</v>
@@ -16252,16 +16252,16 @@
         <v>44939</v>
       </c>
       <c r="B792" t="n">
-        <v>2.227420568466187</v>
+        <v>2.227420806884766</v>
       </c>
       <c r="C792" t="n">
-        <v>2.392414522765486</v>
+        <v>2.392414778844683</v>
       </c>
       <c r="D792" t="n">
-        <v>2.19992157608297</v>
+        <v>2.199921811558113</v>
       </c>
       <c r="E792" t="n">
-        <v>2.319083876410242</v>
+        <v>2.319084124640275</v>
       </c>
       <c r="F792" t="n">
         <v>4284200</v>
@@ -16272,16 +16272,16 @@
         <v>44942</v>
       </c>
       <c r="B793" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C793" t="n">
-        <v>2.869064517857597</v>
+        <v>2.869064242488531</v>
       </c>
       <c r="D793" t="n">
-        <v>2.29158499437473</v>
+        <v>2.291584774431394</v>
       </c>
       <c r="E793" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="F793" t="n">
         <v>29414600</v>
@@ -16312,16 +16312,16 @@
         <v>44944</v>
       </c>
       <c r="B795" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C795" t="n">
-        <v>2.493244498303254</v>
+        <v>2.493244243990096</v>
       </c>
       <c r="D795" t="n">
-        <v>2.319083986406401</v>
+        <v>2.31908374985777</v>
       </c>
       <c r="E795" t="n">
-        <v>2.429080179699046</v>
+        <v>2.429079931930706</v>
       </c>
       <c r="F795" t="n">
         <v>5215700</v>
@@ -16352,16 +16352,16 @@
         <v>44946</v>
       </c>
       <c r="B797" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C797" t="n">
-        <v>2.823232502425061</v>
+        <v>2.823232741620247</v>
       </c>
       <c r="D797" t="n">
-        <v>2.291584880161267</v>
+        <v>2.291585074313209</v>
       </c>
       <c r="E797" t="n">
-        <v>2.30075121094021</v>
+        <v>2.300751405868758</v>
       </c>
       <c r="F797" t="n">
         <v>16674600</v>
@@ -16392,16 +16392,16 @@
         <v>44950</v>
       </c>
       <c r="B799" t="n">
-        <v>2.58490777015686</v>
+        <v>2.584908008575439</v>
       </c>
       <c r="C799" t="n">
-        <v>2.704070292814508</v>
+        <v>2.704070542224025</v>
       </c>
       <c r="D799" t="n">
-        <v>2.54824244581376</v>
+        <v>2.548242680850518</v>
       </c>
       <c r="E799" t="n">
-        <v>2.575741439071086</v>
+        <v>2.575741676644209</v>
       </c>
       <c r="F799" t="n">
         <v>6059800</v>
@@ -16452,16 +16452,16 @@
         <v>44953</v>
       </c>
       <c r="B802" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C802" t="n">
-        <v>2.933229055494139</v>
+        <v>2.933228810175975</v>
       </c>
       <c r="D802" t="n">
-        <v>2.704070538948388</v>
+        <v>2.704070312795705</v>
       </c>
       <c r="E802" t="n">
-        <v>2.731569534708767</v>
+        <v>2.731569306256229</v>
       </c>
       <c r="F802" t="n">
         <v>5877300</v>
@@ -16572,16 +16572,16 @@
         <v>44963</v>
       </c>
       <c r="B808" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C808" t="n">
-        <v>2.676571343363308</v>
+        <v>2.676571086469485</v>
       </c>
       <c r="D808" t="n">
-        <v>2.465745506397427</v>
+        <v>2.465745269738393</v>
       </c>
       <c r="E808" t="n">
-        <v>2.658238680891716</v>
+        <v>2.658238425757438</v>
       </c>
       <c r="F808" t="n">
         <v>3450900</v>
@@ -16692,16 +16692,16 @@
         <v>44971</v>
       </c>
       <c r="B814" t="n">
-        <v>2.034927368164062</v>
+        <v>2.034927606582642</v>
       </c>
       <c r="C814" t="n">
-        <v>2.172422327710077</v>
+        <v>2.172422582238004</v>
       </c>
       <c r="D814" t="n">
-        <v>2.00742837625486</v>
+        <v>2.007428611451569</v>
       </c>
       <c r="E814" t="n">
-        <v>2.099091682618869</v>
+        <v>2.099091928555144</v>
       </c>
       <c r="F814" t="n">
         <v>2996200</v>
@@ -16732,16 +16732,16 @@
         <v>44973</v>
       </c>
       <c r="B816" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C816" t="n">
-        <v>2.144923551085412</v>
+        <v>2.144923303130099</v>
       </c>
       <c r="D816" t="n">
-        <v>2.044093903964798</v>
+        <v>2.044093667665493</v>
       </c>
       <c r="E816" t="n">
-        <v>2.099091893303315</v>
+        <v>2.099091650646187</v>
       </c>
       <c r="F816" t="n">
         <v>2969500</v>
@@ -16752,16 +16752,16 @@
         <v>44974</v>
       </c>
       <c r="B817" t="n">
-        <v>1.961597084999084</v>
+        <v>1.961596965789795</v>
       </c>
       <c r="C817" t="n">
-        <v>2.099092069913735</v>
+        <v>2.099091942348662</v>
       </c>
       <c r="D817" t="n">
-        <v>1.961597084999084</v>
+        <v>1.961596965789795</v>
       </c>
       <c r="E817" t="n">
-        <v>2.053260408275518</v>
+        <v>2.053260283495706</v>
       </c>
       <c r="F817" t="n">
         <v>5027900</v>
@@ -16832,16 +16832,16 @@
         <v>44984</v>
       </c>
       <c r="B821" t="n">
-        <v>1.860766887664795</v>
+        <v>1.860767006874084</v>
       </c>
       <c r="C821" t="n">
-        <v>1.897432210607146</v>
+        <v>1.897432332165384</v>
       </c>
       <c r="D821" t="n">
-        <v>1.814935233986857</v>
+        <v>1.81493535025996</v>
       </c>
       <c r="E821" t="n">
-        <v>1.824101564722445</v>
+        <v>1.824101681582785</v>
       </c>
       <c r="F821" t="n">
         <v>2628700</v>
@@ -16892,16 +16892,16 @@
         <v>44987</v>
       </c>
       <c r="B824" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C824" t="n">
-        <v>2.144923466066379</v>
+        <v>2.144923594024966</v>
       </c>
       <c r="D824" t="n">
-        <v>1.970763173397657</v>
+        <v>1.970763290966453</v>
       </c>
       <c r="E824" t="n">
-        <v>2.126590803680198</v>
+        <v>2.126590930545122</v>
       </c>
       <c r="F824" t="n">
         <v>10060700</v>
@@ -16912,16 +16912,16 @@
         <v>44988</v>
       </c>
       <c r="B825" t="n">
-        <v>2.493244647979736</v>
+        <v>2.493244409561157</v>
       </c>
       <c r="C825" t="n">
-        <v>2.566575302215361</v>
+        <v>2.566575056784478</v>
       </c>
       <c r="D825" t="n">
-        <v>1.998262294804088</v>
+        <v>1.998262103718605</v>
       </c>
       <c r="E825" t="n">
-        <v>2.025761290142448</v>
+        <v>2.025761096427351</v>
       </c>
       <c r="F825" t="n">
         <v>20771000</v>
@@ -16972,16 +16972,16 @@
         <v>44993</v>
       </c>
       <c r="B828" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C828" t="n">
-        <v>2.90573005973376</v>
+        <v>2.905729816715452</v>
       </c>
       <c r="D828" t="n">
-        <v>2.694904207028261</v>
+        <v>2.694903981642197</v>
       </c>
       <c r="E828" t="n">
-        <v>2.704070538948388</v>
+        <v>2.704070312795705</v>
       </c>
       <c r="F828" t="n">
         <v>7104000</v>
@@ -17132,16 +17132,16 @@
         <v>45005</v>
       </c>
       <c r="B836" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C836" t="n">
-        <v>2.621573197467279</v>
+        <v>2.621573447239113</v>
       </c>
       <c r="D836" t="n">
-        <v>2.484078225780274</v>
+        <v>2.484078462452199</v>
       </c>
       <c r="E836" t="n">
-        <v>2.584907871684078</v>
+        <v>2.584908117962603</v>
       </c>
       <c r="F836" t="n">
         <v>2571800</v>
@@ -17152,16 +17152,16 @@
         <v>45006</v>
       </c>
       <c r="B837" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C837" t="n">
-        <v>2.539076214455076</v>
+        <v>2.539076456366965</v>
       </c>
       <c r="D837" t="n">
-        <v>2.474911894334474</v>
+        <v>2.474912130133071</v>
       </c>
       <c r="E837" t="n">
-        <v>2.520743551563476</v>
+        <v>2.52074379172871</v>
       </c>
       <c r="F837" t="n">
         <v>2400000</v>
@@ -17172,16 +17172,16 @@
         <v>45007</v>
       </c>
       <c r="B838" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C838" t="n">
-        <v>2.621573137405957</v>
+        <v>2.621572885790791</v>
       </c>
       <c r="D838" t="n">
-        <v>2.419913850218447</v>
+        <v>2.419913617958275</v>
       </c>
       <c r="E838" t="n">
-        <v>2.493244500104815</v>
+        <v>2.493244260806463</v>
       </c>
       <c r="F838" t="n">
         <v>4450900</v>
@@ -17192,16 +17192,16 @@
         <v>45008</v>
       </c>
       <c r="B839" t="n">
-        <v>2.383248090744019</v>
+        <v>2.383248329162598</v>
       </c>
       <c r="C839" t="n">
-        <v>2.493244274147426</v>
+        <v>2.493244523569952</v>
       </c>
       <c r="D839" t="n">
-        <v>2.300751117098379</v>
+        <v>2.300751347264015</v>
       </c>
       <c r="E839" t="n">
-        <v>2.484077943742355</v>
+        <v>2.484078192247887</v>
       </c>
       <c r="F839" t="n">
         <v>5291300</v>
@@ -17212,16 +17212,16 @@
         <v>45009</v>
       </c>
       <c r="B840" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C840" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="D840" t="n">
-        <v>2.209087841855346</v>
+        <v>2.209088065430759</v>
       </c>
       <c r="E840" t="n">
-        <v>2.383248121822838</v>
+        <v>2.38324836302451</v>
       </c>
       <c r="F840" t="n">
         <v>8035300</v>
@@ -17232,16 +17232,16 @@
         <v>45012</v>
       </c>
       <c r="B841" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C841" t="n">
-        <v>2.557408877346677</v>
+        <v>2.55740912100522</v>
       </c>
       <c r="D841" t="n">
-        <v>2.36491569844229</v>
+        <v>2.364915923760939</v>
       </c>
       <c r="E841" t="n">
-        <v>2.36491569844229</v>
+        <v>2.364915923760939</v>
       </c>
       <c r="F841" t="n">
         <v>3948600</v>
@@ -17272,16 +17272,16 @@
         <v>45014</v>
       </c>
       <c r="B843" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C843" t="n">
-        <v>2.676571393489365</v>
+        <v>2.676571145737662</v>
       </c>
       <c r="D843" t="n">
-        <v>2.511577209612499</v>
+        <v>2.511576977133168</v>
       </c>
       <c r="E843" t="n">
-        <v>2.658238730674444</v>
+        <v>2.658238484619669</v>
       </c>
       <c r="F843" t="n">
         <v>3021100</v>
@@ -17472,16 +17472,16 @@
         <v>45029</v>
       </c>
       <c r="B853" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C853" t="n">
-        <v>2.960728051254518</v>
+        <v>2.960727803636499</v>
       </c>
       <c r="D853" t="n">
-        <v>2.740735866628893</v>
+        <v>2.740735637409736</v>
       </c>
       <c r="E853" t="n">
-        <v>2.804900190069778</v>
+        <v>2.804899955484291</v>
       </c>
       <c r="F853" t="n">
         <v>4826100</v>
@@ -17512,16 +17512,16 @@
         <v>45033</v>
       </c>
       <c r="B855" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="C855" t="n">
-        <v>2.841565475118138</v>
+        <v>2.841565229570771</v>
       </c>
       <c r="D855" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="E855" t="n">
-        <v>2.777401152639914</v>
+        <v>2.77740091263716</v>
       </c>
       <c r="F855" t="n">
         <v>2017100</v>
@@ -17532,16 +17532,16 @@
         <v>45034</v>
       </c>
       <c r="B856" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C856" t="n">
-        <v>2.823232513937895</v>
+        <v>2.823232766284694</v>
       </c>
       <c r="D856" t="n">
-        <v>2.612406686619929</v>
+        <v>2.612406920122646</v>
       </c>
       <c r="E856" t="n">
-        <v>2.804899852305252</v>
+        <v>2.804900103013436</v>
       </c>
       <c r="F856" t="n">
         <v>3770500</v>
@@ -17572,16 +17572,16 @@
         <v>45036</v>
       </c>
       <c r="B858" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C858" t="n">
-        <v>2.603240801706716</v>
+        <v>2.603240558142417</v>
       </c>
       <c r="D858" t="n">
-        <v>2.419914153978682</v>
+        <v>2.419913927566782</v>
       </c>
       <c r="E858" t="n">
-        <v>2.484078480683494</v>
+        <v>2.484078248268254</v>
       </c>
       <c r="F858" t="n">
         <v>4312900</v>
@@ -17672,16 +17672,16 @@
         <v>45044</v>
       </c>
       <c r="B863" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C863" t="n">
-        <v>2.62157346647952</v>
+        <v>2.62157322119998</v>
       </c>
       <c r="D863" t="n">
-        <v>2.438246818751485</v>
+        <v>2.438246590624346</v>
       </c>
       <c r="E863" t="n">
-        <v>2.46574581591069</v>
+        <v>2.465745585210691</v>
       </c>
       <c r="F863" t="n">
         <v>4247000</v>
@@ -17692,16 +17692,16 @@
         <v>45048</v>
       </c>
       <c r="B864" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C864" t="n">
-        <v>2.749902171081845</v>
+        <v>2.749901926967264</v>
       </c>
       <c r="D864" t="n">
-        <v>2.419914006710763</v>
+        <v>2.419913791889924</v>
       </c>
       <c r="E864" t="n">
-        <v>2.548242652310732</v>
+        <v>2.54824242609789</v>
       </c>
       <c r="F864" t="n">
         <v>8626200</v>
@@ -17732,16 +17732,16 @@
         <v>45050</v>
       </c>
       <c r="B866" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C866" t="n">
-        <v>2.869064767891131</v>
+        <v>2.869064525602105</v>
       </c>
       <c r="D866" t="n">
-        <v>2.704070572725299</v>
+        <v>2.704070344369832</v>
       </c>
       <c r="E866" t="n">
-        <v>2.722403236794548</v>
+        <v>2.72240300689091</v>
       </c>
       <c r="F866" t="n">
         <v>5400200</v>
@@ -17772,16 +17772,16 @@
         <v>45054</v>
       </c>
       <c r="B868" t="n">
-        <v>3.125722169876099</v>
+        <v>3.12572193145752</v>
       </c>
       <c r="C868" t="n">
-        <v>3.199052823489703</v>
+        <v>3.199052579477732</v>
       </c>
       <c r="D868" t="n">
-        <v>3.015725970913106</v>
+        <v>3.015725740884632</v>
       </c>
       <c r="E868" t="n">
-        <v>3.024892302614806</v>
+        <v>3.024892071887158</v>
       </c>
       <c r="F868" t="n">
         <v>6228600</v>
@@ -17892,16 +17892,16 @@
         <v>45062</v>
       </c>
       <c r="B874" t="n">
-        <v>3.602371692657471</v>
+        <v>3.60237193107605</v>
       </c>
       <c r="C874" t="n">
-        <v>3.675702561499818</v>
+        <v>3.675702804771711</v>
       </c>
       <c r="D874" t="n">
-        <v>3.529040823815123</v>
+        <v>3.529041057380388</v>
       </c>
       <c r="E874" t="n">
-        <v>3.657369680382299</v>
+        <v>3.657369922440853</v>
       </c>
       <c r="F874" t="n">
         <v>5715400</v>
@@ -17912,16 +17912,16 @@
         <v>45063</v>
       </c>
       <c r="B875" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="C875" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="D875" t="n">
-        <v>3.62987109842838</v>
+        <v>3.629870877835498</v>
       </c>
       <c r="E875" t="n">
-        <v>3.648203763083666</v>
+        <v>3.64820354137668</v>
       </c>
       <c r="F875" t="n">
         <v>6160500</v>
@@ -17972,16 +17972,16 @@
         <v>45068</v>
       </c>
       <c r="B878" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="C878" t="n">
-        <v>3.996524828619315</v>
+        <v>3.996524585744319</v>
       </c>
       <c r="D878" t="n">
-        <v>3.859029625162064</v>
+        <v>3.859029390642864</v>
       </c>
       <c r="E878" t="n">
-        <v>3.904861505342882</v>
+        <v>3.904861268038407</v>
       </c>
       <c r="F878" t="n">
         <v>3483600</v>
@@ -17992,16 +17992,16 @@
         <v>45069</v>
       </c>
       <c r="B879" t="n">
-        <v>3.941526174545288</v>
+        <v>3.941526412963867</v>
       </c>
       <c r="C879" t="n">
-        <v>4.134019339730554</v>
+        <v>4.134019589792833</v>
       </c>
       <c r="D879" t="n">
-        <v>3.877361640455157</v>
+        <v>3.877361874992493</v>
       </c>
       <c r="E879" t="n">
-        <v>3.886527752705101</v>
+        <v>3.886527987796886</v>
       </c>
       <c r="F879" t="n">
         <v>4348000</v>
@@ -18092,16 +18092,16 @@
         <v>45076</v>
       </c>
       <c r="B884" t="n">
-        <v>3.996524333953857</v>
+        <v>3.996524572372437</v>
       </c>
       <c r="C884" t="n">
-        <v>4.244015494709879</v>
+        <v>4.24401574789291</v>
       </c>
       <c r="D884" t="n">
-        <v>3.969025121832011</v>
+        <v>3.969025358610084</v>
       </c>
       <c r="E884" t="n">
-        <v>4.225682832323698</v>
+        <v>4.225683084413067</v>
       </c>
       <c r="F884" t="n">
         <v>3937000</v>
@@ -18172,16 +18172,16 @@
         <v>45082</v>
       </c>
       <c r="B888" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C888" t="n">
-        <v>4.72066517241793</v>
+        <v>4.72066469090588</v>
       </c>
       <c r="D888" t="n">
-        <v>4.399843360854316</v>
+        <v>4.399842912066377</v>
       </c>
       <c r="E888" t="n">
-        <v>4.64733452258455</v>
+        <v>4.647334048552291</v>
       </c>
       <c r="F888" t="n">
         <v>6247400</v>
@@ -18232,16 +18232,16 @@
         <v>45086</v>
       </c>
       <c r="B891" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="C891" t="n">
-        <v>4.500672836977939</v>
+        <v>4.500673329876966</v>
       </c>
       <c r="D891" t="n">
-        <v>4.289846997768588</v>
+        <v>4.289847467578654</v>
       </c>
       <c r="E891" t="n">
-        <v>4.454841398853827</v>
+        <v>4.454841886733544</v>
       </c>
       <c r="F891" t="n">
         <v>5651200</v>
@@ -18252,16 +18252,16 @@
         <v>45089</v>
       </c>
       <c r="B892" t="n">
-        <v>4.491506099700928</v>
+        <v>4.491506576538086</v>
       </c>
       <c r="C892" t="n">
-        <v>4.647333929244392</v>
+        <v>4.647334422624888</v>
       </c>
       <c r="D892" t="n">
-        <v>4.271513741202773</v>
+        <v>4.271514194684618</v>
       </c>
       <c r="E892" t="n">
-        <v>4.363177478876643</v>
+        <v>4.363177942089895</v>
       </c>
       <c r="F892" t="n">
         <v>6649300</v>
@@ -18272,16 +18272,16 @@
         <v>45090</v>
       </c>
       <c r="B893" t="n">
-        <v>4.289846897125244</v>
+        <v>4.289847373962402</v>
       </c>
       <c r="C893" t="n">
-        <v>4.592336479656477</v>
+        <v>4.592336990116809</v>
       </c>
       <c r="D893" t="n">
-        <v>4.234848910415514</v>
+        <v>4.234849381139381</v>
       </c>
       <c r="E893" t="n">
-        <v>4.537338055861602</v>
+        <v>4.537338560208595</v>
       </c>
       <c r="F893" t="n">
         <v>4358900</v>
@@ -18392,16 +18392,16 @@
         <v>45098</v>
       </c>
       <c r="B899" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C899" t="n">
-        <v>4.986488897178933</v>
+        <v>4.986489382037665</v>
       </c>
       <c r="D899" t="n">
-        <v>4.748163852887355</v>
+        <v>4.748164314572671</v>
       </c>
       <c r="E899" t="n">
-        <v>4.821494938343708</v>
+        <v>4.821495407159335</v>
       </c>
       <c r="F899" t="n">
         <v>4163100</v>
@@ -18412,16 +18412,16 @@
         <v>45099</v>
       </c>
       <c r="B900" t="n">
-        <v>4.766496181488037</v>
+        <v>4.766496658325195</v>
       </c>
       <c r="C900" t="n">
-        <v>4.858159922623858</v>
+        <v>4.858160408630997</v>
       </c>
       <c r="D900" t="n">
-        <v>4.592336122334244</v>
+        <v>4.592336581748543</v>
       </c>
       <c r="E900" t="n">
-        <v>4.757330069625522</v>
+        <v>4.757330545545708</v>
       </c>
       <c r="F900" t="n">
         <v>4737400</v>
@@ -18572,16 +18572,16 @@
         <v>45111</v>
       </c>
       <c r="B908" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C908" t="n">
-        <v>5.087318782005757</v>
+        <v>5.087319262304525</v>
       </c>
       <c r="D908" t="n">
-        <v>4.87649294836929</v>
+        <v>4.876493408763784</v>
       </c>
       <c r="E908" t="n">
-        <v>4.940657047463991</v>
+        <v>4.94065751391628</v>
       </c>
       <c r="F908" t="n">
         <v>2828200</v>
@@ -18612,16 +18612,16 @@
         <v>45113</v>
       </c>
       <c r="B910" t="n">
-        <v>5.087319374084473</v>
+        <v>5.087318897247314</v>
       </c>
       <c r="C910" t="n">
-        <v>5.22481413790957</v>
+        <v>5.224813648184956</v>
       </c>
       <c r="D910" t="n">
-        <v>5.041487494752643</v>
+        <v>5.041487022211331</v>
       </c>
       <c r="E910" t="n">
-        <v>5.206481473593878</v>
+        <v>5.206480985587593</v>
       </c>
       <c r="F910" t="n">
         <v>3192100</v>
@@ -18672,16 +18672,16 @@
         <v>45118</v>
       </c>
       <c r="B913" t="n">
-        <v>5.096485614776611</v>
+        <v>5.096485137939453</v>
       </c>
       <c r="C913" t="n">
-        <v>5.114818279549415</v>
+        <v>5.114817800997017</v>
       </c>
       <c r="D913" t="n">
-        <v>4.858160972730167</v>
+        <v>4.858160518191128</v>
       </c>
       <c r="E913" t="n">
-        <v>5.105652165705616</v>
+        <v>5.105651688010817</v>
       </c>
       <c r="F913" t="n">
         <v>3857700</v>
@@ -18692,16 +18692,16 @@
         <v>45119</v>
       </c>
       <c r="B914" t="n">
-        <v>5.325643062591553</v>
+        <v>5.325643539428711</v>
       </c>
       <c r="C914" t="n">
-        <v>5.573134205359659</v>
+        <v>5.573134704356201</v>
       </c>
       <c r="D914" t="n">
-        <v>5.178981774161598</v>
+        <v>5.178982237867281</v>
       </c>
       <c r="E914" t="n">
-        <v>5.178981774161598</v>
+        <v>5.178982237867281</v>
       </c>
       <c r="F914" t="n">
         <v>7685700</v>
@@ -18712,16 +18712,16 @@
         <v>45120</v>
       </c>
       <c r="B915" t="n">
-        <v>5.096485614776611</v>
+        <v>5.096485137939453</v>
       </c>
       <c r="C915" t="n">
-        <v>5.453972796388881</v>
+        <v>5.453972286104523</v>
       </c>
       <c r="D915" t="n">
-        <v>4.99565573998359</v>
+        <v>4.995655272580271</v>
       </c>
       <c r="E915" t="n">
-        <v>5.334810693908262</v>
+        <v>5.334810194772943</v>
       </c>
       <c r="F915" t="n">
         <v>4692200</v>
@@ -18732,16 +18732,16 @@
         <v>45121</v>
       </c>
       <c r="B916" t="n">
-        <v>4.482340335845947</v>
+        <v>4.482339859008789</v>
       </c>
       <c r="C916" t="n">
-        <v>4.903992029460144</v>
+        <v>4.903991507767135</v>
       </c>
       <c r="D916" t="n">
-        <v>4.381510906088113</v>
+        <v>4.381510439977321</v>
       </c>
       <c r="E916" t="n">
-        <v>4.858160589684357</v>
+        <v>4.858160072866955</v>
       </c>
       <c r="F916" t="n">
         <v>15771400</v>
@@ -18772,16 +18772,16 @@
         <v>45125</v>
       </c>
       <c r="B918" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C918" t="n">
-        <v>5.041486987624404</v>
+        <v>5.041486503749065</v>
       </c>
       <c r="D918" t="n">
-        <v>4.711498626050601</v>
+        <v>4.711498173847115</v>
       </c>
       <c r="E918" t="n">
-        <v>4.720665175828972</v>
+        <v>4.720664722745693</v>
       </c>
       <c r="F918" t="n">
         <v>5384000</v>
@@ -18812,16 +18812,16 @@
         <v>45127</v>
       </c>
       <c r="B920" t="n">
-        <v>4.876492977142334</v>
+        <v>4.876493453979492</v>
       </c>
       <c r="C920" t="n">
-        <v>5.004821613174064</v>
+        <v>5.004822102559555</v>
       </c>
       <c r="D920" t="n">
-        <v>4.784829228605952</v>
+        <v>4.784829696479972</v>
       </c>
       <c r="E920" t="n">
-        <v>4.958989738905873</v>
+        <v>4.958990223809796</v>
       </c>
       <c r="F920" t="n">
         <v>2200400</v>
@@ -18832,16 +18832,16 @@
         <v>45128</v>
       </c>
       <c r="B921" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C921" t="n">
-        <v>5.169815688182035</v>
+        <v>5.169815198316529</v>
       </c>
       <c r="D921" t="n">
-        <v>4.858160422351643</v>
+        <v>4.85815996201701</v>
       </c>
       <c r="E921" t="n">
-        <v>4.858160422351643</v>
+        <v>4.85815996201701</v>
       </c>
       <c r="F921" t="n">
         <v>3946200</v>
@@ -18852,16 +18852,16 @@
         <v>45131</v>
       </c>
       <c r="B922" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C922" t="n">
-        <v>5.105651587288944</v>
+        <v>5.105651103503303</v>
       </c>
       <c r="D922" t="n">
-        <v>4.885659197852923</v>
+        <v>4.885658734912646</v>
       </c>
       <c r="E922" t="n">
-        <v>5.068986261897133</v>
+        <v>5.068985781585712</v>
       </c>
       <c r="F922" t="n">
         <v>2320000</v>
@@ -18872,16 +18872,16 @@
         <v>45132</v>
       </c>
       <c r="B923" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C923" t="n">
-        <v>5.270645551552092</v>
+        <v>5.270645052132461</v>
       </c>
       <c r="D923" t="n">
-        <v>4.995655174028355</v>
+        <v>4.995654700665417</v>
       </c>
       <c r="E923" t="n">
-        <v>5.096485037398413</v>
+        <v>5.096484554481348</v>
       </c>
       <c r="F923" t="n">
         <v>3865600</v>
@@ -18952,16 +18952,16 @@
         <v>45138</v>
       </c>
       <c r="B927" t="n">
-        <v>5.224813938140869</v>
+        <v>5.224813461303711</v>
       </c>
       <c r="C927" t="n">
-        <v>5.389808347758803</v>
+        <v>5.389807855863602</v>
       </c>
       <c r="D927" t="n">
-        <v>5.087319179572829</v>
+        <v>5.087318715283986</v>
       </c>
       <c r="E927" t="n">
-        <v>5.087319179572829</v>
+        <v>5.087318715283986</v>
       </c>
       <c r="F927" t="n">
         <v>3571100</v>
@@ -18972,16 +18972,16 @@
         <v>45139</v>
       </c>
       <c r="B928" t="n">
-        <v>5.417306900024414</v>
+        <v>5.417306423187256</v>
       </c>
       <c r="C928" t="n">
-        <v>5.426473449994312</v>
+        <v>5.426472972350305</v>
       </c>
       <c r="D928" t="n">
-        <v>4.995655217282615</v>
+        <v>4.99565477755969</v>
       </c>
       <c r="E928" t="n">
-        <v>5.17898228291414</v>
+        <v>5.17898182705457</v>
       </c>
       <c r="F928" t="n">
         <v>5677300</v>
@@ -18992,16 +18992,16 @@
         <v>45140</v>
       </c>
       <c r="B929" t="n">
-        <v>5.33480978012085</v>
+        <v>5.334810256958008</v>
       </c>
       <c r="C929" t="n">
-        <v>5.518136396447286</v>
+        <v>5.518136889670584</v>
       </c>
       <c r="D929" t="n">
-        <v>5.215647260966101</v>
+        <v>5.215647727152248</v>
       </c>
       <c r="E929" t="n">
-        <v>5.472304523823111</v>
+        <v>5.472305012949855</v>
       </c>
       <c r="F929" t="n">
         <v>6874400</v>
@@ -19032,16 +19032,16 @@
         <v>45142</v>
       </c>
       <c r="B931" t="n">
-        <v>5.628132343292236</v>
+        <v>5.628132820129395</v>
       </c>
       <c r="C931" t="n">
-        <v>5.655631554171628</v>
+        <v>5.655632033338626</v>
       </c>
       <c r="D931" t="n">
-        <v>5.316477096808192</v>
+        <v>5.31647754724071</v>
       </c>
       <c r="E931" t="n">
-        <v>5.32564320904457</v>
+        <v>5.325643660253677</v>
       </c>
       <c r="F931" t="n">
         <v>4666200</v>
@@ -19092,16 +19092,16 @@
         <v>45147</v>
       </c>
       <c r="B934" t="n">
-        <v>5.224813938140869</v>
+        <v>5.224813461303711</v>
       </c>
       <c r="C934" t="n">
-        <v>5.45397245186784</v>
+        <v>5.453971954116771</v>
       </c>
       <c r="D934" t="n">
-        <v>5.197315161261333</v>
+        <v>5.197314686933821</v>
       </c>
       <c r="E934" t="n">
-        <v>5.261479265370371</v>
+        <v>5.26147878518699</v>
       </c>
       <c r="F934" t="n">
         <v>3345000</v>
@@ -19152,16 +19152,16 @@
         <v>45152</v>
       </c>
       <c r="B937" t="n">
-        <v>6.068117141723633</v>
+        <v>6.068116664886475</v>
       </c>
       <c r="C937" t="n">
-        <v>6.28810953504867</v>
+        <v>6.288109040924345</v>
       </c>
       <c r="D937" t="n">
-        <v>5.985620376676263</v>
+        <v>5.985619906321761</v>
       </c>
       <c r="E937" t="n">
-        <v>6.14144779380359</v>
+        <v>6.141447311204055</v>
       </c>
       <c r="F937" t="n">
         <v>5683800</v>
@@ -19232,16 +19232,16 @@
         <v>45156</v>
       </c>
       <c r="B941" t="n">
-        <v>5.710629940032959</v>
+        <v>5.710629463195801</v>
       </c>
       <c r="C941" t="n">
-        <v>5.838958579953599</v>
+        <v>5.838958092401009</v>
       </c>
       <c r="D941" t="n">
-        <v>5.334810133151363</v>
+        <v>5.33480968769513</v>
       </c>
       <c r="E941" t="n">
-        <v>5.609800075838448</v>
+        <v>5.609799607420576</v>
       </c>
       <c r="F941" t="n">
         <v>5405200</v>
@@ -19252,16 +19252,16 @@
         <v>45159</v>
       </c>
       <c r="B942" t="n">
-        <v>5.490636825561523</v>
+        <v>5.490637302398682</v>
       </c>
       <c r="C942" t="n">
-        <v>5.701462639060511</v>
+        <v>5.701463134206945</v>
       </c>
       <c r="D942" t="n">
-        <v>5.463138053457582</v>
+        <v>5.463138527906596</v>
       </c>
       <c r="E942" t="n">
-        <v>5.67396386695657</v>
+        <v>5.673964359714859</v>
       </c>
       <c r="F942" t="n">
         <v>3510600</v>
@@ -19272,16 +19272,16 @@
         <v>45160</v>
       </c>
       <c r="B943" t="n">
-        <v>5.628132343292236</v>
+        <v>5.628132820129395</v>
       </c>
       <c r="C943" t="n">
-        <v>5.646465004850121</v>
+        <v>5.646465483240493</v>
       </c>
       <c r="D943" t="n">
-        <v>5.408140404597616</v>
+        <v>5.408140862796206</v>
       </c>
       <c r="E943" t="n">
-        <v>5.563968246382204</v>
+        <v>5.563968717783131</v>
       </c>
       <c r="F943" t="n">
         <v>4158800</v>
@@ -19412,16 +19412,16 @@
         <v>45169</v>
       </c>
       <c r="B950" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C950" t="n">
-        <v>5.03232033386837</v>
+        <v>5.032320823183499</v>
       </c>
       <c r="D950" t="n">
-        <v>4.858160262529314</v>
+        <v>4.858160734910076</v>
       </c>
       <c r="E950" t="n">
-        <v>5.03232033386837</v>
+        <v>5.032320823183499</v>
       </c>
       <c r="F950" t="n">
         <v>3681000</v>
@@ -19432,16 +19432,16 @@
         <v>45170</v>
       </c>
       <c r="B951" t="n">
-        <v>5.151483058929443</v>
+        <v>5.151482582092285</v>
       </c>
       <c r="C951" t="n">
-        <v>5.169815721744364</v>
+        <v>5.169815243210278</v>
       </c>
       <c r="D951" t="n">
-        <v>4.876493116705634</v>
+        <v>4.876492665322393</v>
       </c>
       <c r="E951" t="n">
-        <v>4.949823767965317</v>
+        <v>4.949823309794364</v>
       </c>
       <c r="F951" t="n">
         <v>4962000</v>
@@ -19472,16 +19472,16 @@
         <v>45174</v>
       </c>
       <c r="B953" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C953" t="n">
-        <v>5.032320437846034</v>
+        <v>5.032319954850488</v>
       </c>
       <c r="D953" t="n">
-        <v>4.858160362908486</v>
+        <v>4.858159896628598</v>
       </c>
       <c r="E953" t="n">
-        <v>4.99565511290285</v>
+        <v>4.995654633426395</v>
       </c>
       <c r="F953" t="n">
         <v>3096400</v>
@@ -19492,16 +19492,16 @@
         <v>45175</v>
       </c>
       <c r="B954" t="n">
-        <v>4.986489295959473</v>
+        <v>4.986488819122314</v>
       </c>
       <c r="C954" t="n">
-        <v>5.105651827634952</v>
+        <v>5.105651339402779</v>
       </c>
       <c r="D954" t="n">
-        <v>4.94982396884166</v>
+        <v>4.949823495510654</v>
       </c>
       <c r="E954" t="n">
-        <v>4.94982396884166</v>
+        <v>4.949823495510654</v>
       </c>
       <c r="F954" t="n">
         <v>4361600</v>
@@ -19512,16 +19512,16 @@
         <v>45177</v>
       </c>
       <c r="B955" t="n">
-        <v>4.876492977142334</v>
+        <v>4.876493453979492</v>
       </c>
       <c r="C955" t="n">
-        <v>5.004821613174064</v>
+        <v>5.004822102559555</v>
       </c>
       <c r="D955" t="n">
-        <v>4.867326427454637</v>
+        <v>4.867326903395464</v>
       </c>
       <c r="E955" t="n">
-        <v>4.97732240119612</v>
+        <v>4.977322887892662</v>
       </c>
       <c r="F955" t="n">
         <v>2168000</v>
@@ -19552,16 +19552,16 @@
         <v>45181</v>
       </c>
       <c r="B957" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C957" t="n">
-        <v>5.105651444187835</v>
+        <v>5.105651926217408</v>
       </c>
       <c r="D957" t="n">
-        <v>4.913158272733446</v>
+        <v>4.913158736589549</v>
       </c>
       <c r="E957" t="n">
-        <v>4.913158272733446</v>
+        <v>4.913158736589549</v>
       </c>
       <c r="F957" t="n">
         <v>2356100</v>
@@ -19672,16 +19672,16 @@
         <v>45189</v>
       </c>
       <c r="B963" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C963" t="n">
-        <v>5.114817637510772</v>
+        <v>5.114817146597253</v>
       </c>
       <c r="D963" t="n">
-        <v>4.711498626050601</v>
+        <v>4.711498173847115</v>
       </c>
       <c r="E963" t="n">
-        <v>4.720665175828972</v>
+        <v>4.720664722745693</v>
       </c>
       <c r="F963" t="n">
         <v>5388800</v>
@@ -19712,16 +19712,16 @@
         <v>45191</v>
       </c>
       <c r="B965" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C965" t="n">
-        <v>4.86732647208469</v>
+        <v>4.867325975613057</v>
       </c>
       <c r="D965" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="E965" t="n">
-        <v>4.812328484709655</v>
+        <v>4.812327993847866</v>
       </c>
       <c r="F965" t="n">
         <v>2426200</v>
@@ -19752,16 +19752,16 @@
         <v>45195</v>
       </c>
       <c r="B967" t="n">
-        <v>4.491506099700928</v>
+        <v>4.491506576538086</v>
       </c>
       <c r="C967" t="n">
-        <v>4.784828661585008</v>
+        <v>4.784829169562522</v>
       </c>
       <c r="D967" t="n">
-        <v>4.418175459229907</v>
+        <v>4.418175928281977</v>
       </c>
       <c r="E967" t="n">
-        <v>4.574002851688278</v>
+        <v>4.574003337283638</v>
       </c>
       <c r="F967" t="n">
         <v>4192900</v>
@@ -19852,16 +19852,16 @@
         <v>45202</v>
       </c>
       <c r="B972" t="n">
-        <v>4.317346096038818</v>
+        <v>4.31734561920166</v>
       </c>
       <c r="C972" t="n">
-        <v>4.674833227119539</v>
+        <v>4.674832710799063</v>
       </c>
       <c r="D972" t="n">
-        <v>4.308179546405524</v>
+        <v>4.308179070580783</v>
       </c>
       <c r="E972" t="n">
-        <v>4.619835240575209</v>
+        <v>4.619834730329086</v>
       </c>
       <c r="F972" t="n">
         <v>3808300</v>
@@ -19892,16 +19892,16 @@
         <v>45204</v>
       </c>
       <c r="B974" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="C974" t="n">
-        <v>4.79399597660141</v>
+        <v>4.793995472791623</v>
       </c>
       <c r="D974" t="n">
-        <v>4.528172143854223</v>
+        <v>4.528171667980348</v>
       </c>
       <c r="E974" t="n">
-        <v>4.67483344824297</v>
+        <v>4.674832956956192</v>
       </c>
       <c r="F974" t="n">
         <v>3401000</v>
@@ -20032,16 +20032,16 @@
         <v>45216</v>
       </c>
       <c r="B981" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C981" t="n">
-        <v>4.812328484709655</v>
+        <v>4.812327993847866</v>
       </c>
       <c r="D981" t="n">
-        <v>4.601502647896112</v>
+        <v>4.601502178538746</v>
       </c>
       <c r="E981" t="n">
-        <v>4.656500635271147</v>
+        <v>4.656500160303938</v>
       </c>
       <c r="F981" t="n">
         <v>2762000</v>
@@ -20052,16 +20052,16 @@
         <v>45217</v>
       </c>
       <c r="B982" t="n">
-        <v>4.509839534759521</v>
+        <v>4.509839057922363</v>
       </c>
       <c r="C982" t="n">
-        <v>4.674833504170784</v>
+        <v>4.67483300988838</v>
       </c>
       <c r="D982" t="n">
-        <v>4.418176218419932</v>
+        <v>4.418175751274577</v>
       </c>
       <c r="E982" t="n">
-        <v>4.647334727811492</v>
+        <v>4.647334236436606</v>
       </c>
       <c r="F982" t="n">
         <v>3515800</v>
@@ -20132,16 +20132,16 @@
         <v>45223</v>
       </c>
       <c r="B986" t="n">
-        <v>4.711498260498047</v>
+        <v>4.711498737335205</v>
       </c>
       <c r="C986" t="n">
-        <v>4.793995453762048</v>
+        <v>4.79399593894851</v>
       </c>
       <c r="D986" t="n">
-        <v>4.619834955251998</v>
+        <v>4.619835422812178</v>
       </c>
       <c r="E986" t="n">
-        <v>4.683999487466791</v>
+        <v>4.683999961520877</v>
       </c>
       <c r="F986" t="n">
         <v>2628000</v>
@@ -20172,16 +20172,16 @@
         <v>45225</v>
       </c>
       <c r="B988" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C988" t="n">
-        <v>4.858160878073153</v>
+        <v>4.858160394853837</v>
       </c>
       <c r="D988" t="n">
-        <v>4.60150313916945</v>
+        <v>4.601502681478721</v>
       </c>
       <c r="E988" t="n">
-        <v>4.60150313916945</v>
+        <v>4.601502681478721</v>
       </c>
       <c r="F988" t="n">
         <v>4908400</v>
@@ -20192,16 +20192,16 @@
         <v>45226</v>
       </c>
       <c r="B989" t="n">
-        <v>4.766496181488037</v>
+        <v>4.766496658325195</v>
       </c>
       <c r="C989" t="n">
-        <v>4.977321999347226</v>
+        <v>4.977322497275261</v>
       </c>
       <c r="D989" t="n">
-        <v>4.720664748005237</v>
+        <v>4.720665220257449</v>
       </c>
       <c r="E989" t="n">
-        <v>4.803161503108321</v>
+        <v>4.803161983613454</v>
       </c>
       <c r="F989" t="n">
         <v>2912800</v>
@@ -20252,16 +20252,16 @@
         <v>45231</v>
       </c>
       <c r="B992" t="n">
-        <v>4.803162097930908</v>
+        <v>4.80316162109375</v>
       </c>
       <c r="C992" t="n">
-        <v>4.848993974174629</v>
+        <v>4.848993492787479</v>
       </c>
       <c r="D992" t="n">
-        <v>4.656500793287267</v>
+        <v>4.656500331010008</v>
       </c>
       <c r="E992" t="n">
-        <v>4.729831445609087</v>
+        <v>4.729830976051879</v>
       </c>
       <c r="F992" t="n">
         <v>2720700</v>
@@ -20332,16 +20332,16 @@
         <v>45238</v>
       </c>
       <c r="B996" t="n">
-        <v>5.518136978149414</v>
+        <v>5.518136501312256</v>
       </c>
       <c r="C996" t="n">
-        <v>5.573134968845035</v>
+        <v>5.573134487255351</v>
       </c>
       <c r="D996" t="n">
-        <v>5.316477678932137</v>
+        <v>5.316477219520905</v>
       </c>
       <c r="E996" t="n">
-        <v>5.316477678932137</v>
+        <v>5.316477219520905</v>
       </c>
       <c r="F996" t="n">
         <v>4022900</v>
@@ -20352,16 +20352,16 @@
         <v>45239</v>
       </c>
       <c r="B997" t="n">
-        <v>5.618966102600098</v>
+        <v>5.618966579437256</v>
       </c>
       <c r="C997" t="n">
-        <v>5.728962069432778</v>
+        <v>5.728962555604424</v>
       </c>
       <c r="D997" t="n">
-        <v>5.417306392988397</v>
+        <v>5.417306852712293</v>
       </c>
       <c r="E997" t="n">
-        <v>5.582300780322537</v>
+        <v>5.5823012540482</v>
       </c>
       <c r="F997" t="n">
         <v>3100500</v>
@@ -20392,16 +20392,16 @@
         <v>45243</v>
       </c>
       <c r="B999" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C999" t="n">
-        <v>7.140579120035365</v>
+        <v>7.140578620094379</v>
       </c>
       <c r="D999" t="n">
-        <v>6.544766908003258</v>
+        <v>6.544766449777509</v>
       </c>
       <c r="E999" t="n">
-        <v>6.608931448004774</v>
+        <v>6.608930985286603</v>
       </c>
       <c r="F999" t="n">
         <v>8835300</v>
@@ -20432,16 +20432,16 @@
         <v>45246</v>
       </c>
       <c r="B1001" t="n">
-        <v>7.360570907592773</v>
+        <v>7.360570430755615</v>
       </c>
       <c r="C1001" t="n">
-        <v>7.562230635986777</v>
+        <v>7.562230146085571</v>
       </c>
       <c r="D1001" t="n">
-        <v>6.627263956657273</v>
+        <v>6.627263527325669</v>
       </c>
       <c r="E1001" t="n">
-        <v>6.78309180939305</v>
+        <v>6.783091369966508</v>
       </c>
       <c r="F1001" t="n">
         <v>9976600</v>
@@ -20452,16 +20452,16 @@
         <v>45247</v>
       </c>
       <c r="B1002" t="n">
-        <v>7.635560989379883</v>
+        <v>7.635561466217041</v>
       </c>
       <c r="C1002" t="n">
-        <v>7.699725088295085</v>
+        <v>7.699725569139261</v>
       </c>
       <c r="D1002" t="n">
-        <v>7.333071845679237</v>
+        <v>7.333072303626092</v>
       </c>
       <c r="E1002" t="n">
-        <v>7.415569043810375</v>
+        <v>7.41556950690914</v>
       </c>
       <c r="F1002" t="n">
         <v>5823800</v>
@@ -20492,16 +20492,16 @@
         <v>45251</v>
       </c>
       <c r="B1004" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1004" t="n">
-        <v>7.543897678065316</v>
+        <v>7.543897193575265</v>
       </c>
       <c r="D1004" t="n">
-        <v>7.287240393386257</v>
+        <v>7.287239925379449</v>
       </c>
       <c r="E1004" t="n">
-        <v>7.543897678065316</v>
+        <v>7.543897193575265</v>
       </c>
       <c r="F1004" t="n">
         <v>4025000</v>
@@ -20532,16 +20532,16 @@
         <v>45253</v>
       </c>
       <c r="B1006" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="C1006" t="n">
-        <v>7.323906062493096</v>
+        <v>7.32390557025422</v>
       </c>
       <c r="D1006" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="E1006" t="n">
-        <v>7.314739949011068</v>
+        <v>7.314739457388246</v>
       </c>
       <c r="F1006" t="n">
         <v>2414400</v>
@@ -20612,16 +20612,16 @@
         <v>45259</v>
       </c>
       <c r="B1010" t="n">
-        <v>7.44306755065918</v>
+        <v>7.443068027496338</v>
       </c>
       <c r="C1010" t="n">
-        <v>7.763889782032437</v>
+        <v>7.763890279422943</v>
       </c>
       <c r="D1010" t="n">
-        <v>7.168077628591552</v>
+        <v>7.16807808781159</v>
       </c>
       <c r="E1010" t="n">
-        <v>7.213909063726926</v>
+        <v>7.213909525883136</v>
       </c>
       <c r="F1010" t="n">
         <v>6571400</v>
@@ -20752,16 +20752,16 @@
         <v>45268</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.718058586120605</v>
+        <v>7.718058109283447</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.800555788512423</v>
+        <v>7.800555306578421</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.580563831581132</v>
+        <v>7.580563363238674</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.699725485957833</v>
+        <v>7.69972501025333</v>
       </c>
       <c r="F1017" t="n">
         <v>1787800</v>
@@ -20772,16 +20772,16 @@
         <v>45271</v>
       </c>
       <c r="B1018" t="n">
-        <v>7.672226905822754</v>
+        <v>7.672226428985596</v>
       </c>
       <c r="C1018" t="n">
-        <v>7.892218868372355</v>
+        <v>7.892218377862459</v>
       </c>
       <c r="D1018" t="n">
-        <v>7.626395028415665</v>
+        <v>7.626394554427008</v>
       </c>
       <c r="E1018" t="n">
-        <v>7.699725682598865</v>
+        <v>7.699725204052629</v>
       </c>
       <c r="F1018" t="n">
         <v>2800600</v>
@@ -20872,16 +20872,16 @@
         <v>45278</v>
       </c>
       <c r="B1023" t="n">
-        <v>7.44306755065918</v>
+        <v>7.443068027496338</v>
       </c>
       <c r="C1023" t="n">
-        <v>7.681392586869585</v>
+        <v>7.681393078974941</v>
       </c>
       <c r="D1023" t="n">
-        <v>7.415568776994981</v>
+        <v>7.415569252070441</v>
       </c>
       <c r="E1023" t="n">
-        <v>7.516398196543881</v>
+        <v>7.516398678078938</v>
       </c>
       <c r="F1023" t="n">
         <v>2448800</v>
@@ -20932,16 +20932,16 @@
         <v>45281</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.498065948486328</v>
+        <v>7.498066425323486</v>
       </c>
       <c r="C1026" t="n">
-        <v>7.653893789041931</v>
+        <v>7.653894275788911</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.406402204334709</v>
+        <v>7.40640267534254</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.461400625659731</v>
+        <v>7.461401100165169</v>
       </c>
       <c r="F1026" t="n">
         <v>2110700</v>
@@ -20972,16 +20972,16 @@
         <v>45286</v>
       </c>
       <c r="B1028" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C1028" t="n">
-        <v>7.433901462933017</v>
+        <v>7.433901956821806</v>
       </c>
       <c r="D1028" t="n">
-        <v>7.168078073639243</v>
+        <v>7.168078549867428</v>
       </c>
       <c r="E1028" t="n">
-        <v>7.37890391218996</v>
+        <v>7.378904402424857</v>
       </c>
       <c r="F1028" t="n">
         <v>1748700</v>
@@ -20992,16 +20992,16 @@
         <v>45287</v>
       </c>
       <c r="B1029" t="n">
-        <v>7.232242107391357</v>
+        <v>7.232241630554199</v>
       </c>
       <c r="C1029" t="n">
-        <v>7.333071969353814</v>
+        <v>7.333071485868728</v>
       </c>
       <c r="D1029" t="n">
-        <v>7.140578795191465</v>
+        <v>7.140578324397864</v>
       </c>
       <c r="E1029" t="n">
-        <v>7.195576782511401</v>
+        <v>7.195576308091665</v>
       </c>
       <c r="F1029" t="n">
         <v>1937700</v>
@@ -21012,16 +21012,16 @@
         <v>45288</v>
       </c>
       <c r="B1030" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C1030" t="n">
-        <v>7.31473937451447</v>
+        <v>7.314739860486446</v>
       </c>
       <c r="D1030" t="n">
-        <v>7.103913535963753</v>
+        <v>7.103914007929016</v>
       </c>
       <c r="E1030" t="n">
-        <v>7.223076061467453</v>
+        <v>7.22307654134956</v>
       </c>
       <c r="F1030" t="n">
         <v>1438100</v>
@@ -21032,16 +21032,16 @@
         <v>45293</v>
       </c>
       <c r="B1031" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1031" t="n">
-        <v>7.204743074499178</v>
+        <v>7.204743572895473</v>
       </c>
       <c r="D1031" t="n">
-        <v>6.828922852298171</v>
+        <v>6.828923324696675</v>
       </c>
       <c r="E1031" t="n">
-        <v>7.195576525064578</v>
+        <v>7.195577022826767</v>
       </c>
       <c r="F1031" t="n">
         <v>2422400</v>
@@ -21052,16 +21052,16 @@
         <v>45294</v>
       </c>
       <c r="B1032" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1032" t="n">
-        <v>7.03974868135747</v>
+        <v>7.039749168340091</v>
       </c>
       <c r="D1032" t="n">
-        <v>6.764758754596515</v>
+        <v>6.764759222556394</v>
       </c>
       <c r="E1032" t="n">
-        <v>6.874754725300897</v>
+        <v>6.874755200869873</v>
       </c>
       <c r="F1032" t="n">
         <v>2218000</v>
@@ -21172,16 +21172,16 @@
         <v>45302</v>
       </c>
       <c r="B1038" t="n">
-        <v>6.847255706787109</v>
+        <v>6.847256183624268</v>
       </c>
       <c r="C1038" t="n">
-        <v>7.213909389872389</v>
+        <v>7.213909892243003</v>
       </c>
       <c r="D1038" t="n">
-        <v>6.819756931879673</v>
+        <v>6.819757406801839</v>
       </c>
       <c r="E1038" t="n">
-        <v>6.993917442272309</v>
+        <v>6.993917929322868</v>
       </c>
       <c r="F1038" t="n">
         <v>2188900</v>
@@ -21192,16 +21192,16 @@
         <v>45303</v>
       </c>
       <c r="B1039" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C1039" t="n">
-        <v>7.085581130213425</v>
+        <v>7.085580634123072</v>
       </c>
       <c r="D1039" t="n">
-        <v>6.792258080744574</v>
+        <v>6.792257605190961</v>
       </c>
       <c r="E1039" t="n">
-        <v>6.83808995747211</v>
+        <v>6.83808947870962</v>
       </c>
       <c r="F1039" t="n">
         <v>1935400</v>
@@ -21212,16 +21212,16 @@
         <v>45306</v>
       </c>
       <c r="B1040" t="n">
-        <v>6.929753303527832</v>
+        <v>6.929752826690674</v>
       </c>
       <c r="C1040" t="n">
-        <v>7.003083956937887</v>
+        <v>7.003083475054838</v>
       </c>
       <c r="D1040" t="n">
-        <v>6.700594793078822</v>
+        <v>6.700594332010089</v>
       </c>
       <c r="E1040" t="n">
-        <v>6.746426670002693</v>
+        <v>6.746426205780263</v>
       </c>
       <c r="F1040" t="n">
         <v>1399400</v>
@@ -21232,16 +21232,16 @@
         <v>45307</v>
       </c>
       <c r="B1041" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C1041" t="n">
-        <v>6.911420074576932</v>
+        <v>6.911420565075185</v>
       </c>
       <c r="D1041" t="n">
-        <v>6.654762808645371</v>
+        <v>6.654763280928852</v>
       </c>
       <c r="E1041" t="n">
-        <v>6.911420074576932</v>
+        <v>6.911420565075185</v>
       </c>
       <c r="F1041" t="n">
         <v>2256200</v>
@@ -21332,16 +21332,16 @@
         <v>45314</v>
       </c>
       <c r="B1046" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C1046" t="n">
-        <v>6.801424103463406</v>
+        <v>6.801424586155328</v>
       </c>
       <c r="D1046" t="n">
-        <v>6.526433738594455</v>
+        <v>6.526434201770518</v>
       </c>
       <c r="E1046" t="n">
-        <v>6.608930935472167</v>
+        <v>6.608931404502994</v>
       </c>
       <c r="F1046" t="n">
         <v>2038100</v>
@@ -21352,16 +21352,16 @@
         <v>45315</v>
       </c>
       <c r="B1047" t="n">
-        <v>6.874755382537842</v>
+        <v>6.874754905700684</v>
       </c>
       <c r="C1047" t="n">
-        <v>6.957252586995552</v>
+        <v>6.957252104436338</v>
       </c>
       <c r="D1047" t="n">
-        <v>6.755592851006743</v>
+        <v>6.75559238243477</v>
       </c>
       <c r="E1047" t="n">
-        <v>6.801424728391066</v>
+        <v>6.801424256640167</v>
       </c>
       <c r="F1047" t="n">
         <v>1933800</v>
@@ -21372,16 +21372,16 @@
         <v>45316</v>
       </c>
       <c r="B1048" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1048" t="n">
-        <v>7.149745089146987</v>
+        <v>7.149745583738733</v>
       </c>
       <c r="D1048" t="n">
-        <v>6.83808940173277</v>
+        <v>6.83808987476538</v>
       </c>
       <c r="E1048" t="n">
-        <v>6.883921274735496</v>
+        <v>6.883921750938578</v>
       </c>
       <c r="F1048" t="n">
         <v>2213100</v>
@@ -21392,16 +21392,16 @@
         <v>45317</v>
       </c>
       <c r="B1049" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="C1049" t="n">
-        <v>7.17724475009915</v>
+        <v>7.177244267717364</v>
       </c>
       <c r="D1049" t="n">
-        <v>6.718927711782881</v>
+        <v>6.718927260204529</v>
       </c>
       <c r="E1049" t="n">
-        <v>6.957252781508231</v>
+        <v>6.957252313912079</v>
       </c>
       <c r="F1049" t="n">
         <v>2582000</v>
@@ -21572,16 +21572,16 @@
         <v>45330</v>
       </c>
       <c r="B1058" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1058" t="n">
-        <v>7.617229205001097</v>
+        <v>7.617228715801493</v>
       </c>
       <c r="D1058" t="n">
-        <v>7.103913761472643</v>
+        <v>7.103913305239581</v>
       </c>
       <c r="E1058" t="n">
-        <v>7.131412974802268</v>
+        <v>7.13141251680313</v>
       </c>
       <c r="F1058" t="n">
         <v>7472200</v>
@@ -21652,16 +21652,16 @@
         <v>45338</v>
       </c>
       <c r="B1062" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1062" t="n">
-        <v>7.443068249055412</v>
+        <v>7.443067771040908</v>
       </c>
       <c r="D1062" t="n">
-        <v>7.158911751046727</v>
+        <v>7.158911291281541</v>
       </c>
       <c r="E1062" t="n">
-        <v>7.333072269907244</v>
+        <v>7.333071798956986</v>
       </c>
       <c r="F1062" t="n">
         <v>2565400</v>
@@ -21692,16 +21692,16 @@
         <v>45342</v>
       </c>
       <c r="B1064" t="n">
-        <v>7.204743385314941</v>
+        <v>7.2047438621521</v>
       </c>
       <c r="C1064" t="n">
-        <v>7.314739360764598</v>
+        <v>7.314739844881705</v>
       </c>
       <c r="D1064" t="n">
-        <v>6.920586896860753</v>
+        <v>6.92058735489136</v>
       </c>
       <c r="E1064" t="n">
-        <v>7.241408710464827</v>
+        <v>7.241409189728635</v>
       </c>
       <c r="F1064" t="n">
         <v>5572100</v>
@@ -21752,16 +21752,16 @@
         <v>45345</v>
       </c>
       <c r="B1067" t="n">
-        <v>7.91055154800415</v>
+        <v>7.910551071166992</v>
       </c>
       <c r="C1067" t="n">
-        <v>8.249706024094255</v>
+        <v>8.249705526813331</v>
       </c>
       <c r="D1067" t="n">
-        <v>7.754723697615412</v>
+        <v>7.754723230171342</v>
       </c>
       <c r="E1067" t="n">
-        <v>8.075545948220533</v>
+        <v>8.07554546143774</v>
       </c>
       <c r="F1067" t="n">
         <v>3191100</v>
@@ -21772,16 +21772,16 @@
         <v>45348</v>
       </c>
       <c r="B1068" t="n">
-        <v>8.084711074829102</v>
+        <v>8.084712028503418</v>
       </c>
       <c r="C1068" t="n">
-        <v>8.11221072244448</v>
+        <v>8.112211679362662</v>
       </c>
       <c r="D1068" t="n">
-        <v>7.828053816277292</v>
+        <v>7.828054739676261</v>
       </c>
       <c r="E1068" t="n">
-        <v>7.910551010782934</v>
+        <v>7.910551943913292</v>
       </c>
       <c r="F1068" t="n">
         <v>1473000</v>
@@ -21892,16 +21892,16 @@
         <v>45356</v>
       </c>
       <c r="B1074" t="n">
-        <v>8.790520668029785</v>
+        <v>8.790519714355469</v>
       </c>
       <c r="C1074" t="n">
-        <v>8.90968319927654</v>
+        <v>8.909682232674404</v>
       </c>
       <c r="D1074" t="n">
-        <v>8.61635970921901</v>
+        <v>8.616358774439233</v>
       </c>
       <c r="E1074" t="n">
-        <v>8.763021891332949</v>
+        <v>8.763020940641946</v>
       </c>
       <c r="F1074" t="n">
         <v>2317900</v>
@@ -22112,16 +22112,16 @@
         <v>45371</v>
       </c>
       <c r="B1085" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1085" t="n">
-        <v>9.193838844589299</v>
+        <v>9.193837883247255</v>
       </c>
       <c r="D1085" t="n">
-        <v>8.341369812594202</v>
+        <v>8.341368940389497</v>
       </c>
       <c r="E1085" t="n">
-        <v>8.387200813603702</v>
+        <v>8.387199936606738</v>
       </c>
       <c r="F1085" t="n">
         <v>3946300</v>
@@ -22172,16 +22172,16 @@
         <v>45376</v>
       </c>
       <c r="B1088" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1088" t="n">
-        <v>8.634692952368088</v>
+        <v>8.634691984306407</v>
       </c>
       <c r="D1088" t="n">
-        <v>8.378035659229033</v>
+        <v>8.378034719941983</v>
       </c>
       <c r="E1088" t="n">
-        <v>8.433033213530791</v>
+        <v>8.433032268077797</v>
       </c>
       <c r="F1088" t="n">
         <v>2424700</v>
@@ -22232,16 +22232,16 @@
         <v>45379</v>
       </c>
       <c r="B1091" t="n">
-        <v>9.752985954284668</v>
+        <v>9.752986907958984</v>
       </c>
       <c r="C1091" t="n">
-        <v>9.881314153231251</v>
+        <v>9.881315119453859</v>
       </c>
       <c r="D1091" t="n">
-        <v>9.340499960041242</v>
+        <v>9.340500873381522</v>
       </c>
       <c r="E1091" t="n">
-        <v>9.386331834309434</v>
+        <v>9.386332752131281</v>
       </c>
       <c r="F1091" t="n">
         <v>5263200</v>
@@ -22312,16 +22312,16 @@
         <v>45386</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C1095" t="n">
-        <v>11.18293335294909</v>
+        <v>11.18293432413664</v>
       </c>
       <c r="D1095" t="n">
-        <v>10.43129383819321</v>
+        <v>10.43129474410425</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.43129383819321</v>
+        <v>10.43129474410425</v>
       </c>
       <c r="F1095" t="n">
         <v>7684100</v>
@@ -22372,16 +22372,16 @@
         <v>45391</v>
       </c>
       <c r="B1098" t="n">
-        <v>11.40292739868164</v>
+        <v>11.40292644500732</v>
       </c>
       <c r="C1098" t="n">
-        <v>11.73291622197656</v>
+        <v>11.7329152407039</v>
       </c>
       <c r="D1098" t="n">
-        <v>11.28376573934777</v>
+        <v>11.28376479563944</v>
       </c>
       <c r="E1098" t="n">
-        <v>11.29293141564012</v>
+        <v>11.29293047116523</v>
       </c>
       <c r="F1098" t="n">
         <v>4003300</v>
@@ -22392,16 +22392,16 @@
         <v>45392</v>
       </c>
       <c r="B1099" t="n">
-        <v>10.58712196350098</v>
+        <v>10.58712291717529</v>
       </c>
       <c r="C1099" t="n">
-        <v>11.36626027193104</v>
+        <v>11.36626129578913</v>
       </c>
       <c r="D1099" t="n">
-        <v>10.44962635083433</v>
+        <v>10.44962729212322</v>
       </c>
       <c r="E1099" t="n">
-        <v>11.36626027193104</v>
+        <v>11.36626129578913</v>
       </c>
       <c r="F1099" t="n">
         <v>6473200</v>
@@ -22412,16 +22412,16 @@
         <v>45393</v>
       </c>
       <c r="B1100" t="n">
-        <v>10.50462627410889</v>
+        <v>10.50462532043457</v>
       </c>
       <c r="C1100" t="n">
-        <v>10.94461019960207</v>
+        <v>10.94460920598332</v>
       </c>
       <c r="D1100" t="n">
-        <v>10.31213308816303</v>
+        <v>10.31213215196442</v>
       </c>
       <c r="E1100" t="n">
-        <v>10.66045413293031</v>
+        <v>10.66045316510899</v>
       </c>
       <c r="F1100" t="n">
         <v>3334800</v>
@@ -22492,16 +22492,16 @@
         <v>45399</v>
       </c>
       <c r="B1104" t="n">
-        <v>9.193839073181152</v>
+        <v>9.193840026855469</v>
       </c>
       <c r="C1104" t="n">
-        <v>9.707154514451329</v>
+        <v>9.707155521371709</v>
       </c>
       <c r="D1104" t="n">
-        <v>9.129674970836255</v>
+        <v>9.129675917854847</v>
       </c>
       <c r="E1104" t="n">
-        <v>9.395498804484115</v>
+        <v>9.395499779076538</v>
       </c>
       <c r="F1104" t="n">
         <v>2870900</v>
@@ -22612,16 +22612,16 @@
         <v>45407</v>
       </c>
       <c r="B1110" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C1110" t="n">
-        <v>10.00964332536244</v>
+        <v>10.00964236464995</v>
       </c>
       <c r="D1110" t="n">
-        <v>9.505494451765941</v>
+        <v>9.505493539440995</v>
       </c>
       <c r="E1110" t="n">
-        <v>9.670488851095419</v>
+        <v>9.670487922934525</v>
       </c>
       <c r="F1110" t="n">
         <v>2344600</v>
@@ -22672,16 +22672,16 @@
         <v>45412</v>
       </c>
       <c r="B1113" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C1113" t="n">
-        <v>10.89877837583131</v>
+        <v>10.89877940479569</v>
       </c>
       <c r="D1113" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="E1113" t="n">
-        <v>10.86211305146715</v>
+        <v>10.86211407696992</v>
       </c>
       <c r="F1113" t="n">
         <v>3726700</v>
@@ -22712,16 +22712,16 @@
         <v>45415</v>
       </c>
       <c r="B1115" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C1115" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="D1115" t="n">
-        <v>10.41296228000361</v>
+        <v>10.41296137869417</v>
       </c>
       <c r="E1115" t="n">
-        <v>10.48629293256791</v>
+        <v>10.48629202491122</v>
       </c>
       <c r="F1115" t="n">
         <v>3177300</v>
@@ -22792,16 +22792,16 @@
         <v>45421</v>
       </c>
       <c r="B1119" t="n">
-        <v>11.2379322052002</v>
+        <v>11.23793315887451</v>
       </c>
       <c r="C1119" t="n">
-        <v>11.33876162292093</v>
+        <v>11.33876258515184</v>
       </c>
       <c r="D1119" t="n">
-        <v>10.56878898092192</v>
+        <v>10.56878987781135</v>
       </c>
       <c r="E1119" t="n">
-        <v>11.30209630064337</v>
+        <v>11.30209725976278</v>
       </c>
       <c r="F1119" t="n">
         <v>4225100</v>
@@ -22832,16 +22832,16 @@
         <v>45425</v>
       </c>
       <c r="B1121" t="n">
-        <v>9.303834915161133</v>
+        <v>9.303833961486816</v>
       </c>
       <c r="C1121" t="n">
-        <v>9.569658744903728</v>
+        <v>9.569657763981576</v>
       </c>
       <c r="D1121" t="n">
-        <v>9.184673262319901</v>
+        <v>9.184672320860052</v>
       </c>
       <c r="E1121" t="n">
-        <v>9.395498666453195</v>
+        <v>9.395497703383034</v>
       </c>
       <c r="F1121" t="n">
         <v>4893500</v>
@@ -22872,16 +22872,16 @@
         <v>45427</v>
       </c>
       <c r="B1123" t="n">
-        <v>9.52382755279541</v>
+        <v>9.523828506469727</v>
       </c>
       <c r="C1123" t="n">
-        <v>9.835482377775513</v>
+        <v>9.835483362657577</v>
       </c>
       <c r="D1123" t="n">
-        <v>9.395498478389273</v>
+        <v>9.395499419213278</v>
       </c>
       <c r="E1123" t="n">
-        <v>9.597158202693118</v>
+        <v>9.597159163710444</v>
       </c>
       <c r="F1123" t="n">
         <v>4359100</v>
@@ -23012,16 +23012,16 @@
         <v>45436</v>
       </c>
       <c r="B1130" t="n">
-        <v>8.708023071289062</v>
+        <v>8.708024024963379</v>
       </c>
       <c r="C1130" t="n">
-        <v>9.083842874498499</v>
+        <v>9.083843869331375</v>
       </c>
       <c r="D1130" t="n">
-        <v>8.67135774595571</v>
+        <v>8.671358695614559</v>
       </c>
       <c r="E1130" t="n">
-        <v>8.882183148079907</v>
+        <v>8.882184120827667</v>
       </c>
       <c r="F1130" t="n">
         <v>2233000</v>
@@ -23032,16 +23032,16 @@
         <v>45439</v>
       </c>
       <c r="B1131" t="n">
-        <v>8.808852195739746</v>
+        <v>8.808853149414062</v>
       </c>
       <c r="C1131" t="n">
-        <v>8.836351844425723</v>
+        <v>8.836352801077238</v>
       </c>
       <c r="D1131" t="n">
-        <v>8.625525575351304</v>
+        <v>8.625526509178098</v>
       </c>
       <c r="E1131" t="n">
-        <v>8.680523998552976</v>
+        <v>8.680524938334075</v>
       </c>
       <c r="F1131" t="n">
         <v>1394600</v>
@@ -23092,16 +23092,16 @@
         <v>45443</v>
       </c>
       <c r="B1134" t="n">
-        <v>8.808852195739746</v>
+        <v>8.808853149414062</v>
       </c>
       <c r="C1134" t="n">
-        <v>9.395498255153042</v>
+        <v>9.395499272339524</v>
       </c>
       <c r="D1134" t="n">
-        <v>8.717189322630665</v>
+        <v>8.717190266381268</v>
       </c>
       <c r="E1134" t="n">
-        <v>9.074676013845558</v>
+        <v>9.074676996298805</v>
       </c>
       <c r="F1134" t="n">
         <v>8270300</v>
@@ -23172,16 +23172,16 @@
         <v>45449</v>
       </c>
       <c r="B1138" t="n">
-        <v>9.074676513671875</v>
+        <v>9.074675559997559</v>
       </c>
       <c r="C1138" t="n">
-        <v>9.239670918194381</v>
+        <v>9.2396699471805</v>
       </c>
       <c r="D1138" t="n">
-        <v>8.772187354827501</v>
+        <v>8.772186432942322</v>
       </c>
       <c r="E1138" t="n">
-        <v>8.937181759350008</v>
+        <v>8.937180820125265</v>
       </c>
       <c r="F1138" t="n">
         <v>3356600</v>
@@ -23252,16 +23252,16 @@
         <v>45455</v>
       </c>
       <c r="B1142" t="n">
-        <v>8.909682273864746</v>
+        <v>8.909683227539062</v>
       </c>
       <c r="C1142" t="n">
-        <v>9.661321836091128</v>
+        <v>9.661322870219418</v>
       </c>
       <c r="D1142" t="n">
-        <v>8.882182625853835</v>
+        <v>8.882183576584646</v>
       </c>
       <c r="E1142" t="n">
-        <v>9.395498024510802</v>
+        <v>9.395499030185853</v>
       </c>
       <c r="F1142" t="n">
         <v>3064700</v>
@@ -23272,16 +23272,16 @@
         <v>45456</v>
       </c>
       <c r="B1143" t="n">
-        <v>8.62552547454834</v>
+        <v>8.625526428222656</v>
       </c>
       <c r="C1143" t="n">
-        <v>8.891349289547579</v>
+        <v>8.891350272612492</v>
       </c>
       <c r="D1143" t="n">
-        <v>8.59802670035401</v>
+        <v>8.598027650987946</v>
       </c>
       <c r="E1143" t="n">
-        <v>8.891349289547579</v>
+        <v>8.891350272612492</v>
       </c>
       <c r="F1143" t="n">
         <v>2367500</v>
@@ -23452,16 +23452,16 @@
         <v>45469</v>
       </c>
       <c r="B1152" t="n">
-        <v>8.735522270202637</v>
+        <v>8.73552131652832</v>
       </c>
       <c r="C1152" t="n">
-        <v>9.01967921093841</v>
+        <v>9.019678226242117</v>
       </c>
       <c r="D1152" t="n">
-        <v>8.735522270202637</v>
+        <v>8.73552131652832</v>
       </c>
       <c r="E1152" t="n">
-        <v>9.01967921093841</v>
+        <v>9.019678226242117</v>
       </c>
       <c r="F1152" t="n">
         <v>1529900</v>
@@ -23512,16 +23512,16 @@
         <v>45474</v>
       </c>
       <c r="B1155" t="n">
-        <v>8.579693794250488</v>
+        <v>8.579694747924805</v>
       </c>
       <c r="C1155" t="n">
-        <v>8.689689767669948</v>
+        <v>8.689690733570847</v>
       </c>
       <c r="D1155" t="n">
-        <v>8.414700271206444</v>
+        <v>8.414701206540935</v>
       </c>
       <c r="E1155" t="n">
-        <v>8.579693794250488</v>
+        <v>8.579694747924805</v>
       </c>
       <c r="F1155" t="n">
         <v>1954600</v>
@@ -23532,16 +23532,16 @@
         <v>45475</v>
       </c>
       <c r="B1156" t="n">
-        <v>8.414699554443359</v>
+        <v>8.414700508117676</v>
       </c>
       <c r="C1156" t="n">
-        <v>8.836351187053534</v>
+        <v>8.836352188515454</v>
       </c>
       <c r="D1156" t="n">
-        <v>8.387199907803193</v>
+        <v>8.387200858360856</v>
       </c>
       <c r="E1156" t="n">
-        <v>8.588859612313334</v>
+        <v>8.588860585725962</v>
       </c>
       <c r="F1156" t="n">
         <v>3229800</v>
@@ -23732,16 +23732,16 @@
         <v>45489</v>
       </c>
       <c r="B1166" t="n">
-        <v>9.303834915161133</v>
+        <v>9.303833961486816</v>
       </c>
       <c r="C1166" t="n">
-        <v>9.789651573170611</v>
+        <v>9.789650569698455</v>
       </c>
       <c r="D1166" t="n">
-        <v>9.258003913685421</v>
+        <v>9.258002964708936</v>
       </c>
       <c r="E1166" t="n">
-        <v>9.743819697524581</v>
+        <v>9.743818698750346</v>
       </c>
       <c r="F1166" t="n">
         <v>1952400</v>
@@ -23832,16 +23832,16 @@
         <v>45496</v>
       </c>
       <c r="B1171" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="C1171" t="n">
-        <v>8.607194619854459</v>
+        <v>8.607193615930459</v>
       </c>
       <c r="D1171" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="E1171" t="n">
-        <v>8.607194619854459</v>
+        <v>8.607193615930459</v>
       </c>
       <c r="F1171" t="n">
         <v>3005900</v>
@@ -23892,16 +23892,16 @@
         <v>45499</v>
       </c>
       <c r="B1174" t="n">
-        <v>7.818887233734131</v>
+        <v>7.818887710571289</v>
       </c>
       <c r="C1174" t="n">
-        <v>7.883052203726183</v>
+        <v>7.883052684476461</v>
       </c>
       <c r="D1174" t="n">
-        <v>7.653893719596588</v>
+        <v>7.653894186371567</v>
       </c>
       <c r="E1174" t="n">
-        <v>7.718057815418397</v>
+        <v>7.718058286106443</v>
       </c>
       <c r="F1174" t="n">
         <v>2119900</v>
@@ -23952,16 +23952,16 @@
         <v>45504</v>
       </c>
       <c r="B1177" t="n">
-        <v>7.736391067504883</v>
+        <v>7.736390590667725</v>
       </c>
       <c r="C1177" t="n">
-        <v>7.873886700753659</v>
+        <v>7.873886215441875</v>
       </c>
       <c r="D1177" t="n">
-        <v>7.617229409194445</v>
+        <v>7.617228939701889</v>
       </c>
       <c r="E1177" t="n">
-        <v>7.718058840907261</v>
+        <v>7.718058365200021</v>
       </c>
       <c r="F1177" t="n">
         <v>1863600</v>
@@ -23972,16 +23972,16 @@
         <v>45505</v>
       </c>
       <c r="B1178" t="n">
-        <v>7.727224349975586</v>
+        <v>7.727224826812744</v>
       </c>
       <c r="C1178" t="n">
-        <v>7.965548508650412</v>
+        <v>7.965549000194251</v>
       </c>
       <c r="D1178" t="n">
-        <v>7.663059380104842</v>
+        <v>7.663059852982463</v>
       </c>
       <c r="E1178" t="n">
-        <v>7.828053768100695</v>
+        <v>7.828054251159909</v>
       </c>
       <c r="F1178" t="n">
         <v>2732500</v>
@@ -24032,16 +24032,16 @@
         <v>45510</v>
       </c>
       <c r="B1181" t="n">
-        <v>7.95638370513916</v>
+        <v>7.956383228302002</v>
       </c>
       <c r="C1181" t="n">
-        <v>8.176375663782647</v>
+        <v>8.176375173761064</v>
       </c>
       <c r="D1181" t="n">
-        <v>7.782222748918646</v>
+        <v>7.782222282519196</v>
       </c>
       <c r="E1181" t="n">
-        <v>7.993049031579741</v>
+        <v>7.993048552545178</v>
       </c>
       <c r="F1181" t="n">
         <v>1835500</v>
@@ -24052,16 +24052,16 @@
         <v>45511</v>
       </c>
       <c r="B1182" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1182" t="n">
-        <v>8.543029196304673</v>
+        <v>8.543028238519694</v>
       </c>
       <c r="D1182" t="n">
-        <v>8.020548059586147</v>
+        <v>8.020547160378118</v>
       </c>
       <c r="E1182" t="n">
-        <v>8.158042819510907</v>
+        <v>8.158041904887924</v>
       </c>
       <c r="F1182" t="n">
         <v>2816900</v>
@@ -24092,16 +24092,16 @@
         <v>45513</v>
       </c>
       <c r="B1184" t="n">
-        <v>7.846388339996338</v>
+        <v>7.84638786315918</v>
       </c>
       <c r="C1184" t="n">
-        <v>8.103045645170351</v>
+        <v>8.103045152735731</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.653895142573226</v>
+        <v>7.653894677434178</v>
       </c>
       <c r="E1184" t="n">
-        <v>8.103045645170351</v>
+        <v>8.103045152735731</v>
       </c>
       <c r="F1184" t="n">
         <v>6458600</v>
@@ -24132,16 +24132,16 @@
         <v>45517</v>
       </c>
       <c r="B1186" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="C1186" t="n">
-        <v>8.497198631398319</v>
+        <v>8.497197640304007</v>
       </c>
       <c r="D1186" t="n">
-        <v>8.103045683802677</v>
+        <v>8.103044738681486</v>
       </c>
       <c r="E1186" t="n">
-        <v>8.497198631398319</v>
+        <v>8.497197640304007</v>
       </c>
       <c r="F1186" t="n">
         <v>4500900</v>
@@ -24192,16 +24192,16 @@
         <v>45520</v>
       </c>
       <c r="B1189" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1189" t="n">
-        <v>8.598027624776794</v>
+        <v>8.598026660825775</v>
       </c>
       <c r="D1189" t="n">
-        <v>8.304705004046447</v>
+        <v>8.304704072980718</v>
       </c>
       <c r="E1189" t="n">
-        <v>8.387201335499084</v>
+        <v>8.387200395184442</v>
       </c>
       <c r="F1189" t="n">
         <v>3088500</v>
@@ -24212,16 +24212,16 @@
         <v>45523</v>
       </c>
       <c r="B1190" t="n">
-        <v>8.744688987731934</v>
+        <v>8.744688034057617</v>
       </c>
       <c r="C1190" t="n">
-        <v>8.827186193851068</v>
+        <v>8.82718523117981</v>
       </c>
       <c r="D1190" t="n">
-        <v>8.442199814742022</v>
+        <v>8.442198894056432</v>
       </c>
       <c r="E1190" t="n">
-        <v>8.478865142553818</v>
+        <v>8.478864217869598</v>
       </c>
       <c r="F1190" t="n">
         <v>2333900</v>
@@ -24272,16 +24272,16 @@
         <v>45526</v>
       </c>
       <c r="B1193" t="n">
-        <v>8.653023719787598</v>
+        <v>8.653024673461914</v>
       </c>
       <c r="C1193" t="n">
-        <v>9.093008450852169</v>
+        <v>9.093009453018452</v>
       </c>
       <c r="D1193" t="n">
-        <v>8.616358398379734</v>
+        <v>8.616359348013061</v>
       </c>
       <c r="E1193" t="n">
-        <v>9.038010031655267</v>
+        <v>9.038011027760017</v>
       </c>
       <c r="F1193" t="n">
         <v>2148900</v>
@@ -24412,16 +24412,16 @@
         <v>45537</v>
       </c>
       <c r="B1200" t="n">
-        <v>8.93718147277832</v>
+        <v>8.937182426452637</v>
       </c>
       <c r="C1200" t="n">
-        <v>9.2488371716963</v>
+        <v>9.248838158626967</v>
       </c>
       <c r="D1200" t="n">
-        <v>8.918848373232414</v>
+        <v>8.918849324950433</v>
       </c>
       <c r="E1200" t="n">
-        <v>9.120508097385867</v>
+        <v>9.120509070622715</v>
       </c>
       <c r="F1200" t="n">
         <v>2102800</v>
@@ -24452,16 +24452,16 @@
         <v>45539</v>
       </c>
       <c r="B1202" t="n">
-        <v>9.294669151306152</v>
+        <v>9.294670104980469</v>
       </c>
       <c r="C1202" t="n">
-        <v>9.468829228106612</v>
+        <v>9.468830199650526</v>
       </c>
       <c r="D1202" t="n">
-        <v>9.184673175300023</v>
+        <v>9.184674117688264</v>
       </c>
       <c r="E1202" t="n">
-        <v>9.212171950758979</v>
+        <v>9.212172895968715</v>
       </c>
       <c r="F1202" t="n">
         <v>2019900</v>
@@ -24572,16 +24572,16 @@
         <v>45547</v>
       </c>
       <c r="B1208" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1208" t="n">
-        <v>9.212171944329347</v>
+        <v>9.212170981070326</v>
       </c>
       <c r="D1208" t="n">
-        <v>8.955514667160847</v>
+        <v>8.955513730738867</v>
       </c>
       <c r="E1208" t="n">
-        <v>9.175506619019561</v>
+        <v>9.175505659594403</v>
       </c>
       <c r="F1208" t="n">
         <v>1127400</v>
@@ -24612,16 +24612,16 @@
         <v>45551</v>
       </c>
       <c r="B1210" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C1210" t="n">
-        <v>10.17463772469192</v>
+        <v>10.17463674814347</v>
       </c>
       <c r="D1210" t="n">
-        <v>9.569658551873937</v>
+        <v>9.569657633390603</v>
       </c>
       <c r="E1210" t="n">
-        <v>9.707154176038602</v>
+        <v>9.707153244358619</v>
       </c>
       <c r="F1210" t="n">
         <v>2756600</v>
@@ -24652,16 +24652,16 @@
         <v>45553</v>
       </c>
       <c r="B1212" t="n">
-        <v>9.890481948852539</v>
+        <v>9.890480995178223</v>
       </c>
       <c r="C1212" t="n">
-        <v>10.26630179168833</v>
+        <v>10.26630080177617</v>
       </c>
       <c r="D1212" t="n">
-        <v>9.606324991929888</v>
+        <v>9.606324065654963</v>
       </c>
       <c r="E1212" t="n">
-        <v>9.697988752013428</v>
+        <v>9.697987816899968</v>
       </c>
       <c r="F1212" t="n">
         <v>2495300</v>
@@ -24672,16 +24672,16 @@
         <v>45554</v>
       </c>
       <c r="B1213" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C1213" t="n">
-        <v>10.15630421586989</v>
+        <v>10.15630519881978</v>
       </c>
       <c r="D1213" t="n">
-        <v>9.798816656451679</v>
+        <v>9.798817604803125</v>
       </c>
       <c r="E1213" t="n">
-        <v>10.00047637259812</v>
+        <v>10.00047734046665</v>
       </c>
       <c r="F1213" t="n">
         <v>3128500</v>
@@ -24732,16 +24732,16 @@
         <v>45559</v>
       </c>
       <c r="B1216" t="n">
-        <v>9.487161636352539</v>
+        <v>9.487162590026855</v>
       </c>
       <c r="C1216" t="n">
-        <v>9.615489828587524</v>
+        <v>9.615490795161728</v>
       </c>
       <c r="D1216" t="n">
-        <v>9.28550192462153</v>
+        <v>9.285502858024484</v>
       </c>
       <c r="E1216" t="n">
-        <v>9.514660409807144</v>
+        <v>9.51466136624571</v>
       </c>
       <c r="F1216" t="n">
         <v>1652000</v>
@@ -24772,16 +24772,16 @@
         <v>45561</v>
       </c>
       <c r="B1218" t="n">
-        <v>9.551325798034668</v>
+        <v>9.551326751708984</v>
       </c>
       <c r="C1218" t="n">
-        <v>9.789650834064538</v>
+        <v>9.78965181153497</v>
       </c>
       <c r="D1218" t="n">
-        <v>9.450496378562148</v>
+        <v>9.450497322168916</v>
       </c>
       <c r="E1218" t="n">
-        <v>9.450496378562148</v>
+        <v>9.450497322168916</v>
       </c>
       <c r="F1218" t="n">
         <v>1643400</v>
@@ -24792,16 +24792,16 @@
         <v>45562</v>
       </c>
       <c r="B1219" t="n">
-        <v>9.587992668151855</v>
+        <v>9.587991714477539</v>
       </c>
       <c r="C1219" t="n">
-        <v>9.752987084977519</v>
+        <v>9.752986114891955</v>
       </c>
       <c r="D1219" t="n">
-        <v>9.450497903577398</v>
+        <v>9.450496963579065</v>
       </c>
       <c r="E1219" t="n">
-        <v>9.532994237819837</v>
+        <v>9.532993289615966</v>
       </c>
       <c r="F1219" t="n">
         <v>1380700</v>
@@ -24892,16 +24892,16 @@
         <v>45569</v>
       </c>
       <c r="B1224" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1224" t="n">
-        <v>9.258003819509156</v>
+        <v>9.258002851457784</v>
       </c>
       <c r="D1224" t="n">
-        <v>9.038010993480132</v>
+        <v>9.03801004843203</v>
       </c>
       <c r="E1224" t="n">
-        <v>9.166340069149538</v>
+        <v>9.166339110682868</v>
       </c>
       <c r="F1224" t="n">
         <v>1258700</v>
@@ -24972,16 +24972,16 @@
         <v>45575</v>
       </c>
       <c r="B1228" t="n">
-        <v>9.422996520996094</v>
+        <v>9.42299747467041</v>
       </c>
       <c r="C1228" t="n">
-        <v>9.441329619130419</v>
+        <v>9.441330574660176</v>
       </c>
       <c r="D1228" t="n">
-        <v>8.946347333716643</v>
+        <v>8.946348239150669</v>
       </c>
       <c r="E1228" t="n">
-        <v>9.065509849079064</v>
+        <v>9.065510766573185</v>
       </c>
       <c r="F1228" t="n">
         <v>2116800</v>
@@ -24992,16 +24992,16 @@
         <v>45576</v>
       </c>
       <c r="B1229" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C1229" t="n">
-        <v>10.3671307354659</v>
+        <v>10.36713171423691</v>
       </c>
       <c r="D1229" t="n">
-        <v>9.432163652924501</v>
+        <v>9.432164543424346</v>
       </c>
       <c r="E1229" t="n">
-        <v>9.432163652924501</v>
+        <v>9.432164543424346</v>
       </c>
       <c r="F1229" t="n">
         <v>6482800</v>
@@ -25112,16 +25112,16 @@
         <v>45586</v>
       </c>
       <c r="B1235" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C1235" t="n">
-        <v>11.2654310852861</v>
+        <v>11.26543206609426</v>
       </c>
       <c r="D1235" t="n">
-        <v>10.89877785903058</v>
+        <v>10.89877880791662</v>
       </c>
       <c r="E1235" t="n">
-        <v>11.07293792295939</v>
+        <v>11.07293888700842</v>
       </c>
       <c r="F1235" t="n">
         <v>2389000</v>
@@ -25132,16 +25132,16 @@
         <v>45587</v>
       </c>
       <c r="B1236" t="n">
-        <v>10.65128612518311</v>
+        <v>10.65128707885742</v>
       </c>
       <c r="C1236" t="n">
-        <v>11.00877367135879</v>
+        <v>11.00877465704114</v>
       </c>
       <c r="D1236" t="n">
-        <v>10.62378735214505</v>
+        <v>10.62378830335723</v>
       </c>
       <c r="E1236" t="n">
-        <v>10.86211238292884</v>
+        <v>10.86211335547971</v>
       </c>
       <c r="F1236" t="n">
         <v>2418100</v>
@@ -25232,16 +25232,16 @@
         <v>45594</v>
       </c>
       <c r="B1241" t="n">
-        <v>11.42125988006592</v>
+        <v>11.4212589263916</v>
       </c>
       <c r="C1241" t="n">
-        <v>11.62291960845494</v>
+        <v>11.62291863794205</v>
       </c>
       <c r="D1241" t="n">
-        <v>11.25626547736851</v>
+        <v>11.25626453747121</v>
       </c>
       <c r="E1241" t="n">
-        <v>11.47625830568849</v>
+        <v>11.47625734742181</v>
       </c>
       <c r="F1241" t="n">
         <v>2046100</v>
@@ -25252,16 +25252,16 @@
         <v>45595</v>
       </c>
       <c r="B1242" t="n">
-        <v>12.09956836700439</v>
+        <v>12.09956932067871</v>
       </c>
       <c r="C1242" t="n">
-        <v>12.35622563676056</v>
+        <v>12.35622661066431</v>
       </c>
       <c r="D1242" t="n">
-        <v>11.3204300081306</v>
+        <v>11.32043090039411</v>
       </c>
       <c r="E1242" t="n">
-        <v>11.3204300081306</v>
+        <v>11.32043090039411</v>
       </c>
       <c r="F1242" t="n">
         <v>5623200</v>
@@ -25412,16 +25412,16 @@
         <v>45607</v>
       </c>
       <c r="B1250" t="n">
-        <v>12.33789348602295</v>
+        <v>12.33789443969727</v>
       </c>
       <c r="C1250" t="n">
-        <v>12.47538823424922</v>
+        <v>12.47538919855138</v>
       </c>
       <c r="D1250" t="n">
-        <v>11.64125144689053</v>
+        <v>11.64125234671695</v>
       </c>
       <c r="E1250" t="n">
-        <v>11.69624987068321</v>
+        <v>11.69625077476081</v>
       </c>
       <c r="F1250" t="n">
         <v>4291300</v>
@@ -25432,16 +25432,16 @@
         <v>45608</v>
       </c>
       <c r="B1251" t="n">
-        <v>11.86124420166016</v>
+        <v>11.86124324798584</v>
       </c>
       <c r="C1251" t="n">
-        <v>12.37455965339907</v>
+        <v>12.37455865845288</v>
       </c>
       <c r="D1251" t="n">
-        <v>11.77874787160726</v>
+        <v>11.77874692456585</v>
       </c>
       <c r="E1251" t="n">
-        <v>12.28289589889094</v>
+        <v>12.28289491131475</v>
       </c>
       <c r="F1251" t="n">
         <v>1595200</v>
@@ -25472,16 +25472,16 @@
         <v>45610</v>
       </c>
       <c r="B1253" t="n">
-        <v>10.58712196350098</v>
+        <v>10.58712291717529</v>
       </c>
       <c r="C1253" t="n">
-        <v>10.99960705316045</v>
+        <v>10.99960804399089</v>
       </c>
       <c r="D1253" t="n">
-        <v>10.40379535411568</v>
+        <v>10.40379629127617</v>
       </c>
       <c r="E1253" t="n">
-        <v>10.55962319063574</v>
+        <v>10.559624141833</v>
       </c>
       <c r="F1253" t="n">
         <v>63226600</v>
@@ -25512,16 +25512,16 @@
         <v>45615</v>
       </c>
       <c r="B1255" t="n">
-        <v>11.35709667205811</v>
+        <v>11.35709571838379</v>
       </c>
       <c r="C1255" t="n">
-        <v>11.46709265778581</v>
+        <v>11.46709169487495</v>
       </c>
       <c r="D1255" t="n">
-        <v>10.91711185497689</v>
+        <v>10.91711093824883</v>
       </c>
       <c r="E1255" t="n">
-        <v>11.00877561350184</v>
+        <v>11.00877468907663</v>
       </c>
       <c r="F1255" t="n">
         <v>7243900</v>
@@ -25532,16 +25532,16 @@
         <v>45617</v>
       </c>
       <c r="B1256" t="n">
-        <v>11.2379322052002</v>
+        <v>11.23793315887451</v>
       </c>
       <c r="C1256" t="n">
-        <v>11.32959507380898</v>
+        <v>11.329596035262</v>
       </c>
       <c r="D1256" t="n">
-        <v>10.94460875280948</v>
+        <v>10.94460968159175</v>
       </c>
       <c r="E1256" t="n">
-        <v>11.30209630064337</v>
+        <v>11.30209725976278</v>
       </c>
       <c r="F1256" t="n">
         <v>3263500</v>
@@ -25592,16 +25592,16 @@
         <v>45622</v>
       </c>
       <c r="B1259" t="n">
-        <v>11.57708835601807</v>
+        <v>11.57708740234375</v>
       </c>
       <c r="C1259" t="n">
-        <v>11.66875123809635</v>
+        <v>11.66875027687121</v>
       </c>
       <c r="D1259" t="n">
-        <v>11.31126451190142</v>
+        <v>11.31126358012461</v>
       </c>
       <c r="E1259" t="n">
-        <v>11.63208591043096</v>
+        <v>11.63208495222617</v>
       </c>
       <c r="F1259" t="n">
         <v>7231300</v>
@@ -25652,16 +25652,16 @@
         <v>45625</v>
       </c>
       <c r="B1262" t="n">
-        <v>9.688821792602539</v>
+        <v>9.688820838928223</v>
       </c>
       <c r="C1262" t="n">
-        <v>9.697988343058428</v>
+        <v>9.697987388481845</v>
       </c>
       <c r="D1262" t="n">
-        <v>9.001346243477393</v>
+        <v>9.00134535747155</v>
       </c>
       <c r="E1262" t="n">
-        <v>9.532993931533877</v>
+        <v>9.532992993197755</v>
       </c>
       <c r="F1262" t="n">
         <v>14865400</v>
@@ -25732,16 +25732,16 @@
         <v>45631</v>
       </c>
       <c r="B1266" t="n">
-        <v>9.404665946960449</v>
+        <v>9.404664993286133</v>
       </c>
       <c r="C1266" t="n">
-        <v>9.835483338655724</v>
+        <v>9.835482341294636</v>
       </c>
       <c r="D1266" t="n">
-        <v>9.294669961367802</v>
+        <v>9.294669018847561</v>
       </c>
       <c r="E1266" t="n">
-        <v>9.624657918145745</v>
+        <v>9.624656942163279</v>
       </c>
       <c r="F1266" t="n">
         <v>7256000</v>
@@ -25952,16 +25952,16 @@
         <v>45646</v>
       </c>
       <c r="B1277" t="n">
-        <v>8.93718147277832</v>
+        <v>8.937182426452637</v>
       </c>
       <c r="C1277" t="n">
-        <v>9.138841196931772</v>
+        <v>9.138842172124919</v>
       </c>
       <c r="D1277" t="n">
-        <v>8.588860448938831</v>
+        <v>8.588861365444293</v>
       </c>
       <c r="E1277" t="n">
-        <v>8.799686722865236</v>
+        <v>8.799687661867678</v>
       </c>
       <c r="F1277" t="n">
         <v>5127000</v>
@@ -26032,16 +26032,16 @@
         <v>45656</v>
       </c>
       <c r="B1281" t="n">
-        <v>7.378904342651367</v>
+        <v>7.378903865814209</v>
       </c>
       <c r="C1281" t="n">
-        <v>7.86472014868406</v>
+        <v>7.86471964045267</v>
       </c>
       <c r="D1281" t="n">
-        <v>7.314739801232726</v>
+        <v>7.314739328541989</v>
       </c>
       <c r="E1281" t="n">
-        <v>7.809722594732624</v>
+        <v>7.809722090055269</v>
       </c>
       <c r="F1281" t="n">
         <v>5347400</v>
@@ -33929,162 +33929,142 @@
     </row>
     <row r="1676">
       <c r="A1676" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1676" t="n">
-        <v>9.439999580383301</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="C1676" t="n">
-        <v>9.609999656677246</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="D1676" t="n">
-        <v>9.420000076293945</v>
+        <v>9.470000267028809</v>
       </c>
       <c r="E1676" t="n">
-        <v>9.479999542236328</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="F1676" t="n">
-        <v>4879600</v>
+        <v>7262200</v>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1677" t="n">
-        <v>9.779999732971191</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="C1677" t="n">
-        <v>9.800000190734863</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="D1677" t="n">
-        <v>9.470000267028809</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="E1677" t="n">
-        <v>9.569999694824219</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="F1677" t="n">
-        <v>7262200</v>
+        <v>8354200</v>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1678" t="n">
-        <v>9.720000267028809</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="C1678" t="n">
-        <v>10.01000022888184</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="D1678" t="n">
-        <v>9.600000381469727</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="E1678" t="n">
-        <v>9.899999618530273</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="F1678" t="n">
-        <v>8354200</v>
+        <v>20128500</v>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1679" t="n">
-        <v>9.340000152587891</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="C1679" t="n">
-        <v>9.930000305175781</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="D1679" t="n">
-        <v>8.979999542236328</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="E1679" t="n">
-        <v>9.850000381469727</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="F1679" t="n">
-        <v>20128500</v>
+        <v>10508100</v>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1680" t="n">
-        <v>9.439999580383301</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="C1680" t="n">
-        <v>9.600000381469727</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="D1680" t="n">
-        <v>9.170000076293945</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="E1680" t="n">
-        <v>9.300000190734863</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="F1680" t="n">
-        <v>10508100</v>
+        <v>13169100</v>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1681" t="n">
-        <v>9.180000305175781</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="C1681" t="n">
-        <v>9.510000228881836</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="D1681" t="n">
-        <v>8.880000114440918</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="E1681" t="n">
-        <v>9.479999542236328</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="F1681" t="n">
-        <v>13169100</v>
+        <v>6481600</v>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1682" t="n">
-        <v>8.909999847412109</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C1682" t="n">
-        <v>9.229999542236328</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D1682" t="n">
-        <v>8.880000114440918</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E1682" t="n">
-        <v>9.170000076293945</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F1682" t="n">
-        <v>7898200</v>
-      </c>
-    </row>
-    <row r="1683">
-      <c r="A1683" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B1683" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="C1683" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D1683" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="E1683" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="F1683" t="n">
-        <v>6481600</v>
+        <v>7526600</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1687"/>
+  <dimension ref="A1:F1686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>43777</v>
       </c>
       <c r="B5" t="n">
-        <v>15.81444644927979</v>
+        <v>15.81444835662842</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12169868961396</v>
+        <v>16.12170063401967</v>
       </c>
       <c r="D5" t="n">
-        <v>15.57948875233966</v>
+        <v>15.57949063135051</v>
       </c>
       <c r="E5" t="n">
-        <v>15.94999850268889</v>
+        <v>15.95000042638619</v>
       </c>
       <c r="F5" t="n">
         <v>463500</v>
@@ -532,16 +532,16 @@
         <v>43780</v>
       </c>
       <c r="B6" t="n">
-        <v>15.80540943145752</v>
+        <v>15.80541133880615</v>
       </c>
       <c r="C6" t="n">
-        <v>15.85962990814695</v>
+        <v>15.85963182203875</v>
       </c>
       <c r="D6" t="n">
-        <v>15.52526829098458</v>
+        <v>15.52527016452663</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65178331113922</v>
+        <v>15.65178519994872</v>
       </c>
       <c r="F6" t="n">
         <v>2507900</v>
@@ -552,16 +552,16 @@
         <v>43781</v>
       </c>
       <c r="B7" t="n">
-        <v>15.18186950683594</v>
+        <v>15.18186855316162</v>
       </c>
       <c r="C7" t="n">
-        <v>15.86866860350472</v>
+        <v>15.86866760668798</v>
       </c>
       <c r="D7" t="n">
-        <v>15.02824337042795</v>
+        <v>15.02824242640391</v>
       </c>
       <c r="E7" t="n">
-        <v>15.79637405246791</v>
+        <v>15.79637306019247</v>
       </c>
       <c r="F7" t="n">
         <v>2855600</v>
@@ -652,16 +652,16 @@
         <v>43790</v>
       </c>
       <c r="B12" t="n">
-        <v>13.97093486785889</v>
+        <v>13.9709358215332</v>
       </c>
       <c r="C12" t="n">
-        <v>14.09745075875241</v>
+        <v>14.09745172106287</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66368260555961</v>
+        <v>13.66368353826049</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9257505595527</v>
+        <v>13.92575151014267</v>
       </c>
       <c r="F12" t="n">
         <v>946900</v>
@@ -672,16 +672,16 @@
         <v>43791</v>
       </c>
       <c r="B13" t="n">
-        <v>14.31433486938477</v>
+        <v>14.31433582305908</v>
       </c>
       <c r="C13" t="n">
-        <v>14.36855535165813</v>
+        <v>14.36855630894482</v>
       </c>
       <c r="D13" t="n">
-        <v>13.77212487573694</v>
+        <v>13.7721257932872</v>
       </c>
       <c r="E13" t="n">
-        <v>13.79923597869265</v>
+        <v>13.79923689804916</v>
       </c>
       <c r="F13" t="n">
         <v>1005200</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572238922119</v>
+        <v>15.14572143554688</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186880124062</v>
+        <v>15.18186784529029</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195510316014</v>
+        <v>14.71195417679867</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113329386751</v>
+        <v>15.00113234929747</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49815940856934</v>
+        <v>15.4981575012207</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52527051261252</v>
+        <v>15.52526860192735</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209753189668</v>
+        <v>14.99209568682876</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15476070887956</v>
+        <v>15.15475884379279</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -812,16 +812,16 @@
         <v>43802</v>
       </c>
       <c r="B20" t="n">
-        <v>15.81444644927979</v>
+        <v>15.81444835662842</v>
       </c>
       <c r="C20" t="n">
-        <v>15.9228891261898</v>
+        <v>15.92289104661748</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29934761214245</v>
+        <v>15.29934945736604</v>
       </c>
       <c r="E20" t="n">
-        <v>15.48912014218763</v>
+        <v>15.4891220102993</v>
       </c>
       <c r="F20" t="n">
         <v>976200</v>
@@ -912,16 +912,16 @@
         <v>43809</v>
       </c>
       <c r="B25" t="n">
-        <v>16.71813201904297</v>
+        <v>16.71813011169434</v>
       </c>
       <c r="C25" t="n">
-        <v>16.97116382686796</v>
+        <v>16.97116189065127</v>
       </c>
       <c r="D25" t="n">
-        <v>16.21207012703117</v>
+        <v>16.21206827741844</v>
       </c>
       <c r="E25" t="n">
-        <v>16.35665923903454</v>
+        <v>16.35665737292584</v>
       </c>
       <c r="F25" t="n">
         <v>1162400</v>
@@ -972,16 +972,16 @@
         <v>43812</v>
       </c>
       <c r="B28" t="n">
-        <v>16.71813201904297</v>
+        <v>16.71813011169434</v>
       </c>
       <c r="C28" t="n">
-        <v>17.50433682374471</v>
+        <v>17.50433482669905</v>
       </c>
       <c r="D28" t="n">
-        <v>16.28436468303286</v>
+        <v>16.28436282517214</v>
       </c>
       <c r="E28" t="n">
-        <v>17.50433682374471</v>
+        <v>17.50433482669905</v>
       </c>
       <c r="F28" t="n">
         <v>3257200</v>
@@ -1012,16 +1012,16 @@
         <v>43816</v>
       </c>
       <c r="B30" t="n">
-        <v>16.71813201904297</v>
+        <v>16.71813011169434</v>
       </c>
       <c r="C30" t="n">
-        <v>16.89886927086627</v>
+        <v>16.89886734289757</v>
       </c>
       <c r="D30" t="n">
-        <v>16.51932242094788</v>
+        <v>16.51932053628116</v>
       </c>
       <c r="E30" t="n">
-        <v>16.85368409609136</v>
+        <v>16.85368217327778</v>
       </c>
       <c r="F30" t="n">
         <v>664900</v>
@@ -1092,16 +1092,16 @@
         <v>43822</v>
       </c>
       <c r="B34" t="n">
-        <v>16.38376617431641</v>
+        <v>16.38376808166504</v>
       </c>
       <c r="C34" t="n">
-        <v>16.60968684354858</v>
+        <v>16.60968877719821</v>
       </c>
       <c r="D34" t="n">
-        <v>16.09458799348129</v>
+        <v>16.09458986716468</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31147162910763</v>
+        <v>16.31147352803995</v>
       </c>
       <c r="F34" t="n">
         <v>766700</v>
@@ -1112,16 +1112,16 @@
         <v>43825</v>
       </c>
       <c r="B35" t="n">
-        <v>16.51932144165039</v>
+        <v>16.51931953430176</v>
       </c>
       <c r="C35" t="n">
-        <v>16.59161599336631</v>
+        <v>16.59161407767043</v>
       </c>
       <c r="D35" t="n">
-        <v>16.37473233821854</v>
+        <v>16.37473044756441</v>
       </c>
       <c r="E35" t="n">
-        <v>16.59161599336631</v>
+        <v>16.59161407767043</v>
       </c>
       <c r="F35" t="n">
         <v>1111500</v>
@@ -33929,242 +33929,222 @@
     </row>
     <row r="1676">
       <c r="A1676" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1676" t="n">
-        <v>9.439999580383301</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="C1676" t="n">
-        <v>9.609999656677246</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="D1676" t="n">
-        <v>9.420000076293945</v>
+        <v>9.470000267028809</v>
       </c>
       <c r="E1676" t="n">
-        <v>9.479999542236328</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="F1676" t="n">
-        <v>4879600</v>
+        <v>7262200</v>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1677" t="n">
-        <v>9.779999732971191</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="C1677" t="n">
-        <v>9.800000190734863</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="D1677" t="n">
-        <v>9.470000267028809</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="E1677" t="n">
-        <v>9.569999694824219</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="F1677" t="n">
-        <v>7262200</v>
+        <v>8354200</v>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1678" t="n">
-        <v>9.720000267028809</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="C1678" t="n">
-        <v>10.01000022888184</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="D1678" t="n">
-        <v>9.600000381469727</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="E1678" t="n">
-        <v>9.899999618530273</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="F1678" t="n">
-        <v>8354200</v>
+        <v>20128500</v>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1679" t="n">
-        <v>9.340000152587891</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="C1679" t="n">
-        <v>9.930000305175781</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="D1679" t="n">
-        <v>8.979999542236328</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="E1679" t="n">
-        <v>9.850000381469727</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="F1679" t="n">
-        <v>20128500</v>
+        <v>10508100</v>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1680" t="n">
-        <v>9.439999580383301</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="C1680" t="n">
-        <v>9.600000381469727</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="D1680" t="n">
-        <v>9.170000076293945</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="E1680" t="n">
-        <v>9.300000190734863</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="F1680" t="n">
-        <v>10508100</v>
+        <v>13169100</v>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1681" t="n">
-        <v>9.180000305175781</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="C1681" t="n">
-        <v>9.510000228881836</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="D1681" t="n">
-        <v>8.880000114440918</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="E1681" t="n">
-        <v>9.479999542236328</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="F1681" t="n">
-        <v>13169100</v>
+        <v>6481600</v>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1682" t="n">
-        <v>8.909999847412109</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="C1682" t="n">
-        <v>9.229999542236328</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="D1682" t="n">
-        <v>8.880000114440918</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="E1682" t="n">
-        <v>9.170000076293945</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="F1682" t="n">
-        <v>7898200</v>
+        <v>7526600</v>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B1683" t="n">
-        <v>8.670000076293945</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="C1683" t="n">
-        <v>9.100000381469727</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="D1683" t="n">
-        <v>8.579999923706055</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E1683" t="n">
-        <v>8.899999618530273</v>
+        <v>8.390000343322754</v>
       </c>
       <c r="F1683" t="n">
-        <v>6481600</v>
+        <v>7704200</v>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B1684" t="n">
-        <v>8.380000114440918</v>
+        <v>8</v>
       </c>
       <c r="C1684" t="n">
-        <v>8.710000038146973</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="D1684" t="n">
-        <v>8.359999656677246</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="E1684" t="n">
-        <v>8.699999809265137</v>
+        <v>8.109999656677246</v>
       </c>
       <c r="F1684" t="n">
-        <v>7526600</v>
+        <v>8377800</v>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B1685" t="n">
-        <v>8.159999847412109</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="C1685" t="n">
-        <v>8.529999732971191</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="D1685" t="n">
-        <v>8.100000381469727</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="E1685" t="n">
-        <v>8.390000343322754</v>
+        <v>7.96999979019165</v>
       </c>
       <c r="F1685" t="n">
-        <v>7704200</v>
+        <v>6506700</v>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B1686" t="n">
-        <v>8</v>
+        <v>7.38</v>
       </c>
       <c r="C1686" t="n">
-        <v>8.149999618530273</v>
+        <v>7.84</v>
       </c>
       <c r="D1686" t="n">
-        <v>7.880000114440918</v>
+        <v>7.38</v>
       </c>
       <c r="E1686" t="n">
-        <v>8.109999656677246</v>
+        <v>7.83</v>
       </c>
       <c r="F1686" t="n">
-        <v>8377800</v>
-      </c>
-    </row>
-    <row r="1687">
-      <c r="A1687" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B1687" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="C1687" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="D1687" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E1687" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="F1687" t="n">
-        <v>6506700</v>
+        <v>10354900</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1686"/>
+  <dimension ref="A1:F1688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43774</v>
       </c>
       <c r="B2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04940511406312</v>
+        <v>16.04940323214578</v>
       </c>
       <c r="E2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="F2" t="n">
         <v>862100</v>
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518585205078</v>
+        <v>15.99518489837646</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073792395533</v>
+        <v>16.13073696219904</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008522099254</v>
+        <v>15.48008429802985</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073792395533</v>
+        <v>16.13073696219904</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -512,16 +512,16 @@
         <v>43777</v>
       </c>
       <c r="B5" t="n">
-        <v>15.81444835662842</v>
+        <v>15.81444644927979</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12170063401967</v>
+        <v>16.12169868961396</v>
       </c>
       <c r="D5" t="n">
-        <v>15.57949063135051</v>
+        <v>15.57948875233966</v>
       </c>
       <c r="E5" t="n">
-        <v>15.95000042638619</v>
+        <v>15.94999850268889</v>
       </c>
       <c r="F5" t="n">
         <v>463500</v>
@@ -532,16 +532,16 @@
         <v>43780</v>
       </c>
       <c r="B6" t="n">
-        <v>15.80541133880615</v>
+        <v>15.80540943145752</v>
       </c>
       <c r="C6" t="n">
-        <v>15.85963182203875</v>
+        <v>15.85962990814695</v>
       </c>
       <c r="D6" t="n">
-        <v>15.52527016452663</v>
+        <v>15.52526829098458</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65178519994872</v>
+        <v>15.65178331113922</v>
       </c>
       <c r="F6" t="n">
         <v>2507900</v>
@@ -552,16 +552,16 @@
         <v>43781</v>
       </c>
       <c r="B7" t="n">
-        <v>15.18186855316162</v>
+        <v>15.18186950683594</v>
       </c>
       <c r="C7" t="n">
-        <v>15.86866760668798</v>
+        <v>15.86866860350472</v>
       </c>
       <c r="D7" t="n">
-        <v>15.02824242640391</v>
+        <v>15.02824337042795</v>
       </c>
       <c r="E7" t="n">
-        <v>15.79637306019247</v>
+        <v>15.79637405246791</v>
       </c>
       <c r="F7" t="n">
         <v>2855600</v>
@@ -572,16 +572,16 @@
         <v>43782</v>
       </c>
       <c r="B8" t="n">
-        <v>13.55524158477783</v>
+        <v>13.55524063110352</v>
       </c>
       <c r="C8" t="n">
-        <v>14.91076574325561</v>
+        <v>14.91076469421387</v>
       </c>
       <c r="D8" t="n">
-        <v>13.3925784099784</v>
+        <v>13.3925774677482</v>
       </c>
       <c r="E8" t="n">
-        <v>14.73002849933667</v>
+        <v>14.73002746301063</v>
       </c>
       <c r="F8" t="n">
         <v>9002100</v>
@@ -592,16 +592,16 @@
         <v>43783</v>
       </c>
       <c r="B9" t="n">
-        <v>13.55524158477783</v>
+        <v>13.55524063110352</v>
       </c>
       <c r="C9" t="n">
-        <v>13.93478841809713</v>
+        <v>13.93478743771993</v>
       </c>
       <c r="D9" t="n">
-        <v>12.80518495269898</v>
+        <v>12.80518405179464</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60946293031733</v>
+        <v>13.60946197282829</v>
       </c>
       <c r="F9" t="n">
         <v>6889800</v>
@@ -632,16 +632,16 @@
         <v>43788</v>
       </c>
       <c r="B11" t="n">
-        <v>13.91671276092529</v>
+        <v>13.91671371459961</v>
       </c>
       <c r="C11" t="n">
-        <v>14.40470136781958</v>
+        <v>14.40470235493443</v>
       </c>
       <c r="D11" t="n">
-        <v>13.79019773880167</v>
+        <v>13.79019868380626</v>
       </c>
       <c r="E11" t="n">
-        <v>14.27818634569596</v>
+        <v>14.27818732414107</v>
       </c>
       <c r="F11" t="n">
         <v>1475000</v>
@@ -652,16 +652,16 @@
         <v>43790</v>
       </c>
       <c r="B12" t="n">
-        <v>13.9709358215332</v>
+        <v>13.97093486785889</v>
       </c>
       <c r="C12" t="n">
-        <v>14.09745172106287</v>
+        <v>14.09745075875241</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66368353826049</v>
+        <v>13.66368260555961</v>
       </c>
       <c r="E12" t="n">
-        <v>13.92575151014267</v>
+        <v>13.9257505595527</v>
       </c>
       <c r="F12" t="n">
         <v>946900</v>
@@ -672,16 +672,16 @@
         <v>43791</v>
       </c>
       <c r="B13" t="n">
-        <v>14.31433582305908</v>
+        <v>14.31433486938477</v>
       </c>
       <c r="C13" t="n">
-        <v>14.36855630894482</v>
+        <v>14.36855535165813</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7721257932872</v>
+        <v>13.77212487573694</v>
       </c>
       <c r="E13" t="n">
-        <v>13.79923689804916</v>
+        <v>13.79923597869265</v>
       </c>
       <c r="F13" t="n">
         <v>1005200</v>
@@ -712,16 +712,16 @@
         <v>43795</v>
       </c>
       <c r="B15" t="n">
-        <v>14.7842493057251</v>
+        <v>14.78425025939941</v>
       </c>
       <c r="C15" t="n">
-        <v>14.7842493057251</v>
+        <v>14.78425025939941</v>
       </c>
       <c r="D15" t="n">
-        <v>14.16974480299746</v>
+        <v>14.16974571703249</v>
       </c>
       <c r="E15" t="n">
-        <v>14.17878097488189</v>
+        <v>14.17878188949981</v>
       </c>
       <c r="F15" t="n">
         <v>3631800</v>
@@ -732,16 +732,16 @@
         <v>43796</v>
       </c>
       <c r="B16" t="n">
-        <v>14.70291900634766</v>
+        <v>14.70291805267334</v>
       </c>
       <c r="C16" t="n">
-        <v>14.9378767321821</v>
+        <v>14.93787576326774</v>
       </c>
       <c r="D16" t="n">
-        <v>14.50410769483647</v>
+        <v>14.50410675405763</v>
       </c>
       <c r="E16" t="n">
-        <v>14.9107656287111</v>
+        <v>14.91076466155524</v>
       </c>
       <c r="F16" t="n">
         <v>575100</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869618523321</v>
+        <v>14.64869711259133</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291838990186</v>
+        <v>14.70291932069259</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572143554688</v>
+        <v>15.14572238922119</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186784529029</v>
+        <v>15.18186880124062</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195417679867</v>
+        <v>14.71195510316014</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113234929747</v>
+        <v>15.00113329386751</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -812,16 +812,16 @@
         <v>43802</v>
       </c>
       <c r="B20" t="n">
-        <v>15.81444835662842</v>
+        <v>15.81444644927979</v>
       </c>
       <c r="C20" t="n">
-        <v>15.92289104661748</v>
+        <v>15.9228891261898</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29934945736604</v>
+        <v>15.29934761214245</v>
       </c>
       <c r="E20" t="n">
-        <v>15.4891220102993</v>
+        <v>15.48912014218763</v>
       </c>
       <c r="F20" t="n">
         <v>976200</v>
@@ -832,16 +832,16 @@
         <v>43803</v>
       </c>
       <c r="B21" t="n">
-        <v>16.10362434387207</v>
+        <v>16.1036262512207</v>
       </c>
       <c r="C21" t="n">
-        <v>16.19399295245853</v>
+        <v>16.19399487051062</v>
       </c>
       <c r="D21" t="n">
-        <v>15.74215163316408</v>
+        <v>15.74215349769909</v>
       </c>
       <c r="E21" t="n">
-        <v>16.0403668349529</v>
+        <v>16.04036873480918</v>
       </c>
       <c r="F21" t="n">
         <v>976000</v>
@@ -852,16 +852,16 @@
         <v>43804</v>
       </c>
       <c r="B22" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C22" t="n">
-        <v>16.4379889546035</v>
+        <v>16.43798702712168</v>
       </c>
       <c r="D22" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="E22" t="n">
-        <v>16.40184081890766</v>
+        <v>16.40183889566449</v>
       </c>
       <c r="F22" t="n">
         <v>1168600</v>
@@ -892,16 +892,16 @@
         <v>43808</v>
       </c>
       <c r="B24" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C24" t="n">
-        <v>16.37473144077376</v>
+        <v>16.37472952070938</v>
       </c>
       <c r="D24" t="n">
-        <v>16.21206827741844</v>
+        <v>16.21206637642758</v>
       </c>
       <c r="E24" t="n">
-        <v>16.33858330507792</v>
+        <v>16.33858138925219</v>
       </c>
       <c r="F24" t="n">
         <v>474400</v>
@@ -932,16 +932,16 @@
         <v>43810</v>
       </c>
       <c r="B26" t="n">
-        <v>17.48626136779785</v>
+        <v>17.48626327514648</v>
       </c>
       <c r="C26" t="n">
-        <v>17.84773411915439</v>
+        <v>17.84773606593138</v>
       </c>
       <c r="D26" t="n">
-        <v>16.9259773104667</v>
+        <v>16.92597915670124</v>
       </c>
       <c r="E26" t="n">
-        <v>16.98019951589871</v>
+        <v>16.98020136804764</v>
       </c>
       <c r="F26" t="n">
         <v>2363200</v>
@@ -1052,16 +1052,16 @@
         <v>43818</v>
       </c>
       <c r="B32" t="n">
-        <v>16.40184020996094</v>
+        <v>16.40184211730957</v>
       </c>
       <c r="C32" t="n">
-        <v>16.59161446804244</v>
+        <v>16.59161639745967</v>
       </c>
       <c r="D32" t="n">
-        <v>16.33858269847974</v>
+        <v>16.33858459847224</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35665676565663</v>
+        <v>16.35665866775094</v>
       </c>
       <c r="F32" t="n">
         <v>961700</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436088562012</v>
+        <v>16.28436279296875</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51931856874445</v>
+        <v>16.51932050361312</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444551937144</v>
+        <v>15.81444737168</v>
       </c>
       <c r="E33" t="n">
-        <v>16.4018388653634</v>
+        <v>16.40184078647195</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739356994629</v>
+        <v>16.53739166259766</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872515501472</v>
+        <v>16.61872323828566</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821536687546</v>
+        <v>16.24821349287934</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872515501472</v>
+        <v>16.61872323828566</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21206855773926</v>
+        <v>16.21207046508789</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620446892584</v>
+        <v>16.73620643793902</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21206855773926</v>
+        <v>16.21207046508789</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813040076541</v>
+        <v>16.71813236765218</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -1252,16 +1252,16 @@
         <v>43838</v>
       </c>
       <c r="B42" t="n">
-        <v>14.91363620758057</v>
+        <v>14.91363525390625</v>
       </c>
       <c r="C42" t="n">
-        <v>15.94943190053661</v>
+        <v>15.94943088062682</v>
       </c>
       <c r="D42" t="n">
-        <v>14.85863690653319</v>
+        <v>14.85863595637589</v>
       </c>
       <c r="E42" t="n">
-        <v>15.84860334529778</v>
+        <v>15.84860233183562</v>
       </c>
       <c r="F42" t="n">
         <v>3770700</v>
@@ -1312,16 +1312,16 @@
         <v>43843</v>
       </c>
       <c r="B45" t="n">
-        <v>15.39945030212402</v>
+        <v>15.39945125579834</v>
       </c>
       <c r="C45" t="n">
-        <v>15.44528305053748</v>
+        <v>15.44528400705018</v>
       </c>
       <c r="D45" t="n">
-        <v>15.06946325525004</v>
+        <v>15.06946418848855</v>
       </c>
       <c r="E45" t="n">
-        <v>15.11529425532292</v>
+        <v>15.1152951913997</v>
       </c>
       <c r="F45" t="n">
         <v>2402600</v>
@@ -1352,16 +1352,16 @@
         <v>43845</v>
       </c>
       <c r="B47" t="n">
-        <v>15.76610565185547</v>
+        <v>15.76610660552979</v>
       </c>
       <c r="C47" t="n">
-        <v>15.76610565185547</v>
+        <v>15.76610660552979</v>
       </c>
       <c r="D47" t="n">
-        <v>15.35361964852889</v>
+        <v>15.35362057725238</v>
       </c>
       <c r="E47" t="n">
-        <v>15.72027290240772</v>
+        <v>15.72027385330967</v>
       </c>
       <c r="F47" t="n">
         <v>1838000</v>
@@ -1412,16 +1412,16 @@
         <v>43850</v>
       </c>
       <c r="B50" t="n">
-        <v>16.16025733947754</v>
+        <v>16.16025924682617</v>
       </c>
       <c r="C50" t="n">
-        <v>16.44441515039353</v>
+        <v>16.44441709128049</v>
       </c>
       <c r="D50" t="n">
-        <v>16.14192598743512</v>
+        <v>16.14192789262016</v>
       </c>
       <c r="E50" t="n">
-        <v>16.2427545428608</v>
+        <v>16.24275645994634</v>
       </c>
       <c r="F50" t="n">
         <v>998100</v>
@@ -1492,16 +1492,16 @@
         <v>43854</v>
       </c>
       <c r="B54" t="n">
-        <v>15.73860740661621</v>
+        <v>15.73860549926758</v>
       </c>
       <c r="C54" t="n">
-        <v>15.80277151322809</v>
+        <v>15.80276959810347</v>
       </c>
       <c r="D54" t="n">
-        <v>15.39945202380098</v>
+        <v>15.39945015755431</v>
       </c>
       <c r="E54" t="n">
-        <v>15.57361299056236</v>
+        <v>15.57361110320926</v>
       </c>
       <c r="F54" t="n">
         <v>887500</v>
@@ -1532,16 +1532,16 @@
         <v>43858</v>
       </c>
       <c r="B56" t="n">
-        <v>15.39945030212402</v>
+        <v>15.39945125579834</v>
       </c>
       <c r="C56" t="n">
-        <v>15.66527499790033</v>
+        <v>15.66527596803693</v>
       </c>
       <c r="D56" t="n">
-        <v>15.05113015588466</v>
+        <v>15.05113108798782</v>
       </c>
       <c r="E56" t="n">
-        <v>15.05113015588466</v>
+        <v>15.05113108798782</v>
       </c>
       <c r="F56" t="n">
         <v>696700</v>
@@ -1632,16 +1632,16 @@
         <v>43865</v>
       </c>
       <c r="B61" t="n">
-        <v>14.92280292510986</v>
+        <v>14.92280197143555</v>
       </c>
       <c r="C61" t="n">
-        <v>15.03279803175682</v>
+        <v>15.03279707105302</v>
       </c>
       <c r="D61" t="n">
-        <v>14.68447786292053</v>
+        <v>14.6844769244769</v>
       </c>
       <c r="E61" t="n">
-        <v>14.92280292510986</v>
+        <v>14.92280197143555</v>
       </c>
       <c r="F61" t="n">
         <v>708300</v>
@@ -1652,16 +1652,16 @@
         <v>43866</v>
       </c>
       <c r="B62" t="n">
-        <v>14.8678035736084</v>
+        <v>14.86780261993408</v>
       </c>
       <c r="C62" t="n">
-        <v>15.21612548961779</v>
+        <v>15.21612451360086</v>
       </c>
       <c r="D62" t="n">
-        <v>14.69364436394439</v>
+        <v>14.69364342144127</v>
       </c>
       <c r="E62" t="n">
-        <v>14.93196942533485</v>
+        <v>14.9319684675447</v>
       </c>
       <c r="F62" t="n">
         <v>931900</v>
@@ -1732,16 +1732,16 @@
         <v>43872</v>
       </c>
       <c r="B66" t="n">
-        <v>14.29032421112061</v>
+        <v>14.29032325744629</v>
       </c>
       <c r="C66" t="n">
-        <v>14.2994907609287</v>
+        <v>14.29948980664265</v>
       </c>
       <c r="D66" t="n">
-        <v>13.69451158614923</v>
+        <v>13.69451067223687</v>
       </c>
       <c r="E66" t="n">
-        <v>13.74951001082748</v>
+        <v>13.74950909324476</v>
       </c>
       <c r="F66" t="n">
         <v>1385400</v>
@@ -1852,16 +1852,16 @@
         <v>43880</v>
       </c>
       <c r="B72" t="n">
-        <v>15.67444133758545</v>
+        <v>15.67444229125977</v>
       </c>
       <c r="C72" t="n">
-        <v>16.20608897367475</v>
+        <v>16.20608995969591</v>
       </c>
       <c r="D72" t="n">
-        <v>15.39028529459131</v>
+        <v>15.39028623097682</v>
       </c>
       <c r="E72" t="n">
-        <v>15.39028529459131</v>
+        <v>15.39028623097682</v>
       </c>
       <c r="F72" t="n">
         <v>5335200</v>
@@ -1872,16 +1872,16 @@
         <v>43881</v>
       </c>
       <c r="B73" t="n">
-        <v>15.85776710510254</v>
+        <v>15.85776805877686</v>
       </c>
       <c r="C73" t="n">
-        <v>15.94026430291195</v>
+        <v>15.94026526154759</v>
       </c>
       <c r="D73" t="n">
-        <v>15.53694661177767</v>
+        <v>15.53694754615808</v>
       </c>
       <c r="E73" t="n">
-        <v>15.67444135867984</v>
+        <v>15.67444230132908</v>
       </c>
       <c r="F73" t="n">
         <v>1537600</v>
@@ -1992,16 +1992,16 @@
         <v>43893</v>
       </c>
       <c r="B79" t="n">
-        <v>14.34532165527344</v>
+        <v>14.34532260894775</v>
       </c>
       <c r="C79" t="n">
-        <v>14.70281010177617</v>
+        <v>14.70281107921626</v>
       </c>
       <c r="D79" t="n">
-        <v>14.25365878038302</v>
+        <v>14.2536597279636</v>
       </c>
       <c r="E79" t="n">
-        <v>14.49198382860465</v>
+        <v>14.49198479202903</v>
       </c>
       <c r="F79" t="n">
         <v>2555600</v>
@@ -2092,16 +2092,16 @@
         <v>43900</v>
       </c>
       <c r="B84" t="n">
-        <v>11.55875396728516</v>
+        <v>11.55875492095947</v>
       </c>
       <c r="C84" t="n">
-        <v>11.60458584030314</v>
+        <v>11.60458679775889</v>
       </c>
       <c r="D84" t="n">
-        <v>10.61462122946393</v>
+        <v>10.614622105241</v>
       </c>
       <c r="E84" t="n">
-        <v>11.60458584030314</v>
+        <v>11.60458679775889</v>
       </c>
       <c r="F84" t="n">
         <v>1791400</v>
@@ -2192,16 +2192,16 @@
         <v>43907</v>
       </c>
       <c r="B89" t="n">
-        <v>6.920586585998535</v>
+        <v>6.920587062835693</v>
       </c>
       <c r="C89" t="n">
-        <v>7.79138867482094</v>
+        <v>7.791389211657462</v>
       </c>
       <c r="D89" t="n">
-        <v>6.8747547130773</v>
+        <v>6.874755186756584</v>
       </c>
       <c r="E89" t="n">
-        <v>7.626394281972599</v>
+        <v>7.626394807440799</v>
       </c>
       <c r="F89" t="n">
         <v>4217900</v>
@@ -2292,16 +2292,16 @@
         <v>43914</v>
       </c>
       <c r="B94" t="n">
-        <v>5.958121299743652</v>
+        <v>5.958120822906494</v>
       </c>
       <c r="C94" t="n">
-        <v>6.453103649678619</v>
+        <v>6.4531031332273</v>
       </c>
       <c r="D94" t="n">
-        <v>5.765628115092812</v>
+        <v>5.765627653661165</v>
       </c>
       <c r="E94" t="n">
-        <v>5.866457982549246</v>
+        <v>5.866457513048037</v>
       </c>
       <c r="F94" t="n">
         <v>2793300</v>
@@ -2312,16 +2312,16 @@
         <v>43915</v>
       </c>
       <c r="B95" t="n">
-        <v>6.453103065490723</v>
+        <v>6.453103542327881</v>
       </c>
       <c r="C95" t="n">
-        <v>6.856422061719535</v>
+        <v>6.856422568359019</v>
       </c>
       <c r="D95" t="n">
-        <v>5.609799749474583</v>
+        <v>5.609800163997789</v>
       </c>
       <c r="E95" t="n">
-        <v>5.95812076036562</v>
+        <v>5.958121200627203</v>
       </c>
       <c r="F95" t="n">
         <v>4465900</v>
@@ -2392,16 +2392,16 @@
         <v>43921</v>
       </c>
       <c r="B99" t="n">
-        <v>6.1414475440979</v>
+        <v>6.141448020935059</v>
       </c>
       <c r="C99" t="n">
-        <v>6.57226576317872</v>
+        <v>6.572266273465669</v>
       </c>
       <c r="D99" t="n">
-        <v>5.985620133306374</v>
+        <v>5.985620598044706</v>
       </c>
       <c r="E99" t="n">
-        <v>6.508101226675047</v>
+        <v>6.508101731980102</v>
       </c>
       <c r="F99" t="n">
         <v>3152400</v>
@@ -2432,16 +2432,16 @@
         <v>43923</v>
       </c>
       <c r="B101" t="n">
-        <v>5.536468982696533</v>
+        <v>5.536469459533691</v>
       </c>
       <c r="C101" t="n">
-        <v>5.793126679144077</v>
+        <v>5.793127178086285</v>
       </c>
       <c r="D101" t="n">
-        <v>5.334809707483203</v>
+        <v>5.334810166952138</v>
       </c>
       <c r="E101" t="n">
-        <v>5.408140353015323</v>
+        <v>5.408140818799975</v>
       </c>
       <c r="F101" t="n">
         <v>2769000</v>
@@ -2452,16 +2452,16 @@
         <v>43924</v>
       </c>
       <c r="B102" t="n">
-        <v>5.582300662994385</v>
+        <v>5.582301139831543</v>
       </c>
       <c r="C102" t="n">
-        <v>5.710629288268649</v>
+        <v>5.71062977606757</v>
       </c>
       <c r="D102" t="n">
-        <v>5.068985724812216</v>
+        <v>5.068986157802285</v>
       </c>
       <c r="E102" t="n">
-        <v>5.609799435582029</v>
+        <v>5.609799914768118</v>
       </c>
       <c r="F102" t="n">
         <v>3057300</v>
@@ -2472,16 +2472,16 @@
         <v>43927</v>
       </c>
       <c r="B103" t="n">
-        <v>6.233111381530762</v>
+        <v>6.23311185836792</v>
       </c>
       <c r="C103" t="n">
-        <v>6.324774694212212</v>
+        <v>6.324775178061675</v>
       </c>
       <c r="D103" t="n">
-        <v>5.637299193473606</v>
+        <v>5.637299624730736</v>
       </c>
       <c r="E103" t="n">
-        <v>6.00395288128456</v>
+        <v>6.00395334059094</v>
       </c>
       <c r="F103" t="n">
         <v>2488400</v>
@@ -2512,16 +2512,16 @@
         <v>43929</v>
       </c>
       <c r="B105" t="n">
-        <v>7.974715232849121</v>
+        <v>7.974715709686279</v>
       </c>
       <c r="C105" t="n">
-        <v>8.662190699028706</v>
+        <v>8.662191216972515</v>
       </c>
       <c r="D105" t="n">
-        <v>7.158911135366518</v>
+        <v>7.158911563423789</v>
       </c>
       <c r="E105" t="n">
-        <v>7.424735384407611</v>
+        <v>7.424735828359477</v>
       </c>
       <c r="F105" t="n">
         <v>3820500</v>
@@ -2532,16 +2532,16 @@
         <v>43930</v>
       </c>
       <c r="B106" t="n">
-        <v>7.883052825927734</v>
+        <v>7.883053302764893</v>
       </c>
       <c r="C106" t="n">
-        <v>8.653024659073285</v>
+        <v>8.653025182485189</v>
       </c>
       <c r="D106" t="n">
-        <v>7.718058424597103</v>
+        <v>7.718058891453932</v>
       </c>
       <c r="E106" t="n">
-        <v>8.12137700386382</v>
+        <v>8.121377495116946</v>
       </c>
       <c r="F106" t="n">
         <v>2853400</v>
@@ -2552,16 +2552,16 @@
         <v>43934</v>
       </c>
       <c r="B107" t="n">
-        <v>7.791388988494873</v>
+        <v>7.791389465332031</v>
       </c>
       <c r="C107" t="n">
-        <v>8.103044687901917</v>
+        <v>8.10304518381257</v>
       </c>
       <c r="D107" t="n">
-        <v>7.635561138791352</v>
+        <v>7.635561606091763</v>
       </c>
       <c r="E107" t="n">
-        <v>7.873886188240302</v>
+        <v>7.873886670126333</v>
       </c>
       <c r="F107" t="n">
         <v>2400700</v>
@@ -2572,16 +2572,16 @@
         <v>43935</v>
       </c>
       <c r="B108" t="n">
-        <v>7.699725151062012</v>
+        <v>7.69972562789917</v>
       </c>
       <c r="C108" t="n">
-        <v>8.561361589488603</v>
+        <v>8.561362119686144</v>
       </c>
       <c r="D108" t="n">
-        <v>7.699725151062012</v>
+        <v>7.69972562789917</v>
       </c>
       <c r="E108" t="n">
-        <v>7.965548972668025</v>
+        <v>7.965549465967418</v>
       </c>
       <c r="F108" t="n">
         <v>1715400</v>
@@ -2652,16 +2652,16 @@
         <v>43941</v>
       </c>
       <c r="B112" t="n">
-        <v>8.469697952270508</v>
+        <v>8.469698905944824</v>
       </c>
       <c r="C112" t="n">
-        <v>8.579693927396972</v>
+        <v>8.579694893456658</v>
       </c>
       <c r="D112" t="n">
-        <v>7.901384977031956</v>
+        <v>7.901385866715149</v>
       </c>
       <c r="E112" t="n">
-        <v>8.112211251652074</v>
+        <v>8.112212165073965</v>
       </c>
       <c r="F112" t="n">
         <v>1598000</v>
@@ -2712,16 +2712,16 @@
         <v>43945</v>
       </c>
       <c r="B115" t="n">
-        <v>7.278073787689209</v>
+        <v>7.278074264526367</v>
       </c>
       <c r="C115" t="n">
-        <v>8.268038844268698</v>
+        <v>8.268039385965343</v>
       </c>
       <c r="D115" t="n">
-        <v>7.140578604518296</v>
+        <v>7.14057907234719</v>
       </c>
       <c r="E115" t="n">
-        <v>8.240539195715323</v>
+        <v>8.240539735610273</v>
       </c>
       <c r="F115" t="n">
         <v>2904600</v>
@@ -2812,16 +2812,16 @@
         <v>43955</v>
       </c>
       <c r="B120" t="n">
-        <v>8.240540504455566</v>
+        <v>8.24053955078125</v>
       </c>
       <c r="C120" t="n">
-        <v>8.543029693221003</v>
+        <v>8.543028704539738</v>
       </c>
       <c r="D120" t="n">
-        <v>8.066380406809268</v>
+        <v>8.066379473290425</v>
       </c>
       <c r="E120" t="n">
-        <v>8.341370816824323</v>
+        <v>8.341369851480955</v>
       </c>
       <c r="F120" t="n">
         <v>1637500</v>
@@ -2832,16 +2832,16 @@
         <v>43956</v>
       </c>
       <c r="B121" t="n">
-        <v>7.892219066619873</v>
+        <v>7.892218589782715</v>
       </c>
       <c r="C121" t="n">
-        <v>8.790520914184377</v>
+        <v>8.790520383073043</v>
       </c>
       <c r="D121" t="n">
-        <v>7.892219066619873</v>
+        <v>7.892218589782715</v>
       </c>
       <c r="E121" t="n">
-        <v>8.570528946108718</v>
+        <v>8.570528428288998</v>
       </c>
       <c r="F121" t="n">
         <v>2603100</v>
@@ -2852,16 +2852,16 @@
         <v>43957</v>
       </c>
       <c r="B122" t="n">
-        <v>7.828054428100586</v>
+        <v>7.828054904937744</v>
       </c>
       <c r="C122" t="n">
-        <v>8.148876681992785</v>
+        <v>8.148877178372471</v>
       </c>
       <c r="D122" t="n">
-        <v>7.553064049645888</v>
+        <v>7.553064509732316</v>
       </c>
       <c r="E122" t="n">
-        <v>7.928883854726839</v>
+        <v>7.928884337705908</v>
       </c>
       <c r="F122" t="n">
         <v>2058000</v>
@@ -2932,16 +2932,16 @@
         <v>43963</v>
       </c>
       <c r="B126" t="n">
-        <v>6.498935222625732</v>
+        <v>6.498935699462891</v>
       </c>
       <c r="C126" t="n">
-        <v>7.213909500361801</v>
+        <v>7.213910029657753</v>
       </c>
       <c r="D126" t="n">
-        <v>6.416438022469589</v>
+        <v>6.416438493253797</v>
       </c>
       <c r="E126" t="n">
-        <v>6.728093723428218</v>
+        <v>6.728094217079098</v>
       </c>
       <c r="F126" t="n">
         <v>2413600</v>
@@ -3012,16 +3012,16 @@
         <v>43969</v>
       </c>
       <c r="B130" t="n">
-        <v>6.783092021942139</v>
+        <v>6.78309154510498</v>
       </c>
       <c r="C130" t="n">
-        <v>6.856422675624999</v>
+        <v>6.856422193632849</v>
       </c>
       <c r="D130" t="n">
-        <v>6.260610458824003</v>
+        <v>6.260610018716203</v>
       </c>
       <c r="E130" t="n">
-        <v>6.46227019353704</v>
+        <v>6.462269739252984</v>
       </c>
       <c r="F130" t="n">
         <v>4121800</v>
@@ -3072,16 +3072,16 @@
         <v>43972</v>
       </c>
       <c r="B133" t="n">
-        <v>7.727224826812744</v>
+        <v>7.727225303649902</v>
       </c>
       <c r="C133" t="n">
-        <v>7.873886125561454</v>
+        <v>7.873886611448894</v>
       </c>
       <c r="D133" t="n">
-        <v>7.461401004288134</v>
+        <v>7.461401464721644</v>
       </c>
       <c r="E133" t="n">
-        <v>7.55306387892093</v>
+        <v>7.553064345010839</v>
       </c>
       <c r="F133" t="n">
         <v>2073000</v>
@@ -3092,16 +3092,16 @@
         <v>43973</v>
       </c>
       <c r="B134" t="n">
-        <v>7.131412982940674</v>
+        <v>7.131412506103516</v>
       </c>
       <c r="C134" t="n">
-        <v>7.562230786971902</v>
+        <v>7.5622302813284</v>
       </c>
       <c r="D134" t="n">
-        <v>7.076414556218658</v>
+        <v>7.076414083058932</v>
       </c>
       <c r="E134" t="n">
-        <v>7.562230786971902</v>
+        <v>7.5622302813284</v>
       </c>
       <c r="F134" t="n">
         <v>2415900</v>
@@ -3112,16 +3112,16 @@
         <v>43976</v>
       </c>
       <c r="B135" t="n">
-        <v>7.754724025726318</v>
+        <v>7.754724502563477</v>
       </c>
       <c r="C135" t="n">
-        <v>7.828054679109565</v>
+        <v>7.828055160455818</v>
       </c>
       <c r="D135" t="n">
-        <v>7.39723643485523</v>
+        <v>7.397236889710515</v>
       </c>
       <c r="E135" t="n">
-        <v>7.39723643485523</v>
+        <v>7.397236889710515</v>
       </c>
       <c r="F135" t="n">
         <v>2073000</v>
@@ -3192,16 +3192,16 @@
         <v>43980</v>
       </c>
       <c r="B139" t="n">
-        <v>8.680523872375488</v>
+        <v>8.680524826049805</v>
       </c>
       <c r="C139" t="n">
-        <v>8.753854519464953</v>
+        <v>8.753855481195645</v>
       </c>
       <c r="D139" t="n">
-        <v>8.03888027325754</v>
+        <v>8.038881156438526</v>
       </c>
       <c r="E139" t="n">
-        <v>8.405533508704863</v>
+        <v>8.405534432167725</v>
       </c>
       <c r="F139" t="n">
         <v>6035800</v>
@@ -3332,16 +3332,16 @@
         <v>43991</v>
       </c>
       <c r="B146" t="n">
-        <v>11.93457412719727</v>
+        <v>11.93457508087158</v>
       </c>
       <c r="C146" t="n">
-        <v>12.34705921875477</v>
+        <v>12.34706020539017</v>
       </c>
       <c r="D146" t="n">
-        <v>11.05460552392848</v>
+        <v>11.0546064072858</v>
       </c>
       <c r="E146" t="n">
-        <v>11.27459745620312</v>
+        <v>11.27459835713967</v>
       </c>
       <c r="F146" t="n">
         <v>3964300</v>
@@ -3372,16 +3372,16 @@
         <v>43994</v>
       </c>
       <c r="B148" t="n">
-        <v>10.56879043579102</v>
+        <v>10.5687894821167</v>
       </c>
       <c r="C148" t="n">
-        <v>10.98127558673764</v>
+        <v>10.98127459584274</v>
       </c>
       <c r="D148" t="n">
-        <v>10.16547183521818</v>
+        <v>10.1654709179373</v>
       </c>
       <c r="E148" t="n">
-        <v>10.39463034954079</v>
+        <v>10.3946294115818</v>
       </c>
       <c r="F148" t="n">
         <v>3038200</v>
@@ -3532,16 +3532,16 @@
         <v>44006</v>
       </c>
       <c r="B156" t="n">
-        <v>9.441329956054688</v>
+        <v>9.441330909729004</v>
       </c>
       <c r="C156" t="n">
-        <v>10.03714167995876</v>
+        <v>10.03714269381637</v>
       </c>
       <c r="D156" t="n">
-        <v>9.29466866242724</v>
+        <v>9.294669601287213</v>
       </c>
       <c r="E156" t="n">
-        <v>10.03714167995876</v>
+        <v>10.03714269381637</v>
       </c>
       <c r="F156" t="n">
         <v>4939500</v>
@@ -3592,16 +3592,16 @@
         <v>44011</v>
       </c>
       <c r="B159" t="n">
-        <v>9.569659233093262</v>
+        <v>9.569658279418945</v>
       </c>
       <c r="C159" t="n">
-        <v>9.569659233093262</v>
+        <v>9.569658279418945</v>
       </c>
       <c r="D159" t="n">
-        <v>8.607194166278726</v>
+        <v>8.607193308519864</v>
       </c>
       <c r="E159" t="n">
-        <v>9.074676874039652</v>
+        <v>9.074675969693315</v>
       </c>
       <c r="F159" t="n">
         <v>2895200</v>
@@ -3672,16 +3672,16 @@
         <v>44015</v>
       </c>
       <c r="B163" t="n">
-        <v>9.102176666259766</v>
+        <v>9.102175712585449</v>
       </c>
       <c r="C163" t="n">
-        <v>9.248837978743365</v>
+        <v>9.24883700970271</v>
       </c>
       <c r="D163" t="n">
-        <v>8.909683475082447</v>
+        <v>8.909682541576473</v>
       </c>
       <c r="E163" t="n">
-        <v>9.010512908872327</v>
+        <v>9.010511964802019</v>
       </c>
       <c r="F163" t="n">
         <v>1732200</v>
@@ -3732,16 +3732,16 @@
         <v>44020</v>
       </c>
       <c r="B166" t="n">
-        <v>10.19297027587891</v>
+        <v>10.19296932220459</v>
       </c>
       <c r="C166" t="n">
-        <v>10.94460989832417</v>
+        <v>10.94460887432498</v>
       </c>
       <c r="D166" t="n">
-        <v>10.14713839969241</v>
+        <v>10.14713745030622</v>
       </c>
       <c r="E166" t="n">
-        <v>10.7704498178199</v>
+        <v>10.77044881011547</v>
       </c>
       <c r="F166" t="n">
         <v>5151100</v>
@@ -3892,16 +3892,16 @@
         <v>44032</v>
       </c>
       <c r="B174" t="n">
-        <v>10.11963844299316</v>
+        <v>10.11963939666748</v>
       </c>
       <c r="C174" t="n">
-        <v>10.28463282834655</v>
+        <v>10.28463379756993</v>
       </c>
       <c r="D174" t="n">
-        <v>10.00964247748098</v>
+        <v>10.00964342078928</v>
       </c>
       <c r="E174" t="n">
-        <v>10.17463686283437</v>
+        <v>10.17463782169173</v>
       </c>
       <c r="F174" t="n">
         <v>2184300</v>
@@ -3932,16 +3932,16 @@
         <v>44034</v>
       </c>
       <c r="B176" t="n">
-        <v>9.936311721801758</v>
+        <v>9.936312675476074</v>
       </c>
       <c r="C176" t="n">
-        <v>10.00047581575137</v>
+        <v>10.00047677558407</v>
       </c>
       <c r="D176" t="n">
-        <v>9.679654471833102</v>
+        <v>9.67965540087379</v>
       </c>
       <c r="E176" t="n">
-        <v>9.881313302580509</v>
+        <v>9.881314250976148</v>
       </c>
       <c r="F176" t="n">
         <v>2365200</v>
@@ -4072,16 +4072,16 @@
         <v>44043</v>
       </c>
       <c r="B183" t="n">
-        <v>9.285502433776855</v>
+        <v>9.285503387451172</v>
       </c>
       <c r="C183" t="n">
-        <v>9.844648853588344</v>
+        <v>9.844649864690203</v>
       </c>
       <c r="D183" t="n">
-        <v>9.221338334141029</v>
+        <v>9.221339281225324</v>
       </c>
       <c r="E183" t="n">
-        <v>9.652155680510571</v>
+        <v>9.652156671842278</v>
       </c>
       <c r="F183" t="n">
         <v>2007600</v>
@@ -4092,16 +4092,16 @@
         <v>44046</v>
       </c>
       <c r="B184" t="n">
-        <v>9.258003234863281</v>
+        <v>9.258004188537598</v>
       </c>
       <c r="C184" t="n">
-        <v>9.50549394653264</v>
+        <v>9.505494925701171</v>
       </c>
       <c r="D184" t="n">
-        <v>9.056343521309181</v>
+        <v>9.056344454210368</v>
       </c>
       <c r="E184" t="n">
-        <v>9.432163300543921</v>
+        <v>9.432164272158605</v>
       </c>
       <c r="F184" t="n">
         <v>2465200</v>
@@ -4112,16 +4112,16 @@
         <v>44047</v>
       </c>
       <c r="B185" t="n">
-        <v>8.845518112182617</v>
+        <v>8.845517158508301</v>
       </c>
       <c r="C185" t="n">
-        <v>9.239671028041045</v>
+        <v>9.239670031871364</v>
       </c>
       <c r="D185" t="n">
-        <v>8.735522132583359</v>
+        <v>8.735521190768194</v>
       </c>
       <c r="E185" t="n">
-        <v>9.17550692515073</v>
+        <v>9.175505935898864</v>
       </c>
       <c r="F185" t="n">
         <v>2392600</v>
@@ -4232,16 +4232,16 @@
         <v>44055</v>
       </c>
       <c r="B191" t="n">
-        <v>10.14713859558105</v>
+        <v>10.14713764190674</v>
       </c>
       <c r="C191" t="n">
-        <v>11.21960049786511</v>
+        <v>11.21959944339594</v>
       </c>
       <c r="D191" t="n">
-        <v>10.06464139168684</v>
+        <v>10.06464044576599</v>
       </c>
       <c r="E191" t="n">
-        <v>10.94461010960785</v>
+        <v>10.94460908098353</v>
       </c>
       <c r="F191" t="n">
         <v>5184500</v>
@@ -4352,16 +4352,16 @@
         <v>44063</v>
       </c>
       <c r="B197" t="n">
-        <v>9.853816032409668</v>
+        <v>9.853815078735352</v>
       </c>
       <c r="C197" t="n">
-        <v>9.945479787030456</v>
+        <v>9.945478824484717</v>
       </c>
       <c r="D197" t="n">
-        <v>9.010512636911677</v>
+        <v>9.010511764854147</v>
       </c>
       <c r="E197" t="n">
-        <v>9.074676740644019</v>
+        <v>9.074675862376543</v>
       </c>
       <c r="F197" t="n">
         <v>3999100</v>
@@ -4372,16 +4372,16 @@
         <v>44064</v>
       </c>
       <c r="B198" t="n">
-        <v>10.38546371459961</v>
+        <v>10.38546276092529</v>
       </c>
       <c r="C198" t="n">
-        <v>10.54129157300373</v>
+        <v>10.54129060502008</v>
       </c>
       <c r="D198" t="n">
-        <v>9.65215629990441</v>
+        <v>9.652155413568103</v>
       </c>
       <c r="E198" t="n">
-        <v>9.853816035633919</v>
+        <v>9.85381513077964</v>
       </c>
       <c r="F198" t="n">
         <v>4055100</v>
@@ -4472,16 +4472,16 @@
         <v>44071</v>
       </c>
       <c r="B203" t="n">
-        <v>11.07293796539307</v>
+        <v>11.07293891906738</v>
       </c>
       <c r="C203" t="n">
-        <v>11.12793638662728</v>
+        <v>11.12793734503842</v>
       </c>
       <c r="D203" t="n">
-        <v>10.35796373436977</v>
+        <v>10.3579646264658</v>
       </c>
       <c r="E203" t="n">
-        <v>10.51379157466809</v>
+        <v>10.51379248018504</v>
       </c>
       <c r="F203" t="n">
         <v>2710200</v>
@@ -4492,16 +4492,16 @@
         <v>44074</v>
       </c>
       <c r="B204" t="n">
-        <v>11.05460739135742</v>
+        <v>11.05460643768311</v>
       </c>
       <c r="C204" t="n">
-        <v>11.32043123963683</v>
+        <v>11.32043026303005</v>
       </c>
       <c r="D204" t="n">
-        <v>10.85294764895465</v>
+        <v>10.85294671267739</v>
       </c>
       <c r="E204" t="n">
-        <v>10.97211018427581</v>
+        <v>10.97210923771848</v>
       </c>
       <c r="F204" t="n">
         <v>3725900</v>
@@ -4652,16 +4652,16 @@
         <v>44085</v>
       </c>
       <c r="B212" t="n">
-        <v>10.83461284637451</v>
+        <v>10.83461380004883</v>
       </c>
       <c r="C212" t="n">
-        <v>11.54958794602793</v>
+        <v>11.54958896263513</v>
       </c>
       <c r="D212" t="n">
-        <v>10.66961933229085</v>
+        <v>10.66962027144226</v>
       </c>
       <c r="E212" t="n">
-        <v>11.43959110441184</v>
+        <v>11.43959211133699</v>
       </c>
       <c r="F212" t="n">
         <v>2696500</v>
@@ -4692,16 +4692,16 @@
         <v>44089</v>
       </c>
       <c r="B214" t="n">
-        <v>11.8245792388916</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="C214" t="n">
-        <v>12.09956963671544</v>
+        <v>12.09956866086264</v>
       </c>
       <c r="D214" t="n">
-        <v>11.62292037143511</v>
+        <v>11.62291943402496</v>
       </c>
       <c r="E214" t="n">
-        <v>12.01707242995125</v>
+        <v>12.017071460752</v>
       </c>
       <c r="F214" t="n">
         <v>2177400</v>
@@ -4732,16 +4732,16 @@
         <v>44091</v>
       </c>
       <c r="B216" t="n">
-        <v>12.11790084838867</v>
+        <v>12.11790180206299</v>
       </c>
       <c r="C216" t="n">
-        <v>12.13623307249431</v>
+        <v>12.13623402761137</v>
       </c>
       <c r="D216" t="n">
-        <v>11.57708668763366</v>
+        <v>11.5770875987461</v>
       </c>
       <c r="E216" t="n">
-        <v>11.91624113820522</v>
+        <v>11.916242076009</v>
       </c>
       <c r="F216" t="n">
         <v>2040800</v>
@@ -4812,16 +4812,16 @@
         <v>44097</v>
       </c>
       <c r="B220" t="n">
-        <v>10.97210884094238</v>
+        <v>10.9721097946167</v>
       </c>
       <c r="C220" t="n">
-        <v>11.67791654168333</v>
+        <v>11.67791755670507</v>
       </c>
       <c r="D220" t="n">
-        <v>10.83461322125006</v>
+        <v>10.83461416297352</v>
       </c>
       <c r="E220" t="n">
-        <v>11.54042179616128</v>
+        <v>11.54042279923225</v>
       </c>
       <c r="F220" t="n">
         <v>1980000</v>
@@ -4832,16 +4832,16 @@
         <v>44098</v>
       </c>
       <c r="B221" t="n">
-        <v>10.93544292449951</v>
+        <v>10.93544387817383</v>
       </c>
       <c r="C221" t="n">
-        <v>11.13710175711273</v>
+        <v>11.13710272837361</v>
       </c>
       <c r="D221" t="n">
-        <v>10.8804445047694</v>
+        <v>10.88044545364733</v>
       </c>
       <c r="E221" t="n">
-        <v>10.97210824626285</v>
+        <v>10.97210920313473</v>
       </c>
       <c r="F221" t="n">
         <v>1588600</v>
@@ -4852,16 +4852,16 @@
         <v>44099</v>
       </c>
       <c r="B222" t="n">
-        <v>11.30209732055664</v>
+        <v>11.30209636688232</v>
       </c>
       <c r="C222" t="n">
-        <v>11.30209732055664</v>
+        <v>11.30209636688232</v>
       </c>
       <c r="D222" t="n">
-        <v>10.63295491006448</v>
+        <v>10.6329540128526</v>
       </c>
       <c r="E222" t="n">
-        <v>10.843780313643</v>
+        <v>10.84377939864161</v>
       </c>
       <c r="F222" t="n">
         <v>2517800</v>
@@ -4872,16 +4872,16 @@
         <v>44102</v>
       </c>
       <c r="B223" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127555847168</v>
       </c>
       <c r="C223" t="n">
-        <v>11.44875814201422</v>
+        <v>11.44875913628738</v>
       </c>
       <c r="D223" t="n">
-        <v>10.8621129572749</v>
+        <v>10.86211390060056</v>
       </c>
       <c r="E223" t="n">
-        <v>11.39376059303005</v>
+        <v>11.39376158252692</v>
       </c>
       <c r="F223" t="n">
         <v>1430300</v>
@@ -4952,16 +4952,16 @@
         <v>44106</v>
       </c>
       <c r="B227" t="n">
-        <v>11.14626979827881</v>
+        <v>11.14626884460449</v>
       </c>
       <c r="C227" t="n">
-        <v>11.25626577829428</v>
+        <v>11.25626481520872</v>
       </c>
       <c r="D227" t="n">
-        <v>10.9354443884584</v>
+        <v>10.9354434528223</v>
       </c>
       <c r="E227" t="n">
-        <v>10.97210971513023</v>
+        <v>10.97210877635704</v>
       </c>
       <c r="F227" t="n">
         <v>1512600</v>
@@ -5072,16 +5072,16 @@
         <v>44117</v>
       </c>
       <c r="B233" t="n">
-        <v>11.19210147857666</v>
+        <v>11.19210052490234</v>
       </c>
       <c r="C233" t="n">
-        <v>11.27459868068182</v>
+        <v>11.27459771997795</v>
       </c>
       <c r="D233" t="n">
-        <v>10.6604538140882</v>
+        <v>10.66045290571536</v>
       </c>
       <c r="E233" t="n">
-        <v>10.67878604001694</v>
+        <v>10.67878513008202</v>
       </c>
       <c r="F233" t="n">
         <v>2120100</v>
@@ -5132,16 +5132,16 @@
         <v>44120</v>
       </c>
       <c r="B236" t="n">
-        <v>11.7329158782959</v>
+        <v>11.73291492462158</v>
       </c>
       <c r="C236" t="n">
-        <v>11.93457561171684</v>
+        <v>11.93457464165123</v>
       </c>
       <c r="D236" t="n">
-        <v>11.47625859205037</v>
+        <v>11.47625765923766</v>
       </c>
       <c r="E236" t="n">
-        <v>11.66875090110676</v>
+        <v>11.6687499526479</v>
       </c>
       <c r="F236" t="n">
         <v>3024000</v>
@@ -5212,16 +5212,16 @@
         <v>44126</v>
       </c>
       <c r="B240" t="n">
-        <v>11.45792484283447</v>
+        <v>11.45792579650879</v>
       </c>
       <c r="C240" t="n">
-        <v>11.77874708810196</v>
+        <v>11.77874806847918</v>
       </c>
       <c r="D240" t="n">
-        <v>11.19210102144753</v>
+        <v>11.1921019529966</v>
       </c>
       <c r="E240" t="n">
-        <v>11.71458211454628</v>
+        <v>11.71458308958288</v>
       </c>
       <c r="F240" t="n">
         <v>3089400</v>
@@ -5232,16 +5232,16 @@
         <v>44127</v>
       </c>
       <c r="B241" t="n">
-        <v>11.8245792388916</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="C241" t="n">
-        <v>11.8245792388916</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="D241" t="n">
-        <v>11.31126464551279</v>
+        <v>11.31126373323825</v>
       </c>
       <c r="E241" t="n">
-        <v>11.49459128600522</v>
+        <v>11.49459035894505</v>
       </c>
       <c r="F241" t="n">
         <v>1343300</v>
@@ -5292,16 +5292,16 @@
         <v>44132</v>
       </c>
       <c r="B244" t="n">
-        <v>11.37542724609375</v>
+        <v>11.37542819976807</v>
       </c>
       <c r="C244" t="n">
-        <v>11.66874983207301</v>
+        <v>11.66875081033842</v>
       </c>
       <c r="D244" t="n">
-        <v>11.08210466011449</v>
+        <v>11.08210558919771</v>
       </c>
       <c r="E244" t="n">
-        <v>11.66874983207301</v>
+        <v>11.66875081033842</v>
       </c>
       <c r="F244" t="n">
         <v>1933600</v>
@@ -5352,16 +5352,16 @@
         <v>44138</v>
       </c>
       <c r="B247" t="n">
-        <v>10.8712797164917</v>
+        <v>10.87127876281738</v>
       </c>
       <c r="C247" t="n">
-        <v>11.17376888857272</v>
+        <v>11.17376790836278</v>
       </c>
       <c r="D247" t="n">
-        <v>10.66962085121793</v>
+        <v>10.66961991523398</v>
       </c>
       <c r="E247" t="n">
-        <v>10.99960880053258</v>
+        <v>10.9996078356007</v>
       </c>
       <c r="F247" t="n">
         <v>2487500</v>
@@ -5372,16 +5372,16 @@
         <v>44139</v>
       </c>
       <c r="B248" t="n">
-        <v>11.7329158782959</v>
+        <v>11.73291492462158</v>
       </c>
       <c r="C248" t="n">
-        <v>11.82457875772699</v>
+        <v>11.82457779660214</v>
       </c>
       <c r="D248" t="n">
-        <v>10.89877904237016</v>
+        <v>10.89877815649612</v>
       </c>
       <c r="E248" t="n">
-        <v>10.99044192180125</v>
+        <v>10.99044102847667</v>
       </c>
       <c r="F248" t="n">
         <v>1346400</v>
@@ -5532,16 +5532,16 @@
         <v>44151</v>
       </c>
       <c r="B256" t="n">
-        <v>12.3745584487915</v>
+        <v>12.37455940246582</v>
       </c>
       <c r="C256" t="n">
-        <v>12.44788909559146</v>
+        <v>12.44789005491718</v>
       </c>
       <c r="D256" t="n">
-        <v>11.76958017560672</v>
+        <v>11.76958108265697</v>
       </c>
       <c r="E256" t="n">
-        <v>12.04457053819169</v>
+        <v>12.04457146643472</v>
       </c>
       <c r="F256" t="n">
         <v>2704300</v>
@@ -5572,16 +5572,16 @@
         <v>44153</v>
       </c>
       <c r="B258" t="n">
-        <v>12.64038372039795</v>
+        <v>12.64038276672363</v>
       </c>
       <c r="C258" t="n">
-        <v>12.76871280418928</v>
+        <v>12.76871184083297</v>
       </c>
       <c r="D258" t="n">
-        <v>12.31956144800481</v>
+        <v>12.31956051853545</v>
       </c>
       <c r="E258" t="n">
-        <v>12.57621961558747</v>
+        <v>12.57621866675412</v>
       </c>
       <c r="F258" t="n">
         <v>1757300</v>
@@ -5612,16 +5612,16 @@
         <v>44158</v>
       </c>
       <c r="B260" t="n">
-        <v>12.97953701019287</v>
+        <v>12.97953796386719</v>
       </c>
       <c r="C260" t="n">
-        <v>12.97953701019287</v>
+        <v>12.97953796386719</v>
       </c>
       <c r="D260" t="n">
-        <v>12.56705189424112</v>
+        <v>12.567052817608</v>
       </c>
       <c r="E260" t="n">
-        <v>12.84204226293238</v>
+        <v>12.84204320650424</v>
       </c>
       <c r="F260" t="n">
         <v>1993600</v>
@@ -5652,16 +5652,16 @@
         <v>44160</v>
       </c>
       <c r="B262" t="n">
-        <v>12.79621124267578</v>
+        <v>12.79621028900146</v>
       </c>
       <c r="C262" t="n">
-        <v>13.15369883323717</v>
+        <v>13.15369785292006</v>
       </c>
       <c r="D262" t="n">
-        <v>12.69538181290375</v>
+        <v>12.69538086674404</v>
       </c>
       <c r="E262" t="n">
-        <v>12.73204713956361</v>
+        <v>12.73204619067131</v>
       </c>
       <c r="F262" t="n">
         <v>852400</v>
@@ -5692,16 +5692,16 @@
         <v>44162</v>
       </c>
       <c r="B264" t="n">
-        <v>12.73204708099365</v>
+        <v>12.73204612731934</v>
       </c>
       <c r="C264" t="n">
-        <v>13.0162031427578</v>
+        <v>13.01620216779922</v>
       </c>
       <c r="D264" t="n">
-        <v>12.65871642801127</v>
+        <v>12.65871547982967</v>
       </c>
       <c r="E264" t="n">
-        <v>12.80537773397604</v>
+        <v>12.805376774809</v>
       </c>
       <c r="F264" t="n">
         <v>1000600</v>
@@ -5732,16 +5732,16 @@
         <v>44166</v>
       </c>
       <c r="B266" t="n">
-        <v>12.13623332977295</v>
+        <v>12.13623428344727</v>
       </c>
       <c r="C266" t="n">
-        <v>12.38372491672248</v>
+        <v>12.38372588984487</v>
       </c>
       <c r="D266" t="n">
-        <v>12.05373613412311</v>
+        <v>12.05373708131473</v>
       </c>
       <c r="E266" t="n">
-        <v>12.32872649489916</v>
+        <v>12.32872746369974</v>
       </c>
       <c r="F266" t="n">
         <v>1296100</v>
@@ -5772,16 +5772,16 @@
         <v>44168</v>
       </c>
       <c r="B268" t="n">
-        <v>12.12706756591797</v>
+        <v>12.12706851959229</v>
       </c>
       <c r="C268" t="n">
-        <v>12.4112244944313</v>
+        <v>12.41122547045176</v>
       </c>
       <c r="D268" t="n">
-        <v>12.03540468916906</v>
+        <v>12.035405635635</v>
       </c>
       <c r="E268" t="n">
-        <v>12.3562260690457</v>
+        <v>12.35622704074108</v>
       </c>
       <c r="F268" t="n">
         <v>1428200</v>
@@ -5792,16 +5792,16 @@
         <v>44169</v>
       </c>
       <c r="B269" t="n">
-        <v>12.3745584487915</v>
+        <v>12.37455940246582</v>
       </c>
       <c r="C269" t="n">
-        <v>12.42039032158404</v>
+        <v>12.4203912787905</v>
       </c>
       <c r="D269" t="n">
-        <v>12.08123586159167</v>
+        <v>12.0812367926604</v>
       </c>
       <c r="E269" t="n">
-        <v>12.20039838118417</v>
+        <v>12.20039932143643</v>
       </c>
       <c r="F269" t="n">
         <v>1171300</v>
@@ -5852,16 +5852,16 @@
         <v>44174</v>
       </c>
       <c r="B272" t="n">
-        <v>12.05373764038086</v>
+        <v>12.05373668670654</v>
       </c>
       <c r="C272" t="n">
-        <v>12.30122925825741</v>
+        <v>12.30122828500191</v>
       </c>
       <c r="D272" t="n">
-        <v>11.87041100167807</v>
+        <v>11.87041006250829</v>
       </c>
       <c r="E272" t="n">
-        <v>12.27373048099458</v>
+        <v>12.27372950991475</v>
       </c>
       <c r="F272" t="n">
         <v>927800</v>
@@ -5892,16 +5892,16 @@
         <v>44176</v>
       </c>
       <c r="B274" t="n">
-        <v>12.05373764038086</v>
+        <v>12.05373668670654</v>
       </c>
       <c r="C274" t="n">
-        <v>12.35622681278306</v>
+        <v>12.35622583517624</v>
       </c>
       <c r="D274" t="n">
-        <v>11.96207475811465</v>
+        <v>11.96207381169257</v>
       </c>
       <c r="E274" t="n">
-        <v>12.15456794729517</v>
+        <v>12.15456698564331</v>
       </c>
       <c r="F274" t="n">
         <v>1470700</v>
@@ -5932,16 +5932,16 @@
         <v>44180</v>
       </c>
       <c r="B276" t="n">
-        <v>12.51205348968506</v>
+        <v>12.51205444335938</v>
       </c>
       <c r="C276" t="n">
-        <v>12.60371723744367</v>
+        <v>12.60371819810464</v>
       </c>
       <c r="D276" t="n">
-        <v>12.16373334621101</v>
+        <v>12.16373427333621</v>
       </c>
       <c r="E276" t="n">
-        <v>12.24622967018942</v>
+        <v>12.24623060360253</v>
       </c>
       <c r="F276" t="n">
         <v>865800</v>
@@ -5972,16 +5972,16 @@
         <v>44182</v>
       </c>
       <c r="B278" t="n">
-        <v>12.32872676849365</v>
+        <v>12.32872772216797</v>
       </c>
       <c r="C278" t="n">
-        <v>12.61288368490788</v>
+        <v>12.61288466056282</v>
       </c>
       <c r="D278" t="n">
-        <v>12.24622957101306</v>
+        <v>12.24623051830591</v>
       </c>
       <c r="E278" t="n">
-        <v>12.54871871232837</v>
+        <v>12.54871968301991</v>
       </c>
       <c r="F278" t="n">
         <v>839700</v>
@@ -6052,16 +6052,16 @@
         <v>44188</v>
       </c>
       <c r="B282" t="n">
-        <v>11.7329158782959</v>
+        <v>11.73291492462158</v>
       </c>
       <c r="C282" t="n">
-        <v>11.87957718472192</v>
+        <v>11.87957621912668</v>
       </c>
       <c r="D282" t="n">
-        <v>11.66875090110676</v>
+        <v>11.6687499526479</v>
       </c>
       <c r="E282" t="n">
-        <v>11.7695812049024</v>
+        <v>11.76958024824786</v>
       </c>
       <c r="F282" t="n">
         <v>692800</v>
@@ -6092,16 +6092,16 @@
         <v>44194</v>
       </c>
       <c r="B284" t="n">
-        <v>11.9162425994873</v>
+        <v>11.91624164581299</v>
       </c>
       <c r="C284" t="n">
-        <v>12.09040268361409</v>
+        <v>12.09040171600149</v>
       </c>
       <c r="D284" t="n">
-        <v>11.70541718848276</v>
+        <v>11.70541625168111</v>
       </c>
       <c r="E284" t="n">
-        <v>11.78791351832996</v>
+        <v>11.78791257492601</v>
       </c>
       <c r="F284" t="n">
         <v>969100</v>
@@ -6172,16 +6172,16 @@
         <v>44202</v>
       </c>
       <c r="B288" t="n">
-        <v>11.07293796539307</v>
+        <v>11.07293891906738</v>
       </c>
       <c r="C288" t="n">
-        <v>11.36626054752155</v>
+        <v>11.36626152645873</v>
       </c>
       <c r="D288" t="n">
-        <v>10.91711012509475</v>
+        <v>10.91711106534815</v>
       </c>
       <c r="E288" t="n">
-        <v>11.2837642269256</v>
+        <v>11.28376519875766</v>
       </c>
       <c r="F288" t="n">
         <v>1263500</v>
@@ -6252,16 +6252,16 @@
         <v>44208</v>
       </c>
       <c r="B292" t="n">
-        <v>10.88044548034668</v>
+        <v>10.880446434021</v>
       </c>
       <c r="C292" t="n">
-        <v>11.03627333035545</v>
+        <v>11.03627429768813</v>
       </c>
       <c r="D292" t="n">
-        <v>10.65128698023617</v>
+        <v>10.65128791382467</v>
       </c>
       <c r="E292" t="n">
-        <v>10.981274905694</v>
+        <v>10.98127586820604</v>
       </c>
       <c r="F292" t="n">
         <v>1241200</v>
@@ -6312,16 +6312,16 @@
         <v>44211</v>
       </c>
       <c r="B295" t="n">
-        <v>11.34792900085449</v>
+        <v>11.34792804718018</v>
       </c>
       <c r="C295" t="n">
-        <v>11.34792900085449</v>
+        <v>11.34792804718018</v>
       </c>
       <c r="D295" t="n">
-        <v>10.9354438765626</v>
+        <v>10.93544295755333</v>
       </c>
       <c r="E295" t="n">
-        <v>11.18293460146961</v>
+        <v>11.18293366166134</v>
       </c>
       <c r="F295" t="n">
         <v>2333900</v>
@@ -6332,16 +6332,16 @@
         <v>44214</v>
       </c>
       <c r="B296" t="n">
-        <v>11.29293060302734</v>
+        <v>11.29292964935303</v>
       </c>
       <c r="C296" t="n">
-        <v>11.44875845299908</v>
+        <v>11.44875748616529</v>
       </c>
       <c r="D296" t="n">
-        <v>11.04543987753537</v>
+        <v>11.04543894476135</v>
       </c>
       <c r="E296" t="n">
-        <v>11.40292657815381</v>
+        <v>11.40292561519047</v>
       </c>
       <c r="F296" t="n">
         <v>2481600</v>
@@ -6352,16 +6352,16 @@
         <v>44215</v>
       </c>
       <c r="B297" t="n">
-        <v>11.34792900085449</v>
+        <v>11.34792804718018</v>
       </c>
       <c r="C297" t="n">
-        <v>11.54958872519487</v>
+        <v>11.54958775457317</v>
       </c>
       <c r="D297" t="n">
-        <v>10.86211322665161</v>
+        <v>10.86211231380501</v>
       </c>
       <c r="E297" t="n">
-        <v>11.35709555063594</v>
+        <v>11.35709459619127</v>
       </c>
       <c r="F297" t="n">
         <v>3202200</v>
@@ -6372,16 +6372,16 @@
         <v>44216</v>
       </c>
       <c r="B298" t="n">
-        <v>11.41209316253662</v>
+        <v>11.41209411621094</v>
       </c>
       <c r="C298" t="n">
-        <v>11.59541978830289</v>
+        <v>11.59542075729726</v>
       </c>
       <c r="D298" t="n">
-        <v>11.07293868632644</v>
+        <v>11.07293961165864</v>
       </c>
       <c r="E298" t="n">
-        <v>11.36626128755248</v>
+        <v>11.36626223739676</v>
       </c>
       <c r="F298" t="n">
         <v>2742100</v>
@@ -6412,16 +6412,16 @@
         <v>44218</v>
       </c>
       <c r="B300" t="n">
-        <v>11.00877571105957</v>
+        <v>11.00877475738525</v>
       </c>
       <c r="C300" t="n">
-        <v>11.19210235556369</v>
+        <v>11.19210138600805</v>
       </c>
       <c r="D300" t="n">
-        <v>10.82544906655545</v>
+        <v>10.82544812876246</v>
       </c>
       <c r="E300" t="n">
-        <v>11.09127291962902</v>
+        <v>11.09127195880809</v>
       </c>
       <c r="F300" t="n">
         <v>3052400</v>
@@ -6432,16 +6432,16 @@
         <v>44222</v>
       </c>
       <c r="B301" t="n">
-        <v>11.30209732055664</v>
+        <v>11.30209636688232</v>
       </c>
       <c r="C301" t="n">
-        <v>11.70541677617602</v>
+        <v>11.70541578846949</v>
       </c>
       <c r="D301" t="n">
-        <v>10.93544406469386</v>
+        <v>10.93544314195785</v>
       </c>
       <c r="E301" t="n">
-        <v>11.03627349151354</v>
+        <v>11.03627256026952</v>
       </c>
       <c r="F301" t="n">
         <v>3718300</v>
@@ -6452,16 +6452,16 @@
         <v>44223</v>
       </c>
       <c r="B302" t="n">
-        <v>11.51292324066162</v>
+        <v>11.51292419433594</v>
       </c>
       <c r="C302" t="n">
-        <v>11.54042201545451</v>
+        <v>11.54042297140669</v>
       </c>
       <c r="D302" t="n">
-        <v>11.04543969833101</v>
+        <v>11.04544061328127</v>
       </c>
       <c r="E302" t="n">
-        <v>11.29293041980761</v>
+        <v>11.2929313552588</v>
       </c>
       <c r="F302" t="n">
         <v>2242600</v>
@@ -6492,16 +6492,16 @@
         <v>44225</v>
       </c>
       <c r="B304" t="n">
-        <v>11.45792484283447</v>
+        <v>11.45792579650879</v>
       </c>
       <c r="C304" t="n">
-        <v>11.98040593593323</v>
+        <v>11.98040693309507</v>
       </c>
       <c r="D304" t="n">
-        <v>11.19210102144753</v>
+        <v>11.1921019529966</v>
       </c>
       <c r="E304" t="n">
-        <v>11.88874306169273</v>
+        <v>11.88874405122522</v>
       </c>
       <c r="F304" t="n">
         <v>4526000</v>
@@ -6552,16 +6552,16 @@
         <v>44230</v>
       </c>
       <c r="B307" t="n">
-        <v>11.34792900085449</v>
+        <v>11.34792804718018</v>
       </c>
       <c r="C307" t="n">
-        <v>11.52208907585052</v>
+        <v>11.52208810753988</v>
       </c>
       <c r="D307" t="n">
-        <v>11.15543582629557</v>
+        <v>11.15543488879828</v>
       </c>
       <c r="E307" t="n">
-        <v>11.43959187615808</v>
+        <v>11.43959091478046</v>
       </c>
       <c r="F307" t="n">
         <v>1665300</v>
@@ -6832,16 +6832,16 @@
         <v>44252</v>
       </c>
       <c r="B321" t="n">
-        <v>10.56879043579102</v>
+        <v>10.5687894821167</v>
       </c>
       <c r="C321" t="n">
-        <v>10.8987792558846</v>
+        <v>10.89877827243376</v>
       </c>
       <c r="D321" t="n">
-        <v>10.37629724879321</v>
+        <v>10.37629631248851</v>
       </c>
       <c r="E321" t="n">
-        <v>10.56879043579102</v>
+        <v>10.5687894821167</v>
       </c>
       <c r="F321" t="n">
         <v>1514700</v>
@@ -6852,16 +6852,16 @@
         <v>44253</v>
       </c>
       <c r="B322" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C322" t="n">
-        <v>10.651287786344</v>
+        <v>10.65128678074554</v>
       </c>
       <c r="D322" t="n">
-        <v>9.945480007155426</v>
+        <v>9.945479068192968</v>
       </c>
       <c r="E322" t="n">
-        <v>10.6054559080192</v>
+        <v>10.60545490674777</v>
       </c>
       <c r="F322" t="n">
         <v>2794300</v>
@@ -6872,16 +6872,16 @@
         <v>44256</v>
       </c>
       <c r="B323" t="n">
-        <v>9.927145957946777</v>
+        <v>9.927146911621094</v>
       </c>
       <c r="C323" t="n">
-        <v>10.24796820140604</v>
+        <v>10.24796918590089</v>
       </c>
       <c r="D323" t="n">
-        <v>9.780484660652355</v>
+        <v>9.780485600237313</v>
       </c>
       <c r="E323" t="n">
-        <v>10.14713790388841</v>
+        <v>10.14713887869676</v>
       </c>
       <c r="F323" t="n">
         <v>1920500</v>
@@ -6892,16 +6892,16 @@
         <v>44257</v>
       </c>
       <c r="B324" t="n">
-        <v>9.679655075073242</v>
+        <v>9.679656028747559</v>
       </c>
       <c r="C324" t="n">
-        <v>9.954644565806294</v>
+        <v>9.954645546573563</v>
       </c>
       <c r="D324" t="n">
-        <v>9.276335640102959</v>
+        <v>9.2763365540408</v>
       </c>
       <c r="E324" t="n">
-        <v>9.917979242097203</v>
+        <v>9.917980219252071</v>
       </c>
       <c r="F324" t="n">
         <v>2798500</v>
@@ -6912,16 +6912,16 @@
         <v>44258</v>
       </c>
       <c r="B325" t="n">
-        <v>9.752986907958984</v>
+        <v>9.752985954284668</v>
       </c>
       <c r="C325" t="n">
-        <v>9.817151013706422</v>
+        <v>9.81715005375796</v>
       </c>
       <c r="D325" t="n">
-        <v>9.184673884304942</v>
+        <v>9.184672986201862</v>
       </c>
       <c r="E325" t="n">
-        <v>9.578825943543972</v>
+        <v>9.578825006899601</v>
       </c>
       <c r="F325" t="n">
         <v>2305100</v>
@@ -7032,16 +7032,16 @@
         <v>44266</v>
       </c>
       <c r="B331" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C331" t="n">
-        <v>10.24796918026058</v>
+        <v>10.24796821273983</v>
       </c>
       <c r="D331" t="n">
-        <v>9.32216855994705</v>
+        <v>9.322167679832035</v>
       </c>
       <c r="E331" t="n">
-        <v>9.404665766097615</v>
+        <v>9.404664878193957</v>
       </c>
       <c r="F331" t="n">
         <v>2921600</v>
@@ -7052,16 +7052,16 @@
         <v>44267</v>
       </c>
       <c r="B332" t="n">
-        <v>10.02797508239746</v>
+        <v>10.02797603607178</v>
       </c>
       <c r="C332" t="n">
-        <v>10.2571335711322</v>
+        <v>10.25713454659981</v>
       </c>
       <c r="D332" t="n">
-        <v>9.826316241713474</v>
+        <v>9.826317176209756</v>
       </c>
       <c r="E332" t="n">
-        <v>10.08297350432871</v>
+        <v>10.08297446323346</v>
       </c>
       <c r="F332" t="n">
         <v>2668700</v>
@@ -7132,16 +7132,16 @@
         <v>44273</v>
       </c>
       <c r="B336" t="n">
-        <v>9.762151718139648</v>
+        <v>9.762150764465332</v>
       </c>
       <c r="C336" t="n">
-        <v>10.19296994148664</v>
+        <v>10.19296894572527</v>
       </c>
       <c r="D336" t="n">
-        <v>9.633823518031825</v>
+        <v>9.633822576894017</v>
       </c>
       <c r="E336" t="n">
-        <v>10.19296994148664</v>
+        <v>10.19296894572527</v>
       </c>
       <c r="F336" t="n">
         <v>902100</v>
@@ -7152,16 +7152,16 @@
         <v>44274</v>
       </c>
       <c r="B337" t="n">
-        <v>9.972977638244629</v>
+        <v>9.972978591918945</v>
       </c>
       <c r="C337" t="n">
-        <v>10.10130670797058</v>
+        <v>10.10130767391647</v>
       </c>
       <c r="D337" t="n">
-        <v>9.679655049351345</v>
+        <v>9.679655974976443</v>
       </c>
       <c r="E337" t="n">
-        <v>9.826316343797988</v>
+        <v>9.826317283447693</v>
       </c>
       <c r="F337" t="n">
         <v>1607200</v>
@@ -7212,16 +7212,16 @@
         <v>44279</v>
       </c>
       <c r="B340" t="n">
-        <v>10.38546371459961</v>
+        <v>10.38546276092529</v>
       </c>
       <c r="C340" t="n">
-        <v>10.60545567675706</v>
+        <v>10.60545470288137</v>
       </c>
       <c r="D340" t="n">
-        <v>10.21130362976755</v>
+        <v>10.21130269208597</v>
       </c>
       <c r="E340" t="n">
-        <v>10.56879034973082</v>
+        <v>10.56878937922202</v>
       </c>
       <c r="F340" t="n">
         <v>3104200</v>
@@ -7272,16 +7272,16 @@
         <v>44284</v>
       </c>
       <c r="B343" t="n">
-        <v>9.853816032409668</v>
+        <v>9.853815078735352</v>
       </c>
       <c r="C343" t="n">
-        <v>10.06464144419899</v>
+        <v>10.06464047012052</v>
       </c>
       <c r="D343" t="n">
-        <v>9.734653501070783</v>
+        <v>9.734652558929284</v>
       </c>
       <c r="E343" t="n">
-        <v>10.04630921777704</v>
+        <v>10.04630824547281</v>
       </c>
       <c r="F343" t="n">
         <v>1233600</v>
@@ -7292,16 +7292,16 @@
         <v>44285</v>
       </c>
       <c r="B344" t="n">
-        <v>10.56879043579102</v>
+        <v>10.5687894821167</v>
       </c>
       <c r="C344" t="n">
-        <v>10.63295541423719</v>
+        <v>10.63295445477295</v>
       </c>
       <c r="D344" t="n">
-        <v>9.798817687799792</v>
+        <v>9.798816803603932</v>
       </c>
       <c r="E344" t="n">
-        <v>9.853816115872176</v>
+        <v>9.853815226713534</v>
       </c>
       <c r="F344" t="n">
         <v>2587600</v>
@@ -7352,16 +7352,16 @@
         <v>44291</v>
       </c>
       <c r="B347" t="n">
-        <v>10.9629430770874</v>
+        <v>10.96294212341309</v>
       </c>
       <c r="C347" t="n">
-        <v>11.08210560635872</v>
+        <v>11.08210464231837</v>
       </c>
       <c r="D347" t="n">
-        <v>10.71545146840767</v>
+        <v>10.71545053626282</v>
       </c>
       <c r="E347" t="n">
-        <v>10.75211679478574</v>
+        <v>10.75211585945135</v>
       </c>
       <c r="F347" t="n">
         <v>1391400</v>
@@ -7392,16 +7392,16 @@
         <v>44293</v>
       </c>
       <c r="B349" t="n">
-        <v>11.06377220153809</v>
+        <v>11.06377124786377</v>
       </c>
       <c r="C349" t="n">
-        <v>11.30209725352048</v>
+        <v>11.30209627930303</v>
       </c>
       <c r="D349" t="n">
-        <v>10.96294277531645</v>
+        <v>10.96294183033342</v>
       </c>
       <c r="E349" t="n">
-        <v>11.23793315266764</v>
+        <v>11.23793218398101</v>
       </c>
       <c r="F349" t="n">
         <v>944900</v>
@@ -7452,16 +7452,16 @@
         <v>44298</v>
       </c>
       <c r="B352" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127555847168</v>
       </c>
       <c r="C352" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127555847168</v>
       </c>
       <c r="D352" t="n">
-        <v>10.69711856198182</v>
+        <v>10.69711949097847</v>
       </c>
       <c r="E352" t="n">
-        <v>10.87127863265874</v>
+        <v>10.8712795767804</v>
       </c>
       <c r="F352" t="n">
         <v>1341200</v>
@@ -7552,16 +7552,16 @@
         <v>44305</v>
       </c>
       <c r="B357" t="n">
-        <v>12.23706436157227</v>
+        <v>12.23706531524658</v>
       </c>
       <c r="C357" t="n">
-        <v>12.86037489283644</v>
+        <v>12.86037589508738</v>
       </c>
       <c r="D357" t="n">
-        <v>12.10873528569743</v>
+        <v>12.10873622937064</v>
       </c>
       <c r="E357" t="n">
-        <v>12.66788171610934</v>
+        <v>12.66788270335866</v>
       </c>
       <c r="F357" t="n">
         <v>3426700</v>
@@ -7592,16 +7592,16 @@
         <v>44308</v>
       </c>
       <c r="B359" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127555847168</v>
       </c>
       <c r="C359" t="n">
-        <v>11.41209281796801</v>
+        <v>11.41209380905695</v>
       </c>
       <c r="D359" t="n">
-        <v>10.91711050625907</v>
+        <v>10.91711145436102</v>
       </c>
       <c r="E359" t="n">
-        <v>11.26543152178318</v>
+        <v>11.26543250013525</v>
       </c>
       <c r="F359" t="n">
         <v>4817400</v>
@@ -7612,16 +7612,16 @@
         <v>44309</v>
       </c>
       <c r="B360" t="n">
-        <v>11.02710628509521</v>
+        <v>11.02710723876953</v>
       </c>
       <c r="C360" t="n">
-        <v>11.18293412810254</v>
+        <v>11.18293509525356</v>
       </c>
       <c r="D360" t="n">
-        <v>10.70628492385739</v>
+        <v>10.70628584978561</v>
       </c>
       <c r="E360" t="n">
-        <v>11.14626880469907</v>
+        <v>11.1462697686791</v>
       </c>
       <c r="F360" t="n">
         <v>3824500</v>
@@ -7672,16 +7672,16 @@
         <v>44314</v>
       </c>
       <c r="B363" t="n">
-        <v>11.20126819610596</v>
+        <v>11.20126724243164</v>
       </c>
       <c r="C363" t="n">
-        <v>11.30209762564745</v>
+        <v>11.30209666338853</v>
       </c>
       <c r="D363" t="n">
-        <v>10.92627780970057</v>
+        <v>10.9262768794389</v>
       </c>
       <c r="E363" t="n">
-        <v>11.18293509573277</v>
+        <v>11.18293414361933</v>
       </c>
       <c r="F363" t="n">
         <v>1629600</v>
@@ -7692,16 +7692,16 @@
         <v>44315</v>
       </c>
       <c r="B364" t="n">
-        <v>11.4212589263916</v>
+        <v>11.42125988006592</v>
       </c>
       <c r="C364" t="n">
-        <v>11.59541899034182</v>
+        <v>11.59541995855849</v>
       </c>
       <c r="D364" t="n">
-        <v>11.08210447352099</v>
+        <v>11.08210539887593</v>
       </c>
       <c r="E364" t="n">
-        <v>11.21959921484115</v>
+        <v>11.2196001516769</v>
       </c>
       <c r="F364" t="n">
         <v>1614300</v>
@@ -7772,16 +7772,16 @@
         <v>44321</v>
       </c>
       <c r="B368" t="n">
-        <v>11.34792900085449</v>
+        <v>11.34792804718018</v>
       </c>
       <c r="C368" t="n">
-        <v>11.44875842593953</v>
+        <v>11.44875746379156</v>
       </c>
       <c r="D368" t="n">
-        <v>11.13710272673267</v>
+        <v>11.13710179077609</v>
       </c>
       <c r="E368" t="n">
-        <v>11.2745983509435</v>
+        <v>11.27459740343186</v>
       </c>
       <c r="F368" t="n">
         <v>936700</v>
@@ -7792,16 +7792,16 @@
         <v>44322</v>
       </c>
       <c r="B369" t="n">
-        <v>11.24709987640381</v>
+        <v>11.24709892272949</v>
       </c>
       <c r="C369" t="n">
-        <v>11.36626153006663</v>
+        <v>11.36626056628825</v>
       </c>
       <c r="D369" t="n">
-        <v>11.07293892258217</v>
+        <v>11.07293798367547</v>
       </c>
       <c r="E369" t="n">
-        <v>11.36626153006663</v>
+        <v>11.36626056628825</v>
       </c>
       <c r="F369" t="n">
         <v>1352700</v>
@@ -7892,16 +7892,16 @@
         <v>44329</v>
       </c>
       <c r="B374" t="n">
-        <v>11.16460132598877</v>
+        <v>11.16460227966309</v>
       </c>
       <c r="C374" t="n">
-        <v>11.43042512545659</v>
+        <v>11.43042610183743</v>
       </c>
       <c r="D374" t="n">
-        <v>11.10043635772397</v>
+        <v>11.10043730591735</v>
       </c>
       <c r="E374" t="n">
-        <v>11.13710167923091</v>
+        <v>11.13710263055622</v>
       </c>
       <c r="F374" t="n">
         <v>1639700</v>
@@ -7912,16 +7912,16 @@
         <v>44330</v>
       </c>
       <c r="B375" t="n">
-        <v>11.77874755859375</v>
+        <v>11.77874660491943</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0445713905988</v>
+        <v>12.04457041540187</v>
       </c>
       <c r="D375" t="n">
-        <v>11.19210146850625</v>
+        <v>11.19210056233014</v>
       </c>
       <c r="E375" t="n">
-        <v>11.21960024445979</v>
+        <v>11.21959933605722</v>
       </c>
       <c r="F375" t="n">
         <v>3767000</v>
@@ -7972,16 +7972,16 @@
         <v>44335</v>
       </c>
       <c r="B378" t="n">
-        <v>12.01707172393799</v>
+        <v>12.01707077026367</v>
       </c>
       <c r="C378" t="n">
-        <v>12.32872743155027</v>
+        <v>12.32872645314297</v>
       </c>
       <c r="D378" t="n">
-        <v>11.79707976827178</v>
+        <v>11.79707883205602</v>
       </c>
       <c r="E378" t="n">
-        <v>12.0995689258554</v>
+        <v>12.0995679656341</v>
       </c>
       <c r="F378" t="n">
         <v>1640700</v>
@@ -7992,16 +7992,16 @@
         <v>44336</v>
       </c>
       <c r="B379" t="n">
-        <v>12.5945520401001</v>
+        <v>12.59455108642578</v>
       </c>
       <c r="C379" t="n">
-        <v>12.5945520401001</v>
+        <v>12.59455108642578</v>
       </c>
       <c r="D379" t="n">
-        <v>11.86124460180745</v>
+        <v>11.86124370366004</v>
       </c>
       <c r="E379" t="n">
-        <v>12.05373779343214</v>
+        <v>12.05373688070891</v>
       </c>
       <c r="F379" t="n">
         <v>2196400</v>
@@ -8012,16 +8012,16 @@
         <v>44337</v>
       </c>
       <c r="B380" t="n">
-        <v>12.5945520401001</v>
+        <v>12.59455108642578</v>
       </c>
       <c r="C380" t="n">
-        <v>12.79621178231891</v>
+        <v>12.79621081337468</v>
       </c>
       <c r="D380" t="n">
-        <v>12.42955850025778</v>
+        <v>12.42955755907697</v>
       </c>
       <c r="E380" t="n">
-        <v>12.53038793428199</v>
+        <v>12.53038698546626</v>
       </c>
       <c r="F380" t="n">
         <v>1466000</v>
@@ -8112,16 +8112,16 @@
         <v>44344</v>
       </c>
       <c r="B385" t="n">
-        <v>12.73204708099365</v>
+        <v>12.73204612731934</v>
       </c>
       <c r="C385" t="n">
-        <v>13.13536567239676</v>
+        <v>13.13536468851249</v>
       </c>
       <c r="D385" t="n">
-        <v>12.62205110152008</v>
+        <v>12.62205015608484</v>
       </c>
       <c r="E385" t="n">
-        <v>12.7412127569887</v>
+        <v>12.74121180262784</v>
       </c>
       <c r="F385" t="n">
         <v>1492100</v>
@@ -8192,16 +8192,16 @@
         <v>44351</v>
       </c>
       <c r="B389" t="n">
-        <v>13.3553581237793</v>
+        <v>13.35535717010498</v>
       </c>
       <c r="C389" t="n">
-        <v>13.47452065781198</v>
+        <v>13.47451969562855</v>
       </c>
       <c r="D389" t="n">
-        <v>12.88787541232228</v>
+        <v>12.88787449202979</v>
       </c>
       <c r="E389" t="n">
-        <v>13.11703392988429</v>
+        <v>13.11703299322814</v>
       </c>
       <c r="F389" t="n">
         <v>1715000</v>
@@ -8212,16 +8212,16 @@
         <v>44354</v>
       </c>
       <c r="B390" t="n">
-        <v>13.23619365692139</v>
+        <v>13.2361946105957</v>
       </c>
       <c r="C390" t="n">
-        <v>13.53868366016865</v>
+        <v>13.53868463563752</v>
       </c>
       <c r="D390" t="n">
-        <v>13.11703201445974</v>
+        <v>13.1170329595484</v>
       </c>
       <c r="E390" t="n">
-        <v>13.53868366016865</v>
+        <v>13.53868463563752</v>
       </c>
       <c r="F390" t="n">
         <v>1299300</v>
@@ -8312,16 +8312,16 @@
         <v>44361</v>
       </c>
       <c r="B395" t="n">
-        <v>13.50201892852783</v>
+        <v>13.50201797485352</v>
       </c>
       <c r="C395" t="n">
-        <v>13.65784678455664</v>
+        <v>13.6578458198759</v>
       </c>
       <c r="D395" t="n">
-        <v>13.30036007004259</v>
+        <v>13.30035913061184</v>
       </c>
       <c r="E395" t="n">
-        <v>13.3186922961911</v>
+        <v>13.3186913554655</v>
       </c>
       <c r="F395" t="n">
         <v>1118700</v>
@@ -8472,16 +8472,16 @@
         <v>44371</v>
       </c>
       <c r="B403" t="n">
-        <v>13.49285316467285</v>
+        <v>13.49285221099854</v>
       </c>
       <c r="C403" t="n">
-        <v>13.63034791948745</v>
+        <v>13.63034695609501</v>
       </c>
       <c r="D403" t="n">
-        <v>13.29119343333049</v>
+        <v>13.29119249390948</v>
       </c>
       <c r="E403" t="n">
-        <v>13.40118941201623</v>
+        <v>13.40118846482071</v>
       </c>
       <c r="F403" t="n">
         <v>1276200</v>
@@ -8572,16 +8572,16 @@
         <v>44378</v>
       </c>
       <c r="B408" t="n">
-        <v>12.79621124267578</v>
+        <v>12.79621028900146</v>
       </c>
       <c r="C408" t="n">
-        <v>13.35535769278123</v>
+        <v>13.35535669743492</v>
       </c>
       <c r="D408" t="n">
-        <v>12.79621124267578</v>
+        <v>12.79621028900146</v>
       </c>
       <c r="E408" t="n">
-        <v>13.19952983593424</v>
+        <v>13.19952885220145</v>
       </c>
       <c r="F408" t="n">
         <v>1624000</v>
@@ -8632,16 +8632,16 @@
         <v>44383</v>
       </c>
       <c r="B411" t="n">
-        <v>12.51205348968506</v>
+        <v>12.51205444335938</v>
       </c>
       <c r="C411" t="n">
-        <v>12.69538098520229</v>
+        <v>12.69538195284991</v>
       </c>
       <c r="D411" t="n">
-        <v>12.18206557126056</v>
+        <v>12.18206649978305</v>
       </c>
       <c r="E411" t="n">
-        <v>12.69538098520229</v>
+        <v>12.69538195284991</v>
       </c>
       <c r="F411" t="n">
         <v>2034200</v>
@@ -8732,16 +8732,16 @@
         <v>44391</v>
       </c>
       <c r="B416" t="n">
-        <v>12.32872676849365</v>
+        <v>12.32872772216797</v>
       </c>
       <c r="C416" t="n">
-        <v>12.61288368490788</v>
+        <v>12.61288466056282</v>
       </c>
       <c r="D416" t="n">
-        <v>12.27372921962011</v>
+        <v>12.27373016904016</v>
       </c>
       <c r="E416" t="n">
-        <v>12.37455864200179</v>
+        <v>12.37455959922138</v>
       </c>
       <c r="F416" t="n">
         <v>2612300</v>
@@ -8752,16 +8752,16 @@
         <v>44392</v>
       </c>
       <c r="B417" t="n">
-        <v>12.06290340423584</v>
+        <v>12.06290245056152</v>
       </c>
       <c r="C417" t="n">
-        <v>12.45705630737188</v>
+        <v>12.45705532253645</v>
       </c>
       <c r="D417" t="n">
-        <v>12.05373685435586</v>
+        <v>12.05373590140624</v>
       </c>
       <c r="E417" t="n">
-        <v>12.29206190621348</v>
+        <v>12.29206093442225</v>
       </c>
       <c r="F417" t="n">
         <v>1763900</v>
@@ -8772,16 +8772,16 @@
         <v>44393</v>
       </c>
       <c r="B418" t="n">
-        <v>11.77874755859375</v>
+        <v>11.77874660491943</v>
       </c>
       <c r="C418" t="n">
-        <v>12.27372989660902</v>
+        <v>12.27372890285813</v>
       </c>
       <c r="D418" t="n">
-        <v>11.74208223259893</v>
+        <v>11.74208128189324</v>
       </c>
       <c r="E418" t="n">
-        <v>12.21873147053163</v>
+        <v>12.21873048123371</v>
       </c>
       <c r="F418" t="n">
         <v>2874100</v>
@@ -8892,16 +8892,16 @@
         <v>44403</v>
       </c>
       <c r="B424" t="n">
-        <v>11.45792484283447</v>
+        <v>11.45792579650879</v>
       </c>
       <c r="C424" t="n">
-        <v>11.81541241263221</v>
+        <v>11.81541339606119</v>
       </c>
       <c r="D424" t="n">
-        <v>11.29293044536316</v>
+        <v>11.29293138530454</v>
       </c>
       <c r="E424" t="n">
-        <v>11.76041398875168</v>
+        <v>11.76041496760299</v>
       </c>
       <c r="F424" t="n">
         <v>1317300</v>
@@ -8952,16 +8952,16 @@
         <v>44406</v>
       </c>
       <c r="B427" t="n">
-        <v>11.25626564025879</v>
+        <v>11.25626468658447</v>
       </c>
       <c r="C427" t="n">
-        <v>11.36626161892538</v>
+        <v>11.36626065593178</v>
       </c>
       <c r="D427" t="n">
-        <v>11.15543621169033</v>
+        <v>11.15543526655867</v>
       </c>
       <c r="E427" t="n">
-        <v>11.36626161892538</v>
+        <v>11.36626065593178</v>
       </c>
       <c r="F427" t="n">
         <v>743300</v>
@@ -9052,16 +9052,16 @@
         <v>44413</v>
       </c>
       <c r="B432" t="n">
-        <v>10.56879043579102</v>
+        <v>10.5687894821167</v>
       </c>
       <c r="C432" t="n">
-        <v>10.7796167235364</v>
+        <v>10.77961575083818</v>
       </c>
       <c r="D432" t="n">
-        <v>10.41296257611801</v>
+        <v>10.41296163650482</v>
       </c>
       <c r="E432" t="n">
-        <v>10.76128362278882</v>
+        <v>10.76128265174489</v>
       </c>
       <c r="F432" t="n">
         <v>2219600</v>
@@ -9132,16 +9132,16 @@
         <v>44419</v>
       </c>
       <c r="B436" t="n">
-        <v>9.890480995178223</v>
+        <v>9.890480041503906</v>
       </c>
       <c r="C436" t="n">
-        <v>10.51379240563549</v>
+        <v>10.51379139185933</v>
       </c>
       <c r="D436" t="n">
-        <v>9.74381969252247</v>
+        <v>9.743818752989743</v>
       </c>
       <c r="E436" t="n">
-        <v>10.51379240563549</v>
+        <v>10.51379139185933</v>
       </c>
       <c r="F436" t="n">
         <v>4618100</v>
@@ -9232,16 +9232,16 @@
         <v>44426</v>
       </c>
       <c r="B441" t="n">
-        <v>8.561361312866211</v>
+        <v>8.561362266540527</v>
       </c>
       <c r="C441" t="n">
-        <v>8.836351675269823</v>
+        <v>8.836352659576097</v>
       </c>
       <c r="D441" t="n">
-        <v>8.222206853097518</v>
+        <v>8.222207768992458</v>
       </c>
       <c r="E441" t="n">
-        <v>8.323036273838396</v>
+        <v>8.323037200965011</v>
       </c>
       <c r="F441" t="n">
         <v>4747100</v>
@@ -9252,16 +9252,16 @@
         <v>44427</v>
       </c>
       <c r="B442" t="n">
-        <v>8.561361312866211</v>
+        <v>8.561362266540527</v>
       </c>
       <c r="C442" t="n">
-        <v>8.735521380358682</v>
+        <v>8.735522353433183</v>
       </c>
       <c r="D442" t="n">
-        <v>8.268038725859832</v>
+        <v>8.268039646860114</v>
       </c>
       <c r="E442" t="n">
-        <v>8.341369372611426</v>
+        <v>8.341370301780216</v>
       </c>
       <c r="F442" t="n">
         <v>2305300</v>
@@ -9292,16 +9292,16 @@
         <v>44431</v>
       </c>
       <c r="B444" t="n">
-        <v>8.268039703369141</v>
+        <v>8.268038749694824</v>
       </c>
       <c r="C444" t="n">
-        <v>8.735522413137284</v>
+        <v>8.735521405541329</v>
       </c>
       <c r="D444" t="n">
-        <v>8.268039703369141</v>
+        <v>8.268038749694824</v>
       </c>
       <c r="E444" t="n">
-        <v>8.689690534956386</v>
+        <v>8.689689532646893</v>
       </c>
       <c r="F444" t="n">
         <v>2564400</v>
@@ -9312,16 +9312,16 @@
         <v>44432</v>
       </c>
       <c r="B445" t="n">
-        <v>9.21217155456543</v>
+        <v>9.212172508239746</v>
       </c>
       <c r="C445" t="n">
-        <v>9.230503779359537</v>
+        <v>9.230504734931666</v>
       </c>
       <c r="D445" t="n">
-        <v>8.286371036950763</v>
+        <v>8.286371894783164</v>
       </c>
       <c r="E445" t="n">
-        <v>8.396367008226228</v>
+        <v>8.396367877445774</v>
       </c>
       <c r="F445" t="n">
         <v>13858100</v>
@@ -9352,16 +9352,16 @@
         <v>44434</v>
       </c>
       <c r="B447" t="n">
-        <v>8.488030433654785</v>
+        <v>8.488031387329102</v>
       </c>
       <c r="C447" t="n">
-        <v>9.093008689872168</v>
+        <v>9.093009711518935</v>
       </c>
       <c r="D447" t="n">
-        <v>8.451365111283133</v>
+        <v>8.451366060837909</v>
       </c>
       <c r="E447" t="n">
-        <v>8.928014302114612</v>
+        <v>8.928015305223402</v>
       </c>
       <c r="F447" t="n">
         <v>2819100</v>
@@ -9372,16 +9372,16 @@
         <v>44435</v>
       </c>
       <c r="B448" t="n">
-        <v>8.680523872375488</v>
+        <v>8.680524826049805</v>
       </c>
       <c r="C448" t="n">
-        <v>8.799686392438435</v>
+        <v>8.799687359204386</v>
       </c>
       <c r="D448" t="n">
-        <v>8.451365381678345</v>
+        <v>8.451366310176466</v>
       </c>
       <c r="E448" t="n">
-        <v>8.588860126428523</v>
+        <v>8.588861070032324</v>
       </c>
       <c r="F448" t="n">
         <v>2539200</v>
@@ -9452,16 +9452,16 @@
         <v>44441</v>
       </c>
       <c r="B452" t="n">
-        <v>7.901384830474854</v>
+        <v>7.901385307312012</v>
       </c>
       <c r="C452" t="n">
-        <v>8.093878001918325</v>
+        <v>8.093878490372168</v>
       </c>
       <c r="D452" t="n">
-        <v>7.892218280841762</v>
+        <v>7.892218757125733</v>
       </c>
       <c r="E452" t="n">
-        <v>8.07554577682243</v>
+        <v>8.075546264169951</v>
       </c>
       <c r="F452" t="n">
         <v>2507800</v>
@@ -9492,16 +9492,16 @@
         <v>44445</v>
       </c>
       <c r="B454" t="n">
-        <v>8.359702110290527</v>
+        <v>8.359701156616211</v>
       </c>
       <c r="C454" t="n">
-        <v>8.396367435916657</v>
+        <v>8.396366478059562</v>
       </c>
       <c r="D454" t="n">
-        <v>7.910551652827854</v>
+        <v>7.910550750392595</v>
       </c>
       <c r="E454" t="n">
-        <v>8.00221452980802</v>
+        <v>8.002213616915865</v>
       </c>
       <c r="F454" t="n">
         <v>1394500</v>
@@ -9532,16 +9532,16 @@
         <v>44448</v>
       </c>
       <c r="B456" t="n">
-        <v>7.956383228302002</v>
+        <v>7.95638370513916</v>
       </c>
       <c r="C456" t="n">
-        <v>8.075545750634898</v>
+        <v>8.075546234613633</v>
       </c>
       <c r="D456" t="n">
-        <v>7.626394435943123</v>
+        <v>7.626394893003591</v>
       </c>
       <c r="E456" t="n">
-        <v>7.883052579815647</v>
+        <v>7.883053052257997</v>
       </c>
       <c r="F456" t="n">
         <v>3062500</v>
@@ -9632,16 +9632,16 @@
         <v>44455</v>
       </c>
       <c r="B461" t="n">
-        <v>7.901384830474854</v>
+        <v>7.901385307312012</v>
       </c>
       <c r="C461" t="n">
-        <v>8.00221425392799</v>
+        <v>8.002214736850059</v>
       </c>
       <c r="D461" t="n">
-        <v>7.800555407021715</v>
+        <v>7.800555877773964</v>
       </c>
       <c r="E461" t="n">
-        <v>7.93805015483693</v>
+        <v>7.938050633886787</v>
       </c>
       <c r="F461" t="n">
         <v>1652200</v>
@@ -9792,16 +9792,16 @@
         <v>44467</v>
       </c>
       <c r="B469" t="n">
-        <v>6.838089466094971</v>
+        <v>6.838089942932129</v>
       </c>
       <c r="C469" t="n">
-        <v>7.177243930834942</v>
+        <v>7.177244431322193</v>
       </c>
       <c r="D469" t="n">
-        <v>6.810590254617477</v>
+        <v>6.810590729537046</v>
       </c>
       <c r="E469" t="n">
-        <v>7.168077818399203</v>
+        <v>7.168078318247279</v>
       </c>
       <c r="F469" t="n">
         <v>2567000</v>
@@ -9812,16 +9812,16 @@
         <v>44468</v>
       </c>
       <c r="B470" t="n">
-        <v>6.838089466094971</v>
+        <v>6.838089942932129</v>
       </c>
       <c r="C470" t="n">
-        <v>7.058081409574367</v>
+        <v>7.058081901752116</v>
       </c>
       <c r="D470" t="n">
-        <v>6.728093494355273</v>
+        <v>6.728093963522135</v>
       </c>
       <c r="E470" t="n">
-        <v>6.929752775878052</v>
+        <v>6.929753259107124</v>
       </c>
       <c r="F470" t="n">
         <v>1734200</v>
@@ -9872,16 +9872,16 @@
         <v>44473</v>
       </c>
       <c r="B473" t="n">
-        <v>6.88392162322998</v>
+        <v>6.883922100067139</v>
       </c>
       <c r="C473" t="n">
-        <v>7.05808170045277</v>
+        <v>7.058082189353691</v>
       </c>
       <c r="D473" t="n">
-        <v>6.792257872584105</v>
+        <v>6.792258343071875</v>
       </c>
       <c r="E473" t="n">
-        <v>6.911420398755618</v>
+        <v>6.911420877497569</v>
       </c>
       <c r="F473" t="n">
         <v>2556200</v>
@@ -9892,16 +9892,16 @@
         <v>44474</v>
       </c>
       <c r="B474" t="n">
-        <v>6.746426582336426</v>
+        <v>6.746426105499268</v>
       </c>
       <c r="C474" t="n">
-        <v>6.948085876593622</v>
+        <v>6.948085385503194</v>
       </c>
       <c r="D474" t="n">
-        <v>6.718927369122407</v>
+        <v>6.718926894228892</v>
       </c>
       <c r="E474" t="n">
-        <v>6.893087887250751</v>
+        <v>6.893087400047578</v>
       </c>
       <c r="F474" t="n">
         <v>1969500</v>
@@ -10012,16 +10012,16 @@
         <v>44483</v>
       </c>
       <c r="B480" t="n">
-        <v>6.618096828460693</v>
+        <v>6.618097305297852</v>
       </c>
       <c r="C480" t="n">
-        <v>7.058081135414113</v>
+        <v>7.058081643952359</v>
       </c>
       <c r="D480" t="n">
-        <v>6.563098844727156</v>
+        <v>6.563099317601682</v>
       </c>
       <c r="E480" t="n">
-        <v>6.84725531255966</v>
+        <v>6.847255805907801</v>
       </c>
       <c r="F480" t="n">
         <v>2383700</v>
@@ -10032,16 +10032,16 @@
         <v>44484</v>
       </c>
       <c r="B481" t="n">
-        <v>6.801424026489258</v>
+        <v>6.801424503326416</v>
       </c>
       <c r="C481" t="n">
-        <v>6.810590138769081</v>
+        <v>6.810590616248861</v>
       </c>
       <c r="D481" t="n">
-        <v>6.581431649666802</v>
+        <v>6.58143211108064</v>
       </c>
       <c r="E481" t="n">
-        <v>6.654762733331041</v>
+        <v>6.654763199886006</v>
       </c>
       <c r="F481" t="n">
         <v>1272200</v>
@@ -10112,16 +10112,16 @@
         <v>44490</v>
       </c>
       <c r="B485" t="n">
-        <v>5.967287063598633</v>
+        <v>5.967287540435791</v>
       </c>
       <c r="C485" t="n">
-        <v>6.29727496201059</v>
+        <v>6.297275465216598</v>
       </c>
       <c r="D485" t="n">
-        <v>5.89395598242197</v>
+        <v>5.89395645339935</v>
       </c>
       <c r="E485" t="n">
-        <v>6.29727496201059</v>
+        <v>6.297275465216598</v>
       </c>
       <c r="F485" t="n">
         <v>2712900</v>
@@ -10152,16 +10152,16 @@
         <v>44494</v>
       </c>
       <c r="B487" t="n">
-        <v>5.985620498657227</v>
+        <v>5.985620021820068</v>
       </c>
       <c r="C487" t="n">
-        <v>6.040618488837999</v>
+        <v>6.040618007619493</v>
       </c>
       <c r="D487" t="n">
-        <v>5.637299457093829</v>
+        <v>5.637299008005241</v>
       </c>
       <c r="E487" t="n">
-        <v>5.765628100848964</v>
+        <v>5.765627641537233</v>
       </c>
       <c r="F487" t="n">
         <v>3945400</v>
@@ -10172,16 +10172,16 @@
         <v>44495</v>
       </c>
       <c r="B488" t="n">
-        <v>5.600634098052979</v>
+        <v>5.60063362121582</v>
       </c>
       <c r="C488" t="n">
-        <v>5.994786577287869</v>
+        <v>5.994786066892628</v>
       </c>
       <c r="D488" t="n">
-        <v>5.600634098052979</v>
+        <v>5.60063362121582</v>
       </c>
       <c r="E488" t="n">
-        <v>5.930622037237235</v>
+        <v>5.930621532304952</v>
       </c>
       <c r="F488" t="n">
         <v>1746800</v>
@@ -10212,16 +10212,16 @@
         <v>44497</v>
       </c>
       <c r="B490" t="n">
-        <v>5.673964500427246</v>
+        <v>5.673964023590088</v>
       </c>
       <c r="C490" t="n">
-        <v>5.912289112637964</v>
+        <v>5.912288615772123</v>
       </c>
       <c r="D490" t="n">
-        <v>5.646465288168049</v>
+        <v>5.646464813641911</v>
       </c>
       <c r="E490" t="n">
-        <v>5.783960475293731</v>
+        <v>5.783959989212565</v>
       </c>
       <c r="F490" t="n">
         <v>2222800</v>
@@ -10232,16 +10232,16 @@
         <v>44498</v>
       </c>
       <c r="B491" t="n">
-        <v>5.554802417755127</v>
+        <v>5.554801940917969</v>
       </c>
       <c r="C491" t="n">
-        <v>5.838958927312109</v>
+        <v>5.838958426082296</v>
       </c>
       <c r="D491" t="n">
-        <v>5.545636304329514</v>
+        <v>5.545635828279196</v>
       </c>
       <c r="E491" t="n">
-        <v>5.701463729246425</v>
+        <v>5.701463239819518</v>
       </c>
       <c r="F491" t="n">
         <v>2502600</v>
@@ -10432,16 +10432,16 @@
         <v>44516</v>
       </c>
       <c r="B501" t="n">
-        <v>6.783092021942139</v>
+        <v>6.78309154510498</v>
       </c>
       <c r="C501" t="n">
-        <v>7.177244504030098</v>
+        <v>7.177243999484845</v>
       </c>
       <c r="D501" t="n">
-        <v>6.691428704838564</v>
+        <v>6.691428234445144</v>
       </c>
       <c r="E501" t="n">
-        <v>7.131413064020896</v>
+        <v>7.131412562697498</v>
       </c>
       <c r="F501" t="n">
         <v>3605600</v>
@@ -10472,16 +10472,16 @@
         <v>44518</v>
       </c>
       <c r="B503" t="n">
-        <v>6.654763698577881</v>
+        <v>6.654763221740723</v>
       </c>
       <c r="C503" t="n">
-        <v>6.764759684401021</v>
+        <v>6.764759199682264</v>
       </c>
       <c r="D503" t="n">
-        <v>6.343107968327123</v>
+        <v>6.343107513821191</v>
       </c>
       <c r="E503" t="n">
-        <v>6.407272074848025</v>
+        <v>6.407271615744509</v>
       </c>
       <c r="F503" t="n">
         <v>2981000</v>
@@ -10492,16 +10492,16 @@
         <v>44519</v>
       </c>
       <c r="B504" t="n">
-        <v>7.232241630554199</v>
+        <v>7.232242107391357</v>
       </c>
       <c r="C504" t="n">
-        <v>7.305572275479267</v>
+        <v>7.305572757151272</v>
       </c>
       <c r="D504" t="n">
-        <v>6.544766178754005</v>
+        <v>6.544766610264437</v>
       </c>
       <c r="E504" t="n">
-        <v>6.645596034068535</v>
+        <v>6.645596472226894</v>
       </c>
       <c r="F504" t="n">
         <v>4026100</v>
@@ -10512,16 +10512,16 @@
         <v>44522</v>
       </c>
       <c r="B505" t="n">
-        <v>6.783092021942139</v>
+        <v>6.78309154510498</v>
       </c>
       <c r="C505" t="n">
-        <v>7.296407034807332</v>
+        <v>7.296406521885203</v>
       </c>
       <c r="D505" t="n">
-        <v>6.57226617406133</v>
+        <v>6.572265712044786</v>
       </c>
       <c r="E505" t="n">
-        <v>7.278074371386616</v>
+        <v>7.278073859753236</v>
       </c>
       <c r="F505" t="n">
         <v>4188800</v>
@@ -10552,16 +10552,16 @@
         <v>44524</v>
       </c>
       <c r="B507" t="n">
-        <v>6.187279224395752</v>
+        <v>6.18727970123291</v>
       </c>
       <c r="C507" t="n">
-        <v>6.398105052488197</v>
+        <v>6.398105545573142</v>
       </c>
       <c r="D507" t="n">
-        <v>6.123114689903222</v>
+        <v>6.123115161795391</v>
       </c>
       <c r="E507" t="n">
-        <v>6.315607856295679</v>
+        <v>6.315608343022784</v>
       </c>
       <c r="F507" t="n">
         <v>3487000</v>
@@ -10592,16 +10592,16 @@
         <v>44526</v>
       </c>
       <c r="B509" t="n">
-        <v>6.003952980041504</v>
+        <v>6.003952503204346</v>
       </c>
       <c r="C509" t="n">
-        <v>6.187279608419881</v>
+        <v>6.187279117022824</v>
       </c>
       <c r="D509" t="n">
-        <v>5.747295263226617</v>
+        <v>5.747294806773351</v>
       </c>
       <c r="E509" t="n">
-        <v>5.903123115890817</v>
+        <v>5.90312264706162</v>
       </c>
       <c r="F509" t="n">
         <v>3339600</v>
@@ -10612,16 +10612,16 @@
         <v>44529</v>
       </c>
       <c r="B510" t="n">
-        <v>5.958121299743652</v>
+        <v>5.958120822906494</v>
       </c>
       <c r="C510" t="n">
-        <v>6.297275791905541</v>
+        <v>6.297275287925354</v>
       </c>
       <c r="D510" t="n">
-        <v>5.912289422603862</v>
+        <v>5.912288949434696</v>
       </c>
       <c r="E510" t="n">
-        <v>6.095616494077848</v>
+        <v>6.095616006236749</v>
       </c>
       <c r="F510" t="n">
         <v>2247900</v>
@@ -10672,16 +10672,16 @@
         <v>44532</v>
       </c>
       <c r="B513" t="n">
-        <v>5.756461620330811</v>
+        <v>5.756462097167969</v>
       </c>
       <c r="C513" t="n">
-        <v>6.104782202580029</v>
+        <v>6.104782708270363</v>
       </c>
       <c r="D513" t="n">
-        <v>5.609799885456521</v>
+        <v>5.609800350144938</v>
       </c>
       <c r="E513" t="n">
-        <v>5.958120904790885</v>
+        <v>5.958121398332513</v>
       </c>
       <c r="F513" t="n">
         <v>2853300</v>
@@ -10732,16 +10732,16 @@
         <v>44537</v>
       </c>
       <c r="B516" t="n">
-        <v>6.1414475440979</v>
+        <v>6.141448020935059</v>
       </c>
       <c r="C516" t="n">
-        <v>6.306441941654446</v>
+        <v>6.306442431302178</v>
       </c>
       <c r="D516" t="n">
-        <v>6.086449557274101</v>
+        <v>6.086450029841079</v>
       </c>
       <c r="E516" t="n">
-        <v>6.168946756052374</v>
+        <v>6.168947235024638</v>
       </c>
       <c r="F516" t="n">
         <v>2815000</v>
@@ -10832,16 +10832,16 @@
         <v>44544</v>
       </c>
       <c r="B521" t="n">
-        <v>5.683130741119385</v>
+        <v>5.683131217956543</v>
       </c>
       <c r="C521" t="n">
-        <v>6.049784436017284</v>
+        <v>6.049784943618139</v>
       </c>
       <c r="D521" t="n">
-        <v>5.600633976654099</v>
+        <v>5.600634446569452</v>
       </c>
       <c r="E521" t="n">
-        <v>6.022285660223909</v>
+        <v>6.022286165517508</v>
       </c>
       <c r="F521" t="n">
         <v>2512100</v>
@@ -11072,16 +11072,16 @@
         <v>44564</v>
       </c>
       <c r="B533" t="n">
-        <v>5.417306423187256</v>
+        <v>5.417306900024414</v>
       </c>
       <c r="C533" t="n">
-        <v>5.774793973013967</v>
+        <v>5.774794481317564</v>
       </c>
       <c r="D533" t="n">
-        <v>5.371474988627377</v>
+        <v>5.371475461430403</v>
       </c>
       <c r="E533" t="n">
-        <v>5.655631456405064</v>
+        <v>5.655631954219848</v>
       </c>
       <c r="F533" t="n">
         <v>2044700</v>
@@ -11092,16 +11092,16 @@
         <v>44565</v>
       </c>
       <c r="B534" t="n">
-        <v>5.059819221496582</v>
+        <v>5.05981969833374</v>
       </c>
       <c r="C534" t="n">
-        <v>5.44480553787433</v>
+        <v>5.444806050992582</v>
       </c>
       <c r="D534" t="n">
-        <v>5.023153899659189</v>
+        <v>5.023154373041008</v>
       </c>
       <c r="E534" t="n">
-        <v>5.417306327953727</v>
+        <v>5.417306838480457</v>
       </c>
       <c r="F534" t="n">
         <v>2338200</v>
@@ -11212,16 +11212,16 @@
         <v>44573</v>
       </c>
       <c r="B540" t="n">
-        <v>5.169816017150879</v>
+        <v>5.169815540313721</v>
       </c>
       <c r="C540" t="n">
-        <v>5.270645886937004</v>
+        <v>5.270645400799818</v>
       </c>
       <c r="D540" t="n">
-        <v>4.995655491914913</v>
+        <v>4.995655031141423</v>
       </c>
       <c r="E540" t="n">
-        <v>5.032320819639834</v>
+        <v>5.032320355484523</v>
       </c>
       <c r="F540" t="n">
         <v>2344800</v>
@@ -11272,16 +11272,16 @@
         <v>44578</v>
       </c>
       <c r="B543" t="n">
-        <v>4.903992176055908</v>
+        <v>4.90399169921875</v>
       </c>
       <c r="C543" t="n">
-        <v>5.105651915770163</v>
+        <v>5.105651419324723</v>
       </c>
       <c r="D543" t="n">
-        <v>4.821495407159335</v>
+        <v>4.821494938343708</v>
       </c>
       <c r="E543" t="n">
-        <v>5.041487373663776</v>
+        <v>5.041486883457342</v>
       </c>
       <c r="F543" t="n">
         <v>1383000</v>
@@ -11312,16 +11312,16 @@
         <v>44580</v>
       </c>
       <c r="B545" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C545" t="n">
-        <v>5.050653052647643</v>
+        <v>5.050653537402776</v>
       </c>
       <c r="D545" t="n">
-        <v>4.812328026305926</v>
+        <v>4.812328488186932</v>
       </c>
       <c r="E545" t="n">
-        <v>4.839827235916551</v>
+        <v>4.839827700436895</v>
       </c>
       <c r="F545" t="n">
         <v>2176700</v>
@@ -11332,16 +11332,16 @@
         <v>44581</v>
       </c>
       <c r="B546" t="n">
-        <v>5.288978099822998</v>
+        <v>5.28897762298584</v>
       </c>
       <c r="C546" t="n">
-        <v>5.499803934807352</v>
+        <v>5.499803438962819</v>
       </c>
       <c r="D546" t="n">
-        <v>5.096484927137929</v>
+        <v>5.096484467655332</v>
       </c>
       <c r="E546" t="n">
-        <v>5.1331502517365</v>
+        <v>5.133149788948276</v>
       </c>
       <c r="F546" t="n">
         <v>3426400</v>
@@ -11412,16 +11412,16 @@
         <v>44587</v>
       </c>
       <c r="B550" t="n">
-        <v>5.389808177947998</v>
+        <v>5.389808654785156</v>
       </c>
       <c r="C550" t="n">
-        <v>5.554802145282468</v>
+        <v>5.554802636716668</v>
       </c>
       <c r="D550" t="n">
-        <v>5.307310975738181</v>
+        <v>5.307311445276799</v>
       </c>
       <c r="E550" t="n">
-        <v>5.463138830096652</v>
+        <v>5.463139313421384</v>
       </c>
       <c r="F550" t="n">
         <v>4467700</v>
@@ -11432,16 +11432,16 @@
         <v>44588</v>
       </c>
       <c r="B551" t="n">
-        <v>5.756461620330811</v>
+        <v>5.756462097167969</v>
       </c>
       <c r="C551" t="n">
-        <v>5.884790255896312</v>
+        <v>5.884790743363587</v>
       </c>
       <c r="D551" t="n">
-        <v>5.508970461769056</v>
+        <v>5.508970918105256</v>
       </c>
       <c r="E551" t="n">
-        <v>5.508970461769056</v>
+        <v>5.508970918105256</v>
       </c>
       <c r="F551" t="n">
         <v>4181600</v>
@@ -11472,16 +11472,16 @@
         <v>44592</v>
       </c>
       <c r="B553" t="n">
-        <v>6.03145170211792</v>
+        <v>6.031451225280762</v>
       </c>
       <c r="C553" t="n">
-        <v>6.077283577347511</v>
+        <v>6.077283096886956</v>
       </c>
       <c r="D553" t="n">
-        <v>5.820625862815083</v>
+        <v>5.820625402645486</v>
       </c>
       <c r="E553" t="n">
-        <v>5.903123063394284</v>
+        <v>5.903122596702588</v>
       </c>
       <c r="F553" t="n">
         <v>2633300</v>
@@ -11552,16 +11552,16 @@
         <v>44596</v>
       </c>
       <c r="B557" t="n">
-        <v>5.490637302398682</v>
+        <v>5.49063777923584</v>
       </c>
       <c r="C557" t="n">
-        <v>5.637299035668652</v>
+        <v>5.637299525242722</v>
       </c>
       <c r="D557" t="n">
-        <v>5.371475217791077</v>
+        <v>5.371475684279544</v>
       </c>
       <c r="E557" t="n">
-        <v>5.628132486114529</v>
+        <v>5.628132974892527</v>
       </c>
       <c r="F557" t="n">
         <v>2310300</v>
@@ -11592,16 +11592,16 @@
         <v>44600</v>
       </c>
       <c r="B559" t="n">
-        <v>5.389808177947998</v>
+        <v>5.389808654785156</v>
       </c>
       <c r="C559" t="n">
-        <v>5.490637606109815</v>
+        <v>5.490638091867368</v>
       </c>
       <c r="D559" t="n">
-        <v>5.252312986626691</v>
+        <v>5.252313451299628</v>
       </c>
       <c r="E559" t="n">
-        <v>5.334810188836508</v>
+        <v>5.334810660807985</v>
       </c>
       <c r="F559" t="n">
         <v>1734000</v>
@@ -11712,16 +11712,16 @@
         <v>44608</v>
       </c>
       <c r="B565" t="n">
-        <v>5.343976020812988</v>
+        <v>5.343976497650146</v>
       </c>
       <c r="C565" t="n">
-        <v>5.499803866977643</v>
+        <v>5.499804357719151</v>
       </c>
       <c r="D565" t="n">
-        <v>5.270645372520242</v>
+        <v>5.270645842814186</v>
       </c>
       <c r="E565" t="n">
-        <v>5.371475232465339</v>
+        <v>5.371475711756221</v>
       </c>
       <c r="F565" t="n">
         <v>2218600</v>
@@ -11752,16 +11752,16 @@
         <v>44610</v>
       </c>
       <c r="B567" t="n">
-        <v>5.21564769744873</v>
+        <v>5.215647220611572</v>
       </c>
       <c r="C567" t="n">
-        <v>5.252313023782434</v>
+        <v>5.252312543593172</v>
       </c>
       <c r="D567" t="n">
-        <v>5.114817831488462</v>
+        <v>5.114817363869609</v>
       </c>
       <c r="E567" t="n">
-        <v>5.188148484155869</v>
+        <v>5.188148009832808</v>
       </c>
       <c r="F567" t="n">
         <v>2313700</v>
@@ -11832,16 +11832,16 @@
         <v>44616</v>
       </c>
       <c r="B571" t="n">
-        <v>4.830661296844482</v>
+        <v>4.830660820007324</v>
       </c>
       <c r="C571" t="n">
-        <v>4.885659285923612</v>
+        <v>4.885658803657574</v>
       </c>
       <c r="D571" t="n">
-        <v>4.509839475340308</v>
+        <v>4.509839030171643</v>
       </c>
       <c r="E571" t="n">
-        <v>4.647334666580715</v>
+        <v>4.647334207839827</v>
       </c>
       <c r="F571" t="n">
         <v>2613100</v>
@@ -11892,16 +11892,16 @@
         <v>44623</v>
       </c>
       <c r="B574" t="n">
-        <v>4.629001617431641</v>
+        <v>4.629002094268799</v>
       </c>
       <c r="C574" t="n">
-        <v>4.913158089180485</v>
+        <v>4.913158595288829</v>
       </c>
       <c r="D574" t="n">
-        <v>4.629001617431641</v>
+        <v>4.629002094268799</v>
       </c>
       <c r="E574" t="n">
-        <v>4.64733427892882</v>
+        <v>4.64733475765444</v>
       </c>
       <c r="F574" t="n">
         <v>2116200</v>
@@ -11992,16 +11992,16 @@
         <v>44630</v>
       </c>
       <c r="B579" t="n">
-        <v>4.13401985168457</v>
+        <v>4.134019374847412</v>
       </c>
       <c r="C579" t="n">
-        <v>4.308179939767546</v>
+        <v>4.308179442841951</v>
       </c>
       <c r="D579" t="n">
-        <v>4.024023431467449</v>
+        <v>4.024022967317792</v>
       </c>
       <c r="E579" t="n">
-        <v>4.308179939767546</v>
+        <v>4.308179442841951</v>
       </c>
       <c r="F579" t="n">
         <v>3138700</v>
@@ -12072,16 +12072,16 @@
         <v>44636</v>
       </c>
       <c r="B583" t="n">
-        <v>4.445674896240234</v>
+        <v>4.445674419403076</v>
       </c>
       <c r="C583" t="n">
-        <v>4.464007559101806</v>
+        <v>4.464007080298311</v>
       </c>
       <c r="D583" t="n">
-        <v>4.253181717651148</v>
+        <v>4.253181261460552</v>
       </c>
       <c r="E583" t="n">
-        <v>4.308179706235864</v>
+        <v>4.308179244146257</v>
       </c>
       <c r="F583" t="n">
         <v>3023600</v>
@@ -12152,16 +12152,16 @@
         <v>44642</v>
       </c>
       <c r="B587" t="n">
-        <v>4.665667057037354</v>
+        <v>4.665667533874512</v>
       </c>
       <c r="C587" t="n">
-        <v>4.784829141204734</v>
+        <v>4.784829630220409</v>
       </c>
       <c r="D587" t="n">
-        <v>4.6290017331266</v>
+        <v>4.629002206216515</v>
       </c>
       <c r="E587" t="n">
-        <v>4.69316583142785</v>
+        <v>4.693166311075418</v>
       </c>
       <c r="F587" t="n">
         <v>2609200</v>
@@ -12212,16 +12212,16 @@
         <v>44645</v>
       </c>
       <c r="B590" t="n">
-        <v>4.986488819122314</v>
+        <v>4.986489295959473</v>
       </c>
       <c r="C590" t="n">
-        <v>5.270645295655251</v>
+        <v>5.270645799665109</v>
       </c>
       <c r="D590" t="n">
-        <v>4.958989607871001</v>
+        <v>4.958990082078524</v>
       </c>
       <c r="E590" t="n">
-        <v>5.078152128151466</v>
+        <v>5.078152613754004</v>
       </c>
       <c r="F590" t="n">
         <v>4172200</v>
@@ -12232,16 +12232,16 @@
         <v>44648</v>
       </c>
       <c r="B591" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C591" t="n">
-        <v>5.142317254043173</v>
+        <v>5.142316768551991</v>
       </c>
       <c r="D591" t="n">
-        <v>4.885659522177632</v>
+        <v>4.885659060917757</v>
       </c>
       <c r="E591" t="n">
-        <v>5.01398816956781</v>
+        <v>5.013987696192302</v>
       </c>
       <c r="F591" t="n">
         <v>3528600</v>
@@ -12292,16 +12292,16 @@
         <v>44651</v>
       </c>
       <c r="B594" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C594" t="n">
-        <v>5.224814023108552</v>
+        <v>5.224813529828769</v>
       </c>
       <c r="D594" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="E594" t="n">
-        <v>5.178982581868937</v>
+        <v>5.178982092916146</v>
       </c>
       <c r="F594" t="n">
         <v>1926600</v>
@@ -12392,16 +12392,16 @@
         <v>44658</v>
       </c>
       <c r="B599" t="n">
-        <v>4.629001617431641</v>
+        <v>4.629002094268799</v>
       </c>
       <c r="C599" t="n">
-        <v>4.738997586414717</v>
+        <v>4.738998074582648</v>
       </c>
       <c r="D599" t="n">
-        <v>4.509839099157411</v>
+        <v>4.509839563719543</v>
       </c>
       <c r="E599" t="n">
-        <v>4.702332263420359</v>
+        <v>4.702332747811365</v>
       </c>
       <c r="F599" t="n">
         <v>6002200</v>
@@ -12412,16 +12412,16 @@
         <v>44659</v>
       </c>
       <c r="B600" t="n">
-        <v>4.528172492980957</v>
+        <v>4.528172016143799</v>
       </c>
       <c r="C600" t="n">
-        <v>4.61983581529126</v>
+        <v>4.619835328801537</v>
       </c>
       <c r="D600" t="n">
-        <v>4.454841835132715</v>
+        <v>4.454841366017608</v>
       </c>
       <c r="E600" t="n">
-        <v>4.6015031508292</v>
+        <v>4.601502666269989</v>
       </c>
       <c r="F600" t="n">
         <v>3786000</v>
@@ -12492,16 +12492,16 @@
         <v>44665</v>
       </c>
       <c r="B604" t="n">
-        <v>4.445674896240234</v>
+        <v>4.445674419403076</v>
       </c>
       <c r="C604" t="n">
-        <v>4.491506771936744</v>
+        <v>4.49150629018372</v>
       </c>
       <c r="D604" t="n">
-        <v>4.36317813190574</v>
+        <v>4.363177663917075</v>
       </c>
       <c r="E604" t="n">
-        <v>4.491506771936744</v>
+        <v>4.49150629018372</v>
       </c>
       <c r="F604" t="n">
         <v>2169000</v>
@@ -12572,16 +12572,16 @@
         <v>44673</v>
       </c>
       <c r="B608" t="n">
-        <v>4.097354412078857</v>
+        <v>4.097353935241699</v>
       </c>
       <c r="C608" t="n">
-        <v>4.308180281690042</v>
+        <v>4.308179780317636</v>
       </c>
       <c r="D608" t="n">
-        <v>4.079021746768547</v>
+        <v>4.079021272064886</v>
       </c>
       <c r="E608" t="n">
-        <v>4.308180281690042</v>
+        <v>4.308179780317636</v>
       </c>
       <c r="F608" t="n">
         <v>4745700</v>
@@ -12632,16 +12632,16 @@
         <v>44678</v>
       </c>
       <c r="B611" t="n">
-        <v>3.978191614151001</v>
+        <v>3.97819185256958</v>
       </c>
       <c r="C611" t="n">
-        <v>4.170684784970252</v>
+        <v>4.170685034925215</v>
       </c>
       <c r="D611" t="n">
-        <v>3.941526289907824</v>
+        <v>3.941526526128999</v>
       </c>
       <c r="E611" t="n">
-        <v>4.170684784970252</v>
+        <v>4.170685034925215</v>
       </c>
       <c r="F611" t="n">
         <v>4173400</v>
@@ -12652,16 +12652,16 @@
         <v>44679</v>
       </c>
       <c r="B612" t="n">
-        <v>4.014856815338135</v>
+        <v>4.014857292175293</v>
       </c>
       <c r="C612" t="n">
-        <v>4.033189476897824</v>
+        <v>4.033189955912318</v>
       </c>
       <c r="D612" t="n">
-        <v>3.950692281336657</v>
+        <v>3.950692750553112</v>
       </c>
       <c r="E612" t="n">
-        <v>4.014856815338135</v>
+        <v>4.014857292175293</v>
       </c>
       <c r="F612" t="n">
         <v>2238100</v>
@@ -12672,16 +12672,16 @@
         <v>44680</v>
       </c>
       <c r="B613" t="n">
-        <v>4.014856815338135</v>
+        <v>4.014857292175293</v>
       </c>
       <c r="C613" t="n">
-        <v>4.16151810781565</v>
+        <v>4.161518602071499</v>
       </c>
       <c r="D613" t="n">
-        <v>3.950692281336657</v>
+        <v>3.950692750553112</v>
       </c>
       <c r="E613" t="n">
-        <v>4.060688250694794</v>
+        <v>4.060688732975267</v>
       </c>
       <c r="F613" t="n">
         <v>3551000</v>
@@ -12712,16 +12712,16 @@
         <v>44684</v>
       </c>
       <c r="B615" t="n">
-        <v>3.895694494247437</v>
+        <v>3.895694732666016</v>
       </c>
       <c r="C615" t="n">
-        <v>4.060688456653144</v>
+        <v>4.060688705169442</v>
       </c>
       <c r="D615" t="n">
-        <v>3.895694494247437</v>
+        <v>3.895694732666016</v>
       </c>
       <c r="E615" t="n">
-        <v>4.024023131674098</v>
+        <v>4.024023377946458</v>
       </c>
       <c r="F615" t="n">
         <v>2214200</v>
@@ -12752,16 +12752,16 @@
         <v>44686</v>
       </c>
       <c r="B617" t="n">
-        <v>3.739866733551025</v>
+        <v>3.739866495132446</v>
       </c>
       <c r="C617" t="n">
-        <v>4.00569056451817</v>
+        <v>4.005690309153175</v>
       </c>
       <c r="D617" t="n">
-        <v>3.73070062063069</v>
+        <v>3.730700382796456</v>
       </c>
       <c r="E617" t="n">
-        <v>4.00569056451817</v>
+        <v>4.005690309153175</v>
       </c>
       <c r="F617" t="n">
         <v>4685400</v>
@@ -12912,16 +12912,16 @@
         <v>44698</v>
       </c>
       <c r="B625" t="n">
-        <v>3.116555690765381</v>
+        <v>3.11655592918396</v>
       </c>
       <c r="C625" t="n">
-        <v>3.272383322323847</v>
+        <v>3.272383572663343</v>
       </c>
       <c r="D625" t="n">
-        <v>3.107389359497236</v>
+        <v>3.107389597214584</v>
       </c>
       <c r="E625" t="n">
-        <v>3.199052672178686</v>
+        <v>3.199052916908339</v>
       </c>
       <c r="F625" t="n">
         <v>2194700</v>
@@ -13032,16 +13032,16 @@
         <v>44706</v>
       </c>
       <c r="B631" t="n">
-        <v>2.924062490463257</v>
+        <v>2.924062728881836</v>
       </c>
       <c r="C631" t="n">
-        <v>3.006559471167609</v>
+        <v>3.006559716312724</v>
       </c>
       <c r="D631" t="n">
-        <v>2.914896159273884</v>
+        <v>2.914896396945071</v>
       </c>
       <c r="E631" t="n">
-        <v>3.006559471167609</v>
+        <v>3.006559716312724</v>
       </c>
       <c r="F631" t="n">
         <v>4016500</v>
@@ -13072,16 +13072,16 @@
         <v>44708</v>
       </c>
       <c r="B633" t="n">
-        <v>3.07072377204895</v>
+        <v>3.070724010467529</v>
       </c>
       <c r="C633" t="n">
-        <v>3.226551619925623</v>
+        <v>3.226551870443061</v>
       </c>
       <c r="D633" t="n">
-        <v>3.06155744091165</v>
+        <v>3.061557678618533</v>
       </c>
       <c r="E633" t="n">
-        <v>3.08905643432355</v>
+        <v>3.089056674165522</v>
       </c>
       <c r="F633" t="n">
         <v>2861700</v>
@@ -13092,16 +13092,16 @@
         <v>44711</v>
       </c>
       <c r="B634" t="n">
-        <v>2.979060649871826</v>
+        <v>2.979060411453247</v>
       </c>
       <c r="C634" t="n">
-        <v>3.134888507644903</v>
+        <v>3.134888256755193</v>
       </c>
       <c r="D634" t="n">
-        <v>2.933228991274623</v>
+        <v>2.933228756524019</v>
       </c>
       <c r="E634" t="n">
-        <v>3.079890298785673</v>
+        <v>3.07989005229755</v>
       </c>
       <c r="F634" t="n">
         <v>2046200</v>
@@ -13132,16 +13132,16 @@
         <v>44713</v>
       </c>
       <c r="B636" t="n">
-        <v>2.786567449569702</v>
+        <v>2.786567211151123</v>
       </c>
       <c r="C636" t="n">
-        <v>2.869064653123893</v>
+        <v>2.869064407646857</v>
       </c>
       <c r="D636" t="n">
-        <v>2.759068454565833</v>
+        <v>2.759068218500067</v>
       </c>
       <c r="E636" t="n">
-        <v>2.859898102913351</v>
+        <v>2.859897858220605</v>
       </c>
       <c r="F636" t="n">
         <v>3347800</v>
@@ -13172,16 +13172,16 @@
         <v>44715</v>
       </c>
       <c r="B638" t="n">
-        <v>2.786567449569702</v>
+        <v>2.786567211151123</v>
       </c>
       <c r="C638" t="n">
-        <v>2.81406644457357</v>
+        <v>2.814066203802179</v>
       </c>
       <c r="D638" t="n">
-        <v>2.731569459561965</v>
+        <v>2.731569225849011</v>
       </c>
       <c r="E638" t="n">
-        <v>2.81406644457357</v>
+        <v>2.814066203802179</v>
       </c>
       <c r="F638" t="n">
         <v>3576500</v>
@@ -13192,16 +13192,16 @@
         <v>44718</v>
       </c>
       <c r="B639" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="C639" t="n">
-        <v>2.859897899145521</v>
+        <v>2.859898153024676</v>
       </c>
       <c r="D639" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="E639" t="n">
-        <v>2.814066244071248</v>
+        <v>2.81406649388183</v>
       </c>
       <c r="F639" t="n">
         <v>3115900</v>
@@ -13252,16 +13252,16 @@
         <v>44721</v>
       </c>
       <c r="B642" t="n">
-        <v>2.630739688873291</v>
+        <v>2.630739450454712</v>
       </c>
       <c r="C642" t="n">
-        <v>2.704070563441105</v>
+        <v>2.704070318376698</v>
       </c>
       <c r="D642" t="n">
-        <v>2.575741696854376</v>
+        <v>2.575741463420153</v>
       </c>
       <c r="E642" t="n">
-        <v>2.676571567431647</v>
+        <v>2.676571324859418</v>
       </c>
       <c r="F642" t="n">
         <v>4374300</v>
@@ -13432,16 +13432,16 @@
         <v>44735</v>
       </c>
       <c r="B651" t="n">
-        <v>2.300751209259033</v>
+        <v>2.300751447677612</v>
       </c>
       <c r="C651" t="n">
-        <v>2.438246389385266</v>
+        <v>2.438246642051976</v>
       </c>
       <c r="D651" t="n">
-        <v>2.236586893853321</v>
+        <v>2.236587125622783</v>
       </c>
       <c r="E651" t="n">
-        <v>2.236586893853321</v>
+        <v>2.236587125622783</v>
       </c>
       <c r="F651" t="n">
         <v>3255000</v>
@@ -13492,16 +13492,16 @@
         <v>44740</v>
       </c>
       <c r="B654" t="n">
-        <v>2.089925527572632</v>
+        <v>2.089925289154053</v>
       </c>
       <c r="C654" t="n">
-        <v>2.199921722993602</v>
+        <v>2.199921472026663</v>
       </c>
       <c r="D654" t="n">
-        <v>2.080759196166099</v>
+        <v>2.080758958793214</v>
       </c>
       <c r="E654" t="n">
-        <v>2.172422510231425</v>
+        <v>2.172422262401595</v>
       </c>
       <c r="F654" t="n">
         <v>3436800</v>
@@ -13612,16 +13612,16 @@
         <v>44748</v>
       </c>
       <c r="B660" t="n">
-        <v>2.300751209259033</v>
+        <v>2.300751447677612</v>
       </c>
       <c r="C660" t="n">
-        <v>2.300751209259033</v>
+        <v>2.300751447677612</v>
       </c>
       <c r="D660" t="n">
-        <v>2.108258044499333</v>
+        <v>2.108258262970537</v>
       </c>
       <c r="E660" t="n">
-        <v>2.108258044499333</v>
+        <v>2.108258262970537</v>
       </c>
       <c r="F660" t="n">
         <v>6223900</v>
@@ -13672,16 +13672,16 @@
         <v>44753</v>
       </c>
       <c r="B663" t="n">
-        <v>2.337416410446167</v>
+        <v>2.337416648864746</v>
       </c>
       <c r="C663" t="n">
-        <v>2.38324806191716</v>
+        <v>2.383248305010609</v>
       </c>
       <c r="D663" t="n">
-        <v>2.273252098386777</v>
+        <v>2.273252330260538</v>
       </c>
       <c r="E663" t="n">
-        <v>2.346582740740366</v>
+        <v>2.346582980093919</v>
       </c>
       <c r="F663" t="n">
         <v>1807800</v>
@@ -13892,16 +13892,16 @@
         <v>44768</v>
       </c>
       <c r="B674" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C674" t="n">
-        <v>2.520743251874533</v>
+        <v>2.520743493812202</v>
       </c>
       <c r="D674" t="n">
-        <v>2.300751104787417</v>
+        <v>2.300751325610525</v>
       </c>
       <c r="E674" t="n">
-        <v>2.374081747635604</v>
+        <v>2.374081975496892</v>
       </c>
       <c r="F674" t="n">
         <v>4848400</v>
@@ -13912,16 +13912,16 @@
         <v>44769</v>
       </c>
       <c r="B675" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242330551147</v>
       </c>
       <c r="C675" t="n">
-        <v>2.603240558142417</v>
+        <v>2.603240314578118</v>
       </c>
       <c r="D675" t="n">
-        <v>2.419913927566782</v>
+        <v>2.419913701154883</v>
       </c>
       <c r="E675" t="n">
-        <v>2.502410911325818</v>
+        <v>2.502410677195339</v>
       </c>
       <c r="F675" t="n">
         <v>5961800</v>
@@ -13952,16 +13952,16 @@
         <v>44771</v>
       </c>
       <c r="B677" t="n">
-        <v>2.575741291046143</v>
+        <v>2.575741529464722</v>
       </c>
       <c r="C677" t="n">
-        <v>2.603240282723132</v>
+        <v>2.603240523687103</v>
       </c>
       <c r="D677" t="n">
-        <v>2.493244316015175</v>
+        <v>2.493244546797579</v>
       </c>
       <c r="E677" t="n">
-        <v>2.566574960487146</v>
+        <v>2.566575198057261</v>
       </c>
       <c r="F677" t="n">
         <v>2895400</v>
@@ -13972,16 +13972,16 @@
         <v>44774</v>
       </c>
       <c r="B678" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="C678" t="n">
-        <v>2.749901926967264</v>
+        <v>2.749902171081845</v>
       </c>
       <c r="D678" t="n">
-        <v>2.520743433053326</v>
+        <v>2.520743656825025</v>
       </c>
       <c r="E678" t="n">
-        <v>2.575741419142454</v>
+        <v>2.57574164779644</v>
       </c>
       <c r="F678" t="n">
         <v>6003000</v>
@@ -13992,16 +13992,16 @@
         <v>44775</v>
       </c>
       <c r="B679" t="n">
-        <v>2.575741291046143</v>
+        <v>2.575741529464722</v>
       </c>
       <c r="C679" t="n">
-        <v>2.740735459650637</v>
+        <v>2.740735713341587</v>
       </c>
       <c r="D679" t="n">
-        <v>2.548242299369153</v>
+        <v>2.548242535242341</v>
       </c>
       <c r="E679" t="n">
-        <v>2.676571145737662</v>
+        <v>2.676571393489365</v>
       </c>
       <c r="F679" t="n">
         <v>4865400</v>
@@ -14052,16 +14052,16 @@
         <v>44778</v>
       </c>
       <c r="B682" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232412338257</v>
       </c>
       <c r="C682" t="n">
-        <v>2.969894169468031</v>
+        <v>2.969893918664065</v>
       </c>
       <c r="D682" t="n">
-        <v>2.731569338151449</v>
+        <v>2.731569107473725</v>
       </c>
       <c r="E682" t="n">
-        <v>2.869064525602105</v>
+        <v>2.86906428331308</v>
       </c>
       <c r="F682" t="n">
         <v>6497600</v>
@@ -14132,16 +14132,16 @@
         <v>44784</v>
       </c>
       <c r="B686" t="n">
-        <v>3.034058332443237</v>
+        <v>3.034058570861816</v>
       </c>
       <c r="C686" t="n">
-        <v>3.15322085125187</v>
+        <v>3.153221099034329</v>
       </c>
       <c r="D686" t="n">
-        <v>2.887397039808076</v>
+        <v>2.887397266701901</v>
       </c>
       <c r="E686" t="n">
-        <v>2.896563370597774</v>
+        <v>2.896563598211896</v>
       </c>
       <c r="F686" t="n">
         <v>13306300</v>
@@ -14192,16 +14192,16 @@
         <v>44789</v>
       </c>
       <c r="B689" t="n">
-        <v>3.32738184928894</v>
+        <v>3.327381610870361</v>
       </c>
       <c r="C689" t="n">
-        <v>3.602372032389388</v>
+        <v>3.602371774266797</v>
       </c>
       <c r="D689" t="n">
-        <v>3.309048966442487</v>
+        <v>3.309048729337523</v>
       </c>
       <c r="E689" t="n">
-        <v>3.538207488783292</v>
+        <v>3.538207235258316</v>
       </c>
       <c r="F689" t="n">
         <v>21092800</v>
@@ -14272,16 +14272,16 @@
         <v>44795</v>
       </c>
       <c r="B693" t="n">
-        <v>2.740735769271851</v>
+        <v>2.740735530853271</v>
       </c>
       <c r="C693" t="n">
-        <v>2.78656742724444</v>
+        <v>2.786567184838932</v>
       </c>
       <c r="D693" t="n">
-        <v>2.694904111299261</v>
+        <v>2.694903876867611</v>
       </c>
       <c r="E693" t="n">
-        <v>2.78656742724444</v>
+        <v>2.786567184838932</v>
       </c>
       <c r="F693" t="n">
         <v>4672100</v>
@@ -14292,16 +14292,16 @@
         <v>44796</v>
       </c>
       <c r="B694" t="n">
-        <v>2.841565370559692</v>
+        <v>2.841565608978271</v>
       </c>
       <c r="C694" t="n">
-        <v>2.887397246328865</v>
+        <v>2.88739748859292</v>
       </c>
       <c r="D694" t="n">
-        <v>2.749902056106508</v>
+        <v>2.749902286834172</v>
       </c>
       <c r="E694" t="n">
-        <v>2.759068387551826</v>
+        <v>2.759068619048582</v>
       </c>
       <c r="F694" t="n">
         <v>5654500</v>
@@ -14352,16 +14352,16 @@
         <v>44799</v>
       </c>
       <c r="B697" t="n">
-        <v>2.887397050857544</v>
+        <v>2.887397289276123</v>
       </c>
       <c r="C697" t="n">
-        <v>3.015725682404397</v>
+        <v>3.015725931419347</v>
       </c>
       <c r="D697" t="n">
-        <v>2.850731509015878</v>
+        <v>2.850731744406904</v>
       </c>
       <c r="E697" t="n">
-        <v>3.015725682404397</v>
+        <v>3.015725931419347</v>
       </c>
       <c r="F697" t="n">
         <v>3689400</v>
@@ -14552,16 +14552,16 @@
         <v>44816</v>
       </c>
       <c r="B707" t="n">
-        <v>3.391546010971069</v>
+        <v>3.39154577255249</v>
       </c>
       <c r="C707" t="n">
-        <v>3.437377669522857</v>
+        <v>3.437377427882408</v>
       </c>
       <c r="D707" t="n">
-        <v>3.327381688998567</v>
+        <v>3.327381455090605</v>
       </c>
       <c r="E707" t="n">
-        <v>3.327381688998567</v>
+        <v>3.327381455090605</v>
       </c>
       <c r="F707" t="n">
         <v>4227100</v>
@@ -14712,16 +14712,16 @@
         <v>44826</v>
       </c>
       <c r="B715" t="n">
-        <v>3.199052810668945</v>
+        <v>3.199052572250366</v>
       </c>
       <c r="C715" t="n">
-        <v>3.199052810668945</v>
+        <v>3.199052572250366</v>
       </c>
       <c r="D715" t="n">
-        <v>3.024892290492027</v>
+        <v>3.02489206505326</v>
       </c>
       <c r="E715" t="n">
-        <v>3.061557617151887</v>
+        <v>3.061557388980531</v>
       </c>
       <c r="F715" t="n">
         <v>6046200</v>
@@ -14812,16 +14812,16 @@
         <v>44833</v>
       </c>
       <c r="B720" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232412338257</v>
       </c>
       <c r="C720" t="n">
-        <v>2.90572985064426</v>
+        <v>2.905729605258892</v>
       </c>
       <c r="D720" t="n">
-        <v>2.79573365697522</v>
+        <v>2.795733420878897</v>
       </c>
       <c r="E720" t="n">
-        <v>2.896563519383722</v>
+        <v>2.896563274772439</v>
       </c>
       <c r="F720" t="n">
         <v>3966200</v>
@@ -15032,16 +15032,16 @@
         <v>44851</v>
       </c>
       <c r="B731" t="n">
-        <v>3.034058332443237</v>
+        <v>3.034058570861816</v>
       </c>
       <c r="C731" t="n">
-        <v>3.11655552809308</v>
+        <v>3.116555772994351</v>
       </c>
       <c r="D731" t="n">
-        <v>3.02489200165354</v>
+        <v>3.024892239351822</v>
       </c>
       <c r="E731" t="n">
-        <v>3.079889986391725</v>
+        <v>3.07989022841179</v>
       </c>
       <c r="F731" t="n">
         <v>3944900</v>
@@ -15092,16 +15092,16 @@
         <v>44854</v>
       </c>
       <c r="B734" t="n">
-        <v>2.814066410064697</v>
+        <v>2.814066171646118</v>
       </c>
       <c r="C734" t="n">
-        <v>2.951561601940523</v>
+        <v>2.95156135187282</v>
       </c>
       <c r="D734" t="n">
-        <v>2.795733746953598</v>
+        <v>2.795733510088233</v>
       </c>
       <c r="E734" t="n">
-        <v>2.942395270384973</v>
+        <v>2.942395021093878</v>
       </c>
       <c r="F734" t="n">
         <v>4518300</v>
@@ -15112,16 +15112,16 @@
         <v>44855</v>
       </c>
       <c r="B735" t="n">
-        <v>2.814066410064697</v>
+        <v>2.814066171646118</v>
       </c>
       <c r="C735" t="n">
-        <v>2.869064617940577</v>
+        <v>2.869064374862337</v>
       </c>
       <c r="D735" t="n">
-        <v>2.685737768287004</v>
+        <v>2.685737540740923</v>
       </c>
       <c r="E735" t="n">
-        <v>2.804900078509148</v>
+        <v>2.804899840867176</v>
       </c>
       <c r="F735" t="n">
         <v>6831600</v>
@@ -15132,16 +15132,16 @@
         <v>44858</v>
       </c>
       <c r="B736" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="C736" t="n">
-        <v>2.814066144805841</v>
+        <v>2.814066387171744</v>
       </c>
       <c r="D736" t="n">
-        <v>2.704070176507662</v>
+        <v>2.704070409399987</v>
       </c>
       <c r="E736" t="n">
-        <v>2.795733483422811</v>
+        <v>2.795733724209785</v>
       </c>
       <c r="F736" t="n">
         <v>4201100</v>
@@ -15152,16 +15152,16 @@
         <v>44859</v>
       </c>
       <c r="B737" t="n">
-        <v>2.740735769271851</v>
+        <v>2.740735530853271</v>
       </c>
       <c r="C737" t="n">
-        <v>2.859898080000583</v>
+        <v>2.859897831215989</v>
       </c>
       <c r="D737" t="n">
-        <v>2.722403106082815</v>
+        <v>2.722402869259008</v>
       </c>
       <c r="E737" t="n">
-        <v>2.740735769271851</v>
+        <v>2.740735530853271</v>
       </c>
       <c r="F737" t="n">
         <v>5037400</v>
@@ -15172,16 +15172,16 @@
         <v>44860</v>
       </c>
       <c r="B738" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C738" t="n">
-        <v>2.749901729317672</v>
+        <v>2.749901993249675</v>
       </c>
       <c r="D738" t="n">
-        <v>2.438246278670322</v>
+        <v>2.438246512690039</v>
       </c>
       <c r="E738" t="n">
-        <v>2.749901729317672</v>
+        <v>2.749901993249675</v>
       </c>
       <c r="F738" t="n">
         <v>9447400</v>
@@ -15232,16 +15232,16 @@
         <v>44865</v>
       </c>
       <c r="B741" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="C741" t="n">
-        <v>2.832398806188871</v>
+        <v>2.832399050133704</v>
       </c>
       <c r="D741" t="n">
-        <v>2.55740866690086</v>
+        <v>2.557408887161731</v>
       </c>
       <c r="E741" t="n">
-        <v>2.59407398966692</v>
+        <v>2.59407421308565</v>
       </c>
       <c r="F741" t="n">
         <v>6603200</v>
@@ -15252,16 +15252,16 @@
         <v>44866</v>
       </c>
       <c r="B742" t="n">
-        <v>2.887397050857544</v>
+        <v>2.887397289276123</v>
       </c>
       <c r="C742" t="n">
-        <v>2.905729712507095</v>
+        <v>2.905729952439441</v>
       </c>
       <c r="D742" t="n">
-        <v>2.722402877469025</v>
+        <v>2.722403102263681</v>
       </c>
       <c r="E742" t="n">
-        <v>2.795733524067226</v>
+        <v>2.795733754916951</v>
       </c>
       <c r="F742" t="n">
         <v>5352800</v>
@@ -15272,16 +15272,16 @@
         <v>44868</v>
       </c>
       <c r="B743" t="n">
-        <v>2.878230810165405</v>
+        <v>2.878231048583984</v>
       </c>
       <c r="C743" t="n">
-        <v>2.960727790171799</v>
+        <v>2.960728035424025</v>
       </c>
       <c r="D743" t="n">
-        <v>2.804899942728261</v>
+        <v>2.804900175072469</v>
       </c>
       <c r="E743" t="n">
-        <v>2.823232604951904</v>
+        <v>2.8232328388147</v>
       </c>
       <c r="F743" t="n">
         <v>5003700</v>
@@ -15292,16 +15292,16 @@
         <v>44869</v>
       </c>
       <c r="B744" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="C744" t="n">
-        <v>2.933228662338098</v>
+        <v>2.933228914967061</v>
       </c>
       <c r="D744" t="n">
-        <v>2.768234491348267</v>
+        <v>2.768234729766846</v>
       </c>
       <c r="E744" t="n">
-        <v>2.924062331646583</v>
+        <v>2.924062583486082</v>
       </c>
       <c r="F744" t="n">
         <v>7869400</v>
@@ -15412,16 +15412,16 @@
         <v>44879</v>
       </c>
       <c r="B750" t="n">
-        <v>2.264086246490479</v>
+        <v>2.264086008071899</v>
       </c>
       <c r="C750" t="n">
-        <v>2.346583236569752</v>
+        <v>2.346582989463864</v>
       </c>
       <c r="D750" t="n">
-        <v>2.199921920873266</v>
+        <v>2.199921689211483</v>
       </c>
       <c r="E750" t="n">
-        <v>2.273252578721509</v>
+        <v>2.273252339337673</v>
       </c>
       <c r="F750" t="n">
         <v>5681600</v>
@@ -15472,16 +15472,16 @@
         <v>44883</v>
       </c>
       <c r="B753" t="n">
-        <v>2.117424488067627</v>
+        <v>2.117424726486206</v>
       </c>
       <c r="C753" t="n">
-        <v>2.291585000560438</v>
+        <v>2.29158525858921</v>
       </c>
       <c r="D753" t="n">
-        <v>2.108258156807088</v>
+        <v>2.108258394193553</v>
       </c>
       <c r="E753" t="n">
-        <v>2.218254350476129</v>
+        <v>2.218254600247988</v>
       </c>
       <c r="F753" t="n">
         <v>5301300</v>
@@ -15672,16 +15672,16 @@
         <v>44897</v>
       </c>
       <c r="B763" t="n">
-        <v>2.181588888168335</v>
+        <v>2.181589126586914</v>
       </c>
       <c r="C763" t="n">
-        <v>2.199921549535921</v>
+        <v>2.199921789958015</v>
       </c>
       <c r="D763" t="n">
-        <v>2.099091693471637</v>
+        <v>2.099091922874372</v>
       </c>
       <c r="E763" t="n">
-        <v>2.154089677574394</v>
+        <v>2.154089912987676</v>
       </c>
       <c r="F763" t="n">
         <v>2941200</v>
@@ -15752,16 +15752,16 @@
         <v>44903</v>
       </c>
       <c r="B767" t="n">
-        <v>2.117424488067627</v>
+        <v>2.117424726486206</v>
       </c>
       <c r="C767" t="n">
-        <v>2.199921687955051</v>
+        <v>2.199921935662682</v>
       </c>
       <c r="D767" t="n">
-        <v>2.099091825546549</v>
+        <v>2.099092061900901</v>
       </c>
       <c r="E767" t="n">
-        <v>2.172422475630859</v>
+        <v>2.172422720242123</v>
       </c>
       <c r="F767" t="n">
         <v>3353500</v>
@@ -15832,16 +15832,16 @@
         <v>44909</v>
       </c>
       <c r="B771" t="n">
-        <v>1.979929685592651</v>
+        <v>1.979929566383362</v>
       </c>
       <c r="C771" t="n">
-        <v>2.007428681685836</v>
+        <v>2.007428560820864</v>
       </c>
       <c r="D771" t="n">
-        <v>1.888266146739441</v>
+        <v>1.888266033049108</v>
       </c>
       <c r="E771" t="n">
-        <v>1.97076335356159</v>
+        <v>1.970763234904195</v>
       </c>
       <c r="F771" t="n">
         <v>6743600</v>
@@ -15892,16 +15892,16 @@
         <v>44914</v>
       </c>
       <c r="B774" t="n">
-        <v>1.924931287765503</v>
+        <v>1.924931406974792</v>
       </c>
       <c r="C774" t="n">
-        <v>1.970763162008669</v>
+        <v>1.970763284056286</v>
       </c>
       <c r="D774" t="n">
-        <v>1.778269989523604</v>
+        <v>1.77827009965029</v>
       </c>
       <c r="E774" t="n">
-        <v>1.80576898294396</v>
+        <v>1.805769094773634</v>
       </c>
       <c r="F774" t="n">
         <v>7674800</v>
@@ -15932,16 +15932,16 @@
         <v>44916</v>
       </c>
       <c r="B776" t="n">
-        <v>1.970763206481934</v>
+        <v>1.970763325691223</v>
       </c>
       <c r="C776" t="n">
-        <v>2.108258176686496</v>
+        <v>2.108258304212705</v>
       </c>
       <c r="D776" t="n">
-        <v>1.961596875134963</v>
+        <v>1.961596993789791</v>
       </c>
       <c r="E776" t="n">
-        <v>2.053260188604671</v>
+        <v>2.053260312804112</v>
       </c>
       <c r="F776" t="n">
         <v>5125400</v>
@@ -15972,16 +15972,16 @@
         <v>44918</v>
       </c>
       <c r="B778" t="n">
-        <v>1.9890958070755</v>
+        <v>1.98909592628479</v>
       </c>
       <c r="C778" t="n">
-        <v>2.016594800257883</v>
+        <v>2.016594921115226</v>
       </c>
       <c r="D778" t="n">
-        <v>1.906598608985781</v>
+        <v>1.906598723250898</v>
       </c>
       <c r="E778" t="n">
-        <v>1.915764940046575</v>
+        <v>1.915765054861043</v>
       </c>
       <c r="F778" t="n">
         <v>4257800</v>
@@ -16012,16 +16012,16 @@
         <v>44922</v>
       </c>
       <c r="B780" t="n">
-        <v>1.970763206481934</v>
+        <v>1.970763325691223</v>
       </c>
       <c r="C780" t="n">
-        <v>2.062426519951642</v>
+        <v>2.062426644705544</v>
       </c>
       <c r="D780" t="n">
-        <v>1.934097662551472</v>
+        <v>1.934097779542904</v>
       </c>
       <c r="E780" t="n">
-        <v>2.007428531869817</v>
+        <v>2.007428653296952</v>
       </c>
       <c r="F780" t="n">
         <v>3370000</v>
@@ -16092,16 +16092,16 @@
         <v>44929</v>
       </c>
       <c r="B784" t="n">
-        <v>1.94326388835907</v>
+        <v>1.943264007568359</v>
       </c>
       <c r="C784" t="n">
-        <v>2.071592738789653</v>
+        <v>2.07159286587126</v>
       </c>
       <c r="D784" t="n">
-        <v>1.94326388835907</v>
+        <v>1.943264007568359</v>
       </c>
       <c r="E784" t="n">
-        <v>2.007428422845644</v>
+        <v>2.007428545991099</v>
       </c>
       <c r="F784" t="n">
         <v>3677800</v>
@@ -16132,16 +16132,16 @@
         <v>44931</v>
       </c>
       <c r="B786" t="n">
-        <v>2.117424488067627</v>
+        <v>2.117424726486206</v>
       </c>
       <c r="C786" t="n">
-        <v>2.144923481849243</v>
+        <v>2.144923723364164</v>
       </c>
       <c r="D786" t="n">
-        <v>2.034927506722779</v>
+        <v>2.034927735852331</v>
       </c>
       <c r="E786" t="n">
-        <v>2.062426500504395</v>
+        <v>2.062426732730289</v>
       </c>
       <c r="F786" t="n">
         <v>4745800</v>
@@ -16232,16 +16232,16 @@
         <v>44938</v>
       </c>
       <c r="B791" t="n">
-        <v>2.337416410446167</v>
+        <v>2.337416648864746</v>
       </c>
       <c r="C791" t="n">
-        <v>2.410747271342309</v>
+        <v>2.410747517240701</v>
       </c>
       <c r="D791" t="n">
-        <v>2.19075512573899</v>
+        <v>2.190755349197985</v>
       </c>
       <c r="E791" t="n">
-        <v>2.282418428680975</v>
+        <v>2.282418661489711</v>
       </c>
       <c r="F791" t="n">
         <v>7447800</v>
@@ -16272,16 +16272,16 @@
         <v>44942</v>
       </c>
       <c r="B793" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C793" t="n">
-        <v>2.869064242488531</v>
+        <v>2.869064517857597</v>
       </c>
       <c r="D793" t="n">
-        <v>2.291584774431394</v>
+        <v>2.29158499437473</v>
       </c>
       <c r="E793" t="n">
-        <v>2.749901729317672</v>
+        <v>2.749901993249675</v>
       </c>
       <c r="F793" t="n">
         <v>29414600</v>
@@ -16292,16 +16292,16 @@
         <v>44943</v>
       </c>
       <c r="B794" t="n">
-        <v>2.392414808273315</v>
+        <v>2.392414569854736</v>
       </c>
       <c r="C794" t="n">
-        <v>2.667405202007624</v>
+        <v>2.667404936184592</v>
       </c>
       <c r="D794" t="n">
-        <v>2.319084153166882</v>
+        <v>2.319083922056145</v>
       </c>
       <c r="E794" t="n">
-        <v>2.438246686257428</v>
+        <v>2.438246443271425</v>
       </c>
       <c r="F794" t="n">
         <v>16937800</v>
@@ -16312,16 +16312,16 @@
         <v>44944</v>
       </c>
       <c r="B795" t="n">
-        <v>2.337416410446167</v>
+        <v>2.337416648864746</v>
       </c>
       <c r="C795" t="n">
-        <v>2.493244243990096</v>
+        <v>2.493244498303254</v>
       </c>
       <c r="D795" t="n">
-        <v>2.31908374985777</v>
+        <v>2.319083986406401</v>
       </c>
       <c r="E795" t="n">
-        <v>2.429079931930706</v>
+        <v>2.429080179699046</v>
       </c>
       <c r="F795" t="n">
         <v>5215700</v>
@@ -16352,16 +16352,16 @@
         <v>44946</v>
       </c>
       <c r="B797" t="n">
-        <v>2.814066410064697</v>
+        <v>2.814066171646118</v>
       </c>
       <c r="C797" t="n">
-        <v>2.823232741620247</v>
+        <v>2.823232502425061</v>
       </c>
       <c r="D797" t="n">
-        <v>2.291585074313209</v>
+        <v>2.291584880161267</v>
       </c>
       <c r="E797" t="n">
-        <v>2.300751405868758</v>
+        <v>2.30075121094021</v>
       </c>
       <c r="F797" t="n">
         <v>16674600</v>
@@ -16392,16 +16392,16 @@
         <v>44950</v>
       </c>
       <c r="B799" t="n">
-        <v>2.584908008575439</v>
+        <v>2.58490777015686</v>
       </c>
       <c r="C799" t="n">
-        <v>2.704070542224025</v>
+        <v>2.704070292814508</v>
       </c>
       <c r="D799" t="n">
-        <v>2.548242680850518</v>
+        <v>2.54824244581376</v>
       </c>
       <c r="E799" t="n">
-        <v>2.575741676644209</v>
+        <v>2.575741439071086</v>
       </c>
       <c r="F799" t="n">
         <v>6059800</v>
@@ -16412,16 +16412,16 @@
         <v>44951</v>
       </c>
       <c r="B800" t="n">
-        <v>2.694904088973999</v>
+        <v>2.694904327392578</v>
       </c>
       <c r="C800" t="n">
-        <v>2.786567404159816</v>
+        <v>2.786567650687862</v>
       </c>
       <c r="D800" t="n">
-        <v>2.566575229171273</v>
+        <v>2.566575456236579</v>
       </c>
       <c r="E800" t="n">
-        <v>2.584907892208437</v>
+        <v>2.584908120895635</v>
       </c>
       <c r="F800" t="n">
         <v>5346100</v>
@@ -16432,16 +16432,16 @@
         <v>44952</v>
       </c>
       <c r="B801" t="n">
-        <v>2.731569290161133</v>
+        <v>2.731569528579712</v>
       </c>
       <c r="C801" t="n">
-        <v>2.759068283459625</v>
+        <v>2.759068524278389</v>
       </c>
       <c r="D801" t="n">
-        <v>2.658238641365152</v>
+        <v>2.658238873383239</v>
       </c>
       <c r="E801" t="n">
-        <v>2.658238641365152</v>
+        <v>2.658238873383239</v>
       </c>
       <c r="F801" t="n">
         <v>3724800</v>
@@ -16492,16 +16492,16 @@
         <v>44957</v>
       </c>
       <c r="B804" t="n">
-        <v>2.731569290161133</v>
+        <v>2.731569528579712</v>
       </c>
       <c r="C804" t="n">
-        <v>2.77740094565862</v>
+        <v>2.777401188077508</v>
       </c>
       <c r="D804" t="n">
-        <v>2.575741442927102</v>
+        <v>2.575741667744615</v>
       </c>
       <c r="E804" t="n">
-        <v>2.649072310265655</v>
+        <v>2.64907254148368</v>
       </c>
       <c r="F804" t="n">
         <v>7856700</v>
@@ -16572,16 +16572,16 @@
         <v>44963</v>
       </c>
       <c r="B808" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C808" t="n">
-        <v>2.676571086469485</v>
+        <v>2.676571343363308</v>
       </c>
       <c r="D808" t="n">
-        <v>2.465745269738393</v>
+        <v>2.465745506397427</v>
       </c>
       <c r="E808" t="n">
-        <v>2.658238425757438</v>
+        <v>2.658238680891716</v>
       </c>
       <c r="F808" t="n">
         <v>3450900</v>
@@ -16592,16 +16592,16 @@
         <v>44964</v>
       </c>
       <c r="B809" t="n">
-        <v>2.392414808273315</v>
+        <v>2.392414569854736</v>
       </c>
       <c r="C809" t="n">
-        <v>2.557409000805383</v>
+        <v>2.557408745944136</v>
       </c>
       <c r="D809" t="n">
-        <v>2.392414808273315</v>
+        <v>2.392414569854736</v>
       </c>
       <c r="E809" t="n">
-        <v>2.484078345698949</v>
+        <v>2.484078098145545</v>
       </c>
       <c r="F809" t="n">
         <v>4061800</v>
@@ -16652,16 +16652,16 @@
         <v>44967</v>
       </c>
       <c r="B812" t="n">
-        <v>2.089925527572632</v>
+        <v>2.089925289154053</v>
       </c>
       <c r="C812" t="n">
-        <v>2.218254385806667</v>
+        <v>2.218254132748339</v>
       </c>
       <c r="D812" t="n">
-        <v>2.062426533353034</v>
+        <v>2.062426298071539</v>
       </c>
       <c r="E812" t="n">
-        <v>2.199921722993602</v>
+        <v>2.199921472026663</v>
       </c>
       <c r="F812" t="n">
         <v>5361500</v>
@@ -16752,16 +16752,16 @@
         <v>44974</v>
       </c>
       <c r="B817" t="n">
-        <v>1.961596965789795</v>
+        <v>1.961596846580505</v>
       </c>
       <c r="C817" t="n">
-        <v>2.099091942348662</v>
+        <v>2.09909181478359</v>
       </c>
       <c r="D817" t="n">
-        <v>1.961596965789795</v>
+        <v>1.961596846580505</v>
       </c>
       <c r="E817" t="n">
-        <v>2.053260283495706</v>
+        <v>2.053260158715895</v>
       </c>
       <c r="F817" t="n">
         <v>5027900</v>
@@ -16792,16 +16792,16 @@
         <v>44980</v>
       </c>
       <c r="B819" t="n">
-        <v>1.869933366775513</v>
+        <v>1.869933247566223</v>
       </c>
       <c r="C819" t="n">
-        <v>1.888266029701345</v>
+        <v>1.888265909323338</v>
       </c>
       <c r="D819" t="n">
-        <v>1.814935377998017</v>
+        <v>1.814935262294879</v>
       </c>
       <c r="E819" t="n">
-        <v>1.851600703849681</v>
+        <v>1.851600585809109</v>
       </c>
       <c r="F819" t="n">
         <v>3707800</v>
@@ -16912,16 +16912,16 @@
         <v>44988</v>
       </c>
       <c r="B825" t="n">
-        <v>2.493244409561157</v>
+        <v>2.493244647979736</v>
       </c>
       <c r="C825" t="n">
-        <v>2.566575056784478</v>
+        <v>2.566575302215361</v>
       </c>
       <c r="D825" t="n">
-        <v>1.998262103718605</v>
+        <v>1.998262294804088</v>
       </c>
       <c r="E825" t="n">
-        <v>2.025761096427351</v>
+        <v>2.025761290142448</v>
       </c>
       <c r="F825" t="n">
         <v>20771000</v>
@@ -17012,16 +17012,16 @@
         <v>44995</v>
       </c>
       <c r="B830" t="n">
-        <v>2.731569290161133</v>
+        <v>2.731569528579712</v>
       </c>
       <c r="C830" t="n">
-        <v>2.786567276758118</v>
+        <v>2.786567519977067</v>
       </c>
       <c r="D830" t="n">
-        <v>2.62157309842459</v>
+        <v>2.621573327242411</v>
       </c>
       <c r="E830" t="n">
-        <v>2.74073562126063</v>
+        <v>2.740735860479271</v>
       </c>
       <c r="F830" t="n">
         <v>5267200</v>
@@ -17032,16 +17032,16 @@
         <v>44998</v>
       </c>
       <c r="B831" t="n">
-        <v>2.841565370559692</v>
+        <v>2.841565608978271</v>
       </c>
       <c r="C831" t="n">
-        <v>2.924062572110139</v>
+        <v>2.92406281745056</v>
       </c>
       <c r="D831" t="n">
-        <v>2.621573197329468</v>
+        <v>2.621573417289834</v>
       </c>
       <c r="E831" t="n">
-        <v>2.685737735989278</v>
+        <v>2.685737961333302</v>
       </c>
       <c r="F831" t="n">
         <v>4540800</v>
@@ -17052,16 +17052,16 @@
         <v>44999</v>
       </c>
       <c r="B832" t="n">
-        <v>2.630739688873291</v>
+        <v>2.630739450454712</v>
       </c>
       <c r="C832" t="n">
-        <v>2.878231090043595</v>
+        <v>2.878230829195374</v>
       </c>
       <c r="D832" t="n">
-        <v>2.612407024866986</v>
+        <v>2.612406788109859</v>
       </c>
       <c r="E832" t="n">
-        <v>2.841565543488392</v>
+        <v>2.841565285963095</v>
       </c>
       <c r="F832" t="n">
         <v>4540300</v>
@@ -17092,16 +17092,16 @@
         <v>45001</v>
       </c>
       <c r="B834" t="n">
-        <v>2.731569290161133</v>
+        <v>2.731569528579712</v>
       </c>
       <c r="C834" t="n">
-        <v>2.795733607857616</v>
+        <v>2.795733851876625</v>
       </c>
       <c r="D834" t="n">
-        <v>2.694903965763142</v>
+        <v>2.694904200981475</v>
       </c>
       <c r="E834" t="n">
-        <v>2.749901952360128</v>
+        <v>2.74990219237883</v>
       </c>
       <c r="F834" t="n">
         <v>2894900</v>
@@ -17172,16 +17172,16 @@
         <v>45007</v>
       </c>
       <c r="B838" t="n">
-        <v>2.484077930450439</v>
+        <v>2.484078168869019</v>
       </c>
       <c r="C838" t="n">
-        <v>2.621572885790791</v>
+        <v>2.621573137405957</v>
       </c>
       <c r="D838" t="n">
-        <v>2.419913617958275</v>
+        <v>2.419913850218447</v>
       </c>
       <c r="E838" t="n">
-        <v>2.493244260806463</v>
+        <v>2.493244500104815</v>
       </c>
       <c r="F838" t="n">
         <v>4450900</v>
@@ -17272,16 +17272,16 @@
         <v>45014</v>
       </c>
       <c r="B843" t="n">
-        <v>2.575741291046143</v>
+        <v>2.575741529464722</v>
       </c>
       <c r="C843" t="n">
-        <v>2.676571145737662</v>
+        <v>2.676571393489365</v>
       </c>
       <c r="D843" t="n">
-        <v>2.511576977133168</v>
+        <v>2.511577209612499</v>
       </c>
       <c r="E843" t="n">
-        <v>2.658238484619669</v>
+        <v>2.658238730674444</v>
       </c>
       <c r="F843" t="n">
         <v>3021100</v>
@@ -17552,16 +17552,16 @@
         <v>45035</v>
       </c>
       <c r="B857" t="n">
-        <v>2.47491192817688</v>
+        <v>2.474911689758301</v>
       </c>
       <c r="C857" t="n">
-        <v>2.658238778142312</v>
+        <v>2.658238522063094</v>
       </c>
       <c r="D857" t="n">
-        <v>2.447412933463453</v>
+        <v>2.447412697693966</v>
       </c>
       <c r="E857" t="n">
-        <v>2.612406901744017</v>
+        <v>2.612406650079974</v>
       </c>
       <c r="F857" t="n">
         <v>4935800</v>
@@ -17572,16 +17572,16 @@
         <v>45036</v>
       </c>
       <c r="B858" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242330551147</v>
       </c>
       <c r="C858" t="n">
-        <v>2.603240558142417</v>
+        <v>2.603240314578118</v>
       </c>
       <c r="D858" t="n">
-        <v>2.419913927566782</v>
+        <v>2.419913701154883</v>
       </c>
       <c r="E858" t="n">
-        <v>2.484078248268254</v>
+        <v>2.484078015853015</v>
       </c>
       <c r="F858" t="n">
         <v>4312900</v>
@@ -17612,16 +17612,16 @@
         <v>45041</v>
       </c>
       <c r="B860" t="n">
-        <v>2.47491192817688</v>
+        <v>2.474911689758301</v>
       </c>
       <c r="C860" t="n">
-        <v>2.58490790703059</v>
+        <v>2.584907658015639</v>
       </c>
       <c r="D860" t="n">
-        <v>2.456579265034595</v>
+        <v>2.456579028382078</v>
       </c>
       <c r="E860" t="n">
-        <v>2.575741575459447</v>
+        <v>2.575741327327528</v>
       </c>
       <c r="F860" t="n">
         <v>2771300</v>
@@ -17652,16 +17652,16 @@
         <v>45043</v>
       </c>
       <c r="B862" t="n">
-        <v>2.47491192817688</v>
+        <v>2.474911689758301</v>
       </c>
       <c r="C862" t="n">
-        <v>2.520743586032592</v>
+        <v>2.520743343198859</v>
       </c>
       <c r="D862" t="n">
-        <v>2.429080270321168</v>
+        <v>2.429080036317743</v>
       </c>
       <c r="E862" t="n">
-        <v>2.520743586032592</v>
+        <v>2.520743343198859</v>
       </c>
       <c r="F862" t="n">
         <v>3614600</v>
@@ -17672,16 +17672,16 @@
         <v>45044</v>
       </c>
       <c r="B863" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242330551147</v>
       </c>
       <c r="C863" t="n">
-        <v>2.62157322119998</v>
+        <v>2.621572975920441</v>
       </c>
       <c r="D863" t="n">
-        <v>2.438246590624346</v>
+        <v>2.438246362497206</v>
       </c>
       <c r="E863" t="n">
-        <v>2.465745585210691</v>
+        <v>2.465745354510692</v>
       </c>
       <c r="F863" t="n">
         <v>4247000</v>
@@ -17692,16 +17692,16 @@
         <v>45048</v>
       </c>
       <c r="B864" t="n">
-        <v>2.685737609863281</v>
+        <v>2.68573784828186</v>
       </c>
       <c r="C864" t="n">
-        <v>2.749901926967264</v>
+        <v>2.749902171081845</v>
       </c>
       <c r="D864" t="n">
-        <v>2.419913791889924</v>
+        <v>2.419914006710763</v>
       </c>
       <c r="E864" t="n">
-        <v>2.54824242609789</v>
+        <v>2.548242652310732</v>
       </c>
       <c r="F864" t="n">
         <v>8626200</v>
@@ -17732,16 +17732,16 @@
         <v>45050</v>
       </c>
       <c r="B866" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232412338257</v>
       </c>
       <c r="C866" t="n">
-        <v>2.869064525602105</v>
+        <v>2.86906428331308</v>
       </c>
       <c r="D866" t="n">
-        <v>2.704070344369832</v>
+        <v>2.704070116014366</v>
       </c>
       <c r="E866" t="n">
-        <v>2.72240300689091</v>
+        <v>2.722402776987272</v>
       </c>
       <c r="F866" t="n">
         <v>5400200</v>
@@ -17812,16 +17812,16 @@
         <v>45056</v>
       </c>
       <c r="B870" t="n">
-        <v>3.373213291168213</v>
+        <v>3.373213052749634</v>
       </c>
       <c r="C870" t="n">
-        <v>3.400712285839649</v>
+        <v>3.400712045477442</v>
       </c>
       <c r="D870" t="n">
-        <v>3.199052773039869</v>
+        <v>3.199052546930949</v>
       </c>
       <c r="E870" t="n">
-        <v>3.199052773039869</v>
+        <v>3.199052546930949</v>
       </c>
       <c r="F870" t="n">
         <v>5129800</v>
@@ -17912,16 +17912,16 @@
         <v>45063</v>
       </c>
       <c r="B875" t="n">
-        <v>3.92319393157959</v>
+        <v>3.923193693161011</v>
       </c>
       <c r="C875" t="n">
-        <v>3.92319393157959</v>
+        <v>3.923193693161011</v>
       </c>
       <c r="D875" t="n">
-        <v>3.629870877835498</v>
+        <v>3.629870657242615</v>
       </c>
       <c r="E875" t="n">
-        <v>3.64820354137668</v>
+        <v>3.648203319669693</v>
       </c>
       <c r="F875" t="n">
         <v>6160500</v>
@@ -17932,16 +17932,16 @@
         <v>45064</v>
       </c>
       <c r="B876" t="n">
-        <v>3.950692415237427</v>
+        <v>3.950692653656006</v>
       </c>
       <c r="C876" t="n">
-        <v>3.959858964870517</v>
+        <v>3.959859203842285</v>
       </c>
       <c r="D876" t="n">
-        <v>3.749033131246008</v>
+        <v>3.749033357494741</v>
       </c>
       <c r="E876" t="n">
-        <v>3.91402709087535</v>
+        <v>3.91402732708123</v>
       </c>
       <c r="F876" t="n">
         <v>6670800</v>
@@ -17952,16 +17952,16 @@
         <v>45065</v>
       </c>
       <c r="B877" t="n">
-        <v>3.895694494247437</v>
+        <v>3.895694732666016</v>
       </c>
       <c r="C877" t="n">
-        <v>4.069855006440481</v>
+        <v>4.069855255517776</v>
       </c>
       <c r="D877" t="n">
-        <v>3.849862619481053</v>
+        <v>3.849862855094697</v>
       </c>
       <c r="E877" t="n">
-        <v>3.996524356482389</v>
+        <v>3.996524601071809</v>
       </c>
       <c r="F877" t="n">
         <v>6191700</v>
@@ -17972,16 +17972,16 @@
         <v>45068</v>
       </c>
       <c r="B878" t="n">
-        <v>3.92319393157959</v>
+        <v>3.923193693161011</v>
       </c>
       <c r="C878" t="n">
-        <v>3.996524585744319</v>
+        <v>3.996524342869322</v>
       </c>
       <c r="D878" t="n">
-        <v>3.859029390642864</v>
+        <v>3.859029156123663</v>
       </c>
       <c r="E878" t="n">
-        <v>3.904861268038407</v>
+        <v>3.904861030733933</v>
       </c>
       <c r="F878" t="n">
         <v>3483600</v>
@@ -17992,16 +17992,16 @@
         <v>45069</v>
       </c>
       <c r="B879" t="n">
-        <v>3.941526412963867</v>
+        <v>3.941526651382446</v>
       </c>
       <c r="C879" t="n">
-        <v>4.134019589792833</v>
+        <v>4.134019839855112</v>
       </c>
       <c r="D879" t="n">
-        <v>3.877361874992493</v>
+        <v>3.87736210952983</v>
       </c>
       <c r="E879" t="n">
-        <v>3.886527987796886</v>
+        <v>3.886528222888671</v>
       </c>
       <c r="F879" t="n">
         <v>4348000</v>
@@ -18012,16 +18012,16 @@
         <v>45070</v>
       </c>
       <c r="B880" t="n">
-        <v>3.88652777671814</v>
+        <v>3.886528015136719</v>
       </c>
       <c r="C880" t="n">
-        <v>4.069854830786153</v>
+        <v>4.069855080450908</v>
       </c>
       <c r="D880" t="n">
-        <v>3.776531806528411</v>
+        <v>3.7765320381993</v>
       </c>
       <c r="E880" t="n">
-        <v>3.923193537199848</v>
+        <v>3.923193777867684</v>
       </c>
       <c r="F880" t="n">
         <v>3446300</v>
@@ -18052,16 +18052,16 @@
         <v>45072</v>
       </c>
       <c r="B882" t="n">
-        <v>4.13401985168457</v>
+        <v>4.134019374847412</v>
       </c>
       <c r="C882" t="n">
-        <v>4.198183956635609</v>
+        <v>4.198183472397464</v>
       </c>
       <c r="D882" t="n">
-        <v>3.996524654227056</v>
+        <v>3.996524193249237</v>
       </c>
       <c r="E882" t="n">
-        <v>4.124853301214317</v>
+        <v>4.124852825434472</v>
       </c>
       <c r="F882" t="n">
         <v>4247000</v>
@@ -18072,16 +18072,16 @@
         <v>45075</v>
       </c>
       <c r="B883" t="n">
-        <v>4.143186092376709</v>
+        <v>4.143185615539551</v>
       </c>
       <c r="C883" t="n">
-        <v>4.189017971965877</v>
+        <v>4.189017489853952</v>
       </c>
       <c r="D883" t="n">
-        <v>4.042356219531656</v>
+        <v>4.042355754298956</v>
       </c>
       <c r="E883" t="n">
-        <v>4.179851421213965</v>
+        <v>4.179850940157013</v>
       </c>
       <c r="F883" t="n">
         <v>2372800</v>
@@ -18152,16 +18152,16 @@
         <v>45079</v>
       </c>
       <c r="B887" t="n">
-        <v>4.665667057037354</v>
+        <v>4.665667533874512</v>
       </c>
       <c r="C887" t="n">
-        <v>5.041486845665148</v>
+        <v>5.04148736091157</v>
       </c>
       <c r="D887" t="n">
-        <v>4.619835183606343</v>
+        <v>4.619835655759424</v>
       </c>
       <c r="E887" t="n">
-        <v>4.97732231027876</v>
+        <v>4.977322818967484</v>
       </c>
       <c r="F887" t="n">
         <v>8152400</v>
@@ -18172,16 +18172,16 @@
         <v>45082</v>
       </c>
       <c r="B888" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="C888" t="n">
-        <v>4.72066469090588</v>
+        <v>4.72066517241793</v>
       </c>
       <c r="D888" t="n">
-        <v>4.399842912066377</v>
+        <v>4.399843360854316</v>
       </c>
       <c r="E888" t="n">
-        <v>4.647334048552291</v>
+        <v>4.64733452258455</v>
       </c>
       <c r="F888" t="n">
         <v>6247400</v>
@@ -18292,16 +18292,16 @@
         <v>45091</v>
       </c>
       <c r="B894" t="n">
-        <v>4.784829616546631</v>
+        <v>4.784829139709473</v>
       </c>
       <c r="C894" t="n">
-        <v>4.80316228032324</v>
+        <v>4.803161801659121</v>
       </c>
       <c r="D894" t="n">
-        <v>4.234849266163195</v>
+        <v>4.234848844134898</v>
       </c>
       <c r="E894" t="n">
-        <v>4.335679135477132</v>
+        <v>4.335678703400531</v>
       </c>
       <c r="F894" t="n">
         <v>8037600</v>
@@ -18312,16 +18312,16 @@
         <v>45092</v>
       </c>
       <c r="B895" t="n">
-        <v>4.564837455749512</v>
+        <v>4.564836978912354</v>
       </c>
       <c r="C895" t="n">
-        <v>4.876493163691157</v>
+        <v>4.876492654298836</v>
       </c>
       <c r="D895" t="n">
-        <v>4.409009601778689</v>
+        <v>4.409009141219112</v>
       </c>
       <c r="E895" t="n">
-        <v>4.812328624678123</v>
+        <v>4.812328121988349</v>
       </c>
       <c r="F895" t="n">
         <v>10214700</v>
@@ -18352,16 +18352,16 @@
         <v>45096</v>
       </c>
       <c r="B897" t="n">
-        <v>4.51900577545166</v>
+        <v>4.519005298614502</v>
       </c>
       <c r="C897" t="n">
-        <v>4.555671103022796</v>
+        <v>4.55567062231678</v>
       </c>
       <c r="D897" t="n">
-        <v>4.390677128952687</v>
+        <v>4.39067666565653</v>
       </c>
       <c r="E897" t="n">
-        <v>4.418176343173629</v>
+        <v>4.418175876975806</v>
       </c>
       <c r="F897" t="n">
         <v>1994200</v>
@@ -18392,16 +18392,16 @@
         <v>45098</v>
       </c>
       <c r="B899" t="n">
-        <v>4.903992176055908</v>
+        <v>4.90399169921875</v>
       </c>
       <c r="C899" t="n">
-        <v>4.986489382037665</v>
+        <v>4.986488897178933</v>
       </c>
       <c r="D899" t="n">
-        <v>4.748164314572671</v>
+        <v>4.748163852887355</v>
       </c>
       <c r="E899" t="n">
-        <v>4.821495407159335</v>
+        <v>4.821494938343708</v>
       </c>
       <c r="F899" t="n">
         <v>4163100</v>
@@ -18452,16 +18452,16 @@
         <v>45103</v>
       </c>
       <c r="B902" t="n">
-        <v>4.922324657440186</v>
+        <v>4.922324180603027</v>
       </c>
       <c r="C902" t="n">
-        <v>4.968156533972024</v>
+        <v>4.968156052695024</v>
       </c>
       <c r="D902" t="n">
-        <v>4.812328678265975</v>
+        <v>4.812328212084386</v>
       </c>
       <c r="E902" t="n">
-        <v>4.968156533972024</v>
+        <v>4.968156052695024</v>
       </c>
       <c r="F902" t="n">
         <v>2732500</v>
@@ -18472,16 +18472,16 @@
         <v>45104</v>
       </c>
       <c r="B903" t="n">
-        <v>4.784829616546631</v>
+        <v>4.784829139709473</v>
       </c>
       <c r="C903" t="n">
-        <v>5.261479311823633</v>
+        <v>5.261478787485455</v>
       </c>
       <c r="D903" t="n">
-        <v>4.665667520541267</v>
+        <v>4.66566705557933</v>
       </c>
       <c r="E903" t="n">
-        <v>5.041487346504331</v>
+        <v>5.041486844089681</v>
       </c>
       <c r="F903" t="n">
         <v>7878800</v>
@@ -18572,16 +18572,16 @@
         <v>45111</v>
       </c>
       <c r="B908" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C908" t="n">
-        <v>5.087319262304525</v>
+        <v>5.087318782005757</v>
       </c>
       <c r="D908" t="n">
-        <v>4.876493408763784</v>
+        <v>4.87649294836929</v>
       </c>
       <c r="E908" t="n">
-        <v>4.94065751391628</v>
+        <v>4.940657047463991</v>
       </c>
       <c r="F908" t="n">
         <v>2828200</v>
@@ -18632,16 +18632,16 @@
         <v>45114</v>
       </c>
       <c r="B911" t="n">
-        <v>5.261479377746582</v>
+        <v>5.261478900909424</v>
       </c>
       <c r="C911" t="n">
-        <v>5.316477806850684</v>
+        <v>5.316477325029131</v>
       </c>
       <c r="D911" t="n">
-        <v>5.087319288229279</v>
+        <v>5.087318827175895</v>
       </c>
       <c r="E911" t="n">
-        <v>5.123984616241889</v>
+        <v>5.1239841518656</v>
       </c>
       <c r="F911" t="n">
         <v>2906900</v>
@@ -18652,16 +18652,16 @@
         <v>45117</v>
       </c>
       <c r="B912" t="n">
-        <v>5.105651378631592</v>
+        <v>5.10565185546875</v>
       </c>
       <c r="C912" t="n">
-        <v>5.261478786635867</v>
+        <v>5.261479278026369</v>
       </c>
       <c r="D912" t="n">
-        <v>5.078152167168991</v>
+        <v>5.078152641437889</v>
       </c>
       <c r="E912" t="n">
-        <v>5.252312674205093</v>
+        <v>5.252313164739535</v>
       </c>
       <c r="F912" t="n">
         <v>2082300</v>
@@ -18672,16 +18672,16 @@
         <v>45118</v>
       </c>
       <c r="B913" t="n">
-        <v>5.096485137939453</v>
+        <v>5.096484661102295</v>
       </c>
       <c r="C913" t="n">
-        <v>5.114817800997017</v>
+        <v>5.114817322444618</v>
       </c>
       <c r="D913" t="n">
-        <v>4.858160518191128</v>
+        <v>4.85816006365209</v>
       </c>
       <c r="E913" t="n">
-        <v>5.105651688010817</v>
+        <v>5.105651210316019</v>
       </c>
       <c r="F913" t="n">
         <v>3857700</v>
@@ -18692,16 +18692,16 @@
         <v>45119</v>
       </c>
       <c r="B914" t="n">
-        <v>5.325643539428711</v>
+        <v>5.325644016265869</v>
       </c>
       <c r="C914" t="n">
-        <v>5.573134704356201</v>
+        <v>5.573135203352744</v>
       </c>
       <c r="D914" t="n">
-        <v>5.178982237867281</v>
+        <v>5.178982701572964</v>
       </c>
       <c r="E914" t="n">
-        <v>5.178982237867281</v>
+        <v>5.178982701572964</v>
       </c>
       <c r="F914" t="n">
         <v>7685700</v>
@@ -18712,16 +18712,16 @@
         <v>45120</v>
       </c>
       <c r="B915" t="n">
-        <v>5.096485137939453</v>
+        <v>5.096484661102295</v>
       </c>
       <c r="C915" t="n">
-        <v>5.453972286104523</v>
+        <v>5.453971775820165</v>
       </c>
       <c r="D915" t="n">
-        <v>4.995655272580271</v>
+        <v>4.995654805176954</v>
       </c>
       <c r="E915" t="n">
-        <v>5.334810194772943</v>
+        <v>5.334809695637624</v>
       </c>
       <c r="F915" t="n">
         <v>4692200</v>
@@ -18772,16 +18772,16 @@
         <v>45125</v>
       </c>
       <c r="B918" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C918" t="n">
-        <v>5.041486503749065</v>
+        <v>5.041486987624404</v>
       </c>
       <c r="D918" t="n">
-        <v>4.711498173847115</v>
+        <v>4.711498626050601</v>
       </c>
       <c r="E918" t="n">
-        <v>4.720664722745693</v>
+        <v>4.720665175828972</v>
       </c>
       <c r="F918" t="n">
         <v>5384000</v>
@@ -18812,16 +18812,16 @@
         <v>45127</v>
       </c>
       <c r="B920" t="n">
-        <v>4.876493453979492</v>
+        <v>4.876492977142334</v>
       </c>
       <c r="C920" t="n">
-        <v>5.004822102559555</v>
+        <v>5.004821613174064</v>
       </c>
       <c r="D920" t="n">
-        <v>4.784829696479972</v>
+        <v>4.784829228605952</v>
       </c>
       <c r="E920" t="n">
-        <v>4.958990223809796</v>
+        <v>4.958989738905873</v>
       </c>
       <c r="F920" t="n">
         <v>2200400</v>
@@ -18832,16 +18832,16 @@
         <v>45128</v>
       </c>
       <c r="B921" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C921" t="n">
-        <v>5.169815198316529</v>
+        <v>5.169815688182035</v>
       </c>
       <c r="D921" t="n">
-        <v>4.85815996201701</v>
+        <v>4.858160422351643</v>
       </c>
       <c r="E921" t="n">
-        <v>4.85815996201701</v>
+        <v>4.858160422351643</v>
       </c>
       <c r="F921" t="n">
         <v>3946200</v>
@@ -18852,16 +18852,16 @@
         <v>45131</v>
       </c>
       <c r="B922" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C922" t="n">
-        <v>5.105651103503303</v>
+        <v>5.105651587288944</v>
       </c>
       <c r="D922" t="n">
-        <v>4.885658734912646</v>
+        <v>4.885659197852923</v>
       </c>
       <c r="E922" t="n">
-        <v>5.068985781585712</v>
+        <v>5.068986261897133</v>
       </c>
       <c r="F922" t="n">
         <v>2320000</v>
@@ -18872,16 +18872,16 @@
         <v>45132</v>
       </c>
       <c r="B923" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C923" t="n">
-        <v>5.270645052132461</v>
+        <v>5.270645551552092</v>
       </c>
       <c r="D923" t="n">
-        <v>4.995654700665417</v>
+        <v>4.995655174028355</v>
       </c>
       <c r="E923" t="n">
-        <v>5.096484554481348</v>
+        <v>5.096485037398413</v>
       </c>
       <c r="F923" t="n">
         <v>3865600</v>
@@ -18972,16 +18972,16 @@
         <v>45139</v>
       </c>
       <c r="B928" t="n">
-        <v>5.417306423187256</v>
+        <v>5.417306900024414</v>
       </c>
       <c r="C928" t="n">
-        <v>5.426472972350305</v>
+        <v>5.426473449994312</v>
       </c>
       <c r="D928" t="n">
-        <v>4.99565477755969</v>
+        <v>4.995655217282615</v>
       </c>
       <c r="E928" t="n">
-        <v>5.17898182705457</v>
+        <v>5.17898228291414</v>
       </c>
       <c r="F928" t="n">
         <v>5677300</v>
@@ -19012,16 +19012,16 @@
         <v>45141</v>
       </c>
       <c r="B930" t="n">
-        <v>5.343976020812988</v>
+        <v>5.343976497650146</v>
       </c>
       <c r="C930" t="n">
-        <v>5.573134515270389</v>
+        <v>5.573135012555111</v>
       </c>
       <c r="D930" t="n">
-        <v>5.298144584172593</v>
+        <v>5.298145056920261</v>
       </c>
       <c r="E930" t="n">
-        <v>5.463138542831271</v>
+        <v>5.463139030301171</v>
       </c>
       <c r="F930" t="n">
         <v>4853200</v>
@@ -19032,16 +19032,16 @@
         <v>45142</v>
       </c>
       <c r="B931" t="n">
-        <v>5.628132820129395</v>
+        <v>5.628132343292236</v>
       </c>
       <c r="C931" t="n">
-        <v>5.655632033338626</v>
+        <v>5.655631554171628</v>
       </c>
       <c r="D931" t="n">
-        <v>5.31647754724071</v>
+        <v>5.316477096808192</v>
       </c>
       <c r="E931" t="n">
-        <v>5.325643660253677</v>
+        <v>5.32564320904457</v>
       </c>
       <c r="F931" t="n">
         <v>4666200</v>
@@ -19052,16 +19052,16 @@
         <v>45145</v>
       </c>
       <c r="B932" t="n">
-        <v>5.343976020812988</v>
+        <v>5.343976497650146</v>
       </c>
       <c r="C932" t="n">
-        <v>5.6556317131423</v>
+        <v>5.655632217788156</v>
       </c>
       <c r="D932" t="n">
-        <v>5.325643358739802</v>
+        <v>5.325643833941156</v>
       </c>
       <c r="E932" t="n">
-        <v>5.6556317131423</v>
+        <v>5.655632217788156</v>
       </c>
       <c r="F932" t="n">
         <v>3282800</v>
@@ -19072,16 +19072,16 @@
         <v>45146</v>
       </c>
       <c r="B933" t="n">
-        <v>5.261479377746582</v>
+        <v>5.261478900909424</v>
       </c>
       <c r="C933" t="n">
-        <v>5.389808462875904</v>
+        <v>5.389807974408543</v>
       </c>
       <c r="D933" t="n">
-        <v>5.087319288229279</v>
+        <v>5.087318827175895</v>
       </c>
       <c r="E933" t="n">
-        <v>5.298145142844379</v>
+        <v>5.298144662684277</v>
       </c>
       <c r="F933" t="n">
         <v>3099900</v>
@@ -19132,16 +19132,16 @@
         <v>45149</v>
       </c>
       <c r="B936" t="n">
-        <v>6.1414475440979</v>
+        <v>6.141448020935059</v>
       </c>
       <c r="C936" t="n">
-        <v>6.324774603929047</v>
+        <v>6.32477509500017</v>
       </c>
       <c r="D936" t="n">
-        <v>5.426473278303354</v>
+        <v>5.426473699628144</v>
       </c>
       <c r="E936" t="n">
-        <v>5.664797887873155</v>
+        <v>5.664798327702056</v>
       </c>
       <c r="F936" t="n">
         <v>15335200</v>
@@ -19152,16 +19152,16 @@
         <v>45152</v>
       </c>
       <c r="B937" t="n">
-        <v>6.068116664886475</v>
+        <v>6.068117141723633</v>
       </c>
       <c r="C937" t="n">
-        <v>6.288109040924345</v>
+        <v>6.28810953504867</v>
       </c>
       <c r="D937" t="n">
-        <v>5.985619906321761</v>
+        <v>5.985620376676263</v>
       </c>
       <c r="E937" t="n">
-        <v>6.141447311204055</v>
+        <v>6.14144779380359</v>
       </c>
       <c r="F937" t="n">
         <v>5683800</v>
@@ -19232,16 +19232,16 @@
         <v>45156</v>
       </c>
       <c r="B941" t="n">
-        <v>5.710629463195801</v>
+        <v>5.710629940032959</v>
       </c>
       <c r="C941" t="n">
-        <v>5.838958092401009</v>
+        <v>5.838958579953599</v>
       </c>
       <c r="D941" t="n">
-        <v>5.33480968769513</v>
+        <v>5.334810133151363</v>
       </c>
       <c r="E941" t="n">
-        <v>5.609799607420576</v>
+        <v>5.609800075838448</v>
       </c>
       <c r="F941" t="n">
         <v>5405200</v>
@@ -19252,16 +19252,16 @@
         <v>45159</v>
       </c>
       <c r="B942" t="n">
-        <v>5.490637302398682</v>
+        <v>5.49063777923584</v>
       </c>
       <c r="C942" t="n">
-        <v>5.701463134206945</v>
+        <v>5.701463629353379</v>
       </c>
       <c r="D942" t="n">
-        <v>5.463138527906596</v>
+        <v>5.46313900235561</v>
       </c>
       <c r="E942" t="n">
-        <v>5.673964359714859</v>
+        <v>5.673964852473148</v>
       </c>
       <c r="F942" t="n">
         <v>3510600</v>
@@ -19272,16 +19272,16 @@
         <v>45160</v>
       </c>
       <c r="B943" t="n">
-        <v>5.628132820129395</v>
+        <v>5.628132343292236</v>
       </c>
       <c r="C943" t="n">
-        <v>5.646465483240493</v>
+        <v>5.646465004850121</v>
       </c>
       <c r="D943" t="n">
-        <v>5.408140862796206</v>
+        <v>5.408140404597616</v>
       </c>
       <c r="E943" t="n">
-        <v>5.563968717783131</v>
+        <v>5.563968246382204</v>
       </c>
       <c r="F943" t="n">
         <v>4158800</v>
@@ -19332,16 +19332,16 @@
         <v>45163</v>
       </c>
       <c r="B946" t="n">
-        <v>5.481471538543701</v>
+        <v>5.481471061706543</v>
       </c>
       <c r="C946" t="n">
-        <v>5.893956678839589</v>
+        <v>5.893956166120052</v>
       </c>
       <c r="D946" t="n">
-        <v>5.481471538543701</v>
+        <v>5.481471061706543</v>
       </c>
       <c r="E946" t="n">
-        <v>5.875624015650554</v>
+        <v>5.875623504525787</v>
       </c>
       <c r="F946" t="n">
         <v>3247600</v>
@@ -19372,16 +19372,16 @@
         <v>45167</v>
       </c>
       <c r="B948" t="n">
-        <v>5.21564769744873</v>
+        <v>5.215647220611572</v>
       </c>
       <c r="C948" t="n">
-        <v>5.33481022657585</v>
+        <v>5.334809738844336</v>
       </c>
       <c r="D948" t="n">
-        <v>5.013987965528194</v>
+        <v>5.013987507127645</v>
       </c>
       <c r="E948" t="n">
-        <v>5.206481147322721</v>
+        <v>5.206480671323608</v>
       </c>
       <c r="F948" t="n">
         <v>3286000</v>
@@ -19412,16 +19412,16 @@
         <v>45169</v>
       </c>
       <c r="B950" t="n">
-        <v>4.903992176055908</v>
+        <v>4.90399169921875</v>
       </c>
       <c r="C950" t="n">
-        <v>5.032320823183499</v>
+        <v>5.03232033386837</v>
       </c>
       <c r="D950" t="n">
-        <v>4.858160734910076</v>
+        <v>4.858160262529314</v>
       </c>
       <c r="E950" t="n">
-        <v>5.032320823183499</v>
+        <v>5.03232033386837</v>
       </c>
       <c r="F950" t="n">
         <v>3681000</v>
@@ -19432,16 +19432,16 @@
         <v>45170</v>
       </c>
       <c r="B951" t="n">
-        <v>5.151482582092285</v>
+        <v>5.151483058929443</v>
       </c>
       <c r="C951" t="n">
-        <v>5.169815243210278</v>
+        <v>5.169815721744364</v>
       </c>
       <c r="D951" t="n">
-        <v>4.876492665322393</v>
+        <v>4.876493116705634</v>
       </c>
       <c r="E951" t="n">
-        <v>4.949823309794364</v>
+        <v>4.949823767965317</v>
       </c>
       <c r="F951" t="n">
         <v>4962000</v>
@@ -19472,16 +19472,16 @@
         <v>45174</v>
       </c>
       <c r="B953" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C953" t="n">
-        <v>5.032319954850488</v>
+        <v>5.032320437846034</v>
       </c>
       <c r="D953" t="n">
-        <v>4.858159896628598</v>
+        <v>4.858160362908486</v>
       </c>
       <c r="E953" t="n">
-        <v>4.995654633426395</v>
+        <v>4.99565511290285</v>
       </c>
       <c r="F953" t="n">
         <v>3096400</v>
@@ -19492,16 +19492,16 @@
         <v>45175</v>
       </c>
       <c r="B954" t="n">
-        <v>4.986488819122314</v>
+        <v>4.986489295959473</v>
       </c>
       <c r="C954" t="n">
-        <v>5.105651339402779</v>
+        <v>5.105651827634952</v>
       </c>
       <c r="D954" t="n">
-        <v>4.949823495510654</v>
+        <v>4.94982396884166</v>
       </c>
       <c r="E954" t="n">
-        <v>4.949823495510654</v>
+        <v>4.94982396884166</v>
       </c>
       <c r="F954" t="n">
         <v>4361600</v>
@@ -19512,16 +19512,16 @@
         <v>45177</v>
       </c>
       <c r="B955" t="n">
-        <v>4.876493453979492</v>
+        <v>4.876492977142334</v>
       </c>
       <c r="C955" t="n">
-        <v>5.004822102559555</v>
+        <v>5.004821613174064</v>
       </c>
       <c r="D955" t="n">
-        <v>4.867326903395464</v>
+        <v>4.867326427454637</v>
       </c>
       <c r="E955" t="n">
-        <v>4.977322887892662</v>
+        <v>4.97732240119612</v>
       </c>
       <c r="F955" t="n">
         <v>2168000</v>
@@ -19552,16 +19552,16 @@
         <v>45181</v>
       </c>
       <c r="B957" t="n">
-        <v>5.05065393447876</v>
+        <v>5.050653457641602</v>
       </c>
       <c r="C957" t="n">
-        <v>5.105651926217408</v>
+        <v>5.105651444187835</v>
       </c>
       <c r="D957" t="n">
-        <v>4.913158736589549</v>
+        <v>4.913158272733446</v>
       </c>
       <c r="E957" t="n">
-        <v>4.913158736589549</v>
+        <v>4.913158272733446</v>
       </c>
       <c r="F957" t="n">
         <v>2356100</v>
@@ -19592,16 +19592,16 @@
         <v>45183</v>
       </c>
       <c r="B959" t="n">
-        <v>5.059819221496582</v>
+        <v>5.05981969833374</v>
       </c>
       <c r="C959" t="n">
-        <v>5.188147847927461</v>
+        <v>5.188148336858303</v>
       </c>
       <c r="D959" t="n">
-        <v>4.995654689738586</v>
+        <v>4.995655160528882</v>
       </c>
       <c r="E959" t="n">
-        <v>5.178981736010669</v>
+        <v>5.178982224077697</v>
       </c>
       <c r="F959" t="n">
         <v>3749200</v>
@@ -19632,16 +19632,16 @@
         <v>45187</v>
       </c>
       <c r="B961" t="n">
-        <v>4.784829616546631</v>
+        <v>4.784829139709473</v>
       </c>
       <c r="C961" t="n">
-        <v>4.876493372514855</v>
+        <v>4.876492886542851</v>
       </c>
       <c r="D961" t="n">
-        <v>4.67483363388698</v>
+        <v>4.674833168011586</v>
       </c>
       <c r="E961" t="n">
-        <v>4.720665511871093</v>
+        <v>4.720665041428274</v>
       </c>
       <c r="F961" t="n">
         <v>2815400</v>
@@ -19672,16 +19672,16 @@
         <v>45189</v>
       </c>
       <c r="B963" t="n">
-        <v>4.968155860900879</v>
+        <v>4.968156337738037</v>
       </c>
       <c r="C963" t="n">
-        <v>5.114817146597253</v>
+        <v>5.114817637510772</v>
       </c>
       <c r="D963" t="n">
-        <v>4.711498173847115</v>
+        <v>4.711498626050601</v>
       </c>
       <c r="E963" t="n">
-        <v>4.720664722745693</v>
+        <v>4.720665175828972</v>
       </c>
       <c r="F963" t="n">
         <v>5388800</v>
@@ -19712,16 +19712,16 @@
         <v>45191</v>
       </c>
       <c r="B965" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="C965" t="n">
-        <v>4.867325975613057</v>
+        <v>4.86732647208469</v>
       </c>
       <c r="D965" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="E965" t="n">
-        <v>4.812327993847866</v>
+        <v>4.812328484709655</v>
       </c>
       <c r="F965" t="n">
         <v>2426200</v>
@@ -19732,16 +19732,16 @@
         <v>45194</v>
       </c>
       <c r="B966" t="n">
-        <v>4.601502418518066</v>
+        <v>4.601502895355225</v>
       </c>
       <c r="C966" t="n">
-        <v>4.665666952466343</v>
+        <v>4.665667435952641</v>
       </c>
       <c r="D966" t="n">
-        <v>4.509839110795621</v>
+        <v>4.50983957813404</v>
       </c>
       <c r="E966" t="n">
-        <v>4.574003207658769</v>
+        <v>4.574003681646282</v>
       </c>
       <c r="F966" t="n">
         <v>3919300</v>
@@ -19772,16 +19772,16 @@
         <v>45196</v>
       </c>
       <c r="B968" t="n">
-        <v>4.57400369644165</v>
+        <v>4.574003219604492</v>
       </c>
       <c r="C968" t="n">
-        <v>4.748164218267839</v>
+        <v>4.748163723274551</v>
       </c>
       <c r="D968" t="n">
-        <v>4.399843611700637</v>
+        <v>4.399843153019563</v>
       </c>
       <c r="E968" t="n">
-        <v>4.537338369434576</v>
+        <v>4.537337896419757</v>
       </c>
       <c r="F968" t="n">
         <v>5812700</v>
@@ -19852,16 +19852,16 @@
         <v>45202</v>
       </c>
       <c r="B972" t="n">
-        <v>4.31734561920166</v>
+        <v>4.317346096038818</v>
       </c>
       <c r="C972" t="n">
-        <v>4.674832710799063</v>
+        <v>4.674833227119539</v>
       </c>
       <c r="D972" t="n">
-        <v>4.308179070580783</v>
+        <v>4.308179546405524</v>
       </c>
       <c r="E972" t="n">
-        <v>4.619834730329086</v>
+        <v>4.619835240575209</v>
       </c>
       <c r="F972" t="n">
         <v>3808300</v>
@@ -19872,16 +19872,16 @@
         <v>45203</v>
       </c>
       <c r="B973" t="n">
-        <v>4.665667057037354</v>
+        <v>4.665667533874512</v>
       </c>
       <c r="C973" t="n">
-        <v>4.711498493383226</v>
+        <v>4.711498974904416</v>
       </c>
       <c r="D973" t="n">
-        <v>4.372344028666186</v>
+        <v>4.372344475525354</v>
       </c>
       <c r="E973" t="n">
-        <v>4.372344028666186</v>
+        <v>4.372344475525354</v>
       </c>
       <c r="F973" t="n">
         <v>5930500</v>
@@ -19932,16 +19932,16 @@
         <v>45208</v>
       </c>
       <c r="B976" t="n">
-        <v>4.564837455749512</v>
+        <v>4.564836978912354</v>
       </c>
       <c r="C976" t="n">
-        <v>4.610669331770987</v>
+        <v>4.61066885014629</v>
       </c>
       <c r="D976" t="n">
-        <v>4.427342264770247</v>
+        <v>4.427341802295663</v>
       </c>
       <c r="E976" t="n">
-        <v>4.564837455749512</v>
+        <v>4.564836978912354</v>
       </c>
       <c r="F976" t="n">
         <v>2689100</v>
@@ -19952,16 +19952,16 @@
         <v>45209</v>
       </c>
       <c r="B977" t="n">
-        <v>4.839827537536621</v>
+        <v>4.839828014373779</v>
       </c>
       <c r="C977" t="n">
-        <v>4.949823508663896</v>
+        <v>4.949823996338252</v>
       </c>
       <c r="D977" t="n">
-        <v>4.610669045812228</v>
+        <v>4.610669500071872</v>
       </c>
       <c r="E977" t="n">
-        <v>4.610669045812228</v>
+        <v>4.610669500071872</v>
       </c>
       <c r="F977" t="n">
         <v>4133600</v>
@@ -20032,16 +20032,16 @@
         <v>45216</v>
       </c>
       <c r="B981" t="n">
-        <v>4.674832820892334</v>
+        <v>4.674833297729492</v>
       </c>
       <c r="C981" t="n">
-        <v>4.812327993847866</v>
+        <v>4.812328484709655</v>
       </c>
       <c r="D981" t="n">
-        <v>4.601502178538746</v>
+        <v>4.601502647896112</v>
       </c>
       <c r="E981" t="n">
-        <v>4.656500160303938</v>
+        <v>4.656500635271147</v>
       </c>
       <c r="F981" t="n">
         <v>2762000</v>
@@ -20212,16 +20212,16 @@
         <v>45229</v>
       </c>
       <c r="B990" t="n">
-        <v>4.528172492980957</v>
+        <v>4.528172016143799</v>
       </c>
       <c r="C990" t="n">
-        <v>4.812329010685496</v>
+        <v>4.812328503925364</v>
       </c>
       <c r="D990" t="n">
-        <v>4.519005942207328</v>
+        <v>4.519005466335449</v>
       </c>
       <c r="E990" t="n">
-        <v>4.775663681761375</v>
+        <v>4.775663178862269</v>
       </c>
       <c r="F990" t="n">
         <v>3890600</v>
@@ -20472,16 +20472,16 @@
         <v>45250</v>
       </c>
       <c r="B1003" t="n">
-        <v>7.571396827697754</v>
+        <v>7.571397304534912</v>
       </c>
       <c r="C1003" t="n">
-        <v>7.763889997017875</v>
+        <v>7.763890485978015</v>
       </c>
       <c r="D1003" t="n">
-        <v>7.543897179101823</v>
+        <v>7.543897654207089</v>
       </c>
       <c r="E1003" t="n">
-        <v>7.699725024464316</v>
+        <v>7.699725509383425</v>
       </c>
       <c r="F1003" t="n">
         <v>4266000</v>
@@ -20532,16 +20532,16 @@
         <v>45253</v>
       </c>
       <c r="B1006" t="n">
-        <v>7.094747066497803</v>
+        <v>7.094746589660645</v>
       </c>
       <c r="C1006" t="n">
-        <v>7.32390557025422</v>
+        <v>7.323905078015344</v>
       </c>
       <c r="D1006" t="n">
-        <v>7.094747066497803</v>
+        <v>7.094746589660645</v>
       </c>
       <c r="E1006" t="n">
-        <v>7.314739457388246</v>
+        <v>7.314738965765423</v>
       </c>
       <c r="F1006" t="n">
         <v>2414400</v>
@@ -20552,16 +20552,16 @@
         <v>45254</v>
       </c>
       <c r="B1007" t="n">
-        <v>7.122246265411377</v>
+        <v>7.122245788574219</v>
       </c>
       <c r="C1007" t="n">
-        <v>7.259741454814795</v>
+        <v>7.25974096877228</v>
       </c>
       <c r="D1007" t="n">
-        <v>6.819757110974954</v>
+        <v>6.819756654389562</v>
       </c>
       <c r="E1007" t="n">
-        <v>7.076414389915185</v>
+        <v>7.076413916146489</v>
       </c>
       <c r="F1007" t="n">
         <v>3112700</v>
@@ -20652,16 +20652,16 @@
         <v>45261</v>
       </c>
       <c r="B1012" t="n">
-        <v>7.901384830474854</v>
+        <v>7.901385307312012</v>
       </c>
       <c r="C1012" t="n">
-        <v>7.910551380107944</v>
+        <v>7.910551857498291</v>
       </c>
       <c r="D1012" t="n">
-        <v>7.433901289230667</v>
+        <v>7.433901737855869</v>
       </c>
       <c r="E1012" t="n">
-        <v>7.534731586854091</v>
+        <v>7.534732041564257</v>
       </c>
       <c r="F1012" t="n">
         <v>6875500</v>
@@ -20752,16 +20752,16 @@
         <v>45268</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.718058109283447</v>
+        <v>7.718058586120605</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.800555306578421</v>
+        <v>7.800555788512423</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.580563363238674</v>
+        <v>7.580563831581132</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.69972501025333</v>
+        <v>7.699725485957833</v>
       </c>
       <c r="F1017" t="n">
         <v>1787800</v>
@@ -20772,16 +20772,16 @@
         <v>45271</v>
       </c>
       <c r="B1018" t="n">
-        <v>7.672226428985596</v>
+        <v>7.672225952148438</v>
       </c>
       <c r="C1018" t="n">
-        <v>7.892218377862459</v>
+        <v>7.892217887352564</v>
       </c>
       <c r="D1018" t="n">
-        <v>7.626394554427008</v>
+        <v>7.62639408043835</v>
       </c>
       <c r="E1018" t="n">
-        <v>7.699725204052629</v>
+        <v>7.699724725506393</v>
       </c>
       <c r="F1018" t="n">
         <v>2800600</v>
@@ -20792,16 +20792,16 @@
         <v>45272</v>
       </c>
       <c r="B1019" t="n">
-        <v>7.855553150177002</v>
+        <v>7.85555362701416</v>
       </c>
       <c r="C1019" t="n">
-        <v>8.048046326366851</v>
+        <v>8.048046814888467</v>
       </c>
       <c r="D1019" t="n">
-        <v>7.672226523846268</v>
+        <v>7.672226989555381</v>
       </c>
       <c r="E1019" t="n">
-        <v>7.672226523846268</v>
+        <v>7.672226989555381</v>
       </c>
       <c r="F1019" t="n">
         <v>3402200</v>
@@ -20832,16 +20832,16 @@
         <v>45274</v>
       </c>
       <c r="B1021" t="n">
-        <v>7.965549468994141</v>
+        <v>7.965548992156982</v>
       </c>
       <c r="C1021" t="n">
-        <v>8.378035488713973</v>
+        <v>8.3780349871844</v>
       </c>
       <c r="D1021" t="n">
-        <v>7.828054711867761</v>
+        <v>7.828054243261374</v>
       </c>
       <c r="E1021" t="n">
-        <v>8.112211650544717</v>
+        <v>8.112211164928006</v>
       </c>
       <c r="F1021" t="n">
         <v>4147000</v>
@@ -20992,16 +20992,16 @@
         <v>45287</v>
       </c>
       <c r="B1029" t="n">
-        <v>7.232241630554199</v>
+        <v>7.232242107391357</v>
       </c>
       <c r="C1029" t="n">
-        <v>7.333071485868728</v>
+        <v>7.333071969353814</v>
       </c>
       <c r="D1029" t="n">
-        <v>7.140578324397864</v>
+        <v>7.140578795191465</v>
       </c>
       <c r="E1029" t="n">
-        <v>7.195576308091665</v>
+        <v>7.195576782511401</v>
       </c>
       <c r="F1029" t="n">
         <v>1937700</v>
@@ -21072,16 +21072,16 @@
         <v>45295</v>
       </c>
       <c r="B1033" t="n">
-        <v>6.654763698577881</v>
+        <v>6.654763221740723</v>
       </c>
       <c r="C1033" t="n">
-        <v>6.865589119529635</v>
+        <v>6.865588627586096</v>
       </c>
       <c r="D1033" t="n">
-        <v>6.645597147883356</v>
+        <v>6.645596671703013</v>
       </c>
       <c r="E1033" t="n">
-        <v>6.847256455225779</v>
+        <v>6.847255964595839</v>
       </c>
       <c r="F1033" t="n">
         <v>2993800</v>
@@ -21132,16 +21132,16 @@
         <v>45300</v>
       </c>
       <c r="B1036" t="n">
-        <v>7.278073787689209</v>
+        <v>7.278074264526367</v>
       </c>
       <c r="C1036" t="n">
-        <v>7.351404872576131</v>
+        <v>7.351405354217717</v>
       </c>
       <c r="D1036" t="n">
-        <v>6.792257590374687</v>
+        <v>6.792258035382652</v>
       </c>
       <c r="E1036" t="n">
-        <v>6.957251985013838</v>
+        <v>6.957252440831732</v>
       </c>
       <c r="F1036" t="n">
         <v>2899300</v>
@@ -21252,16 +21252,16 @@
         <v>45308</v>
       </c>
       <c r="B1042" t="n">
-        <v>6.792257785797119</v>
+        <v>6.792258262634277</v>
       </c>
       <c r="C1042" t="n">
-        <v>6.819756998056547</v>
+        <v>6.819757476824233</v>
       </c>
       <c r="D1042" t="n">
-        <v>6.581431948758679</v>
+        <v>6.581432410795222</v>
       </c>
       <c r="E1042" t="n">
-        <v>6.645596485973909</v>
+        <v>6.645596952514998</v>
       </c>
       <c r="F1042" t="n">
         <v>2272700</v>
@@ -21392,16 +21392,16 @@
         <v>45317</v>
       </c>
       <c r="B1049" t="n">
-        <v>7.094747066497803</v>
+        <v>7.094746589660645</v>
       </c>
       <c r="C1049" t="n">
-        <v>7.177244267717364</v>
+        <v>7.177243785335578</v>
       </c>
       <c r="D1049" t="n">
-        <v>6.718927260204529</v>
+        <v>6.718926808626178</v>
       </c>
       <c r="E1049" t="n">
-        <v>6.957252313912079</v>
+        <v>6.957251846315928</v>
       </c>
       <c r="F1049" t="n">
         <v>2582000</v>
@@ -21472,16 +21472,16 @@
         <v>45323</v>
       </c>
       <c r="B1053" t="n">
-        <v>6.746426582336426</v>
+        <v>6.746426105499268</v>
       </c>
       <c r="C1053" t="n">
-        <v>6.801424571679298</v>
+        <v>6.801424090954884</v>
       </c>
       <c r="D1053" t="n">
-        <v>6.508101524765483</v>
+        <v>6.50810106477313</v>
       </c>
       <c r="E1053" t="n">
-        <v>6.691428592993554</v>
+        <v>6.691428120043652</v>
       </c>
       <c r="F1053" t="n">
         <v>3298500</v>
@@ -21492,16 +21492,16 @@
         <v>45324</v>
       </c>
       <c r="B1054" t="n">
-        <v>6.654763698577881</v>
+        <v>6.654763221740723</v>
       </c>
       <c r="C1054" t="n">
-        <v>6.893088334528017</v>
+        <v>6.893087840614063</v>
       </c>
       <c r="D1054" t="n">
-        <v>6.489769282757977</v>
+        <v>6.489768817743247</v>
       </c>
       <c r="E1054" t="n">
-        <v>6.746427020097165</v>
+        <v>6.746426536692008</v>
       </c>
       <c r="F1054" t="n">
         <v>2155700</v>
@@ -21532,16 +21532,16 @@
         <v>45328</v>
       </c>
       <c r="B1056" t="n">
-        <v>6.792257785797119</v>
+        <v>6.792258262634277</v>
       </c>
       <c r="C1056" t="n">
-        <v>6.856422323012349</v>
+        <v>6.856422804354053</v>
       </c>
       <c r="D1056" t="n">
-        <v>6.434770648935468</v>
+        <v>6.434771100675943</v>
       </c>
       <c r="E1056" t="n">
-        <v>6.434770648935468</v>
+        <v>6.434771100675943</v>
       </c>
       <c r="F1056" t="n">
         <v>4148600</v>
@@ -21612,16 +21612,16 @@
         <v>45336</v>
       </c>
       <c r="B1060" t="n">
-        <v>7.388070583343506</v>
+        <v>7.388070106506348</v>
       </c>
       <c r="C1060" t="n">
-        <v>7.507232236633438</v>
+        <v>7.507231752105407</v>
       </c>
       <c r="D1060" t="n">
-        <v>7.18641085424382</v>
+        <v>7.186410390422084</v>
       </c>
       <c r="E1060" t="n">
-        <v>7.452234684987365</v>
+        <v>7.452234204008959</v>
       </c>
       <c r="F1060" t="n">
         <v>1805400</v>
@@ -21672,16 +21672,16 @@
         <v>45341</v>
       </c>
       <c r="B1063" t="n">
-        <v>7.26890754699707</v>
+        <v>7.268908023834229</v>
       </c>
       <c r="C1063" t="n">
-        <v>7.470566837019639</v>
+        <v>7.470567327085559</v>
       </c>
       <c r="D1063" t="n">
-        <v>7.213909558809097</v>
+        <v>7.213910032038411</v>
       </c>
       <c r="E1063" t="n">
-        <v>7.470566837019639</v>
+        <v>7.470567327085559</v>
       </c>
       <c r="F1063" t="n">
         <v>2309200</v>
@@ -21752,16 +21752,16 @@
         <v>45345</v>
       </c>
       <c r="B1067" t="n">
-        <v>7.910551071166992</v>
+        <v>7.91055154800415</v>
       </c>
       <c r="C1067" t="n">
-        <v>8.249705526813331</v>
+        <v>8.249706024094255</v>
       </c>
       <c r="D1067" t="n">
-        <v>7.754723230171342</v>
+        <v>7.754723697615412</v>
       </c>
       <c r="E1067" t="n">
-        <v>8.07554546143774</v>
+        <v>8.075545948220533</v>
       </c>
       <c r="F1067" t="n">
         <v>3191100</v>
@@ -21812,16 +21812,16 @@
         <v>45350</v>
       </c>
       <c r="B1070" t="n">
-        <v>8.240540504455566</v>
+        <v>8.24053955078125</v>
       </c>
       <c r="C1070" t="n">
-        <v>8.414701476272281</v>
+        <v>8.414700502442388</v>
       </c>
       <c r="D1070" t="n">
-        <v>8.093879185559649</v>
+        <v>8.093878248858385</v>
       </c>
       <c r="E1070" t="n">
-        <v>8.167209845007607</v>
+        <v>8.167208899819817</v>
       </c>
       <c r="F1070" t="n">
         <v>4318300</v>
@@ -21912,16 +21912,16 @@
         <v>45357</v>
       </c>
       <c r="B1075" t="n">
-        <v>8.680523872375488</v>
+        <v>8.680524826049805</v>
       </c>
       <c r="C1075" t="n">
-        <v>8.928014587759865</v>
+        <v>8.928015568624422</v>
       </c>
       <c r="D1075" t="n">
-        <v>8.570527901741292</v>
+        <v>8.570528843331045</v>
       </c>
       <c r="E1075" t="n">
-        <v>8.836351715983168</v>
+        <v>8.836352686777305</v>
       </c>
       <c r="F1075" t="n">
         <v>5652400</v>
@@ -22012,16 +22012,16 @@
         <v>45364</v>
       </c>
       <c r="B1080" t="n">
-        <v>9.083843231201172</v>
+        <v>9.083842277526855</v>
       </c>
       <c r="C1080" t="n">
-        <v>9.166340434983276</v>
+        <v>9.166339472647927</v>
       </c>
       <c r="D1080" t="n">
-        <v>8.900516597335576</v>
+        <v>8.900515662907948</v>
       </c>
       <c r="E1080" t="n">
-        <v>8.94634847434456</v>
+        <v>8.946347535105238</v>
       </c>
       <c r="F1080" t="n">
         <v>1693700</v>
@@ -22132,16 +22132,16 @@
         <v>45372</v>
       </c>
       <c r="B1086" t="n">
-        <v>8.891349792480469</v>
+        <v>8.891348838806152</v>
       </c>
       <c r="C1086" t="n">
-        <v>9.193838948238987</v>
+        <v>9.193837962120087</v>
       </c>
       <c r="D1086" t="n">
-        <v>8.873017566704057</v>
+        <v>8.873016614996031</v>
       </c>
       <c r="E1086" t="n">
-        <v>9.193838948238987</v>
+        <v>9.193837962120087</v>
       </c>
       <c r="F1086" t="n">
         <v>2233600</v>
@@ -22232,16 +22232,16 @@
         <v>45379</v>
       </c>
       <c r="B1091" t="n">
-        <v>9.752986907958984</v>
+        <v>9.752985954284668</v>
       </c>
       <c r="C1091" t="n">
-        <v>9.881315119453859</v>
+        <v>9.881314153231251</v>
       </c>
       <c r="D1091" t="n">
-        <v>9.340500873381522</v>
+        <v>9.340499960041242</v>
       </c>
       <c r="E1091" t="n">
-        <v>9.386332752131281</v>
+        <v>9.386331834309434</v>
       </c>
       <c r="F1091" t="n">
         <v>5263200</v>
@@ -22312,16 +22312,16 @@
         <v>45386</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127555847168</v>
       </c>
       <c r="C1095" t="n">
-        <v>11.18293432413664</v>
+        <v>11.1829352953242</v>
       </c>
       <c r="D1095" t="n">
-        <v>10.43129474410425</v>
+        <v>10.43129565001529</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.43129474410425</v>
+        <v>10.43129565001529</v>
       </c>
       <c r="F1095" t="n">
         <v>7684100</v>
@@ -22332,16 +22332,16 @@
         <v>45387</v>
       </c>
       <c r="B1096" t="n">
-        <v>11.06377220153809</v>
+        <v>11.06377124786377</v>
       </c>
       <c r="C1096" t="n">
-        <v>11.1737681776445</v>
+        <v>11.17376721448876</v>
       </c>
       <c r="D1096" t="n">
-        <v>10.80711492395645</v>
+        <v>10.80711399240546</v>
       </c>
       <c r="E1096" t="n">
-        <v>10.91711090006287</v>
+        <v>10.91710995903045</v>
       </c>
       <c r="F1096" t="n">
         <v>3157700</v>
@@ -22452,16 +22452,16 @@
         <v>45397</v>
       </c>
       <c r="B1102" t="n">
-        <v>9.21217155456543</v>
+        <v>9.212172508239746</v>
       </c>
       <c r="C1102" t="n">
-        <v>10.1838030712505</v>
+        <v>10.18380412551131</v>
       </c>
       <c r="D1102" t="n">
-        <v>9.19383845560105</v>
+        <v>9.193839407377462</v>
       </c>
       <c r="E1102" t="n">
-        <v>10.09214019893942</v>
+        <v>10.09214124371098</v>
       </c>
       <c r="F1102" t="n">
         <v>5108900</v>
@@ -22472,16 +22472,16 @@
         <v>45398</v>
       </c>
       <c r="B1103" t="n">
-        <v>9.258003234863281</v>
+        <v>9.258004188537598</v>
       </c>
       <c r="C1103" t="n">
-        <v>9.578824592521357</v>
+        <v>9.578825579243738</v>
       </c>
       <c r="D1103" t="n">
-        <v>8.946347552326104</v>
+        <v>8.946348473896519</v>
       </c>
       <c r="E1103" t="n">
-        <v>9.111341068715591</v>
+        <v>9.11134200728212</v>
       </c>
       <c r="F1103" t="n">
         <v>5545500</v>
@@ -22612,16 +22612,16 @@
         <v>45407</v>
       </c>
       <c r="B1110" t="n">
-        <v>9.936311721801758</v>
+        <v>9.936312675476074</v>
       </c>
       <c r="C1110" t="n">
-        <v>10.00964236464995</v>
+        <v>10.00964332536244</v>
       </c>
       <c r="D1110" t="n">
-        <v>9.505493539440995</v>
+        <v>9.505494451765941</v>
       </c>
       <c r="E1110" t="n">
-        <v>9.670487922934525</v>
+        <v>9.670488851095419</v>
       </c>
       <c r="F1110" t="n">
         <v>2344600</v>
@@ -22632,16 +22632,16 @@
         <v>45408</v>
       </c>
       <c r="B1111" t="n">
-        <v>10.9629430770874</v>
+        <v>10.96294212341309</v>
       </c>
       <c r="C1111" t="n">
-        <v>10.9629430770874</v>
+        <v>10.96294212341309</v>
       </c>
       <c r="D1111" t="n">
-        <v>9.991310616813005</v>
+        <v>9.991309747661697</v>
       </c>
       <c r="E1111" t="n">
-        <v>10.05547559360238</v>
+        <v>10.05547471886932</v>
       </c>
       <c r="F1111" t="n">
         <v>5850400</v>
@@ -22652,16 +22652,16 @@
         <v>45411</v>
       </c>
       <c r="B1112" t="n">
-        <v>10.91711139678955</v>
+        <v>10.91711044311523</v>
       </c>
       <c r="C1112" t="n">
-        <v>11.02710737790076</v>
+        <v>11.02710641461765</v>
       </c>
       <c r="D1112" t="n">
-        <v>10.58712345345591</v>
+        <v>10.58712252860799</v>
       </c>
       <c r="E1112" t="n">
-        <v>10.97210982443033</v>
+        <v>10.97210886595158</v>
       </c>
       <c r="F1112" t="n">
         <v>2155000</v>
@@ -22672,16 +22672,16 @@
         <v>45412</v>
       </c>
       <c r="B1113" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C1113" t="n">
-        <v>10.89877940479569</v>
+        <v>10.89877837583131</v>
       </c>
       <c r="D1113" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="E1113" t="n">
-        <v>10.86211407696992</v>
+        <v>10.86211305146715</v>
       </c>
       <c r="F1113" t="n">
         <v>3726700</v>
@@ -22692,16 +22692,16 @@
         <v>45414</v>
       </c>
       <c r="B1114" t="n">
-        <v>10.21130275726318</v>
+        <v>10.2113037109375</v>
       </c>
       <c r="C1114" t="n">
-        <v>10.57795599619694</v>
+        <v>10.57795698411446</v>
       </c>
       <c r="D1114" t="n">
-        <v>10.12880555996052</v>
+        <v>10.1288065059301</v>
       </c>
       <c r="E1114" t="n">
-        <v>10.35796405283668</v>
+        <v>10.35796502020828</v>
       </c>
       <c r="F1114" t="n">
         <v>4263300</v>
@@ -22832,16 +22832,16 @@
         <v>45425</v>
       </c>
       <c r="B1121" t="n">
-        <v>9.303833961486816</v>
+        <v>9.303834915161133</v>
       </c>
       <c r="C1121" t="n">
-        <v>9.569657763981576</v>
+        <v>9.569658744903728</v>
       </c>
       <c r="D1121" t="n">
-        <v>9.184672320860052</v>
+        <v>9.184673262319901</v>
       </c>
       <c r="E1121" t="n">
-        <v>9.395497703383034</v>
+        <v>9.395498666453195</v>
       </c>
       <c r="F1121" t="n">
         <v>4893500</v>
@@ -22892,16 +22892,16 @@
         <v>45428</v>
       </c>
       <c r="B1124" t="n">
-        <v>9.679655075073242</v>
+        <v>9.679656028747559</v>
       </c>
       <c r="C1124" t="n">
-        <v>9.890480467857952</v>
+        <v>9.890481442303543</v>
       </c>
       <c r="D1124" t="n">
-        <v>9.441330033879009</v>
+        <v>9.441330964072689</v>
       </c>
       <c r="E1124" t="n">
-        <v>9.64298975136415</v>
+        <v>9.642990701426069</v>
       </c>
       <c r="F1124" t="n">
         <v>3881300</v>
@@ -22952,16 +22952,16 @@
         <v>45433</v>
       </c>
       <c r="B1127" t="n">
-        <v>9.441329956054688</v>
+        <v>9.441330909729004</v>
       </c>
       <c r="C1127" t="n">
-        <v>9.734652543309581</v>
+        <v>9.734653526612586</v>
       </c>
       <c r="D1127" t="n">
-        <v>9.29466866242724</v>
+        <v>9.294669601287213</v>
       </c>
       <c r="E1127" t="n">
-        <v>9.505494053474129</v>
+        <v>9.5054950136297</v>
       </c>
       <c r="F1127" t="n">
         <v>2273300</v>
@@ -23232,16 +23232,16 @@
         <v>45454</v>
       </c>
       <c r="B1141" t="n">
-        <v>9.258003234863281</v>
+        <v>9.258004188537598</v>
       </c>
       <c r="C1141" t="n">
-        <v>9.258003234863281</v>
+        <v>9.258004188537598</v>
       </c>
       <c r="D1141" t="n">
-        <v>8.900515680040591</v>
+        <v>8.900516596889828</v>
       </c>
       <c r="E1141" t="n">
-        <v>8.909682229331745</v>
+        <v>8.909683147125236</v>
       </c>
       <c r="F1141" t="n">
         <v>1877100</v>
@@ -23312,16 +23312,16 @@
         <v>45460</v>
       </c>
       <c r="B1145" t="n">
-        <v>8.799687385559082</v>
+        <v>8.799686431884766</v>
       </c>
       <c r="C1145" t="n">
-        <v>8.863851490461268</v>
+        <v>8.863850529833108</v>
       </c>
       <c r="D1145" t="n">
-        <v>8.533863541316691</v>
+        <v>8.53386261645128</v>
       </c>
       <c r="E1145" t="n">
-        <v>8.689690528340522</v>
+        <v>8.689689586587217</v>
       </c>
       <c r="F1145" t="n">
         <v>3062700</v>
@@ -23372,16 +23372,16 @@
         <v>45463</v>
       </c>
       <c r="B1148" t="n">
-        <v>8.515529632568359</v>
+        <v>8.515530586242676</v>
       </c>
       <c r="C1148" t="n">
-        <v>9.138841018215004</v>
+        <v>9.138842041695439</v>
       </c>
       <c r="D1148" t="n">
-        <v>8.515529632568359</v>
+        <v>8.515530586242676</v>
       </c>
       <c r="E1148" t="n">
-        <v>8.708022803184512</v>
+        <v>8.708023778416594</v>
       </c>
       <c r="F1148" t="n">
         <v>9391200</v>
@@ -23392,16 +23392,16 @@
         <v>45464</v>
       </c>
       <c r="B1149" t="n">
-        <v>8.845518112182617</v>
+        <v>8.845517158508301</v>
       </c>
       <c r="C1149" t="n">
-        <v>8.873017762710186</v>
+        <v>8.873016806071011</v>
       </c>
       <c r="D1149" t="n">
-        <v>8.515530173384843</v>
+        <v>8.515529255287982</v>
       </c>
       <c r="E1149" t="n">
-        <v>8.5246967235607</v>
+        <v>8.524695804475552</v>
       </c>
       <c r="F1149" t="n">
         <v>2442900</v>
@@ -23412,16 +23412,16 @@
         <v>45467</v>
       </c>
       <c r="B1150" t="n">
-        <v>9.258003234863281</v>
+        <v>9.258004188537598</v>
       </c>
       <c r="C1150" t="n">
-        <v>9.294668557857641</v>
+        <v>9.294669515308881</v>
       </c>
       <c r="D1150" t="n">
-        <v>8.946347552326104</v>
+        <v>8.946348473896519</v>
       </c>
       <c r="E1150" t="n">
-        <v>8.946347552326104</v>
+        <v>8.946348473896519</v>
       </c>
       <c r="F1150" t="n">
         <v>2223300</v>
@@ -23492,16 +23492,16 @@
         <v>45471</v>
       </c>
       <c r="B1154" t="n">
-        <v>8.561361312866211</v>
+        <v>8.561362266540527</v>
       </c>
       <c r="C1154" t="n">
-        <v>9.074675840127375</v>
+        <v>9.074676850981254</v>
       </c>
       <c r="D1154" t="n">
-        <v>8.54302821409318</v>
+        <v>8.543029165725322</v>
       </c>
       <c r="E1154" t="n">
-        <v>8.891349223248387</v>
+        <v>8.891350213680994</v>
       </c>
       <c r="F1154" t="n">
         <v>1597200</v>
@@ -23552,16 +23552,16 @@
         <v>45476</v>
       </c>
       <c r="B1157" t="n">
-        <v>8.799687385559082</v>
+        <v>8.799686431884766</v>
       </c>
       <c r="C1157" t="n">
-        <v>8.983014023972736</v>
+        <v>8.983013050430225</v>
       </c>
       <c r="D1157" t="n">
-        <v>8.497198213633959</v>
+        <v>8.497197292742189</v>
       </c>
       <c r="E1157" t="n">
-        <v>8.497198213633959</v>
+        <v>8.497197292742189</v>
       </c>
       <c r="F1157" t="n">
         <v>3434600</v>
@@ -23612,16 +23612,16 @@
         <v>45481</v>
       </c>
       <c r="B1160" t="n">
-        <v>9.03801155090332</v>
+        <v>9.038010597229004</v>
       </c>
       <c r="C1160" t="n">
-        <v>9.166340634487476</v>
+        <v>9.16633966727211</v>
       </c>
       <c r="D1160" t="n">
-        <v>8.827186135911884</v>
+        <v>8.827185204483476</v>
       </c>
       <c r="E1160" t="n">
-        <v>9.157174084052102</v>
+        <v>9.157173117803973</v>
       </c>
       <c r="F1160" t="n">
         <v>5497000</v>
@@ -23692,16 +23692,16 @@
         <v>45485</v>
       </c>
       <c r="B1164" t="n">
-        <v>9.661322593688965</v>
+        <v>9.661321640014648</v>
       </c>
       <c r="C1164" t="n">
-        <v>10.25713436058879</v>
+        <v>10.25713334810158</v>
       </c>
       <c r="D1164" t="n">
-        <v>9.587991941583457</v>
+        <v>9.587990995147649</v>
       </c>
       <c r="E1164" t="n">
-        <v>10.09214083043656</v>
+        <v>10.09213983423595</v>
       </c>
       <c r="F1164" t="n">
         <v>2566400</v>
@@ -23732,16 +23732,16 @@
         <v>45489</v>
       </c>
       <c r="B1166" t="n">
-        <v>9.303833961486816</v>
+        <v>9.303834915161133</v>
       </c>
       <c r="C1166" t="n">
-        <v>9.789650569698455</v>
+        <v>9.789651573170611</v>
       </c>
       <c r="D1166" t="n">
-        <v>9.258002964708936</v>
+        <v>9.258003913685421</v>
       </c>
       <c r="E1166" t="n">
-        <v>9.743818698750346</v>
+        <v>9.743819697524581</v>
       </c>
       <c r="F1166" t="n">
         <v>1952400</v>
@@ -23752,16 +23752,16 @@
         <v>45490</v>
       </c>
       <c r="B1167" t="n">
-        <v>9.03801155090332</v>
+        <v>9.038010597229004</v>
       </c>
       <c r="C1167" t="n">
-        <v>9.422997927485424</v>
+        <v>9.422996933188054</v>
       </c>
       <c r="D1167" t="n">
-        <v>8.955515219496039</v>
+        <v>8.955514274526582</v>
       </c>
       <c r="E1167" t="n">
-        <v>9.322168495207393</v>
+        <v>9.322167511549358</v>
       </c>
       <c r="F1167" t="n">
         <v>2370500</v>
@@ -23852,16 +23852,16 @@
         <v>45497</v>
       </c>
       <c r="B1172" t="n">
-        <v>7.892219066619873</v>
+        <v>7.892218589782715</v>
       </c>
       <c r="C1172" t="n">
-        <v>8.185542564891128</v>
+        <v>8.185542070331762</v>
       </c>
       <c r="D1172" t="n">
-        <v>7.892219066619873</v>
+        <v>7.892218589782715</v>
       </c>
       <c r="E1172" t="n">
-        <v>8.176376014345381</v>
+        <v>8.176375520339846</v>
       </c>
       <c r="F1172" t="n">
         <v>3298400</v>
@@ -23872,16 +23872,16 @@
         <v>45498</v>
       </c>
       <c r="B1173" t="n">
-        <v>7.699725151062012</v>
+        <v>7.69972562789917</v>
       </c>
       <c r="C1173" t="n">
-        <v>7.965548972668025</v>
+        <v>7.965549465967418</v>
       </c>
       <c r="D1173" t="n">
-        <v>7.635561051623754</v>
+        <v>7.635561524487287</v>
       </c>
       <c r="E1173" t="n">
-        <v>7.818887674426128</v>
+        <v>7.818888158642915</v>
       </c>
       <c r="F1173" t="n">
         <v>2073700</v>
@@ -23892,16 +23892,16 @@
         <v>45499</v>
       </c>
       <c r="B1174" t="n">
-        <v>7.818887710571289</v>
+        <v>7.818888187408447</v>
       </c>
       <c r="C1174" t="n">
-        <v>7.883052684476461</v>
+        <v>7.883053165226739</v>
       </c>
       <c r="D1174" t="n">
-        <v>7.653894186371567</v>
+        <v>7.653894653146547</v>
       </c>
       <c r="E1174" t="n">
-        <v>7.718058286106443</v>
+        <v>7.718058756794488</v>
       </c>
       <c r="F1174" t="n">
         <v>2119900</v>
@@ -23912,16 +23912,16 @@
         <v>45502</v>
       </c>
       <c r="B1175" t="n">
-        <v>7.699725151062012</v>
+        <v>7.69972562789917</v>
       </c>
       <c r="C1175" t="n">
-        <v>8.121376820592616</v>
+        <v>8.121377323542289</v>
       </c>
       <c r="D1175" t="n">
-        <v>7.617228826428662</v>
+        <v>7.617229298156897</v>
       </c>
       <c r="E1175" t="n">
-        <v>7.864719548669293</v>
+        <v>7.864720035724408</v>
       </c>
       <c r="F1175" t="n">
         <v>1787300</v>
@@ -23932,16 +23932,16 @@
         <v>45503</v>
       </c>
       <c r="B1176" t="n">
-        <v>7.617228507995605</v>
+        <v>7.617228984832764</v>
       </c>
       <c r="C1176" t="n">
-        <v>7.736390152207957</v>
+        <v>7.736390636504614</v>
       </c>
       <c r="D1176" t="n">
-        <v>7.470566341714527</v>
+        <v>7.47056680937066</v>
       </c>
       <c r="E1176" t="n">
-        <v>7.672226055452036</v>
+        <v>7.672226535732031</v>
       </c>
       <c r="F1176" t="n">
         <v>1625200</v>
@@ -23952,16 +23952,16 @@
         <v>45504</v>
       </c>
       <c r="B1177" t="n">
-        <v>7.736390590667725</v>
+        <v>7.736391067504883</v>
       </c>
       <c r="C1177" t="n">
-        <v>7.873886215441875</v>
+        <v>7.873886700753659</v>
       </c>
       <c r="D1177" t="n">
-        <v>7.617228939701889</v>
+        <v>7.617229409194445</v>
       </c>
       <c r="E1177" t="n">
-        <v>7.718058365200021</v>
+        <v>7.718058840907261</v>
       </c>
       <c r="F1177" t="n">
         <v>1863600</v>
@@ -23972,16 +23972,16 @@
         <v>45505</v>
       </c>
       <c r="B1178" t="n">
-        <v>7.727224826812744</v>
+        <v>7.727225303649902</v>
       </c>
       <c r="C1178" t="n">
-        <v>7.965549000194251</v>
+        <v>7.965549491738089</v>
       </c>
       <c r="D1178" t="n">
-        <v>7.663059852982463</v>
+        <v>7.663060325860083</v>
       </c>
       <c r="E1178" t="n">
-        <v>7.828054251159909</v>
+        <v>7.828054734219122</v>
       </c>
       <c r="F1178" t="n">
         <v>2732500</v>
@@ -24012,16 +24012,16 @@
         <v>45509</v>
       </c>
       <c r="B1180" t="n">
-        <v>7.983881950378418</v>
+        <v>7.983882904052734</v>
       </c>
       <c r="C1180" t="n">
-        <v>8.057212598381986</v>
+        <v>8.057213560815645</v>
       </c>
       <c r="D1180" t="n">
-        <v>7.54389718818673</v>
+        <v>7.543898089304888</v>
       </c>
       <c r="E1180" t="n">
-        <v>7.718058132822914</v>
+        <v>7.718059054744589</v>
       </c>
       <c r="F1180" t="n">
         <v>2386300</v>
@@ -24032,16 +24032,16 @@
         <v>45510</v>
       </c>
       <c r="B1181" t="n">
-        <v>7.956383228302002</v>
+        <v>7.95638370513916</v>
       </c>
       <c r="C1181" t="n">
-        <v>8.176375173761064</v>
+        <v>8.176375663782647</v>
       </c>
       <c r="D1181" t="n">
-        <v>7.782222282519196</v>
+        <v>7.782222748918646</v>
       </c>
       <c r="E1181" t="n">
-        <v>7.993048552545178</v>
+        <v>7.993049031579741</v>
       </c>
       <c r="F1181" t="n">
         <v>1835500</v>
@@ -24072,16 +24072,16 @@
         <v>45512</v>
       </c>
       <c r="B1183" t="n">
-        <v>7.92888355255127</v>
+        <v>7.928884029388428</v>
       </c>
       <c r="C1183" t="n">
-        <v>8.93718127706809</v>
+        <v>8.937181814543523</v>
       </c>
       <c r="D1183" t="n">
-        <v>7.699725058267473</v>
+        <v>7.699725521323209</v>
       </c>
       <c r="E1183" t="n">
-        <v>8.882182853805054</v>
+        <v>8.882183387972923</v>
       </c>
       <c r="F1183" t="n">
         <v>8733800</v>
@@ -24092,16 +24092,16 @@
         <v>45513</v>
       </c>
       <c r="B1184" t="n">
-        <v>7.84638786315918</v>
+        <v>7.846387386322021</v>
       </c>
       <c r="C1184" t="n">
-        <v>8.103045152735731</v>
+        <v>8.103044660301112</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.653894677434178</v>
+        <v>7.653894212295129</v>
       </c>
       <c r="E1184" t="n">
-        <v>8.103045152735731</v>
+        <v>8.103044660301112</v>
       </c>
       <c r="F1184" t="n">
         <v>6458600</v>
@@ -24312,16 +24312,16 @@
         <v>45530</v>
       </c>
       <c r="B1195" t="n">
-        <v>9.258003234863281</v>
+        <v>9.258004188537598</v>
       </c>
       <c r="C1195" t="n">
-        <v>9.523827045114947</v>
+        <v>9.523828026171985</v>
       </c>
       <c r="D1195" t="n">
-        <v>9.038010422726874</v>
+        <v>9.038011353739554</v>
       </c>
       <c r="E1195" t="n">
-        <v>9.50549394653264</v>
+        <v>9.505494925701171</v>
       </c>
       <c r="F1195" t="n">
         <v>2395100</v>
@@ -24412,16 +24412,16 @@
         <v>45537</v>
       </c>
       <c r="B1200" t="n">
-        <v>8.937182426452637</v>
+        <v>8.93718147277832</v>
       </c>
       <c r="C1200" t="n">
-        <v>9.248838158626967</v>
+        <v>9.2488371716963</v>
       </c>
       <c r="D1200" t="n">
-        <v>8.918849324950433</v>
+        <v>8.918848373232414</v>
       </c>
       <c r="E1200" t="n">
-        <v>9.120509070622715</v>
+        <v>9.120508097385867</v>
       </c>
       <c r="F1200" t="n">
         <v>2102800</v>
@@ -24432,16 +24432,16 @@
         <v>45538</v>
       </c>
       <c r="B1201" t="n">
-        <v>9.129674911499023</v>
+        <v>9.129673957824707</v>
       </c>
       <c r="C1201" t="n">
-        <v>9.404665293457553</v>
+        <v>9.404664311058088</v>
       </c>
       <c r="D1201" t="n">
-        <v>8.973847057528202</v>
+        <v>8.973846120131466</v>
       </c>
       <c r="E1201" t="n">
-        <v>9.001345833472957</v>
+        <v>9.001344893203733</v>
       </c>
       <c r="F1201" t="n">
         <v>3313500</v>
@@ -24472,16 +24472,16 @@
         <v>45540</v>
       </c>
       <c r="B1203" t="n">
-        <v>9.441329956054688</v>
+        <v>9.441330909729004</v>
       </c>
       <c r="C1203" t="n">
-        <v>9.450496505448969</v>
+        <v>9.450497460049204</v>
       </c>
       <c r="D1203" t="n">
-        <v>9.193838367430672</v>
+        <v>9.193839296105716</v>
       </c>
       <c r="E1203" t="n">
-        <v>9.193838367430672</v>
+        <v>9.193839296105716</v>
       </c>
       <c r="F1203" t="n">
         <v>1502700</v>
@@ -24532,16 +24532,16 @@
         <v>45545</v>
       </c>
       <c r="B1206" t="n">
-        <v>9.203004837036133</v>
+        <v>9.203005790710449</v>
       </c>
       <c r="C1206" t="n">
-        <v>9.294668581843707</v>
+        <v>9.294669545016808</v>
       </c>
       <c r="D1206" t="n">
-        <v>8.983012898502263</v>
+        <v>8.983013829379605</v>
       </c>
       <c r="E1206" t="n">
-        <v>9.093008867769198</v>
+        <v>9.093009810045027</v>
       </c>
       <c r="F1206" t="n">
         <v>1213500</v>
@@ -24592,16 +24592,16 @@
         <v>45548</v>
       </c>
       <c r="B1209" t="n">
-        <v>9.661322593688965</v>
+        <v>9.661321640014648</v>
       </c>
       <c r="C1209" t="n">
-        <v>9.734653245794471</v>
+        <v>9.734652284881648</v>
       </c>
       <c r="D1209" t="n">
-        <v>9.203005580944383</v>
+        <v>9.203004672510785</v>
       </c>
       <c r="E1209" t="n">
-        <v>9.203005580944383</v>
+        <v>9.203004672510785</v>
       </c>
       <c r="F1209" t="n">
         <v>2443600</v>
@@ -24612,16 +24612,16 @@
         <v>45551</v>
       </c>
       <c r="B1210" t="n">
-        <v>9.936311721801758</v>
+        <v>9.936312675476074</v>
       </c>
       <c r="C1210" t="n">
-        <v>10.17463674814347</v>
+        <v>10.17463772469192</v>
       </c>
       <c r="D1210" t="n">
-        <v>9.569657633390603</v>
+        <v>9.569658551873937</v>
       </c>
       <c r="E1210" t="n">
-        <v>9.707153244358619</v>
+        <v>9.707154176038602</v>
       </c>
       <c r="F1210" t="n">
         <v>2756600</v>
@@ -24632,16 +24632,16 @@
         <v>45552</v>
       </c>
       <c r="B1211" t="n">
-        <v>9.79881763458252</v>
+        <v>9.798816680908203</v>
       </c>
       <c r="C1211" t="n">
-        <v>10.0004773708589</v>
+        <v>10.00047639755796</v>
       </c>
       <c r="D1211" t="n">
-        <v>9.688821653205498</v>
+        <v>9.688820710236589</v>
       </c>
       <c r="E1211" t="n">
-        <v>9.899647939805888</v>
+        <v>9.899646976318216</v>
       </c>
       <c r="F1211" t="n">
         <v>1833800</v>
@@ -24652,16 +24652,16 @@
         <v>45553</v>
       </c>
       <c r="B1212" t="n">
-        <v>9.890480995178223</v>
+        <v>9.890480041503906</v>
       </c>
       <c r="C1212" t="n">
-        <v>10.26630080177617</v>
+        <v>10.26629981186401</v>
       </c>
       <c r="D1212" t="n">
-        <v>9.606324065654963</v>
+        <v>9.60632313938004</v>
       </c>
       <c r="E1212" t="n">
-        <v>9.697987816899968</v>
+        <v>9.697986881786509</v>
       </c>
       <c r="F1212" t="n">
         <v>2495300</v>
@@ -24672,16 +24672,16 @@
         <v>45554</v>
       </c>
       <c r="B1213" t="n">
-        <v>9.853816032409668</v>
+        <v>9.853815078735352</v>
       </c>
       <c r="C1213" t="n">
-        <v>10.15630519881978</v>
+        <v>10.15630421586989</v>
       </c>
       <c r="D1213" t="n">
-        <v>9.798817604803125</v>
+        <v>9.798816656451679</v>
       </c>
       <c r="E1213" t="n">
-        <v>10.00047734046665</v>
+        <v>10.00047637259812</v>
       </c>
       <c r="F1213" t="n">
         <v>3128500</v>
@@ -24832,16 +24832,16 @@
         <v>45566</v>
       </c>
       <c r="B1221" t="n">
-        <v>9.441329956054688</v>
+        <v>9.441330909729004</v>
       </c>
       <c r="C1221" t="n">
-        <v>9.881313836937029</v>
+        <v>9.881314835054377</v>
       </c>
       <c r="D1221" t="n">
-        <v>9.422996857266124</v>
+        <v>9.422997809088603</v>
       </c>
       <c r="E1221" t="n">
-        <v>9.578824700287852</v>
+        <v>9.578825667850595</v>
       </c>
       <c r="F1221" t="n">
         <v>2433000</v>
@@ -24872,16 +24872,16 @@
         <v>45568</v>
       </c>
       <c r="B1223" t="n">
-        <v>9.203004837036133</v>
+        <v>9.203005790710449</v>
       </c>
       <c r="C1223" t="n">
-        <v>9.45049642351443</v>
+        <v>9.450497402835408</v>
       </c>
       <c r="D1223" t="n">
-        <v>9.083842318454389</v>
+        <v>9.083843259780322</v>
       </c>
       <c r="E1223" t="n">
-        <v>9.395498001795834</v>
+        <v>9.395498975417524</v>
       </c>
       <c r="F1223" t="n">
         <v>2332500</v>
@@ -24992,16 +24992,16 @@
         <v>45576</v>
       </c>
       <c r="B1229" t="n">
-        <v>10.10130786895752</v>
+        <v>10.1013069152832</v>
       </c>
       <c r="C1229" t="n">
-        <v>10.36713171423691</v>
+        <v>10.3671307354659</v>
       </c>
       <c r="D1229" t="n">
-        <v>9.432164543424346</v>
+        <v>9.432163652924501</v>
       </c>
       <c r="E1229" t="n">
-        <v>9.432164543424346</v>
+        <v>9.432163652924501</v>
       </c>
       <c r="F1229" t="n">
         <v>6482800</v>
@@ -25132,16 +25132,16 @@
         <v>45587</v>
       </c>
       <c r="B1236" t="n">
-        <v>10.65128707885742</v>
+        <v>10.65128803253174</v>
       </c>
       <c r="C1236" t="n">
-        <v>11.00877465704114</v>
+        <v>11.00877564272349</v>
       </c>
       <c r="D1236" t="n">
-        <v>10.62378830335723</v>
+        <v>10.62378925456942</v>
       </c>
       <c r="E1236" t="n">
-        <v>10.86211335547971</v>
+        <v>10.86211432803058</v>
       </c>
       <c r="F1236" t="n">
         <v>2418100</v>
@@ -25152,16 +25152,16 @@
         <v>45588</v>
       </c>
       <c r="B1237" t="n">
-        <v>10.43129539489746</v>
+        <v>10.43129444122314</v>
       </c>
       <c r="C1237" t="n">
-        <v>10.61462202656598</v>
+        <v>10.61462105613115</v>
       </c>
       <c r="D1237" t="n">
-        <v>10.33046596602236</v>
+        <v>10.33046502156631</v>
       </c>
       <c r="E1237" t="n">
-        <v>10.54129137389857</v>
+        <v>10.54129041016794</v>
       </c>
       <c r="F1237" t="n">
         <v>2300300</v>
@@ -25172,16 +25172,16 @@
         <v>45589</v>
       </c>
       <c r="B1238" t="n">
-        <v>10.97210884094238</v>
+        <v>10.9721097946167</v>
       </c>
       <c r="C1238" t="n">
-        <v>10.99960761521274</v>
+        <v>10.99960857127719</v>
       </c>
       <c r="D1238" t="n">
-        <v>10.27546681551138</v>
+        <v>10.27546770863493</v>
       </c>
       <c r="E1238" t="n">
-        <v>10.40379588572349</v>
+        <v>10.40379679000115</v>
       </c>
       <c r="F1238" t="n">
         <v>2823700</v>
@@ -25232,16 +25232,16 @@
         <v>45594</v>
       </c>
       <c r="B1241" t="n">
-        <v>11.4212589263916</v>
+        <v>11.42125988006592</v>
       </c>
       <c r="C1241" t="n">
-        <v>11.62291863794205</v>
+        <v>11.62291960845494</v>
       </c>
       <c r="D1241" t="n">
-        <v>11.25626453747121</v>
+        <v>11.25626547736851</v>
       </c>
       <c r="E1241" t="n">
-        <v>11.47625734742181</v>
+        <v>11.47625830568849</v>
       </c>
       <c r="F1241" t="n">
         <v>2046100</v>
@@ -25332,16 +25332,16 @@
         <v>45601</v>
       </c>
       <c r="B1246" t="n">
-        <v>12.3745584487915</v>
+        <v>12.37455940246582</v>
       </c>
       <c r="C1246" t="n">
-        <v>12.66788103599134</v>
+        <v>12.66788201227125</v>
       </c>
       <c r="D1246" t="n">
-        <v>12.12706686021395</v>
+        <v>12.12706779481475</v>
       </c>
       <c r="E1246" t="n">
-        <v>12.28289470320642</v>
+        <v>12.28289564981646</v>
       </c>
       <c r="F1246" t="n">
         <v>2964700</v>
@@ -25372,16 +25372,16 @@
         <v>45603</v>
       </c>
       <c r="B1248" t="n">
-        <v>11.54958820343018</v>
+        <v>11.54958915710449</v>
       </c>
       <c r="C1248" t="n">
-        <v>12.92453913840185</v>
+        <v>12.92454020560882</v>
       </c>
       <c r="D1248" t="n">
-        <v>11.46709100746463</v>
+        <v>11.46709195432698</v>
       </c>
       <c r="E1248" t="n">
-        <v>12.73204597253901</v>
+        <v>12.7320470238514</v>
       </c>
       <c r="F1248" t="n">
         <v>7627000</v>
@@ -25392,16 +25392,16 @@
         <v>45604</v>
       </c>
       <c r="B1249" t="n">
-        <v>11.69624996185303</v>
+        <v>11.69625091552734</v>
       </c>
       <c r="C1249" t="n">
-        <v>11.8062459361255</v>
+        <v>11.80624689876853</v>
       </c>
       <c r="D1249" t="n">
-        <v>11.32043016454619</v>
+        <v>11.32043108757737</v>
       </c>
       <c r="E1249" t="n">
-        <v>11.4579249138442</v>
+        <v>11.45792584808626</v>
       </c>
       <c r="F1249" t="n">
         <v>3180500</v>
@@ -25552,16 +25552,16 @@
         <v>45618</v>
       </c>
       <c r="B1257" t="n">
-        <v>11.41209316253662</v>
+        <v>11.41209411621094</v>
       </c>
       <c r="C1257" t="n">
-        <v>11.55875446314964</v>
+        <v>11.55875542908</v>
       </c>
       <c r="D1257" t="n">
-        <v>10.95377616103579</v>
+        <v>10.95377707640993</v>
       </c>
       <c r="E1257" t="n">
-        <v>11.32043028673864</v>
+        <v>11.32043123275296</v>
       </c>
       <c r="F1257" t="n">
         <v>5679300</v>
@@ -25832,16 +25832,16 @@
         <v>45638</v>
       </c>
       <c r="B1271" t="n">
-        <v>9.395498275756836</v>
+        <v>9.395499229431152</v>
       </c>
       <c r="C1271" t="n">
-        <v>9.954644687710331</v>
+        <v>9.954645698139867</v>
       </c>
       <c r="D1271" t="n">
-        <v>9.230503879960274</v>
+        <v>9.230504816887111</v>
       </c>
       <c r="E1271" t="n">
-        <v>9.94547901229852</v>
+        <v>9.94548002179771</v>
       </c>
       <c r="F1271" t="n">
         <v>3814300</v>
@@ -25852,16 +25852,16 @@
         <v>45639</v>
       </c>
       <c r="B1272" t="n">
-        <v>9.083843231201172</v>
+        <v>9.083842277526855</v>
       </c>
       <c r="C1272" t="n">
-        <v>9.624657456732441</v>
+        <v>9.624656446280325</v>
       </c>
       <c r="D1272" t="n">
-        <v>9.0196791278908</v>
+        <v>9.019678180952802</v>
       </c>
       <c r="E1272" t="n">
-        <v>9.404665496093724</v>
+        <v>9.404664508737634</v>
       </c>
       <c r="F1272" t="n">
         <v>4484000</v>
@@ -25952,16 +25952,16 @@
         <v>45646</v>
       </c>
       <c r="B1277" t="n">
-        <v>8.937182426452637</v>
+        <v>8.93718147277832</v>
       </c>
       <c r="C1277" t="n">
-        <v>9.138842172124919</v>
+        <v>9.138841196931772</v>
       </c>
       <c r="D1277" t="n">
-        <v>8.588861365444293</v>
+        <v>8.588860448938831</v>
       </c>
       <c r="E1277" t="n">
-        <v>8.799687661867678</v>
+        <v>8.799686722865236</v>
       </c>
       <c r="F1277" t="n">
         <v>5127000</v>
@@ -25972,16 +25972,16 @@
         <v>45649</v>
       </c>
       <c r="B1278" t="n">
-        <v>8.405533790588379</v>
+        <v>8.405532836914062</v>
       </c>
       <c r="C1278" t="n">
-        <v>8.918848337428875</v>
+        <v>8.918847325514962</v>
       </c>
       <c r="D1278" t="n">
-        <v>8.405533790588379</v>
+        <v>8.405532836914062</v>
       </c>
       <c r="E1278" t="n">
-        <v>8.845517687880234</v>
+        <v>8.845516684286263</v>
       </c>
       <c r="F1278" t="n">
         <v>2696000</v>
@@ -26012,16 +26012,16 @@
         <v>45653</v>
       </c>
       <c r="B1280" t="n">
-        <v>7.763890266418457</v>
+        <v>7.763890743255615</v>
       </c>
       <c r="C1280" t="n">
-        <v>8.185541943647294</v>
+        <v>8.185542446381159</v>
       </c>
       <c r="D1280" t="n">
-        <v>7.571397090418981</v>
+        <v>7.571397555433728</v>
       </c>
       <c r="E1280" t="n">
-        <v>8.15804229409715</v>
+        <v>8.158042795142061</v>
       </c>
       <c r="F1280" t="n">
         <v>4956800</v>
@@ -34029,122 +34029,162 @@
     </row>
     <row r="1681">
       <c r="A1681" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B1681" t="n">
-        <v>8.670000076293945</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="C1681" t="n">
-        <v>9.100000381469727</v>
+        <v>9.229999542236328</v>
       </c>
       <c r="D1681" t="n">
-        <v>8.579999923706055</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="E1681" t="n">
-        <v>8.899999618530273</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="F1681" t="n">
-        <v>6481600</v>
+        <v>7898200</v>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B1682" t="n">
-        <v>8.380000114440918</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="C1682" t="n">
-        <v>8.710000038146973</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="D1682" t="n">
-        <v>8.359999656677246</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="E1682" t="n">
-        <v>8.699999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="F1682" t="n">
-        <v>7526600</v>
+        <v>6481600</v>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B1683" t="n">
-        <v>8.159999847412109</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="C1683" t="n">
-        <v>8.529999732971191</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="D1683" t="n">
-        <v>8.100000381469727</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="E1683" t="n">
-        <v>8.390000343322754</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="F1683" t="n">
-        <v>7704200</v>
+        <v>7526600</v>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B1684" t="n">
-        <v>8</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="C1684" t="n">
-        <v>8.149999618530273</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="D1684" t="n">
-        <v>7.880000114440918</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E1684" t="n">
-        <v>8.109999656677246</v>
+        <v>8.390000343322754</v>
       </c>
       <c r="F1684" t="n">
-        <v>8377800</v>
+        <v>7704200</v>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B1685" t="n">
-        <v>7.840000152587891</v>
+        <v>8</v>
       </c>
       <c r="C1685" t="n">
-        <v>8.079999923706055</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="D1685" t="n">
-        <v>7.809999942779541</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="E1685" t="n">
-        <v>7.96999979019165</v>
+        <v>8.109999656677246</v>
       </c>
       <c r="F1685" t="n">
-        <v>6506700</v>
+        <v>8377800</v>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1686" t="n">
+        <v>7.840000152587891</v>
+      </c>
+      <c r="C1686" t="n">
+        <v>8.079999923706055</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>7.809999942779541</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>7.96999979019165</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>6506700</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="B1686" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="C1686" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="D1686" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="E1686" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="F1686" t="n">
+      <c r="B1687" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="C1687" t="n">
+        <v>7.840000152587891</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>7.829999923706055</v>
+      </c>
+      <c r="F1687" t="n">
         <v>10354900</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1688" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="C1688" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>17490500</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1690"/>
+  <dimension ref="A1:F1692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43774</v>
       </c>
       <c r="B2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04940511406312</v>
+        <v>16.04940323214578</v>
       </c>
       <c r="E2" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="F2" t="n">
         <v>862100</v>
@@ -512,16 +512,16 @@
         <v>43777</v>
       </c>
       <c r="B5" t="n">
-        <v>15.8144474029541</v>
+        <v>15.81444931030273</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12169966181682</v>
+        <v>16.12170160622253</v>
       </c>
       <c r="D5" t="n">
-        <v>15.57948969184508</v>
+        <v>15.57949157085594</v>
       </c>
       <c r="E5" t="n">
-        <v>15.94999946453754</v>
+        <v>15.95000138823483</v>
       </c>
       <c r="F5" t="n">
         <v>463500</v>
@@ -532,16 +532,16 @@
         <v>43780</v>
       </c>
       <c r="B6" t="n">
-        <v>15.80540943145752</v>
+        <v>15.80541133880615</v>
       </c>
       <c r="C6" t="n">
-        <v>15.85962990814695</v>
+        <v>15.85963182203875</v>
       </c>
       <c r="D6" t="n">
-        <v>15.52526829098458</v>
+        <v>15.52527016452663</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65178331113922</v>
+        <v>15.65178519994872</v>
       </c>
       <c r="F6" t="n">
         <v>2507900</v>
@@ -612,16 +612,16 @@
         <v>43787</v>
       </c>
       <c r="B10" t="n">
-        <v>14.11552429199219</v>
+        <v>14.11552333831787</v>
       </c>
       <c r="C10" t="n">
-        <v>14.35048201117233</v>
+        <v>14.35048104162378</v>
       </c>
       <c r="D10" t="n">
-        <v>13.5733151652138</v>
+        <v>13.57331424817226</v>
       </c>
       <c r="E10" t="n">
-        <v>13.64560971545092</v>
+        <v>13.64560879352501</v>
       </c>
       <c r="F10" t="n">
         <v>4129300</v>
@@ -632,16 +632,16 @@
         <v>43788</v>
       </c>
       <c r="B11" t="n">
-        <v>13.91671371459961</v>
+        <v>13.91671276092529</v>
       </c>
       <c r="C11" t="n">
-        <v>14.40470235493443</v>
+        <v>14.40470136781958</v>
       </c>
       <c r="D11" t="n">
-        <v>13.79019868380626</v>
+        <v>13.79019773880167</v>
       </c>
       <c r="E11" t="n">
-        <v>14.27818732414107</v>
+        <v>14.27818634569596</v>
       </c>
       <c r="F11" t="n">
         <v>1475000</v>
@@ -652,16 +652,16 @@
         <v>43790</v>
       </c>
       <c r="B12" t="n">
-        <v>13.97093486785889</v>
+        <v>13.9709358215332</v>
       </c>
       <c r="C12" t="n">
-        <v>14.09745075875241</v>
+        <v>14.09745172106287</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66368260555961</v>
+        <v>13.66368353826049</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9257505595527</v>
+        <v>13.92575151014267</v>
       </c>
       <c r="F12" t="n">
         <v>946900</v>
@@ -712,16 +712,16 @@
         <v>43795</v>
       </c>
       <c r="B15" t="n">
-        <v>14.78425025939941</v>
+        <v>14.7842493057251</v>
       </c>
       <c r="C15" t="n">
-        <v>14.78425025939941</v>
+        <v>14.7842493057251</v>
       </c>
       <c r="D15" t="n">
-        <v>14.16974571703249</v>
+        <v>14.16974480299746</v>
       </c>
       <c r="E15" t="n">
-        <v>14.17878188949981</v>
+        <v>14.17878097488189</v>
       </c>
       <c r="F15" t="n">
         <v>3631800</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869618523321</v>
+        <v>14.64869711259133</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291838990186</v>
+        <v>14.70291932069259</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572429656982</v>
+        <v>15.14572238922119</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18187071314129</v>
+        <v>15.18186880124062</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195695588309</v>
+        <v>14.71195510316014</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113518300758</v>
+        <v>15.00113329386751</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49815940856934</v>
+        <v>15.4981575012207</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52527051261252</v>
+        <v>15.52526860192735</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209753189668</v>
+        <v>14.99209568682876</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15476070887956</v>
+        <v>15.15475884379279</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -812,16 +812,16 @@
         <v>43802</v>
       </c>
       <c r="B20" t="n">
-        <v>15.8144474029541</v>
+        <v>15.81444931030273</v>
       </c>
       <c r="C20" t="n">
-        <v>15.92289008640364</v>
+        <v>15.92289200683133</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29934853475424</v>
+        <v>15.29935037997784</v>
       </c>
       <c r="E20" t="n">
-        <v>15.48912107624346</v>
+        <v>15.48912294435515</v>
       </c>
       <c r="F20" t="n">
         <v>976200</v>
@@ -852,16 +852,16 @@
         <v>43804</v>
       </c>
       <c r="B22" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C22" t="n">
-        <v>16.4379889546035</v>
+        <v>16.43798702712168</v>
       </c>
       <c r="D22" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="E22" t="n">
-        <v>16.40184081890766</v>
+        <v>16.40183889566449</v>
       </c>
       <c r="F22" t="n">
         <v>1168600</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399261474609</v>
+        <v>16.19399452209473</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317077728191</v>
+        <v>16.48317271869031</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977214018008</v>
+        <v>16.13977404114256</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702436878384</v>
+        <v>16.44702630593487</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -892,16 +892,16 @@
         <v>43808</v>
       </c>
       <c r="B24" t="n">
-        <v>16.26628875732422</v>
+        <v>16.26628684997559</v>
       </c>
       <c r="C24" t="n">
-        <v>16.37473144077376</v>
+        <v>16.37472952070938</v>
       </c>
       <c r="D24" t="n">
-        <v>16.21206827741844</v>
+        <v>16.21206637642758</v>
       </c>
       <c r="E24" t="n">
-        <v>16.33858330507792</v>
+        <v>16.33858138925219</v>
       </c>
       <c r="F24" t="n">
         <v>474400</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436470031738</v>
+        <v>16.28436279296875</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51932243848179</v>
+        <v>16.51932050361312</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444922398856</v>
+        <v>15.81444737168</v>
       </c>
       <c r="E33" t="n">
-        <v>16.4018427075805</v>
+        <v>16.40184078647195</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1112,16 +1112,16 @@
         <v>43825</v>
       </c>
       <c r="B35" t="n">
-        <v>16.51932334899902</v>
+        <v>16.51931953430176</v>
       </c>
       <c r="C35" t="n">
-        <v>16.5916179090622</v>
+        <v>16.59161407767043</v>
       </c>
       <c r="D35" t="n">
-        <v>16.37473422887268</v>
+        <v>16.37473044756441</v>
       </c>
       <c r="E35" t="n">
-        <v>16.5916179090622</v>
+        <v>16.59161407767043</v>
       </c>
       <c r="F35" t="n">
         <v>1111500</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620643793902</v>
+        <v>16.73620446892584</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813236765218</v>
+        <v>16.71813040076541</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -1292,16 +1292,16 @@
         <v>43840</v>
       </c>
       <c r="B44" t="n">
-        <v>14.83113956451416</v>
+        <v>14.83113861083984</v>
       </c>
       <c r="C44" t="n">
-        <v>15.08779598573296</v>
+        <v>15.08779501555508</v>
       </c>
       <c r="D44" t="n">
-        <v>14.45531973486599</v>
+        <v>14.4553188053577</v>
       </c>
       <c r="E44" t="n">
-        <v>14.57448139495461</v>
+        <v>14.57448045778397</v>
       </c>
       <c r="F44" t="n">
         <v>2521000</v>
@@ -1352,16 +1352,16 @@
         <v>43845</v>
       </c>
       <c r="B47" t="n">
-        <v>15.76610660552979</v>
+        <v>15.76610469818115</v>
       </c>
       <c r="C47" t="n">
-        <v>15.76610660552979</v>
+        <v>15.76610469818115</v>
       </c>
       <c r="D47" t="n">
-        <v>15.35362057725238</v>
+        <v>15.3536187198054</v>
       </c>
       <c r="E47" t="n">
-        <v>15.72027385330967</v>
+        <v>15.72027195150578</v>
       </c>
       <c r="F47" t="n">
         <v>1838000</v>
@@ -1372,16 +1372,16 @@
         <v>43846</v>
       </c>
       <c r="B48" t="n">
-        <v>16.10525894165039</v>
+        <v>16.10525703430176</v>
       </c>
       <c r="C48" t="n">
-        <v>16.34358398910408</v>
+        <v>16.34358205353058</v>
       </c>
       <c r="D48" t="n">
-        <v>15.56444474710943</v>
+        <v>15.56444290380952</v>
       </c>
       <c r="E48" t="n">
-        <v>15.76610534406134</v>
+        <v>15.76610347687872</v>
       </c>
       <c r="F48" t="n">
         <v>3608000</v>
@@ -1412,16 +1412,16 @@
         <v>43850</v>
       </c>
       <c r="B50" t="n">
-        <v>16.16025543212891</v>
+        <v>16.16025733947754</v>
       </c>
       <c r="C50" t="n">
-        <v>16.44441320950657</v>
+        <v>16.44441515039353</v>
       </c>
       <c r="D50" t="n">
-        <v>16.14192408225009</v>
+        <v>16.14192598743512</v>
       </c>
       <c r="E50" t="n">
-        <v>16.24275262577526</v>
+        <v>16.2427545428608</v>
       </c>
       <c r="F50" t="n">
         <v>998100</v>
@@ -1492,16 +1492,16 @@
         <v>43854</v>
       </c>
       <c r="B54" t="n">
-        <v>15.73860454559326</v>
+        <v>15.73860645294189</v>
       </c>
       <c r="C54" t="n">
-        <v>15.80276864054115</v>
+        <v>15.80277055566578</v>
       </c>
       <c r="D54" t="n">
-        <v>15.39944922443097</v>
+        <v>15.39945109067764</v>
       </c>
       <c r="E54" t="n">
-        <v>15.57361015953271</v>
+        <v>15.57361204688581</v>
       </c>
       <c r="F54" t="n">
         <v>887500</v>
@@ -1552,16 +1552,16 @@
         <v>43859</v>
       </c>
       <c r="B57" t="n">
-        <v>15.21612548828125</v>
+        <v>15.21612453460693</v>
       </c>
       <c r="C57" t="n">
-        <v>15.64694285979114</v>
+        <v>15.64694187911524</v>
       </c>
       <c r="D57" t="n">
-        <v>15.16112793514696</v>
+        <v>15.16112698491963</v>
       </c>
       <c r="E57" t="n">
-        <v>15.40861779842162</v>
+        <v>15.4086168326828</v>
       </c>
       <c r="F57" t="n">
         <v>686700</v>
@@ -1572,16 +1572,16 @@
         <v>43860</v>
       </c>
       <c r="B58" t="n">
-        <v>15.06946468353271</v>
+        <v>15.0694637298584</v>
       </c>
       <c r="C58" t="n">
-        <v>15.12446223850094</v>
+        <v>15.1244612813461</v>
       </c>
       <c r="D58" t="n">
-        <v>14.68447830207361</v>
+        <v>14.68447737276324</v>
       </c>
       <c r="E58" t="n">
-        <v>15.12446223850094</v>
+        <v>15.1244612813461</v>
       </c>
       <c r="F58" t="n">
         <v>1070000</v>
@@ -1652,16 +1652,16 @@
         <v>43866</v>
       </c>
       <c r="B62" t="n">
-        <v>14.86780261993408</v>
+        <v>14.8678035736084</v>
       </c>
       <c r="C62" t="n">
-        <v>15.21612451360086</v>
+        <v>15.21612548961779</v>
       </c>
       <c r="D62" t="n">
-        <v>14.69364342144127</v>
+        <v>14.69364436394439</v>
       </c>
       <c r="E62" t="n">
-        <v>14.9319684675447</v>
+        <v>14.93196942533485</v>
       </c>
       <c r="F62" t="n">
         <v>931900</v>
@@ -1772,16 +1772,16 @@
         <v>43874</v>
       </c>
       <c r="B68" t="n">
-        <v>14.56531429290771</v>
+        <v>14.56531524658203</v>
       </c>
       <c r="C68" t="n">
-        <v>14.62947839193184</v>
+        <v>14.62947934980735</v>
       </c>
       <c r="D68" t="n">
-        <v>14.18032795042238</v>
+        <v>14.18032887888944</v>
       </c>
       <c r="E68" t="n">
-        <v>14.51948241896036</v>
+        <v>14.5194833696338</v>
       </c>
       <c r="F68" t="n">
         <v>729000</v>
@@ -1792,16 +1792,16 @@
         <v>43875</v>
       </c>
       <c r="B69" t="n">
-        <v>14.56531429290771</v>
+        <v>14.56531524658203</v>
       </c>
       <c r="C69" t="n">
-        <v>14.70280991474978</v>
+        <v>14.70281087742672</v>
       </c>
       <c r="D69" t="n">
-        <v>14.34532147279446</v>
+        <v>14.34532241206459</v>
       </c>
       <c r="E69" t="n">
-        <v>14.65697716663214</v>
+        <v>14.65697812630815</v>
       </c>
       <c r="F69" t="n">
         <v>540700</v>
@@ -1852,16 +1852,16 @@
         <v>43880</v>
       </c>
       <c r="B72" t="n">
-        <v>15.67444324493408</v>
+        <v>15.67444133758545</v>
       </c>
       <c r="C72" t="n">
-        <v>16.20609094571707</v>
+        <v>16.20608897367475</v>
       </c>
       <c r="D72" t="n">
-        <v>15.39028716736234</v>
+        <v>15.39028529459131</v>
       </c>
       <c r="E72" t="n">
-        <v>15.39028716736234</v>
+        <v>15.39028529459131</v>
       </c>
       <c r="F72" t="n">
         <v>5335200</v>
@@ -1872,16 +1872,16 @@
         <v>43881</v>
       </c>
       <c r="B73" t="n">
-        <v>15.85776805877686</v>
+        <v>15.85776710510254</v>
       </c>
       <c r="C73" t="n">
-        <v>15.94026526154759</v>
+        <v>15.94026430291195</v>
       </c>
       <c r="D73" t="n">
-        <v>15.53694754615808</v>
+        <v>15.53694661177767</v>
       </c>
       <c r="E73" t="n">
-        <v>15.67444230132908</v>
+        <v>15.67444135867984</v>
       </c>
       <c r="F73" t="n">
         <v>1537600</v>
@@ -1892,16 +1892,16 @@
         <v>43882</v>
       </c>
       <c r="B74" t="n">
-        <v>16.04109382629395</v>
+        <v>16.04109573364258</v>
       </c>
       <c r="C74" t="n">
-        <v>16.04109382629395</v>
+        <v>16.04109573364258</v>
       </c>
       <c r="D74" t="n">
-        <v>15.43611557042667</v>
+        <v>15.43611740584103</v>
       </c>
       <c r="E74" t="n">
-        <v>15.63777440626894</v>
+        <v>15.63777626566132</v>
       </c>
       <c r="F74" t="n">
         <v>1940300</v>
@@ -1932,16 +1932,16 @@
         <v>43888</v>
       </c>
       <c r="B76" t="n">
-        <v>14.47365093231201</v>
+        <v>14.47365188598633</v>
       </c>
       <c r="C76" t="n">
-        <v>14.88613606053529</v>
+        <v>14.88613704138841</v>
       </c>
       <c r="D76" t="n">
-        <v>14.09783112939368</v>
+        <v>14.09783205830509</v>
       </c>
       <c r="E76" t="n">
-        <v>14.56531468265955</v>
+        <v>14.56531564237362</v>
       </c>
       <c r="F76" t="n">
         <v>1056800</v>
@@ -2032,16 +2032,16 @@
         <v>43895</v>
       </c>
       <c r="B81" t="n">
-        <v>13.29119300842285</v>
+        <v>13.29119396209717</v>
       </c>
       <c r="C81" t="n">
-        <v>14.68447710890754</v>
+        <v>14.68447816255327</v>
       </c>
       <c r="D81" t="n">
-        <v>13.22702890811669</v>
+        <v>13.22702985718708</v>
       </c>
       <c r="E81" t="n">
-        <v>14.62031213443108</v>
+        <v>14.62031318347281</v>
       </c>
       <c r="F81" t="n">
         <v>2239700</v>
@@ -2152,16 +2152,16 @@
         <v>43903</v>
       </c>
       <c r="B87" t="n">
-        <v>9.991311073303223</v>
+        <v>9.991310119628906</v>
       </c>
       <c r="C87" t="n">
-        <v>10.72461850853887</v>
+        <v>10.72461748487009</v>
       </c>
       <c r="D87" t="n">
-        <v>9.074676997801262</v>
+        <v>9.074676131620004</v>
       </c>
       <c r="E87" t="n">
-        <v>10.38546400550359</v>
+        <v>10.38546301420723</v>
       </c>
       <c r="F87" t="n">
         <v>3278100</v>
@@ -2172,16 +2172,16 @@
         <v>43906</v>
       </c>
       <c r="B88" t="n">
-        <v>7.562230110168457</v>
+        <v>7.562230587005615</v>
       </c>
       <c r="C88" t="n">
-        <v>8.918847940633317</v>
+        <v>8.918848503012144</v>
       </c>
       <c r="D88" t="n">
-        <v>7.562230110168457</v>
+        <v>7.562230587005615</v>
       </c>
       <c r="E88" t="n">
-        <v>8.918847940633317</v>
+        <v>8.918848503012144</v>
       </c>
       <c r="F88" t="n">
         <v>1319600</v>
@@ -2192,16 +2192,16 @@
         <v>43907</v>
       </c>
       <c r="B89" t="n">
-        <v>6.920587062835693</v>
+        <v>6.920586585998535</v>
       </c>
       <c r="C89" t="n">
-        <v>7.791389211657462</v>
+        <v>7.79138867482094</v>
       </c>
       <c r="D89" t="n">
-        <v>6.874755186756584</v>
+        <v>6.8747547130773</v>
       </c>
       <c r="E89" t="n">
-        <v>7.626394807440799</v>
+        <v>7.626394281972599</v>
       </c>
       <c r="F89" t="n">
         <v>4217900</v>
@@ -2212,16 +2212,16 @@
         <v>43908</v>
       </c>
       <c r="B90" t="n">
-        <v>4.858160018920898</v>
+        <v>4.858160495758057</v>
       </c>
       <c r="C90" t="n">
-        <v>6.69142788461405</v>
+        <v>6.691428541389752</v>
       </c>
       <c r="D90" t="n">
-        <v>4.574003115103555</v>
+        <v>4.574003564050201</v>
       </c>
       <c r="E90" t="n">
-        <v>6.69142788461405</v>
+        <v>6.691428541389752</v>
       </c>
       <c r="F90" t="n">
         <v>3396400</v>
@@ -2252,16 +2252,16 @@
         <v>43910</v>
       </c>
       <c r="B92" t="n">
-        <v>5.820625782012939</v>
+        <v>5.820626258850098</v>
       </c>
       <c r="C92" t="n">
-        <v>6.508101278402306</v>
+        <v>6.508101811558814</v>
       </c>
       <c r="D92" t="n">
-        <v>5.756461682084427</v>
+        <v>5.756462153665136</v>
       </c>
       <c r="E92" t="n">
-        <v>6.27894277960585</v>
+        <v>6.278943293989242</v>
       </c>
       <c r="F92" t="n">
         <v>2218000</v>
@@ -2332,16 +2332,16 @@
         <v>43916</v>
       </c>
       <c r="B96" t="n">
-        <v>6.874754905700684</v>
+        <v>6.874755382537842</v>
       </c>
       <c r="C96" t="n">
-        <v>7.653894144681544</v>
+        <v>7.653894675560271</v>
       </c>
       <c r="D96" t="n">
-        <v>6.297275388721391</v>
+        <v>6.29727582550422</v>
       </c>
       <c r="E96" t="n">
-        <v>6.471435898782693</v>
+        <v>6.471436347645401</v>
       </c>
       <c r="F96" t="n">
         <v>4787500</v>
@@ -2472,16 +2472,16 @@
         <v>43927</v>
       </c>
       <c r="B103" t="n">
-        <v>6.23311185836792</v>
+        <v>6.233111381530762</v>
       </c>
       <c r="C103" t="n">
-        <v>6.324775178061675</v>
+        <v>6.324774694212212</v>
       </c>
       <c r="D103" t="n">
-        <v>5.637299624730736</v>
+        <v>5.637299193473606</v>
       </c>
       <c r="E103" t="n">
-        <v>6.00395334059094</v>
+        <v>6.00395288128456</v>
       </c>
       <c r="F103" t="n">
         <v>2488400</v>
@@ -2532,16 +2532,16 @@
         <v>43930</v>
       </c>
       <c r="B106" t="n">
-        <v>7.883053302764893</v>
+        <v>7.883052349090576</v>
       </c>
       <c r="C106" t="n">
-        <v>8.653025182485189</v>
+        <v>8.653024135661383</v>
       </c>
       <c r="D106" t="n">
-        <v>7.718058891453932</v>
+        <v>7.718057957740275</v>
       </c>
       <c r="E106" t="n">
-        <v>8.121377495116946</v>
+        <v>8.121376512610697</v>
       </c>
       <c r="F106" t="n">
         <v>2853400</v>
@@ -2672,16 +2672,16 @@
         <v>43943</v>
       </c>
       <c r="B113" t="n">
-        <v>8.983013153076172</v>
+        <v>8.983012199401855</v>
       </c>
       <c r="C113" t="n">
-        <v>9.285502295675192</v>
+        <v>9.28550130988736</v>
       </c>
       <c r="D113" t="n">
-        <v>8.570528038092988</v>
+        <v>8.57052712820982</v>
       </c>
       <c r="E113" t="n">
-        <v>8.57969371349729</v>
+        <v>8.579692802641055</v>
       </c>
       <c r="F113" t="n">
         <v>2037400</v>
@@ -2712,16 +2712,16 @@
         <v>43945</v>
       </c>
       <c r="B115" t="n">
-        <v>7.278074264526367</v>
+        <v>7.278073787689209</v>
       </c>
       <c r="C115" t="n">
-        <v>8.268039385965343</v>
+        <v>8.268038844268698</v>
       </c>
       <c r="D115" t="n">
-        <v>7.14057907234719</v>
+        <v>7.140578604518296</v>
       </c>
       <c r="E115" t="n">
-        <v>8.240539735610273</v>
+        <v>8.240539195715323</v>
       </c>
       <c r="F115" t="n">
         <v>2904600</v>
@@ -2792,16 +2792,16 @@
         <v>43951</v>
       </c>
       <c r="B119" t="n">
-        <v>8.662190437316895</v>
+        <v>8.662191390991211</v>
       </c>
       <c r="C119" t="n">
-        <v>9.157172723044425</v>
+        <v>9.157173731214414</v>
       </c>
       <c r="D119" t="n">
-        <v>8.579693244000602</v>
+        <v>8.579694188592288</v>
       </c>
       <c r="E119" t="n">
-        <v>8.909682017265776</v>
+        <v>8.909682998187977</v>
       </c>
       <c r="F119" t="n">
         <v>4677300</v>
@@ -2812,16 +2812,16 @@
         <v>43955</v>
       </c>
       <c r="B120" t="n">
-        <v>8.24053955078125</v>
+        <v>8.240540504455566</v>
       </c>
       <c r="C120" t="n">
-        <v>8.543028704539738</v>
+        <v>8.543029693221003</v>
       </c>
       <c r="D120" t="n">
-        <v>8.066379473290425</v>
+        <v>8.066380406809268</v>
       </c>
       <c r="E120" t="n">
-        <v>8.341369851480955</v>
+        <v>8.341370816824323</v>
       </c>
       <c r="F120" t="n">
         <v>1637500</v>
@@ -2832,16 +2832,16 @@
         <v>43956</v>
       </c>
       <c r="B121" t="n">
-        <v>7.892218112945557</v>
+        <v>7.892219066619873</v>
       </c>
       <c r="C121" t="n">
-        <v>8.790519851961706</v>
+        <v>8.790520914184377</v>
       </c>
       <c r="D121" t="n">
-        <v>7.892218112945557</v>
+        <v>7.892219066619873</v>
       </c>
       <c r="E121" t="n">
-        <v>8.570527910469277</v>
+        <v>8.570528946108718</v>
       </c>
       <c r="F121" t="n">
         <v>2603100</v>
@@ -2852,16 +2852,16 @@
         <v>43957</v>
       </c>
       <c r="B122" t="n">
-        <v>7.828053951263428</v>
+        <v>7.828054904937744</v>
       </c>
       <c r="C122" t="n">
-        <v>8.1488761856131</v>
+        <v>8.148877178372471</v>
       </c>
       <c r="D122" t="n">
-        <v>7.553063589559461</v>
+        <v>7.553064509732316</v>
       </c>
       <c r="E122" t="n">
-        <v>7.928883371747769</v>
+        <v>7.928884337705908</v>
       </c>
       <c r="F122" t="n">
         <v>2058000</v>
@@ -2972,16 +2972,16 @@
         <v>43965</v>
       </c>
       <c r="B128" t="n">
-        <v>6.08644962310791</v>
+        <v>6.086450099945068</v>
       </c>
       <c r="C128" t="n">
-        <v>6.187279485251405</v>
+        <v>6.187279969987983</v>
       </c>
       <c r="D128" t="n">
-        <v>5.701463274091976</v>
+        <v>5.701463720767742</v>
       </c>
       <c r="E128" t="n">
-        <v>5.893956448599943</v>
+        <v>5.893956910356406</v>
       </c>
       <c r="F128" t="n">
         <v>4161800</v>
@@ -3072,16 +3072,16 @@
         <v>43972</v>
       </c>
       <c r="B133" t="n">
-        <v>7.727225303649902</v>
+        <v>7.727224349975586</v>
       </c>
       <c r="C133" t="n">
-        <v>7.873886611448894</v>
+        <v>7.873885639674015</v>
       </c>
       <c r="D133" t="n">
-        <v>7.461401464721644</v>
+        <v>7.461400543854623</v>
       </c>
       <c r="E133" t="n">
-        <v>7.553064345010839</v>
+        <v>7.55306341283102</v>
       </c>
       <c r="F133" t="n">
         <v>2073000</v>
@@ -3192,16 +3192,16 @@
         <v>43980</v>
       </c>
       <c r="B139" t="n">
-        <v>8.680524826049805</v>
+        <v>8.680523872375488</v>
       </c>
       <c r="C139" t="n">
-        <v>8.753855481195645</v>
+        <v>8.753854519464953</v>
       </c>
       <c r="D139" t="n">
-        <v>8.038881156438526</v>
+        <v>8.03888027325754</v>
       </c>
       <c r="E139" t="n">
-        <v>8.405534432167725</v>
+        <v>8.405533508704863</v>
       </c>
       <c r="F139" t="n">
         <v>6035800</v>
@@ -3212,16 +3212,16 @@
         <v>43983</v>
       </c>
       <c r="B140" t="n">
-        <v>8.955514907836914</v>
+        <v>8.955513954162598</v>
       </c>
       <c r="C140" t="n">
-        <v>9.065510886722372</v>
+        <v>9.065509921334565</v>
       </c>
       <c r="D140" t="n">
-        <v>8.561361994536275</v>
+        <v>8.56136108283537</v>
       </c>
       <c r="E140" t="n">
-        <v>8.662191423305361</v>
+        <v>8.662190500867112</v>
       </c>
       <c r="F140" t="n">
         <v>3007600</v>
@@ -3252,16 +3252,16 @@
         <v>43985</v>
       </c>
       <c r="B142" t="n">
-        <v>9.862982749938965</v>
+        <v>9.862981796264648</v>
       </c>
       <c r="C142" t="n">
-        <v>10.25713480348261</v>
+        <v>10.25713381169683</v>
       </c>
       <c r="D142" t="n">
-        <v>9.395499166953094</v>
+        <v>9.395498258480833</v>
       </c>
       <c r="E142" t="n">
-        <v>9.89048152712332</v>
+        <v>9.890480570790084</v>
       </c>
       <c r="F142" t="n">
         <v>6994400</v>
@@ -3292,16 +3292,16 @@
         <v>43987</v>
       </c>
       <c r="B144" t="n">
-        <v>11.09127235412598</v>
+        <v>11.09127140045166</v>
       </c>
       <c r="C144" t="n">
-        <v>11.45792562443991</v>
+        <v>11.4579246392392</v>
       </c>
       <c r="D144" t="n">
-        <v>10.74295131024256</v>
+        <v>10.74295038651836</v>
       </c>
       <c r="E144" t="n">
-        <v>10.99960859946232</v>
+        <v>10.99960765366964</v>
       </c>
       <c r="F144" t="n">
         <v>5476600</v>
@@ -3392,16 +3392,16 @@
         <v>43997</v>
       </c>
       <c r="B149" t="n">
-        <v>10.76128387451172</v>
+        <v>10.7612829208374</v>
       </c>
       <c r="C149" t="n">
-        <v>10.90794518724156</v>
+        <v>10.90794422056999</v>
       </c>
       <c r="D149" t="n">
-        <v>9.780485690003097</v>
+        <v>9.780484823247967</v>
       </c>
       <c r="E149" t="n">
-        <v>10.14713897182771</v>
+        <v>10.14713807257945</v>
       </c>
       <c r="F149" t="n">
         <v>2544600</v>
@@ -3492,16 +3492,16 @@
         <v>44004</v>
       </c>
       <c r="B154" t="n">
-        <v>10.37629699707031</v>
+        <v>10.376296043396</v>
       </c>
       <c r="C154" t="n">
-        <v>10.67878615870432</v>
+        <v>10.67878517722855</v>
       </c>
       <c r="D154" t="n">
-        <v>10.13797281232588</v>
+        <v>10.13797188055568</v>
       </c>
       <c r="E154" t="n">
-        <v>10.37629699707031</v>
+        <v>10.376296043396</v>
       </c>
       <c r="F154" t="n">
         <v>2228300</v>
@@ -3572,16 +3572,16 @@
         <v>44008</v>
       </c>
       <c r="B158" t="n">
-        <v>9.001346588134766</v>
+        <v>9.001345634460449</v>
       </c>
       <c r="C158" t="n">
-        <v>9.349667651262335</v>
+        <v>9.349666660684111</v>
       </c>
       <c r="D158" t="n">
-        <v>8.863851822713272</v>
+        <v>8.863850883606245</v>
       </c>
       <c r="E158" t="n">
-        <v>9.175507556783749</v>
+        <v>9.175506584657434</v>
       </c>
       <c r="F158" t="n">
         <v>2827200</v>
@@ -3652,16 +3652,16 @@
         <v>44014</v>
       </c>
       <c r="B162" t="n">
-        <v>9.047178268432617</v>
+        <v>9.047177314758301</v>
       </c>
       <c r="C162" t="n">
-        <v>9.633824394576017</v>
+        <v>9.633823379062603</v>
       </c>
       <c r="D162" t="n">
-        <v>9.038011717827944</v>
+        <v>9.038010765119886</v>
       </c>
       <c r="E162" t="n">
-        <v>9.578825965118355</v>
+        <v>9.578824955402395</v>
       </c>
       <c r="F162" t="n">
         <v>3744200</v>
@@ -3672,16 +3672,16 @@
         <v>44015</v>
       </c>
       <c r="B163" t="n">
-        <v>9.102175712585449</v>
+        <v>9.102176666259766</v>
       </c>
       <c r="C163" t="n">
-        <v>9.24883700970271</v>
+        <v>9.248837978743365</v>
       </c>
       <c r="D163" t="n">
-        <v>8.909682541576473</v>
+        <v>8.909683475082447</v>
       </c>
       <c r="E163" t="n">
-        <v>9.010511964802019</v>
+        <v>9.010512908872327</v>
       </c>
       <c r="F163" t="n">
         <v>1732200</v>
@@ -3692,16 +3692,16 @@
         <v>44018</v>
       </c>
       <c r="B164" t="n">
-        <v>10.22963619232178</v>
+        <v>10.22963523864746</v>
       </c>
       <c r="C164" t="n">
-        <v>10.24796929352246</v>
+        <v>10.24796833813902</v>
       </c>
       <c r="D164" t="n">
-        <v>9.322168662976866</v>
+        <v>9.322167793902672</v>
       </c>
       <c r="E164" t="n">
-        <v>9.322168662976866</v>
+        <v>9.322167793902672</v>
       </c>
       <c r="F164" t="n">
         <v>6286300</v>
@@ -3712,16 +3712,16 @@
         <v>44019</v>
       </c>
       <c r="B165" t="n">
-        <v>10.60545539855957</v>
+        <v>10.60545444488525</v>
       </c>
       <c r="C165" t="n">
-        <v>10.74295102692902</v>
+        <v>10.74295006089068</v>
       </c>
       <c r="D165" t="n">
-        <v>9.817150451088642</v>
+        <v>9.817149568301065</v>
       </c>
       <c r="E165" t="n">
-        <v>10.08297428359852</v>
+        <v>10.08297337690727</v>
       </c>
       <c r="F165" t="n">
         <v>6820000</v>
@@ -3732,16 +3732,16 @@
         <v>44020</v>
       </c>
       <c r="B166" t="n">
-        <v>10.19297027587891</v>
+        <v>10.19297122955322</v>
       </c>
       <c r="C166" t="n">
-        <v>10.94460989832417</v>
+        <v>10.94461092232337</v>
       </c>
       <c r="D166" t="n">
-        <v>10.14713839969241</v>
+        <v>10.14713934907861</v>
       </c>
       <c r="E166" t="n">
-        <v>10.7704498178199</v>
+        <v>10.77045082552434</v>
       </c>
       <c r="F166" t="n">
         <v>5151100</v>
@@ -3772,16 +3772,16 @@
         <v>44022</v>
       </c>
       <c r="B168" t="n">
-        <v>10.60545539855957</v>
+        <v>10.60545444488525</v>
       </c>
       <c r="C168" t="n">
-        <v>10.73378447687032</v>
+        <v>10.73378351165627</v>
       </c>
       <c r="D168" t="n">
-        <v>10.13797270978036</v>
+        <v>10.13797179814349</v>
       </c>
       <c r="E168" t="n">
-        <v>10.16547148578612</v>
+        <v>10.16547057167647</v>
       </c>
       <c r="F168" t="n">
         <v>4505800</v>
@@ -3872,16 +3872,16 @@
         <v>44029</v>
       </c>
       <c r="B173" t="n">
-        <v>10.18380451202393</v>
+        <v>10.18380355834961</v>
       </c>
       <c r="C173" t="n">
-        <v>10.39463080908999</v>
+        <v>10.3946298356726</v>
       </c>
       <c r="D173" t="n">
-        <v>10.04630974701983</v>
+        <v>10.04630880622137</v>
       </c>
       <c r="E173" t="n">
-        <v>10.32130015119842</v>
+        <v>10.32129918464816</v>
       </c>
       <c r="F173" t="n">
         <v>2077700</v>
@@ -3892,16 +3892,16 @@
         <v>44032</v>
       </c>
       <c r="B174" t="n">
-        <v>10.11963939666748</v>
+        <v>10.11963844299316</v>
       </c>
       <c r="C174" t="n">
-        <v>10.28463379756993</v>
+        <v>10.28463282834655</v>
       </c>
       <c r="D174" t="n">
-        <v>10.00964342078928</v>
+        <v>10.00964247748098</v>
       </c>
       <c r="E174" t="n">
-        <v>10.17463782169173</v>
+        <v>10.17463686283437</v>
       </c>
       <c r="F174" t="n">
         <v>2184300</v>
@@ -3912,16 +3912,16 @@
         <v>44033</v>
       </c>
       <c r="B175" t="n">
-        <v>9.881315231323242</v>
+        <v>9.881314277648926</v>
       </c>
       <c r="C175" t="n">
-        <v>10.28463471988278</v>
+        <v>10.28463372728293</v>
       </c>
       <c r="D175" t="n">
-        <v>9.881315231323242</v>
+        <v>9.881314277648926</v>
       </c>
       <c r="E175" t="n">
-        <v>10.19297096134551</v>
+        <v>10.19296997759239</v>
       </c>
       <c r="F175" t="n">
         <v>2876600</v>
@@ -3952,16 +3952,16 @@
         <v>44035</v>
       </c>
       <c r="B177" t="n">
-        <v>9.771318435668945</v>
+        <v>9.771317481994629</v>
       </c>
       <c r="C177" t="n">
-        <v>10.10130723971515</v>
+        <v>10.10130625383415</v>
       </c>
       <c r="D177" t="n">
-        <v>9.670489008971668</v>
+        <v>9.670488065138237</v>
       </c>
       <c r="E177" t="n">
-        <v>9.982144713161835</v>
+        <v>9.982143738911011</v>
       </c>
       <c r="F177" t="n">
         <v>2784800</v>
@@ -4092,16 +4092,16 @@
         <v>44046</v>
       </c>
       <c r="B184" t="n">
-        <v>9.258004188537598</v>
+        <v>9.258003234863281</v>
       </c>
       <c r="C184" t="n">
-        <v>9.505494925701171</v>
+        <v>9.50549394653264</v>
       </c>
       <c r="D184" t="n">
-        <v>9.056344454210368</v>
+        <v>9.056343521309181</v>
       </c>
       <c r="E184" t="n">
-        <v>9.432164272158605</v>
+        <v>9.432163300543921</v>
       </c>
       <c r="F184" t="n">
         <v>2465200</v>
@@ -4132,16 +4132,16 @@
         <v>44048</v>
       </c>
       <c r="B186" t="n">
-        <v>9.047178268432617</v>
+        <v>9.047177314758301</v>
       </c>
       <c r="C186" t="n">
-        <v>9.148007702572885</v>
+        <v>9.148006738270013</v>
       </c>
       <c r="D186" t="n">
-        <v>8.928015733083003</v>
+        <v>8.928014791969757</v>
       </c>
       <c r="E186" t="n">
-        <v>8.983014162540663</v>
+        <v>8.983013215629965</v>
       </c>
       <c r="F186" t="n">
         <v>1681800</v>
@@ -4212,16 +4212,16 @@
         <v>44054</v>
       </c>
       <c r="B190" t="n">
-        <v>10.89877796173096</v>
+        <v>10.89877891540527</v>
       </c>
       <c r="C190" t="n">
-        <v>10.98127428278814</v>
+        <v>10.98127524368111</v>
       </c>
       <c r="D190" t="n">
-        <v>10.31213192002386</v>
+        <v>10.31213282236497</v>
       </c>
       <c r="E190" t="n">
-        <v>10.37629601668064</v>
+        <v>10.37629692463629</v>
       </c>
       <c r="F190" t="n">
         <v>5002000</v>
@@ -4272,16 +4272,16 @@
         <v>44057</v>
       </c>
       <c r="B193" t="n">
-        <v>10.12880516052246</v>
+        <v>10.12880611419678</v>
       </c>
       <c r="C193" t="n">
-        <v>10.16547048296991</v>
+        <v>10.16547144009644</v>
       </c>
       <c r="D193" t="n">
-        <v>9.34966596580141</v>
+        <v>9.349666846116131</v>
       </c>
       <c r="E193" t="n">
-        <v>9.789650709341016</v>
+        <v>9.789651631082357</v>
       </c>
       <c r="F193" t="n">
         <v>2396300</v>
@@ -4312,16 +4312,16 @@
         <v>44061</v>
       </c>
       <c r="B195" t="n">
-        <v>9.532993316650391</v>
+        <v>9.532992362976074</v>
       </c>
       <c r="C195" t="n">
-        <v>9.73465304282097</v>
+        <v>9.734652068972748</v>
       </c>
       <c r="D195" t="n">
-        <v>9.248837264208962</v>
+        <v>9.248836338961429</v>
       </c>
       <c r="E195" t="n">
-        <v>9.313001364920838</v>
+        <v>9.31300043325437</v>
       </c>
       <c r="F195" t="n">
         <v>3391400</v>
@@ -4492,16 +4492,16 @@
         <v>44074</v>
       </c>
       <c r="B204" t="n">
-        <v>11.05460643768311</v>
+        <v>11.05460739135742</v>
       </c>
       <c r="C204" t="n">
-        <v>11.32043026303005</v>
+        <v>11.32043123963683</v>
       </c>
       <c r="D204" t="n">
-        <v>10.85294671267739</v>
+        <v>10.85294764895465</v>
       </c>
       <c r="E204" t="n">
-        <v>10.97210923771848</v>
+        <v>10.97211018427581</v>
       </c>
       <c r="F204" t="n">
         <v>3725900</v>
@@ -4512,16 +4512,16 @@
         <v>44075</v>
       </c>
       <c r="B205" t="n">
-        <v>11.7237491607666</v>
+        <v>11.72374820709229</v>
       </c>
       <c r="C205" t="n">
-        <v>11.7237491607666</v>
+        <v>11.72374820709229</v>
       </c>
       <c r="D205" t="n">
-        <v>10.96294298891299</v>
+        <v>10.96294209712684</v>
       </c>
       <c r="E205" t="n">
-        <v>11.14626961932886</v>
+        <v>11.14626871262991</v>
       </c>
       <c r="F205" t="n">
         <v>3676800</v>
@@ -4652,16 +4652,16 @@
         <v>44085</v>
       </c>
       <c r="B212" t="n">
-        <v>10.83461284637451</v>
+        <v>10.83461380004883</v>
       </c>
       <c r="C212" t="n">
-        <v>11.54958794602793</v>
+        <v>11.54958896263513</v>
       </c>
       <c r="D212" t="n">
-        <v>10.66961933229085</v>
+        <v>10.66962027144226</v>
       </c>
       <c r="E212" t="n">
-        <v>11.43959110441184</v>
+        <v>11.43959211133699</v>
       </c>
       <c r="F212" t="n">
         <v>2696500</v>
@@ -4692,16 +4692,16 @@
         <v>44089</v>
       </c>
       <c r="B214" t="n">
-        <v>11.82457733154297</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="C214" t="n">
-        <v>12.09956768500983</v>
+        <v>12.09956866086264</v>
       </c>
       <c r="D214" t="n">
-        <v>11.62291849661481</v>
+        <v>11.62291943402496</v>
       </c>
       <c r="E214" t="n">
-        <v>12.01707049155275</v>
+        <v>12.017071460752</v>
       </c>
       <c r="F214" t="n">
         <v>2177400</v>
@@ -4732,16 +4732,16 @@
         <v>44091</v>
       </c>
       <c r="B216" t="n">
-        <v>12.11790180206299</v>
+        <v>12.11790084838867</v>
       </c>
       <c r="C216" t="n">
-        <v>12.13623402761137</v>
+        <v>12.13623307249431</v>
       </c>
       <c r="D216" t="n">
-        <v>11.5770875987461</v>
+        <v>11.57708668763366</v>
       </c>
       <c r="E216" t="n">
-        <v>11.916242076009</v>
+        <v>11.91624113820522</v>
       </c>
       <c r="F216" t="n">
         <v>2040800</v>
@@ -4832,16 +4832,16 @@
         <v>44098</v>
       </c>
       <c r="B221" t="n">
-        <v>10.93544387817383</v>
+        <v>10.93544292449951</v>
       </c>
       <c r="C221" t="n">
-        <v>11.13710272837361</v>
+        <v>11.13710175711273</v>
       </c>
       <c r="D221" t="n">
-        <v>10.88044545364733</v>
+        <v>10.8804445047694</v>
       </c>
       <c r="E221" t="n">
-        <v>10.97210920313473</v>
+        <v>10.97210824626285</v>
       </c>
       <c r="F221" t="n">
         <v>1588600</v>
@@ -4852,16 +4852,16 @@
         <v>44099</v>
       </c>
       <c r="B222" t="n">
-        <v>11.30209827423096</v>
+        <v>11.30209732055664</v>
       </c>
       <c r="C222" t="n">
-        <v>11.30209827423096</v>
+        <v>11.30209732055664</v>
       </c>
       <c r="D222" t="n">
-        <v>10.63295580727637</v>
+        <v>10.63295491006448</v>
       </c>
       <c r="E222" t="n">
-        <v>10.8437812286444</v>
+        <v>10.843780313643</v>
       </c>
       <c r="F222" t="n">
         <v>2517800</v>
@@ -4872,16 +4872,16 @@
         <v>44102</v>
       </c>
       <c r="B223" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C223" t="n">
-        <v>11.44875814201422</v>
+        <v>11.44875714774106</v>
       </c>
       <c r="D223" t="n">
-        <v>10.8621129572749</v>
+        <v>10.86211201394924</v>
       </c>
       <c r="E223" t="n">
-        <v>11.39376059303005</v>
+        <v>11.39375960353318</v>
       </c>
       <c r="F223" t="n">
         <v>1430300</v>
@@ -5012,16 +5012,16 @@
         <v>44111</v>
       </c>
       <c r="B230" t="n">
-        <v>10.95377635955811</v>
+        <v>10.95377540588379</v>
       </c>
       <c r="C230" t="n">
-        <v>11.23793329027351</v>
+        <v>11.23793231185949</v>
       </c>
       <c r="D230" t="n">
-        <v>10.81628160628407</v>
+        <v>10.81628066458053</v>
       </c>
       <c r="E230" t="n">
-        <v>11.10043766282916</v>
+        <v>11.10043669638599</v>
       </c>
       <c r="F230" t="n">
         <v>1553900</v>
@@ -5232,16 +5232,16 @@
         <v>44127</v>
       </c>
       <c r="B241" t="n">
-        <v>11.82457733154297</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="C241" t="n">
-        <v>11.82457733154297</v>
+        <v>11.82457828521729</v>
       </c>
       <c r="D241" t="n">
-        <v>11.31126282096371</v>
+        <v>11.31126373323825</v>
       </c>
       <c r="E241" t="n">
-        <v>11.49458943188488</v>
+        <v>11.49459035894505</v>
       </c>
       <c r="F241" t="n">
         <v>1343300</v>
@@ -5292,16 +5292,16 @@
         <v>44132</v>
       </c>
       <c r="B244" t="n">
-        <v>11.37542819976807</v>
+        <v>11.37542724609375</v>
       </c>
       <c r="C244" t="n">
-        <v>11.66875081033842</v>
+        <v>11.66874983207301</v>
       </c>
       <c r="D244" t="n">
-        <v>11.08210558919771</v>
+        <v>11.08210466011449</v>
       </c>
       <c r="E244" t="n">
-        <v>11.66875081033842</v>
+        <v>11.66874983207301</v>
       </c>
       <c r="F244" t="n">
         <v>1933600</v>
@@ -5492,16 +5492,16 @@
         <v>44147</v>
       </c>
       <c r="B254" t="n">
-        <v>11.64125156402588</v>
+        <v>11.6412525177002</v>
       </c>
       <c r="C254" t="n">
-        <v>12.54871900945897</v>
+        <v>12.54872003747481</v>
       </c>
       <c r="D254" t="n">
-        <v>11.62291933869072</v>
+        <v>11.62292029086322</v>
       </c>
       <c r="E254" t="n">
-        <v>12.54871900945897</v>
+        <v>12.54872003747481</v>
       </c>
       <c r="F254" t="n">
         <v>2275500</v>
@@ -5652,16 +5652,16 @@
         <v>44160</v>
       </c>
       <c r="B262" t="n">
-        <v>12.79621028900146</v>
+        <v>12.79621124267578</v>
       </c>
       <c r="C262" t="n">
-        <v>13.15369785292006</v>
+        <v>13.15369883323717</v>
       </c>
       <c r="D262" t="n">
-        <v>12.69538086674404</v>
+        <v>12.69538181290375</v>
       </c>
       <c r="E262" t="n">
-        <v>12.73204619067131</v>
+        <v>12.73204713956361</v>
       </c>
       <c r="F262" t="n">
         <v>852400</v>
@@ -5712,16 +5712,16 @@
         <v>44165</v>
       </c>
       <c r="B265" t="n">
-        <v>12.20956516265869</v>
+        <v>12.20956420898438</v>
       </c>
       <c r="C265" t="n">
-        <v>12.85120969155017</v>
+        <v>12.85120868775777</v>
       </c>
       <c r="D265" t="n">
-        <v>11.97124097605051</v>
+        <v>11.9712400409914</v>
       </c>
       <c r="E265" t="n">
-        <v>12.69538183443885</v>
+        <v>12.69538084281798</v>
       </c>
       <c r="F265" t="n">
         <v>1362800</v>
@@ -5772,16 +5772,16 @@
         <v>44168</v>
       </c>
       <c r="B268" t="n">
-        <v>12.12706661224365</v>
+        <v>12.12706756591797</v>
       </c>
       <c r="C268" t="n">
-        <v>12.41122351841084</v>
+        <v>12.4112244944313</v>
       </c>
       <c r="D268" t="n">
-        <v>12.03540374270313</v>
+        <v>12.03540468916906</v>
       </c>
       <c r="E268" t="n">
-        <v>12.35622509735033</v>
+        <v>12.3562260690457</v>
       </c>
       <c r="F268" t="n">
         <v>1428200</v>
@@ -5812,16 +5812,16 @@
         <v>44172</v>
       </c>
       <c r="B270" t="n">
-        <v>12.03540515899658</v>
+        <v>12.03540420532227</v>
       </c>
       <c r="C270" t="n">
-        <v>12.40205842864592</v>
+        <v>12.40205744591834</v>
       </c>
       <c r="D270" t="n">
-        <v>11.88874385113685</v>
+        <v>11.88874290908384</v>
       </c>
       <c r="E270" t="n">
-        <v>12.40205842864592</v>
+        <v>12.40205744591834</v>
       </c>
       <c r="F270" t="n">
         <v>1735800</v>
@@ -5872,16 +5872,16 @@
         <v>44175</v>
       </c>
       <c r="B273" t="n">
-        <v>12.25539588928223</v>
+        <v>12.25539684295654</v>
       </c>
       <c r="C273" t="n">
-        <v>12.32872653584334</v>
+        <v>12.328727495224</v>
       </c>
       <c r="D273" t="n">
-        <v>11.68708294134846</v>
+        <v>11.68708385079854</v>
       </c>
       <c r="E273" t="n">
-        <v>12.15456646880326</v>
+        <v>12.15456741463136</v>
       </c>
       <c r="F273" t="n">
         <v>1250600</v>
@@ -5932,16 +5932,16 @@
         <v>44180</v>
       </c>
       <c r="B276" t="n">
-        <v>12.51205444335938</v>
+        <v>12.51205348968506</v>
       </c>
       <c r="C276" t="n">
-        <v>12.60371819810464</v>
+        <v>12.60371723744367</v>
       </c>
       <c r="D276" t="n">
-        <v>12.16373427333621</v>
+        <v>12.16373334621101</v>
       </c>
       <c r="E276" t="n">
-        <v>12.24623060360253</v>
+        <v>12.24622967018942</v>
       </c>
       <c r="F276" t="n">
         <v>865800</v>
@@ -5952,16 +5952,16 @@
         <v>44181</v>
       </c>
       <c r="B277" t="n">
-        <v>12.4753885269165</v>
+        <v>12.47538948059082</v>
       </c>
       <c r="C277" t="n">
-        <v>12.91537330506894</v>
+        <v>12.91537429237765</v>
       </c>
       <c r="D277" t="n">
-        <v>12.38372565067205</v>
+        <v>12.38372659733925</v>
       </c>
       <c r="E277" t="n">
-        <v>12.55788572745573</v>
+        <v>12.5578866874365</v>
       </c>
       <c r="F277" t="n">
         <v>1004500</v>
@@ -5992,16 +5992,16 @@
         <v>44183</v>
       </c>
       <c r="B279" t="n">
-        <v>12.19123268127441</v>
+        <v>12.19123363494873</v>
       </c>
       <c r="C279" t="n">
-        <v>12.51205406483644</v>
+        <v>12.51205504360741</v>
       </c>
       <c r="D279" t="n">
-        <v>12.08123670340998</v>
+        <v>12.08123764847972</v>
       </c>
       <c r="E279" t="n">
-        <v>12.31956088503109</v>
+        <v>12.31956184874404</v>
       </c>
       <c r="F279" t="n">
         <v>677600</v>
@@ -6112,16 +6112,16 @@
         <v>44195</v>
       </c>
       <c r="B285" t="n">
-        <v>11.8154125213623</v>
+        <v>11.81541156768799</v>
       </c>
       <c r="C285" t="n">
-        <v>12.05373669591699</v>
+        <v>12.05373572300648</v>
       </c>
       <c r="D285" t="n">
-        <v>11.77874719649464</v>
+        <v>11.77874624577974</v>
       </c>
       <c r="E285" t="n">
-        <v>11.91624194620582</v>
+        <v>11.91624098439311</v>
       </c>
       <c r="F285" t="n">
         <v>1061200</v>
@@ -6132,16 +6132,16 @@
         <v>44200</v>
       </c>
       <c r="B286" t="n">
-        <v>11.7237491607666</v>
+        <v>11.72374820709229</v>
       </c>
       <c r="C286" t="n">
-        <v>11.8979092411191</v>
+        <v>11.89790827327764</v>
       </c>
       <c r="D286" t="n">
-        <v>11.42126000203783</v>
+        <v>11.42125907296965</v>
       </c>
       <c r="E286" t="n">
-        <v>11.8979092411191</v>
+        <v>11.89790827327764</v>
       </c>
       <c r="F286" t="n">
         <v>1030900</v>
@@ -6232,16 +6232,16 @@
         <v>44207</v>
       </c>
       <c r="B291" t="n">
-        <v>10.95377635955811</v>
+        <v>10.95377540588379</v>
       </c>
       <c r="C291" t="n">
-        <v>11.13710298864692</v>
+        <v>11.13710201901154</v>
       </c>
       <c r="D291" t="n">
-        <v>10.83461383210779</v>
+        <v>10.83461288880819</v>
       </c>
       <c r="E291" t="n">
-        <v>11.04544011118768</v>
+        <v>11.04543914953279</v>
       </c>
       <c r="F291" t="n">
         <v>926700</v>
@@ -6312,16 +6312,16 @@
         <v>44211</v>
       </c>
       <c r="B295" t="n">
-        <v>11.34792995452881</v>
+        <v>11.34792900085449</v>
       </c>
       <c r="C295" t="n">
-        <v>11.34792995452881</v>
+        <v>11.34792900085449</v>
       </c>
       <c r="D295" t="n">
-        <v>10.93544479557187</v>
+        <v>10.9354438765626</v>
       </c>
       <c r="E295" t="n">
-        <v>11.18293554127788</v>
+        <v>11.18293460146961</v>
       </c>
       <c r="F295" t="n">
         <v>2333900</v>
@@ -6332,16 +6332,16 @@
         <v>44214</v>
       </c>
       <c r="B296" t="n">
-        <v>11.29293060302734</v>
+        <v>11.29293155670166</v>
       </c>
       <c r="C296" t="n">
-        <v>11.44875845299908</v>
+        <v>11.44875941983287</v>
       </c>
       <c r="D296" t="n">
-        <v>11.04543987753537</v>
+        <v>11.0454408103094</v>
       </c>
       <c r="E296" t="n">
-        <v>11.40292657815381</v>
+        <v>11.40292754111715</v>
       </c>
       <c r="F296" t="n">
         <v>2481600</v>
@@ -6352,16 +6352,16 @@
         <v>44215</v>
       </c>
       <c r="B297" t="n">
-        <v>11.34792995452881</v>
+        <v>11.34792900085449</v>
       </c>
       <c r="C297" t="n">
-        <v>11.54958969581656</v>
+        <v>11.54958872519487</v>
       </c>
       <c r="D297" t="n">
-        <v>10.86211413949821</v>
+        <v>10.86211322665161</v>
       </c>
       <c r="E297" t="n">
-        <v>11.35709650508061</v>
+        <v>11.35709555063594</v>
       </c>
       <c r="F297" t="n">
         <v>3202200</v>
@@ -6432,16 +6432,16 @@
         <v>44222</v>
       </c>
       <c r="B301" t="n">
-        <v>11.30209827423096</v>
+        <v>11.30209732055664</v>
       </c>
       <c r="C301" t="n">
-        <v>11.70541776388255</v>
+        <v>11.70541677617602</v>
       </c>
       <c r="D301" t="n">
-        <v>10.93544498742986</v>
+        <v>10.93544406469386</v>
       </c>
       <c r="E301" t="n">
-        <v>11.03627442275757</v>
+        <v>11.03627349151354</v>
       </c>
       <c r="F301" t="n">
         <v>3718300</v>
@@ -6552,16 +6552,16 @@
         <v>44230</v>
       </c>
       <c r="B307" t="n">
-        <v>11.34792995452881</v>
+        <v>11.34792900085449</v>
       </c>
       <c r="C307" t="n">
-        <v>11.52209004416116</v>
+        <v>11.52208907585052</v>
       </c>
       <c r="D307" t="n">
-        <v>11.15543676379285</v>
+        <v>11.15543582629557</v>
       </c>
       <c r="E307" t="n">
-        <v>11.4395928375357</v>
+        <v>11.43959187615808</v>
       </c>
       <c r="F307" t="n">
         <v>1665300</v>
@@ -6872,16 +6872,16 @@
         <v>44256</v>
       </c>
       <c r="B323" t="n">
-        <v>9.927146911621094</v>
+        <v>9.927145957946777</v>
       </c>
       <c r="C323" t="n">
-        <v>10.24796918590089</v>
+        <v>10.24796820140604</v>
       </c>
       <c r="D323" t="n">
-        <v>9.780485600237313</v>
+        <v>9.780484660652355</v>
       </c>
       <c r="E323" t="n">
-        <v>10.14713887869676</v>
+        <v>10.14713790388841</v>
       </c>
       <c r="F323" t="n">
         <v>1920500</v>
@@ -6932,16 +6932,16 @@
         <v>44259</v>
       </c>
       <c r="B326" t="n">
-        <v>9.642991065979004</v>
+        <v>9.642990112304688</v>
       </c>
       <c r="C326" t="n">
-        <v>10.10130811190948</v>
+        <v>10.10130711290844</v>
       </c>
       <c r="D326" t="n">
-        <v>9.505495427697626</v>
+        <v>9.505494487621378</v>
       </c>
       <c r="E326" t="n">
-        <v>9.743820501382368</v>
+        <v>9.743819537736204</v>
       </c>
       <c r="F326" t="n">
         <v>1824000</v>
@@ -7052,16 +7052,16 @@
         <v>44267</v>
       </c>
       <c r="B332" t="n">
-        <v>10.02797603607178</v>
+        <v>10.02797508239746</v>
       </c>
       <c r="C332" t="n">
-        <v>10.25713454659981</v>
+        <v>10.2571335711322</v>
       </c>
       <c r="D332" t="n">
-        <v>9.826317176209756</v>
+        <v>9.826316241713474</v>
       </c>
       <c r="E332" t="n">
-        <v>10.08297446323346</v>
+        <v>10.08297350432871</v>
       </c>
       <c r="F332" t="n">
         <v>2668700</v>
@@ -7092,16 +7092,16 @@
         <v>44271</v>
       </c>
       <c r="B334" t="n">
-        <v>9.771318435668945</v>
+        <v>9.771317481994629</v>
       </c>
       <c r="C334" t="n">
-        <v>10.3487979685795</v>
+        <v>10.34879695854355</v>
       </c>
       <c r="D334" t="n">
-        <v>9.734653110127178</v>
+        <v>9.734652160031374</v>
       </c>
       <c r="E334" t="n">
-        <v>10.31213264303773</v>
+        <v>10.3121316365803</v>
       </c>
       <c r="F334" t="n">
         <v>1474300</v>
@@ -7252,16 +7252,16 @@
         <v>44281</v>
       </c>
       <c r="B342" t="n">
-        <v>10.08297348022461</v>
+        <v>10.08297443389893</v>
       </c>
       <c r="C342" t="n">
-        <v>10.48629203479868</v>
+        <v>10.48629302661993</v>
       </c>
       <c r="D342" t="n">
-        <v>9.908813413837462</v>
+        <v>9.908814351039258</v>
       </c>
       <c r="E342" t="n">
-        <v>10.48629203479868</v>
+        <v>10.48629302661993</v>
       </c>
       <c r="F342" t="n">
         <v>3639300</v>
@@ -7352,16 +7352,16 @@
         <v>44291</v>
       </c>
       <c r="B347" t="n">
-        <v>10.96294212341309</v>
+        <v>10.9629430770874</v>
       </c>
       <c r="C347" t="n">
-        <v>11.08210464231837</v>
+        <v>11.08210560635872</v>
       </c>
       <c r="D347" t="n">
-        <v>10.71545053626282</v>
+        <v>10.71545146840767</v>
       </c>
       <c r="E347" t="n">
-        <v>10.75211585945135</v>
+        <v>10.75211679478574</v>
       </c>
       <c r="F347" t="n">
         <v>1391400</v>
@@ -7452,16 +7452,16 @@
         <v>44298</v>
       </c>
       <c r="B352" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C352" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="D352" t="n">
-        <v>10.69711856198182</v>
+        <v>10.69711763298518</v>
       </c>
       <c r="E352" t="n">
-        <v>10.87127863265874</v>
+        <v>10.87127768853708</v>
       </c>
       <c r="F352" t="n">
         <v>1341200</v>
@@ -7512,16 +7512,16 @@
         <v>44301</v>
       </c>
       <c r="B355" t="n">
-        <v>11.58625507354736</v>
+        <v>11.58625411987305</v>
       </c>
       <c r="C355" t="n">
-        <v>11.77874826510893</v>
+        <v>11.77874729559034</v>
       </c>
       <c r="D355" t="n">
-        <v>11.11877148344493</v>
+        <v>11.11877056824958</v>
       </c>
       <c r="E355" t="n">
-        <v>11.24710056920944</v>
+        <v>11.24709964345121</v>
       </c>
       <c r="F355" t="n">
         <v>3631000</v>
@@ -7532,16 +7532,16 @@
         <v>44302</v>
       </c>
       <c r="B356" t="n">
-        <v>12.53955364227295</v>
+        <v>12.53955268859863</v>
       </c>
       <c r="C356" t="n">
-        <v>13.63951428871419</v>
+        <v>13.63951325138424</v>
       </c>
       <c r="D356" t="n">
-        <v>11.47625832157408</v>
+        <v>11.47625744876687</v>
       </c>
       <c r="E356" t="n">
-        <v>11.61375307456536</v>
+        <v>11.61375219130122</v>
       </c>
       <c r="F356" t="n">
         <v>14691000</v>
@@ -7592,16 +7592,16 @@
         <v>44308</v>
       </c>
       <c r="B359" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C359" t="n">
-        <v>11.41209281796801</v>
+        <v>11.41209182687907</v>
       </c>
       <c r="D359" t="n">
-        <v>10.91711050625907</v>
+        <v>10.91710955815712</v>
       </c>
       <c r="E359" t="n">
-        <v>11.26543152178318</v>
+        <v>11.26543054343111</v>
       </c>
       <c r="F359" t="n">
         <v>4817400</v>
@@ -7772,16 +7772,16 @@
         <v>44321</v>
       </c>
       <c r="B368" t="n">
-        <v>11.34792995452881</v>
+        <v>11.34792900085449</v>
       </c>
       <c r="C368" t="n">
-        <v>11.4487593880875</v>
+        <v>11.44875842593953</v>
       </c>
       <c r="D368" t="n">
-        <v>11.13710366268925</v>
+        <v>11.13710272673267</v>
       </c>
       <c r="E368" t="n">
-        <v>11.27459929845515</v>
+        <v>11.2745983509435</v>
       </c>
       <c r="F368" t="n">
         <v>936700</v>
@@ -7792,16 +7792,16 @@
         <v>44322</v>
       </c>
       <c r="B369" t="n">
-        <v>11.24709892272949</v>
+        <v>11.24709987640381</v>
       </c>
       <c r="C369" t="n">
-        <v>11.36626056628825</v>
+        <v>11.36626153006663</v>
       </c>
       <c r="D369" t="n">
-        <v>11.07293798367547</v>
+        <v>11.07293892258217</v>
       </c>
       <c r="E369" t="n">
-        <v>11.36626056628825</v>
+        <v>11.36626153006663</v>
       </c>
       <c r="F369" t="n">
         <v>1352700</v>
@@ -8052,16 +8052,16 @@
         <v>44341</v>
       </c>
       <c r="B382" t="n">
-        <v>12.53955364227295</v>
+        <v>12.53955268859863</v>
       </c>
       <c r="C382" t="n">
-        <v>12.75037904674896</v>
+        <v>12.75037807704068</v>
       </c>
       <c r="D382" t="n">
-        <v>12.40205801511135</v>
+        <v>12.40205707189402</v>
       </c>
       <c r="E382" t="n">
-        <v>12.62205084373585</v>
+        <v>12.62204988378735</v>
       </c>
       <c r="F382" t="n">
         <v>1256400</v>
@@ -8172,16 +8172,16 @@
         <v>44349</v>
       </c>
       <c r="B388" t="n">
-        <v>13.09869956970215</v>
+        <v>13.09870052337646</v>
       </c>
       <c r="C388" t="n">
-        <v>13.19952899303539</v>
+        <v>13.19952995405077</v>
       </c>
       <c r="D388" t="n">
-        <v>12.76871165083586</v>
+        <v>12.76871258048482</v>
       </c>
       <c r="E388" t="n">
-        <v>12.92453949773196</v>
+        <v>12.92454043872624</v>
       </c>
       <c r="F388" t="n">
         <v>2158300</v>
@@ -8192,16 +8192,16 @@
         <v>44351</v>
       </c>
       <c r="B389" t="n">
-        <v>13.35535717010498</v>
+        <v>13.3553581237793</v>
       </c>
       <c r="C389" t="n">
-        <v>13.47451969562855</v>
+        <v>13.47452065781198</v>
       </c>
       <c r="D389" t="n">
-        <v>12.88787449202979</v>
+        <v>12.88787541232228</v>
       </c>
       <c r="E389" t="n">
-        <v>13.11703299322814</v>
+        <v>13.11703392988429</v>
       </c>
       <c r="F389" t="n">
         <v>1715000</v>
@@ -8212,16 +8212,16 @@
         <v>44354</v>
       </c>
       <c r="B390" t="n">
-        <v>13.2361946105957</v>
+        <v>13.23619365692139</v>
       </c>
       <c r="C390" t="n">
-        <v>13.53868463563752</v>
+        <v>13.53868366016865</v>
       </c>
       <c r="D390" t="n">
-        <v>13.1170329595484</v>
+        <v>13.11703201445974</v>
       </c>
       <c r="E390" t="n">
-        <v>13.53868463563752</v>
+        <v>13.53868366016865</v>
       </c>
       <c r="F390" t="n">
         <v>1299300</v>
@@ -8252,16 +8252,16 @@
         <v>44356</v>
       </c>
       <c r="B392" t="n">
-        <v>13.5386848449707</v>
+        <v>13.53868389129639</v>
       </c>
       <c r="C392" t="n">
-        <v>13.84117400051925</v>
+        <v>13.84117302553739</v>
       </c>
       <c r="D392" t="n">
-        <v>13.38285699221293</v>
+        <v>13.38285604951523</v>
       </c>
       <c r="E392" t="n">
-        <v>13.78617557488755</v>
+        <v>13.78617460377982</v>
       </c>
       <c r="F392" t="n">
         <v>1247900</v>
@@ -8292,16 +8292,16 @@
         <v>44358</v>
       </c>
       <c r="B394" t="n">
-        <v>13.30036067962646</v>
+        <v>13.30035972595215</v>
       </c>
       <c r="C394" t="n">
-        <v>13.69451273867269</v>
+        <v>13.69451175673653</v>
       </c>
       <c r="D394" t="n">
-        <v>13.08036871073968</v>
+        <v>13.08036777283943</v>
       </c>
       <c r="E394" t="n">
-        <v>13.69451273867269</v>
+        <v>13.69451175673653</v>
       </c>
       <c r="F394" t="n">
         <v>990400</v>
@@ -8312,16 +8312,16 @@
         <v>44361</v>
       </c>
       <c r="B395" t="n">
-        <v>13.50201892852783</v>
+        <v>13.50201797485352</v>
       </c>
       <c r="C395" t="n">
-        <v>13.65784678455664</v>
+        <v>13.6578458198759</v>
       </c>
       <c r="D395" t="n">
-        <v>13.30036007004259</v>
+        <v>13.30035913061184</v>
       </c>
       <c r="E395" t="n">
-        <v>13.3186922961911</v>
+        <v>13.3186913554655</v>
       </c>
       <c r="F395" t="n">
         <v>1118700</v>
@@ -8372,16 +8372,16 @@
         <v>44364</v>
       </c>
       <c r="B398" t="n">
-        <v>13.4561882019043</v>
+        <v>13.45618724822998</v>
       </c>
       <c r="C398" t="n">
-        <v>13.5661841835611</v>
+        <v>13.56618322209109</v>
       </c>
       <c r="D398" t="n">
-        <v>13.20869658754872</v>
+        <v>13.20869565141477</v>
       </c>
       <c r="E398" t="n">
-        <v>13.46535387808126</v>
+        <v>13.46535292375735</v>
       </c>
       <c r="F398" t="n">
         <v>1288600</v>
@@ -8432,16 +8432,16 @@
         <v>44369</v>
       </c>
       <c r="B401" t="n">
-        <v>13.5386848449707</v>
+        <v>13.53868389129639</v>
       </c>
       <c r="C401" t="n">
-        <v>13.98783530331003</v>
+        <v>13.98783431799724</v>
       </c>
       <c r="D401" t="n">
-        <v>13.41952231791062</v>
+        <v>13.41952137263019</v>
       </c>
       <c r="E401" t="n">
-        <v>13.95116997761234</v>
+        <v>13.95116899488228</v>
       </c>
       <c r="F401" t="n">
         <v>2062700</v>
@@ -8512,16 +8512,16 @@
         <v>44375</v>
       </c>
       <c r="B405" t="n">
-        <v>13.3370246887207</v>
+        <v>13.33702564239502</v>
       </c>
       <c r="C405" t="n">
-        <v>13.5845154106985</v>
+        <v>13.58451638206983</v>
       </c>
       <c r="D405" t="n">
-        <v>12.99787021835392</v>
+        <v>12.99787114777673</v>
       </c>
       <c r="E405" t="n">
-        <v>13.29119281452621</v>
+        <v>13.29119376492328</v>
       </c>
       <c r="F405" t="n">
         <v>1199100</v>
@@ -8532,16 +8532,16 @@
         <v>44376</v>
       </c>
       <c r="B406" t="n">
-        <v>13.15369892120361</v>
+        <v>13.1536979675293</v>
       </c>
       <c r="C406" t="n">
-        <v>13.30036022882386</v>
+        <v>13.30035926451625</v>
       </c>
       <c r="D406" t="n">
-        <v>12.89704075869783</v>
+        <v>12.89703982363184</v>
       </c>
       <c r="E406" t="n">
-        <v>13.2636949019188</v>
+        <v>13.26369394026951</v>
       </c>
       <c r="F406" t="n">
         <v>967400</v>
@@ -8572,16 +8572,16 @@
         <v>44378</v>
       </c>
       <c r="B408" t="n">
-        <v>12.79621028900146</v>
+        <v>12.79621124267578</v>
       </c>
       <c r="C408" t="n">
-        <v>13.35535669743492</v>
+        <v>13.35535769278123</v>
       </c>
       <c r="D408" t="n">
-        <v>12.79621028900146</v>
+        <v>12.79621124267578</v>
       </c>
       <c r="E408" t="n">
-        <v>13.19952885220145</v>
+        <v>13.19952983593424</v>
       </c>
       <c r="F408" t="n">
         <v>1624000</v>
@@ -8632,16 +8632,16 @@
         <v>44383</v>
       </c>
       <c r="B411" t="n">
-        <v>12.51205444335938</v>
+        <v>12.51205348968506</v>
       </c>
       <c r="C411" t="n">
-        <v>12.69538195284991</v>
+        <v>12.69538098520229</v>
       </c>
       <c r="D411" t="n">
-        <v>12.18206649978305</v>
+        <v>12.18206557126056</v>
       </c>
       <c r="E411" t="n">
-        <v>12.69538195284991</v>
+        <v>12.69538098520229</v>
       </c>
       <c r="F411" t="n">
         <v>2034200</v>
@@ -8692,16 +8692,16 @@
         <v>44389</v>
       </c>
       <c r="B414" t="n">
-        <v>12.36539173126221</v>
+        <v>12.36539268493652</v>
       </c>
       <c r="C414" t="n">
-        <v>12.54871834576934</v>
+        <v>12.54871931358263</v>
       </c>
       <c r="D414" t="n">
-        <v>12.28289453619143</v>
+        <v>12.2828954835032</v>
       </c>
       <c r="E414" t="n">
-        <v>12.50288734777025</v>
+        <v>12.50288831204884</v>
       </c>
       <c r="F414" t="n">
         <v>1825900</v>
@@ -8752,16 +8752,16 @@
         <v>44392</v>
       </c>
       <c r="B417" t="n">
-        <v>12.06290245056152</v>
+        <v>12.06290340423584</v>
       </c>
       <c r="C417" t="n">
-        <v>12.45705532253645</v>
+        <v>12.45705630737188</v>
       </c>
       <c r="D417" t="n">
-        <v>12.05373590140624</v>
+        <v>12.05373685435586</v>
       </c>
       <c r="E417" t="n">
-        <v>12.29206093442225</v>
+        <v>12.29206190621348</v>
       </c>
       <c r="F417" t="n">
         <v>1763900</v>
@@ -9132,16 +9132,16 @@
         <v>44419</v>
       </c>
       <c r="B436" t="n">
-        <v>9.890480995178223</v>
+        <v>9.890481948852539</v>
       </c>
       <c r="C436" t="n">
-        <v>10.51379240563549</v>
+        <v>10.51379341941164</v>
       </c>
       <c r="D436" t="n">
-        <v>9.74381969252247</v>
+        <v>9.743820632055199</v>
       </c>
       <c r="E436" t="n">
-        <v>10.51379240563549</v>
+        <v>10.51379341941164</v>
       </c>
       <c r="F436" t="n">
         <v>4618100</v>
@@ -9152,16 +9152,16 @@
         <v>44420</v>
       </c>
       <c r="B437" t="n">
-        <v>9.9088134765625</v>
+        <v>9.908814430236816</v>
       </c>
       <c r="C437" t="n">
-        <v>10.05547477006329</v>
+        <v>10.05547573785303</v>
       </c>
       <c r="D437" t="n">
-        <v>9.697987211527419</v>
+        <v>9.697988144910749</v>
       </c>
       <c r="E437" t="n">
-        <v>9.890480377789769</v>
+        <v>9.890481329699616</v>
       </c>
       <c r="F437" t="n">
         <v>1797300</v>
@@ -9172,16 +9172,16 @@
         <v>44421</v>
       </c>
       <c r="B438" t="n">
-        <v>9.817150115966797</v>
+        <v>9.81714916229248</v>
       </c>
       <c r="C438" t="n">
-        <v>10.00964328977675</v>
+        <v>10.00964231740293</v>
       </c>
       <c r="D438" t="n">
-        <v>9.688821042036732</v>
+        <v>9.688820100828776</v>
       </c>
       <c r="E438" t="n">
-        <v>9.90881386508403</v>
+        <v>9.908812902505156</v>
       </c>
       <c r="F438" t="n">
         <v>1360000</v>
@@ -9332,16 +9332,16 @@
         <v>44433</v>
       </c>
       <c r="B446" t="n">
-        <v>8.955514907836914</v>
+        <v>8.955513954162598</v>
       </c>
       <c r="C446" t="n">
-        <v>9.322168170788439</v>
+        <v>9.322167178069154</v>
       </c>
       <c r="D446" t="n">
-        <v>8.744688626012037</v>
+        <v>8.744687694788647</v>
       </c>
       <c r="E446" t="n">
-        <v>9.175506865607829</v>
+        <v>9.175505888506532</v>
       </c>
       <c r="F446" t="n">
         <v>3539500</v>
@@ -9372,16 +9372,16 @@
         <v>44435</v>
       </c>
       <c r="B448" t="n">
-        <v>8.680524826049805</v>
+        <v>8.680523872375488</v>
       </c>
       <c r="C448" t="n">
-        <v>8.799687359204386</v>
+        <v>8.799686392438435</v>
       </c>
       <c r="D448" t="n">
-        <v>8.451366310176466</v>
+        <v>8.451365381678345</v>
       </c>
       <c r="E448" t="n">
-        <v>8.588861070032324</v>
+        <v>8.588860126428523</v>
       </c>
       <c r="F448" t="n">
         <v>2539200</v>
@@ -9472,16 +9472,16 @@
         <v>44442</v>
       </c>
       <c r="B453" t="n">
-        <v>8.020546913146973</v>
+        <v>8.020547866821289</v>
       </c>
       <c r="C453" t="n">
-        <v>8.048045686367239</v>
+        <v>8.048046643311267</v>
       </c>
       <c r="D453" t="n">
-        <v>7.818887203134468</v>
+        <v>7.818888132830658</v>
       </c>
       <c r="E453" t="n">
-        <v>7.965548492536203</v>
+        <v>7.965549439670992</v>
       </c>
       <c r="F453" t="n">
         <v>2243900</v>
@@ -9492,16 +9492,16 @@
         <v>44445</v>
       </c>
       <c r="B454" t="n">
-        <v>8.359701156616211</v>
+        <v>8.359702110290527</v>
       </c>
       <c r="C454" t="n">
-        <v>8.396366478059562</v>
+        <v>8.396367435916657</v>
       </c>
       <c r="D454" t="n">
-        <v>7.910550750392595</v>
+        <v>7.910551652827854</v>
       </c>
       <c r="E454" t="n">
-        <v>8.002213616915865</v>
+        <v>8.00221452980802</v>
       </c>
       <c r="F454" t="n">
         <v>1394500</v>
@@ -9572,16 +9572,16 @@
         <v>44452</v>
       </c>
       <c r="B458" t="n">
-        <v>8.258872985839844</v>
+        <v>8.258872032165527</v>
       </c>
       <c r="C458" t="n">
-        <v>8.43303307039994</v>
+        <v>8.433032096614889</v>
       </c>
       <c r="D458" t="n">
-        <v>8.038881024025928</v>
+        <v>8.038880095754676</v>
       </c>
       <c r="E458" t="n">
-        <v>8.148877004932885</v>
+        <v>8.148876063960101</v>
       </c>
       <c r="F458" t="n">
         <v>1472800</v>
@@ -9592,16 +9592,16 @@
         <v>44453</v>
       </c>
       <c r="B459" t="n">
-        <v>8.185543060302734</v>
+        <v>8.185542106628418</v>
       </c>
       <c r="C459" t="n">
-        <v>8.42386726972355</v>
+        <v>8.423866288282758</v>
       </c>
       <c r="D459" t="n">
-        <v>8.139711178970506</v>
+        <v>8.139710230635933</v>
       </c>
       <c r="E459" t="n">
-        <v>8.42386726972355</v>
+        <v>8.423866288282758</v>
       </c>
       <c r="F459" t="n">
         <v>1986100</v>
@@ -9652,16 +9652,16 @@
         <v>44456</v>
       </c>
       <c r="B462" t="n">
-        <v>7.516398429870605</v>
+        <v>7.516398906707764</v>
       </c>
       <c r="C462" t="n">
-        <v>7.901384769801296</v>
+        <v>7.901385271061826</v>
       </c>
       <c r="D462" t="n">
-        <v>7.516398429870605</v>
+        <v>7.516398906707764</v>
       </c>
       <c r="E462" t="n">
-        <v>7.883052544846172</v>
+        <v>7.883053044943713</v>
       </c>
       <c r="F462" t="n">
         <v>2328100</v>
@@ -9692,16 +9692,16 @@
         <v>44460</v>
       </c>
       <c r="B464" t="n">
-        <v>7.562230110168457</v>
+        <v>7.562230587005615</v>
       </c>
       <c r="C464" t="n">
-        <v>7.635560756454652</v>
+        <v>7.635561237915681</v>
       </c>
       <c r="D464" t="n">
-        <v>7.213909103223903</v>
+        <v>7.213909558097646</v>
       </c>
       <c r="E464" t="n">
-        <v>7.488899463882262</v>
+        <v>7.488899936095549</v>
       </c>
       <c r="F464" t="n">
         <v>2716900</v>
@@ -9712,16 +9712,16 @@
         <v>44461</v>
       </c>
       <c r="B465" t="n">
-        <v>7.653894901275635</v>
+        <v>7.653894424438477</v>
       </c>
       <c r="C465" t="n">
-        <v>7.773056562150489</v>
+        <v>7.773056077889568</v>
       </c>
       <c r="D465" t="n">
-        <v>7.443068608758569</v>
+        <v>7.443068145055875</v>
       </c>
       <c r="E465" t="n">
-        <v>7.708892456422433</v>
+        <v>7.708891976158931</v>
       </c>
       <c r="F465" t="n">
         <v>2341500</v>
@@ -9752,16 +9752,16 @@
         <v>44463</v>
       </c>
       <c r="B467" t="n">
-        <v>7.488900184631348</v>
+        <v>7.488899707794189</v>
       </c>
       <c r="C467" t="n">
-        <v>7.580563938396152</v>
+        <v>7.580563455722531</v>
       </c>
       <c r="D467" t="n">
-        <v>7.296407001061533</v>
+        <v>7.2964065364809</v>
       </c>
       <c r="E467" t="n">
-        <v>7.580563938396152</v>
+        <v>7.580563455722531</v>
       </c>
       <c r="F467" t="n">
         <v>1855500</v>
@@ -9852,16 +9852,16 @@
         <v>44470</v>
       </c>
       <c r="B472" t="n">
-        <v>7.05808162689209</v>
+        <v>7.058081150054932</v>
       </c>
       <c r="C472" t="n">
-        <v>7.05808162689209</v>
+        <v>7.058081150054932</v>
       </c>
       <c r="D472" t="n">
-        <v>6.590598514062039</v>
+        <v>6.590598068807588</v>
       </c>
       <c r="E472" t="n">
-        <v>6.627263839104194</v>
+        <v>6.627263391372669</v>
       </c>
       <c r="F472" t="n">
         <v>1964300</v>
@@ -9872,16 +9872,16 @@
         <v>44473</v>
       </c>
       <c r="B473" t="n">
-        <v>6.88392162322998</v>
+        <v>6.883921146392822</v>
       </c>
       <c r="C473" t="n">
-        <v>7.05808170045277</v>
+        <v>7.058081211551849</v>
       </c>
       <c r="D473" t="n">
-        <v>6.792257872584105</v>
+        <v>6.792257402096333</v>
       </c>
       <c r="E473" t="n">
-        <v>6.911420398755618</v>
+        <v>6.911419920013668</v>
       </c>
       <c r="F473" t="n">
         <v>2556200</v>
@@ -9932,16 +9932,16 @@
         <v>44476</v>
       </c>
       <c r="B476" t="n">
-        <v>6.471435546875</v>
+        <v>6.471436023712158</v>
       </c>
       <c r="C476" t="n">
-        <v>6.728093241715267</v>
+        <v>6.728093737463828</v>
       </c>
       <c r="D476" t="n">
-        <v>6.471435546875</v>
+        <v>6.471436023712158</v>
       </c>
       <c r="E476" t="n">
-        <v>6.627263386197471</v>
+        <v>6.627263874516548</v>
       </c>
       <c r="F476" t="n">
         <v>1954700</v>
@@ -9952,16 +9952,16 @@
         <v>44477</v>
       </c>
       <c r="B477" t="n">
-        <v>6.728094100952148</v>
+        <v>6.72809362411499</v>
       </c>
       <c r="C477" t="n">
-        <v>7.048915932660414</v>
+        <v>7.048915433085796</v>
       </c>
       <c r="D477" t="n">
-        <v>6.517268250900686</v>
+        <v>6.517267789005293</v>
       </c>
       <c r="E477" t="n">
-        <v>6.544767027772298</v>
+        <v>6.544766563927996</v>
       </c>
       <c r="F477" t="n">
         <v>3425600</v>
@@ -9972,16 +9972,16 @@
         <v>44480</v>
       </c>
       <c r="B478" t="n">
-        <v>6.645596504211426</v>
+        <v>6.645596981048584</v>
       </c>
       <c r="C478" t="n">
-        <v>6.792257804437119</v>
+        <v>6.79225829179757</v>
       </c>
       <c r="D478" t="n">
-        <v>6.526433979235474</v>
+        <v>6.526434447522441</v>
       </c>
       <c r="E478" t="n">
-        <v>6.783091691715589</v>
+        <v>6.783092178418349</v>
       </c>
       <c r="F478" t="n">
         <v>1719800</v>
@@ -10012,16 +10012,16 @@
         <v>44483</v>
       </c>
       <c r="B480" t="n">
-        <v>6.618097305297852</v>
+        <v>6.618096828460693</v>
       </c>
       <c r="C480" t="n">
-        <v>7.058081643952359</v>
+        <v>7.058081135414113</v>
       </c>
       <c r="D480" t="n">
-        <v>6.563099317601682</v>
+        <v>6.563098844727156</v>
       </c>
       <c r="E480" t="n">
-        <v>6.847255805907801</v>
+        <v>6.84725531255966</v>
       </c>
       <c r="F480" t="n">
         <v>2383700</v>
@@ -10052,16 +10052,16 @@
         <v>44487</v>
       </c>
       <c r="B482" t="n">
-        <v>6.819756984710693</v>
+        <v>6.819757461547852</v>
       </c>
       <c r="C482" t="n">
-        <v>6.865588422273182</v>
+        <v>6.865588902314872</v>
       </c>
       <c r="D482" t="n">
-        <v>6.526433948553137</v>
+        <v>6.52643440488116</v>
       </c>
       <c r="E482" t="n">
-        <v>6.783091659826643</v>
+        <v>6.783092134100163</v>
       </c>
       <c r="F482" t="n">
         <v>2088100</v>
@@ -10072,16 +10072,16 @@
         <v>44488</v>
       </c>
       <c r="B483" t="n">
-        <v>6.526433944702148</v>
+        <v>6.526434421539307</v>
       </c>
       <c r="C483" t="n">
-        <v>6.801424318255418</v>
+        <v>6.801424815184043</v>
       </c>
       <c r="D483" t="n">
-        <v>6.434770632546108</v>
+        <v>6.434771102686122</v>
       </c>
       <c r="E483" t="n">
-        <v>6.755592443634823</v>
+        <v>6.75559293721486</v>
       </c>
       <c r="F483" t="n">
         <v>2579600</v>
@@ -10212,16 +10212,16 @@
         <v>44497</v>
       </c>
       <c r="B490" t="n">
-        <v>5.673964977264404</v>
+        <v>5.673964500427246</v>
       </c>
       <c r="C490" t="n">
-        <v>5.912289609503804</v>
+        <v>5.912289112637964</v>
       </c>
       <c r="D490" t="n">
-        <v>5.646465762694187</v>
+        <v>5.646465288168049</v>
       </c>
       <c r="E490" t="n">
-        <v>5.783960961374897</v>
+        <v>5.783960475293731</v>
       </c>
       <c r="F490" t="n">
         <v>2222800</v>
@@ -10232,16 +10232,16 @@
         <v>44498</v>
       </c>
       <c r="B491" t="n">
-        <v>5.554802417755127</v>
+        <v>5.554801940917969</v>
       </c>
       <c r="C491" t="n">
-        <v>5.838958927312109</v>
+        <v>5.838958426082296</v>
       </c>
       <c r="D491" t="n">
-        <v>5.545636304329514</v>
+        <v>5.545635828279196</v>
       </c>
       <c r="E491" t="n">
-        <v>5.701463729246425</v>
+        <v>5.701463239819518</v>
       </c>
       <c r="F491" t="n">
         <v>2502600</v>
@@ -10352,16 +10352,16 @@
         <v>44509</v>
       </c>
       <c r="B497" t="n">
-        <v>6.663929462432861</v>
+        <v>6.663928985595703</v>
       </c>
       <c r="C497" t="n">
-        <v>6.783091992696317</v>
+        <v>6.78309150733249</v>
       </c>
       <c r="D497" t="n">
-        <v>6.489768942144389</v>
+        <v>6.489768477769278</v>
       </c>
       <c r="E497" t="n">
-        <v>6.517268155699483</v>
+        <v>6.517267689356667</v>
       </c>
       <c r="F497" t="n">
         <v>1909500</v>
@@ -10472,16 +10472,16 @@
         <v>44518</v>
       </c>
       <c r="B503" t="n">
-        <v>6.654763221740723</v>
+        <v>6.654763698577881</v>
       </c>
       <c r="C503" t="n">
-        <v>6.764759199682264</v>
+        <v>6.764759684401021</v>
       </c>
       <c r="D503" t="n">
-        <v>6.343107513821191</v>
+        <v>6.343107968327123</v>
       </c>
       <c r="E503" t="n">
-        <v>6.407271615744509</v>
+        <v>6.407272074848025</v>
       </c>
       <c r="F503" t="n">
         <v>2981000</v>
@@ -10492,16 +10492,16 @@
         <v>44519</v>
       </c>
       <c r="B504" t="n">
-        <v>7.232242584228516</v>
+        <v>7.232242107391357</v>
       </c>
       <c r="C504" t="n">
-        <v>7.305573238823276</v>
+        <v>7.305572757151272</v>
       </c>
       <c r="D504" t="n">
-        <v>6.544767041774868</v>
+        <v>6.544766610264437</v>
       </c>
       <c r="E504" t="n">
-        <v>6.645596910385254</v>
+        <v>6.645596472226894</v>
       </c>
       <c r="F504" t="n">
         <v>4026100</v>
@@ -10532,16 +10532,16 @@
         <v>44523</v>
       </c>
       <c r="B506" t="n">
-        <v>6.324774742126465</v>
+        <v>6.324774265289307</v>
       </c>
       <c r="C506" t="n">
-        <v>6.810590521561097</v>
+        <v>6.810590008097336</v>
       </c>
       <c r="D506" t="n">
-        <v>6.251444091425777</v>
+        <v>6.25144362011716</v>
       </c>
       <c r="E506" t="n">
-        <v>6.810590521561097</v>
+        <v>6.810590008097336</v>
       </c>
       <c r="F506" t="n">
         <v>4509800</v>
@@ -10652,16 +10652,16 @@
         <v>44531</v>
       </c>
       <c r="B512" t="n">
-        <v>5.87562370300293</v>
+        <v>5.875624179840088</v>
       </c>
       <c r="C512" t="n">
-        <v>6.315608033212963</v>
+        <v>6.315608545757119</v>
       </c>
       <c r="D512" t="n">
-        <v>5.756461617157511</v>
+        <v>5.756462084324052</v>
       </c>
       <c r="E512" t="n">
-        <v>6.003952775582833</v>
+        <v>6.003953262834558</v>
       </c>
       <c r="F512" t="n">
         <v>3640600</v>
@@ -10752,16 +10752,16 @@
         <v>44538</v>
       </c>
       <c r="B517" t="n">
-        <v>6.269776821136475</v>
+        <v>6.269776344299316</v>
       </c>
       <c r="C517" t="n">
-        <v>6.398105461234748</v>
+        <v>6.398104974637775</v>
       </c>
       <c r="D517" t="n">
-        <v>5.912289239520686</v>
+        <v>5.912288789871634</v>
       </c>
       <c r="E517" t="n">
-        <v>6.22394494541594</v>
+        <v>6.223944472064447</v>
       </c>
       <c r="F517" t="n">
         <v>2255900</v>
@@ -10772,16 +10772,16 @@
         <v>44539</v>
       </c>
       <c r="B518" t="n">
-        <v>6.08644962310791</v>
+        <v>6.086450099945068</v>
       </c>
       <c r="C518" t="n">
-        <v>6.269776684922006</v>
+        <v>6.26977717612175</v>
       </c>
       <c r="D518" t="n">
-        <v>5.994786310743438</v>
+        <v>5.994786780399321</v>
       </c>
       <c r="E518" t="n">
-        <v>6.2056121477243</v>
+        <v>6.205612633897133</v>
       </c>
       <c r="F518" t="n">
         <v>1370200</v>
@@ -10872,16 +10872,16 @@
         <v>44546</v>
       </c>
       <c r="B523" t="n">
-        <v>5.87562370300293</v>
+        <v>5.875624179840088</v>
       </c>
       <c r="C523" t="n">
-        <v>6.159780185855326</v>
+        <v>6.159780685753248</v>
       </c>
       <c r="D523" t="n">
-        <v>5.820625716362319</v>
+        <v>5.820626188736107</v>
       </c>
       <c r="E523" t="n">
-        <v>5.820625716362319</v>
+        <v>5.820626188736107</v>
       </c>
       <c r="F523" t="n">
         <v>2487700</v>
@@ -10912,16 +10912,16 @@
         <v>44550</v>
       </c>
       <c r="B525" t="n">
-        <v>5.701463222503662</v>
+        <v>5.70146369934082</v>
       </c>
       <c r="C525" t="n">
-        <v>5.756461646509856</v>
+        <v>5.756462127946762</v>
       </c>
       <c r="D525" t="n">
-        <v>5.582301136050633</v>
+        <v>5.582301602921769</v>
       </c>
       <c r="E525" t="n">
-        <v>5.710629772199743</v>
+        <v>5.710630249803538</v>
       </c>
       <c r="F525" t="n">
         <v>2934100</v>
@@ -11072,16 +11072,16 @@
         <v>44564</v>
       </c>
       <c r="B533" t="n">
-        <v>5.417306423187256</v>
+        <v>5.417306900024414</v>
       </c>
       <c r="C533" t="n">
-        <v>5.774793973013967</v>
+        <v>5.774794481317564</v>
       </c>
       <c r="D533" t="n">
-        <v>5.371474988627377</v>
+        <v>5.371475461430403</v>
       </c>
       <c r="E533" t="n">
-        <v>5.655631456405064</v>
+        <v>5.655631954219848</v>
       </c>
       <c r="F533" t="n">
         <v>2044700</v>
@@ -11092,16 +11092,16 @@
         <v>44565</v>
       </c>
       <c r="B534" t="n">
-        <v>5.05981969833374</v>
+        <v>5.059819221496582</v>
       </c>
       <c r="C534" t="n">
-        <v>5.444806050992582</v>
+        <v>5.44480553787433</v>
       </c>
       <c r="D534" t="n">
-        <v>5.023154373041008</v>
+        <v>5.023153899659189</v>
       </c>
       <c r="E534" t="n">
-        <v>5.417306838480457</v>
+        <v>5.417306327953727</v>
       </c>
       <c r="F534" t="n">
         <v>2338200</v>
@@ -11112,16 +11112,16 @@
         <v>44566</v>
       </c>
       <c r="B535" t="n">
-        <v>4.885659217834473</v>
+        <v>4.885658740997314</v>
       </c>
       <c r="C535" t="n">
-        <v>5.06898628262846</v>
+        <v>5.0689857878987</v>
       </c>
       <c r="D535" t="n">
-        <v>4.839827779449844</v>
+        <v>4.839827307085804</v>
       </c>
       <c r="E535" t="n">
-        <v>5.023154407158674</v>
+        <v>5.023153916902075</v>
       </c>
       <c r="F535" t="n">
         <v>2302400</v>
@@ -11172,16 +11172,16 @@
         <v>44571</v>
       </c>
       <c r="B538" t="n">
-        <v>4.79399585723877</v>
+        <v>4.793996334075928</v>
       </c>
       <c r="C538" t="n">
-        <v>4.894825720038117</v>
+        <v>4.894826206904368</v>
       </c>
       <c r="D538" t="n">
-        <v>4.629001893909508</v>
+        <v>4.62900235433546</v>
       </c>
       <c r="E538" t="n">
-        <v>4.720665206870209</v>
+        <v>4.720665676413498</v>
       </c>
       <c r="F538" t="n">
         <v>3868800</v>
@@ -11252,16 +11252,16 @@
         <v>44575</v>
       </c>
       <c r="B542" t="n">
-        <v>5.041486740112305</v>
+        <v>5.041487216949463</v>
       </c>
       <c r="C542" t="n">
-        <v>5.188148032684694</v>
+        <v>5.188148523393465</v>
       </c>
       <c r="D542" t="n">
-        <v>4.940656882926223</v>
+        <v>4.940657350226626</v>
       </c>
       <c r="E542" t="n">
-        <v>5.133150047970048</v>
+        <v>5.133150533476964</v>
       </c>
       <c r="F542" t="n">
         <v>1699700</v>
@@ -11292,16 +11292,16 @@
         <v>44579</v>
       </c>
       <c r="B544" t="n">
-        <v>4.803162574768066</v>
+        <v>4.803162097930908</v>
       </c>
       <c r="C544" t="n">
-        <v>4.977323109864876</v>
+        <v>4.977322615737815</v>
       </c>
       <c r="D544" t="n">
-        <v>4.748164580066739</v>
+        <v>4.748164108689543</v>
       </c>
       <c r="E544" t="n">
-        <v>4.913159001255931</v>
+        <v>4.913158513498805</v>
       </c>
       <c r="F544" t="n">
         <v>2424100</v>
@@ -11392,16 +11392,16 @@
         <v>44586</v>
       </c>
       <c r="B549" t="n">
-        <v>5.353142261505127</v>
+        <v>5.353142738342285</v>
       </c>
       <c r="C549" t="n">
-        <v>5.435639017531668</v>
+        <v>5.435639501717318</v>
       </c>
       <c r="D549" t="n">
-        <v>5.004821265128261</v>
+        <v>5.004821710938335</v>
       </c>
       <c r="E549" t="n">
-        <v>5.068985797224562</v>
+        <v>5.068986248750164</v>
       </c>
       <c r="F549" t="n">
         <v>2938800</v>
@@ -11472,16 +11472,16 @@
         <v>44592</v>
       </c>
       <c r="B553" t="n">
-        <v>6.031451225280762</v>
+        <v>6.03145170211792</v>
       </c>
       <c r="C553" t="n">
-        <v>6.077283096886956</v>
+        <v>6.077283577347511</v>
       </c>
       <c r="D553" t="n">
-        <v>5.820625402645486</v>
+        <v>5.820625862815083</v>
       </c>
       <c r="E553" t="n">
-        <v>5.903122596702588</v>
+        <v>5.903123063394284</v>
       </c>
       <c r="F553" t="n">
         <v>2633300</v>
@@ -11552,16 +11552,16 @@
         <v>44596</v>
       </c>
       <c r="B557" t="n">
-        <v>5.490637302398682</v>
+        <v>5.490636825561523</v>
       </c>
       <c r="C557" t="n">
-        <v>5.637299035668652</v>
+        <v>5.637298546094581</v>
       </c>
       <c r="D557" t="n">
-        <v>5.371475217791077</v>
+        <v>5.37147475130261</v>
       </c>
       <c r="E557" t="n">
-        <v>5.628132486114529</v>
+        <v>5.628131997336533</v>
       </c>
       <c r="F557" t="n">
         <v>2310300</v>
@@ -11572,16 +11572,16 @@
         <v>44599</v>
       </c>
       <c r="B558" t="n">
-        <v>5.362309455871582</v>
+        <v>5.362308979034424</v>
       </c>
       <c r="C558" t="n">
-        <v>5.499804659783203</v>
+        <v>5.499804170719443</v>
       </c>
       <c r="D558" t="n">
-        <v>5.298145347908642</v>
+        <v>5.298144876777203</v>
       </c>
       <c r="E558" t="n">
-        <v>5.481471995067334</v>
+        <v>5.481471507633785</v>
       </c>
       <c r="F558" t="n">
         <v>1846600</v>
@@ -11612,16 +11612,16 @@
         <v>44601</v>
       </c>
       <c r="B560" t="n">
-        <v>5.380641937255859</v>
+        <v>5.380641460418701</v>
       </c>
       <c r="C560" t="n">
-        <v>5.600634343435816</v>
+        <v>5.600633847102739</v>
       </c>
       <c r="D560" t="n">
-        <v>5.325643944982168</v>
+        <v>5.325643473018979</v>
       </c>
       <c r="E560" t="n">
-        <v>5.39897460134709</v>
+        <v>5.398974122885275</v>
       </c>
       <c r="F560" t="n">
         <v>1575300</v>
@@ -11632,16 +11632,16 @@
         <v>44602</v>
       </c>
       <c r="B561" t="n">
-        <v>5.380641937255859</v>
+        <v>5.380641460418701</v>
       </c>
       <c r="C561" t="n">
-        <v>5.490637921803243</v>
+        <v>5.490637435218145</v>
       </c>
       <c r="D561" t="n">
-        <v>5.279812503296686</v>
+        <v>5.279812035395119</v>
       </c>
       <c r="E561" t="n">
-        <v>5.39897460134709</v>
+        <v>5.398974122885275</v>
       </c>
       <c r="F561" t="n">
         <v>1995600</v>
@@ -11692,16 +11692,16 @@
         <v>44607</v>
       </c>
       <c r="B564" t="n">
-        <v>5.353142261505127</v>
+        <v>5.353142738342285</v>
       </c>
       <c r="C564" t="n">
-        <v>5.362308373470247</v>
+        <v>5.362308851123887</v>
       </c>
       <c r="D564" t="n">
-        <v>5.160649102301339</v>
+        <v>5.160649561991953</v>
       </c>
       <c r="E564" t="n">
-        <v>5.169815214266459</v>
+        <v>5.169815674773554</v>
       </c>
       <c r="F564" t="n">
         <v>2196800</v>
@@ -11772,16 +11772,16 @@
         <v>44613</v>
       </c>
       <c r="B568" t="n">
-        <v>4.940657615661621</v>
+        <v>4.940657138824463</v>
       </c>
       <c r="C568" t="n">
-        <v>5.224814130705664</v>
+        <v>5.224813626443739</v>
       </c>
       <c r="D568" t="n">
-        <v>4.894826173478179</v>
+        <v>4.894825701064345</v>
       </c>
       <c r="E568" t="n">
-        <v>5.206481466415249</v>
+        <v>5.206480963922662</v>
       </c>
       <c r="F568" t="n">
         <v>2460300</v>
@@ -11792,16 +11792,16 @@
         <v>44614</v>
       </c>
       <c r="B569" t="n">
-        <v>4.913157939910889</v>
+        <v>4.913158416748047</v>
       </c>
       <c r="C569" t="n">
-        <v>5.023153905552112</v>
+        <v>5.023154393064718</v>
       </c>
       <c r="D569" t="n">
-        <v>4.839827296150074</v>
+        <v>4.839827765870266</v>
       </c>
       <c r="E569" t="n">
-        <v>4.995654695599249</v>
+        <v>4.995655180442972</v>
       </c>
       <c r="F569" t="n">
         <v>2231300</v>
@@ -11892,16 +11892,16 @@
         <v>44623</v>
       </c>
       <c r="B574" t="n">
-        <v>4.629002094268799</v>
+        <v>4.629001617431641</v>
       </c>
       <c r="C574" t="n">
-        <v>4.913158595288829</v>
+        <v>4.913158089180485</v>
       </c>
       <c r="D574" t="n">
-        <v>4.629002094268799</v>
+        <v>4.629001617431641</v>
       </c>
       <c r="E574" t="n">
-        <v>4.64733475765444</v>
+        <v>4.64733427892882</v>
       </c>
       <c r="F574" t="n">
         <v>2116200</v>
@@ -11912,16 +11912,16 @@
         <v>44624</v>
       </c>
       <c r="B575" t="n">
-        <v>4.500673294067383</v>
+        <v>4.500672817230225</v>
       </c>
       <c r="C575" t="n">
-        <v>4.656501161102621</v>
+        <v>4.656500667755819</v>
       </c>
       <c r="D575" t="n">
-        <v>4.436509186760072</v>
+        <v>4.43650871672097</v>
       </c>
       <c r="E575" t="n">
-        <v>4.629002382852403</v>
+        <v>4.629001892419039</v>
       </c>
       <c r="F575" t="n">
         <v>2782800</v>
@@ -12092,16 +12092,16 @@
         <v>44637</v>
       </c>
       <c r="B584" t="n">
-        <v>4.555671215057373</v>
+        <v>4.555670738220215</v>
       </c>
       <c r="C584" t="n">
-        <v>4.583170429954586</v>
+        <v>4.583169950239114</v>
       </c>
       <c r="D584" t="n">
-        <v>4.326512693559644</v>
+        <v>4.32651224070826</v>
       </c>
       <c r="E584" t="n">
-        <v>4.4365091160633</v>
+        <v>4.43650865169871</v>
       </c>
       <c r="F584" t="n">
         <v>2229500</v>
@@ -12172,16 +12172,16 @@
         <v>44643</v>
       </c>
       <c r="B588" t="n">
-        <v>4.79399585723877</v>
+        <v>4.793996334075928</v>
       </c>
       <c r="C588" t="n">
-        <v>4.839827732261697</v>
+        <v>4.839828213657545</v>
       </c>
       <c r="D588" t="n">
-        <v>4.574003469047934</v>
+        <v>4.574003924003441</v>
       </c>
       <c r="E588" t="n">
-        <v>4.656500669255141</v>
+        <v>4.656501132416273</v>
       </c>
       <c r="F588" t="n">
         <v>5289000</v>
@@ -12312,16 +12312,16 @@
         <v>44652</v>
       </c>
       <c r="B595" t="n">
-        <v>5.114818096160889</v>
+        <v>5.11481761932373</v>
       </c>
       <c r="C595" t="n">
-        <v>5.133150760276386</v>
+        <v>5.133150281730136</v>
       </c>
       <c r="D595" t="n">
-        <v>4.913158790890416</v>
+        <v>4.913158332853271</v>
       </c>
       <c r="E595" t="n">
-        <v>5.087319318530237</v>
+        <v>5.087318844256697</v>
       </c>
       <c r="F595" t="n">
         <v>7181900</v>
@@ -12332,16 +12332,16 @@
         <v>44655</v>
       </c>
       <c r="B596" t="n">
-        <v>5.114818096160889</v>
+        <v>5.11481761932373</v>
       </c>
       <c r="C596" t="n">
-        <v>5.197315303223222</v>
+        <v>5.197314818695129</v>
       </c>
       <c r="D596" t="n">
-        <v>5.059820103814396</v>
+        <v>5.059819632104515</v>
       </c>
       <c r="E596" t="n">
-        <v>5.14231731087673</v>
+        <v>5.142316831475913</v>
       </c>
       <c r="F596" t="n">
         <v>2303300</v>
@@ -12392,16 +12392,16 @@
         <v>44658</v>
       </c>
       <c r="B599" t="n">
-        <v>4.629002094268799</v>
+        <v>4.629001617431641</v>
       </c>
       <c r="C599" t="n">
-        <v>4.738998074582648</v>
+        <v>4.738997586414717</v>
       </c>
       <c r="D599" t="n">
-        <v>4.509839563719543</v>
+        <v>4.509839099157411</v>
       </c>
       <c r="E599" t="n">
-        <v>4.702332747811365</v>
+        <v>4.702332263420359</v>
       </c>
       <c r="F599" t="n">
         <v>6002200</v>
@@ -12412,16 +12412,16 @@
         <v>44659</v>
       </c>
       <c r="B600" t="n">
-        <v>4.528172016143799</v>
+        <v>4.528172492980957</v>
       </c>
       <c r="C600" t="n">
-        <v>4.619835328801537</v>
+        <v>4.61983581529126</v>
       </c>
       <c r="D600" t="n">
-        <v>4.454841366017608</v>
+        <v>4.454841835132715</v>
       </c>
       <c r="E600" t="n">
-        <v>4.601502666269989</v>
+        <v>4.6015031508292</v>
       </c>
       <c r="F600" t="n">
         <v>3786000</v>
@@ -12472,16 +12472,16 @@
         <v>44664</v>
       </c>
       <c r="B603" t="n">
-        <v>4.482339859008789</v>
+        <v>4.482340335845947</v>
       </c>
       <c r="C603" t="n">
-        <v>4.500672520385886</v>
+        <v>4.500672999173296</v>
       </c>
       <c r="D603" t="n">
-        <v>4.344844680138003</v>
+        <v>4.344845142348245</v>
       </c>
       <c r="E603" t="n">
-        <v>4.4273418748775</v>
+        <v>4.427342345863901</v>
       </c>
       <c r="F603" t="n">
         <v>2309600</v>
@@ -12532,16 +12532,16 @@
         <v>44670</v>
       </c>
       <c r="B606" t="n">
-        <v>4.436509132385254</v>
+        <v>4.436508655548096</v>
       </c>
       <c r="C606" t="n">
-        <v>4.546505118208394</v>
+        <v>4.546504629548838</v>
       </c>
       <c r="D606" t="n">
-        <v>4.39984380377754</v>
+        <v>4.399843330881182</v>
       </c>
       <c r="E606" t="n">
-        <v>4.546505118208394</v>
+        <v>4.546504629548838</v>
       </c>
       <c r="F606" t="n">
         <v>2018200</v>
@@ -12652,16 +12652,16 @@
         <v>44679</v>
       </c>
       <c r="B612" t="n">
-        <v>4.014857292175293</v>
+        <v>4.014856815338135</v>
       </c>
       <c r="C612" t="n">
-        <v>4.033189955912318</v>
+        <v>4.033189476897824</v>
       </c>
       <c r="D612" t="n">
-        <v>3.950692750553112</v>
+        <v>3.950692281336657</v>
       </c>
       <c r="E612" t="n">
-        <v>4.014857292175293</v>
+        <v>4.014856815338135</v>
       </c>
       <c r="F612" t="n">
         <v>2238100</v>
@@ -12672,16 +12672,16 @@
         <v>44680</v>
       </c>
       <c r="B613" t="n">
-        <v>4.014857292175293</v>
+        <v>4.014856815338135</v>
       </c>
       <c r="C613" t="n">
-        <v>4.161518602071499</v>
+        <v>4.16151810781565</v>
       </c>
       <c r="D613" t="n">
-        <v>3.950692750553112</v>
+        <v>3.950692281336657</v>
       </c>
       <c r="E613" t="n">
-        <v>4.060688732975267</v>
+        <v>4.060688250694794</v>
       </c>
       <c r="F613" t="n">
         <v>3551000</v>
@@ -12752,16 +12752,16 @@
         <v>44686</v>
       </c>
       <c r="B617" t="n">
-        <v>3.739866495132446</v>
+        <v>3.739866733551025</v>
       </c>
       <c r="C617" t="n">
-        <v>4.005690309153175</v>
+        <v>4.00569056451817</v>
       </c>
       <c r="D617" t="n">
-        <v>3.730700382796456</v>
+        <v>3.73070062063069</v>
       </c>
       <c r="E617" t="n">
-        <v>4.005690309153175</v>
+        <v>4.00569056451817</v>
       </c>
       <c r="F617" t="n">
         <v>4685400</v>
@@ -12772,16 +12772,16 @@
         <v>44687</v>
       </c>
       <c r="B618" t="n">
-        <v>3.217385292053223</v>
+        <v>3.217385530471802</v>
       </c>
       <c r="C618" t="n">
-        <v>3.694035167304231</v>
+        <v>3.694035441044096</v>
       </c>
       <c r="D618" t="n">
-        <v>3.217385292053223</v>
+        <v>3.217385530471802</v>
       </c>
       <c r="E618" t="n">
-        <v>3.666535955321852</v>
+        <v>3.666536227023938</v>
       </c>
       <c r="F618" t="n">
         <v>15507900</v>
@@ -12812,16 +12812,16 @@
         <v>44691</v>
       </c>
       <c r="B620" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C620" t="n">
-        <v>2.887397154408436</v>
+        <v>2.887397395893507</v>
       </c>
       <c r="D620" t="n">
-        <v>2.694903981642197</v>
+        <v>2.694904207028261</v>
       </c>
       <c r="E620" t="n">
-        <v>2.8140662866378</v>
+        <v>2.814066521989905</v>
       </c>
       <c r="F620" t="n">
         <v>7309900</v>
@@ -12852,16 +12852,16 @@
         <v>44693</v>
       </c>
       <c r="B622" t="n">
-        <v>2.942395210266113</v>
+        <v>2.942394971847534</v>
       </c>
       <c r="C622" t="n">
-        <v>3.024892192580485</v>
+        <v>3.02489194747728</v>
       </c>
       <c r="D622" t="n">
-        <v>2.814066352567845</v>
+        <v>2.814066124547592</v>
       </c>
       <c r="E622" t="n">
-        <v>2.869064559320005</v>
+        <v>2.869064326843316</v>
       </c>
       <c r="F622" t="n">
         <v>3382300</v>
@@ -12872,16 +12872,16 @@
         <v>44694</v>
       </c>
       <c r="B623" t="n">
-        <v>3.043224811553955</v>
+        <v>3.043225049972534</v>
       </c>
       <c r="C623" t="n">
-        <v>3.107389348751661</v>
+        <v>3.10738959219715</v>
       </c>
       <c r="D623" t="n">
-        <v>2.942395167953036</v>
+        <v>2.942395398472212</v>
       </c>
       <c r="E623" t="n">
-        <v>2.969894161662377</v>
+        <v>2.969894394335936</v>
       </c>
       <c r="F623" t="n">
         <v>4357400</v>
@@ -12912,16 +12912,16 @@
         <v>44698</v>
       </c>
       <c r="B625" t="n">
-        <v>3.11655592918396</v>
+        <v>3.116555690765381</v>
       </c>
       <c r="C625" t="n">
-        <v>3.272383572663343</v>
+        <v>3.272383322323847</v>
       </c>
       <c r="D625" t="n">
-        <v>3.107389597214584</v>
+        <v>3.107389359497236</v>
       </c>
       <c r="E625" t="n">
-        <v>3.199052916908339</v>
+        <v>3.199052672178686</v>
       </c>
       <c r="F625" t="n">
         <v>2194700</v>
@@ -12992,16 +12992,16 @@
         <v>44704</v>
       </c>
       <c r="B629" t="n">
-        <v>3.2357177734375</v>
+        <v>3.235718011856079</v>
       </c>
       <c r="C629" t="n">
-        <v>3.263216765339837</v>
+        <v>3.263217005784634</v>
       </c>
       <c r="D629" t="n">
-        <v>2.76823447401265</v>
+        <v>2.768234677985486</v>
       </c>
       <c r="E629" t="n">
-        <v>2.795733465914987</v>
+        <v>2.795733671914041</v>
       </c>
       <c r="F629" t="n">
         <v>11827500</v>
@@ -13112,16 +13112,16 @@
         <v>44712</v>
       </c>
       <c r="B635" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C635" t="n">
-        <v>3.015725790557546</v>
+        <v>3.015726042775277</v>
       </c>
       <c r="D635" t="n">
-        <v>2.804899955484291</v>
+        <v>2.804900190069778</v>
       </c>
       <c r="E635" t="n">
-        <v>2.988226797097023</v>
+        <v>2.988227047014898</v>
       </c>
       <c r="F635" t="n">
         <v>7519800</v>
@@ -13252,16 +13252,16 @@
         <v>44721</v>
       </c>
       <c r="B642" t="n">
-        <v>2.630739450454712</v>
+        <v>2.630739688873291</v>
       </c>
       <c r="C642" t="n">
-        <v>2.704070318376698</v>
+        <v>2.704070563441105</v>
       </c>
       <c r="D642" t="n">
-        <v>2.575741463420153</v>
+        <v>2.575741696854376</v>
       </c>
       <c r="E642" t="n">
-        <v>2.676571324859418</v>
+        <v>2.676571567431647</v>
       </c>
       <c r="F642" t="n">
         <v>4374300</v>
@@ -13292,16 +13292,16 @@
         <v>44725</v>
       </c>
       <c r="B644" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C644" t="n">
-        <v>2.429080238828605</v>
+        <v>2.42907999298842</v>
       </c>
       <c r="D644" t="n">
-        <v>2.282418717049181</v>
+        <v>2.282418486052185</v>
       </c>
       <c r="E644" t="n">
-        <v>2.429080238828605</v>
+        <v>2.42907999298842</v>
       </c>
       <c r="F644" t="n">
         <v>5369000</v>
@@ -13312,16 +13312,16 @@
         <v>44726</v>
       </c>
       <c r="B645" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C645" t="n">
-        <v>2.401580915813275</v>
+        <v>2.401580660851382</v>
       </c>
       <c r="D645" t="n">
-        <v>2.236586957237029</v>
+        <v>2.236586719791586</v>
       </c>
       <c r="E645" t="n">
-        <v>2.374081922717234</v>
+        <v>2.374081670674749</v>
       </c>
       <c r="F645" t="n">
         <v>2610500</v>
@@ -13372,16 +13372,16 @@
         <v>44732</v>
       </c>
       <c r="B648" t="n">
-        <v>2.236586809158325</v>
+        <v>2.236587047576904</v>
       </c>
       <c r="C648" t="n">
-        <v>2.429079966628701</v>
+        <v>2.429080225566915</v>
       </c>
       <c r="D648" t="n">
-        <v>2.236586809158325</v>
+        <v>2.236587047576904</v>
       </c>
       <c r="E648" t="n">
-        <v>2.337416443834802</v>
+        <v>2.337416693001749</v>
       </c>
       <c r="F648" t="n">
         <v>3518000</v>
@@ -13412,16 +13412,16 @@
         <v>44734</v>
       </c>
       <c r="B650" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C650" t="n">
-        <v>2.300751274461124</v>
+        <v>2.300751030203729</v>
       </c>
       <c r="D650" t="n">
-        <v>2.190755302076961</v>
+        <v>2.190755069497199</v>
       </c>
       <c r="E650" t="n">
-        <v>2.236586957237029</v>
+        <v>2.236586719791586</v>
       </c>
       <c r="F650" t="n">
         <v>3144500</v>
@@ -13452,16 +13452,16 @@
         <v>44736</v>
       </c>
       <c r="B652" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C652" t="n">
-        <v>2.355749260653206</v>
+        <v>2.355749010556994</v>
       </c>
       <c r="D652" t="n">
-        <v>2.209087964140989</v>
+        <v>2.209087729614954</v>
       </c>
       <c r="E652" t="n">
-        <v>2.337416598589179</v>
+        <v>2.337416350439239</v>
       </c>
       <c r="F652" t="n">
         <v>3887000</v>
@@ -13472,16 +13472,16 @@
         <v>44739</v>
       </c>
       <c r="B653" t="n">
-        <v>2.163256168365479</v>
+        <v>2.163255929946899</v>
       </c>
       <c r="C653" t="n">
-        <v>2.291585025979039</v>
+        <v>2.291584773416974</v>
       </c>
       <c r="D653" t="n">
-        <v>2.154089837003265</v>
+        <v>2.154089599594934</v>
       </c>
       <c r="E653" t="n">
-        <v>2.273252363254613</v>
+        <v>2.273252112713042</v>
       </c>
       <c r="F653" t="n">
         <v>3063200</v>
@@ -13492,16 +13492,16 @@
         <v>44740</v>
       </c>
       <c r="B654" t="n">
-        <v>2.089925289154053</v>
+        <v>2.089925527572632</v>
       </c>
       <c r="C654" t="n">
-        <v>2.199921472026663</v>
+        <v>2.199921722993602</v>
       </c>
       <c r="D654" t="n">
-        <v>2.080758958793214</v>
+        <v>2.080759196166099</v>
       </c>
       <c r="E654" t="n">
-        <v>2.172422262401595</v>
+        <v>2.172422510231425</v>
       </c>
       <c r="F654" t="n">
         <v>3436800</v>
@@ -13632,16 +13632,16 @@
         <v>44749</v>
       </c>
       <c r="B661" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C661" t="n">
-        <v>2.392414694476813</v>
+        <v>2.392414452347443</v>
       </c>
       <c r="D661" t="n">
-        <v>2.300751379953786</v>
+        <v>2.300751147101395</v>
       </c>
       <c r="E661" t="n">
-        <v>2.337416705762997</v>
+        <v>2.337416469199814</v>
       </c>
       <c r="F661" t="n">
         <v>2762300</v>
@@ -13652,16 +13652,16 @@
         <v>44750</v>
       </c>
       <c r="B662" t="n">
-        <v>2.401581287384033</v>
+        <v>2.401581048965454</v>
       </c>
       <c r="C662" t="n">
-        <v>2.401581287384033</v>
+        <v>2.401581048965454</v>
       </c>
       <c r="D662" t="n">
-        <v>2.300751630431598</v>
+        <v>2.300751402022951</v>
       </c>
       <c r="E662" t="n">
-        <v>2.337416960232484</v>
+        <v>2.337416728183861</v>
       </c>
       <c r="F662" t="n">
         <v>2746100</v>
@@ -13692,16 +13692,16 @@
         <v>44754</v>
       </c>
       <c r="B664" t="n">
-        <v>2.401581287384033</v>
+        <v>2.401581048965454</v>
       </c>
       <c r="C664" t="n">
-        <v>2.447413168177744</v>
+        <v>2.447412925209175</v>
       </c>
       <c r="D664" t="n">
-        <v>2.254919968180492</v>
+        <v>2.254919744321813</v>
       </c>
       <c r="E664" t="n">
-        <v>2.355749625132927</v>
+        <v>2.355749391264316</v>
       </c>
       <c r="F664" t="n">
         <v>5712200</v>
@@ -13752,16 +13752,16 @@
         <v>44757</v>
       </c>
       <c r="B667" t="n">
-        <v>2.163256168365479</v>
+        <v>2.163255929946899</v>
       </c>
       <c r="C667" t="n">
-        <v>2.245753369167974</v>
+        <v>2.245753121657145</v>
       </c>
       <c r="D667" t="n">
-        <v>2.135757174278839</v>
+        <v>2.135756938891002</v>
       </c>
       <c r="E667" t="n">
-        <v>2.227420706443548</v>
+        <v>2.227420460953214</v>
       </c>
       <c r="F667" t="n">
         <v>2806200</v>
@@ -13792,16 +13792,16 @@
         <v>44761</v>
       </c>
       <c r="B669" t="n">
-        <v>2.190755605697632</v>
+        <v>2.190755367279053</v>
       </c>
       <c r="C669" t="n">
-        <v>2.273252596419157</v>
+        <v>2.273252349022482</v>
       </c>
       <c r="D669" t="n">
-        <v>2.154090057945464</v>
+        <v>2.154089823517174</v>
       </c>
       <c r="E669" t="n">
-        <v>2.254919931814374</v>
+        <v>2.254919686412831</v>
       </c>
       <c r="F669" t="n">
         <v>3099000</v>
@@ -13832,16 +13832,16 @@
         <v>44763</v>
       </c>
       <c r="B671" t="n">
-        <v>2.383248329162598</v>
+        <v>2.383248090744019</v>
       </c>
       <c r="C671" t="n">
-        <v>2.474911860925822</v>
+        <v>2.474911613337284</v>
       </c>
       <c r="D671" t="n">
-        <v>2.346583003874339</v>
+        <v>2.346582769123735</v>
       </c>
       <c r="E671" t="n">
-        <v>2.364915666518468</v>
+        <v>2.364915429933876</v>
       </c>
       <c r="F671" t="n">
         <v>3831200</v>
@@ -13872,16 +13872,16 @@
         <v>44767</v>
       </c>
       <c r="B673" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C673" t="n">
-        <v>2.392414694476813</v>
+        <v>2.392414452347443</v>
       </c>
       <c r="D673" t="n">
-        <v>2.254919722692273</v>
+        <v>2.25491949447837</v>
       </c>
       <c r="E673" t="n">
-        <v>2.300751379953786</v>
+        <v>2.300751147101395</v>
       </c>
       <c r="F673" t="n">
         <v>3311300</v>
@@ -13912,16 +13912,16 @@
         <v>44769</v>
       </c>
       <c r="B675" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242807388306</v>
       </c>
       <c r="C675" t="n">
-        <v>2.603240558142417</v>
+        <v>2.603240801706716</v>
       </c>
       <c r="D675" t="n">
-        <v>2.419913927566782</v>
+        <v>2.419914153978682</v>
       </c>
       <c r="E675" t="n">
-        <v>2.502410911325818</v>
+        <v>2.502411145456297</v>
       </c>
       <c r="F675" t="n">
         <v>5961800</v>
@@ -13932,16 +13932,16 @@
         <v>44770</v>
       </c>
       <c r="B676" t="n">
-        <v>2.557409048080444</v>
+        <v>2.557408809661865</v>
       </c>
       <c r="C676" t="n">
-        <v>2.603240708369188</v>
+        <v>2.603240465677878</v>
       </c>
       <c r="D676" t="n">
-        <v>2.484078391618454</v>
+        <v>2.484078160036244</v>
       </c>
       <c r="E676" t="n">
-        <v>2.566575380138193</v>
+        <v>2.566575140865068</v>
       </c>
       <c r="F676" t="n">
         <v>2881100</v>
@@ -14052,16 +14052,16 @@
         <v>44778</v>
       </c>
       <c r="B682" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232889175415</v>
       </c>
       <c r="C682" t="n">
-        <v>2.969894169468031</v>
+        <v>2.969894420271998</v>
       </c>
       <c r="D682" t="n">
-        <v>2.731569338151449</v>
+        <v>2.731569568829172</v>
       </c>
       <c r="E682" t="n">
-        <v>2.869064525602105</v>
+        <v>2.869064767891131</v>
       </c>
       <c r="F682" t="n">
         <v>6497600</v>
@@ -14192,16 +14192,16 @@
         <v>44789</v>
       </c>
       <c r="B689" t="n">
-        <v>3.327381610870361</v>
+        <v>3.32738184928894</v>
       </c>
       <c r="C689" t="n">
-        <v>3.602371774266797</v>
+        <v>3.602372032389388</v>
       </c>
       <c r="D689" t="n">
-        <v>3.309048729337523</v>
+        <v>3.309048966442487</v>
       </c>
       <c r="E689" t="n">
-        <v>3.538207235258316</v>
+        <v>3.538207488783292</v>
       </c>
       <c r="F689" t="n">
         <v>21092800</v>
@@ -14272,16 +14272,16 @@
         <v>44795</v>
       </c>
       <c r="B693" t="n">
-        <v>2.740735530853271</v>
+        <v>2.740735769271851</v>
       </c>
       <c r="C693" t="n">
-        <v>2.786567184838932</v>
+        <v>2.78656742724444</v>
       </c>
       <c r="D693" t="n">
-        <v>2.694903876867611</v>
+        <v>2.694904111299261</v>
       </c>
       <c r="E693" t="n">
-        <v>2.786567184838932</v>
+        <v>2.78656742724444</v>
       </c>
       <c r="F693" t="n">
         <v>4672100</v>
@@ -14512,16 +14512,16 @@
         <v>44812</v>
       </c>
       <c r="B705" t="n">
-        <v>3.162387371063232</v>
+        <v>3.162387132644653</v>
       </c>
       <c r="C705" t="n">
-        <v>3.272383347114264</v>
+        <v>3.272383100402872</v>
       </c>
       <c r="D705" t="n">
-        <v>3.098223051700131</v>
+        <v>3.098222818119026</v>
       </c>
       <c r="E705" t="n">
-        <v>3.171553702400819</v>
+        <v>3.171553463291171</v>
       </c>
       <c r="F705" t="n">
         <v>3894000</v>
@@ -14612,16 +14612,16 @@
         <v>44819</v>
       </c>
       <c r="B710" t="n">
-        <v>2.896563768386841</v>
+        <v>2.896563529968262</v>
       </c>
       <c r="C710" t="n">
-        <v>3.153221284288065</v>
+        <v>3.153221024743792</v>
       </c>
       <c r="D710" t="n">
-        <v>2.869064772241273</v>
+        <v>2.869064536086159</v>
       </c>
       <c r="E710" t="n">
-        <v>3.125722288142498</v>
+        <v>3.12572203086169</v>
       </c>
       <c r="F710" t="n">
         <v>9085600</v>
@@ -14712,16 +14712,16 @@
         <v>44826</v>
       </c>
       <c r="B715" t="n">
-        <v>3.199052572250366</v>
+        <v>3.199052810668945</v>
       </c>
       <c r="C715" t="n">
-        <v>3.199052572250366</v>
+        <v>3.199052810668945</v>
       </c>
       <c r="D715" t="n">
-        <v>3.02489206505326</v>
+        <v>3.024892290492027</v>
       </c>
       <c r="E715" t="n">
-        <v>3.061557388980531</v>
+        <v>3.061557617151887</v>
       </c>
       <c r="F715" t="n">
         <v>6046200</v>
@@ -14732,16 +14732,16 @@
         <v>44827</v>
       </c>
       <c r="B716" t="n">
-        <v>3.134888410568237</v>
+        <v>3.134888172149658</v>
       </c>
       <c r="C716" t="n">
-        <v>3.25405071923092</v>
+        <v>3.254050471749655</v>
       </c>
       <c r="D716" t="n">
-        <v>3.098223084825873</v>
+        <v>3.098222849195813</v>
       </c>
       <c r="E716" t="n">
-        <v>3.098223084825873</v>
+        <v>3.098222849195813</v>
       </c>
       <c r="F716" t="n">
         <v>4782400</v>
@@ -14772,16 +14772,16 @@
         <v>44831</v>
       </c>
       <c r="B718" t="n">
-        <v>2.896563768386841</v>
+        <v>2.896563529968262</v>
       </c>
       <c r="C718" t="n">
-        <v>3.13488862019102</v>
+        <v>3.134888362155724</v>
       </c>
       <c r="D718" t="n">
-        <v>2.869064772241273</v>
+        <v>2.869064536086159</v>
       </c>
       <c r="E718" t="n">
-        <v>3.061557745260246</v>
+        <v>3.061557493260875</v>
       </c>
       <c r="F718" t="n">
         <v>4940800</v>
@@ -14792,16 +14792,16 @@
         <v>44832</v>
       </c>
       <c r="B719" t="n">
-        <v>2.942395210266113</v>
+        <v>2.942394971847534</v>
       </c>
       <c r="C719" t="n">
-        <v>2.96072787300264</v>
+        <v>2.960727633098589</v>
       </c>
       <c r="D719" t="n">
-        <v>2.841565346672636</v>
+        <v>2.841565116424174</v>
       </c>
       <c r="E719" t="n">
-        <v>2.896563553424795</v>
+        <v>2.896563318719898</v>
       </c>
       <c r="F719" t="n">
         <v>3561500</v>
@@ -14812,16 +14812,16 @@
         <v>44833</v>
       </c>
       <c r="B720" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232889175415</v>
       </c>
       <c r="C720" t="n">
-        <v>2.90572985064426</v>
+        <v>2.905730096029628</v>
       </c>
       <c r="D720" t="n">
-        <v>2.79573365697522</v>
+        <v>2.795733893071542</v>
       </c>
       <c r="E720" t="n">
-        <v>2.896563519383722</v>
+        <v>2.896563763995004</v>
       </c>
       <c r="F720" t="n">
         <v>3966200</v>
@@ -14952,16 +14952,16 @@
         <v>44844</v>
       </c>
       <c r="B727" t="n">
-        <v>3.336548089981079</v>
+        <v>3.3365478515625</v>
       </c>
       <c r="C727" t="n">
-        <v>3.492375732292391</v>
+        <v>3.492375482738889</v>
       </c>
       <c r="D727" t="n">
-        <v>3.327381758080413</v>
+        <v>3.32738152031683</v>
       </c>
       <c r="E727" t="n">
-        <v>3.47404306849106</v>
+        <v>3.474042820247549</v>
       </c>
       <c r="F727" t="n">
         <v>2994400</v>
@@ -15012,16 +15012,16 @@
         <v>44848</v>
       </c>
       <c r="B730" t="n">
-        <v>3.052391290664673</v>
+        <v>3.052391052246094</v>
       </c>
       <c r="C730" t="n">
-        <v>3.199052816095478</v>
+        <v>3.199052566221344</v>
       </c>
       <c r="D730" t="n">
-        <v>2.997393300581591</v>
+        <v>2.997393066458838</v>
       </c>
       <c r="E730" t="n">
-        <v>3.153221157692909</v>
+        <v>3.153220911398631</v>
       </c>
       <c r="F730" t="n">
         <v>2652600</v>
@@ -15152,16 +15152,16 @@
         <v>44859</v>
       </c>
       <c r="B737" t="n">
-        <v>2.740735530853271</v>
+        <v>2.740735769271851</v>
       </c>
       <c r="C737" t="n">
-        <v>2.859897831215989</v>
+        <v>2.859898080000583</v>
       </c>
       <c r="D737" t="n">
-        <v>2.722402869259008</v>
+        <v>2.722403106082815</v>
       </c>
       <c r="E737" t="n">
-        <v>2.740735530853271</v>
+        <v>2.740735769271851</v>
       </c>
       <c r="F737" t="n">
         <v>5037400</v>
@@ -15192,16 +15192,16 @@
         <v>44861</v>
       </c>
       <c r="B739" t="n">
-        <v>2.557409048080444</v>
+        <v>2.557408809661865</v>
       </c>
       <c r="C739" t="n">
-        <v>2.594074376311439</v>
+        <v>2.594074134474676</v>
       </c>
       <c r="D739" t="n">
-        <v>2.465745727502957</v>
+        <v>2.465745497629838</v>
       </c>
       <c r="E739" t="n">
-        <v>2.502411055733952</v>
+        <v>2.502410822442649</v>
       </c>
       <c r="F739" t="n">
         <v>6199000</v>
@@ -15332,16 +15332,16 @@
         <v>44873</v>
       </c>
       <c r="B746" t="n">
-        <v>2.594074249267578</v>
+        <v>2.594074010848999</v>
       </c>
       <c r="C746" t="n">
-        <v>2.694904115507303</v>
+        <v>2.694903867821559</v>
       </c>
       <c r="D746" t="n">
-        <v>2.575741586049916</v>
+        <v>2.575741349316273</v>
       </c>
       <c r="E746" t="n">
-        <v>2.621573244094071</v>
+        <v>2.621573003148089</v>
       </c>
       <c r="F746" t="n">
         <v>5184300</v>
@@ -15392,16 +15392,16 @@
         <v>44876</v>
       </c>
       <c r="B749" t="n">
-        <v>2.245753288269043</v>
+        <v>2.245753049850464</v>
       </c>
       <c r="C749" t="n">
-        <v>2.429080127451886</v>
+        <v>2.429079869570562</v>
       </c>
       <c r="D749" t="n">
-        <v>2.227420626205016</v>
+        <v>2.227420389732709</v>
       </c>
       <c r="E749" t="n">
-        <v>2.319083936525152</v>
+        <v>2.319083690321484</v>
       </c>
       <c r="F749" t="n">
         <v>8256600</v>
@@ -15412,16 +15412,16 @@
         <v>44879</v>
       </c>
       <c r="B750" t="n">
-        <v>2.264086008071899</v>
+        <v>2.264086246490479</v>
       </c>
       <c r="C750" t="n">
-        <v>2.346582989463864</v>
+        <v>2.346583236569752</v>
       </c>
       <c r="D750" t="n">
-        <v>2.199921689211483</v>
+        <v>2.199921920873266</v>
       </c>
       <c r="E750" t="n">
-        <v>2.273252339337673</v>
+        <v>2.273252578721509</v>
       </c>
       <c r="F750" t="n">
         <v>5681600</v>
@@ -15432,16 +15432,16 @@
         <v>44881</v>
       </c>
       <c r="B751" t="n">
-        <v>2.190755605697632</v>
+        <v>2.190755367279053</v>
       </c>
       <c r="C751" t="n">
-        <v>2.282418928721549</v>
+        <v>2.282418680327307</v>
       </c>
       <c r="D751" t="n">
-        <v>2.172422722550248</v>
+        <v>2.172422486126825</v>
       </c>
       <c r="E751" t="n">
-        <v>2.273252596419157</v>
+        <v>2.273252349022482</v>
       </c>
       <c r="F751" t="n">
         <v>6245900</v>
@@ -15552,16 +15552,16 @@
         <v>44889</v>
       </c>
       <c r="B757" t="n">
-        <v>2.236586809158325</v>
+        <v>2.236587047576904</v>
       </c>
       <c r="C757" t="n">
-        <v>2.254919470008594</v>
+        <v>2.254919710381422</v>
       </c>
       <c r="D757" t="n">
-        <v>2.154089616789561</v>
+        <v>2.154089846413997</v>
       </c>
       <c r="E757" t="n">
-        <v>2.163255947214695</v>
+        <v>2.163256177816256</v>
       </c>
       <c r="F757" t="n">
         <v>2756200</v>
@@ -15592,16 +15592,16 @@
         <v>44893</v>
       </c>
       <c r="B759" t="n">
-        <v>2.04409384727478</v>
+        <v>2.044094085693359</v>
       </c>
       <c r="C759" t="n">
-        <v>2.144923491599029</v>
+        <v>2.144923741778154</v>
       </c>
       <c r="D759" t="n">
-        <v>2.034927515972576</v>
+        <v>2.034927753322014</v>
       </c>
       <c r="E759" t="n">
-        <v>2.135757160296825</v>
+        <v>2.135757409406809</v>
       </c>
       <c r="F759" t="n">
         <v>2781000</v>
@@ -15712,16 +15712,16 @@
         <v>44901</v>
       </c>
       <c r="B765" t="n">
-        <v>2.190755605697632</v>
+        <v>2.190755367279053</v>
       </c>
       <c r="C765" t="n">
-        <v>2.199921938000024</v>
+        <v>2.199921698583878</v>
       </c>
       <c r="D765" t="n">
-        <v>2.108258396433505</v>
+        <v>2.108258166993047</v>
       </c>
       <c r="E765" t="n">
-        <v>2.117424728735897</v>
+        <v>2.117424498297872</v>
       </c>
       <c r="F765" t="n">
         <v>4038200</v>
@@ -15872,16 +15872,16 @@
         <v>44911</v>
       </c>
       <c r="B773" t="n">
-        <v>1.787436246871948</v>
+        <v>1.787436366081238</v>
       </c>
       <c r="C773" t="n">
-        <v>1.943263869820843</v>
+        <v>1.943263999422727</v>
       </c>
       <c r="D773" t="n">
-        <v>1.750770814553868</v>
+        <v>1.750770931317833</v>
       </c>
       <c r="E773" t="n">
-        <v>1.915764877535744</v>
+        <v>1.91576500530364</v>
       </c>
       <c r="F773" t="n">
         <v>8751900</v>
@@ -15932,16 +15932,16 @@
         <v>44916</v>
       </c>
       <c r="B776" t="n">
-        <v>1.970763325691223</v>
+        <v>1.970763087272644</v>
       </c>
       <c r="C776" t="n">
-        <v>2.108258304212705</v>
+        <v>2.108258049160288</v>
       </c>
       <c r="D776" t="n">
-        <v>1.961596993789791</v>
+        <v>1.961596756480134</v>
       </c>
       <c r="E776" t="n">
-        <v>2.053260312804112</v>
+        <v>2.05326006440523</v>
       </c>
       <c r="F776" t="n">
         <v>5125400</v>
@@ -16012,16 +16012,16 @@
         <v>44922</v>
       </c>
       <c r="B780" t="n">
-        <v>1.970763325691223</v>
+        <v>1.970763087272644</v>
       </c>
       <c r="C780" t="n">
-        <v>2.062426644705544</v>
+        <v>2.06242639519774</v>
       </c>
       <c r="D780" t="n">
-        <v>1.934097779542904</v>
+        <v>1.934097545560041</v>
       </c>
       <c r="E780" t="n">
-        <v>2.007428653296952</v>
+        <v>2.007428410442682</v>
       </c>
       <c r="F780" t="n">
         <v>3370000</v>
@@ -16092,16 +16092,16 @@
         <v>44929</v>
       </c>
       <c r="B784" t="n">
-        <v>1.943264007568359</v>
+        <v>1.94326388835907</v>
       </c>
       <c r="C784" t="n">
-        <v>2.07159286587126</v>
+        <v>2.071592738789653</v>
       </c>
       <c r="D784" t="n">
-        <v>1.943264007568359</v>
+        <v>1.94326388835907</v>
       </c>
       <c r="E784" t="n">
-        <v>2.007428545991099</v>
+        <v>2.007428422845644</v>
       </c>
       <c r="F784" t="n">
         <v>3677800</v>
@@ -16172,16 +16172,16 @@
         <v>44935</v>
       </c>
       <c r="B788" t="n">
-        <v>2.163256168365479</v>
+        <v>2.163255929946899</v>
       </c>
       <c r="C788" t="n">
-        <v>2.190755380994696</v>
+        <v>2.190755139545351</v>
       </c>
       <c r="D788" t="n">
-        <v>2.071592854743348</v>
+        <v>2.071592626427242</v>
       </c>
       <c r="E788" t="n">
-        <v>2.135757174278839</v>
+        <v>2.135756938891002</v>
       </c>
       <c r="F788" t="n">
         <v>5355300</v>
@@ -16212,16 +16212,16 @@
         <v>44937</v>
       </c>
       <c r="B790" t="n">
-        <v>2.410747766494751</v>
+        <v>2.410747528076172</v>
       </c>
       <c r="C790" t="n">
-        <v>2.456579427379279</v>
+        <v>2.456579184428032</v>
       </c>
       <c r="D790" t="n">
-        <v>2.282418897475475</v>
+        <v>2.282418671748388</v>
       </c>
       <c r="E790" t="n">
-        <v>2.337416890536908</v>
+        <v>2.33741665937062</v>
       </c>
       <c r="F790" t="n">
         <v>4328400</v>
@@ -16452,16 +16452,16 @@
         <v>44953</v>
       </c>
       <c r="B802" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C802" t="n">
-        <v>2.933228810175975</v>
+        <v>2.933229055494139</v>
       </c>
       <c r="D802" t="n">
-        <v>2.704070312795705</v>
+        <v>2.704070538948388</v>
       </c>
       <c r="E802" t="n">
-        <v>2.731569306256229</v>
+        <v>2.731569534708767</v>
       </c>
       <c r="F802" t="n">
         <v>5877300</v>
@@ -16652,16 +16652,16 @@
         <v>44967</v>
       </c>
       <c r="B812" t="n">
-        <v>2.089925289154053</v>
+        <v>2.089925527572632</v>
       </c>
       <c r="C812" t="n">
-        <v>2.218254132748339</v>
+        <v>2.218254385806667</v>
       </c>
       <c r="D812" t="n">
-        <v>2.062426298071539</v>
+        <v>2.062426533353034</v>
       </c>
       <c r="E812" t="n">
-        <v>2.199921472026663</v>
+        <v>2.199921722993602</v>
       </c>
       <c r="F812" t="n">
         <v>5361500</v>
@@ -16752,16 +16752,16 @@
         <v>44974</v>
       </c>
       <c r="B817" t="n">
-        <v>1.961596846580505</v>
+        <v>1.961597084999084</v>
       </c>
       <c r="C817" t="n">
-        <v>2.09909181478359</v>
+        <v>2.099092069913735</v>
       </c>
       <c r="D817" t="n">
-        <v>1.961596846580505</v>
+        <v>1.961597084999084</v>
       </c>
       <c r="E817" t="n">
-        <v>2.053260158715895</v>
+        <v>2.053260408275518</v>
       </c>
       <c r="F817" t="n">
         <v>5027900</v>
@@ -16792,16 +16792,16 @@
         <v>44980</v>
       </c>
       <c r="B819" t="n">
-        <v>1.869933247566223</v>
+        <v>1.869933366775513</v>
       </c>
       <c r="C819" t="n">
-        <v>1.888265909323338</v>
+        <v>1.888266029701345</v>
       </c>
       <c r="D819" t="n">
-        <v>1.814935262294879</v>
+        <v>1.814935377998017</v>
       </c>
       <c r="E819" t="n">
-        <v>1.851600585809109</v>
+        <v>1.851600703849681</v>
       </c>
       <c r="F819" t="n">
         <v>3707800</v>
@@ -16812,16 +16812,16 @@
         <v>44981</v>
       </c>
       <c r="B820" t="n">
-        <v>1.842434287071228</v>
+        <v>1.842434406280518</v>
       </c>
       <c r="C820" t="n">
-        <v>1.924931266417377</v>
+        <v>1.924931390964391</v>
       </c>
       <c r="D820" t="n">
-        <v>1.842434287071228</v>
+        <v>1.842434406280518</v>
       </c>
       <c r="E820" t="n">
-        <v>1.879099611225072</v>
+        <v>1.879099732806683</v>
       </c>
       <c r="F820" t="n">
         <v>1669300</v>
@@ -16872,16 +16872,16 @@
         <v>44986</v>
       </c>
       <c r="B823" t="n">
-        <v>1.778270125389099</v>
+        <v>1.77827000617981</v>
       </c>
       <c r="C823" t="n">
-        <v>1.906598771155477</v>
+        <v>1.906598643343464</v>
       </c>
       <c r="D823" t="n">
-        <v>1.723272025075071</v>
+        <v>1.72327190955267</v>
       </c>
       <c r="E823" t="n">
-        <v>1.860767111953199</v>
+        <v>1.860766987213587</v>
       </c>
       <c r="F823" t="n">
         <v>4346800</v>
@@ -16972,16 +16972,16 @@
         <v>44993</v>
       </c>
       <c r="B828" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C828" t="n">
-        <v>2.905729816715452</v>
+        <v>2.90573005973376</v>
       </c>
       <c r="D828" t="n">
-        <v>2.694903981642197</v>
+        <v>2.694904207028261</v>
       </c>
       <c r="E828" t="n">
-        <v>2.704070312795705</v>
+        <v>2.704070538948388</v>
       </c>
       <c r="F828" t="n">
         <v>7104000</v>
@@ -17052,16 +17052,16 @@
         <v>44999</v>
       </c>
       <c r="B832" t="n">
-        <v>2.630739450454712</v>
+        <v>2.630739688873291</v>
       </c>
       <c r="C832" t="n">
-        <v>2.878230829195374</v>
+        <v>2.878231090043595</v>
       </c>
       <c r="D832" t="n">
-        <v>2.612406788109859</v>
+        <v>2.612407024866986</v>
       </c>
       <c r="E832" t="n">
-        <v>2.841565285963095</v>
+        <v>2.841565543488392</v>
       </c>
       <c r="F832" t="n">
         <v>4540300</v>
@@ -17192,16 +17192,16 @@
         <v>45008</v>
       </c>
       <c r="B839" t="n">
-        <v>2.383248329162598</v>
+        <v>2.383248090744019</v>
       </c>
       <c r="C839" t="n">
-        <v>2.493244523569952</v>
+        <v>2.493244274147426</v>
       </c>
       <c r="D839" t="n">
-        <v>2.300751347264015</v>
+        <v>2.300751117098379</v>
       </c>
       <c r="E839" t="n">
-        <v>2.484078192247887</v>
+        <v>2.484077943742355</v>
       </c>
       <c r="F839" t="n">
         <v>5291300</v>
@@ -17212,16 +17212,16 @@
         <v>45009</v>
       </c>
       <c r="B840" t="n">
-        <v>2.355749368667603</v>
+        <v>2.355749130249023</v>
       </c>
       <c r="C840" t="n">
-        <v>2.429080238828605</v>
+        <v>2.42907999298842</v>
       </c>
       <c r="D840" t="n">
-        <v>2.209088065430759</v>
+        <v>2.209087841855346</v>
       </c>
       <c r="E840" t="n">
-        <v>2.38324836302451</v>
+        <v>2.383248121822838</v>
       </c>
       <c r="F840" t="n">
         <v>8035300</v>
@@ -17312,16 +17312,16 @@
         <v>45016</v>
       </c>
       <c r="B845" t="n">
-        <v>2.557409048080444</v>
+        <v>2.557408809661865</v>
       </c>
       <c r="C845" t="n">
-        <v>2.69490424748927</v>
+        <v>2.69490399625248</v>
       </c>
       <c r="D845" t="n">
-        <v>2.493244723676203</v>
+        <v>2.493244491239446</v>
       </c>
       <c r="E845" t="n">
-        <v>2.621573372484685</v>
+        <v>2.621573128084284</v>
       </c>
       <c r="F845" t="n">
         <v>2922500</v>
@@ -17352,16 +17352,16 @@
         <v>45020</v>
       </c>
       <c r="B847" t="n">
-        <v>2.429080009460449</v>
+        <v>2.429080247879028</v>
       </c>
       <c r="C847" t="n">
-        <v>2.639905831498566</v>
+        <v>2.63990609061008</v>
       </c>
       <c r="D847" t="n">
-        <v>2.429080009460449</v>
+        <v>2.429080247879028</v>
       </c>
       <c r="E847" t="n">
-        <v>2.59407396002219</v>
+        <v>2.594074214635222</v>
       </c>
       <c r="F847" t="n">
         <v>7258800</v>
@@ -17372,16 +17372,16 @@
         <v>45021</v>
       </c>
       <c r="B848" t="n">
-        <v>2.429080009460449</v>
+        <v>2.429080247879028</v>
       </c>
       <c r="C848" t="n">
-        <v>2.5665749682619</v>
+        <v>2.566575220175857</v>
       </c>
       <c r="D848" t="n">
-        <v>2.374081807397309</v>
+        <v>2.374082040417716</v>
       </c>
       <c r="E848" t="n">
-        <v>2.474911662394266</v>
+        <v>2.474911905311305</v>
       </c>
       <c r="F848" t="n">
         <v>6355900</v>
@@ -17472,16 +17472,16 @@
         <v>45029</v>
       </c>
       <c r="B853" t="n">
-        <v>2.850731611251831</v>
+        <v>2.85073184967041</v>
       </c>
       <c r="C853" t="n">
-        <v>2.960727803636499</v>
+        <v>2.960728051254518</v>
       </c>
       <c r="D853" t="n">
-        <v>2.740735637409736</v>
+        <v>2.740735866628893</v>
       </c>
       <c r="E853" t="n">
-        <v>2.804899955484291</v>
+        <v>2.804900190069778</v>
       </c>
       <c r="F853" t="n">
         <v>4826100</v>
@@ -17572,16 +17572,16 @@
         <v>45036</v>
       </c>
       <c r="B858" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242807388306</v>
       </c>
       <c r="C858" t="n">
-        <v>2.603240558142417</v>
+        <v>2.603240801706716</v>
       </c>
       <c r="D858" t="n">
-        <v>2.419913927566782</v>
+        <v>2.419914153978682</v>
       </c>
       <c r="E858" t="n">
-        <v>2.484078248268254</v>
+        <v>2.484078480683494</v>
       </c>
       <c r="F858" t="n">
         <v>4312900</v>
@@ -17672,16 +17672,16 @@
         <v>45044</v>
       </c>
       <c r="B863" t="n">
-        <v>2.548242568969727</v>
+        <v>2.548242807388306</v>
       </c>
       <c r="C863" t="n">
-        <v>2.62157322119998</v>
+        <v>2.62157346647952</v>
       </c>
       <c r="D863" t="n">
-        <v>2.438246590624346</v>
+        <v>2.438246818751485</v>
       </c>
       <c r="E863" t="n">
-        <v>2.465745585210691</v>
+        <v>2.46574581591069</v>
       </c>
       <c r="F863" t="n">
         <v>4247000</v>
@@ -17732,16 +17732,16 @@
         <v>45050</v>
       </c>
       <c r="B866" t="n">
-        <v>2.823232650756836</v>
+        <v>2.823232889175415</v>
       </c>
       <c r="C866" t="n">
-        <v>2.869064525602105</v>
+        <v>2.869064767891131</v>
       </c>
       <c r="D866" t="n">
-        <v>2.704070344369832</v>
+        <v>2.704070572725299</v>
       </c>
       <c r="E866" t="n">
-        <v>2.72240300689091</v>
+        <v>2.722403236794548</v>
       </c>
       <c r="F866" t="n">
         <v>5400200</v>
@@ -17892,16 +17892,16 @@
         <v>45062</v>
       </c>
       <c r="B874" t="n">
-        <v>3.602371454238892</v>
+        <v>3.602371692657471</v>
       </c>
       <c r="C874" t="n">
-        <v>3.675702318227925</v>
+        <v>3.675702561499818</v>
       </c>
       <c r="D874" t="n">
-        <v>3.529040590249859</v>
+        <v>3.529040823815123</v>
       </c>
       <c r="E874" t="n">
-        <v>3.657369438323745</v>
+        <v>3.657369680382299</v>
       </c>
       <c r="F874" t="n">
         <v>5715400</v>
@@ -17912,16 +17912,16 @@
         <v>45063</v>
       </c>
       <c r="B875" t="n">
-        <v>3.923193693161011</v>
+        <v>3.923194169998169</v>
       </c>
       <c r="C875" t="n">
-        <v>3.923193693161011</v>
+        <v>3.923194169998169</v>
       </c>
       <c r="D875" t="n">
-        <v>3.629870657242615</v>
+        <v>3.62987109842838</v>
       </c>
       <c r="E875" t="n">
-        <v>3.648203319669693</v>
+        <v>3.648203763083666</v>
       </c>
       <c r="F875" t="n">
         <v>6160500</v>
@@ -17972,16 +17972,16 @@
         <v>45068</v>
       </c>
       <c r="B878" t="n">
-        <v>3.923193693161011</v>
+        <v>3.923194169998169</v>
       </c>
       <c r="C878" t="n">
-        <v>3.996524342869322</v>
+        <v>3.996524828619315</v>
       </c>
       <c r="D878" t="n">
-        <v>3.859029156123663</v>
+        <v>3.859029625162064</v>
       </c>
       <c r="E878" t="n">
-        <v>3.904861030733933</v>
+        <v>3.904861505342882</v>
       </c>
       <c r="F878" t="n">
         <v>3483600</v>
@@ -17992,16 +17992,16 @@
         <v>45069</v>
       </c>
       <c r="B879" t="n">
-        <v>3.941526651382446</v>
+        <v>3.941526174545288</v>
       </c>
       <c r="C879" t="n">
-        <v>4.134019839855112</v>
+        <v>4.134019339730554</v>
       </c>
       <c r="D879" t="n">
-        <v>3.87736210952983</v>
+        <v>3.877361640455157</v>
       </c>
       <c r="E879" t="n">
-        <v>3.886528222888671</v>
+        <v>3.886527752705101</v>
       </c>
       <c r="F879" t="n">
         <v>4348000</v>
@@ -18012,16 +18012,16 @@
         <v>45070</v>
       </c>
       <c r="B880" t="n">
-        <v>3.886528015136719</v>
+        <v>3.88652777671814</v>
       </c>
       <c r="C880" t="n">
-        <v>4.069855080450908</v>
+        <v>4.069854830786153</v>
       </c>
       <c r="D880" t="n">
-        <v>3.7765320381993</v>
+        <v>3.776531806528411</v>
       </c>
       <c r="E880" t="n">
-        <v>3.923193777867684</v>
+        <v>3.923193537199848</v>
       </c>
       <c r="F880" t="n">
         <v>3446300</v>
@@ -18072,16 +18072,16 @@
         <v>45075</v>
       </c>
       <c r="B883" t="n">
-        <v>4.143185615539551</v>
+        <v>4.143186092376709</v>
       </c>
       <c r="C883" t="n">
-        <v>4.189017489853952</v>
+        <v>4.189017971965877</v>
       </c>
       <c r="D883" t="n">
-        <v>4.042355754298956</v>
+        <v>4.042356219531656</v>
       </c>
       <c r="E883" t="n">
-        <v>4.179850940157013</v>
+        <v>4.179851421213965</v>
       </c>
       <c r="F883" t="n">
         <v>2372800</v>
@@ -18192,16 +18192,16 @@
         <v>45083</v>
       </c>
       <c r="B889" t="n">
-        <v>4.555671215057373</v>
+        <v>4.555670738220215</v>
       </c>
       <c r="C889" t="n">
-        <v>4.803162400791513</v>
+        <v>4.803161898049721</v>
       </c>
       <c r="D889" t="n">
-        <v>4.537338550820962</v>
+        <v>4.537338075902665</v>
       </c>
       <c r="E889" t="n">
-        <v>4.71149907960946</v>
+        <v>4.711498586461969</v>
       </c>
       <c r="F889" t="n">
         <v>5177300</v>
@@ -18252,16 +18252,16 @@
         <v>45089</v>
       </c>
       <c r="B892" t="n">
-        <v>4.491506576538086</v>
+        <v>4.491506099700928</v>
       </c>
       <c r="C892" t="n">
-        <v>4.647334422624888</v>
+        <v>4.647333929244392</v>
       </c>
       <c r="D892" t="n">
-        <v>4.271514194684618</v>
+        <v>4.271513741202773</v>
       </c>
       <c r="E892" t="n">
-        <v>4.363177942089895</v>
+        <v>4.363177478876643</v>
       </c>
       <c r="F892" t="n">
         <v>6649300</v>
@@ -18372,16 +18372,16 @@
         <v>45097</v>
       </c>
       <c r="B898" t="n">
-        <v>4.821495532989502</v>
+        <v>4.821495056152344</v>
       </c>
       <c r="C898" t="n">
-        <v>4.876493526050936</v>
+        <v>4.876493043774576</v>
       </c>
       <c r="D898" t="n">
-        <v>4.46400792246239</v>
+        <v>4.464007480980108</v>
       </c>
       <c r="E898" t="n">
-        <v>4.519005915523824</v>
+        <v>4.51900546860234</v>
       </c>
       <c r="F898" t="n">
         <v>6059500</v>
@@ -18412,16 +18412,16 @@
         <v>45099</v>
       </c>
       <c r="B900" t="n">
-        <v>4.766496658325195</v>
+        <v>4.766496181488037</v>
       </c>
       <c r="C900" t="n">
-        <v>4.858160408630997</v>
+        <v>4.858159922623858</v>
       </c>
       <c r="D900" t="n">
-        <v>4.592336581748543</v>
+        <v>4.592336122334244</v>
       </c>
       <c r="E900" t="n">
-        <v>4.757330545545708</v>
+        <v>4.757330069625522</v>
       </c>
       <c r="F900" t="n">
         <v>4737400</v>
@@ -18452,16 +18452,16 @@
         <v>45103</v>
       </c>
       <c r="B902" t="n">
-        <v>4.922324180603027</v>
+        <v>4.922324657440186</v>
       </c>
       <c r="C902" t="n">
-        <v>4.968156052695024</v>
+        <v>4.968156533972024</v>
       </c>
       <c r="D902" t="n">
-        <v>4.812328212084386</v>
+        <v>4.812328678265975</v>
       </c>
       <c r="E902" t="n">
-        <v>4.968156052695024</v>
+        <v>4.968156533972024</v>
       </c>
       <c r="F902" t="n">
         <v>2732500</v>
@@ -18512,16 +18512,16 @@
         <v>45106</v>
       </c>
       <c r="B905" t="n">
-        <v>5.041486740112305</v>
+        <v>5.041487216949463</v>
       </c>
       <c r="C905" t="n">
-        <v>5.059819401683853</v>
+        <v>5.059819880254963</v>
       </c>
       <c r="D905" t="n">
-        <v>4.848993575068479</v>
+        <v>4.848994033699125</v>
       </c>
       <c r="E905" t="n">
-        <v>4.885658898211577</v>
+        <v>4.885659360310125</v>
       </c>
       <c r="F905" t="n">
         <v>3617100</v>
@@ -18552,16 +18552,16 @@
         <v>45110</v>
       </c>
       <c r="B907" t="n">
-        <v>4.940657615661621</v>
+        <v>4.940657138824463</v>
       </c>
       <c r="C907" t="n">
-        <v>5.032320937113701</v>
+        <v>5.03232045142985</v>
       </c>
       <c r="D907" t="n">
-        <v>4.830661629919126</v>
+        <v>4.830661163697998</v>
       </c>
       <c r="E907" t="n">
-        <v>4.995655608532869</v>
+        <v>4.995655126387695</v>
       </c>
       <c r="F907" t="n">
         <v>7170100</v>
@@ -18612,16 +18612,16 @@
         <v>45113</v>
       </c>
       <c r="B910" t="n">
-        <v>5.087318897247314</v>
+        <v>5.087319374084473</v>
       </c>
       <c r="C910" t="n">
-        <v>5.224813648184956</v>
+        <v>5.22481413790957</v>
       </c>
       <c r="D910" t="n">
-        <v>5.041487022211331</v>
+        <v>5.041487494752643</v>
       </c>
       <c r="E910" t="n">
-        <v>5.206480985587593</v>
+        <v>5.206481473593878</v>
       </c>
       <c r="F910" t="n">
         <v>3192100</v>
@@ -18632,16 +18632,16 @@
         <v>45114</v>
       </c>
       <c r="B911" t="n">
-        <v>5.261478900909424</v>
+        <v>5.261479377746582</v>
       </c>
       <c r="C911" t="n">
-        <v>5.316477325029131</v>
+        <v>5.316477806850684</v>
       </c>
       <c r="D911" t="n">
-        <v>5.087318827175895</v>
+        <v>5.087319288229279</v>
       </c>
       <c r="E911" t="n">
-        <v>5.1239841518656</v>
+        <v>5.123984616241889</v>
       </c>
       <c r="F911" t="n">
         <v>2906900</v>
@@ -18672,16 +18672,16 @@
         <v>45118</v>
       </c>
       <c r="B913" t="n">
-        <v>5.096485137939453</v>
+        <v>5.096485614776611</v>
       </c>
       <c r="C913" t="n">
-        <v>5.114817800997017</v>
+        <v>5.114818279549415</v>
       </c>
       <c r="D913" t="n">
-        <v>4.858160518191128</v>
+        <v>4.858160972730167</v>
       </c>
       <c r="E913" t="n">
-        <v>5.105651688010817</v>
+        <v>5.105652165705616</v>
       </c>
       <c r="F913" t="n">
         <v>3857700</v>
@@ -18692,16 +18692,16 @@
         <v>45119</v>
       </c>
       <c r="B914" t="n">
-        <v>5.325643539428711</v>
+        <v>5.325643062591553</v>
       </c>
       <c r="C914" t="n">
-        <v>5.573134704356201</v>
+        <v>5.573134205359659</v>
       </c>
       <c r="D914" t="n">
-        <v>5.178982237867281</v>
+        <v>5.178981774161598</v>
       </c>
       <c r="E914" t="n">
-        <v>5.178982237867281</v>
+        <v>5.178981774161598</v>
       </c>
       <c r="F914" t="n">
         <v>7685700</v>
@@ -18712,16 +18712,16 @@
         <v>45120</v>
       </c>
       <c r="B915" t="n">
-        <v>5.096485137939453</v>
+        <v>5.096485614776611</v>
       </c>
       <c r="C915" t="n">
-        <v>5.453972286104523</v>
+        <v>5.453972796388881</v>
       </c>
       <c r="D915" t="n">
-        <v>4.995655272580271</v>
+        <v>4.99565573998359</v>
       </c>
       <c r="E915" t="n">
-        <v>5.334810194772943</v>
+        <v>5.334810693908262</v>
       </c>
       <c r="F915" t="n">
         <v>4692200</v>
@@ -18732,16 +18732,16 @@
         <v>45121</v>
       </c>
       <c r="B916" t="n">
-        <v>4.482339859008789</v>
+        <v>4.482340335845947</v>
       </c>
       <c r="C916" t="n">
-        <v>4.903991507767135</v>
+        <v>4.903992029460144</v>
       </c>
       <c r="D916" t="n">
-        <v>4.381510439977321</v>
+        <v>4.381510906088113</v>
       </c>
       <c r="E916" t="n">
-        <v>4.858160072866955</v>
+        <v>4.858160589684357</v>
       </c>
       <c r="F916" t="n">
         <v>15771400</v>
@@ -18792,16 +18792,16 @@
         <v>45126</v>
       </c>
       <c r="B919" t="n">
-        <v>4.931491374969482</v>
+        <v>4.931490898132324</v>
       </c>
       <c r="C919" t="n">
-        <v>5.013988143607732</v>
+        <v>5.013987658793773</v>
       </c>
       <c r="D919" t="n">
-        <v>4.876493383515589</v>
+        <v>4.876492911996312</v>
       </c>
       <c r="E919" t="n">
-        <v>4.958990152153838</v>
+        <v>4.95898967265776</v>
       </c>
       <c r="F919" t="n">
         <v>2646000</v>
@@ -18832,16 +18832,16 @@
         <v>45128</v>
       </c>
       <c r="B921" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C921" t="n">
-        <v>5.169815198316529</v>
+        <v>5.169815688182035</v>
       </c>
       <c r="D921" t="n">
-        <v>4.85815996201701</v>
+        <v>4.858160422351643</v>
       </c>
       <c r="E921" t="n">
-        <v>4.85815996201701</v>
+        <v>4.858160422351643</v>
       </c>
       <c r="F921" t="n">
         <v>3946200</v>
@@ -18852,16 +18852,16 @@
         <v>45131</v>
       </c>
       <c r="B922" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C922" t="n">
-        <v>5.105651103503303</v>
+        <v>5.105651587288944</v>
       </c>
       <c r="D922" t="n">
-        <v>4.885658734912646</v>
+        <v>4.885659197852923</v>
       </c>
       <c r="E922" t="n">
-        <v>5.068985781585712</v>
+        <v>5.068986261897133</v>
       </c>
       <c r="F922" t="n">
         <v>2320000</v>
@@ -18872,16 +18872,16 @@
         <v>45132</v>
       </c>
       <c r="B923" t="n">
-        <v>5.032320022583008</v>
+        <v>5.032320499420166</v>
       </c>
       <c r="C923" t="n">
-        <v>5.270645052132461</v>
+        <v>5.270645551552092</v>
       </c>
       <c r="D923" t="n">
-        <v>4.995654700665417</v>
+        <v>4.995655174028355</v>
       </c>
       <c r="E923" t="n">
-        <v>5.096484554481348</v>
+        <v>5.096485037398413</v>
       </c>
       <c r="F923" t="n">
         <v>3865600</v>
@@ -18932,16 +18932,16 @@
         <v>45135</v>
       </c>
       <c r="B926" t="n">
-        <v>5.041486740112305</v>
+        <v>5.041487216949463</v>
       </c>
       <c r="C926" t="n">
-        <v>5.087318612583741</v>
+        <v>5.087319093755799</v>
       </c>
       <c r="D926" t="n">
-        <v>4.986488755397659</v>
+        <v>4.986489227032962</v>
       </c>
       <c r="E926" t="n">
-        <v>5.087318612583741</v>
+        <v>5.087319093755799</v>
       </c>
       <c r="F926" t="n">
         <v>1281500</v>
@@ -18952,16 +18952,16 @@
         <v>45138</v>
       </c>
       <c r="B927" t="n">
-        <v>5.224813461303711</v>
+        <v>5.224813938140869</v>
       </c>
       <c r="C927" t="n">
-        <v>5.389807855863602</v>
+        <v>5.389808347758803</v>
       </c>
       <c r="D927" t="n">
-        <v>5.087318715283986</v>
+        <v>5.087319179572829</v>
       </c>
       <c r="E927" t="n">
-        <v>5.087318715283986</v>
+        <v>5.087319179572829</v>
       </c>
       <c r="F927" t="n">
         <v>3571100</v>
@@ -18972,16 +18972,16 @@
         <v>45139</v>
       </c>
       <c r="B928" t="n">
-        <v>5.417306423187256</v>
+        <v>5.417306900024414</v>
       </c>
       <c r="C928" t="n">
-        <v>5.426472972350305</v>
+        <v>5.426473449994312</v>
       </c>
       <c r="D928" t="n">
-        <v>4.99565477755969</v>
+        <v>4.995655217282615</v>
       </c>
       <c r="E928" t="n">
-        <v>5.17898182705457</v>
+        <v>5.17898228291414</v>
       </c>
       <c r="F928" t="n">
         <v>5677300</v>
@@ -19072,16 +19072,16 @@
         <v>45146</v>
       </c>
       <c r="B933" t="n">
-        <v>5.261478900909424</v>
+        <v>5.261479377746582</v>
       </c>
       <c r="C933" t="n">
-        <v>5.389807974408543</v>
+        <v>5.389808462875904</v>
       </c>
       <c r="D933" t="n">
-        <v>5.087318827175895</v>
+        <v>5.087319288229279</v>
       </c>
       <c r="E933" t="n">
-        <v>5.298144662684277</v>
+        <v>5.298145142844379</v>
       </c>
       <c r="F933" t="n">
         <v>3099900</v>
@@ -19092,16 +19092,16 @@
         <v>45147</v>
       </c>
       <c r="B934" t="n">
-        <v>5.224813461303711</v>
+        <v>5.224813938140869</v>
       </c>
       <c r="C934" t="n">
-        <v>5.453971954116771</v>
+        <v>5.45397245186784</v>
       </c>
       <c r="D934" t="n">
-        <v>5.197314686933821</v>
+        <v>5.197315161261333</v>
       </c>
       <c r="E934" t="n">
-        <v>5.26147878518699</v>
+        <v>5.261479265370371</v>
       </c>
       <c r="F934" t="n">
         <v>3345000</v>
@@ -19112,16 +19112,16 @@
         <v>45148</v>
       </c>
       <c r="B935" t="n">
-        <v>5.353142261505127</v>
+        <v>5.353142738342285</v>
       </c>
       <c r="C935" t="n">
-        <v>5.435639017531668</v>
+        <v>5.435639501717318</v>
       </c>
       <c r="D935" t="n">
-        <v>5.298144278459062</v>
+        <v>5.298144750397213</v>
       </c>
       <c r="E935" t="n">
-        <v>5.316476939474417</v>
+        <v>5.31647741304557</v>
       </c>
       <c r="F935" t="n">
         <v>2440700</v>
@@ -19252,16 +19252,16 @@
         <v>45159</v>
       </c>
       <c r="B942" t="n">
-        <v>5.490637302398682</v>
+        <v>5.490636825561523</v>
       </c>
       <c r="C942" t="n">
-        <v>5.701463134206945</v>
+        <v>5.701462639060511</v>
       </c>
       <c r="D942" t="n">
-        <v>5.463138527906596</v>
+        <v>5.463138053457582</v>
       </c>
       <c r="E942" t="n">
-        <v>5.673964359714859</v>
+        <v>5.67396386695657</v>
       </c>
       <c r="F942" t="n">
         <v>3510600</v>
@@ -19292,16 +19292,16 @@
         <v>45161</v>
       </c>
       <c r="B944" t="n">
-        <v>5.939788818359375</v>
+        <v>5.939788341522217</v>
       </c>
       <c r="C944" t="n">
-        <v>6.00395336090469</v>
+        <v>6.0039528789165</v>
       </c>
       <c r="D944" t="n">
-        <v>5.609800429260191</v>
+        <v>5.609799978913996</v>
       </c>
       <c r="E944" t="n">
-        <v>5.683131085263302</v>
+        <v>5.683130629030233</v>
       </c>
       <c r="F944" t="n">
         <v>3142700</v>
@@ -19332,16 +19332,16 @@
         <v>45163</v>
       </c>
       <c r="B946" t="n">
-        <v>5.481471061706543</v>
+        <v>5.481471538543701</v>
       </c>
       <c r="C946" t="n">
-        <v>5.893956166120052</v>
+        <v>5.893956678839589</v>
       </c>
       <c r="D946" t="n">
-        <v>5.481471061706543</v>
+        <v>5.481471538543701</v>
       </c>
       <c r="E946" t="n">
-        <v>5.875623504525787</v>
+        <v>5.875624015650554</v>
       </c>
       <c r="F946" t="n">
         <v>3247600</v>
@@ -19352,16 +19352,16 @@
         <v>45166</v>
       </c>
       <c r="B947" t="n">
-        <v>5.188148498535156</v>
+        <v>5.188148021697998</v>
       </c>
       <c r="C947" t="n">
-        <v>5.5364695367559</v>
+        <v>5.536469027904929</v>
       </c>
       <c r="D947" t="n">
-        <v>5.013987979424784</v>
+        <v>5.013987518594533</v>
       </c>
       <c r="E947" t="n">
-        <v>5.527303423689653</v>
+        <v>5.52730291568113</v>
       </c>
       <c r="F947" t="n">
         <v>7906800</v>
@@ -19392,16 +19392,16 @@
         <v>45168</v>
       </c>
       <c r="B949" t="n">
-        <v>5.041486740112305</v>
+        <v>5.041487216949463</v>
       </c>
       <c r="C949" t="n">
-        <v>5.24314601739934</v>
+        <v>5.243146513309966</v>
       </c>
       <c r="D949" t="n">
-        <v>5.004821416969207</v>
+        <v>5.004821890338462</v>
       </c>
       <c r="E949" t="n">
-        <v>5.224813355827791</v>
+        <v>5.224813850004466</v>
       </c>
       <c r="F949" t="n">
         <v>3032100</v>
@@ -19532,16 +19532,16 @@
         <v>45180</v>
       </c>
       <c r="B956" t="n">
-        <v>4.913157939910889</v>
+        <v>4.913158416748047</v>
       </c>
       <c r="C956" t="n">
-        <v>5.004821244611908</v>
+        <v>5.004821730345273</v>
       </c>
       <c r="D956" t="n">
-        <v>4.82149463520987</v>
+        <v>4.821495103150821</v>
       </c>
       <c r="E956" t="n">
-        <v>4.931490600851093</v>
+        <v>4.931491079467492</v>
       </c>
       <c r="F956" t="n">
         <v>3226700</v>
@@ -19592,16 +19592,16 @@
         <v>45183</v>
       </c>
       <c r="B959" t="n">
-        <v>5.05981969833374</v>
+        <v>5.059819221496582</v>
       </c>
       <c r="C959" t="n">
-        <v>5.188148336858303</v>
+        <v>5.188147847927461</v>
       </c>
       <c r="D959" t="n">
-        <v>4.995655160528882</v>
+        <v>4.995654689738586</v>
       </c>
       <c r="E959" t="n">
-        <v>5.178982224077697</v>
+        <v>5.178981736010669</v>
       </c>
       <c r="F959" t="n">
         <v>3749200</v>
@@ -19752,16 +19752,16 @@
         <v>45195</v>
       </c>
       <c r="B967" t="n">
-        <v>4.491506576538086</v>
+        <v>4.491506099700928</v>
       </c>
       <c r="C967" t="n">
-        <v>4.784829169562522</v>
+        <v>4.784828661585008</v>
       </c>
       <c r="D967" t="n">
-        <v>4.418175928281977</v>
+        <v>4.418175459229907</v>
       </c>
       <c r="E967" t="n">
-        <v>4.574003337283638</v>
+        <v>4.574002851688278</v>
       </c>
       <c r="F967" t="n">
         <v>4192900</v>
@@ -19812,16 +19812,16 @@
         <v>45198</v>
       </c>
       <c r="B970" t="n">
-        <v>5.041486740112305</v>
+        <v>5.041487216949463</v>
       </c>
       <c r="C970" t="n">
-        <v>5.096484724826951</v>
+        <v>5.096485206865964</v>
       </c>
       <c r="D970" t="n">
-        <v>4.885658898211577</v>
+        <v>4.885659360310125</v>
       </c>
       <c r="E970" t="n">
-        <v>4.903991559783125</v>
+        <v>4.903992023615626</v>
       </c>
       <c r="F970" t="n">
         <v>4590500</v>
@@ -20072,16 +20072,16 @@
         <v>45218</v>
       </c>
       <c r="B983" t="n">
-        <v>4.555671215057373</v>
+        <v>4.555670738220215</v>
       </c>
       <c r="C983" t="n">
-        <v>4.693166415373049</v>
+        <v>4.693165924144417</v>
       </c>
       <c r="D983" t="n">
-        <v>4.454841780299711</v>
+        <v>4.45484131401626</v>
       </c>
       <c r="E983" t="n">
-        <v>4.519005886584552</v>
+        <v>4.519005413585114</v>
       </c>
       <c r="F983" t="n">
         <v>3399700</v>
@@ -20132,16 +20132,16 @@
         <v>45223</v>
       </c>
       <c r="B986" t="n">
-        <v>4.711498737335205</v>
+        <v>4.711498260498047</v>
       </c>
       <c r="C986" t="n">
-        <v>4.79399593894851</v>
+        <v>4.793995453762048</v>
       </c>
       <c r="D986" t="n">
-        <v>4.619835422812178</v>
+        <v>4.619834955251998</v>
       </c>
       <c r="E986" t="n">
-        <v>4.683999961520877</v>
+        <v>4.683999487466791</v>
       </c>
       <c r="F986" t="n">
         <v>2628000</v>
@@ -20172,16 +20172,16 @@
         <v>45225</v>
       </c>
       <c r="B988" t="n">
-        <v>4.79399585723877</v>
+        <v>4.793996334075928</v>
       </c>
       <c r="C988" t="n">
-        <v>4.858160394853837</v>
+        <v>4.858160878073153</v>
       </c>
       <c r="D988" t="n">
-        <v>4.601502681478721</v>
+        <v>4.60150313916945</v>
       </c>
       <c r="E988" t="n">
-        <v>4.601502681478721</v>
+        <v>4.60150313916945</v>
       </c>
       <c r="F988" t="n">
         <v>4908400</v>
@@ -20192,16 +20192,16 @@
         <v>45226</v>
       </c>
       <c r="B989" t="n">
-        <v>4.766496658325195</v>
+        <v>4.766496181488037</v>
       </c>
       <c r="C989" t="n">
-        <v>4.977322497275261</v>
+        <v>4.977321999347226</v>
       </c>
       <c r="D989" t="n">
-        <v>4.720665220257449</v>
+        <v>4.720664748005237</v>
       </c>
       <c r="E989" t="n">
-        <v>4.803161983613454</v>
+        <v>4.803161503108321</v>
       </c>
       <c r="F989" t="n">
         <v>2912800</v>
@@ -20212,16 +20212,16 @@
         <v>45229</v>
       </c>
       <c r="B990" t="n">
-        <v>4.528172016143799</v>
+        <v>4.528172492980957</v>
       </c>
       <c r="C990" t="n">
-        <v>4.812328503925364</v>
+        <v>4.812329010685496</v>
       </c>
       <c r="D990" t="n">
-        <v>4.519005466335449</v>
+        <v>4.519005942207328</v>
       </c>
       <c r="E990" t="n">
-        <v>4.775663178862269</v>
+        <v>4.775663681761375</v>
       </c>
       <c r="F990" t="n">
         <v>3890600</v>
@@ -20252,16 +20252,16 @@
         <v>45231</v>
       </c>
       <c r="B992" t="n">
-        <v>4.803162574768066</v>
+        <v>4.803162097930908</v>
       </c>
       <c r="C992" t="n">
-        <v>4.848994455561778</v>
+        <v>4.848993974174629</v>
       </c>
       <c r="D992" t="n">
-        <v>4.656501255564526</v>
+        <v>4.656500793287267</v>
       </c>
       <c r="E992" t="n">
-        <v>4.729831915166296</v>
+        <v>4.729831445609087</v>
       </c>
       <c r="F992" t="n">
         <v>2720700</v>
@@ -20352,16 +20352,16 @@
         <v>45239</v>
       </c>
       <c r="B997" t="n">
-        <v>5.618966579437256</v>
+        <v>5.618966102600098</v>
       </c>
       <c r="C997" t="n">
-        <v>5.728962555604424</v>
+        <v>5.728962069432778</v>
       </c>
       <c r="D997" t="n">
-        <v>5.417306852712293</v>
+        <v>5.417306392988397</v>
       </c>
       <c r="E997" t="n">
-        <v>5.5823012540482</v>
+        <v>5.582300780322537</v>
       </c>
       <c r="F997" t="n">
         <v>3100500</v>
@@ -20412,16 +20412,16 @@
         <v>45244</v>
       </c>
       <c r="B1000" t="n">
-        <v>6.819756984710693</v>
+        <v>6.819757461547852</v>
       </c>
       <c r="C1000" t="n">
-        <v>7.213909445756814</v>
+        <v>7.213909950153098</v>
       </c>
       <c r="D1000" t="n">
-        <v>6.792257772505081</v>
+        <v>6.792258247419494</v>
       </c>
       <c r="E1000" t="n">
-        <v>6.819756984710693</v>
+        <v>6.819757461547852</v>
       </c>
       <c r="F1000" t="n">
         <v>6125600</v>
@@ -20472,16 +20472,16 @@
         <v>45250</v>
       </c>
       <c r="B1003" t="n">
-        <v>7.571397304534912</v>
+        <v>7.571396827697754</v>
       </c>
       <c r="C1003" t="n">
-        <v>7.763890485978015</v>
+        <v>7.763889997017875</v>
       </c>
       <c r="D1003" t="n">
-        <v>7.543897654207089</v>
+        <v>7.543897179101823</v>
       </c>
       <c r="E1003" t="n">
-        <v>7.699725509383425</v>
+        <v>7.699725024464316</v>
       </c>
       <c r="F1003" t="n">
         <v>4266000</v>
@@ -20592,16 +20592,16 @@
         <v>45258</v>
       </c>
       <c r="B1009" t="n">
-        <v>7.113080501556396</v>
+        <v>7.113080024719238</v>
       </c>
       <c r="C1009" t="n">
-        <v>7.223076483641863</v>
+        <v>7.223075999430942</v>
       </c>
       <c r="D1009" t="n">
-        <v>6.874755436619372</v>
+        <v>6.874754975758731</v>
       </c>
       <c r="E1009" t="n">
-        <v>6.948086091343017</v>
+        <v>6.948085625566533</v>
       </c>
       <c r="F1009" t="n">
         <v>3101800</v>
@@ -20632,16 +20632,16 @@
         <v>45260</v>
       </c>
       <c r="B1011" t="n">
-        <v>7.452234745025635</v>
+        <v>7.452234268188477</v>
       </c>
       <c r="C1011" t="n">
-        <v>7.791389230143193</v>
+        <v>7.791388731604965</v>
       </c>
       <c r="D1011" t="n">
-        <v>7.378904092793207</v>
+        <v>7.37890362064817</v>
       </c>
       <c r="E1011" t="n">
-        <v>7.470566970998577</v>
+        <v>7.470566492988416</v>
       </c>
       <c r="F1011" t="n">
         <v>4982900</v>
@@ -20712,16 +20712,16 @@
         <v>45266</v>
       </c>
       <c r="B1015" t="n">
-        <v>7.41556978225708</v>
+        <v>7.415569305419922</v>
       </c>
       <c r="C1015" t="n">
-        <v>7.69056017868781</v>
+        <v>7.690559684168175</v>
       </c>
       <c r="D1015" t="n">
-        <v>7.342239126431601</v>
+        <v>7.342238654309763</v>
       </c>
       <c r="E1015" t="n">
-        <v>7.626395199212737</v>
+        <v>7.626394708819049</v>
       </c>
       <c r="F1015" t="n">
         <v>3863700</v>
@@ -20772,16 +20772,16 @@
         <v>45271</v>
       </c>
       <c r="B1018" t="n">
-        <v>7.672225952148438</v>
+        <v>7.672226905822754</v>
       </c>
       <c r="C1018" t="n">
-        <v>7.892217887352564</v>
+        <v>7.892218868372355</v>
       </c>
       <c r="D1018" t="n">
-        <v>7.62639408043835</v>
+        <v>7.626395028415665</v>
       </c>
       <c r="E1018" t="n">
-        <v>7.699724725506393</v>
+        <v>7.699725682598865</v>
       </c>
       <c r="F1018" t="n">
         <v>2800600</v>
@@ -20852,16 +20852,16 @@
         <v>45275</v>
       </c>
       <c r="B1022" t="n">
-        <v>7.516398429870605</v>
+        <v>7.516398906707764</v>
       </c>
       <c r="C1022" t="n">
-        <v>8.029713841168286</v>
+        <v>8.029714350569959</v>
       </c>
       <c r="D1022" t="n">
-        <v>7.516398429870605</v>
+        <v>7.516398906707764</v>
       </c>
       <c r="E1022" t="n">
-        <v>7.974715417962353</v>
+        <v>7.974715923874949</v>
       </c>
       <c r="F1022" t="n">
         <v>3029100</v>
@@ -20932,16 +20932,16 @@
         <v>45281</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.498066425323486</v>
+        <v>7.498065948486328</v>
       </c>
       <c r="C1026" t="n">
-        <v>7.653894275788911</v>
+        <v>7.653893789041931</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.40640267534254</v>
+        <v>7.406402204334709</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.461401100165169</v>
+        <v>7.461400625659731</v>
       </c>
       <c r="F1026" t="n">
         <v>2110700</v>
@@ -20992,16 +20992,16 @@
         <v>45287</v>
       </c>
       <c r="B1029" t="n">
-        <v>7.232242584228516</v>
+        <v>7.232242107391357</v>
       </c>
       <c r="C1029" t="n">
-        <v>7.3330724528389</v>
+        <v>7.333071969353814</v>
       </c>
       <c r="D1029" t="n">
-        <v>7.140579265985065</v>
+        <v>7.140578795191465</v>
       </c>
       <c r="E1029" t="n">
-        <v>7.195577256931135</v>
+        <v>7.195576782511401</v>
       </c>
       <c r="F1029" t="n">
         <v>1937700</v>
@@ -21072,16 +21072,16 @@
         <v>45295</v>
       </c>
       <c r="B1033" t="n">
-        <v>6.654763221740723</v>
+        <v>6.654763698577881</v>
       </c>
       <c r="C1033" t="n">
-        <v>6.865588627586096</v>
+        <v>6.865589119529635</v>
       </c>
       <c r="D1033" t="n">
-        <v>6.645596671703013</v>
+        <v>6.645597147883356</v>
       </c>
       <c r="E1033" t="n">
-        <v>6.847255964595839</v>
+        <v>6.847256455225779</v>
       </c>
       <c r="F1033" t="n">
         <v>2993800</v>
@@ -21132,16 +21132,16 @@
         <v>45300</v>
       </c>
       <c r="B1036" t="n">
-        <v>7.278074264526367</v>
+        <v>7.278073787689209</v>
       </c>
       <c r="C1036" t="n">
-        <v>7.351405354217717</v>
+        <v>7.351404872576131</v>
       </c>
       <c r="D1036" t="n">
-        <v>6.792258035382652</v>
+        <v>6.792257590374687</v>
       </c>
       <c r="E1036" t="n">
-        <v>6.957252440831732</v>
+        <v>6.957251985013838</v>
       </c>
       <c r="F1036" t="n">
         <v>2899300</v>
@@ -21172,16 +21172,16 @@
         <v>45302</v>
       </c>
       <c r="B1038" t="n">
-        <v>6.847256183624268</v>
+        <v>6.847255706787109</v>
       </c>
       <c r="C1038" t="n">
-        <v>7.213909892243003</v>
+        <v>7.213909389872389</v>
       </c>
       <c r="D1038" t="n">
-        <v>6.819757406801839</v>
+        <v>6.819756931879673</v>
       </c>
       <c r="E1038" t="n">
-        <v>6.993917929322868</v>
+        <v>6.993917442272309</v>
       </c>
       <c r="F1038" t="n">
         <v>2188900</v>
@@ -21252,16 +21252,16 @@
         <v>45308</v>
       </c>
       <c r="B1042" t="n">
-        <v>6.792258262634277</v>
+        <v>6.792257785797119</v>
       </c>
       <c r="C1042" t="n">
-        <v>6.819757476824233</v>
+        <v>6.819756998056547</v>
       </c>
       <c r="D1042" t="n">
-        <v>6.581432410795222</v>
+        <v>6.581431948758679</v>
       </c>
       <c r="E1042" t="n">
-        <v>6.645596952514998</v>
+        <v>6.645596485973909</v>
       </c>
       <c r="F1042" t="n">
         <v>2272700</v>
@@ -21272,16 +21272,16 @@
         <v>45309</v>
       </c>
       <c r="B1043" t="n">
-        <v>6.553933620452881</v>
+        <v>6.553933143615723</v>
       </c>
       <c r="C1043" t="n">
-        <v>6.92975344541705</v>
+        <v>6.929752941236791</v>
       </c>
       <c r="D1043" t="n">
-        <v>6.434771087679059</v>
+        <v>6.434770619511674</v>
       </c>
       <c r="E1043" t="n">
-        <v>6.902254668367817</v>
+        <v>6.902254166188257</v>
       </c>
       <c r="F1043" t="n">
         <v>3364300</v>
@@ -21352,16 +21352,16 @@
         <v>45315</v>
       </c>
       <c r="B1047" t="n">
-        <v>6.874754905700684</v>
+        <v>6.874755382537842</v>
       </c>
       <c r="C1047" t="n">
-        <v>6.957252104436338</v>
+        <v>6.957252586995552</v>
       </c>
       <c r="D1047" t="n">
-        <v>6.75559238243477</v>
+        <v>6.755592851006743</v>
       </c>
       <c r="E1047" t="n">
-        <v>6.801424256640167</v>
+        <v>6.801424728391066</v>
       </c>
       <c r="F1047" t="n">
         <v>1933800</v>
@@ -21432,16 +21432,16 @@
         <v>45321</v>
       </c>
       <c r="B1051" t="n">
-        <v>6.471435546875</v>
+        <v>6.471436023712158</v>
       </c>
       <c r="C1051" t="n">
-        <v>7.498065889150944</v>
+        <v>7.498066441633683</v>
       </c>
       <c r="D1051" t="n">
-        <v>6.398104901802101</v>
+        <v>6.398105373236011</v>
       </c>
       <c r="E1051" t="n">
-        <v>7.296406178115352</v>
+        <v>7.296406715739123</v>
       </c>
       <c r="F1051" t="n">
         <v>8840000</v>
@@ -21492,16 +21492,16 @@
         <v>45324</v>
       </c>
       <c r="B1054" t="n">
-        <v>6.654763221740723</v>
+        <v>6.654763698577881</v>
       </c>
       <c r="C1054" t="n">
-        <v>6.893087840614063</v>
+        <v>6.893088334528017</v>
       </c>
       <c r="D1054" t="n">
-        <v>6.489768817743247</v>
+        <v>6.489769282757977</v>
       </c>
       <c r="E1054" t="n">
-        <v>6.746426536692008</v>
+        <v>6.746427020097165</v>
       </c>
       <c r="F1054" t="n">
         <v>2155700</v>
@@ -21532,16 +21532,16 @@
         <v>45328</v>
       </c>
       <c r="B1056" t="n">
-        <v>6.792258262634277</v>
+        <v>6.792257785797119</v>
       </c>
       <c r="C1056" t="n">
-        <v>6.856422804354053</v>
+        <v>6.856422323012349</v>
       </c>
       <c r="D1056" t="n">
-        <v>6.434771100675943</v>
+        <v>6.434770648935468</v>
       </c>
       <c r="E1056" t="n">
-        <v>6.434771100675943</v>
+        <v>6.434770648935468</v>
       </c>
       <c r="F1056" t="n">
         <v>4148600</v>
@@ -21592,16 +21592,16 @@
         <v>45331</v>
       </c>
       <c r="B1059" t="n">
-        <v>7.488900184631348</v>
+        <v>7.488899707794189</v>
       </c>
       <c r="C1059" t="n">
-        <v>7.864720001560429</v>
+        <v>7.864719500793875</v>
       </c>
       <c r="D1059" t="n">
-        <v>7.406402981077092</v>
+        <v>7.406402509492739</v>
       </c>
       <c r="E1059" t="n">
-        <v>7.461401408170043</v>
+        <v>7.461400933083801</v>
       </c>
       <c r="F1059" t="n">
         <v>5487800</v>
@@ -21692,16 +21692,16 @@
         <v>45342</v>
       </c>
       <c r="B1064" t="n">
-        <v>7.204742908477783</v>
+        <v>7.204743385314941</v>
       </c>
       <c r="C1064" t="n">
-        <v>7.31473887664749</v>
+        <v>7.314739360764598</v>
       </c>
       <c r="D1064" t="n">
-        <v>6.920586438830145</v>
+        <v>6.920586896860753</v>
       </c>
       <c r="E1064" t="n">
-        <v>7.241408231201019</v>
+        <v>7.241408710464827</v>
       </c>
       <c r="F1064" t="n">
         <v>5572100</v>
@@ -21812,16 +21812,16 @@
         <v>45350</v>
       </c>
       <c r="B1070" t="n">
-        <v>8.24053955078125</v>
+        <v>8.240540504455566</v>
       </c>
       <c r="C1070" t="n">
-        <v>8.414700502442388</v>
+        <v>8.414701476272281</v>
       </c>
       <c r="D1070" t="n">
-        <v>8.093878248858385</v>
+        <v>8.093879185559649</v>
       </c>
       <c r="E1070" t="n">
-        <v>8.167208899819817</v>
+        <v>8.167209845007607</v>
       </c>
       <c r="F1070" t="n">
         <v>4318300</v>
@@ -21872,16 +21872,16 @@
         <v>45355</v>
       </c>
       <c r="B1073" t="n">
-        <v>8.763022422790527</v>
+        <v>8.763021469116211</v>
       </c>
       <c r="C1073" t="n">
-        <v>8.946349068838362</v>
+        <v>8.94634809521272</v>
       </c>
       <c r="D1073" t="n">
-        <v>8.561362675052708</v>
+        <v>8.561361743324897</v>
       </c>
       <c r="E1073" t="n">
-        <v>8.937182517993369</v>
+        <v>8.937181545365318</v>
       </c>
       <c r="F1073" t="n">
         <v>6129500</v>
@@ -21892,16 +21892,16 @@
         <v>45356</v>
       </c>
       <c r="B1074" t="n">
-        <v>8.790519714355469</v>
+        <v>8.790520668029785</v>
       </c>
       <c r="C1074" t="n">
-        <v>8.909682232674404</v>
+        <v>8.90968319927654</v>
       </c>
       <c r="D1074" t="n">
-        <v>8.616358774439233</v>
+        <v>8.61635970921901</v>
       </c>
       <c r="E1074" t="n">
-        <v>8.763020940641946</v>
+        <v>8.763021891332949</v>
       </c>
       <c r="F1074" t="n">
         <v>2317900</v>
@@ -21912,16 +21912,16 @@
         <v>45357</v>
       </c>
       <c r="B1075" t="n">
-        <v>8.680524826049805</v>
+        <v>8.680523872375488</v>
       </c>
       <c r="C1075" t="n">
-        <v>8.928015568624422</v>
+        <v>8.928014587759865</v>
       </c>
       <c r="D1075" t="n">
-        <v>8.570528843331045</v>
+        <v>8.570527901741292</v>
       </c>
       <c r="E1075" t="n">
-        <v>8.836352686777305</v>
+        <v>8.836351715983168</v>
       </c>
       <c r="F1075" t="n">
         <v>5652400</v>
@@ -21932,16 +21932,16 @@
         <v>45358</v>
       </c>
       <c r="B1076" t="n">
-        <v>8.918848991394043</v>
+        <v>8.918848037719727</v>
       </c>
       <c r="C1076" t="n">
-        <v>8.983013970081657</v>
+        <v>8.98301300954631</v>
       </c>
       <c r="D1076" t="n">
-        <v>8.61635982128362</v>
+        <v>8.616358899953854</v>
       </c>
       <c r="E1076" t="n">
-        <v>8.634692922100184</v>
+        <v>8.634691998810096</v>
       </c>
       <c r="F1076" t="n">
         <v>3318000</v>
@@ -21952,16 +21952,16 @@
         <v>45359</v>
       </c>
       <c r="B1077" t="n">
-        <v>9.02884578704834</v>
+        <v>9.028844833374023</v>
       </c>
       <c r="C1077" t="n">
-        <v>9.056344563917332</v>
+        <v>9.05634360733845</v>
       </c>
       <c r="D1077" t="n">
-        <v>8.680524741416479</v>
+        <v>8.680523824533669</v>
       </c>
       <c r="E1077" t="n">
-        <v>8.808852949585342</v>
+        <v>8.80885201914783</v>
       </c>
       <c r="F1077" t="n">
         <v>5864900</v>
@@ -21992,16 +21992,16 @@
         <v>45363</v>
       </c>
       <c r="B1079" t="n">
-        <v>8.946347236633301</v>
+        <v>8.946348190307617</v>
       </c>
       <c r="C1079" t="n">
-        <v>8.95551378560099</v>
+        <v>8.955514740252456</v>
       </c>
       <c r="D1079" t="n">
-        <v>8.671356886794161</v>
+        <v>8.671357811154699</v>
       </c>
       <c r="E1079" t="n">
-        <v>8.827184722563999</v>
+        <v>8.827185663535676</v>
       </c>
       <c r="F1079" t="n">
         <v>1534600</v>
@@ -22032,16 +22032,16 @@
         <v>45365</v>
       </c>
       <c r="B1081" t="n">
-        <v>8.918848991394043</v>
+        <v>8.918848037719727</v>
       </c>
       <c r="C1081" t="n">
-        <v>9.221339035674827</v>
+        <v>9.221338049655866</v>
       </c>
       <c r="D1081" t="n">
-        <v>8.827186109822305</v>
+        <v>8.827185165949313</v>
       </c>
       <c r="E1081" t="n">
-        <v>9.120508729524445</v>
+        <v>9.120507754287065</v>
       </c>
       <c r="F1081" t="n">
         <v>5490900</v>
@@ -22052,16 +22052,16 @@
         <v>45366</v>
       </c>
       <c r="B1082" t="n">
-        <v>8.753854751586914</v>
+        <v>8.75385570526123</v>
       </c>
       <c r="C1082" t="n">
-        <v>9.019678572877519</v>
+        <v>9.019679555511575</v>
       </c>
       <c r="D1082" t="n">
-        <v>8.65302445353753</v>
+        <v>8.653025396227054</v>
       </c>
       <c r="E1082" t="n">
-        <v>8.918848274828134</v>
+        <v>8.918849246477398</v>
       </c>
       <c r="F1082" t="n">
         <v>2427800</v>
@@ -22072,16 +22072,16 @@
         <v>45369</v>
       </c>
       <c r="B1083" t="n">
-        <v>8.598026275634766</v>
+        <v>8.598027229309082</v>
       </c>
       <c r="C1083" t="n">
-        <v>8.909681948343119</v>
+        <v>8.909682936585602</v>
       </c>
       <c r="D1083" t="n">
-        <v>8.588859726632702</v>
+        <v>8.588860679290285</v>
       </c>
       <c r="E1083" t="n">
-        <v>8.799685982829034</v>
+        <v>8.799686958871005</v>
       </c>
       <c r="F1083" t="n">
         <v>2840300</v>
@@ -22252,16 +22252,16 @@
         <v>45383</v>
       </c>
       <c r="B1092" t="n">
-        <v>9.881315231323242</v>
+        <v>9.881314277648926</v>
       </c>
       <c r="C1092" t="n">
-        <v>10.1838044106577</v>
+        <v>10.18380342778928</v>
       </c>
       <c r="D1092" t="n">
-        <v>9.642991032633029</v>
+        <v>9.642990101960072</v>
       </c>
       <c r="E1092" t="n">
-        <v>9.807984574161578</v>
+        <v>9.807983627564616</v>
       </c>
       <c r="F1092" t="n">
         <v>5284900</v>
@@ -22272,16 +22272,16 @@
         <v>45384</v>
       </c>
       <c r="B1093" t="n">
-        <v>9.826315879821777</v>
+        <v>9.826316833496094</v>
       </c>
       <c r="C1093" t="n">
-        <v>9.899646523582593</v>
+        <v>9.899647484373874</v>
       </c>
       <c r="D1093" t="n">
-        <v>9.413830790124633</v>
+        <v>9.413831703765997</v>
       </c>
       <c r="E1093" t="n">
-        <v>9.853814652689527</v>
+        <v>9.853815609032683</v>
       </c>
       <c r="F1093" t="n">
         <v>3197600</v>
@@ -22292,16 +22292,16 @@
         <v>45385</v>
       </c>
       <c r="B1094" t="n">
-        <v>10.22963619232178</v>
+        <v>10.22963523864746</v>
       </c>
       <c r="C1094" t="n">
-        <v>10.26630152055277</v>
+        <v>10.26630056346027</v>
       </c>
       <c r="D1094" t="n">
-        <v>9.707155046487504</v>
+        <v>9.707154141522334</v>
       </c>
       <c r="E1094" t="n">
-        <v>9.752986925318842</v>
+        <v>9.752986016080921</v>
       </c>
       <c r="F1094" t="n">
         <v>5215300</v>
@@ -22312,16 +22312,16 @@
         <v>45386</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.98127460479736</v>
+        <v>10.98127365112305</v>
       </c>
       <c r="C1095" t="n">
-        <v>11.18293432413664</v>
+        <v>11.18293335294909</v>
       </c>
       <c r="D1095" t="n">
-        <v>10.43129474410425</v>
+        <v>10.43129383819321</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.43129474410425</v>
+        <v>10.43129383819321</v>
       </c>
       <c r="F1095" t="n">
         <v>7684100</v>
@@ -22372,16 +22372,16 @@
         <v>45391</v>
       </c>
       <c r="B1098" t="n">
-        <v>11.40292644500732</v>
+        <v>11.40292739868164</v>
       </c>
       <c r="C1098" t="n">
-        <v>11.7329152407039</v>
+        <v>11.73291622197656</v>
       </c>
       <c r="D1098" t="n">
-        <v>11.28376479563944</v>
+        <v>11.28376573934777</v>
       </c>
       <c r="E1098" t="n">
-        <v>11.29293047116523</v>
+        <v>11.29293141564012</v>
       </c>
       <c r="F1098" t="n">
         <v>4003300</v>
@@ -22392,16 +22392,16 @@
         <v>45392</v>
       </c>
       <c r="B1099" t="n">
-        <v>10.58712291717529</v>
+        <v>10.58712196350098</v>
       </c>
       <c r="C1099" t="n">
-        <v>11.36626129578913</v>
+        <v>11.36626027193104</v>
       </c>
       <c r="D1099" t="n">
-        <v>10.44962729212322</v>
+        <v>10.44962635083433</v>
       </c>
       <c r="E1099" t="n">
-        <v>11.36626129578913</v>
+        <v>11.36626027193104</v>
       </c>
       <c r="F1099" t="n">
         <v>6473200</v>
@@ -22432,16 +22432,16 @@
         <v>45394</v>
       </c>
       <c r="B1101" t="n">
-        <v>10.08297348022461</v>
+        <v>10.08297443389893</v>
       </c>
       <c r="C1101" t="n">
-        <v>10.50462513345536</v>
+        <v>10.5046261270106</v>
       </c>
       <c r="D1101" t="n">
-        <v>9.991309735281737</v>
+        <v>9.991310680286254</v>
       </c>
       <c r="E1101" t="n">
-        <v>10.50462513345536</v>
+        <v>10.5046261270106</v>
       </c>
       <c r="F1101" t="n">
         <v>3383500</v>
@@ -22472,16 +22472,16 @@
         <v>45398</v>
       </c>
       <c r="B1103" t="n">
-        <v>9.258004188537598</v>
+        <v>9.258003234863281</v>
       </c>
       <c r="C1103" t="n">
-        <v>9.578825579243738</v>
+        <v>9.578824592521357</v>
       </c>
       <c r="D1103" t="n">
-        <v>8.946348473896519</v>
+        <v>8.946347552326104</v>
       </c>
       <c r="E1103" t="n">
-        <v>9.11134200728212</v>
+        <v>9.111341068715591</v>
       </c>
       <c r="F1103" t="n">
         <v>5545500</v>
@@ -22532,16 +22532,16 @@
         <v>45401</v>
       </c>
       <c r="B1106" t="n">
-        <v>9.826315879821777</v>
+        <v>9.826316833496094</v>
       </c>
       <c r="C1106" t="n">
-        <v>10.08297313298463</v>
+        <v>10.08297411156833</v>
       </c>
       <c r="D1106" t="n">
-        <v>9.16633921180421</v>
+        <v>9.166340101425751</v>
       </c>
       <c r="E1106" t="n">
-        <v>9.221337631709936</v>
+        <v>9.221338526669244</v>
       </c>
       <c r="F1106" t="n">
         <v>6611100</v>
@@ -22572,16 +22572,16 @@
         <v>45405</v>
       </c>
       <c r="B1108" t="n">
-        <v>9.862982749938965</v>
+        <v>9.862981796264648</v>
       </c>
       <c r="C1108" t="n">
-        <v>10.05547593857018</v>
+        <v>10.05547496628326</v>
       </c>
       <c r="D1108" t="n">
-        <v>9.67965611175932</v>
+        <v>9.679655175811273</v>
       </c>
       <c r="E1108" t="n">
-        <v>9.872149300390539</v>
+        <v>9.872148345829888</v>
       </c>
       <c r="F1108" t="n">
         <v>2407700</v>
@@ -22632,16 +22632,16 @@
         <v>45408</v>
       </c>
       <c r="B1111" t="n">
-        <v>10.96294212341309</v>
+        <v>10.9629430770874</v>
       </c>
       <c r="C1111" t="n">
-        <v>10.96294212341309</v>
+        <v>10.9629430770874</v>
       </c>
       <c r="D1111" t="n">
-        <v>9.991309747661697</v>
+        <v>9.991310616813005</v>
       </c>
       <c r="E1111" t="n">
-        <v>10.05547471886932</v>
+        <v>10.05547559360238</v>
       </c>
       <c r="F1111" t="n">
         <v>5850400</v>
@@ -22792,16 +22792,16 @@
         <v>45421</v>
       </c>
       <c r="B1119" t="n">
-        <v>11.23793315887451</v>
+        <v>11.2379322052002</v>
       </c>
       <c r="C1119" t="n">
-        <v>11.33876258515184</v>
+        <v>11.33876162292093</v>
       </c>
       <c r="D1119" t="n">
-        <v>10.56878987781135</v>
+        <v>10.56878898092192</v>
       </c>
       <c r="E1119" t="n">
-        <v>11.30209725976278</v>
+        <v>11.30209630064337</v>
       </c>
       <c r="F1119" t="n">
         <v>4225100</v>
@@ -22812,16 +22812,16 @@
         <v>45422</v>
       </c>
       <c r="B1120" t="n">
-        <v>9.377165794372559</v>
+        <v>9.377164840698242</v>
       </c>
       <c r="C1120" t="n">
-        <v>11.49459080796945</v>
+        <v>11.49458963894927</v>
       </c>
       <c r="D1120" t="n">
-        <v>9.349667017984904</v>
+        <v>9.349666067107263</v>
       </c>
       <c r="E1120" t="n">
-        <v>11.4579254813958</v>
+        <v>11.45792431610455</v>
       </c>
       <c r="F1120" t="n">
         <v>14221700</v>
@@ -22832,16 +22832,16 @@
         <v>45425</v>
       </c>
       <c r="B1121" t="n">
-        <v>9.303835868835449</v>
+        <v>9.303834915161133</v>
       </c>
       <c r="C1121" t="n">
-        <v>9.569659725825879</v>
+        <v>9.569658744903728</v>
       </c>
       <c r="D1121" t="n">
-        <v>9.184674203779746</v>
+        <v>9.184673262319901</v>
       </c>
       <c r="E1121" t="n">
-        <v>9.395499629523353</v>
+        <v>9.395498666453195</v>
       </c>
       <c r="F1121" t="n">
         <v>4893500</v>
@@ -22872,16 +22872,16 @@
         <v>45427</v>
       </c>
       <c r="B1123" t="n">
-        <v>9.523826599121094</v>
+        <v>9.52382755279541</v>
       </c>
       <c r="C1123" t="n">
-        <v>9.835481392893451</v>
+        <v>9.835482377775513</v>
       </c>
       <c r="D1123" t="n">
-        <v>9.395497537565268</v>
+        <v>9.395498478389273</v>
       </c>
       <c r="E1123" t="n">
-        <v>9.597157241675792</v>
+        <v>9.597158202693118</v>
       </c>
       <c r="F1123" t="n">
         <v>4359100</v>
@@ -23032,16 +23032,16 @@
         <v>45439</v>
       </c>
       <c r="B1131" t="n">
-        <v>8.808853149414062</v>
+        <v>8.808852195739746</v>
       </c>
       <c r="C1131" t="n">
-        <v>8.836352801077238</v>
+        <v>8.836351844425723</v>
       </c>
       <c r="D1131" t="n">
-        <v>8.625526509178098</v>
+        <v>8.625525575351304</v>
       </c>
       <c r="E1131" t="n">
-        <v>8.680524938334075</v>
+        <v>8.680523998552976</v>
       </c>
       <c r="F1131" t="n">
         <v>1394600</v>
@@ -23072,16 +23072,16 @@
         <v>45441</v>
       </c>
       <c r="B1133" t="n">
-        <v>9.001346588134766</v>
+        <v>9.001345634460449</v>
       </c>
       <c r="C1133" t="n">
-        <v>9.093010347862693</v>
+        <v>9.093009384476789</v>
       </c>
       <c r="D1133" t="n">
-        <v>8.497198532142356</v>
+        <v>8.497197631881498</v>
       </c>
       <c r="E1133" t="n">
-        <v>8.524697310392575</v>
+        <v>8.524696407218277</v>
       </c>
       <c r="F1133" t="n">
         <v>3964600</v>
@@ -23092,16 +23092,16 @@
         <v>45443</v>
       </c>
       <c r="B1134" t="n">
-        <v>8.808853149414062</v>
+        <v>8.808852195739746</v>
       </c>
       <c r="C1134" t="n">
-        <v>9.395499272339524</v>
+        <v>9.395498255153042</v>
       </c>
       <c r="D1134" t="n">
-        <v>8.717190266381268</v>
+        <v>8.717189322630665</v>
       </c>
       <c r="E1134" t="n">
-        <v>9.074676996298805</v>
+        <v>9.074676013845558</v>
       </c>
       <c r="F1134" t="n">
         <v>8270300</v>
@@ -23112,16 +23112,16 @@
         <v>45446</v>
       </c>
       <c r="B1135" t="n">
-        <v>8.763022422790527</v>
+        <v>8.763021469116211</v>
       </c>
       <c r="C1135" t="n">
-        <v>8.946349068838362</v>
+        <v>8.94634809521272</v>
       </c>
       <c r="D1135" t="n">
-        <v>8.524697345843141</v>
+        <v>8.524696418105595</v>
       </c>
       <c r="E1135" t="n">
-        <v>8.790521201155101</v>
+        <v>8.790520244488111</v>
       </c>
       <c r="F1135" t="n">
         <v>5677300</v>
@@ -23152,16 +23152,16 @@
         <v>45448</v>
       </c>
       <c r="B1137" t="n">
-        <v>8.900515556335449</v>
+        <v>8.900516510009766</v>
       </c>
       <c r="C1137" t="n">
-        <v>8.955513977147712</v>
+        <v>8.95551493671501</v>
       </c>
       <c r="D1137" t="n">
-        <v>8.341369169900293</v>
+        <v>8.341370063663074</v>
       </c>
       <c r="E1137" t="n">
-        <v>8.350534844893801</v>
+        <v>8.350535739638667</v>
       </c>
       <c r="F1137" t="n">
         <v>3791100</v>
@@ -23192,16 +23192,16 @@
         <v>45450</v>
       </c>
       <c r="B1139" t="n">
-        <v>8.854683876037598</v>
+        <v>8.854684829711914</v>
       </c>
       <c r="C1139" t="n">
-        <v>9.148006462254413</v>
+        <v>9.148007447520396</v>
       </c>
       <c r="D1139" t="n">
-        <v>8.808852003398655</v>
+        <v>8.80885295213675</v>
       </c>
       <c r="E1139" t="n">
-        <v>8.818018552760496</v>
+        <v>8.818019502485853</v>
       </c>
       <c r="F1139" t="n">
         <v>2125600</v>
@@ -23212,16 +23212,16 @@
         <v>45453</v>
       </c>
       <c r="B1140" t="n">
-        <v>8.854683876037598</v>
+        <v>8.854684829711914</v>
       </c>
       <c r="C1140" t="n">
-        <v>9.074675815700209</v>
+        <v>9.074676793068274</v>
       </c>
       <c r="D1140" t="n">
-        <v>8.781353229483393</v>
+        <v>8.781354175259793</v>
       </c>
       <c r="E1140" t="n">
-        <v>8.937181071953642</v>
+        <v>8.937182034513139</v>
       </c>
       <c r="F1140" t="n">
         <v>1908300</v>
@@ -23232,16 +23232,16 @@
         <v>45454</v>
       </c>
       <c r="B1141" t="n">
-        <v>9.258004188537598</v>
+        <v>9.258003234863281</v>
       </c>
       <c r="C1141" t="n">
-        <v>9.258004188537598</v>
+        <v>9.258003234863281</v>
       </c>
       <c r="D1141" t="n">
-        <v>8.900516596889828</v>
+        <v>8.900515680040591</v>
       </c>
       <c r="E1141" t="n">
-        <v>8.909683147125236</v>
+        <v>8.909682229331745</v>
       </c>
       <c r="F1141" t="n">
         <v>1877100</v>
@@ -23332,16 +23332,16 @@
         <v>45461</v>
       </c>
       <c r="B1146" t="n">
-        <v>8.763022422790527</v>
+        <v>8.763021469116211</v>
       </c>
       <c r="C1146" t="n">
-        <v>8.928015967148378</v>
+        <v>8.928014995517914</v>
       </c>
       <c r="D1146" t="n">
-        <v>8.689690890200991</v>
+        <v>8.689689944507299</v>
       </c>
       <c r="E1146" t="n">
-        <v>8.753855871945534</v>
+        <v>8.753854919268807</v>
       </c>
       <c r="F1146" t="n">
         <v>1101800</v>
@@ -23352,16 +23352,16 @@
         <v>45462</v>
       </c>
       <c r="B1147" t="n">
-        <v>8.598026275634766</v>
+        <v>8.598027229309082</v>
       </c>
       <c r="C1147" t="n">
-        <v>8.763020660991005</v>
+        <v>8.76302163296614</v>
       </c>
       <c r="D1147" t="n">
-        <v>8.54302785579261</v>
+        <v>8.543028803366621</v>
       </c>
       <c r="E1147" t="n">
-        <v>8.662190370308759</v>
+        <v>8.662191331100015</v>
       </c>
       <c r="F1147" t="n">
         <v>1395100</v>
@@ -23412,16 +23412,16 @@
         <v>45467</v>
       </c>
       <c r="B1150" t="n">
-        <v>9.258004188537598</v>
+        <v>9.258003234863281</v>
       </c>
       <c r="C1150" t="n">
-        <v>9.294669515308881</v>
+        <v>9.294668557857641</v>
       </c>
       <c r="D1150" t="n">
-        <v>8.946348473896519</v>
+        <v>8.946347552326104</v>
       </c>
       <c r="E1150" t="n">
-        <v>8.946348473896519</v>
+        <v>8.946347552326104</v>
       </c>
       <c r="F1150" t="n">
         <v>2223300</v>
@@ -23432,16 +23432,16 @@
         <v>45468</v>
       </c>
       <c r="B1151" t="n">
-        <v>9.111342430114746</v>
+        <v>9.11134147644043</v>
       </c>
       <c r="C1151" t="n">
-        <v>9.340500951612476</v>
+        <v>9.340499973952385</v>
       </c>
       <c r="D1151" t="n">
-        <v>9.102176753624331</v>
+        <v>9.102175800909375</v>
       </c>
       <c r="E1151" t="n">
-        <v>9.166340859909171</v>
+        <v>9.166339900478228</v>
       </c>
       <c r="F1151" t="n">
         <v>1250500</v>
@@ -23472,16 +23472,16 @@
         <v>45470</v>
       </c>
       <c r="B1153" t="n">
-        <v>9.001346588134766</v>
+        <v>9.001345634460449</v>
       </c>
       <c r="C1153" t="n">
-        <v>9.019679689748511</v>
+        <v>9.019678734131839</v>
       </c>
       <c r="D1153" t="n">
-        <v>8.799687715405961</v>
+        <v>8.799686783096991</v>
       </c>
       <c r="E1153" t="n">
-        <v>8.836353044463053</v>
+        <v>8.836352108269466</v>
       </c>
       <c r="F1153" t="n">
         <v>1939500</v>
@@ -23532,16 +23532,16 @@
         <v>45475</v>
       </c>
       <c r="B1156" t="n">
-        <v>8.414700508117676</v>
+        <v>8.414699554443359</v>
       </c>
       <c r="C1156" t="n">
-        <v>8.836352188515454</v>
+        <v>8.836351187053534</v>
       </c>
       <c r="D1156" t="n">
-        <v>8.387200858360856</v>
+        <v>8.387199907803193</v>
       </c>
       <c r="E1156" t="n">
-        <v>8.588860585725962</v>
+        <v>8.588859612313334</v>
       </c>
       <c r="F1156" t="n">
         <v>3229800</v>
@@ -23632,16 +23632,16 @@
         <v>45482</v>
       </c>
       <c r="B1161" t="n">
-        <v>9.111342430114746</v>
+        <v>9.11134147644043</v>
       </c>
       <c r="C1161" t="n">
-        <v>9.230504966194012</v>
+        <v>9.230504000047082</v>
       </c>
       <c r="D1161" t="n">
-        <v>9.001346444696283</v>
+        <v>9.001345502535127</v>
       </c>
       <c r="E1161" t="n">
-        <v>9.038011773169105</v>
+        <v>9.038010827170227</v>
       </c>
       <c r="F1161" t="n">
         <v>1530600</v>
@@ -23672,16 +23672,16 @@
         <v>45484</v>
       </c>
       <c r="B1163" t="n">
-        <v>10.08297348022461</v>
+        <v>10.08297443389893</v>
       </c>
       <c r="C1163" t="n">
-        <v>10.08297348022461</v>
+        <v>10.08297443389893</v>
       </c>
       <c r="D1163" t="n">
-        <v>9.624656503850764</v>
+        <v>9.624657414176248</v>
       </c>
       <c r="E1163" t="n">
-        <v>9.624656503850764</v>
+        <v>9.624657414176248</v>
       </c>
       <c r="F1163" t="n">
         <v>2671800</v>
@@ -23732,16 +23732,16 @@
         <v>45489</v>
       </c>
       <c r="B1166" t="n">
-        <v>9.303835868835449</v>
+        <v>9.303834915161133</v>
       </c>
       <c r="C1166" t="n">
-        <v>9.789652576642766</v>
+        <v>9.789651573170611</v>
       </c>
       <c r="D1166" t="n">
-        <v>9.258004862661906</v>
+        <v>9.258003913685421</v>
       </c>
       <c r="E1166" t="n">
-        <v>9.743820696298814</v>
+        <v>9.743819697524581</v>
       </c>
       <c r="F1166" t="n">
         <v>1952400</v>
@@ -23792,16 +23792,16 @@
         <v>45492</v>
       </c>
       <c r="B1169" t="n">
-        <v>8.524696350097656</v>
+        <v>8.524697303771973</v>
       </c>
       <c r="C1169" t="n">
-        <v>8.662191100030562</v>
+        <v>8.662192069086682</v>
       </c>
       <c r="D1169" t="n">
-        <v>8.433032600695519</v>
+        <v>8.433033544115233</v>
       </c>
       <c r="E1169" t="n">
-        <v>8.524696350097656</v>
+        <v>8.524697303771973</v>
       </c>
       <c r="F1169" t="n">
         <v>1837700</v>
@@ -23832,16 +23832,16 @@
         <v>45496</v>
       </c>
       <c r="B1171" t="n">
-        <v>8.176375389099121</v>
+        <v>8.176376342773438</v>
       </c>
       <c r="C1171" t="n">
-        <v>8.607193615930459</v>
+        <v>8.607194619854459</v>
       </c>
       <c r="D1171" t="n">
-        <v>8.176375389099121</v>
+        <v>8.176376342773438</v>
       </c>
       <c r="E1171" t="n">
-        <v>8.607193615930459</v>
+        <v>8.607194619854459</v>
       </c>
       <c r="F1171" t="n">
         <v>3005900</v>
@@ -23852,16 +23852,16 @@
         <v>45497</v>
       </c>
       <c r="B1172" t="n">
-        <v>7.892218112945557</v>
+        <v>7.892219066619873</v>
       </c>
       <c r="C1172" t="n">
-        <v>8.185541575772396</v>
+        <v>8.185542564891128</v>
       </c>
       <c r="D1172" t="n">
-        <v>7.892218112945557</v>
+        <v>7.892219066619873</v>
       </c>
       <c r="E1172" t="n">
-        <v>8.176375026334311</v>
+        <v>8.176376014345381</v>
       </c>
       <c r="F1172" t="n">
         <v>3298400</v>
@@ -23892,16 +23892,16 @@
         <v>45499</v>
       </c>
       <c r="B1174" t="n">
-        <v>7.818888187408447</v>
+        <v>7.818887233734131</v>
       </c>
       <c r="C1174" t="n">
-        <v>7.883053165226739</v>
+        <v>7.883052203726183</v>
       </c>
       <c r="D1174" t="n">
-        <v>7.653894653146547</v>
+        <v>7.653893719596588</v>
       </c>
       <c r="E1174" t="n">
-        <v>7.718058756794488</v>
+        <v>7.718057815418397</v>
       </c>
       <c r="F1174" t="n">
         <v>2119900</v>
@@ -23932,16 +23932,16 @@
         <v>45503</v>
       </c>
       <c r="B1176" t="n">
-        <v>7.617228984832764</v>
+        <v>7.617228507995605</v>
       </c>
       <c r="C1176" t="n">
-        <v>7.736390636504614</v>
+        <v>7.736390152207957</v>
       </c>
       <c r="D1176" t="n">
-        <v>7.47056680937066</v>
+        <v>7.470566341714527</v>
       </c>
       <c r="E1176" t="n">
-        <v>7.672226535732031</v>
+        <v>7.672226055452036</v>
       </c>
       <c r="F1176" t="n">
         <v>1625200</v>
@@ -23952,16 +23952,16 @@
         <v>45504</v>
       </c>
       <c r="B1177" t="n">
-        <v>7.736390113830566</v>
+        <v>7.736391067504883</v>
       </c>
       <c r="C1177" t="n">
-        <v>7.873885730130089</v>
+        <v>7.873886700753659</v>
       </c>
       <c r="D1177" t="n">
-        <v>7.617228470209331</v>
+        <v>7.617229409194445</v>
       </c>
       <c r="E1177" t="n">
-        <v>7.718057889492781</v>
+        <v>7.718058840907261</v>
       </c>
       <c r="F1177" t="n">
         <v>1863600</v>
@@ -23972,16 +23972,16 @@
         <v>45505</v>
       </c>
       <c r="B1178" t="n">
-        <v>7.727225303649902</v>
+        <v>7.727224349975586</v>
       </c>
       <c r="C1178" t="n">
-        <v>7.965549491738089</v>
+        <v>7.965548508650412</v>
       </c>
       <c r="D1178" t="n">
-        <v>7.663060325860083</v>
+        <v>7.663059380104842</v>
       </c>
       <c r="E1178" t="n">
-        <v>7.828054734219122</v>
+        <v>7.828053768100695</v>
       </c>
       <c r="F1178" t="n">
         <v>2732500</v>
@@ -24072,16 +24072,16 @@
         <v>45512</v>
       </c>
       <c r="B1183" t="n">
-        <v>7.928884029388428</v>
+        <v>7.92888355255127</v>
       </c>
       <c r="C1183" t="n">
-        <v>8.937181814543523</v>
+        <v>8.93718127706809</v>
       </c>
       <c r="D1183" t="n">
-        <v>7.699725521323209</v>
+        <v>7.699725058267473</v>
       </c>
       <c r="E1183" t="n">
-        <v>8.882183387972923</v>
+        <v>8.882182853805054</v>
       </c>
       <c r="F1183" t="n">
         <v>8733800</v>
@@ -24092,16 +24092,16 @@
         <v>45513</v>
       </c>
       <c r="B1184" t="n">
-        <v>7.846387386322021</v>
+        <v>7.846388339996338</v>
       </c>
       <c r="C1184" t="n">
-        <v>8.103044660301112</v>
+        <v>8.103045645170351</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.653894212295129</v>
+        <v>7.653895142573226</v>
       </c>
       <c r="E1184" t="n">
-        <v>8.103044660301112</v>
+        <v>8.103045645170351</v>
       </c>
       <c r="F1184" t="n">
         <v>6458600</v>
@@ -24112,16 +24112,16 @@
         <v>45516</v>
       </c>
       <c r="B1185" t="n">
-        <v>8.524696350097656</v>
+        <v>8.524697303771973</v>
       </c>
       <c r="C1185" t="n">
-        <v>8.607193549725519</v>
+        <v>8.607194512628958</v>
       </c>
       <c r="D1185" t="n">
-        <v>7.855553077470774</v>
+        <v>7.855553956286735</v>
       </c>
       <c r="E1185" t="n">
-        <v>7.919718051720391</v>
+        <v>7.919718937714611</v>
       </c>
       <c r="F1185" t="n">
         <v>5036600</v>
@@ -24132,16 +24132,16 @@
         <v>45517</v>
       </c>
       <c r="B1186" t="n">
-        <v>8.176375389099121</v>
+        <v>8.176376342773438</v>
       </c>
       <c r="C1186" t="n">
-        <v>8.497197640304007</v>
+        <v>8.497198631398319</v>
       </c>
       <c r="D1186" t="n">
-        <v>8.103044738681486</v>
+        <v>8.103045683802677</v>
       </c>
       <c r="E1186" t="n">
-        <v>8.497197640304007</v>
+        <v>8.497198631398319</v>
       </c>
       <c r="F1186" t="n">
         <v>4500900</v>
@@ -24252,16 +24252,16 @@
         <v>45525</v>
       </c>
       <c r="B1192" t="n">
-        <v>9.065511703491211</v>
+        <v>9.065510749816895</v>
       </c>
       <c r="C1192" t="n">
-        <v>9.340501238395222</v>
+        <v>9.340500255792538</v>
       </c>
       <c r="D1192" t="n">
-        <v>8.845518851729427</v>
+        <v>8.845517921197933</v>
       </c>
       <c r="E1192" t="n">
-        <v>8.845518851729427</v>
+        <v>8.845517921197933</v>
       </c>
       <c r="F1192" t="n">
         <v>3272300</v>
@@ -24272,16 +24272,16 @@
         <v>45526</v>
       </c>
       <c r="B1193" t="n">
-        <v>8.653024673461914</v>
+        <v>8.653023719787598</v>
       </c>
       <c r="C1193" t="n">
-        <v>9.093009453018452</v>
+        <v>9.093008450852169</v>
       </c>
       <c r="D1193" t="n">
-        <v>8.616359348013061</v>
+        <v>8.616358398379734</v>
       </c>
       <c r="E1193" t="n">
-        <v>9.038011027760017</v>
+        <v>9.038010031655267</v>
       </c>
       <c r="F1193" t="n">
         <v>2148900</v>
@@ -24312,16 +24312,16 @@
         <v>45530</v>
       </c>
       <c r="B1195" t="n">
-        <v>9.258004188537598</v>
+        <v>9.258003234863281</v>
       </c>
       <c r="C1195" t="n">
-        <v>9.523828026171985</v>
+        <v>9.523827045114947</v>
       </c>
       <c r="D1195" t="n">
-        <v>9.038011353739554</v>
+        <v>9.038010422726874</v>
       </c>
       <c r="E1195" t="n">
-        <v>9.505494925701171</v>
+        <v>9.50549394653264</v>
       </c>
       <c r="F1195" t="n">
         <v>2395100</v>
@@ -24332,16 +24332,16 @@
         <v>45531</v>
       </c>
       <c r="B1196" t="n">
-        <v>9.716320037841797</v>
+        <v>9.716320991516113</v>
       </c>
       <c r="C1196" t="n">
-        <v>9.881313551318417</v>
+        <v>9.881314521187145</v>
       </c>
       <c r="D1196" t="n">
-        <v>9.184672426724402</v>
+        <v>9.184673328216547</v>
       </c>
       <c r="E1196" t="n">
-        <v>9.184672426724402</v>
+        <v>9.184673328216547</v>
       </c>
       <c r="F1196" t="n">
         <v>2543500</v>
@@ -24512,16 +24512,16 @@
         <v>45544</v>
       </c>
       <c r="B1205" t="n">
-        <v>9.111342430114746</v>
+        <v>9.11134147644043</v>
       </c>
       <c r="C1205" t="n">
-        <v>9.523828468146968</v>
+        <v>9.523827471298185</v>
       </c>
       <c r="D1205" t="n">
-        <v>9.010512995357084</v>
+        <v>9.010512052236475</v>
       </c>
       <c r="E1205" t="n">
-        <v>9.368000603594881</v>
+        <v>9.367999623056432</v>
       </c>
       <c r="F1205" t="n">
         <v>1653000</v>
@@ -24652,16 +24652,16 @@
         <v>45553</v>
       </c>
       <c r="B1212" t="n">
-        <v>9.890480995178223</v>
+        <v>9.890481948852539</v>
       </c>
       <c r="C1212" t="n">
-        <v>10.26630080177617</v>
+        <v>10.26630179168833</v>
       </c>
       <c r="D1212" t="n">
-        <v>9.606324065654963</v>
+        <v>9.606324991929888</v>
       </c>
       <c r="E1212" t="n">
-        <v>9.697987816899968</v>
+        <v>9.697988752013428</v>
       </c>
       <c r="F1212" t="n">
         <v>2495300</v>
@@ -24792,16 +24792,16 @@
         <v>45562</v>
       </c>
       <c r="B1219" t="n">
-        <v>9.587991714477539</v>
+        <v>9.587992668151855</v>
       </c>
       <c r="C1219" t="n">
-        <v>9.752986114891955</v>
+        <v>9.752987084977519</v>
       </c>
       <c r="D1219" t="n">
-        <v>9.450496963579065</v>
+        <v>9.450497903577398</v>
       </c>
       <c r="E1219" t="n">
-        <v>9.532993289615966</v>
+        <v>9.532994237819837</v>
       </c>
       <c r="F1219" t="n">
         <v>1380700</v>
@@ -24952,16 +24952,16 @@
         <v>45574</v>
       </c>
       <c r="B1227" t="n">
-        <v>9.02884578704834</v>
+        <v>9.028844833374023</v>
       </c>
       <c r="C1227" t="n">
-        <v>9.06551111426378</v>
+        <v>9.065510156716678</v>
       </c>
       <c r="D1227" t="n">
-        <v>8.836352600624689</v>
+        <v>8.836351667282518</v>
       </c>
       <c r="E1227" t="n">
-        <v>8.836352600624689</v>
+        <v>8.836351667282518</v>
       </c>
       <c r="F1227" t="n">
         <v>1510000</v>
@@ -24972,16 +24972,16 @@
         <v>45575</v>
       </c>
       <c r="B1228" t="n">
-        <v>9.42299747467041</v>
+        <v>9.422996520996094</v>
       </c>
       <c r="C1228" t="n">
-        <v>9.441330574660176</v>
+        <v>9.441329619130419</v>
       </c>
       <c r="D1228" t="n">
-        <v>8.946348239150669</v>
+        <v>8.946347333716643</v>
       </c>
       <c r="E1228" t="n">
-        <v>9.065510766573185</v>
+        <v>9.065509849079064</v>
       </c>
       <c r="F1228" t="n">
         <v>2116800</v>
@@ -25112,16 +25112,16 @@
         <v>45586</v>
       </c>
       <c r="B1235" t="n">
-        <v>10.95377635955811</v>
+        <v>10.95377540588379</v>
       </c>
       <c r="C1235" t="n">
-        <v>11.26543206609426</v>
+        <v>11.2654310852861</v>
       </c>
       <c r="D1235" t="n">
-        <v>10.89877880791662</v>
+        <v>10.89877785903058</v>
       </c>
       <c r="E1235" t="n">
-        <v>11.07293888700842</v>
+        <v>11.07293792295939</v>
       </c>
       <c r="F1235" t="n">
         <v>2389000</v>
@@ -25132,16 +25132,16 @@
         <v>45587</v>
       </c>
       <c r="B1236" t="n">
-        <v>10.65128707885742</v>
+        <v>10.65128612518311</v>
       </c>
       <c r="C1236" t="n">
-        <v>11.00877465704114</v>
+        <v>11.00877367135879</v>
       </c>
       <c r="D1236" t="n">
-        <v>10.62378830335723</v>
+        <v>10.62378735214505</v>
       </c>
       <c r="E1236" t="n">
-        <v>10.86211335547971</v>
+        <v>10.86211238292884</v>
       </c>
       <c r="F1236" t="n">
         <v>2418100</v>
@@ -25412,16 +25412,16 @@
         <v>45607</v>
       </c>
       <c r="B1250" t="n">
-        <v>12.33789443969727</v>
+        <v>12.33789348602295</v>
       </c>
       <c r="C1250" t="n">
-        <v>12.47538919855138</v>
+        <v>12.47538823424922</v>
       </c>
       <c r="D1250" t="n">
-        <v>11.64125234671695</v>
+        <v>11.64125144689053</v>
       </c>
       <c r="E1250" t="n">
-        <v>11.69625077476081</v>
+        <v>11.69624987068321</v>
       </c>
       <c r="F1250" t="n">
         <v>4291300</v>
@@ -25472,16 +25472,16 @@
         <v>45610</v>
       </c>
       <c r="B1253" t="n">
-        <v>10.58712291717529</v>
+        <v>10.58712196350098</v>
       </c>
       <c r="C1253" t="n">
-        <v>10.99960804399089</v>
+        <v>10.99960705316045</v>
       </c>
       <c r="D1253" t="n">
-        <v>10.40379629127617</v>
+        <v>10.40379535411568</v>
       </c>
       <c r="E1253" t="n">
-        <v>10.559624141833</v>
+        <v>10.55962319063574</v>
       </c>
       <c r="F1253" t="n">
         <v>63226600</v>
@@ -25512,16 +25512,16 @@
         <v>45615</v>
       </c>
       <c r="B1255" t="n">
-        <v>11.35709571838379</v>
+        <v>11.35709667205811</v>
       </c>
       <c r="C1255" t="n">
-        <v>11.46709169487495</v>
+        <v>11.46709265778581</v>
       </c>
       <c r="D1255" t="n">
-        <v>10.91711093824883</v>
+        <v>10.91711185497689</v>
       </c>
       <c r="E1255" t="n">
-        <v>11.00877468907663</v>
+        <v>11.00877561350184</v>
       </c>
       <c r="F1255" t="n">
         <v>7243900</v>
@@ -25532,16 +25532,16 @@
         <v>45617</v>
       </c>
       <c r="B1256" t="n">
-        <v>11.23793315887451</v>
+        <v>11.2379322052002</v>
       </c>
       <c r="C1256" t="n">
-        <v>11.329596035262</v>
+        <v>11.32959507380898</v>
       </c>
       <c r="D1256" t="n">
-        <v>10.94460968159175</v>
+        <v>10.94460875280948</v>
       </c>
       <c r="E1256" t="n">
-        <v>11.30209725976278</v>
+        <v>11.30209630064337</v>
       </c>
       <c r="F1256" t="n">
         <v>3263500</v>
@@ -25612,16 +25612,16 @@
         <v>45623</v>
       </c>
       <c r="B1260" t="n">
-        <v>10.94460868835449</v>
+        <v>10.94460964202881</v>
       </c>
       <c r="C1260" t="n">
-        <v>11.76041319693857</v>
+        <v>11.76041422169919</v>
       </c>
       <c r="D1260" t="n">
-        <v>10.84377927122756</v>
+        <v>10.84378021611596</v>
       </c>
       <c r="E1260" t="n">
-        <v>11.60458535963408</v>
+        <v>11.60458637081642</v>
       </c>
       <c r="F1260" t="n">
         <v>5633000</v>
@@ -25732,16 +25732,16 @@
         <v>45631</v>
       </c>
       <c r="B1266" t="n">
-        <v>9.404664993286133</v>
+        <v>9.404665946960449</v>
       </c>
       <c r="C1266" t="n">
-        <v>9.835482341294636</v>
+        <v>9.835483338655724</v>
       </c>
       <c r="D1266" t="n">
-        <v>9.294669018847561</v>
+        <v>9.294669961367802</v>
       </c>
       <c r="E1266" t="n">
-        <v>9.624656942163279</v>
+        <v>9.624657918145745</v>
       </c>
       <c r="F1266" t="n">
         <v>7256000</v>
@@ -25792,16 +25792,16 @@
         <v>45636</v>
       </c>
       <c r="B1269" t="n">
-        <v>9.862982749938965</v>
+        <v>9.862981796264648</v>
       </c>
       <c r="C1269" t="n">
-        <v>9.89048152712332</v>
+        <v>9.890480570790084</v>
       </c>
       <c r="D1269" t="n">
-        <v>9.45966327177338</v>
+        <v>9.459662357096944</v>
       </c>
       <c r="E1269" t="n">
-        <v>9.496328599409308</v>
+        <v>9.496327681187619</v>
       </c>
       <c r="F1269" t="n">
         <v>3728900</v>
@@ -25812,16 +25812,16 @@
         <v>45637</v>
       </c>
       <c r="B1270" t="n">
-        <v>9.991311073303223</v>
+        <v>9.991310119628906</v>
       </c>
       <c r="C1270" t="n">
-        <v>10.31213334939706</v>
+        <v>10.31213236510014</v>
       </c>
       <c r="D1270" t="n">
-        <v>9.707154999433026</v>
+        <v>9.70715407288151</v>
       </c>
       <c r="E1270" t="n">
-        <v>9.945480068864425</v>
+        <v>9.945479119564695</v>
       </c>
       <c r="F1270" t="n">
         <v>4552800</v>
@@ -25872,16 +25872,16 @@
         <v>45642</v>
       </c>
       <c r="B1273" t="n">
-        <v>9.047178268432617</v>
+        <v>9.047177314758301</v>
       </c>
       <c r="C1273" t="n">
-        <v>9.221339233239892</v>
+        <v>9.221338261207052</v>
       </c>
       <c r="D1273" t="n">
-        <v>8.909683506044034</v>
+        <v>8.909682566863212</v>
       </c>
       <c r="E1273" t="n">
-        <v>9.093010147285604</v>
+        <v>9.093009188780092</v>
       </c>
       <c r="F1273" t="n">
         <v>2711300</v>
@@ -25912,16 +25912,16 @@
         <v>45644</v>
       </c>
       <c r="B1275" t="n">
-        <v>8.662190437316895</v>
+        <v>8.662191390991211</v>
       </c>
       <c r="C1275" t="n">
-        <v>9.193838045166085</v>
+        <v>9.193839057372786</v>
       </c>
       <c r="D1275" t="n">
-        <v>8.478863826708594</v>
+        <v>8.478864760199345</v>
       </c>
       <c r="E1275" t="n">
-        <v>9.074675529728131</v>
+        <v>9.074676528815491</v>
       </c>
       <c r="F1275" t="n">
         <v>4674700</v>
@@ -25972,16 +25972,16 @@
         <v>45649</v>
       </c>
       <c r="B1278" t="n">
-        <v>8.405532836914062</v>
+        <v>8.405533790588379</v>
       </c>
       <c r="C1278" t="n">
-        <v>8.918847325514962</v>
+        <v>8.918848337428875</v>
       </c>
       <c r="D1278" t="n">
-        <v>8.405532836914062</v>
+        <v>8.405533790588379</v>
       </c>
       <c r="E1278" t="n">
-        <v>8.845516684286263</v>
+        <v>8.845517687880234</v>
       </c>
       <c r="F1278" t="n">
         <v>2696000</v>
@@ -26052,16 +26052,16 @@
         <v>45659</v>
       </c>
       <c r="B1282" t="n">
-        <v>7.153563022613525</v>
+        <v>7.153562545776367</v>
       </c>
       <c r="C1282" t="n">
-        <v>7.60365360163207</v>
+        <v>7.603653094793091</v>
       </c>
       <c r="D1282" t="n">
-        <v>7.009917540061675</v>
+        <v>7.009917072799536</v>
       </c>
       <c r="E1282" t="n">
-        <v>7.574924231138988</v>
+        <v>7.574923726215032</v>
       </c>
       <c r="F1282" t="n">
         <v>7282600</v>
@@ -26072,16 +26072,16 @@
         <v>45660</v>
       </c>
       <c r="B1283" t="n">
-        <v>7.124833583831787</v>
+        <v>7.124834060668945</v>
       </c>
       <c r="C1283" t="n">
-        <v>7.268479512438287</v>
+        <v>7.268479998889104</v>
       </c>
       <c r="D1283" t="n">
-        <v>7.067375303716751</v>
+        <v>7.067375776708452</v>
       </c>
       <c r="E1283" t="n">
-        <v>7.153562495570395</v>
+        <v>7.153562974330267</v>
       </c>
       <c r="F1283" t="n">
         <v>5051000</v>
@@ -26132,16 +26132,16 @@
         <v>45665</v>
       </c>
       <c r="B1286" t="n">
-        <v>7.373819828033447</v>
+        <v>7.373819351196289</v>
       </c>
       <c r="C1286" t="n">
-        <v>7.756875960969692</v>
+        <v>7.756875459361737</v>
       </c>
       <c r="D1286" t="n">
-        <v>7.316361545084363</v>
+        <v>7.316361071962816</v>
       </c>
       <c r="E1286" t="n">
-        <v>7.613229568640219</v>
+        <v>7.613229076321335</v>
       </c>
       <c r="F1286" t="n">
         <v>5756000</v>
@@ -26152,16 +26152,16 @@
         <v>45666</v>
       </c>
       <c r="B1287" t="n">
-        <v>7.373819828033447</v>
+        <v>7.373819351196289</v>
       </c>
       <c r="C1287" t="n">
-        <v>7.460007480775994</v>
+        <v>7.460006998365405</v>
       </c>
       <c r="D1287" t="n">
-        <v>7.278056023118307</v>
+        <v>7.278055552473833</v>
       </c>
       <c r="E1287" t="n">
-        <v>7.345090914877826</v>
+        <v>7.345090439898458</v>
       </c>
       <c r="F1287" t="n">
         <v>2780600</v>
@@ -26252,16 +26252,16 @@
         <v>45673</v>
       </c>
       <c r="B1292" t="n">
-        <v>7.469583511352539</v>
+        <v>7.469583988189697</v>
       </c>
       <c r="C1292" t="n">
-        <v>7.967555258362382</v>
+        <v>7.967555766988652</v>
       </c>
       <c r="D1292" t="n">
-        <v>7.45043075185216</v>
+        <v>7.45043122746666</v>
       </c>
       <c r="E1292" t="n">
-        <v>7.967555258362382</v>
+        <v>7.967555766988652</v>
       </c>
       <c r="F1292" t="n">
         <v>5833700</v>
@@ -26312,16 +26312,16 @@
         <v>45678</v>
       </c>
       <c r="B1295" t="n">
-        <v>7.910098075866699</v>
+        <v>7.910097599029541</v>
       </c>
       <c r="C1295" t="n">
-        <v>7.919674684709862</v>
+        <v>7.919674207295405</v>
       </c>
       <c r="D1295" t="n">
-        <v>7.670688334441743</v>
+        <v>7.670687872036702</v>
       </c>
       <c r="E1295" t="n">
-        <v>7.747299378635674</v>
+        <v>7.74729891161236</v>
       </c>
       <c r="F1295" t="n">
         <v>3494700</v>
@@ -26412,16 +26412,16 @@
         <v>45685</v>
       </c>
       <c r="B1300" t="n">
-        <v>9.097569465637207</v>
+        <v>9.097570419311523</v>
       </c>
       <c r="C1300" t="n">
-        <v>9.279520453108681</v>
+        <v>9.279521425856441</v>
       </c>
       <c r="D1300" t="n">
-        <v>8.810277615646172</v>
+        <v>8.810278539204438</v>
       </c>
       <c r="E1300" t="n">
-        <v>8.85815974285728</v>
+        <v>8.858160671434904</v>
       </c>
       <c r="F1300" t="n">
         <v>3554800</v>
@@ -26452,16 +26452,16 @@
         <v>45687</v>
       </c>
       <c r="B1302" t="n">
-        <v>9.432744026184082</v>
+        <v>9.432743072509766</v>
       </c>
       <c r="C1302" t="n">
-        <v>9.57638950342519</v>
+        <v>9.576388535227952</v>
       </c>
       <c r="D1302" t="n">
-        <v>8.858160290668302</v>
+        <v>8.858159395085856</v>
       </c>
       <c r="E1302" t="n">
-        <v>8.896465812150975</v>
+        <v>8.896464912695745</v>
       </c>
       <c r="F1302" t="n">
         <v>7000600</v>
@@ -26532,16 +26532,16 @@
         <v>45693</v>
       </c>
       <c r="B1306" t="n">
-        <v>9.068841934204102</v>
+        <v>9.068840980529785</v>
       </c>
       <c r="C1306" t="n">
-        <v>9.289098474295518</v>
+        <v>9.289097497459148</v>
       </c>
       <c r="D1306" t="n">
-        <v>8.896466615332033</v>
+        <v>8.896465679784608</v>
       </c>
       <c r="E1306" t="n">
-        <v>9.289098474295518</v>
+        <v>9.289097497459148</v>
       </c>
       <c r="F1306" t="n">
         <v>2011300</v>
@@ -26592,16 +26592,16 @@
         <v>45698</v>
       </c>
       <c r="B1309" t="n">
-        <v>9.365708351135254</v>
+        <v>9.36570930480957</v>
       </c>
       <c r="C1309" t="n">
-        <v>9.64342360049249</v>
+        <v>9.643424582445491</v>
       </c>
       <c r="D1309" t="n">
-        <v>9.298673919203532</v>
+        <v>9.298674866051989</v>
       </c>
       <c r="E1309" t="n">
-        <v>9.308250527558247</v>
+        <v>9.308251475381853</v>
       </c>
       <c r="F1309" t="n">
         <v>1788100</v>
@@ -26612,16 +26612,16 @@
         <v>45699</v>
       </c>
       <c r="B1310" t="n">
-        <v>9.451896667480469</v>
+        <v>9.451895713806152</v>
       </c>
       <c r="C1310" t="n">
-        <v>9.595543063121781</v>
+        <v>9.595542094953879</v>
       </c>
       <c r="D1310" t="n">
-        <v>9.269945662265652</v>
+        <v>9.269944726949767</v>
       </c>
       <c r="E1310" t="n">
-        <v>9.308251185114861</v>
+        <v>9.308250245934039</v>
       </c>
       <c r="F1310" t="n">
         <v>2270500</v>
@@ -26792,16 +26792,16 @@
         <v>45712</v>
       </c>
       <c r="B1319" t="n">
-        <v>8.800702095031738</v>
+        <v>8.800701141357422</v>
       </c>
       <c r="C1319" t="n">
-        <v>9.480625828274396</v>
+        <v>9.480624800921209</v>
       </c>
       <c r="D1319" t="n">
-        <v>8.752820875179671</v>
+        <v>8.752819926693927</v>
       </c>
       <c r="E1319" t="n">
-        <v>9.432744608422329</v>
+        <v>9.432743586257715</v>
       </c>
       <c r="F1319" t="n">
         <v>2699300</v>
@@ -26812,16 +26812,16 @@
         <v>45713</v>
       </c>
       <c r="B1320" t="n">
-        <v>8.781548500061035</v>
+        <v>8.781549453735352</v>
       </c>
       <c r="C1320" t="n">
-        <v>8.963499483293909</v>
+        <v>8.963500456728063</v>
       </c>
       <c r="D1320" t="n">
-        <v>8.71451407149244</v>
+        <v>8.71451501788683</v>
       </c>
       <c r="E1320" t="n">
-        <v>8.810277410408206</v>
+        <v>8.810278367202477</v>
       </c>
       <c r="F1320" t="n">
         <v>2412200</v>
@@ -26872,16 +26872,16 @@
         <v>45716</v>
       </c>
       <c r="B1323" t="n">
-        <v>9.451896667480469</v>
+        <v>9.451895713806152</v>
       </c>
       <c r="C1323" t="n">
-        <v>10.01690381446308</v>
+        <v>10.01690280378086</v>
       </c>
       <c r="D1323" t="n">
-        <v>9.308251185114861</v>
+        <v>9.308250245934039</v>
       </c>
       <c r="E1323" t="n">
-        <v>9.308251185114861</v>
+        <v>9.308250245934039</v>
       </c>
       <c r="F1323" t="n">
         <v>9373900</v>
@@ -26892,16 +26892,16 @@
         <v>45721</v>
       </c>
       <c r="B1324" t="n">
-        <v>9.250791549682617</v>
+        <v>9.250792503356934</v>
       </c>
       <c r="C1324" t="n">
-        <v>9.557235702844167</v>
+        <v>9.557236688110148</v>
       </c>
       <c r="D1324" t="n">
-        <v>9.126298384141835</v>
+        <v>9.126299324982012</v>
       </c>
       <c r="E1324" t="n">
-        <v>9.557235702844167</v>
+        <v>9.557236688110148</v>
       </c>
       <c r="F1324" t="n">
         <v>3135300</v>
@@ -26932,16 +26932,16 @@
         <v>45723</v>
       </c>
       <c r="B1326" t="n">
-        <v>10.07436275482178</v>
+        <v>10.07436180114746</v>
       </c>
       <c r="C1326" t="n">
-        <v>10.12224397437444</v>
+        <v>10.12224301616752</v>
       </c>
       <c r="D1326" t="n">
-        <v>9.384862416609938</v>
+        <v>9.384861528206129</v>
       </c>
       <c r="E1326" t="n">
-        <v>9.499778987432624</v>
+        <v>9.499778088150411</v>
       </c>
       <c r="F1326" t="n">
         <v>6657400</v>
@@ -27032,16 +27032,16 @@
         <v>45730</v>
       </c>
       <c r="B1331" t="n">
-        <v>10.33292388916016</v>
+        <v>10.33292484283447</v>
       </c>
       <c r="C1331" t="n">
-        <v>10.33292388916016</v>
+        <v>10.33292484283447</v>
       </c>
       <c r="D1331" t="n">
-        <v>9.787069998123471</v>
+        <v>9.787070901418355</v>
       </c>
       <c r="E1331" t="n">
-        <v>9.825375518314191</v>
+        <v>9.825376425144473</v>
       </c>
       <c r="F1331" t="n">
         <v>3811800</v>
@@ -27072,16 +27072,16 @@
         <v>45734</v>
       </c>
       <c r="B1333" t="n">
-        <v>10.35207653045654</v>
+        <v>10.35207748413086</v>
       </c>
       <c r="C1333" t="n">
-        <v>10.47656877919955</v>
+        <v>10.47656974434259</v>
       </c>
       <c r="D1333" t="n">
-        <v>10.13181911664653</v>
+        <v>10.13182005002986</v>
       </c>
       <c r="E1333" t="n">
-        <v>10.29461779672658</v>
+        <v>10.29461874510757</v>
       </c>
       <c r="F1333" t="n">
         <v>3107600</v>
@@ -27092,16 +27092,16 @@
         <v>45735</v>
       </c>
       <c r="B1334" t="n">
-        <v>10.62979221343994</v>
+        <v>10.62979316711426</v>
       </c>
       <c r="C1334" t="n">
-        <v>10.67767342808128</v>
+        <v>10.67767438605136</v>
       </c>
       <c r="D1334" t="n">
-        <v>10.26588931985684</v>
+        <v>10.26589024088284</v>
       </c>
       <c r="E1334" t="n">
-        <v>10.39995818209361</v>
+        <v>10.39995911514788</v>
       </c>
       <c r="F1334" t="n">
         <v>4029100</v>
@@ -27192,16 +27192,16 @@
         <v>45742</v>
       </c>
       <c r="B1339" t="n">
-        <v>10.64894485473633</v>
+        <v>10.64894580841064</v>
       </c>
       <c r="C1339" t="n">
-        <v>10.85962567629456</v>
+        <v>10.85962664883656</v>
       </c>
       <c r="D1339" t="n">
-        <v>10.32334747049424</v>
+        <v>10.32334839500943</v>
       </c>
       <c r="E1339" t="n">
-        <v>10.32334747049424</v>
+        <v>10.32334839500943</v>
       </c>
       <c r="F1339" t="n">
         <v>4272600</v>
@@ -27232,16 +27232,16 @@
         <v>45744</v>
       </c>
       <c r="B1341" t="n">
-        <v>10.57233428955078</v>
+        <v>10.57233333587646</v>
       </c>
       <c r="C1341" t="n">
-        <v>10.78301512060656</v>
+        <v>10.78301414792785</v>
       </c>
       <c r="D1341" t="n">
-        <v>10.32334793587356</v>
+        <v>10.32334700465898</v>
       </c>
       <c r="E1341" t="n">
-        <v>10.78301512060656</v>
+        <v>10.78301414792785</v>
       </c>
       <c r="F1341" t="n">
         <v>2413100</v>
@@ -27312,16 +27312,16 @@
         <v>45750</v>
       </c>
       <c r="B1345" t="n">
-        <v>11.53954982757568</v>
+        <v>11.53954887390137</v>
       </c>
       <c r="C1345" t="n">
-        <v>11.75980635338026</v>
+        <v>11.75980538150306</v>
       </c>
       <c r="D1345" t="n">
-        <v>10.9458137728658</v>
+        <v>10.94581286826019</v>
       </c>
       <c r="E1345" t="n">
-        <v>11.03200142671131</v>
+        <v>11.03200051498281</v>
       </c>
       <c r="F1345" t="n">
         <v>5397200</v>
@@ -27332,16 +27332,16 @@
         <v>45751</v>
       </c>
       <c r="B1346" t="n">
-        <v>10.84047317504883</v>
+        <v>10.84047222137451</v>
       </c>
       <c r="C1346" t="n">
-        <v>11.20437610421549</v>
+        <v>11.20437511852736</v>
       </c>
       <c r="D1346" t="n">
-        <v>10.59148772943014</v>
+        <v>10.59148679765994</v>
       </c>
       <c r="E1346" t="n">
-        <v>11.20437610421549</v>
+        <v>11.20437511852736</v>
       </c>
       <c r="F1346" t="n">
         <v>4512700</v>
@@ -27372,16 +27372,16 @@
         <v>45755</v>
       </c>
       <c r="B1348" t="n">
-        <v>10.37123012542725</v>
+        <v>10.37122917175293</v>
       </c>
       <c r="C1348" t="n">
-        <v>10.85004961750893</v>
+        <v>10.85004861980533</v>
       </c>
       <c r="D1348" t="n">
-        <v>10.25631355692073</v>
+        <v>10.25631261381343</v>
       </c>
       <c r="E1348" t="n">
-        <v>10.6489453943036</v>
+        <v>10.6489444150923</v>
       </c>
       <c r="F1348" t="n">
         <v>3075500</v>
@@ -27392,16 +27392,16 @@
         <v>45756</v>
       </c>
       <c r="B1349" t="n">
-        <v>11.11818695068359</v>
+        <v>11.11818790435791</v>
       </c>
       <c r="C1349" t="n">
-        <v>11.25225672124789</v>
+        <v>11.25225768642218</v>
       </c>
       <c r="D1349" t="n">
-        <v>10.09351365214581</v>
+        <v>10.09351451792768</v>
       </c>
       <c r="E1349" t="n">
-        <v>10.15097238618067</v>
+        <v>10.15097325689113</v>
       </c>
       <c r="F1349" t="n">
         <v>4047500</v>
@@ -27412,16 +27412,16 @@
         <v>45757</v>
       </c>
       <c r="B1350" t="n">
-        <v>11.20437622070312</v>
+        <v>11.20437526702881</v>
       </c>
       <c r="C1350" t="n">
-        <v>11.2905638776223</v>
+        <v>11.29056291661202</v>
       </c>
       <c r="D1350" t="n">
-        <v>10.81174437320528</v>
+        <v>10.81174345295031</v>
       </c>
       <c r="E1350" t="n">
-        <v>11.07988303996161</v>
+        <v>11.07988209688369</v>
       </c>
       <c r="F1350" t="n">
         <v>2979100</v>
@@ -27432,16 +27432,16 @@
         <v>45758</v>
       </c>
       <c r="B1351" t="n">
-        <v>11.53954982757568</v>
+        <v>11.53954887390137</v>
       </c>
       <c r="C1351" t="n">
-        <v>11.64488978601148</v>
+        <v>11.64488882363145</v>
       </c>
       <c r="D1351" t="n">
-        <v>11.21395243005962</v>
+        <v>11.21395150329397</v>
       </c>
       <c r="E1351" t="n">
-        <v>11.33844560636139</v>
+        <v>11.33844466930713</v>
       </c>
       <c r="F1351" t="n">
         <v>4056000</v>
@@ -34049,182 +34049,222 @@
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B1682" t="n">
-        <v>8.670000076293945</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="C1682" t="n">
-        <v>9.100000381469727</v>
+        <v>9.229999542236328</v>
       </c>
       <c r="D1682" t="n">
-        <v>8.579999923706055</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="E1682" t="n">
-        <v>8.899999618530273</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="F1682" t="n">
-        <v>6481600</v>
+        <v>7898200</v>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B1683" t="n">
-        <v>8.380000114440918</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="C1683" t="n">
-        <v>8.710000038146973</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="D1683" t="n">
-        <v>8.359999656677246</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="E1683" t="n">
-        <v>8.699999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="F1683" t="n">
-        <v>7526600</v>
+        <v>6481600</v>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B1684" t="n">
-        <v>8.159999847412109</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="C1684" t="n">
-        <v>8.529999732971191</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="D1684" t="n">
-        <v>8.100000381469727</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="E1684" t="n">
-        <v>8.390000343322754</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="F1684" t="n">
-        <v>7704200</v>
+        <v>7526600</v>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B1685" t="n">
-        <v>8</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="C1685" t="n">
-        <v>8.149999618530273</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="D1685" t="n">
-        <v>7.880000114440918</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E1685" t="n">
-        <v>8.109999656677246</v>
+        <v>8.390000343322754</v>
       </c>
       <c r="F1685" t="n">
-        <v>8377800</v>
+        <v>7704200</v>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B1686" t="n">
-        <v>7.840000152587891</v>
+        <v>8</v>
       </c>
       <c r="C1686" t="n">
-        <v>8.079999923706055</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="D1686" t="n">
-        <v>7.809999942779541</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="E1686" t="n">
-        <v>7.96999979019165</v>
+        <v>8.109999656677246</v>
       </c>
       <c r="F1686" t="n">
-        <v>6506700</v>
+        <v>8377800</v>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B1687" t="n">
-        <v>7.380000114440918</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="C1687" t="n">
-        <v>7.840000152587891</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="D1687" t="n">
-        <v>7.380000114440918</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="E1687" t="n">
-        <v>7.829999923706055</v>
+        <v>7.96999979019165</v>
       </c>
       <c r="F1687" t="n">
-        <v>10354900</v>
+        <v>6506700</v>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B1688" t="n">
-        <v>7.440000057220459</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="C1688" t="n">
-        <v>7.599999904632568</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="D1688" t="n">
-        <v>7.329999923706055</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="E1688" t="n">
-        <v>7.570000171661377</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="F1688" t="n">
-        <v>17490500</v>
+        <v>10354900</v>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B1689" t="n">
-        <v>7.28000020980835</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="C1689" t="n">
-        <v>7.5</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="D1689" t="n">
-        <v>7.190000057220459</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="E1689" t="n">
-        <v>7.369999885559082</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="F1689" t="n">
-        <v>13406400</v>
+        <v>17490500</v>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1690" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="C1690" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>7.190000057220459</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>7.369999885559082</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>13406400</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B1690" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="C1690" t="n">
+      <c r="B1691" t="n">
+        <v>7.639999866485596</v>
+      </c>
+      <c r="C1691" t="n">
         <v>7.75</v>
       </c>
-      <c r="D1690" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="E1690" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="F1690" t="n">
-        <v>14620300</v>
+      <c r="D1691" t="n">
+        <v>7.329999923706055</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>7.349999904632568</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>14627600</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1692" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1692" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>7458400</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1693"/>
+  <dimension ref="A1:F1694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43774</v>
       </c>
       <c r="B2" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="C2" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04940323214578</v>
+        <v>16.04940511406312</v>
       </c>
       <c r="E2" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="F2" t="n">
         <v>862100</v>
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518489837646</v>
+        <v>15.99518394470215</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073696219904</v>
+        <v>16.13073600044276</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008429802985</v>
+        <v>15.48008337506717</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073696219904</v>
+        <v>16.13073600044276</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -512,16 +512,16 @@
         <v>43777</v>
       </c>
       <c r="B5" t="n">
-        <v>15.81444644927979</v>
+        <v>15.8144474029541</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12169868961396</v>
+        <v>16.12169966181682</v>
       </c>
       <c r="D5" t="n">
-        <v>15.57948875233966</v>
+        <v>15.57948969184508</v>
       </c>
       <c r="E5" t="n">
-        <v>15.94999850268889</v>
+        <v>15.94999946453754</v>
       </c>
       <c r="F5" t="n">
         <v>463500</v>
@@ -652,16 +652,16 @@
         <v>43790</v>
       </c>
       <c r="B12" t="n">
-        <v>13.97093486785889</v>
+        <v>13.9709358215332</v>
       </c>
       <c r="C12" t="n">
-        <v>14.09745075875241</v>
+        <v>14.09745172106287</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66368260555961</v>
+        <v>13.66368353826049</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9257505595527</v>
+        <v>13.92575151014267</v>
       </c>
       <c r="F12" t="n">
         <v>946900</v>
@@ -712,16 +712,16 @@
         <v>43795</v>
       </c>
       <c r="B15" t="n">
-        <v>14.78425025939941</v>
+        <v>14.7842493057251</v>
       </c>
       <c r="C15" t="n">
-        <v>14.78425025939941</v>
+        <v>14.7842493057251</v>
       </c>
       <c r="D15" t="n">
-        <v>14.16974571703249</v>
+        <v>14.16974480299746</v>
       </c>
       <c r="E15" t="n">
-        <v>14.17878188949981</v>
+        <v>14.17878097488189</v>
       </c>
       <c r="F15" t="n">
         <v>3631800</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439208984375</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439208984375</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869711259133</v>
+        <v>14.64869618523321</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291932069259</v>
+        <v>14.70291838990186</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -812,16 +812,16 @@
         <v>43802</v>
       </c>
       <c r="B20" t="n">
-        <v>15.81444644927979</v>
+        <v>15.8144474029541</v>
       </c>
       <c r="C20" t="n">
-        <v>15.9228891261898</v>
+        <v>15.92289008640364</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29934761214245</v>
+        <v>15.29934853475424</v>
       </c>
       <c r="E20" t="n">
-        <v>15.48912014218763</v>
+        <v>15.48912107624346</v>
       </c>
       <c r="F20" t="n">
         <v>976200</v>
@@ -832,16 +832,16 @@
         <v>43803</v>
       </c>
       <c r="B21" t="n">
-        <v>16.1036262512207</v>
+        <v>16.10362434387207</v>
       </c>
       <c r="C21" t="n">
-        <v>16.19399487051062</v>
+        <v>16.19399295245853</v>
       </c>
       <c r="D21" t="n">
-        <v>15.74215349769909</v>
+        <v>15.74215163316408</v>
       </c>
       <c r="E21" t="n">
-        <v>16.04036873480918</v>
+        <v>16.0403668349529</v>
       </c>
       <c r="F21" t="n">
         <v>976000</v>
@@ -852,16 +852,16 @@
         <v>43804</v>
       </c>
       <c r="B22" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="C22" t="n">
-        <v>16.43798702712168</v>
+        <v>16.4379889546035</v>
       </c>
       <c r="D22" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="E22" t="n">
-        <v>16.40183889566449</v>
+        <v>16.40184081890766</v>
       </c>
       <c r="F22" t="n">
         <v>1168600</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399452209473</v>
+        <v>16.19399261474609</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317271869031</v>
+        <v>16.48317077728191</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977404114256</v>
+        <v>16.13977214018008</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702630593487</v>
+        <v>16.44702436878384</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -892,16 +892,16 @@
         <v>43808</v>
       </c>
       <c r="B24" t="n">
-        <v>16.26628684997559</v>
+        <v>16.26628875732422</v>
       </c>
       <c r="C24" t="n">
-        <v>16.37472952070938</v>
+        <v>16.37473144077376</v>
       </c>
       <c r="D24" t="n">
-        <v>16.21206637642758</v>
+        <v>16.21206827741844</v>
       </c>
       <c r="E24" t="n">
-        <v>16.33858138925219</v>
+        <v>16.33858330507792</v>
       </c>
       <c r="F24" t="n">
         <v>474400</v>
@@ -912,16 +912,16 @@
         <v>43809</v>
       </c>
       <c r="B25" t="n">
-        <v>16.71813011169434</v>
+        <v>16.71813201904297</v>
       </c>
       <c r="C25" t="n">
-        <v>16.97116189065127</v>
+        <v>16.97116382686796</v>
       </c>
       <c r="D25" t="n">
-        <v>16.21206827741844</v>
+        <v>16.21207012703117</v>
       </c>
       <c r="E25" t="n">
-        <v>16.35665737292584</v>
+        <v>16.35665923903454</v>
       </c>
       <c r="F25" t="n">
         <v>1162400</v>
@@ -972,16 +972,16 @@
         <v>43812</v>
       </c>
       <c r="B28" t="n">
-        <v>16.71813011169434</v>
+        <v>16.71813201904297</v>
       </c>
       <c r="C28" t="n">
-        <v>17.50433482669905</v>
+        <v>17.50433682374471</v>
       </c>
       <c r="D28" t="n">
-        <v>16.28436282517214</v>
+        <v>16.28436468303286</v>
       </c>
       <c r="E28" t="n">
-        <v>17.50433482669905</v>
+        <v>17.50433682374471</v>
       </c>
       <c r="F28" t="n">
         <v>3257200</v>
@@ -1012,16 +1012,16 @@
         <v>43816</v>
       </c>
       <c r="B30" t="n">
-        <v>16.71813011169434</v>
+        <v>16.71813201904297</v>
       </c>
       <c r="C30" t="n">
-        <v>16.89886734289757</v>
+        <v>16.89886927086627</v>
       </c>
       <c r="D30" t="n">
-        <v>16.51932053628116</v>
+        <v>16.51932242094788</v>
       </c>
       <c r="E30" t="n">
-        <v>16.85368217327778</v>
+        <v>16.85368409609136</v>
       </c>
       <c r="F30" t="n">
         <v>664900</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436279296875</v>
+        <v>16.28436088562012</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51932050361312</v>
+        <v>16.51931856874445</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444737168</v>
+        <v>15.81444551937144</v>
       </c>
       <c r="E33" t="n">
-        <v>16.40184078647195</v>
+        <v>16.4018388653634</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1092,16 +1092,16 @@
         <v>43822</v>
       </c>
       <c r="B34" t="n">
-        <v>16.38376808166504</v>
+        <v>16.38376617431641</v>
       </c>
       <c r="C34" t="n">
-        <v>16.60968877719821</v>
+        <v>16.60968684354858</v>
       </c>
       <c r="D34" t="n">
-        <v>16.09458986716468</v>
+        <v>16.09458799348129</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31147352803995</v>
+        <v>16.31147162910763</v>
       </c>
       <c r="F34" t="n">
         <v>766700</v>
@@ -1112,16 +1112,16 @@
         <v>43825</v>
       </c>
       <c r="B35" t="n">
-        <v>16.51931953430176</v>
+        <v>16.51932144165039</v>
       </c>
       <c r="C35" t="n">
-        <v>16.59161407767043</v>
+        <v>16.59161599336631</v>
       </c>
       <c r="D35" t="n">
-        <v>16.37473044756441</v>
+        <v>16.37473233821854</v>
       </c>
       <c r="E35" t="n">
-        <v>16.59161407767043</v>
+        <v>16.59161599336631</v>
       </c>
       <c r="F35" t="n">
         <v>1111500</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739166259766</v>
+        <v>16.53739356994629</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872323828566</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821349287934</v>
+        <v>16.24821536687546</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872323828566</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620643793902</v>
+        <v>16.73620446892584</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813236765218</v>
+        <v>16.71813040076541</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -34275,16 +34275,36 @@
         <v>8</v>
       </c>
       <c r="C1693" t="n">
-        <v>8.02</v>
+        <v>8.020000457763672</v>
       </c>
       <c r="D1693" t="n">
-        <v>7.41</v>
+        <v>7.409999847412109</v>
       </c>
       <c r="E1693" t="n">
-        <v>7.57</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="F1693" t="n">
         <v>10649900</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1694" t="n">
+        <v>7.849999904632568</v>
+      </c>
+      <c r="C1694" t="n">
+        <v>8.140000343322754</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>7.849999904632568</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>8.010000228881836</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>8795000</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518394470215</v>
+        <v>15.99518585205078</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073600044276</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008337506717</v>
+        <v>15.48008522099254</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073600044276</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439113616943</v>
+        <v>15.06439208984375</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869618523321</v>
+        <v>14.64869711259133</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291838990186</v>
+        <v>14.70291932069259</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572238922119</v>
+        <v>15.14572143554688</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186880124062</v>
+        <v>15.18186784529029</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195510316014</v>
+        <v>14.71195417679867</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113329386751</v>
+        <v>15.00113234929747</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.4981575012207</v>
+        <v>15.49815845489502</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52526860192735</v>
+        <v>15.52526955726993</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209568682876</v>
+        <v>14.99209660936272</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15475884379279</v>
+        <v>15.15475977633618</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399261474609</v>
+        <v>16.19399452209473</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317077728191</v>
+        <v>16.48317271869031</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977214018008</v>
+        <v>16.13977404114256</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702436878384</v>
+        <v>16.44702630593487</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -1052,16 +1052,16 @@
         <v>43818</v>
       </c>
       <c r="B32" t="n">
-        <v>16.40184211730957</v>
+        <v>16.40184020996094</v>
       </c>
       <c r="C32" t="n">
-        <v>16.59161639745967</v>
+        <v>16.59161446804244</v>
       </c>
       <c r="D32" t="n">
-        <v>16.33858459847224</v>
+        <v>16.33858269847974</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35665866775094</v>
+        <v>16.35665676565663</v>
       </c>
       <c r="F32" t="n">
         <v>961700</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436088562012</v>
+        <v>16.28436279296875</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51931856874445</v>
+        <v>16.51932050361312</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444551937144</v>
+        <v>15.81444737168</v>
       </c>
       <c r="E33" t="n">
-        <v>16.4018388653634</v>
+        <v>16.40184078647195</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1092,16 +1092,16 @@
         <v>43822</v>
       </c>
       <c r="B34" t="n">
-        <v>16.38376617431641</v>
+        <v>16.38376808166504</v>
       </c>
       <c r="C34" t="n">
-        <v>16.60968684354858</v>
+        <v>16.60968877719821</v>
       </c>
       <c r="D34" t="n">
-        <v>16.09458799348129</v>
+        <v>16.09458986716468</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31147162910763</v>
+        <v>16.31147352803995</v>
       </c>
       <c r="F34" t="n">
         <v>766700</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21206855773926</v>
+        <v>16.21206665039062</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620446892584</v>
+        <v>16.73620249991266</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21206855773926</v>
+        <v>16.21206665039062</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813040076541</v>
+        <v>16.71812843387864</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -34049,262 +34049,262 @@
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B1682" t="n">
-        <v>8.909999847412109</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="C1682" t="n">
-        <v>9.229999542236328</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="D1682" t="n">
-        <v>8.880000114440918</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="E1682" t="n">
-        <v>9.170000076293945</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="F1682" t="n">
-        <v>7898200</v>
+        <v>6481600</v>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B1683" t="n">
-        <v>8.670000076293945</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="C1683" t="n">
-        <v>9.100000381469727</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="D1683" t="n">
-        <v>8.579999923706055</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="E1683" t="n">
-        <v>8.899999618530273</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="F1683" t="n">
-        <v>6481600</v>
+        <v>7526600</v>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B1684" t="n">
-        <v>8.380000114440918</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="C1684" t="n">
-        <v>8.710000038146973</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="D1684" t="n">
-        <v>8.359999656677246</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E1684" t="n">
-        <v>8.699999809265137</v>
+        <v>8.390000343322754</v>
       </c>
       <c r="F1684" t="n">
-        <v>7526600</v>
+        <v>7704200</v>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B1685" t="n">
-        <v>8.159999847412109</v>
+        <v>8</v>
       </c>
       <c r="C1685" t="n">
-        <v>8.529999732971191</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="D1685" t="n">
-        <v>8.100000381469727</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="E1685" t="n">
-        <v>8.390000343322754</v>
+        <v>8.109999656677246</v>
       </c>
       <c r="F1685" t="n">
-        <v>7704200</v>
+        <v>8377800</v>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B1686" t="n">
-        <v>8</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="C1686" t="n">
-        <v>8.149999618530273</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="D1686" t="n">
-        <v>7.880000114440918</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="E1686" t="n">
-        <v>8.109999656677246</v>
+        <v>7.96999979019165</v>
       </c>
       <c r="F1686" t="n">
-        <v>8377800</v>
+        <v>6506700</v>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B1687" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="C1687" t="n">
         <v>7.840000152587891</v>
       </c>
-      <c r="C1687" t="n">
-        <v>8.079999923706055</v>
-      </c>
       <c r="D1687" t="n">
-        <v>7.809999942779541</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="E1687" t="n">
-        <v>7.96999979019165</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="F1687" t="n">
-        <v>6506700</v>
+        <v>10354900</v>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B1688" t="n">
-        <v>7.380000114440918</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="C1688" t="n">
-        <v>7.840000152587891</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="D1688" t="n">
-        <v>7.380000114440918</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="E1688" t="n">
-        <v>7.829999923706055</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="F1688" t="n">
-        <v>10354900</v>
+        <v>17490500</v>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B1689" t="n">
-        <v>7.440000057220459</v>
+        <v>7.28000020980835</v>
       </c>
       <c r="C1689" t="n">
-        <v>7.599999904632568</v>
+        <v>7.5</v>
       </c>
       <c r="D1689" t="n">
-        <v>7.329999923706055</v>
+        <v>7.190000057220459</v>
       </c>
       <c r="E1689" t="n">
-        <v>7.570000171661377</v>
+        <v>7.369999885559082</v>
       </c>
       <c r="F1689" t="n">
-        <v>17490500</v>
+        <v>13406400</v>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B1690" t="n">
-        <v>7.28000020980835</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="C1690" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="D1690" t="n">
-        <v>7.190000057220459</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="E1690" t="n">
-        <v>7.369999885559082</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="F1690" t="n">
-        <v>13406400</v>
+        <v>14627600</v>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B1691" t="n">
-        <v>7.639999866485596</v>
+        <v>7.5</v>
       </c>
       <c r="C1691" t="n">
-        <v>7.75</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="D1691" t="n">
-        <v>7.329999923706055</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="E1691" t="n">
-        <v>7.349999904632568</v>
+        <v>7.519999980926514</v>
       </c>
       <c r="F1691" t="n">
-        <v>14627600</v>
+        <v>7458400</v>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B1692" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="C1692" t="n">
-        <v>7.699999809265137</v>
+        <v>8.020000457763672</v>
       </c>
       <c r="D1692" t="n">
-        <v>7.440000057220459</v>
+        <v>7.409999847412109</v>
       </c>
       <c r="E1692" t="n">
-        <v>7.519999980926514</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="F1692" t="n">
-        <v>7458400</v>
+        <v>10649900</v>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B1693" t="n">
-        <v>8</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="C1693" t="n">
-        <v>8.020000457763672</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="D1693" t="n">
-        <v>7.409999847412109</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="E1693" t="n">
-        <v>7.570000171661377</v>
+        <v>8.010000228881836</v>
       </c>
       <c r="F1693" t="n">
-        <v>10649900</v>
+        <v>8845600</v>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B1694" t="n">
-        <v>7.849999904632568</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="C1694" t="n">
-        <v>8.140000343322754</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D1694" t="n">
-        <v>7.849999904632568</v>
+        <v>7.81</v>
       </c>
       <c r="E1694" t="n">
-        <v>8.010000228881836</v>
+        <v>7.85</v>
       </c>
       <c r="F1694" t="n">
-        <v>8795000</v>
+        <v>13550500</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1696"/>
+  <dimension ref="A1:F1698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34331,12 +34331,60 @@
       <c r="A1696" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B1696" t="inlineStr"/>
-      <c r="C1696" t="inlineStr"/>
-      <c r="D1696" t="inlineStr"/>
-      <c r="E1696" t="inlineStr"/>
+      <c r="B1696" t="n">
+        <v>8.260000228881836</v>
+      </c>
+      <c r="C1696" t="n">
+        <v>8.470000267028809</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>8.090000152587891</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>8.210000038146973</v>
+      </c>
       <c r="F1696" t="n">
-        <v>12184400</v>
+        <v>12209800</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1697" t="n">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="C1697" t="n">
+        <v>8.470000267028809</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>8.159999847412109</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>8.340000152587891</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>19293200</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="C1698" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>12959100</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1699"/>
+  <dimension ref="A1:F1700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>43775</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1307373046875</v>
+        <v>16.13073921203613</v>
       </c>
       <c r="C3" t="n">
-        <v>16.32050985334077</v>
+        <v>16.3205117831287</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94096303239619</v>
+        <v>15.94096491730532</v>
       </c>
       <c r="E3" t="n">
-        <v>16.26628937138813</v>
+        <v>16.26629129476486</v>
       </c>
       <c r="F3" t="n">
         <v>1352600</v>
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518489837646</v>
+        <v>15.99518585205078</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073696219904</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008429802985</v>
+        <v>15.48008522099254</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073696219904</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572238922119</v>
+        <v>15.14572143554688</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186880124062</v>
+        <v>15.18186784529029</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195510316014</v>
+        <v>14.71195417679867</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113329386751</v>
+        <v>15.00113234929747</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49815845489502</v>
+        <v>15.4981575012207</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52526955726993</v>
+        <v>15.52526860192735</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209660936272</v>
+        <v>14.99209568682876</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15475977633618</v>
+        <v>15.15475884379279</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -832,16 +832,16 @@
         <v>43803</v>
       </c>
       <c r="B21" t="n">
-        <v>16.1036262512207</v>
+        <v>16.10362434387207</v>
       </c>
       <c r="C21" t="n">
-        <v>16.19399487051062</v>
+        <v>16.19399295245853</v>
       </c>
       <c r="D21" t="n">
-        <v>15.74215349769909</v>
+        <v>15.74215163316408</v>
       </c>
       <c r="E21" t="n">
-        <v>16.04036873480918</v>
+        <v>16.0403668349529</v>
       </c>
       <c r="F21" t="n">
         <v>976000</v>
@@ -932,16 +932,16 @@
         <v>43810</v>
       </c>
       <c r="B26" t="n">
-        <v>17.48626327514648</v>
+        <v>17.48626136779785</v>
       </c>
       <c r="C26" t="n">
-        <v>17.84773606593138</v>
+        <v>17.84773411915439</v>
       </c>
       <c r="D26" t="n">
-        <v>16.92597915670124</v>
+        <v>16.9259773104667</v>
       </c>
       <c r="E26" t="n">
-        <v>16.98020136804764</v>
+        <v>16.98019951589871</v>
       </c>
       <c r="F26" t="n">
         <v>2363200</v>
@@ -952,16 +952,16 @@
         <v>43811</v>
       </c>
       <c r="B27" t="n">
-        <v>17.3055248260498</v>
+        <v>17.30552291870117</v>
       </c>
       <c r="C27" t="n">
-        <v>17.82966076749858</v>
+        <v>17.82965880238169</v>
       </c>
       <c r="D27" t="n">
-        <v>17.17900978889814</v>
+        <v>17.1790078954935</v>
       </c>
       <c r="E27" t="n">
-        <v>17.66699759193894</v>
+        <v>17.66699564475017</v>
       </c>
       <c r="F27" t="n">
         <v>1801300</v>
@@ -1052,16 +1052,16 @@
         <v>43818</v>
       </c>
       <c r="B32" t="n">
-        <v>16.40184211730957</v>
+        <v>16.40184020996094</v>
       </c>
       <c r="C32" t="n">
-        <v>16.59161639745967</v>
+        <v>16.59161446804244</v>
       </c>
       <c r="D32" t="n">
-        <v>16.33858459847224</v>
+        <v>16.33858269847974</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35665866775094</v>
+        <v>16.35665676565663</v>
       </c>
       <c r="F32" t="n">
         <v>961700</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436279296875</v>
+        <v>16.28436088562012</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51932050361312</v>
+        <v>16.51931856874445</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444737168</v>
+        <v>15.81444551937144</v>
       </c>
       <c r="E33" t="n">
-        <v>16.40184078647195</v>
+        <v>16.4018388653634</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739166259766</v>
+        <v>16.53739356994629</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872323828566</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821349287934</v>
+        <v>16.24821536687546</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872323828566</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620643793902</v>
+        <v>16.73620446892584</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813236765218</v>
+        <v>16.71813040076541</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -1192,16 +1192,16 @@
         <v>43833</v>
       </c>
       <c r="B39" t="n">
-        <v>16.49941253662109</v>
+        <v>16.49941062927246</v>
       </c>
       <c r="C39" t="n">
-        <v>16.67357349182081</v>
+        <v>16.673571564339</v>
       </c>
       <c r="D39" t="n">
-        <v>16.20608992681567</v>
+        <v>16.20608805337542</v>
       </c>
       <c r="E39" t="n">
-        <v>16.22442302701367</v>
+        <v>16.22442115145411</v>
       </c>
       <c r="F39" t="n">
         <v>1551100</v>
@@ -1212,16 +1212,16 @@
         <v>43836</v>
       </c>
       <c r="B40" t="n">
-        <v>16.32525253295898</v>
+        <v>16.32525062561035</v>
       </c>
       <c r="C40" t="n">
-        <v>16.5819107056687</v>
+        <v>16.58190876833361</v>
       </c>
       <c r="D40" t="n">
-        <v>16.3160859823257</v>
+        <v>16.31608407604803</v>
       </c>
       <c r="E40" t="n">
-        <v>16.49941349830989</v>
+        <v>16.49941157061329</v>
       </c>
       <c r="F40" t="n">
         <v>970100</v>
@@ -1272,16 +1272,16 @@
         <v>43839</v>
       </c>
       <c r="B43" t="n">
-        <v>14.40032005310059</v>
+        <v>14.4003210067749</v>
       </c>
       <c r="C43" t="n">
-        <v>15.28945527034375</v>
+        <v>15.28945628290185</v>
       </c>
       <c r="D43" t="n">
-        <v>14.30865630420819</v>
+        <v>14.30865725181199</v>
       </c>
       <c r="E43" t="n">
-        <v>15.09696122283566</v>
+        <v>15.09696222264567</v>
       </c>
       <c r="F43" t="n">
         <v>3315800</v>
@@ -1332,16 +1332,16 @@
         <v>43844</v>
       </c>
       <c r="B46" t="n">
-        <v>15.7202730178833</v>
+        <v>15.72027206420898</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74777266775395</v>
+        <v>15.74777171241136</v>
       </c>
       <c r="D46" t="n">
-        <v>15.2436229101692</v>
+        <v>15.24362198541098</v>
       </c>
       <c r="E46" t="n">
-        <v>15.35361976131116</v>
+        <v>15.35361882987996</v>
       </c>
       <c r="F46" t="n">
         <v>2831800</v>
@@ -1352,16 +1352,16 @@
         <v>43845</v>
       </c>
       <c r="B47" t="n">
-        <v>15.76610469818115</v>
+        <v>15.76610565185547</v>
       </c>
       <c r="C47" t="n">
-        <v>15.76610469818115</v>
+        <v>15.76610565185547</v>
       </c>
       <c r="D47" t="n">
-        <v>15.3536187198054</v>
+        <v>15.35361964852889</v>
       </c>
       <c r="E47" t="n">
-        <v>15.72027195150578</v>
+        <v>15.72027290240772</v>
       </c>
       <c r="F47" t="n">
         <v>1838000</v>
@@ -1372,16 +1372,16 @@
         <v>43846</v>
       </c>
       <c r="B48" t="n">
-        <v>16.10525703430176</v>
+        <v>16.10525894165039</v>
       </c>
       <c r="C48" t="n">
-        <v>16.34358205353058</v>
+        <v>16.34358398910408</v>
       </c>
       <c r="D48" t="n">
-        <v>15.56444290380952</v>
+        <v>15.56444474710943</v>
       </c>
       <c r="E48" t="n">
-        <v>15.76610347687872</v>
+        <v>15.76610534406134</v>
       </c>
       <c r="F48" t="n">
         <v>3608000</v>
@@ -1392,16 +1392,16 @@
         <v>43847</v>
       </c>
       <c r="B49" t="n">
-        <v>16.31608581542969</v>
+        <v>16.31608390808105</v>
       </c>
       <c r="C49" t="n">
-        <v>16.31608581542969</v>
+        <v>16.31608390808105</v>
       </c>
       <c r="D49" t="n">
-        <v>15.93109943447349</v>
+        <v>15.93109757212972</v>
       </c>
       <c r="E49" t="n">
-        <v>16.22442380671596</v>
+        <v>16.2244219100826</v>
       </c>
       <c r="F49" t="n">
         <v>2719000</v>
@@ -1492,16 +1492,16 @@
         <v>43854</v>
       </c>
       <c r="B54" t="n">
-        <v>15.73860645294189</v>
+        <v>15.73860740661621</v>
       </c>
       <c r="C54" t="n">
-        <v>15.80277055566578</v>
+        <v>15.80277151322809</v>
       </c>
       <c r="D54" t="n">
-        <v>15.39945109067764</v>
+        <v>15.39945202380098</v>
       </c>
       <c r="E54" t="n">
-        <v>15.57361204688581</v>
+        <v>15.57361299056236</v>
       </c>
       <c r="F54" t="n">
         <v>887500</v>
@@ -1552,16 +1552,16 @@
         <v>43859</v>
       </c>
       <c r="B57" t="n">
-        <v>15.21612453460693</v>
+        <v>15.21612548828125</v>
       </c>
       <c r="C57" t="n">
-        <v>15.64694187911524</v>
+        <v>15.64694285979114</v>
       </c>
       <c r="D57" t="n">
-        <v>15.16112698491963</v>
+        <v>15.16112793514696</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4086168326828</v>
+        <v>15.40861779842162</v>
       </c>
       <c r="F57" t="n">
         <v>686700</v>
@@ -1592,16 +1592,16 @@
         <v>43861</v>
       </c>
       <c r="B59" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C59" t="n">
-        <v>15.21612414517745</v>
+        <v>15.21612513461457</v>
       </c>
       <c r="D59" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="E59" t="n">
-        <v>14.94113290709765</v>
+        <v>14.94113387865332</v>
       </c>
       <c r="F59" t="n">
         <v>897400</v>
@@ -1612,16 +1612,16 @@
         <v>43864</v>
       </c>
       <c r="B60" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C60" t="n">
-        <v>15.01446355425082</v>
+        <v>15.01446453057486</v>
       </c>
       <c r="D60" t="n">
-        <v>14.59281277020523</v>
+        <v>14.59281371911118</v>
       </c>
       <c r="E60" t="n">
-        <v>14.73030751507486</v>
+        <v>14.73030847292148</v>
       </c>
       <c r="F60" t="n">
         <v>1344600</v>
@@ -1632,16 +1632,16 @@
         <v>43865</v>
       </c>
       <c r="B61" t="n">
-        <v>14.92280197143555</v>
+        <v>14.92280292510986</v>
       </c>
       <c r="C61" t="n">
-        <v>15.03279707105302</v>
+        <v>15.03279803175682</v>
       </c>
       <c r="D61" t="n">
-        <v>14.6844769244769</v>
+        <v>14.68447786292053</v>
       </c>
       <c r="E61" t="n">
-        <v>14.92280197143555</v>
+        <v>14.92280292510986</v>
       </c>
       <c r="F61" t="n">
         <v>708300</v>
@@ -1752,16 +1752,16 @@
         <v>43873</v>
       </c>
       <c r="B67" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C67" t="n">
-        <v>14.757807163385</v>
+        <v>14.7578081230198</v>
       </c>
       <c r="D67" t="n">
-        <v>14.29949018159255</v>
+        <v>14.29949111142503</v>
       </c>
       <c r="E67" t="n">
-        <v>14.29949018159255</v>
+        <v>14.29949111142503</v>
       </c>
       <c r="F67" t="n">
         <v>2320900</v>
@@ -1832,16 +1832,16 @@
         <v>43879</v>
       </c>
       <c r="B71" t="n">
-        <v>15.48194694519043</v>
+        <v>15.48194789886475</v>
       </c>
       <c r="C71" t="n">
-        <v>15.57361069038642</v>
+        <v>15.57361164970714</v>
       </c>
       <c r="D71" t="n">
-        <v>14.48281666823953</v>
+        <v>14.4828175603683</v>
       </c>
       <c r="E71" t="n">
-        <v>14.64781018575394</v>
+        <v>14.64781108804616</v>
       </c>
       <c r="F71" t="n">
         <v>4553800</v>
@@ -1892,16 +1892,16 @@
         <v>43882</v>
       </c>
       <c r="B74" t="n">
-        <v>16.04109573364258</v>
+        <v>16.04109382629395</v>
       </c>
       <c r="C74" t="n">
-        <v>16.04109573364258</v>
+        <v>16.04109382629395</v>
       </c>
       <c r="D74" t="n">
-        <v>15.43611740584103</v>
+        <v>15.43611557042667</v>
       </c>
       <c r="E74" t="n">
-        <v>15.63777626566132</v>
+        <v>15.63777440626894</v>
       </c>
       <c r="F74" t="n">
         <v>1940300</v>
@@ -1932,16 +1932,16 @@
         <v>43888</v>
       </c>
       <c r="B76" t="n">
-        <v>14.47365188598633</v>
+        <v>14.47365093231201</v>
       </c>
       <c r="C76" t="n">
-        <v>14.88613704138841</v>
+        <v>14.88613606053529</v>
       </c>
       <c r="D76" t="n">
-        <v>14.09783205830509</v>
+        <v>14.09783112939368</v>
       </c>
       <c r="E76" t="n">
-        <v>14.56531564237362</v>
+        <v>14.56531468265955</v>
       </c>
       <c r="F76" t="n">
         <v>1056800</v>
@@ -2032,16 +2032,16 @@
         <v>43895</v>
       </c>
       <c r="B81" t="n">
-        <v>13.29119396209717</v>
+        <v>13.29119300842285</v>
       </c>
       <c r="C81" t="n">
-        <v>14.68447816255327</v>
+        <v>14.68447710890754</v>
       </c>
       <c r="D81" t="n">
-        <v>13.22702985718708</v>
+        <v>13.22702890811669</v>
       </c>
       <c r="E81" t="n">
-        <v>14.62031318347281</v>
+        <v>14.62031213443108</v>
       </c>
       <c r="F81" t="n">
         <v>2239700</v>
@@ -2172,16 +2172,16 @@
         <v>43906</v>
       </c>
       <c r="B88" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="C88" t="n">
-        <v>8.918848503012144</v>
+        <v>8.918849065390972</v>
       </c>
       <c r="D88" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="E88" t="n">
-        <v>8.918848503012144</v>
+        <v>8.918849065390972</v>
       </c>
       <c r="F88" t="n">
         <v>1319600</v>
@@ -2252,16 +2252,16 @@
         <v>43910</v>
       </c>
       <c r="B92" t="n">
-        <v>5.820626258850098</v>
+        <v>5.820625782012939</v>
       </c>
       <c r="C92" t="n">
-        <v>6.508101811558814</v>
+        <v>6.508101278402306</v>
       </c>
       <c r="D92" t="n">
-        <v>5.756462153665136</v>
+        <v>5.756461682084427</v>
       </c>
       <c r="E92" t="n">
-        <v>6.278943293989242</v>
+        <v>6.27894277960585</v>
       </c>
       <c r="F92" t="n">
         <v>2218000</v>
@@ -2332,16 +2332,16 @@
         <v>43916</v>
       </c>
       <c r="B96" t="n">
-        <v>6.874755382537842</v>
+        <v>6.874754905700684</v>
       </c>
       <c r="C96" t="n">
-        <v>7.653894675560271</v>
+        <v>7.653894144681544</v>
       </c>
       <c r="D96" t="n">
-        <v>6.29727582550422</v>
+        <v>6.297275388721391</v>
       </c>
       <c r="E96" t="n">
-        <v>6.471436347645401</v>
+        <v>6.471435898782693</v>
       </c>
       <c r="F96" t="n">
         <v>4787500</v>
@@ -2432,16 +2432,16 @@
         <v>43923</v>
       </c>
       <c r="B101" t="n">
-        <v>5.536469459533691</v>
+        <v>5.536468982696533</v>
       </c>
       <c r="C101" t="n">
-        <v>5.793127178086285</v>
+        <v>5.793126679144077</v>
       </c>
       <c r="D101" t="n">
-        <v>5.334810166952138</v>
+        <v>5.334809707483203</v>
       </c>
       <c r="E101" t="n">
-        <v>5.408140818799975</v>
+        <v>5.408140353015323</v>
       </c>
       <c r="F101" t="n">
         <v>2769000</v>
@@ -2452,16 +2452,16 @@
         <v>43924</v>
       </c>
       <c r="B102" t="n">
-        <v>5.582301139831543</v>
+        <v>5.582300662994385</v>
       </c>
       <c r="C102" t="n">
-        <v>5.71062977606757</v>
+        <v>5.710629288268649</v>
       </c>
       <c r="D102" t="n">
-        <v>5.068986157802285</v>
+        <v>5.068985724812216</v>
       </c>
       <c r="E102" t="n">
-        <v>5.609799914768118</v>
+        <v>5.609799435582029</v>
       </c>
       <c r="F102" t="n">
         <v>3057300</v>
@@ -2492,16 +2492,16 @@
         <v>43928</v>
       </c>
       <c r="B104" t="n">
-        <v>7.342238426208496</v>
+        <v>7.342238903045654</v>
       </c>
       <c r="C104" t="n">
-        <v>7.846387292556186</v>
+        <v>7.846387802134982</v>
       </c>
       <c r="D104" t="n">
-        <v>6.608931063718246</v>
+        <v>6.608931492931209</v>
       </c>
       <c r="E104" t="n">
-        <v>6.773925023590238</v>
+        <v>6.773925463518632</v>
       </c>
       <c r="F104" t="n">
         <v>4216400</v>
@@ -2532,16 +2532,16 @@
         <v>43930</v>
       </c>
       <c r="B106" t="n">
-        <v>7.883052349090576</v>
+        <v>7.883052825927734</v>
       </c>
       <c r="C106" t="n">
-        <v>8.653024135661383</v>
+        <v>8.653024659073285</v>
       </c>
       <c r="D106" t="n">
-        <v>7.718057957740275</v>
+        <v>7.718058424597103</v>
       </c>
       <c r="E106" t="n">
-        <v>8.121376512610697</v>
+        <v>8.12137700386382</v>
       </c>
       <c r="F106" t="n">
         <v>2853400</v>
@@ -2672,16 +2672,16 @@
         <v>43943</v>
       </c>
       <c r="B113" t="n">
-        <v>8.983012199401855</v>
+        <v>8.983013153076172</v>
       </c>
       <c r="C113" t="n">
-        <v>9.28550130988736</v>
+        <v>9.285502295675192</v>
       </c>
       <c r="D113" t="n">
-        <v>8.57052712820982</v>
+        <v>8.570528038092988</v>
       </c>
       <c r="E113" t="n">
-        <v>8.579692802641055</v>
+        <v>8.57969371349729</v>
       </c>
       <c r="F113" t="n">
         <v>2037400</v>
@@ -2732,16 +2732,16 @@
         <v>43948</v>
       </c>
       <c r="B116" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C116" t="n">
-        <v>7.947216534214704</v>
+        <v>7.947217050986978</v>
       </c>
       <c r="D116" t="n">
-        <v>7.296406385102614</v>
+        <v>7.296406859555589</v>
       </c>
       <c r="E116" t="n">
-        <v>7.928883435341277</v>
+        <v>7.928883950921431</v>
       </c>
       <c r="F116" t="n">
         <v>2360400</v>
@@ -2772,16 +2772,16 @@
         <v>43950</v>
       </c>
       <c r="B118" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C118" t="n">
-        <v>9.166340069149538</v>
+        <v>9.166339110682868</v>
       </c>
       <c r="D118" t="n">
-        <v>8.258872612104607</v>
+        <v>8.258871748526117</v>
       </c>
       <c r="E118" t="n">
-        <v>8.442199238653536</v>
+        <v>8.442198355905731</v>
       </c>
       <c r="F118" t="n">
         <v>3867700</v>
@@ -2852,16 +2852,16 @@
         <v>43957</v>
       </c>
       <c r="B122" t="n">
-        <v>7.828054904937744</v>
+        <v>7.828054428100586</v>
       </c>
       <c r="C122" t="n">
-        <v>8.148877178372471</v>
+        <v>8.148876681992785</v>
       </c>
       <c r="D122" t="n">
-        <v>7.553064509732316</v>
+        <v>7.553064049645888</v>
       </c>
       <c r="E122" t="n">
-        <v>7.928884337705908</v>
+        <v>7.928883854726839</v>
       </c>
       <c r="F122" t="n">
         <v>2058000</v>
@@ -2912,16 +2912,16 @@
         <v>43962</v>
       </c>
       <c r="B125" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C125" t="n">
-        <v>7.058081369394968</v>
+        <v>7.058081870301661</v>
       </c>
       <c r="D125" t="n">
-        <v>6.700594244733439</v>
+        <v>6.700594720269542</v>
       </c>
       <c r="E125" t="n">
-        <v>7.058081369394968</v>
+        <v>7.058081870301661</v>
       </c>
       <c r="F125" t="n">
         <v>2505400</v>
@@ -2972,16 +2972,16 @@
         <v>43965</v>
       </c>
       <c r="B128" t="n">
-        <v>6.086450099945068</v>
+        <v>6.08644962310791</v>
       </c>
       <c r="C128" t="n">
-        <v>6.187279969987983</v>
+        <v>6.187279485251405</v>
       </c>
       <c r="D128" t="n">
-        <v>5.701463720767742</v>
+        <v>5.701463274091976</v>
       </c>
       <c r="E128" t="n">
-        <v>5.893956910356406</v>
+        <v>5.893956448599943</v>
       </c>
       <c r="F128" t="n">
         <v>4161800</v>
@@ -2992,16 +2992,16 @@
         <v>43966</v>
       </c>
       <c r="B129" t="n">
-        <v>6.049784183502197</v>
+        <v>6.049784660339355</v>
       </c>
       <c r="C129" t="n">
-        <v>6.645596358206725</v>
+        <v>6.645596882005126</v>
       </c>
       <c r="D129" t="n">
-        <v>5.857291012642501</v>
+        <v>5.857291474307565</v>
       </c>
       <c r="E129" t="n">
-        <v>6.049784183502197</v>
+        <v>6.049784660339355</v>
       </c>
       <c r="F129" t="n">
         <v>4143200</v>
@@ -3012,16 +3012,16 @@
         <v>43969</v>
       </c>
       <c r="B130" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C130" t="n">
-        <v>6.856422193632849</v>
+        <v>6.856422675624999</v>
       </c>
       <c r="D130" t="n">
-        <v>6.260610018716203</v>
+        <v>6.260610458824003</v>
       </c>
       <c r="E130" t="n">
-        <v>6.462269739252984</v>
+        <v>6.46227019353704</v>
       </c>
       <c r="F130" t="n">
         <v>4121800</v>
@@ -3032,16 +3032,16 @@
         <v>43970</v>
       </c>
       <c r="B131" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C131" t="n">
-        <v>7.553063650138711</v>
+        <v>7.55306414128097</v>
       </c>
       <c r="D131" t="n">
-        <v>6.709760770792116</v>
+        <v>6.709761207098126</v>
       </c>
       <c r="E131" t="n">
-        <v>6.828922853873451</v>
+        <v>6.828923297928043</v>
       </c>
       <c r="F131" t="n">
         <v>3759800</v>
@@ -3072,16 +3072,16 @@
         <v>43972</v>
       </c>
       <c r="B133" t="n">
-        <v>7.727224349975586</v>
+        <v>7.727224826812744</v>
       </c>
       <c r="C133" t="n">
-        <v>7.873885639674015</v>
+        <v>7.873886125561454</v>
       </c>
       <c r="D133" t="n">
-        <v>7.461400543854623</v>
+        <v>7.461401004288134</v>
       </c>
       <c r="E133" t="n">
-        <v>7.55306341283102</v>
+        <v>7.55306387892093</v>
       </c>
       <c r="F133" t="n">
         <v>2073000</v>
@@ -3112,16 +3112,16 @@
         <v>43976</v>
       </c>
       <c r="B135" t="n">
-        <v>7.75472354888916</v>
+        <v>7.754724025726318</v>
       </c>
       <c r="C135" t="n">
-        <v>7.828054197763313</v>
+        <v>7.828054679109565</v>
       </c>
       <c r="D135" t="n">
-        <v>7.397235979999946</v>
+        <v>7.39723643485523</v>
       </c>
       <c r="E135" t="n">
-        <v>7.397235979999946</v>
+        <v>7.39723643485523</v>
       </c>
       <c r="F135" t="n">
         <v>2073000</v>
@@ -3132,16 +3132,16 @@
         <v>43977</v>
       </c>
       <c r="B136" t="n">
-        <v>7.626394271850586</v>
+        <v>7.626394748687744</v>
       </c>
       <c r="C136" t="n">
-        <v>8.286370968197739</v>
+        <v>8.286371486299668</v>
       </c>
       <c r="D136" t="n">
-        <v>7.608062047208583</v>
+        <v>7.608062522899527</v>
       </c>
       <c r="E136" t="n">
-        <v>7.974715281751298</v>
+        <v>7.974715780367084</v>
       </c>
       <c r="F136" t="n">
         <v>2630000</v>
@@ -3152,16 +3152,16 @@
         <v>43978</v>
       </c>
       <c r="B137" t="n">
-        <v>8.158042907714844</v>
+        <v>8.158041954040527</v>
       </c>
       <c r="C137" t="n">
-        <v>8.158042907714844</v>
+        <v>8.158041954040527</v>
       </c>
       <c r="D137" t="n">
-        <v>7.653894866426351</v>
+        <v>7.653893971686885</v>
       </c>
       <c r="E137" t="n">
-        <v>7.745557749310453</v>
+        <v>7.745556843855605</v>
       </c>
       <c r="F137" t="n">
         <v>2323900</v>
@@ -3212,16 +3212,16 @@
         <v>43983</v>
       </c>
       <c r="B140" t="n">
-        <v>8.955513954162598</v>
+        <v>8.955514907836914</v>
       </c>
       <c r="C140" t="n">
-        <v>9.065509921334565</v>
+        <v>9.065510886722372</v>
       </c>
       <c r="D140" t="n">
-        <v>8.56136108283537</v>
+        <v>8.561361994536275</v>
       </c>
       <c r="E140" t="n">
-        <v>8.662190500867112</v>
+        <v>8.662191423305361</v>
       </c>
       <c r="F140" t="n">
         <v>3007600</v>
@@ -3332,16 +3332,16 @@
         <v>43991</v>
       </c>
       <c r="B146" t="n">
-        <v>11.93457508087158</v>
+        <v>11.93457412719727</v>
       </c>
       <c r="C146" t="n">
-        <v>12.34706020539017</v>
+        <v>12.34705921875477</v>
       </c>
       <c r="D146" t="n">
-        <v>11.0546064072858</v>
+        <v>11.05460552392848</v>
       </c>
       <c r="E146" t="n">
-        <v>11.27459835713967</v>
+        <v>11.27459745620312</v>
       </c>
       <c r="F146" t="n">
         <v>3964300</v>
@@ -3612,16 +3612,16 @@
         <v>44012</v>
       </c>
       <c r="B160" t="n">
-        <v>9.450497627258301</v>
+        <v>9.450496673583984</v>
       </c>
       <c r="C160" t="n">
-        <v>9.633824266054166</v>
+        <v>9.633823293879882</v>
       </c>
       <c r="D160" t="n">
-        <v>9.120508803255376</v>
+        <v>9.120507882881091</v>
       </c>
       <c r="E160" t="n">
-        <v>9.532993959088664</v>
+        <v>9.532992997089428</v>
       </c>
       <c r="F160" t="n">
         <v>4221600</v>
@@ -3732,16 +3732,16 @@
         <v>44020</v>
       </c>
       <c r="B166" t="n">
-        <v>10.19297122955322</v>
+        <v>10.19297027587891</v>
       </c>
       <c r="C166" t="n">
-        <v>10.94461092232337</v>
+        <v>10.94460989832417</v>
       </c>
       <c r="D166" t="n">
-        <v>10.14713934907861</v>
+        <v>10.14713839969241</v>
       </c>
       <c r="E166" t="n">
-        <v>10.77045082552434</v>
+        <v>10.7704498178199</v>
       </c>
       <c r="F166" t="n">
         <v>5151100</v>
@@ -3792,16 +3792,16 @@
         <v>44025</v>
       </c>
       <c r="B169" t="n">
-        <v>10.50462627410889</v>
+        <v>10.50462532043457</v>
       </c>
       <c r="C169" t="n">
-        <v>11.09127238227016</v>
+        <v>11.09127137533651</v>
       </c>
       <c r="D169" t="n">
-        <v>10.32129963848672</v>
+        <v>10.32129870145592</v>
       </c>
       <c r="E169" t="n">
-        <v>10.8896126460006</v>
+        <v>10.88961165737486</v>
       </c>
       <c r="F169" t="n">
         <v>4409000</v>
@@ -3932,16 +3932,16 @@
         <v>44034</v>
       </c>
       <c r="B176" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C176" t="n">
-        <v>10.00047677558407</v>
+        <v>10.00047581575137</v>
       </c>
       <c r="D176" t="n">
-        <v>9.67965540087379</v>
+        <v>9.679654471833102</v>
       </c>
       <c r="E176" t="n">
-        <v>9.881314250976148</v>
+        <v>9.881313302580509</v>
       </c>
       <c r="F176" t="n">
         <v>2365200</v>
@@ -3952,16 +3952,16 @@
         <v>44035</v>
       </c>
       <c r="B177" t="n">
-        <v>9.771317481994629</v>
+        <v>9.771318435668945</v>
       </c>
       <c r="C177" t="n">
-        <v>10.10130625383415</v>
+        <v>10.10130723971515</v>
       </c>
       <c r="D177" t="n">
-        <v>9.670488065138237</v>
+        <v>9.670489008971668</v>
       </c>
       <c r="E177" t="n">
-        <v>9.982143738911011</v>
+        <v>9.982144713161835</v>
       </c>
       <c r="F177" t="n">
         <v>2784800</v>
@@ -3972,16 +3972,16 @@
         <v>44036</v>
       </c>
       <c r="B178" t="n">
-        <v>9.578825950622559</v>
+        <v>9.578824996948242</v>
       </c>
       <c r="C178" t="n">
-        <v>9.72548726339387</v>
+        <v>9.725486295117854</v>
       </c>
       <c r="D178" t="n">
-        <v>9.193839567512681</v>
+        <v>9.193838652167866</v>
       </c>
       <c r="E178" t="n">
-        <v>9.652156607008214</v>
+        <v>9.652155646033048</v>
       </c>
       <c r="F178" t="n">
         <v>3085100</v>
@@ -4312,16 +4312,16 @@
         <v>44061</v>
       </c>
       <c r="B195" t="n">
-        <v>9.532992362976074</v>
+        <v>9.532993316650391</v>
       </c>
       <c r="C195" t="n">
-        <v>9.734652068972748</v>
+        <v>9.73465304282097</v>
       </c>
       <c r="D195" t="n">
-        <v>9.248836338961429</v>
+        <v>9.248837264208962</v>
       </c>
       <c r="E195" t="n">
-        <v>9.31300043325437</v>
+        <v>9.313001364920838</v>
       </c>
       <c r="F195" t="n">
         <v>3391400</v>
@@ -4352,16 +4352,16 @@
         <v>44063</v>
       </c>
       <c r="B197" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C197" t="n">
-        <v>9.945478824484717</v>
+        <v>9.945479787030456</v>
       </c>
       <c r="D197" t="n">
-        <v>9.010511764854147</v>
+        <v>9.010512636911677</v>
       </c>
       <c r="E197" t="n">
-        <v>9.074675862376543</v>
+        <v>9.074676740644019</v>
       </c>
       <c r="F197" t="n">
         <v>3999100</v>
@@ -4372,16 +4372,16 @@
         <v>44064</v>
       </c>
       <c r="B198" t="n">
-        <v>10.38546276092529</v>
+        <v>10.38546371459961</v>
       </c>
       <c r="C198" t="n">
-        <v>10.54129060502008</v>
+        <v>10.54129157300373</v>
       </c>
       <c r="D198" t="n">
-        <v>9.652155413568103</v>
+        <v>9.65215629990441</v>
       </c>
       <c r="E198" t="n">
-        <v>9.85381513077964</v>
+        <v>9.853816035633919</v>
       </c>
       <c r="F198" t="n">
         <v>4055100</v>
@@ -4392,16 +4392,16 @@
         <v>44067</v>
       </c>
       <c r="B199" t="n">
-        <v>10.22046947479248</v>
+        <v>10.22046852111816</v>
       </c>
       <c r="C199" t="n">
-        <v>10.74295148626354</v>
+        <v>10.7429504838363</v>
       </c>
       <c r="D199" t="n">
-        <v>10.16547192042944</v>
+        <v>10.16547097188696</v>
       </c>
       <c r="E199" t="n">
-        <v>10.54129174720154</v>
+        <v>10.54129076359123</v>
       </c>
       <c r="F199" t="n">
         <v>2579200</v>
@@ -4472,16 +4472,16 @@
         <v>44071</v>
       </c>
       <c r="B203" t="n">
-        <v>11.07293891906738</v>
+        <v>11.07293796539307</v>
       </c>
       <c r="C203" t="n">
-        <v>11.12793734503842</v>
+        <v>11.12793638662728</v>
       </c>
       <c r="D203" t="n">
-        <v>10.3579646264658</v>
+        <v>10.35796373436977</v>
       </c>
       <c r="E203" t="n">
-        <v>10.51379248018504</v>
+        <v>10.51379157466809</v>
       </c>
       <c r="F203" t="n">
         <v>2710200</v>
@@ -4512,16 +4512,16 @@
         <v>44075</v>
       </c>
       <c r="B205" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="C205" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="D205" t="n">
-        <v>10.96294209712684</v>
+        <v>10.96294298891299</v>
       </c>
       <c r="E205" t="n">
-        <v>11.14626871262991</v>
+        <v>11.14626961932886</v>
       </c>
       <c r="F205" t="n">
         <v>3676800</v>
@@ -4652,16 +4652,16 @@
         <v>44085</v>
       </c>
       <c r="B212" t="n">
-        <v>10.83461380004883</v>
+        <v>10.83461284637451</v>
       </c>
       <c r="C212" t="n">
-        <v>11.54958896263513</v>
+        <v>11.54958794602793</v>
       </c>
       <c r="D212" t="n">
-        <v>10.66962027144226</v>
+        <v>10.66961933229085</v>
       </c>
       <c r="E212" t="n">
-        <v>11.43959211133699</v>
+        <v>11.43959110441184</v>
       </c>
       <c r="F212" t="n">
         <v>2696500</v>
@@ -4692,16 +4692,16 @@
         <v>44089</v>
       </c>
       <c r="B214" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="C214" t="n">
-        <v>12.09956866086264</v>
+        <v>12.09956963671544</v>
       </c>
       <c r="D214" t="n">
-        <v>11.62291943402496</v>
+        <v>11.62292037143511</v>
       </c>
       <c r="E214" t="n">
-        <v>12.017071460752</v>
+        <v>12.01707242995125</v>
       </c>
       <c r="F214" t="n">
         <v>2177400</v>
@@ -4772,16 +4772,16 @@
         <v>44095</v>
       </c>
       <c r="B218" t="n">
-        <v>11.32043075561523</v>
+        <v>11.32042980194092</v>
       </c>
       <c r="C218" t="n">
-        <v>11.73291589921649</v>
+        <v>11.73291491079292</v>
       </c>
       <c r="D218" t="n">
-        <v>11.00877504181907</v>
+        <v>11.00877411439977</v>
       </c>
       <c r="E218" t="n">
-        <v>11.70541712275516</v>
+        <v>11.70541613664819</v>
       </c>
       <c r="F218" t="n">
         <v>2982400</v>
@@ -4872,16 +4872,16 @@
         <v>44102</v>
       </c>
       <c r="B223" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C223" t="n">
-        <v>11.44875714774106</v>
+        <v>11.44875814201422</v>
       </c>
       <c r="D223" t="n">
-        <v>10.86211201394924</v>
+        <v>10.8621129572749</v>
       </c>
       <c r="E223" t="n">
-        <v>11.39375960353318</v>
+        <v>11.39376059303005</v>
       </c>
       <c r="F223" t="n">
         <v>1430300</v>
@@ -4932,16 +4932,16 @@
         <v>44105</v>
       </c>
       <c r="B226" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C226" t="n">
-        <v>11.18293500609905</v>
+        <v>11.18293403814347</v>
       </c>
       <c r="D226" t="n">
-        <v>10.58712323547157</v>
+        <v>10.58712231908736</v>
       </c>
       <c r="E226" t="n">
-        <v>10.61462201164059</v>
+        <v>10.61462109287619</v>
       </c>
       <c r="F226" t="n">
         <v>1825000</v>
@@ -4992,16 +4992,16 @@
         <v>44110</v>
       </c>
       <c r="B229" t="n">
-        <v>11.03627395629883</v>
+        <v>11.03627300262451</v>
       </c>
       <c r="C229" t="n">
-        <v>11.35709622431771</v>
+        <v>11.35709524292028</v>
       </c>
       <c r="D229" t="n">
-        <v>10.99960862916841</v>
+        <v>10.99960767866245</v>
       </c>
       <c r="E229" t="n">
-        <v>11.35709622431771</v>
+        <v>11.35709524292028</v>
       </c>
       <c r="F229" t="n">
         <v>1315200</v>
@@ -5012,16 +5012,16 @@
         <v>44111</v>
       </c>
       <c r="B230" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C230" t="n">
-        <v>11.23793231185949</v>
+        <v>11.23793329027351</v>
       </c>
       <c r="D230" t="n">
-        <v>10.81628066458053</v>
+        <v>10.81628160628407</v>
       </c>
       <c r="E230" t="n">
-        <v>11.10043669638599</v>
+        <v>11.10043766282916</v>
       </c>
       <c r="F230" t="n">
         <v>1553900</v>
@@ -5032,16 +5032,16 @@
         <v>44112</v>
       </c>
       <c r="B231" t="n">
-        <v>11.03627395629883</v>
+        <v>11.03627300262451</v>
       </c>
       <c r="C231" t="n">
-        <v>11.09127238407963</v>
+        <v>11.09127142565275</v>
       </c>
       <c r="D231" t="n">
-        <v>10.83461421999638</v>
+        <v>10.83461328374802</v>
       </c>
       <c r="E231" t="n">
-        <v>10.99960862916841</v>
+        <v>10.99960767866245</v>
       </c>
       <c r="F231" t="n">
         <v>1563000</v>
@@ -5112,16 +5112,16 @@
         <v>44119</v>
       </c>
       <c r="B235" t="n">
-        <v>11.57708835601807</v>
+        <v>11.57708740234375</v>
       </c>
       <c r="C235" t="n">
-        <v>11.62292023414239</v>
+        <v>11.62291927669263</v>
       </c>
       <c r="D235" t="n">
-        <v>10.92627813432967</v>
+        <v>10.92627723426651</v>
       </c>
       <c r="E235" t="n">
-        <v>10.99960878966045</v>
+        <v>10.99960788355659</v>
       </c>
       <c r="F235" t="n">
         <v>4442200</v>
@@ -5232,16 +5232,16 @@
         <v>44127</v>
       </c>
       <c r="B241" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="C241" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="D241" t="n">
-        <v>11.31126373323825</v>
+        <v>11.31126464551279</v>
       </c>
       <c r="E241" t="n">
-        <v>11.49459035894505</v>
+        <v>11.49459128600522</v>
       </c>
       <c r="F241" t="n">
         <v>1343300</v>
@@ -5272,16 +5272,16 @@
         <v>44131</v>
       </c>
       <c r="B243" t="n">
-        <v>11.90707588195801</v>
+        <v>11.90707492828369</v>
       </c>
       <c r="C243" t="n">
-        <v>12.45705665156882</v>
+        <v>12.45705565384485</v>
       </c>
       <c r="D243" t="n">
-        <v>11.77874767677373</v>
+        <v>11.77874673337762</v>
       </c>
       <c r="E243" t="n">
-        <v>12.20956504299285</v>
+        <v>12.20956406509125</v>
       </c>
       <c r="F243" t="n">
         <v>2061500</v>
@@ -5352,16 +5352,16 @@
         <v>44138</v>
       </c>
       <c r="B247" t="n">
-        <v>10.87127876281738</v>
+        <v>10.8712797164917</v>
       </c>
       <c r="C247" t="n">
-        <v>11.17376790836278</v>
+        <v>11.17376888857272</v>
       </c>
       <c r="D247" t="n">
-        <v>10.66961991523398</v>
+        <v>10.66962085121793</v>
       </c>
       <c r="E247" t="n">
-        <v>10.9996078356007</v>
+        <v>10.99960880053258</v>
       </c>
       <c r="F247" t="n">
         <v>2487500</v>
@@ -5492,16 +5492,16 @@
         <v>44147</v>
       </c>
       <c r="B254" t="n">
-        <v>11.6412525177002</v>
+        <v>11.64125156402588</v>
       </c>
       <c r="C254" t="n">
-        <v>12.54872003747481</v>
+        <v>12.54871900945897</v>
       </c>
       <c r="D254" t="n">
-        <v>11.62292029086322</v>
+        <v>11.62291933869072</v>
       </c>
       <c r="E254" t="n">
-        <v>12.54872003747481</v>
+        <v>12.54871900945897</v>
       </c>
       <c r="F254" t="n">
         <v>2275500</v>
@@ -5512,16 +5512,16 @@
         <v>44148</v>
       </c>
       <c r="B255" t="n">
-        <v>11.86124420166016</v>
+        <v>11.86124324798584</v>
       </c>
       <c r="C255" t="n">
-        <v>12.05373738679096</v>
+        <v>12.0537364176397</v>
       </c>
       <c r="D255" t="n">
-        <v>11.47625870556891</v>
+        <v>11.47625778284841</v>
       </c>
       <c r="E255" t="n">
-        <v>11.60458691287587</v>
+        <v>11.60458597983746</v>
       </c>
       <c r="F255" t="n">
         <v>1796700</v>
@@ -5572,16 +5572,16 @@
         <v>44153</v>
       </c>
       <c r="B258" t="n">
-        <v>12.64038276672363</v>
+        <v>12.64038372039795</v>
       </c>
       <c r="C258" t="n">
-        <v>12.76871184083297</v>
+        <v>12.76871280418928</v>
       </c>
       <c r="D258" t="n">
-        <v>12.31956051853545</v>
+        <v>12.31956144800481</v>
       </c>
       <c r="E258" t="n">
-        <v>12.57621866675412</v>
+        <v>12.57621961558747</v>
       </c>
       <c r="F258" t="n">
         <v>1757300</v>
@@ -5712,16 +5712,16 @@
         <v>44165</v>
       </c>
       <c r="B265" t="n">
-        <v>12.20956420898438</v>
+        <v>12.20956516265869</v>
       </c>
       <c r="C265" t="n">
-        <v>12.85120868775777</v>
+        <v>12.85120969155017</v>
       </c>
       <c r="D265" t="n">
-        <v>11.9712400409914</v>
+        <v>11.97124097605051</v>
       </c>
       <c r="E265" t="n">
-        <v>12.69538084281798</v>
+        <v>12.69538183443885</v>
       </c>
       <c r="F265" t="n">
         <v>1362800</v>
@@ -5732,16 +5732,16 @@
         <v>44166</v>
       </c>
       <c r="B266" t="n">
-        <v>12.13623428344727</v>
+        <v>12.13623332977295</v>
       </c>
       <c r="C266" t="n">
-        <v>12.38372588984487</v>
+        <v>12.38372491672248</v>
       </c>
       <c r="D266" t="n">
-        <v>12.05373708131473</v>
+        <v>12.05373613412311</v>
       </c>
       <c r="E266" t="n">
-        <v>12.32872746369974</v>
+        <v>12.32872649489916</v>
       </c>
       <c r="F266" t="n">
         <v>1296100</v>
@@ -5752,16 +5752,16 @@
         <v>44167</v>
       </c>
       <c r="B267" t="n">
-        <v>12.3837251663208</v>
+        <v>12.38372611999512</v>
       </c>
       <c r="C267" t="n">
-        <v>12.67704775750314</v>
+        <v>12.67704873376632</v>
       </c>
       <c r="D267" t="n">
-        <v>12.22789732121261</v>
+        <v>12.22789826288658</v>
       </c>
       <c r="E267" t="n">
-        <v>12.25539609559339</v>
+        <v>12.25539703938504</v>
       </c>
       <c r="F267" t="n">
         <v>1547700</v>
@@ -5852,16 +5852,16 @@
         <v>44174</v>
       </c>
       <c r="B272" t="n">
-        <v>12.05373668670654</v>
+        <v>12.05373764038086</v>
       </c>
       <c r="C272" t="n">
-        <v>12.30122828500191</v>
+        <v>12.30122925825741</v>
       </c>
       <c r="D272" t="n">
-        <v>11.87041006250829</v>
+        <v>11.87041100167807</v>
       </c>
       <c r="E272" t="n">
-        <v>12.27372950991475</v>
+        <v>12.27373048099458</v>
       </c>
       <c r="F272" t="n">
         <v>927800</v>
@@ -5892,16 +5892,16 @@
         <v>44176</v>
       </c>
       <c r="B274" t="n">
-        <v>12.05373668670654</v>
+        <v>12.05373764038086</v>
       </c>
       <c r="C274" t="n">
-        <v>12.35622583517624</v>
+        <v>12.35622681278306</v>
       </c>
       <c r="D274" t="n">
-        <v>11.96207381169257</v>
+        <v>11.96207475811465</v>
       </c>
       <c r="E274" t="n">
-        <v>12.15456698564331</v>
+        <v>12.15456794729517</v>
       </c>
       <c r="F274" t="n">
         <v>1470700</v>
@@ -5952,16 +5952,16 @@
         <v>44181</v>
       </c>
       <c r="B277" t="n">
-        <v>12.47538948059082</v>
+        <v>12.4753885269165</v>
       </c>
       <c r="C277" t="n">
-        <v>12.91537429237765</v>
+        <v>12.91537330506894</v>
       </c>
       <c r="D277" t="n">
-        <v>12.38372659733925</v>
+        <v>12.38372565067205</v>
       </c>
       <c r="E277" t="n">
-        <v>12.5578866874365</v>
+        <v>12.55788572745573</v>
       </c>
       <c r="F277" t="n">
         <v>1004500</v>
@@ -5992,16 +5992,16 @@
         <v>44183</v>
       </c>
       <c r="B279" t="n">
-        <v>12.19123363494873</v>
+        <v>12.19123268127441</v>
       </c>
       <c r="C279" t="n">
-        <v>12.51205504360741</v>
+        <v>12.51205406483644</v>
       </c>
       <c r="D279" t="n">
-        <v>12.08123764847972</v>
+        <v>12.08123670340998</v>
       </c>
       <c r="E279" t="n">
-        <v>12.31956184874404</v>
+        <v>12.31956088503109</v>
       </c>
       <c r="F279" t="n">
         <v>677600</v>
@@ -6112,16 +6112,16 @@
         <v>44195</v>
       </c>
       <c r="B285" t="n">
-        <v>11.81541156768799</v>
+        <v>11.8154125213623</v>
       </c>
       <c r="C285" t="n">
-        <v>12.05373572300648</v>
+        <v>12.05373669591699</v>
       </c>
       <c r="D285" t="n">
-        <v>11.77874624577974</v>
+        <v>11.77874719649464</v>
       </c>
       <c r="E285" t="n">
-        <v>11.91624098439311</v>
+        <v>11.91624194620582</v>
       </c>
       <c r="F285" t="n">
         <v>1061200</v>
@@ -6132,16 +6132,16 @@
         <v>44200</v>
       </c>
       <c r="B286" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="C286" t="n">
-        <v>11.89790827327764</v>
+        <v>11.8979092411191</v>
       </c>
       <c r="D286" t="n">
-        <v>11.42125907296965</v>
+        <v>11.42126000203783</v>
       </c>
       <c r="E286" t="n">
-        <v>11.89790827327764</v>
+        <v>11.8979092411191</v>
       </c>
       <c r="F286" t="n">
         <v>1030900</v>
@@ -6152,16 +6152,16 @@
         <v>44201</v>
       </c>
       <c r="B287" t="n">
-        <v>11.26543140411377</v>
+        <v>11.26543235778809</v>
       </c>
       <c r="C287" t="n">
-        <v>11.73291493644768</v>
+        <v>11.73291592969678</v>
       </c>
       <c r="D287" t="n">
-        <v>11.16460198258245</v>
+        <v>11.16460292772106</v>
       </c>
       <c r="E287" t="n">
-        <v>11.73291493644768</v>
+        <v>11.73291592969678</v>
       </c>
       <c r="F287" t="n">
         <v>2157200</v>
@@ -6172,16 +6172,16 @@
         <v>44202</v>
       </c>
       <c r="B288" t="n">
-        <v>11.07293891906738</v>
+        <v>11.07293796539307</v>
       </c>
       <c r="C288" t="n">
-        <v>11.36626152645873</v>
+        <v>11.36626054752155</v>
       </c>
       <c r="D288" t="n">
-        <v>10.91711106534815</v>
+        <v>10.91711012509475</v>
       </c>
       <c r="E288" t="n">
-        <v>11.28376519875766</v>
+        <v>11.2837642269256</v>
       </c>
       <c r="F288" t="n">
         <v>1263500</v>
@@ -6232,16 +6232,16 @@
         <v>44207</v>
       </c>
       <c r="B291" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C291" t="n">
-        <v>11.13710201901154</v>
+        <v>11.13710298864692</v>
       </c>
       <c r="D291" t="n">
-        <v>10.83461288880819</v>
+        <v>10.83461383210779</v>
       </c>
       <c r="E291" t="n">
-        <v>11.04543914953279</v>
+        <v>11.04544011118768</v>
       </c>
       <c r="F291" t="n">
         <v>926700</v>
@@ -6272,16 +6272,16 @@
         <v>44209</v>
       </c>
       <c r="B293" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C293" t="n">
-        <v>10.98127437212461</v>
+        <v>10.98127533221018</v>
       </c>
       <c r="D293" t="n">
-        <v>10.67878523661001</v>
+        <v>10.67878617024915</v>
       </c>
       <c r="E293" t="n">
-        <v>10.8712784023166</v>
+        <v>10.87127935278529</v>
       </c>
       <c r="F293" t="n">
         <v>2157000</v>
@@ -6332,16 +6332,16 @@
         <v>44214</v>
       </c>
       <c r="B296" t="n">
-        <v>11.29293155670166</v>
+        <v>11.29293060302734</v>
       </c>
       <c r="C296" t="n">
-        <v>11.44875941983287</v>
+        <v>11.44875845299908</v>
       </c>
       <c r="D296" t="n">
-        <v>11.0454408103094</v>
+        <v>11.04543987753537</v>
       </c>
       <c r="E296" t="n">
-        <v>11.40292754111715</v>
+        <v>11.40292657815381</v>
       </c>
       <c r="F296" t="n">
         <v>2481600</v>
@@ -6412,16 +6412,16 @@
         <v>44218</v>
       </c>
       <c r="B300" t="n">
-        <v>11.00877475738525</v>
+        <v>11.00877571105957</v>
       </c>
       <c r="C300" t="n">
-        <v>11.19210138600805</v>
+        <v>11.19210235556369</v>
       </c>
       <c r="D300" t="n">
-        <v>10.82544812876246</v>
+        <v>10.82544906655545</v>
       </c>
       <c r="E300" t="n">
-        <v>11.09127195880809</v>
+        <v>11.09127291962902</v>
       </c>
       <c r="F300" t="n">
         <v>3052400</v>
@@ -6612,16 +6612,16 @@
         <v>44235</v>
       </c>
       <c r="B310" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C310" t="n">
-        <v>11.33876286134076</v>
+        <v>11.33876187989727</v>
       </c>
       <c r="D310" t="n">
-        <v>10.91711117201089</v>
+        <v>10.91711022706409</v>
       </c>
       <c r="E310" t="n">
-        <v>11.27459875888959</v>
+        <v>11.27459778299992</v>
       </c>
       <c r="F310" t="n">
         <v>1845700</v>
@@ -6792,16 +6792,16 @@
         <v>44250</v>
       </c>
       <c r="B319" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C319" t="n">
-        <v>10.99960747084441</v>
+        <v>10.99960843253283</v>
       </c>
       <c r="D319" t="n">
-        <v>10.55045704225246</v>
+        <v>10.55045796467195</v>
       </c>
       <c r="E319" t="n">
-        <v>10.67878523661001</v>
+        <v>10.67878617024915</v>
       </c>
       <c r="F319" t="n">
         <v>1964300</v>
@@ -6852,16 +6852,16 @@
         <v>44253</v>
       </c>
       <c r="B322" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C322" t="n">
-        <v>10.65128678074554</v>
+        <v>10.651287786344</v>
       </c>
       <c r="D322" t="n">
-        <v>9.945479068192968</v>
+        <v>9.945480007155426</v>
       </c>
       <c r="E322" t="n">
-        <v>10.60545490674777</v>
+        <v>10.6054559080192</v>
       </c>
       <c r="F322" t="n">
         <v>2794300</v>
@@ -6912,16 +6912,16 @@
         <v>44258</v>
       </c>
       <c r="B325" t="n">
-        <v>9.752985954284668</v>
+        <v>9.752986907958984</v>
       </c>
       <c r="C325" t="n">
-        <v>9.81715005375796</v>
+        <v>9.817151013706422</v>
       </c>
       <c r="D325" t="n">
-        <v>9.184672986201862</v>
+        <v>9.184673884304942</v>
       </c>
       <c r="E325" t="n">
-        <v>9.578825006899601</v>
+        <v>9.578825943543972</v>
       </c>
       <c r="F325" t="n">
         <v>2305100</v>
@@ -7032,16 +7032,16 @@
         <v>44266</v>
       </c>
       <c r="B331" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C331" t="n">
-        <v>10.24796821273983</v>
+        <v>10.24796918026058</v>
       </c>
       <c r="D331" t="n">
-        <v>9.322167679832035</v>
+        <v>9.32216855994705</v>
       </c>
       <c r="E331" t="n">
-        <v>9.404664878193957</v>
+        <v>9.404665766097615</v>
       </c>
       <c r="F331" t="n">
         <v>2921600</v>
@@ -7092,16 +7092,16 @@
         <v>44271</v>
       </c>
       <c r="B334" t="n">
-        <v>9.771317481994629</v>
+        <v>9.771318435668945</v>
       </c>
       <c r="C334" t="n">
-        <v>10.34879695854355</v>
+        <v>10.3487979685795</v>
       </c>
       <c r="D334" t="n">
-        <v>9.734652160031374</v>
+        <v>9.734653110127178</v>
       </c>
       <c r="E334" t="n">
-        <v>10.3121316365803</v>
+        <v>10.31213264303773</v>
       </c>
       <c r="F334" t="n">
         <v>1474300</v>
@@ -7152,16 +7152,16 @@
         <v>44274</v>
       </c>
       <c r="B337" t="n">
-        <v>9.972978591918945</v>
+        <v>9.972977638244629</v>
       </c>
       <c r="C337" t="n">
-        <v>10.10130767391647</v>
+        <v>10.10130670797058</v>
       </c>
       <c r="D337" t="n">
-        <v>9.679655974976443</v>
+        <v>9.679655049351345</v>
       </c>
       <c r="E337" t="n">
-        <v>9.826317283447693</v>
+        <v>9.826316343797988</v>
       </c>
       <c r="F337" t="n">
         <v>1607200</v>
@@ -7212,16 +7212,16 @@
         <v>44279</v>
       </c>
       <c r="B340" t="n">
-        <v>10.38546276092529</v>
+        <v>10.38546371459961</v>
       </c>
       <c r="C340" t="n">
-        <v>10.60545470288137</v>
+        <v>10.60545567675706</v>
       </c>
       <c r="D340" t="n">
-        <v>10.21130269208597</v>
+        <v>10.21130362976755</v>
       </c>
       <c r="E340" t="n">
-        <v>10.56878937922202</v>
+        <v>10.56879034973082</v>
       </c>
       <c r="F340" t="n">
         <v>3104200</v>
@@ -7272,16 +7272,16 @@
         <v>44284</v>
       </c>
       <c r="B343" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C343" t="n">
-        <v>10.06464047012052</v>
+        <v>10.06464144419899</v>
       </c>
       <c r="D343" t="n">
-        <v>9.734652558929284</v>
+        <v>9.734653501070783</v>
       </c>
       <c r="E343" t="n">
-        <v>10.04630824547281</v>
+        <v>10.04630921777704</v>
       </c>
       <c r="F343" t="n">
         <v>1233600</v>
@@ -7452,16 +7452,16 @@
         <v>44298</v>
       </c>
       <c r="B352" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C352" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="D352" t="n">
-        <v>10.69711763298518</v>
+        <v>10.69711856198182</v>
       </c>
       <c r="E352" t="n">
-        <v>10.87127768853708</v>
+        <v>10.87127863265874</v>
       </c>
       <c r="F352" t="n">
         <v>1341200</v>
@@ -7532,16 +7532,16 @@
         <v>44302</v>
       </c>
       <c r="B356" t="n">
-        <v>12.53955268859863</v>
+        <v>12.53955364227295</v>
       </c>
       <c r="C356" t="n">
-        <v>13.63951325138424</v>
+        <v>13.63951428871419</v>
       </c>
       <c r="D356" t="n">
-        <v>11.47625744876687</v>
+        <v>11.47625832157408</v>
       </c>
       <c r="E356" t="n">
-        <v>11.61375219130122</v>
+        <v>11.61375307456536</v>
       </c>
       <c r="F356" t="n">
         <v>14691000</v>
@@ -7592,16 +7592,16 @@
         <v>44308</v>
       </c>
       <c r="B359" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C359" t="n">
-        <v>11.41209182687907</v>
+        <v>11.41209281796801</v>
       </c>
       <c r="D359" t="n">
-        <v>10.91710955815712</v>
+        <v>10.91711050625907</v>
       </c>
       <c r="E359" t="n">
-        <v>11.26543054343111</v>
+        <v>11.26543152178318</v>
       </c>
       <c r="F359" t="n">
         <v>4817400</v>
@@ -7612,16 +7612,16 @@
         <v>44309</v>
       </c>
       <c r="B360" t="n">
-        <v>11.02710723876953</v>
+        <v>11.02710628509521</v>
       </c>
       <c r="C360" t="n">
-        <v>11.18293509525356</v>
+        <v>11.18293412810254</v>
       </c>
       <c r="D360" t="n">
-        <v>10.70628584978561</v>
+        <v>10.70628492385739</v>
       </c>
       <c r="E360" t="n">
-        <v>11.1462697686791</v>
+        <v>11.14626880469907</v>
       </c>
       <c r="F360" t="n">
         <v>3824500</v>
@@ -7672,16 +7672,16 @@
         <v>44314</v>
       </c>
       <c r="B363" t="n">
-        <v>11.20126724243164</v>
+        <v>11.20126819610596</v>
       </c>
       <c r="C363" t="n">
-        <v>11.30209666338853</v>
+        <v>11.30209762564745</v>
       </c>
       <c r="D363" t="n">
-        <v>10.9262768794389</v>
+        <v>10.92627780970057</v>
       </c>
       <c r="E363" t="n">
-        <v>11.18293414361933</v>
+        <v>11.18293509573277</v>
       </c>
       <c r="F363" t="n">
         <v>1629600</v>
@@ -7692,16 +7692,16 @@
         <v>44315</v>
       </c>
       <c r="B364" t="n">
-        <v>11.42125988006592</v>
+        <v>11.4212589263916</v>
       </c>
       <c r="C364" t="n">
-        <v>11.59541995855849</v>
+        <v>11.59541899034182</v>
       </c>
       <c r="D364" t="n">
-        <v>11.08210539887593</v>
+        <v>11.08210447352099</v>
       </c>
       <c r="E364" t="n">
-        <v>11.2196001516769</v>
+        <v>11.21959921484115</v>
       </c>
       <c r="F364" t="n">
         <v>1614300</v>
@@ -7892,16 +7892,16 @@
         <v>44329</v>
       </c>
       <c r="B374" t="n">
-        <v>11.16460227966309</v>
+        <v>11.16460132598877</v>
       </c>
       <c r="C374" t="n">
-        <v>11.43042610183743</v>
+        <v>11.43042512545659</v>
       </c>
       <c r="D374" t="n">
-        <v>11.10043730591735</v>
+        <v>11.10043635772397</v>
       </c>
       <c r="E374" t="n">
-        <v>11.13710263055622</v>
+        <v>11.13710167923091</v>
       </c>
       <c r="F374" t="n">
         <v>1639700</v>
@@ -7952,16 +7952,16 @@
         <v>44334</v>
       </c>
       <c r="B377" t="n">
-        <v>12.26456356048584</v>
+        <v>12.26456260681152</v>
       </c>
       <c r="C377" t="n">
-        <v>12.59455150019489</v>
+        <v>12.5945505208612</v>
       </c>
       <c r="D377" t="n">
-        <v>12.18206635701599</v>
+        <v>12.18206540975654</v>
       </c>
       <c r="E377" t="n">
-        <v>12.35622643998652</v>
+        <v>12.35622547918463</v>
       </c>
       <c r="F377" t="n">
         <v>1445400</v>
@@ -7992,16 +7992,16 @@
         <v>44336</v>
       </c>
       <c r="B379" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="C379" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="D379" t="n">
-        <v>11.86124370366004</v>
+        <v>11.86124460180745</v>
       </c>
       <c r="E379" t="n">
-        <v>12.05373688070891</v>
+        <v>12.05373779343214</v>
       </c>
       <c r="F379" t="n">
         <v>2196400</v>
@@ -8012,16 +8012,16 @@
         <v>44337</v>
       </c>
       <c r="B380" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="C380" t="n">
-        <v>12.79621081337468</v>
+        <v>12.79621178231891</v>
       </c>
       <c r="D380" t="n">
-        <v>12.42955755907697</v>
+        <v>12.42955850025778</v>
       </c>
       <c r="E380" t="n">
-        <v>12.53038698546626</v>
+        <v>12.53038793428199</v>
       </c>
       <c r="F380" t="n">
         <v>1466000</v>
@@ -8052,16 +8052,16 @@
         <v>44341</v>
       </c>
       <c r="B382" t="n">
-        <v>12.53955268859863</v>
+        <v>12.53955364227295</v>
       </c>
       <c r="C382" t="n">
-        <v>12.75037807704068</v>
+        <v>12.75037904674896</v>
       </c>
       <c r="D382" t="n">
-        <v>12.40205707189402</v>
+        <v>12.40205801511135</v>
       </c>
       <c r="E382" t="n">
-        <v>12.62204988378735</v>
+        <v>12.62205084373585</v>
       </c>
       <c r="F382" t="n">
         <v>1256400</v>
@@ -8252,16 +8252,16 @@
         <v>44356</v>
       </c>
       <c r="B392" t="n">
-        <v>13.53868389129639</v>
+        <v>13.5386848449707</v>
       </c>
       <c r="C392" t="n">
-        <v>13.84117302553739</v>
+        <v>13.84117400051925</v>
       </c>
       <c r="D392" t="n">
-        <v>13.38285604951523</v>
+        <v>13.38285699221293</v>
       </c>
       <c r="E392" t="n">
-        <v>13.78617460377982</v>
+        <v>13.78617557488755</v>
       </c>
       <c r="F392" t="n">
         <v>1247900</v>
@@ -8272,16 +8272,16 @@
         <v>44357</v>
       </c>
       <c r="B393" t="n">
-        <v>13.62118148803711</v>
+        <v>13.62118053436279</v>
       </c>
       <c r="C393" t="n">
-        <v>13.77700934440852</v>
+        <v>13.77700837982407</v>
       </c>
       <c r="D393" t="n">
-        <v>13.32785887565343</v>
+        <v>13.32785794251582</v>
       </c>
       <c r="E393" t="n">
-        <v>13.56618393530034</v>
+        <v>13.56618298547662</v>
       </c>
       <c r="F393" t="n">
         <v>1127800</v>
@@ -8312,16 +8312,16 @@
         <v>44361</v>
       </c>
       <c r="B395" t="n">
-        <v>13.50201797485352</v>
+        <v>13.50201892852783</v>
       </c>
       <c r="C395" t="n">
-        <v>13.6578458198759</v>
+        <v>13.65784678455664</v>
       </c>
       <c r="D395" t="n">
-        <v>13.30035913061184</v>
+        <v>13.30036007004259</v>
       </c>
       <c r="E395" t="n">
-        <v>13.3186913554655</v>
+        <v>13.3186922961911</v>
       </c>
       <c r="F395" t="n">
         <v>1118700</v>
@@ -8392,16 +8392,16 @@
         <v>44365</v>
       </c>
       <c r="B399" t="n">
-        <v>13.74034309387207</v>
+        <v>13.74034404754639</v>
       </c>
       <c r="C399" t="n">
-        <v>13.75867619299839</v>
+        <v>13.75867714794514</v>
       </c>
       <c r="D399" t="n">
-        <v>13.34619107852938</v>
+        <v>13.34619200484684</v>
       </c>
       <c r="E399" t="n">
-        <v>13.40118862756777</v>
+        <v>13.40118955770243</v>
       </c>
       <c r="F399" t="n">
         <v>1818300</v>
@@ -8412,16 +8412,16 @@
         <v>44368</v>
       </c>
       <c r="B400" t="n">
-        <v>14.03366756439209</v>
+        <v>14.03366661071777</v>
       </c>
       <c r="C400" t="n">
-        <v>14.28115830110597</v>
+        <v>14.28115733061313</v>
       </c>
       <c r="D400" t="n">
-        <v>13.86867315713594</v>
+        <v>13.86867221467401</v>
       </c>
       <c r="E400" t="n">
-        <v>13.99700223768743</v>
+        <v>13.99700128650475</v>
       </c>
       <c r="F400" t="n">
         <v>2278000</v>
@@ -8432,16 +8432,16 @@
         <v>44369</v>
       </c>
       <c r="B401" t="n">
-        <v>13.53868389129639</v>
+        <v>13.5386848449707</v>
       </c>
       <c r="C401" t="n">
-        <v>13.98783431799724</v>
+        <v>13.98783530331003</v>
       </c>
       <c r="D401" t="n">
-        <v>13.41952137263019</v>
+        <v>13.41952231791062</v>
       </c>
       <c r="E401" t="n">
-        <v>13.95116899488228</v>
+        <v>13.95116997761234</v>
       </c>
       <c r="F401" t="n">
         <v>2062700</v>
@@ -8492,16 +8492,16 @@
         <v>44372</v>
       </c>
       <c r="B404" t="n">
-        <v>13.43785381317139</v>
+        <v>13.4378547668457</v>
       </c>
       <c r="C404" t="n">
-        <v>13.5661828832223</v>
+        <v>13.56618384600404</v>
       </c>
       <c r="D404" t="n">
-        <v>12.83287553496186</v>
+        <v>12.83287644570132</v>
       </c>
       <c r="E404" t="n">
-        <v>13.53868410898649</v>
+        <v>13.53868506981665</v>
       </c>
       <c r="F404" t="n">
         <v>1465200</v>
@@ -8532,16 +8532,16 @@
         <v>44376</v>
       </c>
       <c r="B406" t="n">
-        <v>13.1536979675293</v>
+        <v>13.15369892120361</v>
       </c>
       <c r="C406" t="n">
-        <v>13.30035926451625</v>
+        <v>13.30036022882386</v>
       </c>
       <c r="D406" t="n">
-        <v>12.89703982363184</v>
+        <v>12.89704075869783</v>
       </c>
       <c r="E406" t="n">
-        <v>13.26369394026951</v>
+        <v>13.2636949019188</v>
       </c>
       <c r="F406" t="n">
         <v>967400</v>
@@ -8672,16 +8672,16 @@
         <v>44385</v>
       </c>
       <c r="B413" t="n">
-        <v>12.45705699920654</v>
+        <v>12.45705604553223</v>
       </c>
       <c r="C413" t="n">
-        <v>12.57621953175335</v>
+        <v>12.57621856895631</v>
       </c>
       <c r="D413" t="n">
-        <v>12.17290005633794</v>
+        <v>12.17289912441782</v>
       </c>
       <c r="E413" t="n">
-        <v>12.3195613658816</v>
+        <v>12.31956042273353</v>
       </c>
       <c r="F413" t="n">
         <v>1082500</v>
@@ -8812,16 +8812,16 @@
         <v>44397</v>
       </c>
       <c r="B420" t="n">
-        <v>11.48542308807373</v>
+        <v>11.48542404174805</v>
       </c>
       <c r="C420" t="n">
-        <v>11.68708280077636</v>
+        <v>11.68708377119518</v>
       </c>
       <c r="D420" t="n">
-        <v>11.37542711955509</v>
+        <v>11.37542806409606</v>
       </c>
       <c r="E420" t="n">
-        <v>11.57708683225772</v>
+        <v>11.5770877935432</v>
       </c>
       <c r="F420" t="n">
         <v>1744400</v>
@@ -8832,16 +8832,16 @@
         <v>44398</v>
       </c>
       <c r="B421" t="n">
-        <v>11.48542308807373</v>
+        <v>11.48542404174805</v>
       </c>
       <c r="C421" t="n">
-        <v>11.66874970227147</v>
+        <v>11.66875067116803</v>
       </c>
       <c r="D421" t="n">
-        <v>11.2287658281969</v>
+        <v>11.22876676056008</v>
       </c>
       <c r="E421" t="n">
-        <v>11.54042150941818</v>
+        <v>11.5404224676592</v>
       </c>
       <c r="F421" t="n">
         <v>2115800</v>
@@ -8872,16 +8872,16 @@
         <v>44400</v>
       </c>
       <c r="B423" t="n">
-        <v>11.68708419799805</v>
+        <v>11.68708324432373</v>
       </c>
       <c r="C423" t="n">
-        <v>11.7145829748727</v>
+        <v>11.71458201895446</v>
       </c>
       <c r="D423" t="n">
-        <v>11.43959258361514</v>
+        <v>11.43959165013631</v>
       </c>
       <c r="E423" t="n">
-        <v>11.62292009390042</v>
+        <v>11.62291914546194</v>
       </c>
       <c r="F423" t="n">
         <v>1513600</v>
@@ -8912,16 +8912,16 @@
         <v>44404</v>
       </c>
       <c r="B425" t="n">
-        <v>11.43959140777588</v>
+        <v>11.4395923614502</v>
       </c>
       <c r="C425" t="n">
-        <v>11.61375234981137</v>
+        <v>11.61375331800481</v>
       </c>
       <c r="D425" t="n">
-        <v>11.19210069300211</v>
+        <v>11.19210162604409</v>
       </c>
       <c r="E425" t="n">
-        <v>11.39376040908574</v>
+        <v>11.3937613589393</v>
       </c>
       <c r="F425" t="n">
         <v>1727000</v>
@@ -8952,16 +8952,16 @@
         <v>44406</v>
       </c>
       <c r="B427" t="n">
-        <v>11.25626468658447</v>
+        <v>11.25626564025879</v>
       </c>
       <c r="C427" t="n">
-        <v>11.36626065593178</v>
+        <v>11.36626161892538</v>
       </c>
       <c r="D427" t="n">
-        <v>11.15543526655867</v>
+        <v>11.15543621169033</v>
       </c>
       <c r="E427" t="n">
-        <v>11.36626065593178</v>
+        <v>11.36626161892538</v>
       </c>
       <c r="F427" t="n">
         <v>743300</v>
@@ -8992,16 +8992,16 @@
         <v>44410</v>
       </c>
       <c r="B429" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C429" t="n">
-        <v>11.2012671859109</v>
+        <v>11.20126816523029</v>
       </c>
       <c r="D429" t="n">
-        <v>10.86211272712696</v>
+        <v>10.8621136767943</v>
       </c>
       <c r="E429" t="n">
-        <v>10.96294214757507</v>
+        <v>10.96294310605787</v>
       </c>
       <c r="F429" t="n">
         <v>1959100</v>
@@ -9132,16 +9132,16 @@
         <v>44419</v>
       </c>
       <c r="B436" t="n">
-        <v>9.890481948852539</v>
+        <v>9.890480995178223</v>
       </c>
       <c r="C436" t="n">
-        <v>10.51379341941164</v>
+        <v>10.51379240563549</v>
       </c>
       <c r="D436" t="n">
-        <v>9.743820632055199</v>
+        <v>9.74381969252247</v>
       </c>
       <c r="E436" t="n">
-        <v>10.51379341941164</v>
+        <v>10.51379240563549</v>
       </c>
       <c r="F436" t="n">
         <v>4618100</v>
@@ -9172,16 +9172,16 @@
         <v>44421</v>
       </c>
       <c r="B438" t="n">
-        <v>9.81714916229248</v>
+        <v>9.817150115966797</v>
       </c>
       <c r="C438" t="n">
-        <v>10.00964231740293</v>
+        <v>10.00964328977675</v>
       </c>
       <c r="D438" t="n">
-        <v>9.688820100828776</v>
+        <v>9.688821042036732</v>
       </c>
       <c r="E438" t="n">
-        <v>9.908812902505156</v>
+        <v>9.90881386508403</v>
       </c>
       <c r="F438" t="n">
         <v>1360000</v>
@@ -9212,16 +9212,16 @@
         <v>44425</v>
       </c>
       <c r="B440" t="n">
-        <v>8.323036193847656</v>
+        <v>8.323037147521973</v>
       </c>
       <c r="C440" t="n">
-        <v>9.294668565223555</v>
+        <v>9.29466963022994</v>
       </c>
       <c r="D440" t="n">
-        <v>8.304703969421075</v>
+        <v>8.30470492099484</v>
       </c>
       <c r="E440" t="n">
-        <v>9.285502015925136</v>
+        <v>9.285503079881195</v>
       </c>
       <c r="F440" t="n">
         <v>6613600</v>
@@ -9272,16 +9272,16 @@
         <v>44428</v>
       </c>
       <c r="B443" t="n">
-        <v>8.62552547454834</v>
+        <v>8.625526428222656</v>
       </c>
       <c r="C443" t="n">
-        <v>8.689689572391865</v>
+        <v>8.689690533160434</v>
       </c>
       <c r="D443" t="n">
-        <v>8.414700082108032</v>
+        <v>8.414701012472607</v>
       </c>
       <c r="E443" t="n">
-        <v>8.515529503600753</v>
+        <v>8.515530445113452</v>
       </c>
       <c r="F443" t="n">
         <v>1662000</v>
@@ -9332,16 +9332,16 @@
         <v>44433</v>
       </c>
       <c r="B446" t="n">
-        <v>8.955513954162598</v>
+        <v>8.955514907836914</v>
       </c>
       <c r="C446" t="n">
-        <v>9.322167178069154</v>
+        <v>9.322168170788439</v>
       </c>
       <c r="D446" t="n">
-        <v>8.744687694788647</v>
+        <v>8.744688626012037</v>
       </c>
       <c r="E446" t="n">
-        <v>9.175505888506532</v>
+        <v>9.175506865607829</v>
       </c>
       <c r="F446" t="n">
         <v>3539500</v>
@@ -9352,16 +9352,16 @@
         <v>44434</v>
       </c>
       <c r="B447" t="n">
-        <v>8.488031387329102</v>
+        <v>8.488030433654785</v>
       </c>
       <c r="C447" t="n">
-        <v>9.093009711518935</v>
+        <v>9.093008689872168</v>
       </c>
       <c r="D447" t="n">
-        <v>8.451366060837909</v>
+        <v>8.451365111283133</v>
       </c>
       <c r="E447" t="n">
-        <v>8.928015305223402</v>
+        <v>8.928014302114612</v>
       </c>
       <c r="F447" t="n">
         <v>2819100</v>
@@ -9412,16 +9412,16 @@
         <v>44439</v>
       </c>
       <c r="B450" t="n">
-        <v>8.148877143859863</v>
+        <v>8.148876190185547</v>
       </c>
       <c r="C450" t="n">
-        <v>8.478865092206572</v>
+        <v>8.478864099913311</v>
       </c>
       <c r="D450" t="n">
-        <v>8.075546488671705</v>
+        <v>8.075545543579377</v>
       </c>
       <c r="E450" t="n">
-        <v>8.359702558983225</v>
+        <v>8.35970158063572</v>
       </c>
       <c r="F450" t="n">
         <v>2719700</v>
@@ -9472,16 +9472,16 @@
         <v>44442</v>
       </c>
       <c r="B453" t="n">
-        <v>8.020547866821289</v>
+        <v>8.020546913146973</v>
       </c>
       <c r="C453" t="n">
-        <v>8.048046643311267</v>
+        <v>8.048045686367239</v>
       </c>
       <c r="D453" t="n">
-        <v>7.818888132830658</v>
+        <v>7.818887203134468</v>
       </c>
       <c r="E453" t="n">
-        <v>7.965549439670992</v>
+        <v>7.965548492536203</v>
       </c>
       <c r="F453" t="n">
         <v>2243900</v>
@@ -9532,16 +9532,16 @@
         <v>44448</v>
       </c>
       <c r="B456" t="n">
-        <v>7.95638370513916</v>
+        <v>7.956383228302002</v>
       </c>
       <c r="C456" t="n">
-        <v>8.075546234613633</v>
+        <v>8.075545750634898</v>
       </c>
       <c r="D456" t="n">
-        <v>7.626394893003591</v>
+        <v>7.626394435943123</v>
       </c>
       <c r="E456" t="n">
-        <v>7.883053052257997</v>
+        <v>7.883052579815647</v>
       </c>
       <c r="F456" t="n">
         <v>3062500</v>
@@ -9672,16 +9672,16 @@
         <v>44459</v>
       </c>
       <c r="B463" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C463" t="n">
-        <v>7.415568905269083</v>
+        <v>7.415569387470669</v>
       </c>
       <c r="D463" t="n">
-        <v>7.140578541359559</v>
+        <v>7.14057900567974</v>
       </c>
       <c r="E463" t="n">
-        <v>7.21390918851273</v>
+        <v>7.213909657601278</v>
       </c>
       <c r="F463" t="n">
         <v>2478700</v>
@@ -9692,16 +9692,16 @@
         <v>44460</v>
       </c>
       <c r="B464" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="C464" t="n">
-        <v>7.635561237915681</v>
+        <v>7.63556171937671</v>
       </c>
       <c r="D464" t="n">
-        <v>7.213909558097646</v>
+        <v>7.21391001297139</v>
       </c>
       <c r="E464" t="n">
-        <v>7.488899936095549</v>
+        <v>7.488900408308837</v>
       </c>
       <c r="F464" t="n">
         <v>2716900</v>
@@ -9712,16 +9712,16 @@
         <v>44461</v>
       </c>
       <c r="B465" t="n">
-        <v>7.653894424438477</v>
+        <v>7.653893947601318</v>
       </c>
       <c r="C465" t="n">
-        <v>7.773056077889568</v>
+        <v>7.773055593628645</v>
       </c>
       <c r="D465" t="n">
-        <v>7.443068145055875</v>
+        <v>7.443067681353181</v>
       </c>
       <c r="E465" t="n">
-        <v>7.708891976158931</v>
+        <v>7.708891495895427</v>
       </c>
       <c r="F465" t="n">
         <v>2341500</v>
@@ -9732,16 +9732,16 @@
         <v>44462</v>
       </c>
       <c r="B466" t="n">
-        <v>7.635560989379883</v>
+        <v>7.635561466217041</v>
       </c>
       <c r="C466" t="n">
-        <v>7.809721935250124</v>
+        <v>7.809722422963551</v>
       </c>
       <c r="D466" t="n">
-        <v>7.553063791248745</v>
+        <v>7.553064262933993</v>
       </c>
       <c r="E466" t="n">
-        <v>7.6630597640335</v>
+        <v>7.663060242587944</v>
       </c>
       <c r="F466" t="n">
         <v>1813900</v>
@@ -9852,16 +9852,16 @@
         <v>44470</v>
       </c>
       <c r="B472" t="n">
-        <v>7.058081150054932</v>
+        <v>7.05808162689209</v>
       </c>
       <c r="C472" t="n">
-        <v>7.058081150054932</v>
+        <v>7.05808162689209</v>
       </c>
       <c r="D472" t="n">
-        <v>6.590598068807588</v>
+        <v>6.590598514062039</v>
       </c>
       <c r="E472" t="n">
-        <v>6.627263391372669</v>
+        <v>6.627263839104194</v>
       </c>
       <c r="F472" t="n">
         <v>1964300</v>
@@ -9872,16 +9872,16 @@
         <v>44473</v>
       </c>
       <c r="B473" t="n">
-        <v>6.883921146392822</v>
+        <v>6.88392162322998</v>
       </c>
       <c r="C473" t="n">
-        <v>7.058081211551849</v>
+        <v>7.05808170045277</v>
       </c>
       <c r="D473" t="n">
-        <v>6.792257402096333</v>
+        <v>6.792257872584105</v>
       </c>
       <c r="E473" t="n">
-        <v>6.911419920013668</v>
+        <v>6.911420398755618</v>
       </c>
       <c r="F473" t="n">
         <v>2556200</v>
@@ -9972,16 +9972,16 @@
         <v>44480</v>
       </c>
       <c r="B478" t="n">
-        <v>6.645596981048584</v>
+        <v>6.645596504211426</v>
       </c>
       <c r="C478" t="n">
-        <v>6.79225829179757</v>
+        <v>6.792257804437119</v>
       </c>
       <c r="D478" t="n">
-        <v>6.526434447522441</v>
+        <v>6.526433979235474</v>
       </c>
       <c r="E478" t="n">
-        <v>6.783092178418349</v>
+        <v>6.783091691715589</v>
       </c>
       <c r="F478" t="n">
         <v>1719800</v>
@@ -9992,16 +9992,16 @@
         <v>44482</v>
       </c>
       <c r="B479" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C479" t="n">
-        <v>6.89308794729405</v>
+        <v>6.893087464680927</v>
       </c>
       <c r="D479" t="n">
-        <v>6.581432234551219</v>
+        <v>6.58143177375838</v>
       </c>
       <c r="E479" t="n">
-        <v>6.645596774552734</v>
+        <v>6.645596309267474</v>
       </c>
       <c r="F479" t="n">
         <v>1797400</v>
@@ -10032,16 +10032,16 @@
         <v>44484</v>
       </c>
       <c r="B481" t="n">
-        <v>6.801424503326416</v>
+        <v>6.801424026489258</v>
       </c>
       <c r="C481" t="n">
-        <v>6.810590616248861</v>
+        <v>6.810590138769081</v>
       </c>
       <c r="D481" t="n">
-        <v>6.58143211108064</v>
+        <v>6.581431649666802</v>
       </c>
       <c r="E481" t="n">
-        <v>6.654763199886006</v>
+        <v>6.654762733331041</v>
       </c>
       <c r="F481" t="n">
         <v>1272200</v>
@@ -10112,16 +10112,16 @@
         <v>44490</v>
       </c>
       <c r="B485" t="n">
-        <v>5.967287540435791</v>
+        <v>5.967287063598633</v>
       </c>
       <c r="C485" t="n">
-        <v>6.297275465216598</v>
+        <v>6.29727496201059</v>
       </c>
       <c r="D485" t="n">
-        <v>5.89395645339935</v>
+        <v>5.89395598242197</v>
       </c>
       <c r="E485" t="n">
-        <v>6.297275465216598</v>
+        <v>6.29727496201059</v>
       </c>
       <c r="F485" t="n">
         <v>2712900</v>
@@ -10172,16 +10172,16 @@
         <v>44495</v>
       </c>
       <c r="B488" t="n">
-        <v>5.60063362121582</v>
+        <v>5.600634098052979</v>
       </c>
       <c r="C488" t="n">
-        <v>5.994786066892628</v>
+        <v>5.994786577287869</v>
       </c>
       <c r="D488" t="n">
-        <v>5.60063362121582</v>
+        <v>5.600634098052979</v>
       </c>
       <c r="E488" t="n">
-        <v>5.930621532304952</v>
+        <v>5.930622037237235</v>
       </c>
       <c r="F488" t="n">
         <v>1746800</v>
@@ -10232,16 +10232,16 @@
         <v>44498</v>
       </c>
       <c r="B491" t="n">
-        <v>5.554801940917969</v>
+        <v>5.554802417755127</v>
       </c>
       <c r="C491" t="n">
-        <v>5.838958426082296</v>
+        <v>5.838958927312109</v>
       </c>
       <c r="D491" t="n">
-        <v>5.545635828279196</v>
+        <v>5.545636304329514</v>
       </c>
       <c r="E491" t="n">
-        <v>5.701463239819518</v>
+        <v>5.701463729246425</v>
       </c>
       <c r="F491" t="n">
         <v>2502600</v>
@@ -10312,16 +10312,16 @@
         <v>44505</v>
       </c>
       <c r="B495" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C495" t="n">
-        <v>6.94808593711599</v>
+        <v>6.948085450652234</v>
       </c>
       <c r="D495" t="n">
-        <v>6.398105601811419</v>
+        <v>6.398105153854022</v>
       </c>
       <c r="E495" t="n">
-        <v>6.398105601811419</v>
+        <v>6.398105153854022</v>
       </c>
       <c r="F495" t="n">
         <v>3968000</v>
@@ -10372,16 +10372,16 @@
         <v>44510</v>
       </c>
       <c r="B498" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C498" t="n">
-        <v>7.333072037123874</v>
+        <v>7.333072524313823</v>
       </c>
       <c r="D498" t="n">
-        <v>6.874755034803632</v>
+        <v>6.874755491544209</v>
       </c>
       <c r="E498" t="n">
-        <v>6.874755034803632</v>
+        <v>6.874755491544209</v>
       </c>
       <c r="F498" t="n">
         <v>8294800</v>
@@ -10432,16 +10432,16 @@
         <v>44516</v>
       </c>
       <c r="B501" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C501" t="n">
-        <v>7.177243999484845</v>
+        <v>7.177244504030098</v>
       </c>
       <c r="D501" t="n">
-        <v>6.691428234445144</v>
+        <v>6.691428704838564</v>
       </c>
       <c r="E501" t="n">
-        <v>7.131412562697498</v>
+        <v>7.131413064020896</v>
       </c>
       <c r="F501" t="n">
         <v>3605600</v>
@@ -10492,16 +10492,16 @@
         <v>44519</v>
       </c>
       <c r="B504" t="n">
-        <v>7.232242107391357</v>
+        <v>7.232241630554199</v>
       </c>
       <c r="C504" t="n">
-        <v>7.305572757151272</v>
+        <v>7.305572275479267</v>
       </c>
       <c r="D504" t="n">
-        <v>6.544766610264437</v>
+        <v>6.544766178754005</v>
       </c>
       <c r="E504" t="n">
-        <v>6.645596472226894</v>
+        <v>6.645596034068535</v>
       </c>
       <c r="F504" t="n">
         <v>4026100</v>
@@ -10512,16 +10512,16 @@
         <v>44522</v>
       </c>
       <c r="B505" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C505" t="n">
-        <v>7.296406521885203</v>
+        <v>7.296407034807332</v>
       </c>
       <c r="D505" t="n">
-        <v>6.572265712044786</v>
+        <v>6.57226617406133</v>
       </c>
       <c r="E505" t="n">
-        <v>7.278073859753236</v>
+        <v>7.278074371386616</v>
       </c>
       <c r="F505" t="n">
         <v>4188800</v>
@@ -10752,16 +10752,16 @@
         <v>44538</v>
       </c>
       <c r="B517" t="n">
-        <v>6.269776344299316</v>
+        <v>6.269776821136475</v>
       </c>
       <c r="C517" t="n">
-        <v>6.398104974637775</v>
+        <v>6.398105461234748</v>
       </c>
       <c r="D517" t="n">
-        <v>5.912288789871634</v>
+        <v>5.912289239520686</v>
       </c>
       <c r="E517" t="n">
-        <v>6.223944472064447</v>
+        <v>6.22394494541594</v>
       </c>
       <c r="F517" t="n">
         <v>2255900</v>
@@ -10772,16 +10772,16 @@
         <v>44539</v>
       </c>
       <c r="B518" t="n">
-        <v>6.086450099945068</v>
+        <v>6.08644962310791</v>
       </c>
       <c r="C518" t="n">
-        <v>6.26977717612175</v>
+        <v>6.269776684922006</v>
       </c>
       <c r="D518" t="n">
-        <v>5.994786780399321</v>
+        <v>5.994786310743438</v>
       </c>
       <c r="E518" t="n">
-        <v>6.205612633897133</v>
+        <v>6.2056121477243</v>
       </c>
       <c r="F518" t="n">
         <v>1370200</v>
@@ -10792,16 +10792,16 @@
         <v>44540</v>
       </c>
       <c r="B519" t="n">
-        <v>6.13228178024292</v>
+        <v>6.132281303405762</v>
       </c>
       <c r="C519" t="n">
-        <v>6.242277760145935</v>
+        <v>6.242277274755653</v>
       </c>
       <c r="D519" t="n">
-        <v>6.077283790291412</v>
+        <v>6.077283317730816</v>
       </c>
       <c r="E519" t="n">
-        <v>6.233111647029936</v>
+        <v>6.233111162352396</v>
       </c>
       <c r="F519" t="n">
         <v>1440000</v>
@@ -10812,16 +10812,16 @@
         <v>44543</v>
       </c>
       <c r="B520" t="n">
-        <v>5.930622100830078</v>
+        <v>5.93062162399292</v>
       </c>
       <c r="C520" t="n">
-        <v>6.233111703953602</v>
+        <v>6.233111202795508</v>
       </c>
       <c r="D520" t="n">
-        <v>5.930622100830078</v>
+        <v>5.93062162399292</v>
       </c>
       <c r="E520" t="n">
-        <v>6.123115285960878</v>
+        <v>6.123114793646776</v>
       </c>
       <c r="F520" t="n">
         <v>1532500</v>
@@ -10852,16 +10852,16 @@
         <v>44545</v>
       </c>
       <c r="B522" t="n">
-        <v>5.783960342407227</v>
+        <v>5.783960819244385</v>
       </c>
       <c r="C522" t="n">
-        <v>5.848124878147738</v>
+        <v>5.848125360274703</v>
       </c>
       <c r="D522" t="n">
-        <v>5.527303073615463</v>
+        <v>5.527303529293464</v>
       </c>
       <c r="E522" t="n">
-        <v>5.683130482553606</v>
+        <v>5.68313095107822</v>
       </c>
       <c r="F522" t="n">
         <v>1794200</v>
@@ -10912,16 +10912,16 @@
         <v>44550</v>
       </c>
       <c r="B525" t="n">
-        <v>5.70146369934082</v>
+        <v>5.701463222503662</v>
       </c>
       <c r="C525" t="n">
-        <v>5.756462127946762</v>
+        <v>5.756461646509856</v>
       </c>
       <c r="D525" t="n">
-        <v>5.582301602921769</v>
+        <v>5.582301136050633</v>
       </c>
       <c r="E525" t="n">
-        <v>5.710630249803538</v>
+        <v>5.710629772199743</v>
       </c>
       <c r="F525" t="n">
         <v>2934100</v>
@@ -10952,16 +10952,16 @@
         <v>44552</v>
       </c>
       <c r="B527" t="n">
-        <v>5.453971862792969</v>
+        <v>5.453972339630127</v>
       </c>
       <c r="C527" t="n">
-        <v>5.646465028499557</v>
+        <v>5.646465522166265</v>
       </c>
       <c r="D527" t="n">
-        <v>5.42647308888353</v>
+        <v>5.426473563316489</v>
       </c>
       <c r="E527" t="n">
-        <v>5.618966254590118</v>
+        <v>5.618966745852627</v>
       </c>
       <c r="F527" t="n">
         <v>3033600</v>
@@ -10972,16 +10972,16 @@
         <v>44553</v>
       </c>
       <c r="B528" t="n">
-        <v>5.453971862792969</v>
+        <v>5.453972339630127</v>
       </c>
       <c r="C528" t="n">
-        <v>5.481471073787537</v>
+        <v>5.481471553028933</v>
       </c>
       <c r="D528" t="n">
-        <v>5.325643231350287</v>
+        <v>5.325643696967758</v>
       </c>
       <c r="E528" t="n">
-        <v>5.444805750518199</v>
+        <v>5.444806226553971</v>
       </c>
       <c r="F528" t="n">
         <v>2899900</v>
@@ -11012,16 +11012,16 @@
         <v>44558</v>
       </c>
       <c r="B530" t="n">
-        <v>5.719795703887939</v>
+        <v>5.719796180725098</v>
       </c>
       <c r="C530" t="n">
-        <v>5.756461464427344</v>
+        <v>5.756461944321184</v>
       </c>
       <c r="D530" t="n">
-        <v>5.527302974295581</v>
+        <v>5.527303435085368</v>
       </c>
       <c r="E530" t="n">
-        <v>5.563968297749852</v>
+        <v>5.563968761596285</v>
       </c>
       <c r="F530" t="n">
         <v>2551400</v>
@@ -11072,16 +11072,16 @@
         <v>44564</v>
       </c>
       <c r="B533" t="n">
-        <v>5.417306900024414</v>
+        <v>5.417306423187256</v>
       </c>
       <c r="C533" t="n">
-        <v>5.774794481317564</v>
+        <v>5.774793973013967</v>
       </c>
       <c r="D533" t="n">
-        <v>5.371475461430403</v>
+        <v>5.371474988627377</v>
       </c>
       <c r="E533" t="n">
-        <v>5.655631954219848</v>
+        <v>5.655631456405064</v>
       </c>
       <c r="F533" t="n">
         <v>2044700</v>
@@ -11112,16 +11112,16 @@
         <v>44566</v>
       </c>
       <c r="B535" t="n">
-        <v>4.885658740997314</v>
+        <v>4.885659217834473</v>
       </c>
       <c r="C535" t="n">
-        <v>5.0689857878987</v>
+        <v>5.06898628262846</v>
       </c>
       <c r="D535" t="n">
-        <v>4.839827307085804</v>
+        <v>4.839827779449844</v>
       </c>
       <c r="E535" t="n">
-        <v>5.023153916902075</v>
+        <v>5.023154407158674</v>
       </c>
       <c r="F535" t="n">
         <v>2302400</v>
@@ -11172,16 +11172,16 @@
         <v>44571</v>
       </c>
       <c r="B538" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C538" t="n">
-        <v>4.894826206904368</v>
+        <v>4.894825720038117</v>
       </c>
       <c r="D538" t="n">
-        <v>4.62900235433546</v>
+        <v>4.629001893909508</v>
       </c>
       <c r="E538" t="n">
-        <v>4.720665676413498</v>
+        <v>4.720665206870209</v>
       </c>
       <c r="F538" t="n">
         <v>3868800</v>
@@ -11192,16 +11192,16 @@
         <v>44572</v>
       </c>
       <c r="B539" t="n">
-        <v>5.00482177734375</v>
+        <v>5.004822254180908</v>
       </c>
       <c r="C539" t="n">
-        <v>5.059819766018552</v>
+        <v>5.059820248095674</v>
       </c>
       <c r="D539" t="n">
-        <v>4.766496722667781</v>
+        <v>4.766497176798388</v>
       </c>
       <c r="E539" t="n">
-        <v>4.775663272656161</v>
+        <v>4.775663727660117</v>
       </c>
       <c r="F539" t="n">
         <v>2192500</v>
@@ -11212,16 +11212,16 @@
         <v>44573</v>
       </c>
       <c r="B540" t="n">
-        <v>5.169815540313721</v>
+        <v>5.169816017150879</v>
       </c>
       <c r="C540" t="n">
-        <v>5.270645400799818</v>
+        <v>5.270645886937004</v>
       </c>
       <c r="D540" t="n">
-        <v>4.995655031141423</v>
+        <v>4.995655491914913</v>
       </c>
       <c r="E540" t="n">
-        <v>5.032320355484523</v>
+        <v>5.032320819639834</v>
       </c>
       <c r="F540" t="n">
         <v>2344800</v>
@@ -11272,16 +11272,16 @@
         <v>44578</v>
       </c>
       <c r="B543" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C543" t="n">
-        <v>5.105651419324723</v>
+        <v>5.105651915770163</v>
       </c>
       <c r="D543" t="n">
-        <v>4.821494938343708</v>
+        <v>4.821495407159335</v>
       </c>
       <c r="E543" t="n">
-        <v>5.041486883457342</v>
+        <v>5.041487373663776</v>
       </c>
       <c r="F543" t="n">
         <v>1383000</v>
@@ -11292,16 +11292,16 @@
         <v>44579</v>
       </c>
       <c r="B544" t="n">
-        <v>4.803162097930908</v>
+        <v>4.80316162109375</v>
       </c>
       <c r="C544" t="n">
-        <v>4.977322615737815</v>
+        <v>4.977322121610753</v>
       </c>
       <c r="D544" t="n">
-        <v>4.748164108689543</v>
+        <v>4.748163637312347</v>
       </c>
       <c r="E544" t="n">
-        <v>4.913158513498805</v>
+        <v>4.913158025741677</v>
       </c>
       <c r="F544" t="n">
         <v>2424100</v>
@@ -11312,16 +11312,16 @@
         <v>44580</v>
       </c>
       <c r="B545" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C545" t="n">
-        <v>5.050653537402776</v>
+        <v>5.050653052647643</v>
       </c>
       <c r="D545" t="n">
-        <v>4.812328488186932</v>
+        <v>4.812328026305926</v>
       </c>
       <c r="E545" t="n">
-        <v>4.839827700436895</v>
+        <v>4.839827235916551</v>
       </c>
       <c r="F545" t="n">
         <v>2176700</v>
@@ -11552,16 +11552,16 @@
         <v>44596</v>
       </c>
       <c r="B557" t="n">
-        <v>5.490636825561523</v>
+        <v>5.490637302398682</v>
       </c>
       <c r="C557" t="n">
-        <v>5.637298546094581</v>
+        <v>5.637299035668652</v>
       </c>
       <c r="D557" t="n">
-        <v>5.37147475130261</v>
+        <v>5.371475217791077</v>
       </c>
       <c r="E557" t="n">
-        <v>5.628131997336533</v>
+        <v>5.628132486114529</v>
       </c>
       <c r="F557" t="n">
         <v>2310300</v>
@@ -11812,16 +11812,16 @@
         <v>44615</v>
       </c>
       <c r="B570" t="n">
-        <v>4.867326736450195</v>
+        <v>4.867326259613037</v>
       </c>
       <c r="C570" t="n">
-        <v>5.013988044082764</v>
+        <v>5.013987552877644</v>
       </c>
       <c r="D570" t="n">
-        <v>4.803162195818359</v>
+        <v>4.803161725267206</v>
       </c>
       <c r="E570" t="n">
-        <v>4.949823940536103</v>
+        <v>4.949823455616944</v>
       </c>
       <c r="F570" t="n">
         <v>3505100</v>
@@ -11872,16 +11872,16 @@
         <v>44622</v>
       </c>
       <c r="B573" t="n">
-        <v>4.647334575653076</v>
+        <v>4.647335052490234</v>
       </c>
       <c r="C573" t="n">
-        <v>4.738997888991517</v>
+        <v>4.738998375233738</v>
       </c>
       <c r="D573" t="n">
-        <v>4.58317003777359</v>
+        <v>4.583170508027182</v>
       </c>
       <c r="E573" t="n">
-        <v>4.665667238320764</v>
+        <v>4.665667717038935</v>
       </c>
       <c r="F573" t="n">
         <v>2274100</v>
@@ -11932,16 +11932,16 @@
         <v>44627</v>
       </c>
       <c r="B576" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="C576" t="n">
-        <v>4.46400783481362</v>
+        <v>4.464007312971596</v>
       </c>
       <c r="D576" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="E576" t="n">
-        <v>4.46400783481362</v>
+        <v>4.464007312971596</v>
       </c>
       <c r="F576" t="n">
         <v>3496200</v>
@@ -11952,16 +11952,16 @@
         <v>44628</v>
       </c>
       <c r="B577" t="n">
-        <v>4.124853134155273</v>
+        <v>4.124852657318115</v>
       </c>
       <c r="C577" t="n">
-        <v>4.207350336705632</v>
+        <v>4.207349850331715</v>
       </c>
       <c r="D577" t="n">
-        <v>3.969025279153559</v>
+        <v>3.969024820330257</v>
       </c>
       <c r="E577" t="n">
-        <v>4.134019684254276</v>
+        <v>4.134019206357456</v>
       </c>
       <c r="F577" t="n">
         <v>4412200</v>
@@ -11972,16 +11972,16 @@
         <v>44629</v>
       </c>
       <c r="B578" t="n">
-        <v>4.335678577423096</v>
+        <v>4.335679054260254</v>
       </c>
       <c r="C578" t="n">
-        <v>4.418175772342043</v>
+        <v>4.418176258252227</v>
       </c>
       <c r="D578" t="n">
-        <v>4.161518075419278</v>
+        <v>4.161518533102296</v>
       </c>
       <c r="E578" t="n">
-        <v>4.170684624670328</v>
+        <v>4.17068508336148</v>
       </c>
       <c r="F578" t="n">
         <v>3479000</v>
@@ -12172,16 +12172,16 @@
         <v>44643</v>
       </c>
       <c r="B588" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C588" t="n">
-        <v>4.839828213657545</v>
+        <v>4.839827732261697</v>
       </c>
       <c r="D588" t="n">
-        <v>4.574003924003441</v>
+        <v>4.574003469047934</v>
       </c>
       <c r="E588" t="n">
-        <v>4.656501132416273</v>
+        <v>4.656500669255141</v>
       </c>
       <c r="F588" t="n">
         <v>5289000</v>
@@ -12212,16 +12212,16 @@
         <v>44645</v>
       </c>
       <c r="B590" t="n">
-        <v>4.986489295959473</v>
+        <v>4.986488819122314</v>
       </c>
       <c r="C590" t="n">
-        <v>5.270645799665109</v>
+        <v>5.270645295655251</v>
       </c>
       <c r="D590" t="n">
-        <v>4.958990082078524</v>
+        <v>4.958989607871001</v>
       </c>
       <c r="E590" t="n">
-        <v>5.078152613754004</v>
+        <v>5.078152128151466</v>
       </c>
       <c r="F590" t="n">
         <v>4172200</v>
@@ -12232,16 +12232,16 @@
         <v>44648</v>
       </c>
       <c r="B591" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C591" t="n">
-        <v>5.142316768551991</v>
+        <v>5.142317254043173</v>
       </c>
       <c r="D591" t="n">
-        <v>4.885659060917757</v>
+        <v>4.885659522177632</v>
       </c>
       <c r="E591" t="n">
-        <v>5.013987696192302</v>
+        <v>5.01398816956781</v>
       </c>
       <c r="F591" t="n">
         <v>3528600</v>
@@ -12252,16 +12252,16 @@
         <v>44649</v>
       </c>
       <c r="B592" t="n">
-        <v>5.33480978012085</v>
+        <v>5.334810256958008</v>
       </c>
       <c r="C592" t="n">
-        <v>5.362308554027249</v>
+        <v>5.362309033322309</v>
       </c>
       <c r="D592" t="n">
-        <v>5.142316614435527</v>
+        <v>5.142317074067217</v>
       </c>
       <c r="E592" t="n">
-        <v>5.16064927606817</v>
+        <v>5.160649737338475</v>
       </c>
       <c r="F592" t="n">
         <v>3923800</v>
@@ -12292,16 +12292,16 @@
         <v>44651</v>
       </c>
       <c r="B594" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C594" t="n">
-        <v>5.224813529828769</v>
+        <v>5.224814023108552</v>
       </c>
       <c r="D594" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="E594" t="n">
-        <v>5.178982092916146</v>
+        <v>5.178982581868937</v>
       </c>
       <c r="F594" t="n">
         <v>1926600</v>
@@ -12452,16 +12452,16 @@
         <v>44663</v>
       </c>
       <c r="B602" t="n">
-        <v>4.372344493865967</v>
+        <v>4.372344017028809</v>
       </c>
       <c r="C602" t="n">
-        <v>4.519005805113152</v>
+        <v>4.519005312281472</v>
       </c>
       <c r="D602" t="n">
-        <v>4.36317838045561</v>
+        <v>4.363177904618086</v>
       </c>
       <c r="E602" t="n">
-        <v>4.464007813395457</v>
+        <v>4.464007326561723</v>
       </c>
       <c r="F602" t="n">
         <v>2977800</v>
@@ -12472,16 +12472,16 @@
         <v>44664</v>
       </c>
       <c r="B603" t="n">
-        <v>4.482340335845947</v>
+        <v>4.482339859008789</v>
       </c>
       <c r="C603" t="n">
-        <v>4.500672999173296</v>
+        <v>4.500672520385886</v>
       </c>
       <c r="D603" t="n">
-        <v>4.344845142348245</v>
+        <v>4.344844680138003</v>
       </c>
       <c r="E603" t="n">
-        <v>4.427342345863901</v>
+        <v>4.4273418748775</v>
       </c>
       <c r="F603" t="n">
         <v>2309600</v>
@@ -12512,16 +12512,16 @@
         <v>44669</v>
       </c>
       <c r="B605" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="C605" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="D605" t="n">
-        <v>4.372344289398597</v>
+        <v>4.372343829900955</v>
       </c>
       <c r="E605" t="n">
-        <v>4.45484149165985</v>
+        <v>4.454841023492427</v>
       </c>
       <c r="F605" t="n">
         <v>2710700</v>
@@ -12552,16 +12552,16 @@
         <v>44671</v>
       </c>
       <c r="B607" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="C607" t="n">
-        <v>4.509839386853855</v>
+        <v>4.509839880756772</v>
       </c>
       <c r="D607" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="E607" t="n">
-        <v>4.418176073520475</v>
+        <v>4.418176557384724</v>
       </c>
       <c r="F607" t="n">
         <v>2075500</v>
@@ -12572,16 +12572,16 @@
         <v>44673</v>
       </c>
       <c r="B608" t="n">
-        <v>4.097353935241699</v>
+        <v>4.097354412078857</v>
       </c>
       <c r="C608" t="n">
-        <v>4.308179780317636</v>
+        <v>4.308180281690042</v>
       </c>
       <c r="D608" t="n">
-        <v>4.079021272064886</v>
+        <v>4.079021746768547</v>
       </c>
       <c r="E608" t="n">
-        <v>4.308179780317636</v>
+        <v>4.308180281690042</v>
       </c>
       <c r="F608" t="n">
         <v>4745700</v>
@@ -12612,16 +12612,16 @@
         <v>44677</v>
       </c>
       <c r="B610" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="C610" t="n">
-        <v>4.189017874905755</v>
+        <v>4.189017385210027</v>
       </c>
       <c r="D610" t="n">
-        <v>4.024023461875849</v>
+        <v>4.02402299146795</v>
       </c>
       <c r="E610" t="n">
-        <v>4.042356125869706</v>
+        <v>4.042355653318721</v>
       </c>
       <c r="F610" t="n">
         <v>5064800</v>
@@ -12632,16 +12632,16 @@
         <v>44678</v>
       </c>
       <c r="B611" t="n">
-        <v>3.97819185256958</v>
+        <v>3.978191614151001</v>
       </c>
       <c r="C611" t="n">
-        <v>4.170685034925215</v>
+        <v>4.170684784970252</v>
       </c>
       <c r="D611" t="n">
-        <v>3.941526526128999</v>
+        <v>3.941526289907824</v>
       </c>
       <c r="E611" t="n">
-        <v>4.170685034925215</v>
+        <v>4.170684784970252</v>
       </c>
       <c r="F611" t="n">
         <v>4173400</v>
@@ -12812,16 +12812,16 @@
         <v>44691</v>
       </c>
       <c r="B620" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C620" t="n">
-        <v>2.887397395893507</v>
+        <v>2.887397154408436</v>
       </c>
       <c r="D620" t="n">
-        <v>2.694904207028261</v>
+        <v>2.694903981642197</v>
       </c>
       <c r="E620" t="n">
-        <v>2.814066521989905</v>
+        <v>2.8140662866378</v>
       </c>
       <c r="F620" t="n">
         <v>7309900</v>
@@ -12852,16 +12852,16 @@
         <v>44693</v>
       </c>
       <c r="B622" t="n">
-        <v>2.942394971847534</v>
+        <v>2.942395210266113</v>
       </c>
       <c r="C622" t="n">
-        <v>3.02489194747728</v>
+        <v>3.024892192580485</v>
       </c>
       <c r="D622" t="n">
-        <v>2.814066124547592</v>
+        <v>2.814066352567845</v>
       </c>
       <c r="E622" t="n">
-        <v>2.869064326843316</v>
+        <v>2.869064559320005</v>
       </c>
       <c r="F622" t="n">
         <v>3382300</v>
@@ -12872,16 +12872,16 @@
         <v>44694</v>
       </c>
       <c r="B623" t="n">
-        <v>3.043225049972534</v>
+        <v>3.043224811553955</v>
       </c>
       <c r="C623" t="n">
-        <v>3.10738959219715</v>
+        <v>3.107389348751661</v>
       </c>
       <c r="D623" t="n">
-        <v>2.942395398472212</v>
+        <v>2.942395167953036</v>
       </c>
       <c r="E623" t="n">
-        <v>2.969894394335936</v>
+        <v>2.969894161662377</v>
       </c>
       <c r="F623" t="n">
         <v>4357400</v>
@@ -12932,16 +12932,16 @@
         <v>44699</v>
       </c>
       <c r="B626" t="n">
-        <v>2.85989785194397</v>
+        <v>2.859898090362549</v>
       </c>
       <c r="C626" t="n">
-        <v>3.089056342075733</v>
+        <v>3.089056599598365</v>
       </c>
       <c r="D626" t="n">
-        <v>2.850731521080402</v>
+        <v>2.85073175873482</v>
       </c>
       <c r="E626" t="n">
-        <v>3.079890011212165</v>
+        <v>3.079890267970636</v>
       </c>
       <c r="F626" t="n">
         <v>5243400</v>
@@ -13112,16 +13112,16 @@
         <v>44712</v>
       </c>
       <c r="B635" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C635" t="n">
-        <v>3.015726042775277</v>
+        <v>3.015725790557546</v>
       </c>
       <c r="D635" t="n">
-        <v>2.804900190069778</v>
+        <v>2.804899955484291</v>
       </c>
       <c r="E635" t="n">
-        <v>2.988227047014898</v>
+        <v>2.988226797097023</v>
       </c>
       <c r="F635" t="n">
         <v>7519800</v>
@@ -13192,16 +13192,16 @@
         <v>44718</v>
       </c>
       <c r="B639" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C639" t="n">
-        <v>2.859898153024676</v>
+        <v>2.859897899145521</v>
       </c>
       <c r="D639" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="E639" t="n">
-        <v>2.81406649388183</v>
+        <v>2.814066244071248</v>
       </c>
       <c r="F639" t="n">
         <v>3115900</v>
@@ -13212,16 +13212,16 @@
         <v>44719</v>
       </c>
       <c r="B640" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C640" t="n">
-        <v>2.713236544142034</v>
+        <v>2.713236786657148</v>
       </c>
       <c r="D640" t="n">
-        <v>2.584907694170964</v>
+        <v>2.584907925215759</v>
       </c>
       <c r="E640" t="n">
-        <v>2.658238559244103</v>
+        <v>2.658238796843375</v>
       </c>
       <c r="F640" t="n">
         <v>2825300</v>
@@ -13232,16 +13232,16 @@
         <v>44720</v>
       </c>
       <c r="B641" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C641" t="n">
-        <v>2.722402874958356</v>
+        <v>2.722403118292777</v>
       </c>
       <c r="D641" t="n">
-        <v>2.63990589761146</v>
+        <v>2.639906133572117</v>
       </c>
       <c r="E641" t="n">
-        <v>2.649072228427781</v>
+        <v>2.649072465207746</v>
       </c>
       <c r="F641" t="n">
         <v>3025200</v>
@@ -13272,16 +13272,16 @@
         <v>44722</v>
       </c>
       <c r="B643" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C643" t="n">
-        <v>2.63073952891308</v>
+        <v>2.630739779558241</v>
       </c>
       <c r="D643" t="n">
-        <v>2.493244557226074</v>
+        <v>2.493244794771327</v>
       </c>
       <c r="E643" t="n">
-        <v>2.594074203129878</v>
+        <v>2.594074450281731</v>
       </c>
       <c r="F643" t="n">
         <v>4379600</v>
@@ -13292,16 +13292,16 @@
         <v>44725</v>
       </c>
       <c r="B644" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C644" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="D644" t="n">
-        <v>2.282418486052185</v>
+        <v>2.282418717049181</v>
       </c>
       <c r="E644" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="F644" t="n">
         <v>5369000</v>
@@ -13312,16 +13312,16 @@
         <v>44726</v>
       </c>
       <c r="B645" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C645" t="n">
-        <v>2.401580660851382</v>
+        <v>2.401580915813275</v>
       </c>
       <c r="D645" t="n">
-        <v>2.236586719791586</v>
+        <v>2.236586957237029</v>
       </c>
       <c r="E645" t="n">
-        <v>2.374081670674749</v>
+        <v>2.374081922717234</v>
       </c>
       <c r="F645" t="n">
         <v>2610500</v>
@@ -13392,16 +13392,16 @@
         <v>44733</v>
       </c>
       <c r="B649" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="C649" t="n">
-        <v>2.328250420451433</v>
+        <v>2.328250174279411</v>
       </c>
       <c r="D649" t="n">
-        <v>2.236587104111843</v>
+        <v>2.236586867631624</v>
       </c>
       <c r="E649" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="F649" t="n">
         <v>3435200</v>
@@ -13412,16 +13412,16 @@
         <v>44734</v>
       </c>
       <c r="B650" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C650" t="n">
-        <v>2.300751030203729</v>
+        <v>2.300751274461124</v>
       </c>
       <c r="D650" t="n">
-        <v>2.190755069497199</v>
+        <v>2.190755302076961</v>
       </c>
       <c r="E650" t="n">
-        <v>2.236586719791586</v>
+        <v>2.236586957237029</v>
       </c>
       <c r="F650" t="n">
         <v>3144500</v>
@@ -13452,16 +13452,16 @@
         <v>44736</v>
       </c>
       <c r="B652" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C652" t="n">
-        <v>2.355749010556994</v>
+        <v>2.355749260653206</v>
       </c>
       <c r="D652" t="n">
-        <v>2.209087729614954</v>
+        <v>2.209087964140989</v>
       </c>
       <c r="E652" t="n">
-        <v>2.337416350439239</v>
+        <v>2.337416598589179</v>
       </c>
       <c r="F652" t="n">
         <v>3887000</v>
@@ -13472,16 +13472,16 @@
         <v>44739</v>
       </c>
       <c r="B653" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C653" t="n">
-        <v>2.291584773416974</v>
+        <v>2.291585025979039</v>
       </c>
       <c r="D653" t="n">
-        <v>2.154089599594934</v>
+        <v>2.154089837003265</v>
       </c>
       <c r="E653" t="n">
-        <v>2.273252112713042</v>
+        <v>2.273252363254613</v>
       </c>
       <c r="F653" t="n">
         <v>3063200</v>
@@ -13512,16 +13512,16 @@
         <v>44741</v>
       </c>
       <c r="B655" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C655" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="D655" t="n">
-        <v>2.016594984404464</v>
+        <v>2.016594758317869</v>
       </c>
       <c r="E655" t="n">
-        <v>2.089925639587051</v>
+        <v>2.089925405279133</v>
       </c>
       <c r="F655" t="n">
         <v>5733700</v>
@@ -13632,16 +13632,16 @@
         <v>44749</v>
       </c>
       <c r="B661" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C661" t="n">
-        <v>2.392414452347443</v>
+        <v>2.392414694476813</v>
       </c>
       <c r="D661" t="n">
-        <v>2.300751147101395</v>
+        <v>2.300751379953786</v>
       </c>
       <c r="E661" t="n">
-        <v>2.337416469199814</v>
+        <v>2.337416705762997</v>
       </c>
       <c r="F661" t="n">
         <v>2762300</v>
@@ -13652,16 +13652,16 @@
         <v>44750</v>
       </c>
       <c r="B662" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="C662" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="D662" t="n">
-        <v>2.300751402022951</v>
+        <v>2.300751173614302</v>
       </c>
       <c r="E662" t="n">
-        <v>2.337416728183861</v>
+        <v>2.337416496135238</v>
       </c>
       <c r="F662" t="n">
         <v>2746100</v>
@@ -13672,16 +13672,16 @@
         <v>44753</v>
       </c>
       <c r="B663" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C663" t="n">
-        <v>2.383248305010609</v>
+        <v>2.38324806191716</v>
       </c>
       <c r="D663" t="n">
-        <v>2.273252330260538</v>
+        <v>2.273252098386777</v>
       </c>
       <c r="E663" t="n">
-        <v>2.346582980093919</v>
+        <v>2.346582740740366</v>
       </c>
       <c r="F663" t="n">
         <v>1807800</v>
@@ -13692,16 +13692,16 @@
         <v>44754</v>
       </c>
       <c r="B664" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="C664" t="n">
-        <v>2.447412925209175</v>
+        <v>2.447412682240605</v>
       </c>
       <c r="D664" t="n">
-        <v>2.254919744321813</v>
+        <v>2.254919520463134</v>
       </c>
       <c r="E664" t="n">
-        <v>2.355749391264316</v>
+        <v>2.355749157395706</v>
       </c>
       <c r="F664" t="n">
         <v>5712200</v>
@@ -13752,16 +13752,16 @@
         <v>44757</v>
       </c>
       <c r="B667" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C667" t="n">
-        <v>2.245753121657145</v>
+        <v>2.245753369167974</v>
       </c>
       <c r="D667" t="n">
-        <v>2.135756938891002</v>
+        <v>2.135757174278839</v>
       </c>
       <c r="E667" t="n">
-        <v>2.227420460953214</v>
+        <v>2.227420706443548</v>
       </c>
       <c r="F667" t="n">
         <v>2806200</v>
@@ -13772,16 +13772,16 @@
         <v>44760</v>
       </c>
       <c r="B668" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="C668" t="n">
-        <v>2.346583083719351</v>
+        <v>2.346582835608969</v>
       </c>
       <c r="D668" t="n">
-        <v>2.199921777576007</v>
+        <v>2.19992154497251</v>
       </c>
       <c r="E668" t="n">
-        <v>2.199921777576007</v>
+        <v>2.19992154497251</v>
       </c>
       <c r="F668" t="n">
         <v>4381400</v>
@@ -13832,16 +13832,16 @@
         <v>44763</v>
       </c>
       <c r="B671" t="n">
-        <v>2.383248090744019</v>
+        <v>2.383248329162598</v>
       </c>
       <c r="C671" t="n">
-        <v>2.474911613337284</v>
+        <v>2.474911860925822</v>
       </c>
       <c r="D671" t="n">
-        <v>2.346582769123735</v>
+        <v>2.346583003874339</v>
       </c>
       <c r="E671" t="n">
-        <v>2.364915429933876</v>
+        <v>2.364915666518468</v>
       </c>
       <c r="F671" t="n">
         <v>3831200</v>
@@ -13872,16 +13872,16 @@
         <v>44767</v>
       </c>
       <c r="B673" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C673" t="n">
-        <v>2.392414452347443</v>
+        <v>2.392414694476813</v>
       </c>
       <c r="D673" t="n">
-        <v>2.25491949447837</v>
+        <v>2.254919722692273</v>
       </c>
       <c r="E673" t="n">
-        <v>2.300751147101395</v>
+        <v>2.300751379953786</v>
       </c>
       <c r="F673" t="n">
         <v>3311300</v>
@@ -13892,16 +13892,16 @@
         <v>44768</v>
       </c>
       <c r="B674" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C674" t="n">
-        <v>2.520743493812202</v>
+        <v>2.520743251874533</v>
       </c>
       <c r="D674" t="n">
-        <v>2.300751325610525</v>
+        <v>2.300751104787417</v>
       </c>
       <c r="E674" t="n">
-        <v>2.374081975496892</v>
+        <v>2.374081747635604</v>
       </c>
       <c r="F674" t="n">
         <v>4848400</v>
@@ -13912,16 +13912,16 @@
         <v>44769</v>
       </c>
       <c r="B675" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C675" t="n">
-        <v>2.603240801706716</v>
+        <v>2.603240558142417</v>
       </c>
       <c r="D675" t="n">
-        <v>2.419914153978682</v>
+        <v>2.419913927566782</v>
       </c>
       <c r="E675" t="n">
-        <v>2.502411145456297</v>
+        <v>2.502410911325818</v>
       </c>
       <c r="F675" t="n">
         <v>5961800</v>
@@ -13952,16 +13952,16 @@
         <v>44771</v>
       </c>
       <c r="B677" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C677" t="n">
-        <v>2.603240523687103</v>
+        <v>2.603240282723132</v>
       </c>
       <c r="D677" t="n">
-        <v>2.493244546797579</v>
+        <v>2.493244316015175</v>
       </c>
       <c r="E677" t="n">
-        <v>2.566575198057261</v>
+        <v>2.566574960487146</v>
       </c>
       <c r="F677" t="n">
         <v>2895400</v>
@@ -13972,16 +13972,16 @@
         <v>44774</v>
       </c>
       <c r="B678" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C678" t="n">
-        <v>2.749902171081845</v>
+        <v>2.749901926967264</v>
       </c>
       <c r="D678" t="n">
-        <v>2.520743656825025</v>
+        <v>2.520743433053326</v>
       </c>
       <c r="E678" t="n">
-        <v>2.57574164779644</v>
+        <v>2.575741419142454</v>
       </c>
       <c r="F678" t="n">
         <v>6003000</v>
@@ -13992,16 +13992,16 @@
         <v>44775</v>
       </c>
       <c r="B679" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C679" t="n">
-        <v>2.740735713341587</v>
+        <v>2.740735459650637</v>
       </c>
       <c r="D679" t="n">
-        <v>2.548242535242341</v>
+        <v>2.548242299369153</v>
       </c>
       <c r="E679" t="n">
-        <v>2.676571393489365</v>
+        <v>2.676571145737662</v>
       </c>
       <c r="F679" t="n">
         <v>4865400</v>
@@ -14032,16 +14032,16 @@
         <v>44777</v>
       </c>
       <c r="B681" t="n">
-        <v>2.85989785194397</v>
+        <v>2.859898090362549</v>
       </c>
       <c r="C681" t="n">
-        <v>2.878230732213672</v>
+        <v>2.878230972160592</v>
       </c>
       <c r="D681" t="n">
-        <v>2.704070227263316</v>
+        <v>2.704070452691151</v>
       </c>
       <c r="E681" t="n">
-        <v>2.722402888990452</v>
+        <v>2.72240311594661</v>
       </c>
       <c r="F681" t="n">
         <v>7566500</v>
@@ -14052,16 +14052,16 @@
         <v>44778</v>
       </c>
       <c r="B682" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C682" t="n">
-        <v>2.969894420271998</v>
+        <v>2.969894169468031</v>
       </c>
       <c r="D682" t="n">
-        <v>2.731569568829172</v>
+        <v>2.731569338151449</v>
       </c>
       <c r="E682" t="n">
-        <v>2.869064767891131</v>
+        <v>2.869064525602105</v>
       </c>
       <c r="F682" t="n">
         <v>6497600</v>
@@ -14072,16 +14072,16 @@
         <v>44781</v>
       </c>
       <c r="B683" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="C683" t="n">
-        <v>2.924062679704158</v>
+        <v>2.924062427027984</v>
       </c>
       <c r="D683" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="E683" t="n">
-        <v>2.850731806900742</v>
+        <v>2.850731560561287</v>
       </c>
       <c r="F683" t="n">
         <v>8446700</v>
@@ -14132,16 +14132,16 @@
         <v>44784</v>
       </c>
       <c r="B686" t="n">
-        <v>3.034058570861816</v>
+        <v>3.034058332443237</v>
       </c>
       <c r="C686" t="n">
-        <v>3.153221099034329</v>
+        <v>3.15322085125187</v>
       </c>
       <c r="D686" t="n">
-        <v>2.887397266701901</v>
+        <v>2.887397039808076</v>
       </c>
       <c r="E686" t="n">
-        <v>2.896563598211896</v>
+        <v>2.896563370597774</v>
       </c>
       <c r="F686" t="n">
         <v>13306300</v>
@@ -14232,16 +14232,16 @@
         <v>44791</v>
       </c>
       <c r="B691" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="C691" t="n">
-        <v>3.272383248987116</v>
+        <v>3.272383506912668</v>
       </c>
       <c r="D691" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="E691" t="n">
-        <v>3.263216917924395</v>
+        <v>3.263217175127469</v>
       </c>
       <c r="F691" t="n">
         <v>6872400</v>
@@ -14392,16 +14392,16 @@
         <v>44803</v>
       </c>
       <c r="B699" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="C699" t="n">
-        <v>3.162387276234473</v>
+        <v>3.162387525490268</v>
       </c>
       <c r="D699" t="n">
-        <v>2.951561443249337</v>
+        <v>2.951561675888077</v>
       </c>
       <c r="E699" t="n">
-        <v>3.07989007812742</v>
+        <v>3.079890320880878</v>
       </c>
       <c r="F699" t="n">
         <v>4644000</v>
@@ -14432,16 +14432,16 @@
         <v>44805</v>
       </c>
       <c r="B701" t="n">
-        <v>3.125722169876099</v>
+        <v>3.12572193145752</v>
       </c>
       <c r="C701" t="n">
-        <v>3.134888501577799</v>
+        <v>3.134888262460046</v>
       </c>
       <c r="D701" t="n">
-        <v>2.942395317299501</v>
+        <v>2.94239509286442</v>
       </c>
       <c r="E701" t="n">
-        <v>2.951561649001202</v>
+        <v>2.951561423866946</v>
       </c>
       <c r="F701" t="n">
         <v>5408300</v>
@@ -14552,16 +14552,16 @@
         <v>44816</v>
       </c>
       <c r="B707" t="n">
-        <v>3.39154577255249</v>
+        <v>3.391546010971069</v>
       </c>
       <c r="C707" t="n">
-        <v>3.437377427882408</v>
+        <v>3.437377669522857</v>
       </c>
       <c r="D707" t="n">
-        <v>3.327381455090605</v>
+        <v>3.327381688998567</v>
       </c>
       <c r="E707" t="n">
-        <v>3.327381455090605</v>
+        <v>3.327381688998567</v>
       </c>
       <c r="F707" t="n">
         <v>4227100</v>
@@ -14732,16 +14732,16 @@
         <v>44827</v>
       </c>
       <c r="B716" t="n">
-        <v>3.134888172149658</v>
+        <v>3.134888410568237</v>
       </c>
       <c r="C716" t="n">
-        <v>3.254050471749655</v>
+        <v>3.25405071923092</v>
       </c>
       <c r="D716" t="n">
-        <v>3.098222849195813</v>
+        <v>3.098223084825873</v>
       </c>
       <c r="E716" t="n">
-        <v>3.098222849195813</v>
+        <v>3.098223084825873</v>
       </c>
       <c r="F716" t="n">
         <v>4782400</v>
@@ -14792,16 +14792,16 @@
         <v>44832</v>
       </c>
       <c r="B719" t="n">
-        <v>2.942394971847534</v>
+        <v>2.942395210266113</v>
       </c>
       <c r="C719" t="n">
-        <v>2.960727633098589</v>
+        <v>2.96072787300264</v>
       </c>
       <c r="D719" t="n">
-        <v>2.841565116424174</v>
+        <v>2.841565346672636</v>
       </c>
       <c r="E719" t="n">
-        <v>2.896563318719898</v>
+        <v>2.896563553424795</v>
       </c>
       <c r="F719" t="n">
         <v>3561500</v>
@@ -14812,16 +14812,16 @@
         <v>44833</v>
       </c>
       <c r="B720" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C720" t="n">
-        <v>2.905730096029628</v>
+        <v>2.90572985064426</v>
       </c>
       <c r="D720" t="n">
-        <v>2.795733893071542</v>
+        <v>2.79573365697522</v>
       </c>
       <c r="E720" t="n">
-        <v>2.896563763995004</v>
+        <v>2.896563519383722</v>
       </c>
       <c r="F720" t="n">
         <v>3966200</v>
@@ -14932,16 +14932,16 @@
         <v>44841</v>
       </c>
       <c r="B726" t="n">
-        <v>3.44654369354248</v>
+        <v>3.44654393196106</v>
       </c>
       <c r="C726" t="n">
-        <v>3.602371537249589</v>
+        <v>3.602371786447736</v>
       </c>
       <c r="D726" t="n">
-        <v>3.419044700866385</v>
+        <v>3.41904493738269</v>
       </c>
       <c r="E726" t="n">
-        <v>3.464876355326544</v>
+        <v>3.464876595013306</v>
       </c>
       <c r="F726" t="n">
         <v>4739800</v>
@@ -15012,16 +15012,16 @@
         <v>44848</v>
       </c>
       <c r="B730" t="n">
-        <v>3.052391052246094</v>
+        <v>3.052391290664673</v>
       </c>
       <c r="C730" t="n">
-        <v>3.199052566221344</v>
+        <v>3.199052816095478</v>
       </c>
       <c r="D730" t="n">
-        <v>2.997393066458838</v>
+        <v>2.997393300581591</v>
       </c>
       <c r="E730" t="n">
-        <v>3.153220911398631</v>
+        <v>3.153221157692909</v>
       </c>
       <c r="F730" t="n">
         <v>2652600</v>
@@ -15032,16 +15032,16 @@
         <v>44851</v>
       </c>
       <c r="B731" t="n">
-        <v>3.034058570861816</v>
+        <v>3.034058332443237</v>
       </c>
       <c r="C731" t="n">
-        <v>3.116555772994351</v>
+        <v>3.11655552809308</v>
       </c>
       <c r="D731" t="n">
-        <v>3.024892239351822</v>
+        <v>3.02489200165354</v>
       </c>
       <c r="E731" t="n">
-        <v>3.07989022841179</v>
+        <v>3.079889986391725</v>
       </c>
       <c r="F731" t="n">
         <v>3944900</v>
@@ -15092,16 +15092,16 @@
         <v>44854</v>
       </c>
       <c r="B734" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C734" t="n">
-        <v>2.95156135187282</v>
+        <v>2.951561601940523</v>
       </c>
       <c r="D734" t="n">
-        <v>2.795733510088233</v>
+        <v>2.795733746953598</v>
       </c>
       <c r="E734" t="n">
-        <v>2.942395021093878</v>
+        <v>2.942395270384973</v>
       </c>
       <c r="F734" t="n">
         <v>4518300</v>
@@ -15112,16 +15112,16 @@
         <v>44855</v>
       </c>
       <c r="B735" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C735" t="n">
-        <v>2.869064374862337</v>
+        <v>2.869064617940577</v>
       </c>
       <c r="D735" t="n">
-        <v>2.685737540740923</v>
+        <v>2.685737768287004</v>
       </c>
       <c r="E735" t="n">
-        <v>2.804899840867176</v>
+        <v>2.804900078509148</v>
       </c>
       <c r="F735" t="n">
         <v>6831600</v>
@@ -15132,16 +15132,16 @@
         <v>44858</v>
       </c>
       <c r="B736" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C736" t="n">
-        <v>2.814066387171744</v>
+        <v>2.814066144805841</v>
       </c>
       <c r="D736" t="n">
-        <v>2.704070409399987</v>
+        <v>2.704070176507662</v>
       </c>
       <c r="E736" t="n">
-        <v>2.795733724209785</v>
+        <v>2.795733483422811</v>
       </c>
       <c r="F736" t="n">
         <v>4201100</v>
@@ -15172,16 +15172,16 @@
         <v>44860</v>
       </c>
       <c r="B738" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C738" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="D738" t="n">
-        <v>2.438246512690039</v>
+        <v>2.438246278670322</v>
       </c>
       <c r="E738" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="F738" t="n">
         <v>9447400</v>
@@ -15232,16 +15232,16 @@
         <v>44865</v>
       </c>
       <c r="B741" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C741" t="n">
-        <v>2.832399050133704</v>
+        <v>2.832398806188871</v>
       </c>
       <c r="D741" t="n">
-        <v>2.557408887161731</v>
+        <v>2.55740866690086</v>
       </c>
       <c r="E741" t="n">
-        <v>2.59407421308565</v>
+        <v>2.59407398966692</v>
       </c>
       <c r="F741" t="n">
         <v>6603200</v>
@@ -15292,16 +15292,16 @@
         <v>44869</v>
       </c>
       <c r="B744" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C744" t="n">
-        <v>2.933228914967061</v>
+        <v>2.933228662338098</v>
       </c>
       <c r="D744" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="E744" t="n">
-        <v>2.924062583486082</v>
+        <v>2.924062331646583</v>
       </c>
       <c r="F744" t="n">
         <v>7869400</v>
@@ -15392,16 +15392,16 @@
         <v>44876</v>
       </c>
       <c r="B749" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C749" t="n">
-        <v>2.429079869570562</v>
+        <v>2.429080127451886</v>
       </c>
       <c r="D749" t="n">
-        <v>2.227420389732709</v>
+        <v>2.227420626205016</v>
       </c>
       <c r="E749" t="n">
-        <v>2.319083690321484</v>
+        <v>2.319083936525152</v>
       </c>
       <c r="F749" t="n">
         <v>8256600</v>
@@ -15512,16 +15512,16 @@
         <v>44887</v>
       </c>
       <c r="B755" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C755" t="n">
-        <v>2.209087984933213</v>
+        <v>2.209088230483989</v>
       </c>
       <c r="D755" t="n">
-        <v>2.108258124089469</v>
+        <v>2.10825835843252</v>
       </c>
       <c r="E755" t="n">
-        <v>2.181588991578348</v>
+        <v>2.181589234072479</v>
       </c>
       <c r="F755" t="n">
         <v>3236000</v>
@@ -15572,16 +15572,16 @@
         <v>44890</v>
       </c>
       <c r="B758" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C758" t="n">
-        <v>2.254919640524655</v>
+        <v>2.25491989116984</v>
       </c>
       <c r="D758" t="n">
-        <v>2.117424455207757</v>
+        <v>2.117424690569691</v>
       </c>
       <c r="E758" t="n">
-        <v>2.22742064716979</v>
+        <v>2.22742089475833</v>
       </c>
       <c r="F758" t="n">
         <v>2578200</v>
@@ -15592,16 +15592,16 @@
         <v>44893</v>
       </c>
       <c r="B759" t="n">
-        <v>2.044094085693359</v>
+        <v>2.04409384727478</v>
       </c>
       <c r="C759" t="n">
-        <v>2.144923741778154</v>
+        <v>2.144923491599029</v>
       </c>
       <c r="D759" t="n">
-        <v>2.034927753322014</v>
+        <v>2.034927515972576</v>
       </c>
       <c r="E759" t="n">
-        <v>2.135757409406809</v>
+        <v>2.135757160296825</v>
       </c>
       <c r="F759" t="n">
         <v>2781000</v>
@@ -15672,16 +15672,16 @@
         <v>44897</v>
       </c>
       <c r="B763" t="n">
-        <v>2.181589126586914</v>
+        <v>2.181588888168335</v>
       </c>
       <c r="C763" t="n">
-        <v>2.199921789958015</v>
+        <v>2.199921549535921</v>
       </c>
       <c r="D763" t="n">
-        <v>2.099091922874372</v>
+        <v>2.099091693471637</v>
       </c>
       <c r="E763" t="n">
-        <v>2.154089912987676</v>
+        <v>2.154089677574394</v>
       </c>
       <c r="F763" t="n">
         <v>2941200</v>
@@ -15772,16 +15772,16 @@
         <v>44904</v>
       </c>
       <c r="B768" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C768" t="n">
-        <v>2.172422626667462</v>
+        <v>2.172422383110556</v>
       </c>
       <c r="D768" t="n">
-        <v>2.071592975791404</v>
+        <v>2.071592743538817</v>
       </c>
       <c r="E768" t="n">
-        <v>2.135757299076168</v>
+        <v>2.135757059629924</v>
       </c>
       <c r="F768" t="n">
         <v>2468100</v>
@@ -15792,16 +15792,16 @@
         <v>44907</v>
       </c>
       <c r="B769" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C769" t="n">
-        <v>2.135757299076168</v>
+        <v>2.135757059629924</v>
       </c>
       <c r="D769" t="n">
-        <v>2.034927648200111</v>
+        <v>2.034927420058185</v>
       </c>
       <c r="E769" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="F769" t="n">
         <v>2948100</v>
@@ -15812,16 +15812,16 @@
         <v>44908</v>
       </c>
       <c r="B770" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C770" t="n">
-        <v>2.190755340574407</v>
+        <v>2.190755471267162</v>
       </c>
       <c r="D770" t="n">
-        <v>1.989095835783838</v>
+        <v>1.989095954446297</v>
       </c>
       <c r="E770" t="n">
-        <v>2.144923466066379</v>
+        <v>2.144923594024966</v>
       </c>
       <c r="F770" t="n">
         <v>3298100</v>
@@ -15832,16 +15832,16 @@
         <v>44909</v>
       </c>
       <c r="B771" t="n">
-        <v>1.979929566383362</v>
+        <v>1.979929685592651</v>
       </c>
       <c r="C771" t="n">
-        <v>2.007428560820864</v>
+        <v>2.007428681685836</v>
       </c>
       <c r="D771" t="n">
-        <v>1.888266033049108</v>
+        <v>1.888266146739441</v>
       </c>
       <c r="E771" t="n">
-        <v>1.970763234904195</v>
+        <v>1.97076335356159</v>
       </c>
       <c r="F771" t="n">
         <v>6743600</v>
@@ -15852,16 +15852,16 @@
         <v>44910</v>
       </c>
       <c r="B772" t="n">
-        <v>1.906598567962646</v>
+        <v>1.906598687171936</v>
       </c>
       <c r="C772" t="n">
-        <v>2.044093749458731</v>
+        <v>2.04409387726485</v>
       </c>
       <c r="D772" t="n">
-        <v>1.897432237099079</v>
+        <v>1.897432355735247</v>
       </c>
       <c r="E772" t="n">
-        <v>1.952430440823052</v>
+        <v>1.952430562897961</v>
       </c>
       <c r="F772" t="n">
         <v>3868500</v>
@@ -15912,16 +15912,16 @@
         <v>44915</v>
       </c>
       <c r="B775" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C775" t="n">
-        <v>2.108258224859735</v>
+        <v>2.10825798114297</v>
       </c>
       <c r="D775" t="n">
-        <v>1.879099717406664</v>
+        <v>1.879099500180852</v>
       </c>
       <c r="E775" t="n">
-        <v>1.924931375188761</v>
+        <v>1.924931152664764</v>
       </c>
       <c r="F775" t="n">
         <v>8464700</v>
@@ -15932,16 +15932,16 @@
         <v>44916</v>
       </c>
       <c r="B776" t="n">
-        <v>1.970763087272644</v>
+        <v>1.970763206481934</v>
       </c>
       <c r="C776" t="n">
-        <v>2.108258049160288</v>
+        <v>2.108258176686496</v>
       </c>
       <c r="D776" t="n">
-        <v>1.961596756480134</v>
+        <v>1.961596875134963</v>
       </c>
       <c r="E776" t="n">
-        <v>2.05326006440523</v>
+        <v>2.053260188604671</v>
       </c>
       <c r="F776" t="n">
         <v>5125400</v>
@@ -15952,16 +15952,16 @@
         <v>44917</v>
       </c>
       <c r="B777" t="n">
-        <v>1.906598567962646</v>
+        <v>1.906598687171936</v>
       </c>
       <c r="C777" t="n">
-        <v>1.989095764277324</v>
+        <v>1.989095888644717</v>
       </c>
       <c r="D777" t="n">
-        <v>1.869933244508375</v>
+        <v>1.869933361425181</v>
       </c>
       <c r="E777" t="n">
-        <v>1.952430440823052</v>
+        <v>1.952430562897961</v>
       </c>
       <c r="F777" t="n">
         <v>5426000</v>
@@ -15972,16 +15972,16 @@
         <v>44918</v>
       </c>
       <c r="B778" t="n">
-        <v>1.98909592628479</v>
+        <v>1.9890958070755</v>
       </c>
       <c r="C778" t="n">
-        <v>2.016594921115226</v>
+        <v>2.016594800257883</v>
       </c>
       <c r="D778" t="n">
-        <v>1.906598723250898</v>
+        <v>1.906598608985781</v>
       </c>
       <c r="E778" t="n">
-        <v>1.915765054861043</v>
+        <v>1.915764940046575</v>
       </c>
       <c r="F778" t="n">
         <v>4257800</v>
@@ -15992,16 +15992,16 @@
         <v>44921</v>
       </c>
       <c r="B779" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C779" t="n">
-        <v>2.044093822942382</v>
+        <v>2.044093944885827</v>
       </c>
       <c r="D779" t="n">
-        <v>1.952430511011476</v>
+        <v>1.95243062748661</v>
       </c>
       <c r="E779" t="n">
-        <v>1.989095835783838</v>
+        <v>1.989095954446297</v>
       </c>
       <c r="F779" t="n">
         <v>2247800</v>
@@ -16012,16 +16012,16 @@
         <v>44922</v>
       </c>
       <c r="B780" t="n">
-        <v>1.970763087272644</v>
+        <v>1.970763206481934</v>
       </c>
       <c r="C780" t="n">
-        <v>2.06242639519774</v>
+        <v>2.062426519951642</v>
       </c>
       <c r="D780" t="n">
-        <v>1.934097545560041</v>
+        <v>1.934097662551472</v>
       </c>
       <c r="E780" t="n">
-        <v>2.007428410442682</v>
+        <v>2.007428531869817</v>
       </c>
       <c r="F780" t="n">
         <v>3370000</v>
@@ -16032,16 +16032,16 @@
         <v>44923</v>
       </c>
       <c r="B781" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C781" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="D781" t="n">
-        <v>1.952430495078567</v>
+        <v>1.952430712100627</v>
       </c>
       <c r="E781" t="n">
-        <v>1.970763157315144</v>
+        <v>1.970763376374967</v>
       </c>
       <c r="F781" t="n">
         <v>4579800</v>
@@ -16112,16 +16112,16 @@
         <v>44930</v>
       </c>
       <c r="B785" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C785" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="D785" t="n">
-        <v>1.952430588400603</v>
+        <v>1.952430362697669</v>
       </c>
       <c r="E785" t="n">
-        <v>1.961596919957022</v>
+        <v>1.961596693194451</v>
       </c>
       <c r="F785" t="n">
         <v>2931500</v>
@@ -16172,16 +16172,16 @@
         <v>44935</v>
       </c>
       <c r="B788" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C788" t="n">
-        <v>2.190755139545351</v>
+        <v>2.190755380994696</v>
       </c>
       <c r="D788" t="n">
-        <v>2.071592626427242</v>
+        <v>2.071592854743348</v>
       </c>
       <c r="E788" t="n">
-        <v>2.135756938891002</v>
+        <v>2.135757174278839</v>
       </c>
       <c r="F788" t="n">
         <v>5355300</v>
@@ -16232,16 +16232,16 @@
         <v>44938</v>
       </c>
       <c r="B791" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C791" t="n">
-        <v>2.410747517240701</v>
+        <v>2.410747271342309</v>
       </c>
       <c r="D791" t="n">
-        <v>2.190755349197985</v>
+        <v>2.19075512573899</v>
       </c>
       <c r="E791" t="n">
-        <v>2.282418661489711</v>
+        <v>2.282418428680975</v>
       </c>
       <c r="F791" t="n">
         <v>7447800</v>
@@ -16252,16 +16252,16 @@
         <v>44939</v>
       </c>
       <c r="B792" t="n">
-        <v>2.227420568466187</v>
+        <v>2.227420806884766</v>
       </c>
       <c r="C792" t="n">
-        <v>2.392414522765486</v>
+        <v>2.392414778844683</v>
       </c>
       <c r="D792" t="n">
-        <v>2.19992157608297</v>
+        <v>2.199921811558113</v>
       </c>
       <c r="E792" t="n">
-        <v>2.319083876410242</v>
+        <v>2.319084124640275</v>
       </c>
       <c r="F792" t="n">
         <v>4284200</v>
@@ -16272,16 +16272,16 @@
         <v>44942</v>
       </c>
       <c r="B793" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C793" t="n">
-        <v>2.869064517857597</v>
+        <v>2.869064242488531</v>
       </c>
       <c r="D793" t="n">
-        <v>2.29158499437473</v>
+        <v>2.291584774431394</v>
       </c>
       <c r="E793" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="F793" t="n">
         <v>29414600</v>
@@ -16312,16 +16312,16 @@
         <v>44944</v>
       </c>
       <c r="B795" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C795" t="n">
-        <v>2.493244498303254</v>
+        <v>2.493244243990096</v>
       </c>
       <c r="D795" t="n">
-        <v>2.319083986406401</v>
+        <v>2.31908374985777</v>
       </c>
       <c r="E795" t="n">
-        <v>2.429080179699046</v>
+        <v>2.429079931930706</v>
       </c>
       <c r="F795" t="n">
         <v>5215700</v>
@@ -16352,16 +16352,16 @@
         <v>44946</v>
       </c>
       <c r="B797" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C797" t="n">
-        <v>2.823232502425061</v>
+        <v>2.823232741620247</v>
       </c>
       <c r="D797" t="n">
-        <v>2.291584880161267</v>
+        <v>2.291585074313209</v>
       </c>
       <c r="E797" t="n">
-        <v>2.30075121094021</v>
+        <v>2.300751405868758</v>
       </c>
       <c r="F797" t="n">
         <v>16674600</v>
@@ -16392,16 +16392,16 @@
         <v>44950</v>
       </c>
       <c r="B799" t="n">
-        <v>2.58490777015686</v>
+        <v>2.584908008575439</v>
       </c>
       <c r="C799" t="n">
-        <v>2.704070292814508</v>
+        <v>2.704070542224025</v>
       </c>
       <c r="D799" t="n">
-        <v>2.54824244581376</v>
+        <v>2.548242680850518</v>
       </c>
       <c r="E799" t="n">
-        <v>2.575741439071086</v>
+        <v>2.575741676644209</v>
       </c>
       <c r="F799" t="n">
         <v>6059800</v>
@@ -16452,16 +16452,16 @@
         <v>44953</v>
       </c>
       <c r="B802" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C802" t="n">
-        <v>2.933229055494139</v>
+        <v>2.933228810175975</v>
       </c>
       <c r="D802" t="n">
-        <v>2.704070538948388</v>
+        <v>2.704070312795705</v>
       </c>
       <c r="E802" t="n">
-        <v>2.731569534708767</v>
+        <v>2.731569306256229</v>
       </c>
       <c r="F802" t="n">
         <v>5877300</v>
@@ -16572,16 +16572,16 @@
         <v>44963</v>
       </c>
       <c r="B808" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C808" t="n">
-        <v>2.676571343363308</v>
+        <v>2.676571086469485</v>
       </c>
       <c r="D808" t="n">
-        <v>2.465745506397427</v>
+        <v>2.465745269738393</v>
       </c>
       <c r="E808" t="n">
-        <v>2.658238680891716</v>
+        <v>2.658238425757438</v>
       </c>
       <c r="F808" t="n">
         <v>3450900</v>
@@ -16692,16 +16692,16 @@
         <v>44971</v>
       </c>
       <c r="B814" t="n">
-        <v>2.034927368164062</v>
+        <v>2.034927606582642</v>
       </c>
       <c r="C814" t="n">
-        <v>2.172422327710077</v>
+        <v>2.172422582238004</v>
       </c>
       <c r="D814" t="n">
-        <v>2.00742837625486</v>
+        <v>2.007428611451569</v>
       </c>
       <c r="E814" t="n">
-        <v>2.099091682618869</v>
+        <v>2.099091928555144</v>
       </c>
       <c r="F814" t="n">
         <v>2996200</v>
@@ -16732,16 +16732,16 @@
         <v>44973</v>
       </c>
       <c r="B816" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C816" t="n">
-        <v>2.144923551085412</v>
+        <v>2.144923303130099</v>
       </c>
       <c r="D816" t="n">
-        <v>2.044093903964798</v>
+        <v>2.044093667665493</v>
       </c>
       <c r="E816" t="n">
-        <v>2.099091893303315</v>
+        <v>2.099091650646187</v>
       </c>
       <c r="F816" t="n">
         <v>2969500</v>
@@ -16752,16 +16752,16 @@
         <v>44974</v>
       </c>
       <c r="B817" t="n">
-        <v>1.961597084999084</v>
+        <v>1.961596965789795</v>
       </c>
       <c r="C817" t="n">
-        <v>2.099092069913735</v>
+        <v>2.099091942348662</v>
       </c>
       <c r="D817" t="n">
-        <v>1.961597084999084</v>
+        <v>1.961596965789795</v>
       </c>
       <c r="E817" t="n">
-        <v>2.053260408275518</v>
+        <v>2.053260283495706</v>
       </c>
       <c r="F817" t="n">
         <v>5027900</v>
@@ -16832,16 +16832,16 @@
         <v>44984</v>
       </c>
       <c r="B821" t="n">
-        <v>1.860766887664795</v>
+        <v>1.860767006874084</v>
       </c>
       <c r="C821" t="n">
-        <v>1.897432210607146</v>
+        <v>1.897432332165384</v>
       </c>
       <c r="D821" t="n">
-        <v>1.814935233986857</v>
+        <v>1.81493535025996</v>
       </c>
       <c r="E821" t="n">
-        <v>1.824101564722445</v>
+        <v>1.824101681582785</v>
       </c>
       <c r="F821" t="n">
         <v>2628700</v>
@@ -16892,16 +16892,16 @@
         <v>44987</v>
       </c>
       <c r="B824" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C824" t="n">
-        <v>2.144923466066379</v>
+        <v>2.144923594024966</v>
       </c>
       <c r="D824" t="n">
-        <v>1.970763173397657</v>
+        <v>1.970763290966453</v>
       </c>
       <c r="E824" t="n">
-        <v>2.126590803680198</v>
+        <v>2.126590930545122</v>
       </c>
       <c r="F824" t="n">
         <v>10060700</v>
@@ -16912,16 +16912,16 @@
         <v>44988</v>
       </c>
       <c r="B825" t="n">
-        <v>2.493244647979736</v>
+        <v>2.493244409561157</v>
       </c>
       <c r="C825" t="n">
-        <v>2.566575302215361</v>
+        <v>2.566575056784478</v>
       </c>
       <c r="D825" t="n">
-        <v>1.998262294804088</v>
+        <v>1.998262103718605</v>
       </c>
       <c r="E825" t="n">
-        <v>2.025761290142448</v>
+        <v>2.025761096427351</v>
       </c>
       <c r="F825" t="n">
         <v>20771000</v>
@@ -16972,16 +16972,16 @@
         <v>44993</v>
       </c>
       <c r="B828" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C828" t="n">
-        <v>2.90573005973376</v>
+        <v>2.905729816715452</v>
       </c>
       <c r="D828" t="n">
-        <v>2.694904207028261</v>
+        <v>2.694903981642197</v>
       </c>
       <c r="E828" t="n">
-        <v>2.704070538948388</v>
+        <v>2.704070312795705</v>
       </c>
       <c r="F828" t="n">
         <v>7104000</v>
@@ -17132,16 +17132,16 @@
         <v>45005</v>
       </c>
       <c r="B836" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C836" t="n">
-        <v>2.621573197467279</v>
+        <v>2.621573447239113</v>
       </c>
       <c r="D836" t="n">
-        <v>2.484078225780274</v>
+        <v>2.484078462452199</v>
       </c>
       <c r="E836" t="n">
-        <v>2.584907871684078</v>
+        <v>2.584908117962603</v>
       </c>
       <c r="F836" t="n">
         <v>2571800</v>
@@ -17152,16 +17152,16 @@
         <v>45006</v>
       </c>
       <c r="B837" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C837" t="n">
-        <v>2.539076214455076</v>
+        <v>2.539076456366965</v>
       </c>
       <c r="D837" t="n">
-        <v>2.474911894334474</v>
+        <v>2.474912130133071</v>
       </c>
       <c r="E837" t="n">
-        <v>2.520743551563476</v>
+        <v>2.52074379172871</v>
       </c>
       <c r="F837" t="n">
         <v>2400000</v>
@@ -17172,16 +17172,16 @@
         <v>45007</v>
       </c>
       <c r="B838" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C838" t="n">
-        <v>2.621573137405957</v>
+        <v>2.621572885790791</v>
       </c>
       <c r="D838" t="n">
-        <v>2.419913850218447</v>
+        <v>2.419913617958275</v>
       </c>
       <c r="E838" t="n">
-        <v>2.493244500104815</v>
+        <v>2.493244260806463</v>
       </c>
       <c r="F838" t="n">
         <v>4450900</v>
@@ -17192,16 +17192,16 @@
         <v>45008</v>
       </c>
       <c r="B839" t="n">
-        <v>2.383248090744019</v>
+        <v>2.383248329162598</v>
       </c>
       <c r="C839" t="n">
-        <v>2.493244274147426</v>
+        <v>2.493244523569952</v>
       </c>
       <c r="D839" t="n">
-        <v>2.300751117098379</v>
+        <v>2.300751347264015</v>
       </c>
       <c r="E839" t="n">
-        <v>2.484077943742355</v>
+        <v>2.484078192247887</v>
       </c>
       <c r="F839" t="n">
         <v>5291300</v>
@@ -17212,16 +17212,16 @@
         <v>45009</v>
       </c>
       <c r="B840" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C840" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="D840" t="n">
-        <v>2.209087841855346</v>
+        <v>2.209088065430759</v>
       </c>
       <c r="E840" t="n">
-        <v>2.383248121822838</v>
+        <v>2.38324836302451</v>
       </c>
       <c r="F840" t="n">
         <v>8035300</v>
@@ -17232,16 +17232,16 @@
         <v>45012</v>
       </c>
       <c r="B841" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C841" t="n">
-        <v>2.557408877346677</v>
+        <v>2.55740912100522</v>
       </c>
       <c r="D841" t="n">
-        <v>2.36491569844229</v>
+        <v>2.364915923760939</v>
       </c>
       <c r="E841" t="n">
-        <v>2.36491569844229</v>
+        <v>2.364915923760939</v>
       </c>
       <c r="F841" t="n">
         <v>3948600</v>
@@ -17272,16 +17272,16 @@
         <v>45014</v>
       </c>
       <c r="B843" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C843" t="n">
-        <v>2.676571393489365</v>
+        <v>2.676571145737662</v>
       </c>
       <c r="D843" t="n">
-        <v>2.511577209612499</v>
+        <v>2.511576977133168</v>
       </c>
       <c r="E843" t="n">
-        <v>2.658238730674444</v>
+        <v>2.658238484619669</v>
       </c>
       <c r="F843" t="n">
         <v>3021100</v>
@@ -17472,16 +17472,16 @@
         <v>45029</v>
       </c>
       <c r="B853" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C853" t="n">
-        <v>2.960728051254518</v>
+        <v>2.960727803636499</v>
       </c>
       <c r="D853" t="n">
-        <v>2.740735866628893</v>
+        <v>2.740735637409736</v>
       </c>
       <c r="E853" t="n">
-        <v>2.804900190069778</v>
+        <v>2.804899955484291</v>
       </c>
       <c r="F853" t="n">
         <v>4826100</v>
@@ -17512,16 +17512,16 @@
         <v>45033</v>
       </c>
       <c r="B855" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="C855" t="n">
-        <v>2.841565475118138</v>
+        <v>2.841565229570771</v>
       </c>
       <c r="D855" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="E855" t="n">
-        <v>2.777401152639914</v>
+        <v>2.77740091263716</v>
       </c>
       <c r="F855" t="n">
         <v>2017100</v>
@@ -17532,16 +17532,16 @@
         <v>45034</v>
       </c>
       <c r="B856" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C856" t="n">
-        <v>2.823232513937895</v>
+        <v>2.823232766284694</v>
       </c>
       <c r="D856" t="n">
-        <v>2.612406686619929</v>
+        <v>2.612406920122646</v>
       </c>
       <c r="E856" t="n">
-        <v>2.804899852305252</v>
+        <v>2.804900103013436</v>
       </c>
       <c r="F856" t="n">
         <v>3770500</v>
@@ -17572,16 +17572,16 @@
         <v>45036</v>
       </c>
       <c r="B858" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C858" t="n">
-        <v>2.603240801706716</v>
+        <v>2.603240558142417</v>
       </c>
       <c r="D858" t="n">
-        <v>2.419914153978682</v>
+        <v>2.419913927566782</v>
       </c>
       <c r="E858" t="n">
-        <v>2.484078480683494</v>
+        <v>2.484078248268254</v>
       </c>
       <c r="F858" t="n">
         <v>4312900</v>
@@ -17672,16 +17672,16 @@
         <v>45044</v>
       </c>
       <c r="B863" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C863" t="n">
-        <v>2.62157346647952</v>
+        <v>2.62157322119998</v>
       </c>
       <c r="D863" t="n">
-        <v>2.438246818751485</v>
+        <v>2.438246590624346</v>
       </c>
       <c r="E863" t="n">
-        <v>2.46574581591069</v>
+        <v>2.465745585210691</v>
       </c>
       <c r="F863" t="n">
         <v>4247000</v>
@@ -17692,16 +17692,16 @@
         <v>45048</v>
       </c>
       <c r="B864" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C864" t="n">
-        <v>2.749902171081845</v>
+        <v>2.749901926967264</v>
       </c>
       <c r="D864" t="n">
-        <v>2.419914006710763</v>
+        <v>2.419913791889924</v>
       </c>
       <c r="E864" t="n">
-        <v>2.548242652310732</v>
+        <v>2.54824242609789</v>
       </c>
       <c r="F864" t="n">
         <v>8626200</v>
@@ -17732,16 +17732,16 @@
         <v>45050</v>
       </c>
       <c r="B866" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C866" t="n">
-        <v>2.869064767891131</v>
+        <v>2.869064525602105</v>
       </c>
       <c r="D866" t="n">
-        <v>2.704070572725299</v>
+        <v>2.704070344369832</v>
       </c>
       <c r="E866" t="n">
-        <v>2.722403236794548</v>
+        <v>2.72240300689091</v>
       </c>
       <c r="F866" t="n">
         <v>5400200</v>
@@ -17772,16 +17772,16 @@
         <v>45054</v>
       </c>
       <c r="B868" t="n">
-        <v>3.125722169876099</v>
+        <v>3.12572193145752</v>
       </c>
       <c r="C868" t="n">
-        <v>3.199052823489703</v>
+        <v>3.199052579477732</v>
       </c>
       <c r="D868" t="n">
-        <v>3.015725970913106</v>
+        <v>3.015725740884632</v>
       </c>
       <c r="E868" t="n">
-        <v>3.024892302614806</v>
+        <v>3.024892071887158</v>
       </c>
       <c r="F868" t="n">
         <v>6228600</v>
@@ -17892,16 +17892,16 @@
         <v>45062</v>
       </c>
       <c r="B874" t="n">
-        <v>3.602371692657471</v>
+        <v>3.60237193107605</v>
       </c>
       <c r="C874" t="n">
-        <v>3.675702561499818</v>
+        <v>3.675702804771711</v>
       </c>
       <c r="D874" t="n">
-        <v>3.529040823815123</v>
+        <v>3.529041057380388</v>
       </c>
       <c r="E874" t="n">
-        <v>3.657369680382299</v>
+        <v>3.657369922440853</v>
       </c>
       <c r="F874" t="n">
         <v>5715400</v>
@@ -17912,16 +17912,16 @@
         <v>45063</v>
       </c>
       <c r="B875" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="C875" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="D875" t="n">
-        <v>3.62987109842838</v>
+        <v>3.629870877835498</v>
       </c>
       <c r="E875" t="n">
-        <v>3.648203763083666</v>
+        <v>3.64820354137668</v>
       </c>
       <c r="F875" t="n">
         <v>6160500</v>
@@ -17972,16 +17972,16 @@
         <v>45068</v>
       </c>
       <c r="B878" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="C878" t="n">
-        <v>3.996524828619315</v>
+        <v>3.996524585744319</v>
       </c>
       <c r="D878" t="n">
-        <v>3.859029625162064</v>
+        <v>3.859029390642864</v>
       </c>
       <c r="E878" t="n">
-        <v>3.904861505342882</v>
+        <v>3.904861268038407</v>
       </c>
       <c r="F878" t="n">
         <v>3483600</v>
@@ -17992,16 +17992,16 @@
         <v>45069</v>
       </c>
       <c r="B879" t="n">
-        <v>3.941526174545288</v>
+        <v>3.941526412963867</v>
       </c>
       <c r="C879" t="n">
-        <v>4.134019339730554</v>
+        <v>4.134019589792833</v>
       </c>
       <c r="D879" t="n">
-        <v>3.877361640455157</v>
+        <v>3.877361874992493</v>
       </c>
       <c r="E879" t="n">
-        <v>3.886527752705101</v>
+        <v>3.886527987796886</v>
       </c>
       <c r="F879" t="n">
         <v>4348000</v>
@@ -18092,16 +18092,16 @@
         <v>45076</v>
       </c>
       <c r="B884" t="n">
-        <v>3.996524333953857</v>
+        <v>3.996524572372437</v>
       </c>
       <c r="C884" t="n">
-        <v>4.244015494709879</v>
+        <v>4.24401574789291</v>
       </c>
       <c r="D884" t="n">
-        <v>3.969025121832011</v>
+        <v>3.969025358610084</v>
       </c>
       <c r="E884" t="n">
-        <v>4.225682832323698</v>
+        <v>4.225683084413067</v>
       </c>
       <c r="F884" t="n">
         <v>3937000</v>
@@ -18172,16 +18172,16 @@
         <v>45082</v>
       </c>
       <c r="B888" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C888" t="n">
-        <v>4.72066517241793</v>
+        <v>4.72066469090588</v>
       </c>
       <c r="D888" t="n">
-        <v>4.399843360854316</v>
+        <v>4.399842912066377</v>
       </c>
       <c r="E888" t="n">
-        <v>4.64733452258455</v>
+        <v>4.647334048552291</v>
       </c>
       <c r="F888" t="n">
         <v>6247400</v>
@@ -18232,16 +18232,16 @@
         <v>45086</v>
       </c>
       <c r="B891" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="C891" t="n">
-        <v>4.500672836977939</v>
+        <v>4.500673329876966</v>
       </c>
       <c r="D891" t="n">
-        <v>4.289846997768588</v>
+        <v>4.289847467578654</v>
       </c>
       <c r="E891" t="n">
-        <v>4.454841398853827</v>
+        <v>4.454841886733544</v>
       </c>
       <c r="F891" t="n">
         <v>5651200</v>
@@ -18252,16 +18252,16 @@
         <v>45089</v>
       </c>
       <c r="B892" t="n">
-        <v>4.491506099700928</v>
+        <v>4.491506576538086</v>
       </c>
       <c r="C892" t="n">
-        <v>4.647333929244392</v>
+        <v>4.647334422624888</v>
       </c>
       <c r="D892" t="n">
-        <v>4.271513741202773</v>
+        <v>4.271514194684618</v>
       </c>
       <c r="E892" t="n">
-        <v>4.363177478876643</v>
+        <v>4.363177942089895</v>
       </c>
       <c r="F892" t="n">
         <v>6649300</v>
@@ -18272,16 +18272,16 @@
         <v>45090</v>
       </c>
       <c r="B893" t="n">
-        <v>4.289846897125244</v>
+        <v>4.289847373962402</v>
       </c>
       <c r="C893" t="n">
-        <v>4.592336479656477</v>
+        <v>4.592336990116809</v>
       </c>
       <c r="D893" t="n">
-        <v>4.234848910415514</v>
+        <v>4.234849381139381</v>
       </c>
       <c r="E893" t="n">
-        <v>4.537338055861602</v>
+        <v>4.537338560208595</v>
       </c>
       <c r="F893" t="n">
         <v>4358900</v>
@@ -18392,16 +18392,16 @@
         <v>45098</v>
       </c>
       <c r="B899" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C899" t="n">
-        <v>4.986488897178933</v>
+        <v>4.986489382037665</v>
       </c>
       <c r="D899" t="n">
-        <v>4.748163852887355</v>
+        <v>4.748164314572671</v>
       </c>
       <c r="E899" t="n">
-        <v>4.821494938343708</v>
+        <v>4.821495407159335</v>
       </c>
       <c r="F899" t="n">
         <v>4163100</v>
@@ -18412,16 +18412,16 @@
         <v>45099</v>
       </c>
       <c r="B900" t="n">
-        <v>4.766496181488037</v>
+        <v>4.766496658325195</v>
       </c>
       <c r="C900" t="n">
-        <v>4.858159922623858</v>
+        <v>4.858160408630997</v>
       </c>
       <c r="D900" t="n">
-        <v>4.592336122334244</v>
+        <v>4.592336581748543</v>
       </c>
       <c r="E900" t="n">
-        <v>4.757330069625522</v>
+        <v>4.757330545545708</v>
       </c>
       <c r="F900" t="n">
         <v>4737400</v>
@@ -18572,16 +18572,16 @@
         <v>45111</v>
       </c>
       <c r="B908" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C908" t="n">
-        <v>5.087318782005757</v>
+        <v>5.087319262304525</v>
       </c>
       <c r="D908" t="n">
-        <v>4.87649294836929</v>
+        <v>4.876493408763784</v>
       </c>
       <c r="E908" t="n">
-        <v>4.940657047463991</v>
+        <v>4.94065751391628</v>
       </c>
       <c r="F908" t="n">
         <v>2828200</v>
@@ -18612,16 +18612,16 @@
         <v>45113</v>
       </c>
       <c r="B910" t="n">
-        <v>5.087319374084473</v>
+        <v>5.087318897247314</v>
       </c>
       <c r="C910" t="n">
-        <v>5.22481413790957</v>
+        <v>5.224813648184956</v>
       </c>
       <c r="D910" t="n">
-        <v>5.041487494752643</v>
+        <v>5.041487022211331</v>
       </c>
       <c r="E910" t="n">
-        <v>5.206481473593878</v>
+        <v>5.206480985587593</v>
       </c>
       <c r="F910" t="n">
         <v>3192100</v>
@@ -18672,16 +18672,16 @@
         <v>45118</v>
       </c>
       <c r="B913" t="n">
-        <v>5.096485614776611</v>
+        <v>5.096485137939453</v>
       </c>
       <c r="C913" t="n">
-        <v>5.114818279549415</v>
+        <v>5.114817800997017</v>
       </c>
       <c r="D913" t="n">
-        <v>4.858160972730167</v>
+        <v>4.858160518191128</v>
       </c>
       <c r="E913" t="n">
-        <v>5.105652165705616</v>
+        <v>5.105651688010817</v>
       </c>
       <c r="F913" t="n">
         <v>3857700</v>
@@ -18692,16 +18692,16 @@
         <v>45119</v>
       </c>
       <c r="B914" t="n">
-        <v>5.325643062591553</v>
+        <v>5.325643539428711</v>
       </c>
       <c r="C914" t="n">
-        <v>5.573134205359659</v>
+        <v>5.573134704356201</v>
       </c>
       <c r="D914" t="n">
-        <v>5.178981774161598</v>
+        <v>5.178982237867281</v>
       </c>
       <c r="E914" t="n">
-        <v>5.178981774161598</v>
+        <v>5.178982237867281</v>
       </c>
       <c r="F914" t="n">
         <v>7685700</v>
@@ -18712,16 +18712,16 @@
         <v>45120</v>
       </c>
       <c r="B915" t="n">
-        <v>5.096485614776611</v>
+        <v>5.096485137939453</v>
       </c>
       <c r="C915" t="n">
-        <v>5.453972796388881</v>
+        <v>5.453972286104523</v>
       </c>
       <c r="D915" t="n">
-        <v>4.99565573998359</v>
+        <v>4.995655272580271</v>
       </c>
       <c r="E915" t="n">
-        <v>5.334810693908262</v>
+        <v>5.334810194772943</v>
       </c>
       <c r="F915" t="n">
         <v>4692200</v>
@@ -18732,16 +18732,16 @@
         <v>45121</v>
       </c>
       <c r="B916" t="n">
-        <v>4.482340335845947</v>
+        <v>4.482339859008789</v>
       </c>
       <c r="C916" t="n">
-        <v>4.903992029460144</v>
+        <v>4.903991507767135</v>
       </c>
       <c r="D916" t="n">
-        <v>4.381510906088113</v>
+        <v>4.381510439977321</v>
       </c>
       <c r="E916" t="n">
-        <v>4.858160589684357</v>
+        <v>4.858160072866955</v>
       </c>
       <c r="F916" t="n">
         <v>15771400</v>
@@ -18772,16 +18772,16 @@
         <v>45125</v>
       </c>
       <c r="B918" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C918" t="n">
-        <v>5.041486987624404</v>
+        <v>5.041486503749065</v>
       </c>
       <c r="D918" t="n">
-        <v>4.711498626050601</v>
+        <v>4.711498173847115</v>
       </c>
       <c r="E918" t="n">
-        <v>4.720665175828972</v>
+        <v>4.720664722745693</v>
       </c>
       <c r="F918" t="n">
         <v>5384000</v>
@@ -18812,16 +18812,16 @@
         <v>45127</v>
       </c>
       <c r="B920" t="n">
-        <v>4.876492977142334</v>
+        <v>4.876493453979492</v>
       </c>
       <c r="C920" t="n">
-        <v>5.004821613174064</v>
+        <v>5.004822102559555</v>
       </c>
       <c r="D920" t="n">
-        <v>4.784829228605952</v>
+        <v>4.784829696479972</v>
       </c>
       <c r="E920" t="n">
-        <v>4.958989738905873</v>
+        <v>4.958990223809796</v>
       </c>
       <c r="F920" t="n">
         <v>2200400</v>
@@ -18832,16 +18832,16 @@
         <v>45128</v>
       </c>
       <c r="B921" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C921" t="n">
-        <v>5.169815688182035</v>
+        <v>5.169815198316529</v>
       </c>
       <c r="D921" t="n">
-        <v>4.858160422351643</v>
+        <v>4.85815996201701</v>
       </c>
       <c r="E921" t="n">
-        <v>4.858160422351643</v>
+        <v>4.85815996201701</v>
       </c>
       <c r="F921" t="n">
         <v>3946200</v>
@@ -18852,16 +18852,16 @@
         <v>45131</v>
       </c>
       <c r="B922" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C922" t="n">
-        <v>5.105651587288944</v>
+        <v>5.105651103503303</v>
       </c>
       <c r="D922" t="n">
-        <v>4.885659197852923</v>
+        <v>4.885658734912646</v>
       </c>
       <c r="E922" t="n">
-        <v>5.068986261897133</v>
+        <v>5.068985781585712</v>
       </c>
       <c r="F922" t="n">
         <v>2320000</v>
@@ -18872,16 +18872,16 @@
         <v>45132</v>
       </c>
       <c r="B923" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C923" t="n">
-        <v>5.270645551552092</v>
+        <v>5.270645052132461</v>
       </c>
       <c r="D923" t="n">
-        <v>4.995655174028355</v>
+        <v>4.995654700665417</v>
       </c>
       <c r="E923" t="n">
-        <v>5.096485037398413</v>
+        <v>5.096484554481348</v>
       </c>
       <c r="F923" t="n">
         <v>3865600</v>
@@ -18952,16 +18952,16 @@
         <v>45138</v>
       </c>
       <c r="B927" t="n">
-        <v>5.224813938140869</v>
+        <v>5.224813461303711</v>
       </c>
       <c r="C927" t="n">
-        <v>5.389808347758803</v>
+        <v>5.389807855863602</v>
       </c>
       <c r="D927" t="n">
-        <v>5.087319179572829</v>
+        <v>5.087318715283986</v>
       </c>
       <c r="E927" t="n">
-        <v>5.087319179572829</v>
+        <v>5.087318715283986</v>
       </c>
       <c r="F927" t="n">
         <v>3571100</v>
@@ -18972,16 +18972,16 @@
         <v>45139</v>
       </c>
       <c r="B928" t="n">
-        <v>5.417306900024414</v>
+        <v>5.417306423187256</v>
       </c>
       <c r="C928" t="n">
-        <v>5.426473449994312</v>
+        <v>5.426472972350305</v>
       </c>
       <c r="D928" t="n">
-        <v>4.995655217282615</v>
+        <v>4.99565477755969</v>
       </c>
       <c r="E928" t="n">
-        <v>5.17898228291414</v>
+        <v>5.17898182705457</v>
       </c>
       <c r="F928" t="n">
         <v>5677300</v>
@@ -18992,16 +18992,16 @@
         <v>45140</v>
       </c>
       <c r="B929" t="n">
-        <v>5.33480978012085</v>
+        <v>5.334810256958008</v>
       </c>
       <c r="C929" t="n">
-        <v>5.518136396447286</v>
+        <v>5.518136889670584</v>
       </c>
       <c r="D929" t="n">
-        <v>5.215647260966101</v>
+        <v>5.215647727152248</v>
       </c>
       <c r="E929" t="n">
-        <v>5.472304523823111</v>
+        <v>5.472305012949855</v>
       </c>
       <c r="F929" t="n">
         <v>6874400</v>
@@ -19032,16 +19032,16 @@
         <v>45142</v>
       </c>
       <c r="B931" t="n">
-        <v>5.628132343292236</v>
+        <v>5.628132820129395</v>
       </c>
       <c r="C931" t="n">
-        <v>5.655631554171628</v>
+        <v>5.655632033338626</v>
       </c>
       <c r="D931" t="n">
-        <v>5.316477096808192</v>
+        <v>5.31647754724071</v>
       </c>
       <c r="E931" t="n">
-        <v>5.32564320904457</v>
+        <v>5.325643660253677</v>
       </c>
       <c r="F931" t="n">
         <v>4666200</v>
@@ -19092,16 +19092,16 @@
         <v>45147</v>
       </c>
       <c r="B934" t="n">
-        <v>5.224813938140869</v>
+        <v>5.224813461303711</v>
       </c>
       <c r="C934" t="n">
-        <v>5.45397245186784</v>
+        <v>5.453971954116771</v>
       </c>
       <c r="D934" t="n">
-        <v>5.197315161261333</v>
+        <v>5.197314686933821</v>
       </c>
       <c r="E934" t="n">
-        <v>5.261479265370371</v>
+        <v>5.26147878518699</v>
       </c>
       <c r="F934" t="n">
         <v>3345000</v>
@@ -19152,16 +19152,16 @@
         <v>45152</v>
       </c>
       <c r="B937" t="n">
-        <v>6.068117141723633</v>
+        <v>6.068116664886475</v>
       </c>
       <c r="C937" t="n">
-        <v>6.28810953504867</v>
+        <v>6.288109040924345</v>
       </c>
       <c r="D937" t="n">
-        <v>5.985620376676263</v>
+        <v>5.985619906321761</v>
       </c>
       <c r="E937" t="n">
-        <v>6.14144779380359</v>
+        <v>6.141447311204055</v>
       </c>
       <c r="F937" t="n">
         <v>5683800</v>
@@ -19232,16 +19232,16 @@
         <v>45156</v>
       </c>
       <c r="B941" t="n">
-        <v>5.710629940032959</v>
+        <v>5.710629463195801</v>
       </c>
       <c r="C941" t="n">
-        <v>5.838958579953599</v>
+        <v>5.838958092401009</v>
       </c>
       <c r="D941" t="n">
-        <v>5.334810133151363</v>
+        <v>5.33480968769513</v>
       </c>
       <c r="E941" t="n">
-        <v>5.609800075838448</v>
+        <v>5.609799607420576</v>
       </c>
       <c r="F941" t="n">
         <v>5405200</v>
@@ -19252,16 +19252,16 @@
         <v>45159</v>
       </c>
       <c r="B942" t="n">
-        <v>5.490636825561523</v>
+        <v>5.490637302398682</v>
       </c>
       <c r="C942" t="n">
-        <v>5.701462639060511</v>
+        <v>5.701463134206945</v>
       </c>
       <c r="D942" t="n">
-        <v>5.463138053457582</v>
+        <v>5.463138527906596</v>
       </c>
       <c r="E942" t="n">
-        <v>5.67396386695657</v>
+        <v>5.673964359714859</v>
       </c>
       <c r="F942" t="n">
         <v>3510600</v>
@@ -19272,16 +19272,16 @@
         <v>45160</v>
       </c>
       <c r="B943" t="n">
-        <v>5.628132343292236</v>
+        <v>5.628132820129395</v>
       </c>
       <c r="C943" t="n">
-        <v>5.646465004850121</v>
+        <v>5.646465483240493</v>
       </c>
       <c r="D943" t="n">
-        <v>5.408140404597616</v>
+        <v>5.408140862796206</v>
       </c>
       <c r="E943" t="n">
-        <v>5.563968246382204</v>
+        <v>5.563968717783131</v>
       </c>
       <c r="F943" t="n">
         <v>4158800</v>
@@ -19412,16 +19412,16 @@
         <v>45169</v>
       </c>
       <c r="B950" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C950" t="n">
-        <v>5.03232033386837</v>
+        <v>5.032320823183499</v>
       </c>
       <c r="D950" t="n">
-        <v>4.858160262529314</v>
+        <v>4.858160734910076</v>
       </c>
       <c r="E950" t="n">
-        <v>5.03232033386837</v>
+        <v>5.032320823183499</v>
       </c>
       <c r="F950" t="n">
         <v>3681000</v>
@@ -19432,16 +19432,16 @@
         <v>45170</v>
       </c>
       <c r="B951" t="n">
-        <v>5.151483058929443</v>
+        <v>5.151482582092285</v>
       </c>
       <c r="C951" t="n">
-        <v>5.169815721744364</v>
+        <v>5.169815243210278</v>
       </c>
       <c r="D951" t="n">
-        <v>4.876493116705634</v>
+        <v>4.876492665322393</v>
       </c>
       <c r="E951" t="n">
-        <v>4.949823767965317</v>
+        <v>4.949823309794364</v>
       </c>
       <c r="F951" t="n">
         <v>4962000</v>
@@ -19472,16 +19472,16 @@
         <v>45174</v>
       </c>
       <c r="B953" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C953" t="n">
-        <v>5.032320437846034</v>
+        <v>5.032319954850488</v>
       </c>
       <c r="D953" t="n">
-        <v>4.858160362908486</v>
+        <v>4.858159896628598</v>
       </c>
       <c r="E953" t="n">
-        <v>4.99565511290285</v>
+        <v>4.995654633426395</v>
       </c>
       <c r="F953" t="n">
         <v>3096400</v>
@@ -19492,16 +19492,16 @@
         <v>45175</v>
       </c>
       <c r="B954" t="n">
-        <v>4.986489295959473</v>
+        <v>4.986488819122314</v>
       </c>
       <c r="C954" t="n">
-        <v>5.105651827634952</v>
+        <v>5.105651339402779</v>
       </c>
       <c r="D954" t="n">
-        <v>4.94982396884166</v>
+        <v>4.949823495510654</v>
       </c>
       <c r="E954" t="n">
-        <v>4.94982396884166</v>
+        <v>4.949823495510654</v>
       </c>
       <c r="F954" t="n">
         <v>4361600</v>
@@ -19512,16 +19512,16 @@
         <v>45177</v>
       </c>
       <c r="B955" t="n">
-        <v>4.876492977142334</v>
+        <v>4.876493453979492</v>
       </c>
       <c r="C955" t="n">
-        <v>5.004821613174064</v>
+        <v>5.004822102559555</v>
       </c>
       <c r="D955" t="n">
-        <v>4.867326427454637</v>
+        <v>4.867326903395464</v>
       </c>
       <c r="E955" t="n">
-        <v>4.97732240119612</v>
+        <v>4.977322887892662</v>
       </c>
       <c r="F955" t="n">
         <v>2168000</v>
@@ -19552,16 +19552,16 @@
         <v>45181</v>
       </c>
       <c r="B957" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C957" t="n">
-        <v>5.105651444187835</v>
+        <v>5.105651926217408</v>
       </c>
       <c r="D957" t="n">
-        <v>4.913158272733446</v>
+        <v>4.913158736589549</v>
       </c>
       <c r="E957" t="n">
-        <v>4.913158272733446</v>
+        <v>4.913158736589549</v>
       </c>
       <c r="F957" t="n">
         <v>2356100</v>
@@ -19672,16 +19672,16 @@
         <v>45189</v>
       </c>
       <c r="B963" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C963" t="n">
-        <v>5.114817637510772</v>
+        <v>5.114817146597253</v>
       </c>
       <c r="D963" t="n">
-        <v>4.711498626050601</v>
+        <v>4.711498173847115</v>
       </c>
       <c r="E963" t="n">
-        <v>4.720665175828972</v>
+        <v>4.720664722745693</v>
       </c>
       <c r="F963" t="n">
         <v>5388800</v>
@@ -19712,16 +19712,16 @@
         <v>45191</v>
       </c>
       <c r="B965" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C965" t="n">
-        <v>4.86732647208469</v>
+        <v>4.867325975613057</v>
       </c>
       <c r="D965" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="E965" t="n">
-        <v>4.812328484709655</v>
+        <v>4.812327993847866</v>
       </c>
       <c r="F965" t="n">
         <v>2426200</v>
@@ -19752,16 +19752,16 @@
         <v>45195</v>
       </c>
       <c r="B967" t="n">
-        <v>4.491506099700928</v>
+        <v>4.491506576538086</v>
       </c>
       <c r="C967" t="n">
-        <v>4.784828661585008</v>
+        <v>4.784829169562522</v>
       </c>
       <c r="D967" t="n">
-        <v>4.418175459229907</v>
+        <v>4.418175928281977</v>
       </c>
       <c r="E967" t="n">
-        <v>4.574002851688278</v>
+        <v>4.574003337283638</v>
       </c>
       <c r="F967" t="n">
         <v>4192900</v>
@@ -19852,16 +19852,16 @@
         <v>45202</v>
       </c>
       <c r="B972" t="n">
-        <v>4.317346096038818</v>
+        <v>4.31734561920166</v>
       </c>
       <c r="C972" t="n">
-        <v>4.674833227119539</v>
+        <v>4.674832710799063</v>
       </c>
       <c r="D972" t="n">
-        <v>4.308179546405524</v>
+        <v>4.308179070580783</v>
       </c>
       <c r="E972" t="n">
-        <v>4.619835240575209</v>
+        <v>4.619834730329086</v>
       </c>
       <c r="F972" t="n">
         <v>3808300</v>
@@ -19892,16 +19892,16 @@
         <v>45204</v>
       </c>
       <c r="B974" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="C974" t="n">
-        <v>4.79399597660141</v>
+        <v>4.793995472791623</v>
       </c>
       <c r="D974" t="n">
-        <v>4.528172143854223</v>
+        <v>4.528171667980348</v>
       </c>
       <c r="E974" t="n">
-        <v>4.67483344824297</v>
+        <v>4.674832956956192</v>
       </c>
       <c r="F974" t="n">
         <v>3401000</v>
@@ -20032,16 +20032,16 @@
         <v>45216</v>
       </c>
       <c r="B981" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C981" t="n">
-        <v>4.812328484709655</v>
+        <v>4.812327993847866</v>
       </c>
       <c r="D981" t="n">
-        <v>4.601502647896112</v>
+        <v>4.601502178538746</v>
       </c>
       <c r="E981" t="n">
-        <v>4.656500635271147</v>
+        <v>4.656500160303938</v>
       </c>
       <c r="F981" t="n">
         <v>2762000</v>
@@ -20052,16 +20052,16 @@
         <v>45217</v>
       </c>
       <c r="B982" t="n">
-        <v>4.509839534759521</v>
+        <v>4.509839057922363</v>
       </c>
       <c r="C982" t="n">
-        <v>4.674833504170784</v>
+        <v>4.67483300988838</v>
       </c>
       <c r="D982" t="n">
-        <v>4.418176218419932</v>
+        <v>4.418175751274577</v>
       </c>
       <c r="E982" t="n">
-        <v>4.647334727811492</v>
+        <v>4.647334236436606</v>
       </c>
       <c r="F982" t="n">
         <v>3515800</v>
@@ -20132,16 +20132,16 @@
         <v>45223</v>
       </c>
       <c r="B986" t="n">
-        <v>4.711498260498047</v>
+        <v>4.711498737335205</v>
       </c>
       <c r="C986" t="n">
-        <v>4.793995453762048</v>
+        <v>4.79399593894851</v>
       </c>
       <c r="D986" t="n">
-        <v>4.619834955251998</v>
+        <v>4.619835422812178</v>
       </c>
       <c r="E986" t="n">
-        <v>4.683999487466791</v>
+        <v>4.683999961520877</v>
       </c>
       <c r="F986" t="n">
         <v>2628000</v>
@@ -20172,16 +20172,16 @@
         <v>45225</v>
       </c>
       <c r="B988" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C988" t="n">
-        <v>4.858160878073153</v>
+        <v>4.858160394853837</v>
       </c>
       <c r="D988" t="n">
-        <v>4.60150313916945</v>
+        <v>4.601502681478721</v>
       </c>
       <c r="E988" t="n">
-        <v>4.60150313916945</v>
+        <v>4.601502681478721</v>
       </c>
       <c r="F988" t="n">
         <v>4908400</v>
@@ -20192,16 +20192,16 @@
         <v>45226</v>
       </c>
       <c r="B989" t="n">
-        <v>4.766496181488037</v>
+        <v>4.766496658325195</v>
       </c>
       <c r="C989" t="n">
-        <v>4.977321999347226</v>
+        <v>4.977322497275261</v>
       </c>
       <c r="D989" t="n">
-        <v>4.720664748005237</v>
+        <v>4.720665220257449</v>
       </c>
       <c r="E989" t="n">
-        <v>4.803161503108321</v>
+        <v>4.803161983613454</v>
       </c>
       <c r="F989" t="n">
         <v>2912800</v>
@@ -20252,16 +20252,16 @@
         <v>45231</v>
       </c>
       <c r="B992" t="n">
-        <v>4.803162097930908</v>
+        <v>4.80316162109375</v>
       </c>
       <c r="C992" t="n">
-        <v>4.848993974174629</v>
+        <v>4.848993492787479</v>
       </c>
       <c r="D992" t="n">
-        <v>4.656500793287267</v>
+        <v>4.656500331010008</v>
       </c>
       <c r="E992" t="n">
-        <v>4.729831445609087</v>
+        <v>4.729830976051879</v>
       </c>
       <c r="F992" t="n">
         <v>2720700</v>
@@ -20332,16 +20332,16 @@
         <v>45238</v>
       </c>
       <c r="B996" t="n">
-        <v>5.518136978149414</v>
+        <v>5.518136501312256</v>
       </c>
       <c r="C996" t="n">
-        <v>5.573134968845035</v>
+        <v>5.573134487255351</v>
       </c>
       <c r="D996" t="n">
-        <v>5.316477678932137</v>
+        <v>5.316477219520905</v>
       </c>
       <c r="E996" t="n">
-        <v>5.316477678932137</v>
+        <v>5.316477219520905</v>
       </c>
       <c r="F996" t="n">
         <v>4022900</v>
@@ -20352,16 +20352,16 @@
         <v>45239</v>
       </c>
       <c r="B997" t="n">
-        <v>5.618966102600098</v>
+        <v>5.618966579437256</v>
       </c>
       <c r="C997" t="n">
-        <v>5.728962069432778</v>
+        <v>5.728962555604424</v>
       </c>
       <c r="D997" t="n">
-        <v>5.417306392988397</v>
+        <v>5.417306852712293</v>
       </c>
       <c r="E997" t="n">
-        <v>5.582300780322537</v>
+        <v>5.5823012540482</v>
       </c>
       <c r="F997" t="n">
         <v>3100500</v>
@@ -20392,16 +20392,16 @@
         <v>45243</v>
       </c>
       <c r="B999" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C999" t="n">
-        <v>7.140579120035365</v>
+        <v>7.140578620094379</v>
       </c>
       <c r="D999" t="n">
-        <v>6.544766908003258</v>
+        <v>6.544766449777509</v>
       </c>
       <c r="E999" t="n">
-        <v>6.608931448004774</v>
+        <v>6.608930985286603</v>
       </c>
       <c r="F999" t="n">
         <v>8835300</v>
@@ -20432,16 +20432,16 @@
         <v>45246</v>
       </c>
       <c r="B1001" t="n">
-        <v>7.360570907592773</v>
+        <v>7.360570430755615</v>
       </c>
       <c r="C1001" t="n">
-        <v>7.562230635986777</v>
+        <v>7.562230146085571</v>
       </c>
       <c r="D1001" t="n">
-        <v>6.627263956657273</v>
+        <v>6.627263527325669</v>
       </c>
       <c r="E1001" t="n">
-        <v>6.78309180939305</v>
+        <v>6.783091369966508</v>
       </c>
       <c r="F1001" t="n">
         <v>9976600</v>
@@ -20452,16 +20452,16 @@
         <v>45247</v>
       </c>
       <c r="B1002" t="n">
-        <v>7.635560989379883</v>
+        <v>7.635561466217041</v>
       </c>
       <c r="C1002" t="n">
-        <v>7.699725088295085</v>
+        <v>7.699725569139261</v>
       </c>
       <c r="D1002" t="n">
-        <v>7.333071845679237</v>
+        <v>7.333072303626092</v>
       </c>
       <c r="E1002" t="n">
-        <v>7.415569043810375</v>
+        <v>7.41556950690914</v>
       </c>
       <c r="F1002" t="n">
         <v>5823800</v>
@@ -20492,16 +20492,16 @@
         <v>45251</v>
       </c>
       <c r="B1004" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1004" t="n">
-        <v>7.543897678065316</v>
+        <v>7.543897193575265</v>
       </c>
       <c r="D1004" t="n">
-        <v>7.287240393386257</v>
+        <v>7.287239925379449</v>
       </c>
       <c r="E1004" t="n">
-        <v>7.543897678065316</v>
+        <v>7.543897193575265</v>
       </c>
       <c r="F1004" t="n">
         <v>4025000</v>
@@ -20532,16 +20532,16 @@
         <v>45253</v>
       </c>
       <c r="B1006" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="C1006" t="n">
-        <v>7.323906062493096</v>
+        <v>7.32390557025422</v>
       </c>
       <c r="D1006" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="E1006" t="n">
-        <v>7.314739949011068</v>
+        <v>7.314739457388246</v>
       </c>
       <c r="F1006" t="n">
         <v>2414400</v>
@@ -20612,16 +20612,16 @@
         <v>45259</v>
       </c>
       <c r="B1010" t="n">
-        <v>7.44306755065918</v>
+        <v>7.443068027496338</v>
       </c>
       <c r="C1010" t="n">
-        <v>7.763889782032437</v>
+        <v>7.763890279422943</v>
       </c>
       <c r="D1010" t="n">
-        <v>7.168077628591552</v>
+        <v>7.16807808781159</v>
       </c>
       <c r="E1010" t="n">
-        <v>7.213909063726926</v>
+        <v>7.213909525883136</v>
       </c>
       <c r="F1010" t="n">
         <v>6571400</v>
@@ -20752,16 +20752,16 @@
         <v>45268</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.718058586120605</v>
+        <v>7.718058109283447</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.800555788512423</v>
+        <v>7.800555306578421</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.580563831581132</v>
+        <v>7.580563363238674</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.699725485957833</v>
+        <v>7.69972501025333</v>
       </c>
       <c r="F1017" t="n">
         <v>1787800</v>
@@ -20772,16 +20772,16 @@
         <v>45271</v>
       </c>
       <c r="B1018" t="n">
-        <v>7.672226905822754</v>
+        <v>7.672226428985596</v>
       </c>
       <c r="C1018" t="n">
-        <v>7.892218868372355</v>
+        <v>7.892218377862459</v>
       </c>
       <c r="D1018" t="n">
-        <v>7.626395028415665</v>
+        <v>7.626394554427008</v>
       </c>
       <c r="E1018" t="n">
-        <v>7.699725682598865</v>
+        <v>7.699725204052629</v>
       </c>
       <c r="F1018" t="n">
         <v>2800600</v>
@@ -20872,16 +20872,16 @@
         <v>45278</v>
       </c>
       <c r="B1023" t="n">
-        <v>7.44306755065918</v>
+        <v>7.443068027496338</v>
       </c>
       <c r="C1023" t="n">
-        <v>7.681392586869585</v>
+        <v>7.681393078974941</v>
       </c>
       <c r="D1023" t="n">
-        <v>7.415568776994981</v>
+        <v>7.415569252070441</v>
       </c>
       <c r="E1023" t="n">
-        <v>7.516398196543881</v>
+        <v>7.516398678078938</v>
       </c>
       <c r="F1023" t="n">
         <v>2448800</v>
@@ -20932,16 +20932,16 @@
         <v>45281</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.498065948486328</v>
+        <v>7.498066425323486</v>
       </c>
       <c r="C1026" t="n">
-        <v>7.653893789041931</v>
+        <v>7.653894275788911</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.406402204334709</v>
+        <v>7.40640267534254</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.461400625659731</v>
+        <v>7.461401100165169</v>
       </c>
       <c r="F1026" t="n">
         <v>2110700</v>
@@ -20972,16 +20972,16 @@
         <v>45286</v>
       </c>
       <c r="B1028" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C1028" t="n">
-        <v>7.433901462933017</v>
+        <v>7.433901956821806</v>
       </c>
       <c r="D1028" t="n">
-        <v>7.168078073639243</v>
+        <v>7.168078549867428</v>
       </c>
       <c r="E1028" t="n">
-        <v>7.37890391218996</v>
+        <v>7.378904402424857</v>
       </c>
       <c r="F1028" t="n">
         <v>1748700</v>
@@ -20992,16 +20992,16 @@
         <v>45287</v>
       </c>
       <c r="B1029" t="n">
-        <v>7.232242107391357</v>
+        <v>7.232241630554199</v>
       </c>
       <c r="C1029" t="n">
-        <v>7.333071969353814</v>
+        <v>7.333071485868728</v>
       </c>
       <c r="D1029" t="n">
-        <v>7.140578795191465</v>
+        <v>7.140578324397864</v>
       </c>
       <c r="E1029" t="n">
-        <v>7.195576782511401</v>
+        <v>7.195576308091665</v>
       </c>
       <c r="F1029" t="n">
         <v>1937700</v>
@@ -21012,16 +21012,16 @@
         <v>45288</v>
       </c>
       <c r="B1030" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C1030" t="n">
-        <v>7.31473937451447</v>
+        <v>7.314739860486446</v>
       </c>
       <c r="D1030" t="n">
-        <v>7.103913535963753</v>
+        <v>7.103914007929016</v>
       </c>
       <c r="E1030" t="n">
-        <v>7.223076061467453</v>
+        <v>7.22307654134956</v>
       </c>
       <c r="F1030" t="n">
         <v>1438100</v>
@@ -21032,16 +21032,16 @@
         <v>45293</v>
       </c>
       <c r="B1031" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1031" t="n">
-        <v>7.204743074499178</v>
+        <v>7.204743572895473</v>
       </c>
       <c r="D1031" t="n">
-        <v>6.828922852298171</v>
+        <v>6.828923324696675</v>
       </c>
       <c r="E1031" t="n">
-        <v>7.195576525064578</v>
+        <v>7.195577022826767</v>
       </c>
       <c r="F1031" t="n">
         <v>2422400</v>
@@ -21052,16 +21052,16 @@
         <v>45294</v>
       </c>
       <c r="B1032" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1032" t="n">
-        <v>7.03974868135747</v>
+        <v>7.039749168340091</v>
       </c>
       <c r="D1032" t="n">
-        <v>6.764758754596515</v>
+        <v>6.764759222556394</v>
       </c>
       <c r="E1032" t="n">
-        <v>6.874754725300897</v>
+        <v>6.874755200869873</v>
       </c>
       <c r="F1032" t="n">
         <v>2218000</v>
@@ -21172,16 +21172,16 @@
         <v>45302</v>
       </c>
       <c r="B1038" t="n">
-        <v>6.847255706787109</v>
+        <v>6.847256183624268</v>
       </c>
       <c r="C1038" t="n">
-        <v>7.213909389872389</v>
+        <v>7.213909892243003</v>
       </c>
       <c r="D1038" t="n">
-        <v>6.819756931879673</v>
+        <v>6.819757406801839</v>
       </c>
       <c r="E1038" t="n">
-        <v>6.993917442272309</v>
+        <v>6.993917929322868</v>
       </c>
       <c r="F1038" t="n">
         <v>2188900</v>
@@ -21192,16 +21192,16 @@
         <v>45303</v>
       </c>
       <c r="B1039" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C1039" t="n">
-        <v>7.085581130213425</v>
+        <v>7.085580634123072</v>
       </c>
       <c r="D1039" t="n">
-        <v>6.792258080744574</v>
+        <v>6.792257605190961</v>
       </c>
       <c r="E1039" t="n">
-        <v>6.83808995747211</v>
+        <v>6.83808947870962</v>
       </c>
       <c r="F1039" t="n">
         <v>1935400</v>
@@ -21212,16 +21212,16 @@
         <v>45306</v>
       </c>
       <c r="B1040" t="n">
-        <v>6.929753303527832</v>
+        <v>6.929752826690674</v>
       </c>
       <c r="C1040" t="n">
-        <v>7.003083956937887</v>
+        <v>7.003083475054838</v>
       </c>
       <c r="D1040" t="n">
-        <v>6.700594793078822</v>
+        <v>6.700594332010089</v>
       </c>
       <c r="E1040" t="n">
-        <v>6.746426670002693</v>
+        <v>6.746426205780263</v>
       </c>
       <c r="F1040" t="n">
         <v>1399400</v>
@@ -21232,16 +21232,16 @@
         <v>45307</v>
       </c>
       <c r="B1041" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C1041" t="n">
-        <v>6.911420074576932</v>
+        <v>6.911420565075185</v>
       </c>
       <c r="D1041" t="n">
-        <v>6.654762808645371</v>
+        <v>6.654763280928852</v>
       </c>
       <c r="E1041" t="n">
-        <v>6.911420074576932</v>
+        <v>6.911420565075185</v>
       </c>
       <c r="F1041" t="n">
         <v>2256200</v>
@@ -21332,16 +21332,16 @@
         <v>45314</v>
       </c>
       <c r="B1046" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C1046" t="n">
-        <v>6.801424103463406</v>
+        <v>6.801424586155328</v>
       </c>
       <c r="D1046" t="n">
-        <v>6.526433738594455</v>
+        <v>6.526434201770518</v>
       </c>
       <c r="E1046" t="n">
-        <v>6.608930935472167</v>
+        <v>6.608931404502994</v>
       </c>
       <c r="F1046" t="n">
         <v>2038100</v>
@@ -21352,16 +21352,16 @@
         <v>45315</v>
       </c>
       <c r="B1047" t="n">
-        <v>6.874755382537842</v>
+        <v>6.874754905700684</v>
       </c>
       <c r="C1047" t="n">
-        <v>6.957252586995552</v>
+        <v>6.957252104436338</v>
       </c>
       <c r="D1047" t="n">
-        <v>6.755592851006743</v>
+        <v>6.75559238243477</v>
       </c>
       <c r="E1047" t="n">
-        <v>6.801424728391066</v>
+        <v>6.801424256640167</v>
       </c>
       <c r="F1047" t="n">
         <v>1933800</v>
@@ -21372,16 +21372,16 @@
         <v>45316</v>
       </c>
       <c r="B1048" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1048" t="n">
-        <v>7.149745089146987</v>
+        <v>7.149745583738733</v>
       </c>
       <c r="D1048" t="n">
-        <v>6.83808940173277</v>
+        <v>6.83808987476538</v>
       </c>
       <c r="E1048" t="n">
-        <v>6.883921274735496</v>
+        <v>6.883921750938578</v>
       </c>
       <c r="F1048" t="n">
         <v>2213100</v>
@@ -21392,16 +21392,16 @@
         <v>45317</v>
       </c>
       <c r="B1049" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="C1049" t="n">
-        <v>7.17724475009915</v>
+        <v>7.177244267717364</v>
       </c>
       <c r="D1049" t="n">
-        <v>6.718927711782881</v>
+        <v>6.718927260204529</v>
       </c>
       <c r="E1049" t="n">
-        <v>6.957252781508231</v>
+        <v>6.957252313912079</v>
       </c>
       <c r="F1049" t="n">
         <v>2582000</v>
@@ -21572,16 +21572,16 @@
         <v>45330</v>
       </c>
       <c r="B1058" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1058" t="n">
-        <v>7.617229205001097</v>
+        <v>7.617228715801493</v>
       </c>
       <c r="D1058" t="n">
-        <v>7.103913761472643</v>
+        <v>7.103913305239581</v>
       </c>
       <c r="E1058" t="n">
-        <v>7.131412974802268</v>
+        <v>7.13141251680313</v>
       </c>
       <c r="F1058" t="n">
         <v>7472200</v>
@@ -21652,16 +21652,16 @@
         <v>45338</v>
       </c>
       <c r="B1062" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1062" t="n">
-        <v>7.443068249055412</v>
+        <v>7.443067771040908</v>
       </c>
       <c r="D1062" t="n">
-        <v>7.158911751046727</v>
+        <v>7.158911291281541</v>
       </c>
       <c r="E1062" t="n">
-        <v>7.333072269907244</v>
+        <v>7.333071798956986</v>
       </c>
       <c r="F1062" t="n">
         <v>2565400</v>
@@ -21692,16 +21692,16 @@
         <v>45342</v>
       </c>
       <c r="B1064" t="n">
-        <v>7.204743385314941</v>
+        <v>7.2047438621521</v>
       </c>
       <c r="C1064" t="n">
-        <v>7.314739360764598</v>
+        <v>7.314739844881705</v>
       </c>
       <c r="D1064" t="n">
-        <v>6.920586896860753</v>
+        <v>6.92058735489136</v>
       </c>
       <c r="E1064" t="n">
-        <v>7.241408710464827</v>
+        <v>7.241409189728635</v>
       </c>
       <c r="F1064" t="n">
         <v>5572100</v>
@@ -21752,16 +21752,16 @@
         <v>45345</v>
       </c>
       <c r="B1067" t="n">
-        <v>7.91055154800415</v>
+        <v>7.910551071166992</v>
       </c>
       <c r="C1067" t="n">
-        <v>8.249706024094255</v>
+        <v>8.249705526813331</v>
       </c>
       <c r="D1067" t="n">
-        <v>7.754723697615412</v>
+        <v>7.754723230171342</v>
       </c>
       <c r="E1067" t="n">
-        <v>8.075545948220533</v>
+        <v>8.07554546143774</v>
       </c>
       <c r="F1067" t="n">
         <v>3191100</v>
@@ -21772,16 +21772,16 @@
         <v>45348</v>
       </c>
       <c r="B1068" t="n">
-        <v>8.084711074829102</v>
+        <v>8.084712028503418</v>
       </c>
       <c r="C1068" t="n">
-        <v>8.11221072244448</v>
+        <v>8.112211679362662</v>
       </c>
       <c r="D1068" t="n">
-        <v>7.828053816277292</v>
+        <v>7.828054739676261</v>
       </c>
       <c r="E1068" t="n">
-        <v>7.910551010782934</v>
+        <v>7.910551943913292</v>
       </c>
       <c r="F1068" t="n">
         <v>1473000</v>
@@ -21892,16 +21892,16 @@
         <v>45356</v>
       </c>
       <c r="B1074" t="n">
-        <v>8.790520668029785</v>
+        <v>8.790519714355469</v>
       </c>
       <c r="C1074" t="n">
-        <v>8.90968319927654</v>
+        <v>8.909682232674404</v>
       </c>
       <c r="D1074" t="n">
-        <v>8.61635970921901</v>
+        <v>8.616358774439233</v>
       </c>
       <c r="E1074" t="n">
-        <v>8.763021891332949</v>
+        <v>8.763020940641946</v>
       </c>
       <c r="F1074" t="n">
         <v>2317900</v>
@@ -22112,16 +22112,16 @@
         <v>45371</v>
       </c>
       <c r="B1085" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1085" t="n">
-        <v>9.193838844589299</v>
+        <v>9.193837883247255</v>
       </c>
       <c r="D1085" t="n">
-        <v>8.341369812594202</v>
+        <v>8.341368940389497</v>
       </c>
       <c r="E1085" t="n">
-        <v>8.387200813603702</v>
+        <v>8.387199936606738</v>
       </c>
       <c r="F1085" t="n">
         <v>3946300</v>
@@ -22172,16 +22172,16 @@
         <v>45376</v>
       </c>
       <c r="B1088" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1088" t="n">
-        <v>8.634692952368088</v>
+        <v>8.634691984306407</v>
       </c>
       <c r="D1088" t="n">
-        <v>8.378035659229033</v>
+        <v>8.378034719941983</v>
       </c>
       <c r="E1088" t="n">
-        <v>8.433033213530791</v>
+        <v>8.433032268077797</v>
       </c>
       <c r="F1088" t="n">
         <v>2424700</v>
@@ -22232,16 +22232,16 @@
         <v>45379</v>
       </c>
       <c r="B1091" t="n">
-        <v>9.752985954284668</v>
+        <v>9.752986907958984</v>
       </c>
       <c r="C1091" t="n">
-        <v>9.881314153231251</v>
+        <v>9.881315119453859</v>
       </c>
       <c r="D1091" t="n">
-        <v>9.340499960041242</v>
+        <v>9.340500873381522</v>
       </c>
       <c r="E1091" t="n">
-        <v>9.386331834309434</v>
+        <v>9.386332752131281</v>
       </c>
       <c r="F1091" t="n">
         <v>5263200</v>
@@ -22312,16 +22312,16 @@
         <v>45386</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C1095" t="n">
-        <v>11.18293335294909</v>
+        <v>11.18293432413664</v>
       </c>
       <c r="D1095" t="n">
-        <v>10.43129383819321</v>
+        <v>10.43129474410425</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.43129383819321</v>
+        <v>10.43129474410425</v>
       </c>
       <c r="F1095" t="n">
         <v>7684100</v>
@@ -22372,16 +22372,16 @@
         <v>45391</v>
       </c>
       <c r="B1098" t="n">
-        <v>11.40292739868164</v>
+        <v>11.40292644500732</v>
       </c>
       <c r="C1098" t="n">
-        <v>11.73291622197656</v>
+        <v>11.7329152407039</v>
       </c>
       <c r="D1098" t="n">
-        <v>11.28376573934777</v>
+        <v>11.28376479563944</v>
       </c>
       <c r="E1098" t="n">
-        <v>11.29293141564012</v>
+        <v>11.29293047116523</v>
       </c>
       <c r="F1098" t="n">
         <v>4003300</v>
@@ -22392,16 +22392,16 @@
         <v>45392</v>
       </c>
       <c r="B1099" t="n">
-        <v>10.58712196350098</v>
+        <v>10.58712291717529</v>
       </c>
       <c r="C1099" t="n">
-        <v>11.36626027193104</v>
+        <v>11.36626129578913</v>
       </c>
       <c r="D1099" t="n">
-        <v>10.44962635083433</v>
+        <v>10.44962729212322</v>
       </c>
       <c r="E1099" t="n">
-        <v>11.36626027193104</v>
+        <v>11.36626129578913</v>
       </c>
       <c r="F1099" t="n">
         <v>6473200</v>
@@ -22412,16 +22412,16 @@
         <v>45393</v>
       </c>
       <c r="B1100" t="n">
-        <v>10.50462627410889</v>
+        <v>10.50462532043457</v>
       </c>
       <c r="C1100" t="n">
-        <v>10.94461019960207</v>
+        <v>10.94460920598332</v>
       </c>
       <c r="D1100" t="n">
-        <v>10.31213308816303</v>
+        <v>10.31213215196442</v>
       </c>
       <c r="E1100" t="n">
-        <v>10.66045413293031</v>
+        <v>10.66045316510899</v>
       </c>
       <c r="F1100" t="n">
         <v>3334800</v>
@@ -22492,16 +22492,16 @@
         <v>45399</v>
       </c>
       <c r="B1104" t="n">
-        <v>9.193839073181152</v>
+        <v>9.193840026855469</v>
       </c>
       <c r="C1104" t="n">
-        <v>9.707154514451329</v>
+        <v>9.707155521371709</v>
       </c>
       <c r="D1104" t="n">
-        <v>9.129674970836255</v>
+        <v>9.129675917854847</v>
       </c>
       <c r="E1104" t="n">
-        <v>9.395498804484115</v>
+        <v>9.395499779076538</v>
       </c>
       <c r="F1104" t="n">
         <v>2870900</v>
@@ -22612,16 +22612,16 @@
         <v>45407</v>
       </c>
       <c r="B1110" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C1110" t="n">
-        <v>10.00964332536244</v>
+        <v>10.00964236464995</v>
       </c>
       <c r="D1110" t="n">
-        <v>9.505494451765941</v>
+        <v>9.505493539440995</v>
       </c>
       <c r="E1110" t="n">
-        <v>9.670488851095419</v>
+        <v>9.670487922934525</v>
       </c>
       <c r="F1110" t="n">
         <v>2344600</v>
@@ -22672,16 +22672,16 @@
         <v>45412</v>
       </c>
       <c r="B1113" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C1113" t="n">
-        <v>10.89877837583131</v>
+        <v>10.89877940479569</v>
       </c>
       <c r="D1113" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="E1113" t="n">
-        <v>10.86211305146715</v>
+        <v>10.86211407696992</v>
       </c>
       <c r="F1113" t="n">
         <v>3726700</v>
@@ -22712,16 +22712,16 @@
         <v>45415</v>
       </c>
       <c r="B1115" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C1115" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="D1115" t="n">
-        <v>10.41296228000361</v>
+        <v>10.41296137869417</v>
       </c>
       <c r="E1115" t="n">
-        <v>10.48629293256791</v>
+        <v>10.48629202491122</v>
       </c>
       <c r="F1115" t="n">
         <v>3177300</v>
@@ -22792,16 +22792,16 @@
         <v>45421</v>
       </c>
       <c r="B1119" t="n">
-        <v>11.2379322052002</v>
+        <v>11.23793315887451</v>
       </c>
       <c r="C1119" t="n">
-        <v>11.33876162292093</v>
+        <v>11.33876258515184</v>
       </c>
       <c r="D1119" t="n">
-        <v>10.56878898092192</v>
+        <v>10.56878987781135</v>
       </c>
       <c r="E1119" t="n">
-        <v>11.30209630064337</v>
+        <v>11.30209725976278</v>
       </c>
       <c r="F1119" t="n">
         <v>4225100</v>
@@ -22832,16 +22832,16 @@
         <v>45425</v>
       </c>
       <c r="B1121" t="n">
-        <v>9.303834915161133</v>
+        <v>9.303833961486816</v>
       </c>
       <c r="C1121" t="n">
-        <v>9.569658744903728</v>
+        <v>9.569657763981576</v>
       </c>
       <c r="D1121" t="n">
-        <v>9.184673262319901</v>
+        <v>9.184672320860052</v>
       </c>
       <c r="E1121" t="n">
-        <v>9.395498666453195</v>
+        <v>9.395497703383034</v>
       </c>
       <c r="F1121" t="n">
         <v>4893500</v>
@@ -22872,16 +22872,16 @@
         <v>45427</v>
       </c>
       <c r="B1123" t="n">
-        <v>9.52382755279541</v>
+        <v>9.523828506469727</v>
       </c>
       <c r="C1123" t="n">
-        <v>9.835482377775513</v>
+        <v>9.835483362657577</v>
       </c>
       <c r="D1123" t="n">
-        <v>9.395498478389273</v>
+        <v>9.395499419213278</v>
       </c>
       <c r="E1123" t="n">
-        <v>9.597158202693118</v>
+        <v>9.597159163710444</v>
       </c>
       <c r="F1123" t="n">
         <v>4359100</v>
@@ -23012,16 +23012,16 @@
         <v>45436</v>
       </c>
       <c r="B1130" t="n">
-        <v>8.708023071289062</v>
+        <v>8.708024024963379</v>
       </c>
       <c r="C1130" t="n">
-        <v>9.083842874498499</v>
+        <v>9.083843869331375</v>
       </c>
       <c r="D1130" t="n">
-        <v>8.67135774595571</v>
+        <v>8.671358695614559</v>
       </c>
       <c r="E1130" t="n">
-        <v>8.882183148079907</v>
+        <v>8.882184120827667</v>
       </c>
       <c r="F1130" t="n">
         <v>2233000</v>
@@ -23032,16 +23032,16 @@
         <v>45439</v>
       </c>
       <c r="B1131" t="n">
-        <v>8.808852195739746</v>
+        <v>8.808853149414062</v>
       </c>
       <c r="C1131" t="n">
-        <v>8.836351844425723</v>
+        <v>8.836352801077238</v>
       </c>
       <c r="D1131" t="n">
-        <v>8.625525575351304</v>
+        <v>8.625526509178098</v>
       </c>
       <c r="E1131" t="n">
-        <v>8.680523998552976</v>
+        <v>8.680524938334075</v>
       </c>
       <c r="F1131" t="n">
         <v>1394600</v>
@@ -23092,16 +23092,16 @@
         <v>45443</v>
       </c>
       <c r="B1134" t="n">
-        <v>8.808852195739746</v>
+        <v>8.808853149414062</v>
       </c>
       <c r="C1134" t="n">
-        <v>9.395498255153042</v>
+        <v>9.395499272339524</v>
       </c>
       <c r="D1134" t="n">
-        <v>8.717189322630665</v>
+        <v>8.717190266381268</v>
       </c>
       <c r="E1134" t="n">
-        <v>9.074676013845558</v>
+        <v>9.074676996298805</v>
       </c>
       <c r="F1134" t="n">
         <v>8270300</v>
@@ -23172,16 +23172,16 @@
         <v>45449</v>
       </c>
       <c r="B1138" t="n">
-        <v>9.074676513671875</v>
+        <v>9.074675559997559</v>
       </c>
       <c r="C1138" t="n">
-        <v>9.239670918194381</v>
+        <v>9.2396699471805</v>
       </c>
       <c r="D1138" t="n">
-        <v>8.772187354827501</v>
+        <v>8.772186432942322</v>
       </c>
       <c r="E1138" t="n">
-        <v>8.937181759350008</v>
+        <v>8.937180820125265</v>
       </c>
       <c r="F1138" t="n">
         <v>3356600</v>
@@ -23252,16 +23252,16 @@
         <v>45455</v>
       </c>
       <c r="B1142" t="n">
-        <v>8.909682273864746</v>
+        <v>8.909683227539062</v>
       </c>
       <c r="C1142" t="n">
-        <v>9.661321836091128</v>
+        <v>9.661322870219418</v>
       </c>
       <c r="D1142" t="n">
-        <v>8.882182625853835</v>
+        <v>8.882183576584646</v>
       </c>
       <c r="E1142" t="n">
-        <v>9.395498024510802</v>
+        <v>9.395499030185853</v>
       </c>
       <c r="F1142" t="n">
         <v>3064700</v>
@@ -23272,16 +23272,16 @@
         <v>45456</v>
       </c>
       <c r="B1143" t="n">
-        <v>8.62552547454834</v>
+        <v>8.625526428222656</v>
       </c>
       <c r="C1143" t="n">
-        <v>8.891349289547579</v>
+        <v>8.891350272612492</v>
       </c>
       <c r="D1143" t="n">
-        <v>8.59802670035401</v>
+        <v>8.598027650987946</v>
       </c>
       <c r="E1143" t="n">
-        <v>8.891349289547579</v>
+        <v>8.891350272612492</v>
       </c>
       <c r="F1143" t="n">
         <v>2367500</v>
@@ -23452,16 +23452,16 @@
         <v>45469</v>
       </c>
       <c r="B1152" t="n">
-        <v>8.735522270202637</v>
+        <v>8.73552131652832</v>
       </c>
       <c r="C1152" t="n">
-        <v>9.01967921093841</v>
+        <v>9.019678226242117</v>
       </c>
       <c r="D1152" t="n">
-        <v>8.735522270202637</v>
+        <v>8.73552131652832</v>
       </c>
       <c r="E1152" t="n">
-        <v>9.01967921093841</v>
+        <v>9.019678226242117</v>
       </c>
       <c r="F1152" t="n">
         <v>1529900</v>
@@ -23512,16 +23512,16 @@
         <v>45474</v>
       </c>
       <c r="B1155" t="n">
-        <v>8.579693794250488</v>
+        <v>8.579694747924805</v>
       </c>
       <c r="C1155" t="n">
-        <v>8.689689767669948</v>
+        <v>8.689690733570847</v>
       </c>
       <c r="D1155" t="n">
-        <v>8.414700271206444</v>
+        <v>8.414701206540935</v>
       </c>
       <c r="E1155" t="n">
-        <v>8.579693794250488</v>
+        <v>8.579694747924805</v>
       </c>
       <c r="F1155" t="n">
         <v>1954600</v>
@@ -23532,16 +23532,16 @@
         <v>45475</v>
       </c>
       <c r="B1156" t="n">
-        <v>8.414699554443359</v>
+        <v>8.414700508117676</v>
       </c>
       <c r="C1156" t="n">
-        <v>8.836351187053534</v>
+        <v>8.836352188515454</v>
       </c>
       <c r="D1156" t="n">
-        <v>8.387199907803193</v>
+        <v>8.387200858360856</v>
       </c>
       <c r="E1156" t="n">
-        <v>8.588859612313334</v>
+        <v>8.588860585725962</v>
       </c>
       <c r="F1156" t="n">
         <v>3229800</v>
@@ -23732,16 +23732,16 @@
         <v>45489</v>
       </c>
       <c r="B1166" t="n">
-        <v>9.303834915161133</v>
+        <v>9.303833961486816</v>
       </c>
       <c r="C1166" t="n">
-        <v>9.789651573170611</v>
+        <v>9.789650569698455</v>
       </c>
       <c r="D1166" t="n">
-        <v>9.258003913685421</v>
+        <v>9.258002964708936</v>
       </c>
       <c r="E1166" t="n">
-        <v>9.743819697524581</v>
+        <v>9.743818698750346</v>
       </c>
       <c r="F1166" t="n">
         <v>1952400</v>
@@ -23832,16 +23832,16 @@
         <v>45496</v>
       </c>
       <c r="B1171" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="C1171" t="n">
-        <v>8.607194619854459</v>
+        <v>8.607193615930459</v>
       </c>
       <c r="D1171" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="E1171" t="n">
-        <v>8.607194619854459</v>
+        <v>8.607193615930459</v>
       </c>
       <c r="F1171" t="n">
         <v>3005900</v>
@@ -23892,16 +23892,16 @@
         <v>45499</v>
       </c>
       <c r="B1174" t="n">
-        <v>7.818887233734131</v>
+        <v>7.818887710571289</v>
       </c>
       <c r="C1174" t="n">
-        <v>7.883052203726183</v>
+        <v>7.883052684476461</v>
       </c>
       <c r="D1174" t="n">
-        <v>7.653893719596588</v>
+        <v>7.653894186371567</v>
       </c>
       <c r="E1174" t="n">
-        <v>7.718057815418397</v>
+        <v>7.718058286106443</v>
       </c>
       <c r="F1174" t="n">
         <v>2119900</v>
@@ -23952,16 +23952,16 @@
         <v>45504</v>
       </c>
       <c r="B1177" t="n">
-        <v>7.736391067504883</v>
+        <v>7.736390590667725</v>
       </c>
       <c r="C1177" t="n">
-        <v>7.873886700753659</v>
+        <v>7.873886215441875</v>
       </c>
       <c r="D1177" t="n">
-        <v>7.617229409194445</v>
+        <v>7.617228939701889</v>
       </c>
       <c r="E1177" t="n">
-        <v>7.718058840907261</v>
+        <v>7.718058365200021</v>
       </c>
       <c r="F1177" t="n">
         <v>1863600</v>
@@ -23972,16 +23972,16 @@
         <v>45505</v>
       </c>
       <c r="B1178" t="n">
-        <v>7.727224349975586</v>
+        <v>7.727224826812744</v>
       </c>
       <c r="C1178" t="n">
-        <v>7.965548508650412</v>
+        <v>7.965549000194251</v>
       </c>
       <c r="D1178" t="n">
-        <v>7.663059380104842</v>
+        <v>7.663059852982463</v>
       </c>
       <c r="E1178" t="n">
-        <v>7.828053768100695</v>
+        <v>7.828054251159909</v>
       </c>
       <c r="F1178" t="n">
         <v>2732500</v>
@@ -24032,16 +24032,16 @@
         <v>45510</v>
       </c>
       <c r="B1181" t="n">
-        <v>7.95638370513916</v>
+        <v>7.956383228302002</v>
       </c>
       <c r="C1181" t="n">
-        <v>8.176375663782647</v>
+        <v>8.176375173761064</v>
       </c>
       <c r="D1181" t="n">
-        <v>7.782222748918646</v>
+        <v>7.782222282519196</v>
       </c>
       <c r="E1181" t="n">
-        <v>7.993049031579741</v>
+        <v>7.993048552545178</v>
       </c>
       <c r="F1181" t="n">
         <v>1835500</v>
@@ -24052,16 +24052,16 @@
         <v>45511</v>
       </c>
       <c r="B1182" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1182" t="n">
-        <v>8.543029196304673</v>
+        <v>8.543028238519694</v>
       </c>
       <c r="D1182" t="n">
-        <v>8.020548059586147</v>
+        <v>8.020547160378118</v>
       </c>
       <c r="E1182" t="n">
-        <v>8.158042819510907</v>
+        <v>8.158041904887924</v>
       </c>
       <c r="F1182" t="n">
         <v>2816900</v>
@@ -24092,16 +24092,16 @@
         <v>45513</v>
       </c>
       <c r="B1184" t="n">
-        <v>7.846388339996338</v>
+        <v>7.84638786315918</v>
       </c>
       <c r="C1184" t="n">
-        <v>8.103045645170351</v>
+        <v>8.103045152735731</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.653895142573226</v>
+        <v>7.653894677434178</v>
       </c>
       <c r="E1184" t="n">
-        <v>8.103045645170351</v>
+        <v>8.103045152735731</v>
       </c>
       <c r="F1184" t="n">
         <v>6458600</v>
@@ -24132,16 +24132,16 @@
         <v>45517</v>
       </c>
       <c r="B1186" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="C1186" t="n">
-        <v>8.497198631398319</v>
+        <v>8.497197640304007</v>
       </c>
       <c r="D1186" t="n">
-        <v>8.103045683802677</v>
+        <v>8.103044738681486</v>
       </c>
       <c r="E1186" t="n">
-        <v>8.497198631398319</v>
+        <v>8.497197640304007</v>
       </c>
       <c r="F1186" t="n">
         <v>4500900</v>
@@ -24192,16 +24192,16 @@
         <v>45520</v>
       </c>
       <c r="B1189" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1189" t="n">
-        <v>8.598027624776794</v>
+        <v>8.598026660825775</v>
       </c>
       <c r="D1189" t="n">
-        <v>8.304705004046447</v>
+        <v>8.304704072980718</v>
       </c>
       <c r="E1189" t="n">
-        <v>8.387201335499084</v>
+        <v>8.387200395184442</v>
       </c>
       <c r="F1189" t="n">
         <v>3088500</v>
@@ -24212,16 +24212,16 @@
         <v>45523</v>
       </c>
       <c r="B1190" t="n">
-        <v>8.744688987731934</v>
+        <v>8.744688034057617</v>
       </c>
       <c r="C1190" t="n">
-        <v>8.827186193851068</v>
+        <v>8.82718523117981</v>
       </c>
       <c r="D1190" t="n">
-        <v>8.442199814742022</v>
+        <v>8.442198894056432</v>
       </c>
       <c r="E1190" t="n">
-        <v>8.478865142553818</v>
+        <v>8.478864217869598</v>
       </c>
       <c r="F1190" t="n">
         <v>2333900</v>
@@ -24272,16 +24272,16 @@
         <v>45526</v>
       </c>
       <c r="B1193" t="n">
-        <v>8.653023719787598</v>
+        <v>8.653024673461914</v>
       </c>
       <c r="C1193" t="n">
-        <v>9.093008450852169</v>
+        <v>9.093009453018452</v>
       </c>
       <c r="D1193" t="n">
-        <v>8.616358398379734</v>
+        <v>8.616359348013061</v>
       </c>
       <c r="E1193" t="n">
-        <v>9.038010031655267</v>
+        <v>9.038011027760017</v>
       </c>
       <c r="F1193" t="n">
         <v>2148900</v>
@@ -24412,16 +24412,16 @@
         <v>45537</v>
       </c>
       <c r="B1200" t="n">
-        <v>8.93718147277832</v>
+        <v>8.937182426452637</v>
       </c>
       <c r="C1200" t="n">
-        <v>9.2488371716963</v>
+        <v>9.248838158626967</v>
       </c>
       <c r="D1200" t="n">
-        <v>8.918848373232414</v>
+        <v>8.918849324950433</v>
       </c>
       <c r="E1200" t="n">
-        <v>9.120508097385867</v>
+        <v>9.120509070622715</v>
       </c>
       <c r="F1200" t="n">
         <v>2102800</v>
@@ -24452,16 +24452,16 @@
         <v>45539</v>
       </c>
       <c r="B1202" t="n">
-        <v>9.294669151306152</v>
+        <v>9.294670104980469</v>
       </c>
       <c r="C1202" t="n">
-        <v>9.468829228106612</v>
+        <v>9.468830199650526</v>
       </c>
       <c r="D1202" t="n">
-        <v>9.184673175300023</v>
+        <v>9.184674117688264</v>
       </c>
       <c r="E1202" t="n">
-        <v>9.212171950758979</v>
+        <v>9.212172895968715</v>
       </c>
       <c r="F1202" t="n">
         <v>2019900</v>
@@ -24572,16 +24572,16 @@
         <v>45547</v>
       </c>
       <c r="B1208" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1208" t="n">
-        <v>9.212171944329347</v>
+        <v>9.212170981070326</v>
       </c>
       <c r="D1208" t="n">
-        <v>8.955514667160847</v>
+        <v>8.955513730738867</v>
       </c>
       <c r="E1208" t="n">
-        <v>9.175506619019561</v>
+        <v>9.175505659594403</v>
       </c>
       <c r="F1208" t="n">
         <v>1127400</v>
@@ -24612,16 +24612,16 @@
         <v>45551</v>
       </c>
       <c r="B1210" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C1210" t="n">
-        <v>10.17463772469192</v>
+        <v>10.17463674814347</v>
       </c>
       <c r="D1210" t="n">
-        <v>9.569658551873937</v>
+        <v>9.569657633390603</v>
       </c>
       <c r="E1210" t="n">
-        <v>9.707154176038602</v>
+        <v>9.707153244358619</v>
       </c>
       <c r="F1210" t="n">
         <v>2756600</v>
@@ -24652,16 +24652,16 @@
         <v>45553</v>
       </c>
       <c r="B1212" t="n">
-        <v>9.890481948852539</v>
+        <v>9.890480995178223</v>
       </c>
       <c r="C1212" t="n">
-        <v>10.26630179168833</v>
+        <v>10.26630080177617</v>
       </c>
       <c r="D1212" t="n">
-        <v>9.606324991929888</v>
+        <v>9.606324065654963</v>
       </c>
       <c r="E1212" t="n">
-        <v>9.697988752013428</v>
+        <v>9.697987816899968</v>
       </c>
       <c r="F1212" t="n">
         <v>2495300</v>
@@ -24672,16 +24672,16 @@
         <v>45554</v>
       </c>
       <c r="B1213" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C1213" t="n">
-        <v>10.15630421586989</v>
+        <v>10.15630519881978</v>
       </c>
       <c r="D1213" t="n">
-        <v>9.798816656451679</v>
+        <v>9.798817604803125</v>
       </c>
       <c r="E1213" t="n">
-        <v>10.00047637259812</v>
+        <v>10.00047734046665</v>
       </c>
       <c r="F1213" t="n">
         <v>3128500</v>
@@ -24732,16 +24732,16 @@
         <v>45559</v>
       </c>
       <c r="B1216" t="n">
-        <v>9.487161636352539</v>
+        <v>9.487162590026855</v>
       </c>
       <c r="C1216" t="n">
-        <v>9.615489828587524</v>
+        <v>9.615490795161728</v>
       </c>
       <c r="D1216" t="n">
-        <v>9.28550192462153</v>
+        <v>9.285502858024484</v>
       </c>
       <c r="E1216" t="n">
-        <v>9.514660409807144</v>
+        <v>9.51466136624571</v>
       </c>
       <c r="F1216" t="n">
         <v>1652000</v>
@@ -24772,16 +24772,16 @@
         <v>45561</v>
       </c>
       <c r="B1218" t="n">
-        <v>9.551325798034668</v>
+        <v>9.551326751708984</v>
       </c>
       <c r="C1218" t="n">
-        <v>9.789650834064538</v>
+        <v>9.78965181153497</v>
       </c>
       <c r="D1218" t="n">
-        <v>9.450496378562148</v>
+        <v>9.450497322168916</v>
       </c>
       <c r="E1218" t="n">
-        <v>9.450496378562148</v>
+        <v>9.450497322168916</v>
       </c>
       <c r="F1218" t="n">
         <v>1643400</v>
@@ -24792,16 +24792,16 @@
         <v>45562</v>
       </c>
       <c r="B1219" t="n">
-        <v>9.587992668151855</v>
+        <v>9.587991714477539</v>
       </c>
       <c r="C1219" t="n">
-        <v>9.752987084977519</v>
+        <v>9.752986114891955</v>
       </c>
       <c r="D1219" t="n">
-        <v>9.450497903577398</v>
+        <v>9.450496963579065</v>
       </c>
       <c r="E1219" t="n">
-        <v>9.532994237819837</v>
+        <v>9.532993289615966</v>
       </c>
       <c r="F1219" t="n">
         <v>1380700</v>
@@ -24892,16 +24892,16 @@
         <v>45569</v>
       </c>
       <c r="B1224" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1224" t="n">
-        <v>9.258003819509156</v>
+        <v>9.258002851457784</v>
       </c>
       <c r="D1224" t="n">
-        <v>9.038010993480132</v>
+        <v>9.03801004843203</v>
       </c>
       <c r="E1224" t="n">
-        <v>9.166340069149538</v>
+        <v>9.166339110682868</v>
       </c>
       <c r="F1224" t="n">
         <v>1258700</v>
@@ -24972,16 +24972,16 @@
         <v>45575</v>
       </c>
       <c r="B1228" t="n">
-        <v>9.422996520996094</v>
+        <v>9.42299747467041</v>
       </c>
       <c r="C1228" t="n">
-        <v>9.441329619130419</v>
+        <v>9.441330574660176</v>
       </c>
       <c r="D1228" t="n">
-        <v>8.946347333716643</v>
+        <v>8.946348239150669</v>
       </c>
       <c r="E1228" t="n">
-        <v>9.065509849079064</v>
+        <v>9.065510766573185</v>
       </c>
       <c r="F1228" t="n">
         <v>2116800</v>
@@ -24992,16 +24992,16 @@
         <v>45576</v>
       </c>
       <c r="B1229" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C1229" t="n">
-        <v>10.3671307354659</v>
+        <v>10.36713171423691</v>
       </c>
       <c r="D1229" t="n">
-        <v>9.432163652924501</v>
+        <v>9.432164543424346</v>
       </c>
       <c r="E1229" t="n">
-        <v>9.432163652924501</v>
+        <v>9.432164543424346</v>
       </c>
       <c r="F1229" t="n">
         <v>6482800</v>
@@ -25112,16 +25112,16 @@
         <v>45586</v>
       </c>
       <c r="B1235" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C1235" t="n">
-        <v>11.2654310852861</v>
+        <v>11.26543206609426</v>
       </c>
       <c r="D1235" t="n">
-        <v>10.89877785903058</v>
+        <v>10.89877880791662</v>
       </c>
       <c r="E1235" t="n">
-        <v>11.07293792295939</v>
+        <v>11.07293888700842</v>
       </c>
       <c r="F1235" t="n">
         <v>2389000</v>
@@ -25132,16 +25132,16 @@
         <v>45587</v>
       </c>
       <c r="B1236" t="n">
-        <v>10.65128612518311</v>
+        <v>10.65128707885742</v>
       </c>
       <c r="C1236" t="n">
-        <v>11.00877367135879</v>
+        <v>11.00877465704114</v>
       </c>
       <c r="D1236" t="n">
-        <v>10.62378735214505</v>
+        <v>10.62378830335723</v>
       </c>
       <c r="E1236" t="n">
-        <v>10.86211238292884</v>
+        <v>10.86211335547971</v>
       </c>
       <c r="F1236" t="n">
         <v>2418100</v>
@@ -25232,16 +25232,16 @@
         <v>45594</v>
       </c>
       <c r="B1241" t="n">
-        <v>11.42125988006592</v>
+        <v>11.4212589263916</v>
       </c>
       <c r="C1241" t="n">
-        <v>11.62291960845494</v>
+        <v>11.62291863794205</v>
       </c>
       <c r="D1241" t="n">
-        <v>11.25626547736851</v>
+        <v>11.25626453747121</v>
       </c>
       <c r="E1241" t="n">
-        <v>11.47625830568849</v>
+        <v>11.47625734742181</v>
       </c>
       <c r="F1241" t="n">
         <v>2046100</v>
@@ -25252,16 +25252,16 @@
         <v>45595</v>
       </c>
       <c r="B1242" t="n">
-        <v>12.09956836700439</v>
+        <v>12.09956932067871</v>
       </c>
       <c r="C1242" t="n">
-        <v>12.35622563676056</v>
+        <v>12.35622661066431</v>
       </c>
       <c r="D1242" t="n">
-        <v>11.3204300081306</v>
+        <v>11.32043090039411</v>
       </c>
       <c r="E1242" t="n">
-        <v>11.3204300081306</v>
+        <v>11.32043090039411</v>
       </c>
       <c r="F1242" t="n">
         <v>5623200</v>
@@ -25412,16 +25412,16 @@
         <v>45607</v>
       </c>
       <c r="B1250" t="n">
-        <v>12.33789348602295</v>
+        <v>12.33789443969727</v>
       </c>
       <c r="C1250" t="n">
-        <v>12.47538823424922</v>
+        <v>12.47538919855138</v>
       </c>
       <c r="D1250" t="n">
-        <v>11.64125144689053</v>
+        <v>11.64125234671695</v>
       </c>
       <c r="E1250" t="n">
-        <v>11.69624987068321</v>
+        <v>11.69625077476081</v>
       </c>
       <c r="F1250" t="n">
         <v>4291300</v>
@@ -25432,16 +25432,16 @@
         <v>45608</v>
       </c>
       <c r="B1251" t="n">
-        <v>11.86124420166016</v>
+        <v>11.86124324798584</v>
       </c>
       <c r="C1251" t="n">
-        <v>12.37455965339907</v>
+        <v>12.37455865845288</v>
       </c>
       <c r="D1251" t="n">
-        <v>11.77874787160726</v>
+        <v>11.77874692456585</v>
       </c>
       <c r="E1251" t="n">
-        <v>12.28289589889094</v>
+        <v>12.28289491131475</v>
       </c>
       <c r="F1251" t="n">
         <v>1595200</v>
@@ -25472,16 +25472,16 @@
         <v>45610</v>
       </c>
       <c r="B1253" t="n">
-        <v>10.58712196350098</v>
+        <v>10.58712291717529</v>
       </c>
       <c r="C1253" t="n">
-        <v>10.99960705316045</v>
+        <v>10.99960804399089</v>
       </c>
       <c r="D1253" t="n">
-        <v>10.40379535411568</v>
+        <v>10.40379629127617</v>
       </c>
       <c r="E1253" t="n">
-        <v>10.55962319063574</v>
+        <v>10.559624141833</v>
       </c>
       <c r="F1253" t="n">
         <v>63226600</v>
@@ -25512,16 +25512,16 @@
         <v>45615</v>
       </c>
       <c r="B1255" t="n">
-        <v>11.35709667205811</v>
+        <v>11.35709571838379</v>
       </c>
       <c r="C1255" t="n">
-        <v>11.46709265778581</v>
+        <v>11.46709169487495</v>
       </c>
       <c r="D1255" t="n">
-        <v>10.91711185497689</v>
+        <v>10.91711093824883</v>
       </c>
       <c r="E1255" t="n">
-        <v>11.00877561350184</v>
+        <v>11.00877468907663</v>
       </c>
       <c r="F1255" t="n">
         <v>7243900</v>
@@ -25532,16 +25532,16 @@
         <v>45617</v>
       </c>
       <c r="B1256" t="n">
-        <v>11.2379322052002</v>
+        <v>11.23793315887451</v>
       </c>
       <c r="C1256" t="n">
-        <v>11.32959507380898</v>
+        <v>11.329596035262</v>
       </c>
       <c r="D1256" t="n">
-        <v>10.94460875280948</v>
+        <v>10.94460968159175</v>
       </c>
       <c r="E1256" t="n">
-        <v>11.30209630064337</v>
+        <v>11.30209725976278</v>
       </c>
       <c r="F1256" t="n">
         <v>3263500</v>
@@ -25592,16 +25592,16 @@
         <v>45622</v>
       </c>
       <c r="B1259" t="n">
-        <v>11.57708835601807</v>
+        <v>11.57708740234375</v>
       </c>
       <c r="C1259" t="n">
-        <v>11.66875123809635</v>
+        <v>11.66875027687121</v>
       </c>
       <c r="D1259" t="n">
-        <v>11.31126451190142</v>
+        <v>11.31126358012461</v>
       </c>
       <c r="E1259" t="n">
-        <v>11.63208591043096</v>
+        <v>11.63208495222617</v>
       </c>
       <c r="F1259" t="n">
         <v>7231300</v>
@@ -25652,16 +25652,16 @@
         <v>45625</v>
       </c>
       <c r="B1262" t="n">
-        <v>9.688821792602539</v>
+        <v>9.688820838928223</v>
       </c>
       <c r="C1262" t="n">
-        <v>9.697988343058428</v>
+        <v>9.697987388481845</v>
       </c>
       <c r="D1262" t="n">
-        <v>9.001346243477393</v>
+        <v>9.00134535747155</v>
       </c>
       <c r="E1262" t="n">
-        <v>9.532993931533877</v>
+        <v>9.532992993197755</v>
       </c>
       <c r="F1262" t="n">
         <v>14865400</v>
@@ -25732,16 +25732,16 @@
         <v>45631</v>
       </c>
       <c r="B1266" t="n">
-        <v>9.404665946960449</v>
+        <v>9.404664993286133</v>
       </c>
       <c r="C1266" t="n">
-        <v>9.835483338655724</v>
+        <v>9.835482341294636</v>
       </c>
       <c r="D1266" t="n">
-        <v>9.294669961367802</v>
+        <v>9.294669018847561</v>
       </c>
       <c r="E1266" t="n">
-        <v>9.624657918145745</v>
+        <v>9.624656942163279</v>
       </c>
       <c r="F1266" t="n">
         <v>7256000</v>
@@ -25952,16 +25952,16 @@
         <v>45646</v>
       </c>
       <c r="B1277" t="n">
-        <v>8.93718147277832</v>
+        <v>8.937182426452637</v>
       </c>
       <c r="C1277" t="n">
-        <v>9.138841196931772</v>
+        <v>9.138842172124919</v>
       </c>
       <c r="D1277" t="n">
-        <v>8.588860448938831</v>
+        <v>8.588861365444293</v>
       </c>
       <c r="E1277" t="n">
-        <v>8.799686722865236</v>
+        <v>8.799687661867678</v>
       </c>
       <c r="F1277" t="n">
         <v>5127000</v>
@@ -26032,16 +26032,16 @@
         <v>45656</v>
       </c>
       <c r="B1281" t="n">
-        <v>7.378904342651367</v>
+        <v>7.378903865814209</v>
       </c>
       <c r="C1281" t="n">
-        <v>7.86472014868406</v>
+        <v>7.86471964045267</v>
       </c>
       <c r="D1281" t="n">
-        <v>7.314739801232726</v>
+        <v>7.314739328541989</v>
       </c>
       <c r="E1281" t="n">
-        <v>7.809722594732624</v>
+        <v>7.809722090055269</v>
       </c>
       <c r="F1281" t="n">
         <v>5347400</v>
@@ -34392,19 +34392,39 @@
         <v>46267</v>
       </c>
       <c r="B1699" t="n">
-        <v>9.390000000000001</v>
+        <v>9.390000343322754</v>
       </c>
       <c r="C1699" t="n">
-        <v>9.58</v>
+        <v>9.579999923706055</v>
       </c>
       <c r="D1699" t="n">
         <v>8.75</v>
       </c>
       <c r="E1699" t="n">
-        <v>8.85</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="F1699" t="n">
         <v>13800800</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1700" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="C1700" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>9252000</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -572,16 +572,16 @@
         <v>43782</v>
       </c>
       <c r="B8" t="n">
-        <v>13.55524063110352</v>
+        <v>13.55524158477783</v>
       </c>
       <c r="C8" t="n">
-        <v>14.91076469421387</v>
+        <v>14.91076574325561</v>
       </c>
       <c r="D8" t="n">
-        <v>13.3925774677482</v>
+        <v>13.3925784099784</v>
       </c>
       <c r="E8" t="n">
-        <v>14.73002746301063</v>
+        <v>14.73002849933667</v>
       </c>
       <c r="F8" t="n">
         <v>9002100</v>
@@ -592,16 +592,16 @@
         <v>43783</v>
       </c>
       <c r="B9" t="n">
-        <v>13.55524063110352</v>
+        <v>13.55524158477783</v>
       </c>
       <c r="C9" t="n">
-        <v>13.93478743771993</v>
+        <v>13.93478841809713</v>
       </c>
       <c r="D9" t="n">
-        <v>12.80518405179464</v>
+        <v>12.80518495269898</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60946197282829</v>
+        <v>13.60946293031733</v>
       </c>
       <c r="F9" t="n">
         <v>6889800</v>
@@ -632,16 +632,16 @@
         <v>43788</v>
       </c>
       <c r="B11" t="n">
-        <v>13.91671466827393</v>
+        <v>13.91671371459961</v>
       </c>
       <c r="C11" t="n">
-        <v>14.40470334204927</v>
+        <v>14.40470235493443</v>
       </c>
       <c r="D11" t="n">
-        <v>13.79019962881084</v>
+        <v>13.79019868380626</v>
       </c>
       <c r="E11" t="n">
-        <v>14.27818830258619</v>
+        <v>14.27818732414107</v>
       </c>
       <c r="F11" t="n">
         <v>1475000</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.0643892288208</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="C17" t="n">
-        <v>15.0643892288208</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869433051699</v>
+        <v>14.64869618523321</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7029165283204</v>
+        <v>14.70291838990186</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -952,16 +952,16 @@
         <v>43811</v>
       </c>
       <c r="B27" t="n">
-        <v>17.3055248260498</v>
+        <v>17.30552673339844</v>
       </c>
       <c r="C27" t="n">
-        <v>17.82966076749858</v>
+        <v>17.82966273261547</v>
       </c>
       <c r="D27" t="n">
-        <v>17.17900978889814</v>
+        <v>17.17901168230276</v>
       </c>
       <c r="E27" t="n">
-        <v>17.66699759193894</v>
+        <v>17.66699953912772</v>
       </c>
       <c r="F27" t="n">
         <v>1801300</v>
@@ -992,16 +992,16 @@
         <v>43815</v>
       </c>
       <c r="B29" t="n">
-        <v>16.83560943603516</v>
+        <v>16.83561134338379</v>
       </c>
       <c r="C29" t="n">
-        <v>17.0434577854376</v>
+        <v>17.0434597163339</v>
       </c>
       <c r="D29" t="n">
-        <v>16.62776281027082</v>
+        <v>16.62776469407199</v>
       </c>
       <c r="E29" t="n">
-        <v>16.93501509341728</v>
+        <v>16.93501701202783</v>
       </c>
       <c r="F29" t="n">
         <v>1329000</v>
@@ -1092,16 +1092,16 @@
         <v>43822</v>
       </c>
       <c r="B34" t="n">
-        <v>16.38376808166504</v>
+        <v>16.38376617431641</v>
       </c>
       <c r="C34" t="n">
-        <v>16.60968877719821</v>
+        <v>16.60968684354858</v>
       </c>
       <c r="D34" t="n">
-        <v>16.09458986716468</v>
+        <v>16.09458799348129</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31147352803995</v>
+        <v>16.31147162910763</v>
       </c>
       <c r="F34" t="n">
         <v>766700</v>
@@ -34432,16 +34432,16 @@
         <v>46269</v>
       </c>
       <c r="B1701" t="n">
-        <v>9.210000000000001</v>
+        <v>9.210000038146973</v>
       </c>
       <c r="C1701" t="n">
-        <v>9.44</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="D1701" t="n">
-        <v>9.07</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="E1701" t="n">
-        <v>9.24</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="F1701" t="n">
         <v>5155400</v>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1702"/>
+  <dimension ref="A1:F1703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518585205078</v>
+        <v>15.99518489837646</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073792395533</v>
+        <v>16.13073696219904</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008522099254</v>
+        <v>15.48008429802985</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073792395533</v>
+        <v>16.13073696219904</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -512,16 +512,16 @@
         <v>43777</v>
       </c>
       <c r="B5" t="n">
-        <v>15.81444931030273</v>
+        <v>15.81444835662842</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12170160622253</v>
+        <v>16.12170063401967</v>
       </c>
       <c r="D5" t="n">
-        <v>15.57949157085594</v>
+        <v>15.57949063135051</v>
       </c>
       <c r="E5" t="n">
-        <v>15.95000138823483</v>
+        <v>15.95000042638619</v>
       </c>
       <c r="F5" t="n">
         <v>463500</v>
@@ -752,16 +752,16 @@
         <v>43797</v>
       </c>
       <c r="B17" t="n">
-        <v>15.06439208984375</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="C17" t="n">
-        <v>15.06439208984375</v>
+        <v>15.06439113616943</v>
       </c>
       <c r="D17" t="n">
-        <v>14.64869711259133</v>
+        <v>14.64869618523321</v>
       </c>
       <c r="E17" t="n">
-        <v>14.70291932069259</v>
+        <v>14.70291838990186</v>
       </c>
       <c r="F17" t="n">
         <v>238200</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49815940856934</v>
+        <v>15.49815845489502</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52527051261252</v>
+        <v>15.52526955726993</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209753189668</v>
+        <v>14.99209660936272</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15476070887956</v>
+        <v>15.15475977633618</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -812,16 +812,16 @@
         <v>43802</v>
       </c>
       <c r="B20" t="n">
-        <v>15.81444931030273</v>
+        <v>15.81444835662842</v>
       </c>
       <c r="C20" t="n">
-        <v>15.92289200683133</v>
+        <v>15.92289104661748</v>
       </c>
       <c r="D20" t="n">
-        <v>15.29935037997784</v>
+        <v>15.29934945736604</v>
       </c>
       <c r="E20" t="n">
-        <v>15.48912294435515</v>
+        <v>15.4891220102993</v>
       </c>
       <c r="F20" t="n">
         <v>976200</v>
@@ -872,16 +872,16 @@
         <v>43805</v>
       </c>
       <c r="B23" t="n">
-        <v>16.19399261474609</v>
+        <v>16.19399452209473</v>
       </c>
       <c r="C23" t="n">
-        <v>16.48317077728191</v>
+        <v>16.48317271869031</v>
       </c>
       <c r="D23" t="n">
-        <v>16.13977214018008</v>
+        <v>16.13977404114256</v>
       </c>
       <c r="E23" t="n">
-        <v>16.44702436878384</v>
+        <v>16.44702630593487</v>
       </c>
       <c r="F23" t="n">
         <v>1067700</v>
@@ -1112,16 +1112,16 @@
         <v>43825</v>
       </c>
       <c r="B35" t="n">
-        <v>16.51932144165039</v>
+        <v>16.51931953430176</v>
       </c>
       <c r="C35" t="n">
-        <v>16.59161599336631</v>
+        <v>16.59161407767043</v>
       </c>
       <c r="D35" t="n">
-        <v>16.37473233821854</v>
+        <v>16.37473044756441</v>
       </c>
       <c r="E35" t="n">
-        <v>16.59161599336631</v>
+        <v>16.59161407767043</v>
       </c>
       <c r="F35" t="n">
         <v>1111500</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739356994629</v>
+        <v>16.53739166259766</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872515501472</v>
+        <v>16.61872323828566</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821536687546</v>
+        <v>16.24821349287934</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872515501472</v>
+        <v>16.61872323828566</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -34452,19 +34452,39 @@
         <v>46273</v>
       </c>
       <c r="B1702" t="n">
-        <v>9.359999999999999</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="C1702" t="n">
-        <v>9.56</v>
+        <v>9.560000419616699</v>
       </c>
       <c r="D1702" t="n">
-        <v>9.32</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="E1702" t="n">
-        <v>9.41</v>
+        <v>9.409999847412109</v>
       </c>
       <c r="F1702" t="n">
         <v>6635600</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1703" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="C1703" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>6444200</v>
       </c>
     </row>
   </sheetData>

--- a/database/CEAB3.xlsx
+++ b/database/CEAB3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1703"/>
+  <dimension ref="A1:F1704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>43775</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1307373046875</v>
+        <v>16.13073921203613</v>
       </c>
       <c r="C3" t="n">
-        <v>16.32050985334077</v>
+        <v>16.3205117831287</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94096303239619</v>
+        <v>15.94096491730532</v>
       </c>
       <c r="E3" t="n">
-        <v>16.26628937138813</v>
+        <v>16.26629129476486</v>
       </c>
       <c r="F3" t="n">
         <v>1352600</v>
@@ -492,16 +492,16 @@
         <v>43776</v>
       </c>
       <c r="B4" t="n">
-        <v>15.99518489837646</v>
+        <v>15.99518585205078</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13073696219904</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48008429802985</v>
+        <v>15.48008522099254</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13073696219904</v>
+        <v>16.13073792395533</v>
       </c>
       <c r="F4" t="n">
         <v>2452400</v>
@@ -772,16 +772,16 @@
         <v>43798</v>
       </c>
       <c r="B18" t="n">
-        <v>15.14572238922119</v>
+        <v>15.14572143554688</v>
       </c>
       <c r="C18" t="n">
-        <v>15.18186880124062</v>
+        <v>15.18186784529029</v>
       </c>
       <c r="D18" t="n">
-        <v>14.71195510316014</v>
+        <v>14.71195417679867</v>
       </c>
       <c r="E18" t="n">
-        <v>15.00113329386751</v>
+        <v>15.00113234929747</v>
       </c>
       <c r="F18" t="n">
         <v>377300</v>
@@ -792,16 +792,16 @@
         <v>43801</v>
       </c>
       <c r="B19" t="n">
-        <v>15.49815845489502</v>
+        <v>15.4981575012207</v>
       </c>
       <c r="C19" t="n">
-        <v>15.52526955726993</v>
+        <v>15.52526860192735</v>
       </c>
       <c r="D19" t="n">
-        <v>14.99209660936272</v>
+        <v>14.99209568682876</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15475977633618</v>
+        <v>15.15475884379279</v>
       </c>
       <c r="F19" t="n">
         <v>881700</v>
@@ -832,16 +832,16 @@
         <v>43803</v>
       </c>
       <c r="B21" t="n">
-        <v>16.1036262512207</v>
+        <v>16.10362434387207</v>
       </c>
       <c r="C21" t="n">
-        <v>16.19399487051062</v>
+        <v>16.19399295245853</v>
       </c>
       <c r="D21" t="n">
-        <v>15.74215349769909</v>
+        <v>15.74215163316408</v>
       </c>
       <c r="E21" t="n">
-        <v>16.04036873480918</v>
+        <v>16.0403668349529</v>
       </c>
       <c r="F21" t="n">
         <v>976000</v>
@@ -932,16 +932,16 @@
         <v>43810</v>
       </c>
       <c r="B26" t="n">
-        <v>17.48626327514648</v>
+        <v>17.48626136779785</v>
       </c>
       <c r="C26" t="n">
-        <v>17.84773606593138</v>
+        <v>17.84773411915439</v>
       </c>
       <c r="D26" t="n">
-        <v>16.92597915670124</v>
+        <v>16.9259773104667</v>
       </c>
       <c r="E26" t="n">
-        <v>16.98020136804764</v>
+        <v>16.98019951589871</v>
       </c>
       <c r="F26" t="n">
         <v>2363200</v>
@@ -952,16 +952,16 @@
         <v>43811</v>
       </c>
       <c r="B27" t="n">
-        <v>17.3055248260498</v>
+        <v>17.30552291870117</v>
       </c>
       <c r="C27" t="n">
-        <v>17.82966076749858</v>
+        <v>17.82965880238169</v>
       </c>
       <c r="D27" t="n">
-        <v>17.17900978889814</v>
+        <v>17.1790078954935</v>
       </c>
       <c r="E27" t="n">
-        <v>17.66699759193894</v>
+        <v>17.66699564475017</v>
       </c>
       <c r="F27" t="n">
         <v>1801300</v>
@@ -1052,16 +1052,16 @@
         <v>43818</v>
       </c>
       <c r="B32" t="n">
-        <v>16.40184211730957</v>
+        <v>16.40184020996094</v>
       </c>
       <c r="C32" t="n">
-        <v>16.59161639745967</v>
+        <v>16.59161446804244</v>
       </c>
       <c r="D32" t="n">
-        <v>16.33858459847224</v>
+        <v>16.33858269847974</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35665866775094</v>
+        <v>16.35665676565663</v>
       </c>
       <c r="F32" t="n">
         <v>961700</v>
@@ -1072,16 +1072,16 @@
         <v>43819</v>
       </c>
       <c r="B33" t="n">
-        <v>16.28436279296875</v>
+        <v>16.28436088562012</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51932050361312</v>
+        <v>16.51931856874445</v>
       </c>
       <c r="D33" t="n">
-        <v>15.81444737168</v>
+        <v>15.81444551937144</v>
       </c>
       <c r="E33" t="n">
-        <v>16.40184078647195</v>
+        <v>16.4018388653634</v>
       </c>
       <c r="F33" t="n">
         <v>984600</v>
@@ -1132,16 +1132,16 @@
         <v>43826</v>
       </c>
       <c r="B36" t="n">
-        <v>16.53739166259766</v>
+        <v>16.53739356994629</v>
       </c>
       <c r="C36" t="n">
-        <v>16.61872323828566</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="D36" t="n">
-        <v>16.24821349287934</v>
+        <v>16.24821536687546</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61872323828566</v>
+        <v>16.61872515501472</v>
       </c>
       <c r="F36" t="n">
         <v>1050700</v>
@@ -1152,16 +1152,16 @@
         <v>43829</v>
       </c>
       <c r="B37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="C37" t="n">
-        <v>16.73620643793902</v>
+        <v>16.73620446892584</v>
       </c>
       <c r="D37" t="n">
-        <v>16.21207046508789</v>
+        <v>16.21206855773926</v>
       </c>
       <c r="E37" t="n">
-        <v>16.71813236765218</v>
+        <v>16.71813040076541</v>
       </c>
       <c r="F37" t="n">
         <v>1191300</v>
@@ -1192,16 +1192,16 @@
         <v>43833</v>
       </c>
       <c r="B39" t="n">
-        <v>16.49941253662109</v>
+        <v>16.49941062927246</v>
       </c>
       <c r="C39" t="n">
-        <v>16.67357349182081</v>
+        <v>16.673571564339</v>
       </c>
       <c r="D39" t="n">
-        <v>16.20608992681567</v>
+        <v>16.20608805337542</v>
       </c>
       <c r="E39" t="n">
-        <v>16.22442302701367</v>
+        <v>16.22442115145411</v>
       </c>
       <c r="F39" t="n">
         <v>1551100</v>
@@ -1212,16 +1212,16 @@
         <v>43836</v>
       </c>
       <c r="B40" t="n">
-        <v>16.32525253295898</v>
+        <v>16.32525062561035</v>
       </c>
       <c r="C40" t="n">
-        <v>16.5819107056687</v>
+        <v>16.58190876833361</v>
       </c>
       <c r="D40" t="n">
-        <v>16.3160859823257</v>
+        <v>16.31608407604803</v>
       </c>
       <c r="E40" t="n">
-        <v>16.49941349830989</v>
+        <v>16.49941157061329</v>
       </c>
       <c r="F40" t="n">
         <v>970100</v>
@@ -1272,16 +1272,16 @@
         <v>43839</v>
       </c>
       <c r="B43" t="n">
-        <v>14.40032005310059</v>
+        <v>14.4003210067749</v>
       </c>
       <c r="C43" t="n">
-        <v>15.28945527034375</v>
+        <v>15.28945628290185</v>
       </c>
       <c r="D43" t="n">
-        <v>14.30865630420819</v>
+        <v>14.30865725181199</v>
       </c>
       <c r="E43" t="n">
-        <v>15.09696122283566</v>
+        <v>15.09696222264567</v>
       </c>
       <c r="F43" t="n">
         <v>3315800</v>
@@ -1332,16 +1332,16 @@
         <v>43844</v>
       </c>
       <c r="B46" t="n">
-        <v>15.7202730178833</v>
+        <v>15.72027206420898</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74777266775395</v>
+        <v>15.74777171241136</v>
       </c>
       <c r="D46" t="n">
-        <v>15.2436229101692</v>
+        <v>15.24362198541098</v>
       </c>
       <c r="E46" t="n">
-        <v>15.35361976131116</v>
+        <v>15.35361882987996</v>
       </c>
       <c r="F46" t="n">
         <v>2831800</v>
@@ -1352,16 +1352,16 @@
         <v>43845</v>
       </c>
       <c r="B47" t="n">
-        <v>15.76610469818115</v>
+        <v>15.76610565185547</v>
       </c>
       <c r="C47" t="n">
-        <v>15.76610469818115</v>
+        <v>15.76610565185547</v>
       </c>
       <c r="D47" t="n">
-        <v>15.3536187198054</v>
+        <v>15.35361964852889</v>
       </c>
       <c r="E47" t="n">
-        <v>15.72027195150578</v>
+        <v>15.72027290240772</v>
       </c>
       <c r="F47" t="n">
         <v>1838000</v>
@@ -1372,16 +1372,16 @@
         <v>43846</v>
       </c>
       <c r="B48" t="n">
-        <v>16.10525703430176</v>
+        <v>16.10525894165039</v>
       </c>
       <c r="C48" t="n">
-        <v>16.34358205353058</v>
+        <v>16.34358398910408</v>
       </c>
       <c r="D48" t="n">
-        <v>15.56444290380952</v>
+        <v>15.56444474710943</v>
       </c>
       <c r="E48" t="n">
-        <v>15.76610347687872</v>
+        <v>15.76610534406134</v>
       </c>
       <c r="F48" t="n">
         <v>3608000</v>
@@ -1392,16 +1392,16 @@
         <v>43847</v>
       </c>
       <c r="B49" t="n">
-        <v>16.31608581542969</v>
+        <v>16.31608390808105</v>
       </c>
       <c r="C49" t="n">
-        <v>16.31608581542969</v>
+        <v>16.31608390808105</v>
       </c>
       <c r="D49" t="n">
-        <v>15.93109943447349</v>
+        <v>15.93109757212972</v>
       </c>
       <c r="E49" t="n">
-        <v>16.22442380671596</v>
+        <v>16.2244219100826</v>
       </c>
       <c r="F49" t="n">
         <v>2719000</v>
@@ -1492,16 +1492,16 @@
         <v>43854</v>
       </c>
       <c r="B54" t="n">
-        <v>15.73860645294189</v>
+        <v>15.73860740661621</v>
       </c>
       <c r="C54" t="n">
-        <v>15.80277055566578</v>
+        <v>15.80277151322809</v>
       </c>
       <c r="D54" t="n">
-        <v>15.39945109067764</v>
+        <v>15.39945202380098</v>
       </c>
       <c r="E54" t="n">
-        <v>15.57361204688581</v>
+        <v>15.57361299056236</v>
       </c>
       <c r="F54" t="n">
         <v>887500</v>
@@ -1552,16 +1552,16 @@
         <v>43859</v>
       </c>
       <c r="B57" t="n">
-        <v>15.21612453460693</v>
+        <v>15.21612548828125</v>
       </c>
       <c r="C57" t="n">
-        <v>15.64694187911524</v>
+        <v>15.64694285979114</v>
       </c>
       <c r="D57" t="n">
-        <v>15.16112698491963</v>
+        <v>15.16112793514696</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4086168326828</v>
+        <v>15.40861779842162</v>
       </c>
       <c r="F57" t="n">
         <v>686700</v>
@@ -1592,16 +1592,16 @@
         <v>43861</v>
       </c>
       <c r="B59" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C59" t="n">
-        <v>15.21612414517745</v>
+        <v>15.21612513461457</v>
       </c>
       <c r="D59" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="E59" t="n">
-        <v>14.94113290709765</v>
+        <v>14.94113387865332</v>
       </c>
       <c r="F59" t="n">
         <v>897400</v>
@@ -1612,16 +1612,16 @@
         <v>43864</v>
       </c>
       <c r="B60" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C60" t="n">
-        <v>15.01446355425082</v>
+        <v>15.01446453057486</v>
       </c>
       <c r="D60" t="n">
-        <v>14.59281277020523</v>
+        <v>14.59281371911118</v>
       </c>
       <c r="E60" t="n">
-        <v>14.73030751507486</v>
+        <v>14.73030847292148</v>
       </c>
       <c r="F60" t="n">
         <v>1344600</v>
@@ -1632,16 +1632,16 @@
         <v>43865</v>
       </c>
       <c r="B61" t="n">
-        <v>14.92280197143555</v>
+        <v>14.92280292510986</v>
       </c>
       <c r="C61" t="n">
-        <v>15.03279707105302</v>
+        <v>15.03279803175682</v>
       </c>
       <c r="D61" t="n">
-        <v>14.6844769244769</v>
+        <v>14.68447786292053</v>
       </c>
       <c r="E61" t="n">
-        <v>14.92280197143555</v>
+        <v>14.92280292510986</v>
       </c>
       <c r="F61" t="n">
         <v>708300</v>
@@ -1752,16 +1752,16 @@
         <v>43873</v>
       </c>
       <c r="B67" t="n">
-        <v>14.6661434173584</v>
+        <v>14.66614437103271</v>
       </c>
       <c r="C67" t="n">
-        <v>14.757807163385</v>
+        <v>14.7578081230198</v>
       </c>
       <c r="D67" t="n">
-        <v>14.29949018159255</v>
+        <v>14.29949111142503</v>
       </c>
       <c r="E67" t="n">
-        <v>14.29949018159255</v>
+        <v>14.29949111142503</v>
       </c>
       <c r="F67" t="n">
         <v>2320900</v>
@@ -1832,16 +1832,16 @@
         <v>43879</v>
       </c>
       <c r="B71" t="n">
-        <v>15.48194694519043</v>
+        <v>15.48194789886475</v>
       </c>
       <c r="C71" t="n">
-        <v>15.57361069038642</v>
+        <v>15.57361164970714</v>
       </c>
       <c r="D71" t="n">
-        <v>14.48281666823953</v>
+        <v>14.4828175603683</v>
       </c>
       <c r="E71" t="n">
-        <v>14.64781018575394</v>
+        <v>14.64781108804616</v>
       </c>
       <c r="F71" t="n">
         <v>4553800</v>
@@ -1892,16 +1892,16 @@
         <v>43882</v>
       </c>
       <c r="B74" t="n">
-        <v>16.04109573364258</v>
+        <v>16.04109382629395</v>
       </c>
       <c r="C74" t="n">
-        <v>16.04109573364258</v>
+        <v>16.04109382629395</v>
       </c>
       <c r="D74" t="n">
-        <v>15.43611740584103</v>
+        <v>15.43611557042667</v>
       </c>
       <c r="E74" t="n">
-        <v>15.63777626566132</v>
+        <v>15.63777440626894</v>
       </c>
       <c r="F74" t="n">
         <v>1940300</v>
@@ -1932,16 +1932,16 @@
         <v>43888</v>
       </c>
       <c r="B76" t="n">
-        <v>14.47365188598633</v>
+        <v>14.47365093231201</v>
       </c>
       <c r="C76" t="n">
-        <v>14.88613704138841</v>
+        <v>14.88613606053529</v>
       </c>
       <c r="D76" t="n">
-        <v>14.09783205830509</v>
+        <v>14.09783112939368</v>
       </c>
       <c r="E76" t="n">
-        <v>14.56531564237362</v>
+        <v>14.56531468265955</v>
       </c>
       <c r="F76" t="n">
         <v>1056800</v>
@@ -2032,16 +2032,16 @@
         <v>43895</v>
       </c>
       <c r="B81" t="n">
-        <v>13.29119396209717</v>
+        <v>13.29119300842285</v>
       </c>
       <c r="C81" t="n">
-        <v>14.68447816255327</v>
+        <v>14.68447710890754</v>
       </c>
       <c r="D81" t="n">
-        <v>13.22702985718708</v>
+        <v>13.22702890811669</v>
       </c>
       <c r="E81" t="n">
-        <v>14.62031318347281</v>
+        <v>14.62031213443108</v>
       </c>
       <c r="F81" t="n">
         <v>2239700</v>
@@ -2172,16 +2172,16 @@
         <v>43906</v>
       </c>
       <c r="B88" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="C88" t="n">
-        <v>8.918848503012144</v>
+        <v>8.918849065390972</v>
       </c>
       <c r="D88" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="E88" t="n">
-        <v>8.918848503012144</v>
+        <v>8.918849065390972</v>
       </c>
       <c r="F88" t="n">
         <v>1319600</v>
@@ -2252,16 +2252,16 @@
         <v>43910</v>
       </c>
       <c r="B92" t="n">
-        <v>5.820626258850098</v>
+        <v>5.820625782012939</v>
       </c>
       <c r="C92" t="n">
-        <v>6.508101811558814</v>
+        <v>6.508101278402306</v>
       </c>
       <c r="D92" t="n">
-        <v>5.756462153665136</v>
+        <v>5.756461682084427</v>
       </c>
       <c r="E92" t="n">
-        <v>6.278943293989242</v>
+        <v>6.27894277960585</v>
       </c>
       <c r="F92" t="n">
         <v>2218000</v>
@@ -2332,16 +2332,16 @@
         <v>43916</v>
       </c>
       <c r="B96" t="n">
-        <v>6.874755382537842</v>
+        <v>6.874754905700684</v>
       </c>
       <c r="C96" t="n">
-        <v>7.653894675560271</v>
+        <v>7.653894144681544</v>
       </c>
       <c r="D96" t="n">
-        <v>6.29727582550422</v>
+        <v>6.297275388721391</v>
       </c>
       <c r="E96" t="n">
-        <v>6.471436347645401</v>
+        <v>6.471435898782693</v>
       </c>
       <c r="F96" t="n">
         <v>4787500</v>
@@ -2432,16 +2432,16 @@
         <v>43923</v>
       </c>
       <c r="B101" t="n">
-        <v>5.536469459533691</v>
+        <v>5.536468982696533</v>
       </c>
       <c r="C101" t="n">
-        <v>5.793127178086285</v>
+        <v>5.793126679144077</v>
       </c>
       <c r="D101" t="n">
-        <v>5.334810166952138</v>
+        <v>5.334809707483203</v>
       </c>
       <c r="E101" t="n">
-        <v>5.408140818799975</v>
+        <v>5.408140353015323</v>
       </c>
       <c r="F101" t="n">
         <v>2769000</v>
@@ -2452,16 +2452,16 @@
         <v>43924</v>
       </c>
       <c r="B102" t="n">
-        <v>5.582301139831543</v>
+        <v>5.582300662994385</v>
       </c>
       <c r="C102" t="n">
-        <v>5.71062977606757</v>
+        <v>5.710629288268649</v>
       </c>
       <c r="D102" t="n">
-        <v>5.068986157802285</v>
+        <v>5.068985724812216</v>
       </c>
       <c r="E102" t="n">
-        <v>5.609799914768118</v>
+        <v>5.609799435582029</v>
       </c>
       <c r="F102" t="n">
         <v>3057300</v>
@@ -2492,16 +2492,16 @@
         <v>43928</v>
       </c>
       <c r="B104" t="n">
-        <v>7.342238426208496</v>
+        <v>7.342238903045654</v>
       </c>
       <c r="C104" t="n">
-        <v>7.846387292556186</v>
+        <v>7.846387802134982</v>
       </c>
       <c r="D104" t="n">
-        <v>6.608931063718246</v>
+        <v>6.608931492931209</v>
       </c>
       <c r="E104" t="n">
-        <v>6.773925023590238</v>
+        <v>6.773925463518632</v>
       </c>
       <c r="F104" t="n">
         <v>4216400</v>
@@ -2532,16 +2532,16 @@
         <v>43930</v>
       </c>
       <c r="B106" t="n">
-        <v>7.883052349090576</v>
+        <v>7.883052825927734</v>
       </c>
       <c r="C106" t="n">
-        <v>8.653024135661383</v>
+        <v>8.653024659073285</v>
       </c>
       <c r="D106" t="n">
-        <v>7.718057957740275</v>
+        <v>7.718058424597103</v>
       </c>
       <c r="E106" t="n">
-        <v>8.121376512610697</v>
+        <v>8.12137700386382</v>
       </c>
       <c r="F106" t="n">
         <v>2853400</v>
@@ -2672,16 +2672,16 @@
         <v>43943</v>
       </c>
       <c r="B113" t="n">
-        <v>8.983012199401855</v>
+        <v>8.983013153076172</v>
       </c>
       <c r="C113" t="n">
-        <v>9.28550130988736</v>
+        <v>9.285502295675192</v>
       </c>
       <c r="D113" t="n">
-        <v>8.57052712820982</v>
+        <v>8.570528038092988</v>
       </c>
       <c r="E113" t="n">
-        <v>8.579692802641055</v>
+        <v>8.57969371349729</v>
       </c>
       <c r="F113" t="n">
         <v>2037400</v>
@@ -2732,16 +2732,16 @@
         <v>43948</v>
       </c>
       <c r="B116" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C116" t="n">
-        <v>7.947216534214704</v>
+        <v>7.947217050986978</v>
       </c>
       <c r="D116" t="n">
-        <v>7.296406385102614</v>
+        <v>7.296406859555589</v>
       </c>
       <c r="E116" t="n">
-        <v>7.928883435341277</v>
+        <v>7.928883950921431</v>
       </c>
       <c r="F116" t="n">
         <v>2360400</v>
@@ -2772,16 +2772,16 @@
         <v>43950</v>
       </c>
       <c r="B118" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C118" t="n">
-        <v>9.166340069149538</v>
+        <v>9.166339110682868</v>
       </c>
       <c r="D118" t="n">
-        <v>8.258872612104607</v>
+        <v>8.258871748526117</v>
       </c>
       <c r="E118" t="n">
-        <v>8.442199238653536</v>
+        <v>8.442198355905731</v>
       </c>
       <c r="F118" t="n">
         <v>3867700</v>
@@ -2852,16 +2852,16 @@
         <v>43957</v>
       </c>
       <c r="B122" t="n">
-        <v>7.828054904937744</v>
+        <v>7.828054428100586</v>
       </c>
       <c r="C122" t="n">
-        <v>8.148877178372471</v>
+        <v>8.148876681992785</v>
       </c>
       <c r="D122" t="n">
-        <v>7.553064509732316</v>
+        <v>7.553064049645888</v>
       </c>
       <c r="E122" t="n">
-        <v>7.928884337705908</v>
+        <v>7.928883854726839</v>
       </c>
       <c r="F122" t="n">
         <v>2058000</v>
@@ -2912,16 +2912,16 @@
         <v>43962</v>
       </c>
       <c r="B125" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C125" t="n">
-        <v>7.058081369394968</v>
+        <v>7.058081870301661</v>
       </c>
       <c r="D125" t="n">
-        <v>6.700594244733439</v>
+        <v>6.700594720269542</v>
       </c>
       <c r="E125" t="n">
-        <v>7.058081369394968</v>
+        <v>7.058081870301661</v>
       </c>
       <c r="F125" t="n">
         <v>2505400</v>
@@ -2972,16 +2972,16 @@
         <v>43965</v>
       </c>
       <c r="B128" t="n">
-        <v>6.086450099945068</v>
+        <v>6.08644962310791</v>
       </c>
       <c r="C128" t="n">
-        <v>6.187279969987983</v>
+        <v>6.187279485251405</v>
       </c>
       <c r="D128" t="n">
-        <v>5.701463720767742</v>
+        <v>5.701463274091976</v>
       </c>
       <c r="E128" t="n">
-        <v>5.893956910356406</v>
+        <v>5.893956448599943</v>
       </c>
       <c r="F128" t="n">
         <v>4161800</v>
@@ -2992,16 +2992,16 @@
         <v>43966</v>
       </c>
       <c r="B129" t="n">
-        <v>6.049784183502197</v>
+        <v>6.049784660339355</v>
       </c>
       <c r="C129" t="n">
-        <v>6.645596358206725</v>
+        <v>6.645596882005126</v>
       </c>
       <c r="D129" t="n">
-        <v>5.857291012642501</v>
+        <v>5.857291474307565</v>
       </c>
       <c r="E129" t="n">
-        <v>6.049784183502197</v>
+        <v>6.049784660339355</v>
       </c>
       <c r="F129" t="n">
         <v>4143200</v>
@@ -3012,16 +3012,16 @@
         <v>43969</v>
       </c>
       <c r="B130" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C130" t="n">
-        <v>6.856422193632849</v>
+        <v>6.856422675624999</v>
       </c>
       <c r="D130" t="n">
-        <v>6.260610018716203</v>
+        <v>6.260610458824003</v>
       </c>
       <c r="E130" t="n">
-        <v>6.462269739252984</v>
+        <v>6.46227019353704</v>
       </c>
       <c r="F130" t="n">
         <v>4121800</v>
@@ -3032,16 +3032,16 @@
         <v>43970</v>
       </c>
       <c r="B131" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C131" t="n">
-        <v>7.553063650138711</v>
+        <v>7.55306414128097</v>
       </c>
       <c r="D131" t="n">
-        <v>6.709760770792116</v>
+        <v>6.709761207098126</v>
       </c>
       <c r="E131" t="n">
-        <v>6.828922853873451</v>
+        <v>6.828923297928043</v>
       </c>
       <c r="F131" t="n">
         <v>3759800</v>
@@ -3072,16 +3072,16 @@
         <v>43972</v>
       </c>
       <c r="B133" t="n">
-        <v>7.727224349975586</v>
+        <v>7.727224826812744</v>
       </c>
       <c r="C133" t="n">
-        <v>7.873885639674015</v>
+        <v>7.873886125561454</v>
       </c>
       <c r="D133" t="n">
-        <v>7.461400543854623</v>
+        <v>7.461401004288134</v>
       </c>
       <c r="E133" t="n">
-        <v>7.55306341283102</v>
+        <v>7.55306387892093</v>
       </c>
       <c r="F133" t="n">
         <v>2073000</v>
@@ -3112,16 +3112,16 @@
         <v>43976</v>
       </c>
       <c r="B135" t="n">
-        <v>7.75472354888916</v>
+        <v>7.754724025726318</v>
       </c>
       <c r="C135" t="n">
-        <v>7.828054197763313</v>
+        <v>7.828054679109565</v>
       </c>
       <c r="D135" t="n">
-        <v>7.397235979999946</v>
+        <v>7.39723643485523</v>
       </c>
       <c r="E135" t="n">
-        <v>7.397235979999946</v>
+        <v>7.39723643485523</v>
       </c>
       <c r="F135" t="n">
         <v>2073000</v>
@@ -3132,16 +3132,16 @@
         <v>43977</v>
       </c>
       <c r="B136" t="n">
-        <v>7.626394271850586</v>
+        <v>7.626394748687744</v>
       </c>
       <c r="C136" t="n">
-        <v>8.286370968197739</v>
+        <v>8.286371486299668</v>
       </c>
       <c r="D136" t="n">
-        <v>7.608062047208583</v>
+        <v>7.608062522899527</v>
       </c>
       <c r="E136" t="n">
-        <v>7.974715281751298</v>
+        <v>7.974715780367084</v>
       </c>
       <c r="F136" t="n">
         <v>2630000</v>
@@ -3152,16 +3152,16 @@
         <v>43978</v>
       </c>
       <c r="B137" t="n">
-        <v>8.158042907714844</v>
+        <v>8.158041954040527</v>
       </c>
       <c r="C137" t="n">
-        <v>8.158042907714844</v>
+        <v>8.158041954040527</v>
       </c>
       <c r="D137" t="n">
-        <v>7.653894866426351</v>
+        <v>7.653893971686885</v>
       </c>
       <c r="E137" t="n">
-        <v>7.745557749310453</v>
+        <v>7.745556843855605</v>
       </c>
       <c r="F137" t="n">
         <v>2323900</v>
@@ -3212,16 +3212,16 @@
         <v>43983</v>
       </c>
       <c r="B140" t="n">
-        <v>8.955513954162598</v>
+        <v>8.955514907836914</v>
       </c>
       <c r="C140" t="n">
-        <v>9.065509921334565</v>
+        <v>9.065510886722372</v>
       </c>
       <c r="D140" t="n">
-        <v>8.56136108283537</v>
+        <v>8.561361994536275</v>
       </c>
       <c r="E140" t="n">
-        <v>8.662190500867112</v>
+        <v>8.662191423305361</v>
       </c>
       <c r="F140" t="n">
         <v>3007600</v>
@@ -3332,16 +3332,16 @@
         <v>43991</v>
       </c>
       <c r="B146" t="n">
-        <v>11.93457508087158</v>
+        <v>11.93457412719727</v>
       </c>
       <c r="C146" t="n">
-        <v>12.34706020539017</v>
+        <v>12.34705921875477</v>
       </c>
       <c r="D146" t="n">
-        <v>11.0546064072858</v>
+        <v>11.05460552392848</v>
       </c>
       <c r="E146" t="n">
-        <v>11.27459835713967</v>
+        <v>11.27459745620312</v>
       </c>
       <c r="F146" t="n">
         <v>3964300</v>
@@ -3612,16 +3612,16 @@
         <v>44012</v>
       </c>
       <c r="B160" t="n">
-        <v>9.450497627258301</v>
+        <v>9.450496673583984</v>
       </c>
       <c r="C160" t="n">
-        <v>9.633824266054166</v>
+        <v>9.633823293879882</v>
       </c>
       <c r="D160" t="n">
-        <v>9.120508803255376</v>
+        <v>9.120507882881091</v>
       </c>
       <c r="E160" t="n">
-        <v>9.532993959088664</v>
+        <v>9.532992997089428</v>
       </c>
       <c r="F160" t="n">
         <v>4221600</v>
@@ -3732,16 +3732,16 @@
         <v>44020</v>
       </c>
       <c r="B166" t="n">
-        <v>10.19297122955322</v>
+        <v>10.19297027587891</v>
       </c>
       <c r="C166" t="n">
-        <v>10.94461092232337</v>
+        <v>10.94460989832417</v>
       </c>
       <c r="D166" t="n">
-        <v>10.14713934907861</v>
+        <v>10.14713839969241</v>
       </c>
       <c r="E166" t="n">
-        <v>10.77045082552434</v>
+        <v>10.7704498178199</v>
       </c>
       <c r="F166" t="n">
         <v>5151100</v>
@@ -3792,16 +3792,16 @@
         <v>44025</v>
       </c>
       <c r="B169" t="n">
-        <v>10.50462627410889</v>
+        <v>10.50462532043457</v>
       </c>
       <c r="C169" t="n">
-        <v>11.09127238227016</v>
+        <v>11.09127137533651</v>
       </c>
       <c r="D169" t="n">
-        <v>10.32129963848672</v>
+        <v>10.32129870145592</v>
       </c>
       <c r="E169" t="n">
-        <v>10.8896126460006</v>
+        <v>10.88961165737486</v>
       </c>
       <c r="F169" t="n">
         <v>4409000</v>
@@ -3932,16 +3932,16 @@
         <v>44034</v>
       </c>
       <c r="B176" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C176" t="n">
-        <v>10.00047677558407</v>
+        <v>10.00047581575137</v>
       </c>
       <c r="D176" t="n">
-        <v>9.67965540087379</v>
+        <v>9.679654471833102</v>
       </c>
       <c r="E176" t="n">
-        <v>9.881314250976148</v>
+        <v>9.881313302580509</v>
       </c>
       <c r="F176" t="n">
         <v>2365200</v>
@@ -3952,16 +3952,16 @@
         <v>44035</v>
       </c>
       <c r="B177" t="n">
-        <v>9.771317481994629</v>
+        <v>9.771318435668945</v>
       </c>
       <c r="C177" t="n">
-        <v>10.10130625383415</v>
+        <v>10.10130723971515</v>
       </c>
       <c r="D177" t="n">
-        <v>9.670488065138237</v>
+        <v>9.670489008971668</v>
       </c>
       <c r="E177" t="n">
-        <v>9.982143738911011</v>
+        <v>9.982144713161835</v>
       </c>
       <c r="F177" t="n">
         <v>2784800</v>
@@ -3972,16 +3972,16 @@
         <v>44036</v>
       </c>
       <c r="B178" t="n">
-        <v>9.578825950622559</v>
+        <v>9.578824996948242</v>
       </c>
       <c r="C178" t="n">
-        <v>9.72548726339387</v>
+        <v>9.725486295117854</v>
       </c>
       <c r="D178" t="n">
-        <v>9.193839567512681</v>
+        <v>9.193838652167866</v>
       </c>
       <c r="E178" t="n">
-        <v>9.652156607008214</v>
+        <v>9.652155646033048</v>
       </c>
       <c r="F178" t="n">
         <v>3085100</v>
@@ -4312,16 +4312,16 @@
         <v>44061</v>
       </c>
       <c r="B195" t="n">
-        <v>9.532992362976074</v>
+        <v>9.532993316650391</v>
       </c>
       <c r="C195" t="n">
-        <v>9.734652068972748</v>
+        <v>9.73465304282097</v>
       </c>
       <c r="D195" t="n">
-        <v>9.248836338961429</v>
+        <v>9.248837264208962</v>
       </c>
       <c r="E195" t="n">
-        <v>9.31300043325437</v>
+        <v>9.313001364920838</v>
       </c>
       <c r="F195" t="n">
         <v>3391400</v>
@@ -4352,16 +4352,16 @@
         <v>44063</v>
       </c>
       <c r="B197" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C197" t="n">
-        <v>9.945478824484717</v>
+        <v>9.945479787030456</v>
       </c>
       <c r="D197" t="n">
-        <v>9.010511764854147</v>
+        <v>9.010512636911677</v>
       </c>
       <c r="E197" t="n">
-        <v>9.074675862376543</v>
+        <v>9.074676740644019</v>
       </c>
       <c r="F197" t="n">
         <v>3999100</v>
@@ -4372,16 +4372,16 @@
         <v>44064</v>
       </c>
       <c r="B198" t="n">
-        <v>10.38546276092529</v>
+        <v>10.38546371459961</v>
       </c>
       <c r="C198" t="n">
-        <v>10.54129060502008</v>
+        <v>10.54129157300373</v>
       </c>
       <c r="D198" t="n">
-        <v>9.652155413568103</v>
+        <v>9.65215629990441</v>
       </c>
       <c r="E198" t="n">
-        <v>9.85381513077964</v>
+        <v>9.853816035633919</v>
       </c>
       <c r="F198" t="n">
         <v>4055100</v>
@@ -4392,16 +4392,16 @@
         <v>44067</v>
       </c>
       <c r="B199" t="n">
-        <v>10.22046947479248</v>
+        <v>10.22046852111816</v>
       </c>
       <c r="C199" t="n">
-        <v>10.74295148626354</v>
+        <v>10.7429504838363</v>
       </c>
       <c r="D199" t="n">
-        <v>10.16547192042944</v>
+        <v>10.16547097188696</v>
       </c>
       <c r="E199" t="n">
-        <v>10.54129174720154</v>
+        <v>10.54129076359123</v>
       </c>
       <c r="F199" t="n">
         <v>2579200</v>
@@ -4472,16 +4472,16 @@
         <v>44071</v>
       </c>
       <c r="B203" t="n">
-        <v>11.07293891906738</v>
+        <v>11.07293796539307</v>
       </c>
       <c r="C203" t="n">
-        <v>11.12793734503842</v>
+        <v>11.12793638662728</v>
       </c>
       <c r="D203" t="n">
-        <v>10.3579646264658</v>
+        <v>10.35796373436977</v>
       </c>
       <c r="E203" t="n">
-        <v>10.51379248018504</v>
+        <v>10.51379157466809</v>
       </c>
       <c r="F203" t="n">
         <v>2710200</v>
@@ -4512,16 +4512,16 @@
         <v>44075</v>
       </c>
       <c r="B205" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="C205" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="D205" t="n">
-        <v>10.96294209712684</v>
+        <v>10.96294298891299</v>
       </c>
       <c r="E205" t="n">
-        <v>11.14626871262991</v>
+        <v>11.14626961932886</v>
       </c>
       <c r="F205" t="n">
         <v>3676800</v>
@@ -4652,16 +4652,16 @@
         <v>44085</v>
       </c>
       <c r="B212" t="n">
-        <v>10.83461380004883</v>
+        <v>10.83461284637451</v>
       </c>
       <c r="C212" t="n">
-        <v>11.54958896263513</v>
+        <v>11.54958794602793</v>
       </c>
       <c r="D212" t="n">
-        <v>10.66962027144226</v>
+        <v>10.66961933229085</v>
       </c>
       <c r="E212" t="n">
-        <v>11.43959211133699</v>
+        <v>11.43959110441184</v>
       </c>
       <c r="F212" t="n">
         <v>2696500</v>
@@ -4692,16 +4692,16 @@
         <v>44089</v>
       </c>
       <c r="B214" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="C214" t="n">
-        <v>12.09956866086264</v>
+        <v>12.09956963671544</v>
       </c>
       <c r="D214" t="n">
-        <v>11.62291943402496</v>
+        <v>11.62292037143511</v>
       </c>
       <c r="E214" t="n">
-        <v>12.017071460752</v>
+        <v>12.01707242995125</v>
       </c>
       <c r="F214" t="n">
         <v>2177400</v>
@@ -4772,16 +4772,16 @@
         <v>44095</v>
       </c>
       <c r="B218" t="n">
-        <v>11.32043075561523</v>
+        <v>11.32042980194092</v>
       </c>
       <c r="C218" t="n">
-        <v>11.73291589921649</v>
+        <v>11.73291491079292</v>
       </c>
       <c r="D218" t="n">
-        <v>11.00877504181907</v>
+        <v>11.00877411439977</v>
       </c>
       <c r="E218" t="n">
-        <v>11.70541712275516</v>
+        <v>11.70541613664819</v>
       </c>
       <c r="F218" t="n">
         <v>2982400</v>
@@ -4872,16 +4872,16 @@
         <v>44102</v>
       </c>
       <c r="B223" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C223" t="n">
-        <v>11.44875714774106</v>
+        <v>11.44875814201422</v>
       </c>
       <c r="D223" t="n">
-        <v>10.86211201394924</v>
+        <v>10.8621129572749</v>
       </c>
       <c r="E223" t="n">
-        <v>11.39375960353318</v>
+        <v>11.39376059303005</v>
       </c>
       <c r="F223" t="n">
         <v>1430300</v>
@@ -4932,16 +4932,16 @@
         <v>44105</v>
       </c>
       <c r="B226" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C226" t="n">
-        <v>11.18293500609905</v>
+        <v>11.18293403814347</v>
       </c>
       <c r="D226" t="n">
-        <v>10.58712323547157</v>
+        <v>10.58712231908736</v>
       </c>
       <c r="E226" t="n">
-        <v>10.61462201164059</v>
+        <v>10.61462109287619</v>
       </c>
       <c r="F226" t="n">
         <v>1825000</v>
@@ -4992,16 +4992,16 @@
         <v>44110</v>
       </c>
       <c r="B229" t="n">
-        <v>11.03627395629883</v>
+        <v>11.03627300262451</v>
       </c>
       <c r="C229" t="n">
-        <v>11.35709622431771</v>
+        <v>11.35709524292028</v>
       </c>
       <c r="D229" t="n">
-        <v>10.99960862916841</v>
+        <v>10.99960767866245</v>
       </c>
       <c r="E229" t="n">
-        <v>11.35709622431771</v>
+        <v>11.35709524292028</v>
       </c>
       <c r="F229" t="n">
         <v>1315200</v>
@@ -5012,16 +5012,16 @@
         <v>44111</v>
       </c>
       <c r="B230" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C230" t="n">
-        <v>11.23793231185949</v>
+        <v>11.23793329027351</v>
       </c>
       <c r="D230" t="n">
-        <v>10.81628066458053</v>
+        <v>10.81628160628407</v>
       </c>
       <c r="E230" t="n">
-        <v>11.10043669638599</v>
+        <v>11.10043766282916</v>
       </c>
       <c r="F230" t="n">
         <v>1553900</v>
@@ -5032,16 +5032,16 @@
         <v>44112</v>
       </c>
       <c r="B231" t="n">
-        <v>11.03627395629883</v>
+        <v>11.03627300262451</v>
       </c>
       <c r="C231" t="n">
-        <v>11.09127238407963</v>
+        <v>11.09127142565275</v>
       </c>
       <c r="D231" t="n">
-        <v>10.83461421999638</v>
+        <v>10.83461328374802</v>
       </c>
       <c r="E231" t="n">
-        <v>10.99960862916841</v>
+        <v>10.99960767866245</v>
       </c>
       <c r="F231" t="n">
         <v>1563000</v>
@@ -5112,16 +5112,16 @@
         <v>44119</v>
       </c>
       <c r="B235" t="n">
-        <v>11.57708835601807</v>
+        <v>11.57708740234375</v>
       </c>
       <c r="C235" t="n">
-        <v>11.62292023414239</v>
+        <v>11.62291927669263</v>
       </c>
       <c r="D235" t="n">
-        <v>10.92627813432967</v>
+        <v>10.92627723426651</v>
       </c>
       <c r="E235" t="n">
-        <v>10.99960878966045</v>
+        <v>10.99960788355659</v>
       </c>
       <c r="F235" t="n">
         <v>4442200</v>
@@ -5232,16 +5232,16 @@
         <v>44127</v>
       </c>
       <c r="B241" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="C241" t="n">
-        <v>11.82457828521729</v>
+        <v>11.8245792388916</v>
       </c>
       <c r="D241" t="n">
-        <v>11.31126373323825</v>
+        <v>11.31126464551279</v>
       </c>
       <c r="E241" t="n">
-        <v>11.49459035894505</v>
+        <v>11.49459128600522</v>
       </c>
       <c r="F241" t="n">
         <v>1343300</v>
@@ -5272,16 +5272,16 @@
         <v>44131</v>
       </c>
       <c r="B243" t="n">
-        <v>11.90707588195801</v>
+        <v>11.90707492828369</v>
       </c>
       <c r="C243" t="n">
-        <v>12.45705665156882</v>
+        <v>12.45705565384485</v>
       </c>
       <c r="D243" t="n">
-        <v>11.77874767677373</v>
+        <v>11.77874673337762</v>
       </c>
       <c r="E243" t="n">
-        <v>12.20956504299285</v>
+        <v>12.20956406509125</v>
       </c>
       <c r="F243" t="n">
         <v>2061500</v>
@@ -5352,16 +5352,16 @@
         <v>44138</v>
       </c>
       <c r="B247" t="n">
-        <v>10.87127876281738</v>
+        <v>10.8712797164917</v>
       </c>
       <c r="C247" t="n">
-        <v>11.17376790836278</v>
+        <v>11.17376888857272</v>
       </c>
       <c r="D247" t="n">
-        <v>10.66961991523398</v>
+        <v>10.66962085121793</v>
       </c>
       <c r="E247" t="n">
-        <v>10.9996078356007</v>
+        <v>10.99960880053258</v>
       </c>
       <c r="F247" t="n">
         <v>2487500</v>
@@ -5492,16 +5492,16 @@
         <v>44147</v>
       </c>
       <c r="B254" t="n">
-        <v>11.6412525177002</v>
+        <v>11.64125156402588</v>
       </c>
       <c r="C254" t="n">
-        <v>12.54872003747481</v>
+        <v>12.54871900945897</v>
       </c>
       <c r="D254" t="n">
-        <v>11.62292029086322</v>
+        <v>11.62291933869072</v>
       </c>
       <c r="E254" t="n">
-        <v>12.54872003747481</v>
+        <v>12.54871900945897</v>
       </c>
       <c r="F254" t="n">
         <v>2275500</v>
@@ -5512,16 +5512,16 @@
         <v>44148</v>
       </c>
       <c r="B255" t="n">
-        <v>11.86124420166016</v>
+        <v>11.86124324798584</v>
       </c>
       <c r="C255" t="n">
-        <v>12.05373738679096</v>
+        <v>12.0537364176397</v>
       </c>
       <c r="D255" t="n">
-        <v>11.47625870556891</v>
+        <v>11.47625778284841</v>
       </c>
       <c r="E255" t="n">
-        <v>11.60458691287587</v>
+        <v>11.60458597983746</v>
       </c>
       <c r="F255" t="n">
         <v>1796700</v>
@@ -5572,16 +5572,16 @@
         <v>44153</v>
       </c>
       <c r="B258" t="n">
-        <v>12.64038276672363</v>
+        <v>12.64038372039795</v>
       </c>
       <c r="C258" t="n">
-        <v>12.76871184083297</v>
+        <v>12.76871280418928</v>
       </c>
       <c r="D258" t="n">
-        <v>12.31956051853545</v>
+        <v>12.31956144800481</v>
       </c>
       <c r="E258" t="n">
-        <v>12.57621866675412</v>
+        <v>12.57621961558747</v>
       </c>
       <c r="F258" t="n">
         <v>1757300</v>
@@ -5712,16 +5712,16 @@
         <v>44165</v>
       </c>
       <c r="B265" t="n">
-        <v>12.20956420898438</v>
+        <v>12.20956516265869</v>
       </c>
       <c r="C265" t="n">
-        <v>12.85120868775777</v>
+        <v>12.85120969155017</v>
       </c>
       <c r="D265" t="n">
-        <v>11.9712400409914</v>
+        <v>11.97124097605051</v>
       </c>
       <c r="E265" t="n">
-        <v>12.69538084281798</v>
+        <v>12.69538183443885</v>
       </c>
       <c r="F265" t="n">
         <v>1362800</v>
@@ -5732,16 +5732,16 @@
         <v>44166</v>
       </c>
       <c r="B266" t="n">
-        <v>12.13623428344727</v>
+        <v>12.13623332977295</v>
       </c>
       <c r="C266" t="n">
-        <v>12.38372588984487</v>
+        <v>12.38372491672248</v>
       </c>
       <c r="D266" t="n">
-        <v>12.05373708131473</v>
+        <v>12.05373613412311</v>
       </c>
       <c r="E266" t="n">
-        <v>12.32872746369974</v>
+        <v>12.32872649489916</v>
       </c>
       <c r="F266" t="n">
         <v>1296100</v>
@@ -5752,16 +5752,16 @@
         <v>44167</v>
       </c>
       <c r="B267" t="n">
-        <v>12.3837251663208</v>
+        <v>12.38372611999512</v>
       </c>
       <c r="C267" t="n">
-        <v>12.67704775750314</v>
+        <v>12.67704873376632</v>
       </c>
       <c r="D267" t="n">
-        <v>12.22789732121261</v>
+        <v>12.22789826288658</v>
       </c>
       <c r="E267" t="n">
-        <v>12.25539609559339</v>
+        <v>12.25539703938504</v>
       </c>
       <c r="F267" t="n">
         <v>1547700</v>
@@ -5852,16 +5852,16 @@
         <v>44174</v>
       </c>
       <c r="B272" t="n">
-        <v>12.05373668670654</v>
+        <v>12.05373764038086</v>
       </c>
       <c r="C272" t="n">
-        <v>12.30122828500191</v>
+        <v>12.30122925825741</v>
       </c>
       <c r="D272" t="n">
-        <v>11.87041006250829</v>
+        <v>11.87041100167807</v>
       </c>
       <c r="E272" t="n">
-        <v>12.27372950991475</v>
+        <v>12.27373048099458</v>
       </c>
       <c r="F272" t="n">
         <v>927800</v>
@@ -5892,16 +5892,16 @@
         <v>44176</v>
       </c>
       <c r="B274" t="n">
-        <v>12.05373668670654</v>
+        <v>12.05373764038086</v>
       </c>
       <c r="C274" t="n">
-        <v>12.35622583517624</v>
+        <v>12.35622681278306</v>
       </c>
       <c r="D274" t="n">
-        <v>11.96207381169257</v>
+        <v>11.96207475811465</v>
       </c>
       <c r="E274" t="n">
-        <v>12.15456698564331</v>
+        <v>12.15456794729517</v>
       </c>
       <c r="F274" t="n">
         <v>1470700</v>
@@ -5952,16 +5952,16 @@
         <v>44181</v>
       </c>
       <c r="B277" t="n">
-        <v>12.47538948059082</v>
+        <v>12.4753885269165</v>
       </c>
       <c r="C277" t="n">
-        <v>12.91537429237765</v>
+        <v>12.91537330506894</v>
       </c>
       <c r="D277" t="n">
-        <v>12.38372659733925</v>
+        <v>12.38372565067205</v>
       </c>
       <c r="E277" t="n">
-        <v>12.5578866874365</v>
+        <v>12.55788572745573</v>
       </c>
       <c r="F277" t="n">
         <v>1004500</v>
@@ -5992,16 +5992,16 @@
         <v>44183</v>
       </c>
       <c r="B279" t="n">
-        <v>12.19123363494873</v>
+        <v>12.19123268127441</v>
       </c>
       <c r="C279" t="n">
-        <v>12.51205504360741</v>
+        <v>12.51205406483644</v>
       </c>
       <c r="D279" t="n">
-        <v>12.08123764847972</v>
+        <v>12.08123670340998</v>
       </c>
       <c r="E279" t="n">
-        <v>12.31956184874404</v>
+        <v>12.31956088503109</v>
       </c>
       <c r="F279" t="n">
         <v>677600</v>
@@ -6112,16 +6112,16 @@
         <v>44195</v>
       </c>
       <c r="B285" t="n">
-        <v>11.81541156768799</v>
+        <v>11.8154125213623</v>
       </c>
       <c r="C285" t="n">
-        <v>12.05373572300648</v>
+        <v>12.05373669591699</v>
       </c>
       <c r="D285" t="n">
-        <v>11.77874624577974</v>
+        <v>11.77874719649464</v>
       </c>
       <c r="E285" t="n">
-        <v>11.91624098439311</v>
+        <v>11.91624194620582</v>
       </c>
       <c r="F285" t="n">
         <v>1061200</v>
@@ -6132,16 +6132,16 @@
         <v>44200</v>
       </c>
       <c r="B286" t="n">
-        <v>11.72374820709229</v>
+        <v>11.7237491607666</v>
       </c>
       <c r="C286" t="n">
-        <v>11.89790827327764</v>
+        <v>11.8979092411191</v>
       </c>
       <c r="D286" t="n">
-        <v>11.42125907296965</v>
+        <v>11.42126000203783</v>
       </c>
       <c r="E286" t="n">
-        <v>11.89790827327764</v>
+        <v>11.8979092411191</v>
       </c>
       <c r="F286" t="n">
         <v>1030900</v>
@@ -6152,16 +6152,16 @@
         <v>44201</v>
       </c>
       <c r="B287" t="n">
-        <v>11.26543140411377</v>
+        <v>11.26543235778809</v>
       </c>
       <c r="C287" t="n">
-        <v>11.73291493644768</v>
+        <v>11.73291592969678</v>
       </c>
       <c r="D287" t="n">
-        <v>11.16460198258245</v>
+        <v>11.16460292772106</v>
       </c>
       <c r="E287" t="n">
-        <v>11.73291493644768</v>
+        <v>11.73291592969678</v>
       </c>
       <c r="F287" t="n">
         <v>2157200</v>
@@ -6172,16 +6172,16 @@
         <v>44202</v>
       </c>
       <c r="B288" t="n">
-        <v>11.07293891906738</v>
+        <v>11.07293796539307</v>
       </c>
       <c r="C288" t="n">
-        <v>11.36626152645873</v>
+        <v>11.36626054752155</v>
       </c>
       <c r="D288" t="n">
-        <v>10.91711106534815</v>
+        <v>10.91711012509475</v>
       </c>
       <c r="E288" t="n">
-        <v>11.28376519875766</v>
+        <v>11.2837642269256</v>
       </c>
       <c r="F288" t="n">
         <v>1263500</v>
@@ -6232,16 +6232,16 @@
         <v>44207</v>
       </c>
       <c r="B291" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C291" t="n">
-        <v>11.13710201901154</v>
+        <v>11.13710298864692</v>
       </c>
       <c r="D291" t="n">
-        <v>10.83461288880819</v>
+        <v>10.83461383210779</v>
       </c>
       <c r="E291" t="n">
-        <v>11.04543914953279</v>
+        <v>11.04544011118768</v>
       </c>
       <c r="F291" t="n">
         <v>926700</v>
@@ -6272,16 +6272,16 @@
         <v>44209</v>
       </c>
       <c r="B293" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C293" t="n">
-        <v>10.98127437212461</v>
+        <v>10.98127533221018</v>
       </c>
       <c r="D293" t="n">
-        <v>10.67878523661001</v>
+        <v>10.67878617024915</v>
       </c>
       <c r="E293" t="n">
-        <v>10.8712784023166</v>
+        <v>10.87127935278529</v>
       </c>
       <c r="F293" t="n">
         <v>2157000</v>
@@ -6332,16 +6332,16 @@
         <v>44214</v>
       </c>
       <c r="B296" t="n">
-        <v>11.29293155670166</v>
+        <v>11.29293060302734</v>
       </c>
       <c r="C296" t="n">
-        <v>11.44875941983287</v>
+        <v>11.44875845299908</v>
       </c>
       <c r="D296" t="n">
-        <v>11.0454408103094</v>
+        <v>11.04543987753537</v>
       </c>
       <c r="E296" t="n">
-        <v>11.40292754111715</v>
+        <v>11.40292657815381</v>
       </c>
       <c r="F296" t="n">
         <v>2481600</v>
@@ -6412,16 +6412,16 @@
         <v>44218</v>
       </c>
       <c r="B300" t="n">
-        <v>11.00877475738525</v>
+        <v>11.00877571105957</v>
       </c>
       <c r="C300" t="n">
-        <v>11.19210138600805</v>
+        <v>11.19210235556369</v>
       </c>
       <c r="D300" t="n">
-        <v>10.82544812876246</v>
+        <v>10.82544906655545</v>
       </c>
       <c r="E300" t="n">
-        <v>11.09127195880809</v>
+        <v>11.09127291962902</v>
       </c>
       <c r="F300" t="n">
         <v>3052400</v>
@@ -6612,16 +6612,16 @@
         <v>44235</v>
       </c>
       <c r="B310" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C310" t="n">
-        <v>11.33876286134076</v>
+        <v>11.33876187989727</v>
       </c>
       <c r="D310" t="n">
-        <v>10.91711117201089</v>
+        <v>10.91711022706409</v>
       </c>
       <c r="E310" t="n">
-        <v>11.27459875888959</v>
+        <v>11.27459778299992</v>
       </c>
       <c r="F310" t="n">
         <v>1845700</v>
@@ -6792,16 +6792,16 @@
         <v>44250</v>
       </c>
       <c r="B319" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C319" t="n">
-        <v>10.99960747084441</v>
+        <v>10.99960843253283</v>
       </c>
       <c r="D319" t="n">
-        <v>10.55045704225246</v>
+        <v>10.55045796467195</v>
       </c>
       <c r="E319" t="n">
-        <v>10.67878523661001</v>
+        <v>10.67878617024915</v>
       </c>
       <c r="F319" t="n">
         <v>1964300</v>
@@ -6852,16 +6852,16 @@
         <v>44253</v>
       </c>
       <c r="B322" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C322" t="n">
-        <v>10.65128678074554</v>
+        <v>10.651287786344</v>
       </c>
       <c r="D322" t="n">
-        <v>9.945479068192968</v>
+        <v>9.945480007155426</v>
       </c>
       <c r="E322" t="n">
-        <v>10.60545490674777</v>
+        <v>10.6054559080192</v>
       </c>
       <c r="F322" t="n">
         <v>2794300</v>
@@ -6912,16 +6912,16 @@
         <v>44258</v>
       </c>
       <c r="B325" t="n">
-        <v>9.752985954284668</v>
+        <v>9.752986907958984</v>
       </c>
       <c r="C325" t="n">
-        <v>9.81715005375796</v>
+        <v>9.817151013706422</v>
       </c>
       <c r="D325" t="n">
-        <v>9.184672986201862</v>
+        <v>9.184673884304942</v>
       </c>
       <c r="E325" t="n">
-        <v>9.578825006899601</v>
+        <v>9.578825943543972</v>
       </c>
       <c r="F325" t="n">
         <v>2305100</v>
@@ -7032,16 +7032,16 @@
         <v>44266</v>
       </c>
       <c r="B331" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C331" t="n">
-        <v>10.24796821273983</v>
+        <v>10.24796918026058</v>
       </c>
       <c r="D331" t="n">
-        <v>9.322167679832035</v>
+        <v>9.32216855994705</v>
       </c>
       <c r="E331" t="n">
-        <v>9.404664878193957</v>
+        <v>9.404665766097615</v>
       </c>
       <c r="F331" t="n">
         <v>2921600</v>
@@ -7092,16 +7092,16 @@
         <v>44271</v>
       </c>
       <c r="B334" t="n">
-        <v>9.771317481994629</v>
+        <v>9.771318435668945</v>
       </c>
       <c r="C334" t="n">
-        <v>10.34879695854355</v>
+        <v>10.3487979685795</v>
       </c>
       <c r="D334" t="n">
-        <v>9.734652160031374</v>
+        <v>9.734653110127178</v>
       </c>
       <c r="E334" t="n">
-        <v>10.3121316365803</v>
+        <v>10.31213264303773</v>
       </c>
       <c r="F334" t="n">
         <v>1474300</v>
@@ -7152,16 +7152,16 @@
         <v>44274</v>
       </c>
       <c r="B337" t="n">
-        <v>9.972978591918945</v>
+        <v>9.972977638244629</v>
       </c>
       <c r="C337" t="n">
-        <v>10.10130767391647</v>
+        <v>10.10130670797058</v>
       </c>
       <c r="D337" t="n">
-        <v>9.679655974976443</v>
+        <v>9.679655049351345</v>
       </c>
       <c r="E337" t="n">
-        <v>9.826317283447693</v>
+        <v>9.826316343797988</v>
       </c>
       <c r="F337" t="n">
         <v>1607200</v>
@@ -7212,16 +7212,16 @@
         <v>44279</v>
       </c>
       <c r="B340" t="n">
-        <v>10.38546276092529</v>
+        <v>10.38546371459961</v>
       </c>
       <c r="C340" t="n">
-        <v>10.60545470288137</v>
+        <v>10.60545567675706</v>
       </c>
       <c r="D340" t="n">
-        <v>10.21130269208597</v>
+        <v>10.21130362976755</v>
       </c>
       <c r="E340" t="n">
-        <v>10.56878937922202</v>
+        <v>10.56879034973082</v>
       </c>
       <c r="F340" t="n">
         <v>3104200</v>
@@ -7272,16 +7272,16 @@
         <v>44284</v>
       </c>
       <c r="B343" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C343" t="n">
-        <v>10.06464047012052</v>
+        <v>10.06464144419899</v>
       </c>
       <c r="D343" t="n">
-        <v>9.734652558929284</v>
+        <v>9.734653501070783</v>
       </c>
       <c r="E343" t="n">
-        <v>10.04630824547281</v>
+        <v>10.04630921777704</v>
       </c>
       <c r="F343" t="n">
         <v>1233600</v>
@@ -7452,16 +7452,16 @@
         <v>44298</v>
       </c>
       <c r="B352" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C352" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="D352" t="n">
-        <v>10.69711763298518</v>
+        <v>10.69711856198182</v>
       </c>
       <c r="E352" t="n">
-        <v>10.87127768853708</v>
+        <v>10.87127863265874</v>
       </c>
       <c r="F352" t="n">
         <v>1341200</v>
@@ -7532,16 +7532,16 @@
         <v>44302</v>
       </c>
       <c r="B356" t="n">
-        <v>12.53955268859863</v>
+        <v>12.53955364227295</v>
       </c>
       <c r="C356" t="n">
-        <v>13.63951325138424</v>
+        <v>13.63951428871419</v>
       </c>
       <c r="D356" t="n">
-        <v>11.47625744876687</v>
+        <v>11.47625832157408</v>
       </c>
       <c r="E356" t="n">
-        <v>11.61375219130122</v>
+        <v>11.61375307456536</v>
       </c>
       <c r="F356" t="n">
         <v>14691000</v>
@@ -7592,16 +7592,16 @@
         <v>44308</v>
       </c>
       <c r="B359" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C359" t="n">
-        <v>11.41209182687907</v>
+        <v>11.41209281796801</v>
       </c>
       <c r="D359" t="n">
-        <v>10.91710955815712</v>
+        <v>10.91711050625907</v>
       </c>
       <c r="E359" t="n">
-        <v>11.26543054343111</v>
+        <v>11.26543152178318</v>
       </c>
       <c r="F359" t="n">
         <v>4817400</v>
@@ -7612,16 +7612,16 @@
         <v>44309</v>
       </c>
       <c r="B360" t="n">
-        <v>11.02710723876953</v>
+        <v>11.02710628509521</v>
       </c>
       <c r="C360" t="n">
-        <v>11.18293509525356</v>
+        <v>11.18293412810254</v>
       </c>
       <c r="D360" t="n">
-        <v>10.70628584978561</v>
+        <v>10.70628492385739</v>
       </c>
       <c r="E360" t="n">
-        <v>11.1462697686791</v>
+        <v>11.14626880469907</v>
       </c>
       <c r="F360" t="n">
         <v>3824500</v>
@@ -7672,16 +7672,16 @@
         <v>44314</v>
       </c>
       <c r="B363" t="n">
-        <v>11.20126724243164</v>
+        <v>11.20126819610596</v>
       </c>
       <c r="C363" t="n">
-        <v>11.30209666338853</v>
+        <v>11.30209762564745</v>
       </c>
       <c r="D363" t="n">
-        <v>10.9262768794389</v>
+        <v>10.92627780970057</v>
       </c>
       <c r="E363" t="n">
-        <v>11.18293414361933</v>
+        <v>11.18293509573277</v>
       </c>
       <c r="F363" t="n">
         <v>1629600</v>
@@ -7692,16 +7692,16 @@
         <v>44315</v>
       </c>
       <c r="B364" t="n">
-        <v>11.42125988006592</v>
+        <v>11.4212589263916</v>
       </c>
       <c r="C364" t="n">
-        <v>11.59541995855849</v>
+        <v>11.59541899034182</v>
       </c>
       <c r="D364" t="n">
-        <v>11.08210539887593</v>
+        <v>11.08210447352099</v>
       </c>
       <c r="E364" t="n">
-        <v>11.2196001516769</v>
+        <v>11.21959921484115</v>
       </c>
       <c r="F364" t="n">
         <v>1614300</v>
@@ -7892,16 +7892,16 @@
         <v>44329</v>
       </c>
       <c r="B374" t="n">
-        <v>11.16460227966309</v>
+        <v>11.16460132598877</v>
       </c>
       <c r="C374" t="n">
-        <v>11.43042610183743</v>
+        <v>11.43042512545659</v>
       </c>
       <c r="D374" t="n">
-        <v>11.10043730591735</v>
+        <v>11.10043635772397</v>
       </c>
       <c r="E374" t="n">
-        <v>11.13710263055622</v>
+        <v>11.13710167923091</v>
       </c>
       <c r="F374" t="n">
         <v>1639700</v>
@@ -7952,16 +7952,16 @@
         <v>44334</v>
       </c>
       <c r="B377" t="n">
-        <v>12.26456356048584</v>
+        <v>12.26456260681152</v>
       </c>
       <c r="C377" t="n">
-        <v>12.59455150019489</v>
+        <v>12.5945505208612</v>
       </c>
       <c r="D377" t="n">
-        <v>12.18206635701599</v>
+        <v>12.18206540975654</v>
       </c>
       <c r="E377" t="n">
-        <v>12.35622643998652</v>
+        <v>12.35622547918463</v>
       </c>
       <c r="F377" t="n">
         <v>1445400</v>
@@ -7992,16 +7992,16 @@
         <v>44336</v>
       </c>
       <c r="B379" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="C379" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="D379" t="n">
-        <v>11.86124370366004</v>
+        <v>11.86124460180745</v>
       </c>
       <c r="E379" t="n">
-        <v>12.05373688070891</v>
+        <v>12.05373779343214</v>
       </c>
       <c r="F379" t="n">
         <v>2196400</v>
@@ -8012,16 +8012,16 @@
         <v>44337</v>
       </c>
       <c r="B380" t="n">
-        <v>12.59455108642578</v>
+        <v>12.5945520401001</v>
       </c>
       <c r="C380" t="n">
-        <v>12.79621081337468</v>
+        <v>12.79621178231891</v>
       </c>
       <c r="D380" t="n">
-        <v>12.42955755907697</v>
+        <v>12.42955850025778</v>
       </c>
       <c r="E380" t="n">
-        <v>12.53038698546626</v>
+        <v>12.53038793428199</v>
       </c>
       <c r="F380" t="n">
         <v>1466000</v>
@@ -8052,16 +8052,16 @@
         <v>44341</v>
       </c>
       <c r="B382" t="n">
-        <v>12.53955268859863</v>
+        <v>12.53955364227295</v>
       </c>
       <c r="C382" t="n">
-        <v>12.75037807704068</v>
+        <v>12.75037904674896</v>
       </c>
       <c r="D382" t="n">
-        <v>12.40205707189402</v>
+        <v>12.40205801511135</v>
       </c>
       <c r="E382" t="n">
-        <v>12.62204988378735</v>
+        <v>12.62205084373585</v>
       </c>
       <c r="F382" t="n">
         <v>1256400</v>
@@ -8252,16 +8252,16 @@
         <v>44356</v>
       </c>
       <c r="B392" t="n">
-        <v>13.53868389129639</v>
+        <v>13.5386848449707</v>
       </c>
       <c r="C392" t="n">
-        <v>13.84117302553739</v>
+        <v>13.84117400051925</v>
       </c>
       <c r="D392" t="n">
-        <v>13.38285604951523</v>
+        <v>13.38285699221293</v>
       </c>
       <c r="E392" t="n">
-        <v>13.78617460377982</v>
+        <v>13.78617557488755</v>
       </c>
       <c r="F392" t="n">
         <v>1247900</v>
@@ -8272,16 +8272,16 @@
         <v>44357</v>
       </c>
       <c r="B393" t="n">
-        <v>13.62118148803711</v>
+        <v>13.62118053436279</v>
       </c>
       <c r="C393" t="n">
-        <v>13.77700934440852</v>
+        <v>13.77700837982407</v>
       </c>
       <c r="D393" t="n">
-        <v>13.32785887565343</v>
+        <v>13.32785794251582</v>
       </c>
       <c r="E393" t="n">
-        <v>13.56618393530034</v>
+        <v>13.56618298547662</v>
       </c>
       <c r="F393" t="n">
         <v>1127800</v>
@@ -8312,16 +8312,16 @@
         <v>44361</v>
       </c>
       <c r="B395" t="n">
-        <v>13.50201797485352</v>
+        <v>13.50201892852783</v>
       </c>
       <c r="C395" t="n">
-        <v>13.6578458198759</v>
+        <v>13.65784678455664</v>
       </c>
       <c r="D395" t="n">
-        <v>13.30035913061184</v>
+        <v>13.30036007004259</v>
       </c>
       <c r="E395" t="n">
-        <v>13.3186913554655</v>
+        <v>13.3186922961911</v>
       </c>
       <c r="F395" t="n">
         <v>1118700</v>
@@ -8392,16 +8392,16 @@
         <v>44365</v>
       </c>
       <c r="B399" t="n">
-        <v>13.74034309387207</v>
+        <v>13.74034404754639</v>
       </c>
       <c r="C399" t="n">
-        <v>13.75867619299839</v>
+        <v>13.75867714794514</v>
       </c>
       <c r="D399" t="n">
-        <v>13.34619107852938</v>
+        <v>13.34619200484684</v>
       </c>
       <c r="E399" t="n">
-        <v>13.40118862756777</v>
+        <v>13.40118955770243</v>
       </c>
       <c r="F399" t="n">
         <v>1818300</v>
@@ -8412,16 +8412,16 @@
         <v>44368</v>
       </c>
       <c r="B400" t="n">
-        <v>14.03366756439209</v>
+        <v>14.03366661071777</v>
       </c>
       <c r="C400" t="n">
-        <v>14.28115830110597</v>
+        <v>14.28115733061313</v>
       </c>
       <c r="D400" t="n">
-        <v>13.86867315713594</v>
+        <v>13.86867221467401</v>
       </c>
       <c r="E400" t="n">
-        <v>13.99700223768743</v>
+        <v>13.99700128650475</v>
       </c>
       <c r="F400" t="n">
         <v>2278000</v>
@@ -8432,16 +8432,16 @@
         <v>44369</v>
       </c>
       <c r="B401" t="n">
-        <v>13.53868389129639</v>
+        <v>13.5386848449707</v>
       </c>
       <c r="C401" t="n">
-        <v>13.98783431799724</v>
+        <v>13.98783530331003</v>
       </c>
       <c r="D401" t="n">
-        <v>13.41952137263019</v>
+        <v>13.41952231791062</v>
       </c>
       <c r="E401" t="n">
-        <v>13.95116899488228</v>
+        <v>13.95116997761234</v>
       </c>
       <c r="F401" t="n">
         <v>2062700</v>
@@ -8492,16 +8492,16 @@
         <v>44372</v>
       </c>
       <c r="B404" t="n">
-        <v>13.43785381317139</v>
+        <v>13.4378547668457</v>
       </c>
       <c r="C404" t="n">
-        <v>13.5661828832223</v>
+        <v>13.56618384600404</v>
       </c>
       <c r="D404" t="n">
-        <v>12.83287553496186</v>
+        <v>12.83287644570132</v>
       </c>
       <c r="E404" t="n">
-        <v>13.53868410898649</v>
+        <v>13.53868506981665</v>
       </c>
       <c r="F404" t="n">
         <v>1465200</v>
@@ -8532,16 +8532,16 @@
         <v>44376</v>
       </c>
       <c r="B406" t="n">
-        <v>13.1536979675293</v>
+        <v>13.15369892120361</v>
       </c>
       <c r="C406" t="n">
-        <v>13.30035926451625</v>
+        <v>13.30036022882386</v>
       </c>
       <c r="D406" t="n">
-        <v>12.89703982363184</v>
+        <v>12.89704075869783</v>
       </c>
       <c r="E406" t="n">
-        <v>13.26369394026951</v>
+        <v>13.2636949019188</v>
       </c>
       <c r="F406" t="n">
         <v>967400</v>
@@ -8672,16 +8672,16 @@
         <v>44385</v>
       </c>
       <c r="B413" t="n">
-        <v>12.45705699920654</v>
+        <v>12.45705604553223</v>
       </c>
       <c r="C413" t="n">
-        <v>12.57621953175335</v>
+        <v>12.57621856895631</v>
       </c>
       <c r="D413" t="n">
-        <v>12.17290005633794</v>
+        <v>12.17289912441782</v>
       </c>
       <c r="E413" t="n">
-        <v>12.3195613658816</v>
+        <v>12.31956042273353</v>
       </c>
       <c r="F413" t="n">
         <v>1082500</v>
@@ -8812,16 +8812,16 @@
         <v>44397</v>
       </c>
       <c r="B420" t="n">
-        <v>11.48542308807373</v>
+        <v>11.48542404174805</v>
       </c>
       <c r="C420" t="n">
-        <v>11.68708280077636</v>
+        <v>11.68708377119518</v>
       </c>
       <c r="D420" t="n">
-        <v>11.37542711955509</v>
+        <v>11.37542806409606</v>
       </c>
       <c r="E420" t="n">
-        <v>11.57708683225772</v>
+        <v>11.5770877935432</v>
       </c>
       <c r="F420" t="n">
         <v>1744400</v>
@@ -8832,16 +8832,16 @@
         <v>44398</v>
       </c>
       <c r="B421" t="n">
-        <v>11.48542308807373</v>
+        <v>11.48542404174805</v>
       </c>
       <c r="C421" t="n">
-        <v>11.66874970227147</v>
+        <v>11.66875067116803</v>
       </c>
       <c r="D421" t="n">
-        <v>11.2287658281969</v>
+        <v>11.22876676056008</v>
       </c>
       <c r="E421" t="n">
-        <v>11.54042150941818</v>
+        <v>11.5404224676592</v>
       </c>
       <c r="F421" t="n">
         <v>2115800</v>
@@ -8872,16 +8872,16 @@
         <v>44400</v>
       </c>
       <c r="B423" t="n">
-        <v>11.68708419799805</v>
+        <v>11.68708324432373</v>
       </c>
       <c r="C423" t="n">
-        <v>11.7145829748727</v>
+        <v>11.71458201895446</v>
       </c>
       <c r="D423" t="n">
-        <v>11.43959258361514</v>
+        <v>11.43959165013631</v>
       </c>
       <c r="E423" t="n">
-        <v>11.62292009390042</v>
+        <v>11.62291914546194</v>
       </c>
       <c r="F423" t="n">
         <v>1513600</v>
@@ -8912,16 +8912,16 @@
         <v>44404</v>
       </c>
       <c r="B425" t="n">
-        <v>11.43959140777588</v>
+        <v>11.4395923614502</v>
       </c>
       <c r="C425" t="n">
-        <v>11.61375234981137</v>
+        <v>11.61375331800481</v>
       </c>
       <c r="D425" t="n">
-        <v>11.19210069300211</v>
+        <v>11.19210162604409</v>
       </c>
       <c r="E425" t="n">
-        <v>11.39376040908574</v>
+        <v>11.3937613589393</v>
       </c>
       <c r="F425" t="n">
         <v>1727000</v>
@@ -8952,16 +8952,16 @@
         <v>44406</v>
       </c>
       <c r="B427" t="n">
-        <v>11.25626468658447</v>
+        <v>11.25626564025879</v>
       </c>
       <c r="C427" t="n">
-        <v>11.36626065593178</v>
+        <v>11.36626161892538</v>
       </c>
       <c r="D427" t="n">
-        <v>11.15543526655867</v>
+        <v>11.15543621169033</v>
       </c>
       <c r="E427" t="n">
-        <v>11.36626065593178</v>
+        <v>11.36626161892538</v>
       </c>
       <c r="F427" t="n">
         <v>743300</v>
@@ -8992,16 +8992,16 @@
         <v>44410</v>
       </c>
       <c r="B429" t="n">
-        <v>10.90794372558594</v>
+        <v>10.90794467926025</v>
       </c>
       <c r="C429" t="n">
-        <v>11.2012671859109</v>
+        <v>11.20126816523029</v>
       </c>
       <c r="D429" t="n">
-        <v>10.86211272712696</v>
+        <v>10.8621136767943</v>
       </c>
       <c r="E429" t="n">
-        <v>10.96294214757507</v>
+        <v>10.96294310605787</v>
       </c>
       <c r="F429" t="n">
         <v>1959100</v>
@@ -9132,16 +9132,16 @@
         <v>44419</v>
       </c>
       <c r="B436" t="n">
-        <v>9.890481948852539</v>
+        <v>9.890480995178223</v>
       </c>
       <c r="C436" t="n">
-        <v>10.51379341941164</v>
+        <v>10.51379240563549</v>
       </c>
       <c r="D436" t="n">
-        <v>9.743820632055199</v>
+        <v>9.74381969252247</v>
       </c>
       <c r="E436" t="n">
-        <v>10.51379341941164</v>
+        <v>10.51379240563549</v>
       </c>
       <c r="F436" t="n">
         <v>4618100</v>
@@ -9172,16 +9172,16 @@
         <v>44421</v>
       </c>
       <c r="B438" t="n">
-        <v>9.81714916229248</v>
+        <v>9.817150115966797</v>
       </c>
       <c r="C438" t="n">
-        <v>10.00964231740293</v>
+        <v>10.00964328977675</v>
       </c>
       <c r="D438" t="n">
-        <v>9.688820100828776</v>
+        <v>9.688821042036732</v>
       </c>
       <c r="E438" t="n">
-        <v>9.908812902505156</v>
+        <v>9.90881386508403</v>
       </c>
       <c r="F438" t="n">
         <v>1360000</v>
@@ -9212,16 +9212,16 @@
         <v>44425</v>
       </c>
       <c r="B440" t="n">
-        <v>8.323036193847656</v>
+        <v>8.323037147521973</v>
       </c>
       <c r="C440" t="n">
-        <v>9.294668565223555</v>
+        <v>9.29466963022994</v>
       </c>
       <c r="D440" t="n">
-        <v>8.304703969421075</v>
+        <v>8.30470492099484</v>
       </c>
       <c r="E440" t="n">
-        <v>9.285502015925136</v>
+        <v>9.285503079881195</v>
       </c>
       <c r="F440" t="n">
         <v>6613600</v>
@@ -9272,16 +9272,16 @@
         <v>44428</v>
       </c>
       <c r="B443" t="n">
-        <v>8.62552547454834</v>
+        <v>8.625526428222656</v>
       </c>
       <c r="C443" t="n">
-        <v>8.689689572391865</v>
+        <v>8.689690533160434</v>
       </c>
       <c r="D443" t="n">
-        <v>8.414700082108032</v>
+        <v>8.414701012472607</v>
       </c>
       <c r="E443" t="n">
-        <v>8.515529503600753</v>
+        <v>8.515530445113452</v>
       </c>
       <c r="F443" t="n">
         <v>1662000</v>
@@ -9332,16 +9332,16 @@
         <v>44433</v>
       </c>
       <c r="B446" t="n">
-        <v>8.955513954162598</v>
+        <v>8.955514907836914</v>
       </c>
       <c r="C446" t="n">
-        <v>9.322167178069154</v>
+        <v>9.322168170788439</v>
       </c>
       <c r="D446" t="n">
-        <v>8.744687694788647</v>
+        <v>8.744688626012037</v>
       </c>
       <c r="E446" t="n">
-        <v>9.175505888506532</v>
+        <v>9.175506865607829</v>
       </c>
       <c r="F446" t="n">
         <v>3539500</v>
@@ -9352,16 +9352,16 @@
         <v>44434</v>
       </c>
       <c r="B447" t="n">
-        <v>8.488031387329102</v>
+        <v>8.488030433654785</v>
       </c>
       <c r="C447" t="n">
-        <v>9.093009711518935</v>
+        <v>9.093008689872168</v>
       </c>
       <c r="D447" t="n">
-        <v>8.451366060837909</v>
+        <v>8.451365111283133</v>
       </c>
       <c r="E447" t="n">
-        <v>8.928015305223402</v>
+        <v>8.928014302114612</v>
       </c>
       <c r="F447" t="n">
         <v>2819100</v>
@@ -9412,16 +9412,16 @@
         <v>44439</v>
       </c>
       <c r="B450" t="n">
-        <v>8.148877143859863</v>
+        <v>8.148876190185547</v>
       </c>
       <c r="C450" t="n">
-        <v>8.478865092206572</v>
+        <v>8.478864099913311</v>
       </c>
       <c r="D450" t="n">
-        <v>8.075546488671705</v>
+        <v>8.075545543579377</v>
       </c>
       <c r="E450" t="n">
-        <v>8.359702558983225</v>
+        <v>8.35970158063572</v>
       </c>
       <c r="F450" t="n">
         <v>2719700</v>
@@ -9472,16 +9472,16 @@
         <v>44442</v>
       </c>
       <c r="B453" t="n">
-        <v>8.020547866821289</v>
+        <v>8.020546913146973</v>
       </c>
       <c r="C453" t="n">
-        <v>8.048046643311267</v>
+        <v>8.048045686367239</v>
       </c>
       <c r="D453" t="n">
-        <v>7.818888132830658</v>
+        <v>7.818887203134468</v>
       </c>
       <c r="E453" t="n">
-        <v>7.965549439670992</v>
+        <v>7.965548492536203</v>
       </c>
       <c r="F453" t="n">
         <v>2243900</v>
@@ -9532,16 +9532,16 @@
         <v>44448</v>
       </c>
       <c r="B456" t="n">
-        <v>7.95638370513916</v>
+        <v>7.956383228302002</v>
       </c>
       <c r="C456" t="n">
-        <v>8.075546234613633</v>
+        <v>8.075545750634898</v>
       </c>
       <c r="D456" t="n">
-        <v>7.626394893003591</v>
+        <v>7.626394435943123</v>
       </c>
       <c r="E456" t="n">
-        <v>7.883053052257997</v>
+        <v>7.883052579815647</v>
       </c>
       <c r="F456" t="n">
         <v>3062500</v>
@@ -9672,16 +9672,16 @@
         <v>44459</v>
       </c>
       <c r="B463" t="n">
-        <v>7.333071708679199</v>
+        <v>7.333072185516357</v>
       </c>
       <c r="C463" t="n">
-        <v>7.415568905269083</v>
+        <v>7.415569387470669</v>
       </c>
       <c r="D463" t="n">
-        <v>7.140578541359559</v>
+        <v>7.14057900567974</v>
       </c>
       <c r="E463" t="n">
-        <v>7.21390918851273</v>
+        <v>7.213909657601278</v>
       </c>
       <c r="F463" t="n">
         <v>2478700</v>
@@ -9692,16 +9692,16 @@
         <v>44460</v>
       </c>
       <c r="B464" t="n">
-        <v>7.562230587005615</v>
+        <v>7.562231063842773</v>
       </c>
       <c r="C464" t="n">
-        <v>7.635561237915681</v>
+        <v>7.63556171937671</v>
       </c>
       <c r="D464" t="n">
-        <v>7.213909558097646</v>
+        <v>7.21391001297139</v>
       </c>
       <c r="E464" t="n">
-        <v>7.488899936095549</v>
+        <v>7.488900408308837</v>
       </c>
       <c r="F464" t="n">
         <v>2716900</v>
@@ -9712,16 +9712,16 @@
         <v>44461</v>
       </c>
       <c r="B465" t="n">
-        <v>7.653894424438477</v>
+        <v>7.653893947601318</v>
       </c>
       <c r="C465" t="n">
-        <v>7.773056077889568</v>
+        <v>7.773055593628645</v>
       </c>
       <c r="D465" t="n">
-        <v>7.443068145055875</v>
+        <v>7.443067681353181</v>
       </c>
       <c r="E465" t="n">
-        <v>7.708891976158931</v>
+        <v>7.708891495895427</v>
       </c>
       <c r="F465" t="n">
         <v>2341500</v>
@@ -9732,16 +9732,16 @@
         <v>44462</v>
       </c>
       <c r="B466" t="n">
-        <v>7.635560989379883</v>
+        <v>7.635561466217041</v>
       </c>
       <c r="C466" t="n">
-        <v>7.809721935250124</v>
+        <v>7.809722422963551</v>
       </c>
       <c r="D466" t="n">
-        <v>7.553063791248745</v>
+        <v>7.553064262933993</v>
       </c>
       <c r="E466" t="n">
-        <v>7.6630597640335</v>
+        <v>7.663060242587944</v>
       </c>
       <c r="F466" t="n">
         <v>1813900</v>
@@ -9852,16 +9852,16 @@
         <v>44470</v>
       </c>
       <c r="B472" t="n">
-        <v>7.058081150054932</v>
+        <v>7.05808162689209</v>
       </c>
       <c r="C472" t="n">
-        <v>7.058081150054932</v>
+        <v>7.05808162689209</v>
       </c>
       <c r="D472" t="n">
-        <v>6.590598068807588</v>
+        <v>6.590598514062039</v>
       </c>
       <c r="E472" t="n">
-        <v>6.627263391372669</v>
+        <v>6.627263839104194</v>
       </c>
       <c r="F472" t="n">
         <v>1964300</v>
@@ -9872,16 +9872,16 @@
         <v>44473</v>
       </c>
       <c r="B473" t="n">
-        <v>6.883921146392822</v>
+        <v>6.88392162322998</v>
       </c>
       <c r="C473" t="n">
-        <v>7.058081211551849</v>
+        <v>7.05808170045277</v>
       </c>
       <c r="D473" t="n">
-        <v>6.792257402096333</v>
+        <v>6.792257872584105</v>
       </c>
       <c r="E473" t="n">
-        <v>6.911419920013668</v>
+        <v>6.911420398755618</v>
       </c>
       <c r="F473" t="n">
         <v>2556200</v>
@@ -9972,16 +9972,16 @@
         <v>44480</v>
       </c>
       <c r="B478" t="n">
-        <v>6.645596981048584</v>
+        <v>6.645596504211426</v>
       </c>
       <c r="C478" t="n">
-        <v>6.79225829179757</v>
+        <v>6.792257804437119</v>
       </c>
       <c r="D478" t="n">
-        <v>6.526434447522441</v>
+        <v>6.526433979235474</v>
       </c>
       <c r="E478" t="n">
-        <v>6.783092178418349</v>
+        <v>6.783091691715589</v>
       </c>
       <c r="F478" t="n">
         <v>1719800</v>
@@ -9992,16 +9992,16 @@
         <v>44482</v>
       </c>
       <c r="B479" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C479" t="n">
-        <v>6.89308794729405</v>
+        <v>6.893087464680927</v>
       </c>
       <c r="D479" t="n">
-        <v>6.581432234551219</v>
+        <v>6.58143177375838</v>
       </c>
       <c r="E479" t="n">
-        <v>6.645596774552734</v>
+        <v>6.645596309267474</v>
       </c>
       <c r="F479" t="n">
         <v>1797400</v>
@@ -10032,16 +10032,16 @@
         <v>44484</v>
       </c>
       <c r="B481" t="n">
-        <v>6.801424503326416</v>
+        <v>6.801424026489258</v>
       </c>
       <c r="C481" t="n">
-        <v>6.810590616248861</v>
+        <v>6.810590138769081</v>
       </c>
       <c r="D481" t="n">
-        <v>6.58143211108064</v>
+        <v>6.581431649666802</v>
       </c>
       <c r="E481" t="n">
-        <v>6.654763199886006</v>
+        <v>6.654762733331041</v>
       </c>
       <c r="F481" t="n">
         <v>1272200</v>
@@ -10112,16 +10112,16 @@
         <v>44490</v>
       </c>
       <c r="B485" t="n">
-        <v>5.967287540435791</v>
+        <v>5.967287063598633</v>
       </c>
       <c r="C485" t="n">
-        <v>6.297275465216598</v>
+        <v>6.29727496201059</v>
       </c>
       <c r="D485" t="n">
-        <v>5.89395645339935</v>
+        <v>5.89395598242197</v>
       </c>
       <c r="E485" t="n">
-        <v>6.297275465216598</v>
+        <v>6.29727496201059</v>
       </c>
       <c r="F485" t="n">
         <v>2712900</v>
@@ -10172,16 +10172,16 @@
         <v>44495</v>
       </c>
       <c r="B488" t="n">
-        <v>5.60063362121582</v>
+        <v>5.600634098052979</v>
       </c>
       <c r="C488" t="n">
-        <v>5.994786066892628</v>
+        <v>5.994786577287869</v>
       </c>
       <c r="D488" t="n">
-        <v>5.60063362121582</v>
+        <v>5.600634098052979</v>
       </c>
       <c r="E488" t="n">
-        <v>5.930621532304952</v>
+        <v>5.930622037237235</v>
       </c>
       <c r="F488" t="n">
         <v>1746800</v>
@@ -10232,16 +10232,16 @@
         <v>44498</v>
       </c>
       <c r="B491" t="n">
-        <v>5.554801940917969</v>
+        <v>5.554802417755127</v>
       </c>
       <c r="C491" t="n">
-        <v>5.838958426082296</v>
+        <v>5.838958927312109</v>
       </c>
       <c r="D491" t="n">
-        <v>5.545635828279196</v>
+        <v>5.545636304329514</v>
       </c>
       <c r="E491" t="n">
-        <v>5.701463239819518</v>
+        <v>5.701463729246425</v>
       </c>
       <c r="F491" t="n">
         <v>2502600</v>
@@ -10312,16 +10312,16 @@
         <v>44505</v>
       </c>
       <c r="B495" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C495" t="n">
-        <v>6.94808593711599</v>
+        <v>6.948085450652234</v>
       </c>
       <c r="D495" t="n">
-        <v>6.398105601811419</v>
+        <v>6.398105153854022</v>
       </c>
       <c r="E495" t="n">
-        <v>6.398105601811419</v>
+        <v>6.398105153854022</v>
       </c>
       <c r="F495" t="n">
         <v>3968000</v>
@@ -10372,16 +10372,16 @@
         <v>44510</v>
       </c>
       <c r="B498" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C498" t="n">
-        <v>7.333072037123874</v>
+        <v>7.333072524313823</v>
       </c>
       <c r="D498" t="n">
-        <v>6.874755034803632</v>
+        <v>6.874755491544209</v>
       </c>
       <c r="E498" t="n">
-        <v>6.874755034803632</v>
+        <v>6.874755491544209</v>
       </c>
       <c r="F498" t="n">
         <v>8294800</v>
@@ -10432,16 +10432,16 @@
         <v>44516</v>
       </c>
       <c r="B501" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C501" t="n">
-        <v>7.177243999484845</v>
+        <v>7.177244504030098</v>
       </c>
       <c r="D501" t="n">
-        <v>6.691428234445144</v>
+        <v>6.691428704838564</v>
       </c>
       <c r="E501" t="n">
-        <v>7.131412562697498</v>
+        <v>7.131413064020896</v>
       </c>
       <c r="F501" t="n">
         <v>3605600</v>
@@ -10492,16 +10492,16 @@
         <v>44519</v>
       </c>
       <c r="B504" t="n">
-        <v>7.232242107391357</v>
+        <v>7.232241630554199</v>
       </c>
       <c r="C504" t="n">
-        <v>7.305572757151272</v>
+        <v>7.305572275479267</v>
       </c>
       <c r="D504" t="n">
-        <v>6.544766610264437</v>
+        <v>6.544766178754005</v>
       </c>
       <c r="E504" t="n">
-        <v>6.645596472226894</v>
+        <v>6.645596034068535</v>
       </c>
       <c r="F504" t="n">
         <v>4026100</v>
@@ -10512,16 +10512,16 @@
         <v>44522</v>
       </c>
       <c r="B505" t="n">
-        <v>6.78309154510498</v>
+        <v>6.783092021942139</v>
       </c>
       <c r="C505" t="n">
-        <v>7.296406521885203</v>
+        <v>7.296407034807332</v>
       </c>
       <c r="D505" t="n">
-        <v>6.572265712044786</v>
+        <v>6.57226617406133</v>
       </c>
       <c r="E505" t="n">
-        <v>7.278073859753236</v>
+        <v>7.278074371386616</v>
       </c>
       <c r="F505" t="n">
         <v>4188800</v>
@@ -10752,16 +10752,16 @@
         <v>44538</v>
       </c>
       <c r="B517" t="n">
-        <v>6.269776344299316</v>
+        <v>6.269776821136475</v>
       </c>
       <c r="C517" t="n">
-        <v>6.398104974637775</v>
+        <v>6.398105461234748</v>
       </c>
       <c r="D517" t="n">
-        <v>5.912288789871634</v>
+        <v>5.912289239520686</v>
       </c>
       <c r="E517" t="n">
-        <v>6.223944472064447</v>
+        <v>6.22394494541594</v>
       </c>
       <c r="F517" t="n">
         <v>2255900</v>
@@ -10772,16 +10772,16 @@
         <v>44539</v>
       </c>
       <c r="B518" t="n">
-        <v>6.086450099945068</v>
+        <v>6.08644962310791</v>
       </c>
       <c r="C518" t="n">
-        <v>6.26977717612175</v>
+        <v>6.269776684922006</v>
       </c>
       <c r="D518" t="n">
-        <v>5.994786780399321</v>
+        <v>5.994786310743438</v>
       </c>
       <c r="E518" t="n">
-        <v>6.205612633897133</v>
+        <v>6.2056121477243</v>
       </c>
       <c r="F518" t="n">
         <v>1370200</v>
@@ -10792,16 +10792,16 @@
         <v>44540</v>
       </c>
       <c r="B519" t="n">
-        <v>6.13228178024292</v>
+        <v>6.132281303405762</v>
       </c>
       <c r="C519" t="n">
-        <v>6.242277760145935</v>
+        <v>6.242277274755653</v>
       </c>
       <c r="D519" t="n">
-        <v>6.077283790291412</v>
+        <v>6.077283317730816</v>
       </c>
       <c r="E519" t="n">
-        <v>6.233111647029936</v>
+        <v>6.233111162352396</v>
       </c>
       <c r="F519" t="n">
         <v>1440000</v>
@@ -10812,16 +10812,16 @@
         <v>44543</v>
       </c>
       <c r="B520" t="n">
-        <v>5.930622100830078</v>
+        <v>5.93062162399292</v>
       </c>
       <c r="C520" t="n">
-        <v>6.233111703953602</v>
+        <v>6.233111202795508</v>
       </c>
       <c r="D520" t="n">
-        <v>5.930622100830078</v>
+        <v>5.93062162399292</v>
       </c>
       <c r="E520" t="n">
-        <v>6.123115285960878</v>
+        <v>6.123114793646776</v>
       </c>
       <c r="F520" t="n">
         <v>1532500</v>
@@ -10852,16 +10852,16 @@
         <v>44545</v>
       </c>
       <c r="B522" t="n">
-        <v>5.783960342407227</v>
+        <v>5.783960819244385</v>
       </c>
       <c r="C522" t="n">
-        <v>5.848124878147738</v>
+        <v>5.848125360274703</v>
       </c>
       <c r="D522" t="n">
-        <v>5.527303073615463</v>
+        <v>5.527303529293464</v>
       </c>
       <c r="E522" t="n">
-        <v>5.683130482553606</v>
+        <v>5.68313095107822</v>
       </c>
       <c r="F522" t="n">
         <v>1794200</v>
@@ -10912,16 +10912,16 @@
         <v>44550</v>
       </c>
       <c r="B525" t="n">
-        <v>5.70146369934082</v>
+        <v>5.701463222503662</v>
       </c>
       <c r="C525" t="n">
-        <v>5.756462127946762</v>
+        <v>5.756461646509856</v>
       </c>
       <c r="D525" t="n">
-        <v>5.582301602921769</v>
+        <v>5.582301136050633</v>
       </c>
       <c r="E525" t="n">
-        <v>5.710630249803538</v>
+        <v>5.710629772199743</v>
       </c>
       <c r="F525" t="n">
         <v>2934100</v>
@@ -10952,16 +10952,16 @@
         <v>44552</v>
       </c>
       <c r="B527" t="n">
-        <v>5.453971862792969</v>
+        <v>5.453972339630127</v>
       </c>
       <c r="C527" t="n">
-        <v>5.646465028499557</v>
+        <v>5.646465522166265</v>
       </c>
       <c r="D527" t="n">
-        <v>5.42647308888353</v>
+        <v>5.426473563316489</v>
       </c>
       <c r="E527" t="n">
-        <v>5.618966254590118</v>
+        <v>5.618966745852627</v>
       </c>
       <c r="F527" t="n">
         <v>3033600</v>
@@ -10972,16 +10972,16 @@
         <v>44553</v>
       </c>
       <c r="B528" t="n">
-        <v>5.453971862792969</v>
+        <v>5.453972339630127</v>
       </c>
       <c r="C528" t="n">
-        <v>5.481471073787537</v>
+        <v>5.481471553028933</v>
       </c>
       <c r="D528" t="n">
-        <v>5.325643231350287</v>
+        <v>5.325643696967758</v>
       </c>
       <c r="E528" t="n">
-        <v>5.444805750518199</v>
+        <v>5.444806226553971</v>
       </c>
       <c r="F528" t="n">
         <v>2899900</v>
@@ -11012,16 +11012,16 @@
         <v>44558</v>
       </c>
       <c r="B530" t="n">
-        <v>5.719795703887939</v>
+        <v>5.719796180725098</v>
       </c>
       <c r="C530" t="n">
-        <v>5.756461464427344</v>
+        <v>5.756461944321184</v>
       </c>
       <c r="D530" t="n">
-        <v>5.527302974295581</v>
+        <v>5.527303435085368</v>
       </c>
       <c r="E530" t="n">
-        <v>5.563968297749852</v>
+        <v>5.563968761596285</v>
       </c>
       <c r="F530" t="n">
         <v>2551400</v>
@@ -11072,16 +11072,16 @@
         <v>44564</v>
       </c>
       <c r="B533" t="n">
-        <v>5.417306900024414</v>
+        <v>5.417306423187256</v>
       </c>
       <c r="C533" t="n">
-        <v>5.774794481317564</v>
+        <v>5.774793973013967</v>
       </c>
       <c r="D533" t="n">
-        <v>5.371475461430403</v>
+        <v>5.371474988627377</v>
       </c>
       <c r="E533" t="n">
-        <v>5.655631954219848</v>
+        <v>5.655631456405064</v>
       </c>
       <c r="F533" t="n">
         <v>2044700</v>
@@ -11112,16 +11112,16 @@
         <v>44566</v>
       </c>
       <c r="B535" t="n">
-        <v>4.885658740997314</v>
+        <v>4.885659217834473</v>
       </c>
       <c r="C535" t="n">
-        <v>5.0689857878987</v>
+        <v>5.06898628262846</v>
       </c>
       <c r="D535" t="n">
-        <v>4.839827307085804</v>
+        <v>4.839827779449844</v>
       </c>
       <c r="E535" t="n">
-        <v>5.023153916902075</v>
+        <v>5.023154407158674</v>
       </c>
       <c r="F535" t="n">
         <v>2302400</v>
@@ -11172,16 +11172,16 @@
         <v>44571</v>
       </c>
       <c r="B538" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C538" t="n">
-        <v>4.894826206904368</v>
+        <v>4.894825720038117</v>
       </c>
       <c r="D538" t="n">
-        <v>4.62900235433546</v>
+        <v>4.629001893909508</v>
       </c>
       <c r="E538" t="n">
-        <v>4.720665676413498</v>
+        <v>4.720665206870209</v>
       </c>
       <c r="F538" t="n">
         <v>3868800</v>
@@ -11192,16 +11192,16 @@
         <v>44572</v>
       </c>
       <c r="B539" t="n">
-        <v>5.00482177734375</v>
+        <v>5.004822254180908</v>
       </c>
       <c r="C539" t="n">
-        <v>5.059819766018552</v>
+        <v>5.059820248095674</v>
       </c>
       <c r="D539" t="n">
-        <v>4.766496722667781</v>
+        <v>4.766497176798388</v>
       </c>
       <c r="E539" t="n">
-        <v>4.775663272656161</v>
+        <v>4.775663727660117</v>
       </c>
       <c r="F539" t="n">
         <v>2192500</v>
@@ -11212,16 +11212,16 @@
         <v>44573</v>
       </c>
       <c r="B540" t="n">
-        <v>5.169815540313721</v>
+        <v>5.169816017150879</v>
       </c>
       <c r="C540" t="n">
-        <v>5.270645400799818</v>
+        <v>5.270645886937004</v>
       </c>
       <c r="D540" t="n">
-        <v>4.995655031141423</v>
+        <v>4.995655491914913</v>
       </c>
       <c r="E540" t="n">
-        <v>5.032320355484523</v>
+        <v>5.032320819639834</v>
       </c>
       <c r="F540" t="n">
         <v>2344800</v>
@@ -11272,16 +11272,16 @@
         <v>44578</v>
       </c>
       <c r="B543" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C543" t="n">
-        <v>5.105651419324723</v>
+        <v>5.105651915770163</v>
       </c>
       <c r="D543" t="n">
-        <v>4.821494938343708</v>
+        <v>4.821495407159335</v>
       </c>
       <c r="E543" t="n">
-        <v>5.041486883457342</v>
+        <v>5.041487373663776</v>
       </c>
       <c r="F543" t="n">
         <v>1383000</v>
@@ -11292,16 +11292,16 @@
         <v>44579</v>
       </c>
       <c r="B544" t="n">
-        <v>4.803162097930908</v>
+        <v>4.80316162109375</v>
       </c>
       <c r="C544" t="n">
-        <v>4.977322615737815</v>
+        <v>4.977322121610753</v>
       </c>
       <c r="D544" t="n">
-        <v>4.748164108689543</v>
+        <v>4.748163637312347</v>
       </c>
       <c r="E544" t="n">
-        <v>4.913158513498805</v>
+        <v>4.913158025741677</v>
       </c>
       <c r="F544" t="n">
         <v>2424100</v>
@@ -11312,16 +11312,16 @@
         <v>44580</v>
       </c>
       <c r="B545" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C545" t="n">
-        <v>5.050653537402776</v>
+        <v>5.050653052647643</v>
       </c>
       <c r="D545" t="n">
-        <v>4.812328488186932</v>
+        <v>4.812328026305926</v>
       </c>
       <c r="E545" t="n">
-        <v>4.839827700436895</v>
+        <v>4.839827235916551</v>
       </c>
       <c r="F545" t="n">
         <v>2176700</v>
@@ -11552,16 +11552,16 @@
         <v>44596</v>
       </c>
       <c r="B557" t="n">
-        <v>5.490636825561523</v>
+        <v>5.490637302398682</v>
       </c>
       <c r="C557" t="n">
-        <v>5.637298546094581</v>
+        <v>5.637299035668652</v>
       </c>
       <c r="D557" t="n">
-        <v>5.37147475130261</v>
+        <v>5.371475217791077</v>
       </c>
       <c r="E557" t="n">
-        <v>5.628131997336533</v>
+        <v>5.628132486114529</v>
       </c>
       <c r="F557" t="n">
         <v>2310300</v>
@@ -11812,16 +11812,16 @@
         <v>44615</v>
       </c>
       <c r="B570" t="n">
-        <v>4.867326736450195</v>
+        <v>4.867326259613037</v>
       </c>
       <c r="C570" t="n">
-        <v>5.013988044082764</v>
+        <v>5.013987552877644</v>
       </c>
       <c r="D570" t="n">
-        <v>4.803162195818359</v>
+        <v>4.803161725267206</v>
       </c>
       <c r="E570" t="n">
-        <v>4.949823940536103</v>
+        <v>4.949823455616944</v>
       </c>
       <c r="F570" t="n">
         <v>3505100</v>
@@ -11872,16 +11872,16 @@
         <v>44622</v>
       </c>
       <c r="B573" t="n">
-        <v>4.647334575653076</v>
+        <v>4.647335052490234</v>
       </c>
       <c r="C573" t="n">
-        <v>4.738997888991517</v>
+        <v>4.738998375233738</v>
       </c>
       <c r="D573" t="n">
-        <v>4.58317003777359</v>
+        <v>4.583170508027182</v>
       </c>
       <c r="E573" t="n">
-        <v>4.665667238320764</v>
+        <v>4.665667717038935</v>
       </c>
       <c r="F573" t="n">
         <v>2274100</v>
@@ -11932,16 +11932,16 @@
         <v>44627</v>
       </c>
       <c r="B576" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="C576" t="n">
-        <v>4.46400783481362</v>
+        <v>4.464007312971596</v>
       </c>
       <c r="D576" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="E576" t="n">
-        <v>4.46400783481362</v>
+        <v>4.464007312971596</v>
       </c>
       <c r="F576" t="n">
         <v>3496200</v>
@@ -11952,16 +11952,16 @@
         <v>44628</v>
       </c>
       <c r="B577" t="n">
-        <v>4.124853134155273</v>
+        <v>4.124852657318115</v>
       </c>
       <c r="C577" t="n">
-        <v>4.207350336705632</v>
+        <v>4.207349850331715</v>
       </c>
       <c r="D577" t="n">
-        <v>3.969025279153559</v>
+        <v>3.969024820330257</v>
       </c>
       <c r="E577" t="n">
-        <v>4.134019684254276</v>
+        <v>4.134019206357456</v>
       </c>
       <c r="F577" t="n">
         <v>4412200</v>
@@ -11972,16 +11972,16 @@
         <v>44629</v>
       </c>
       <c r="B578" t="n">
-        <v>4.335678577423096</v>
+        <v>4.335679054260254</v>
       </c>
       <c r="C578" t="n">
-        <v>4.418175772342043</v>
+        <v>4.418176258252227</v>
       </c>
       <c r="D578" t="n">
-        <v>4.161518075419278</v>
+        <v>4.161518533102296</v>
       </c>
       <c r="E578" t="n">
-        <v>4.170684624670328</v>
+        <v>4.17068508336148</v>
       </c>
       <c r="F578" t="n">
         <v>3479000</v>
@@ -12172,16 +12172,16 @@
         <v>44643</v>
       </c>
       <c r="B588" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C588" t="n">
-        <v>4.839828213657545</v>
+        <v>4.839827732261697</v>
       </c>
       <c r="D588" t="n">
-        <v>4.574003924003441</v>
+        <v>4.574003469047934</v>
       </c>
       <c r="E588" t="n">
-        <v>4.656501132416273</v>
+        <v>4.656500669255141</v>
       </c>
       <c r="F588" t="n">
         <v>5289000</v>
@@ -12212,16 +12212,16 @@
         <v>44645</v>
       </c>
       <c r="B590" t="n">
-        <v>4.986489295959473</v>
+        <v>4.986488819122314</v>
       </c>
       <c r="C590" t="n">
-        <v>5.270645799665109</v>
+        <v>5.270645295655251</v>
       </c>
       <c r="D590" t="n">
-        <v>4.958990082078524</v>
+        <v>4.958989607871001</v>
       </c>
       <c r="E590" t="n">
-        <v>5.078152613754004</v>
+        <v>5.078152128151466</v>
       </c>
       <c r="F590" t="n">
         <v>4172200</v>
@@ -12232,16 +12232,16 @@
         <v>44648</v>
       </c>
       <c r="B591" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C591" t="n">
-        <v>5.142316768551991</v>
+        <v>5.142317254043173</v>
       </c>
       <c r="D591" t="n">
-        <v>4.885659060917757</v>
+        <v>4.885659522177632</v>
       </c>
       <c r="E591" t="n">
-        <v>5.013987696192302</v>
+        <v>5.01398816956781</v>
       </c>
       <c r="F591" t="n">
         <v>3528600</v>
@@ -12252,16 +12252,16 @@
         <v>44649</v>
       </c>
       <c r="B592" t="n">
-        <v>5.33480978012085</v>
+        <v>5.334810256958008</v>
       </c>
       <c r="C592" t="n">
-        <v>5.362308554027249</v>
+        <v>5.362309033322309</v>
       </c>
       <c r="D592" t="n">
-        <v>5.142316614435527</v>
+        <v>5.142317074067217</v>
       </c>
       <c r="E592" t="n">
-        <v>5.16064927606817</v>
+        <v>5.160649737338475</v>
       </c>
       <c r="F592" t="n">
         <v>3923800</v>
@@ -12292,16 +12292,16 @@
         <v>44651</v>
       </c>
       <c r="B594" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C594" t="n">
-        <v>5.224813529828769</v>
+        <v>5.224814023108552</v>
       </c>
       <c r="D594" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="E594" t="n">
-        <v>5.178982092916146</v>
+        <v>5.178982581868937</v>
       </c>
       <c r="F594" t="n">
         <v>1926600</v>
@@ -12452,16 +12452,16 @@
         <v>44663</v>
       </c>
       <c r="B602" t="n">
-        <v>4.372344493865967</v>
+        <v>4.372344017028809</v>
       </c>
       <c r="C602" t="n">
-        <v>4.519005805113152</v>
+        <v>4.519005312281472</v>
       </c>
       <c r="D602" t="n">
-        <v>4.36317838045561</v>
+        <v>4.363177904618086</v>
       </c>
       <c r="E602" t="n">
-        <v>4.464007813395457</v>
+        <v>4.464007326561723</v>
       </c>
       <c r="F602" t="n">
         <v>2977800</v>
@@ -12472,16 +12472,16 @@
         <v>44664</v>
       </c>
       <c r="B603" t="n">
-        <v>4.482340335845947</v>
+        <v>4.482339859008789</v>
       </c>
       <c r="C603" t="n">
-        <v>4.500672999173296</v>
+        <v>4.500672520385886</v>
       </c>
       <c r="D603" t="n">
-        <v>4.344845142348245</v>
+        <v>4.344844680138003</v>
       </c>
       <c r="E603" t="n">
-        <v>4.427342345863901</v>
+        <v>4.4273418748775</v>
       </c>
       <c r="F603" t="n">
         <v>2309600</v>
@@ -12512,16 +12512,16 @@
         <v>44669</v>
       </c>
       <c r="B605" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="C605" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="D605" t="n">
-        <v>4.372344289398597</v>
+        <v>4.372343829900955</v>
       </c>
       <c r="E605" t="n">
-        <v>4.45484149165985</v>
+        <v>4.454841023492427</v>
       </c>
       <c r="F605" t="n">
         <v>2710700</v>
@@ -12552,16 +12552,16 @@
         <v>44671</v>
       </c>
       <c r="B607" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="C607" t="n">
-        <v>4.509839386853855</v>
+        <v>4.509839880756772</v>
       </c>
       <c r="D607" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="E607" t="n">
-        <v>4.418176073520475</v>
+        <v>4.418176557384724</v>
       </c>
       <c r="F607" t="n">
         <v>2075500</v>
@@ -12572,16 +12572,16 @@
         <v>44673</v>
       </c>
       <c r="B608" t="n">
-        <v>4.097353935241699</v>
+        <v>4.097354412078857</v>
       </c>
       <c r="C608" t="n">
-        <v>4.308179780317636</v>
+        <v>4.308180281690042</v>
       </c>
       <c r="D608" t="n">
-        <v>4.079021272064886</v>
+        <v>4.079021746768547</v>
       </c>
       <c r="E608" t="n">
-        <v>4.308179780317636</v>
+        <v>4.308180281690042</v>
       </c>
       <c r="F608" t="n">
         <v>4745700</v>
@@ -12612,16 +12612,16 @@
         <v>44677</v>
       </c>
       <c r="B610" t="n">
-        <v>4.079021453857422</v>
+        <v>4.079020977020264</v>
       </c>
       <c r="C610" t="n">
-        <v>4.189017874905755</v>
+        <v>4.189017385210027</v>
       </c>
       <c r="D610" t="n">
-        <v>4.024023461875849</v>
+        <v>4.02402299146795</v>
       </c>
       <c r="E610" t="n">
-        <v>4.042356125869706</v>
+        <v>4.042355653318721</v>
       </c>
       <c r="F610" t="n">
         <v>5064800</v>
@@ -12632,16 +12632,16 @@
         <v>44678</v>
       </c>
       <c r="B611" t="n">
-        <v>3.97819185256958</v>
+        <v>3.978191614151001</v>
       </c>
       <c r="C611" t="n">
-        <v>4.170685034925215</v>
+        <v>4.170684784970252</v>
       </c>
       <c r="D611" t="n">
-        <v>3.941526526128999</v>
+        <v>3.941526289907824</v>
       </c>
       <c r="E611" t="n">
-        <v>4.170685034925215</v>
+        <v>4.170684784970252</v>
       </c>
       <c r="F611" t="n">
         <v>4173400</v>
@@ -12812,16 +12812,16 @@
         <v>44691</v>
       </c>
       <c r="B620" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C620" t="n">
-        <v>2.887397395893507</v>
+        <v>2.887397154408436</v>
       </c>
       <c r="D620" t="n">
-        <v>2.694904207028261</v>
+        <v>2.694903981642197</v>
       </c>
       <c r="E620" t="n">
-        <v>2.814066521989905</v>
+        <v>2.8140662866378</v>
       </c>
       <c r="F620" t="n">
         <v>7309900</v>
@@ -12852,16 +12852,16 @@
         <v>44693</v>
       </c>
       <c r="B622" t="n">
-        <v>2.942394971847534</v>
+        <v>2.942395210266113</v>
       </c>
       <c r="C622" t="n">
-        <v>3.02489194747728</v>
+        <v>3.024892192580485</v>
       </c>
       <c r="D622" t="n">
-        <v>2.814066124547592</v>
+        <v>2.814066352567845</v>
       </c>
       <c r="E622" t="n">
-        <v>2.869064326843316</v>
+        <v>2.869064559320005</v>
       </c>
       <c r="F622" t="n">
         <v>3382300</v>
@@ -12872,16 +12872,16 @@
         <v>44694</v>
       </c>
       <c r="B623" t="n">
-        <v>3.043225049972534</v>
+        <v>3.043224811553955</v>
       </c>
       <c r="C623" t="n">
-        <v>3.10738959219715</v>
+        <v>3.107389348751661</v>
       </c>
       <c r="D623" t="n">
-        <v>2.942395398472212</v>
+        <v>2.942395167953036</v>
       </c>
       <c r="E623" t="n">
-        <v>2.969894394335936</v>
+        <v>2.969894161662377</v>
       </c>
       <c r="F623" t="n">
         <v>4357400</v>
@@ -12932,16 +12932,16 @@
         <v>44699</v>
       </c>
       <c r="B626" t="n">
-        <v>2.85989785194397</v>
+        <v>2.859898090362549</v>
       </c>
       <c r="C626" t="n">
-        <v>3.089056342075733</v>
+        <v>3.089056599598365</v>
       </c>
       <c r="D626" t="n">
-        <v>2.850731521080402</v>
+        <v>2.85073175873482</v>
       </c>
       <c r="E626" t="n">
-        <v>3.079890011212165</v>
+        <v>3.079890267970636</v>
       </c>
       <c r="F626" t="n">
         <v>5243400</v>
@@ -13112,16 +13112,16 @@
         <v>44712</v>
       </c>
       <c r="B635" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C635" t="n">
-        <v>3.015726042775277</v>
+        <v>3.015725790557546</v>
       </c>
       <c r="D635" t="n">
-        <v>2.804900190069778</v>
+        <v>2.804899955484291</v>
       </c>
       <c r="E635" t="n">
-        <v>2.988227047014898</v>
+        <v>2.988226797097023</v>
       </c>
       <c r="F635" t="n">
         <v>7519800</v>
@@ -13192,16 +13192,16 @@
         <v>44718</v>
       </c>
       <c r="B639" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C639" t="n">
-        <v>2.859898153024676</v>
+        <v>2.859897899145521</v>
       </c>
       <c r="D639" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="E639" t="n">
-        <v>2.81406649388183</v>
+        <v>2.814066244071248</v>
       </c>
       <c r="F639" t="n">
         <v>3115900</v>
@@ -13212,16 +13212,16 @@
         <v>44719</v>
       </c>
       <c r="B640" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C640" t="n">
-        <v>2.713236544142034</v>
+        <v>2.713236786657148</v>
       </c>
       <c r="D640" t="n">
-        <v>2.584907694170964</v>
+        <v>2.584907925215759</v>
       </c>
       <c r="E640" t="n">
-        <v>2.658238559244103</v>
+        <v>2.658238796843375</v>
       </c>
       <c r="F640" t="n">
         <v>2825300</v>
@@ -13232,16 +13232,16 @@
         <v>44720</v>
       </c>
       <c r="B641" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C641" t="n">
-        <v>2.722402874958356</v>
+        <v>2.722403118292777</v>
       </c>
       <c r="D641" t="n">
-        <v>2.63990589761146</v>
+        <v>2.639906133572117</v>
       </c>
       <c r="E641" t="n">
-        <v>2.649072228427781</v>
+        <v>2.649072465207746</v>
       </c>
       <c r="F641" t="n">
         <v>3025200</v>
@@ -13272,16 +13272,16 @@
         <v>44722</v>
       </c>
       <c r="B643" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C643" t="n">
-        <v>2.63073952891308</v>
+        <v>2.630739779558241</v>
       </c>
       <c r="D643" t="n">
-        <v>2.493244557226074</v>
+        <v>2.493244794771327</v>
       </c>
       <c r="E643" t="n">
-        <v>2.594074203129878</v>
+        <v>2.594074450281731</v>
       </c>
       <c r="F643" t="n">
         <v>4379600</v>
@@ -13292,16 +13292,16 @@
         <v>44725</v>
       </c>
       <c r="B644" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C644" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="D644" t="n">
-        <v>2.282418486052185</v>
+        <v>2.282418717049181</v>
       </c>
       <c r="E644" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="F644" t="n">
         <v>5369000</v>
@@ -13312,16 +13312,16 @@
         <v>44726</v>
       </c>
       <c r="B645" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C645" t="n">
-        <v>2.401580660851382</v>
+        <v>2.401580915813275</v>
       </c>
       <c r="D645" t="n">
-        <v>2.236586719791586</v>
+        <v>2.236586957237029</v>
       </c>
       <c r="E645" t="n">
-        <v>2.374081670674749</v>
+        <v>2.374081922717234</v>
       </c>
       <c r="F645" t="n">
         <v>2610500</v>
@@ -13392,16 +13392,16 @@
         <v>44733</v>
       </c>
       <c r="B649" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="C649" t="n">
-        <v>2.328250420451433</v>
+        <v>2.328250174279411</v>
       </c>
       <c r="D649" t="n">
-        <v>2.236587104111843</v>
+        <v>2.236586867631624</v>
       </c>
       <c r="E649" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="F649" t="n">
         <v>3435200</v>
@@ -13412,16 +13412,16 @@
         <v>44734</v>
       </c>
       <c r="B650" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C650" t="n">
-        <v>2.300751030203729</v>
+        <v>2.300751274461124</v>
       </c>
       <c r="D650" t="n">
-        <v>2.190755069497199</v>
+        <v>2.190755302076961</v>
       </c>
       <c r="E650" t="n">
-        <v>2.236586719791586</v>
+        <v>2.236586957237029</v>
       </c>
       <c r="F650" t="n">
         <v>3144500</v>
@@ -13452,16 +13452,16 @@
         <v>44736</v>
       </c>
       <c r="B652" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C652" t="n">
-        <v>2.355749010556994</v>
+        <v>2.355749260653206</v>
       </c>
       <c r="D652" t="n">
-        <v>2.209087729614954</v>
+        <v>2.209087964140989</v>
       </c>
       <c r="E652" t="n">
-        <v>2.337416350439239</v>
+        <v>2.337416598589179</v>
       </c>
       <c r="F652" t="n">
         <v>3887000</v>
@@ -13472,16 +13472,16 @@
         <v>44739</v>
       </c>
       <c r="B653" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C653" t="n">
-        <v>2.291584773416974</v>
+        <v>2.291585025979039</v>
       </c>
       <c r="D653" t="n">
-        <v>2.154089599594934</v>
+        <v>2.154089837003265</v>
       </c>
       <c r="E653" t="n">
-        <v>2.273252112713042</v>
+        <v>2.273252363254613</v>
       </c>
       <c r="F653" t="n">
         <v>3063200</v>
@@ -13512,16 +13512,16 @@
         <v>44741</v>
       </c>
       <c r="B655" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C655" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="D655" t="n">
-        <v>2.016594984404464</v>
+        <v>2.016594758317869</v>
       </c>
       <c r="E655" t="n">
-        <v>2.089925639587051</v>
+        <v>2.089925405279133</v>
       </c>
       <c r="F655" t="n">
         <v>5733700</v>
@@ -13632,16 +13632,16 @@
         <v>44749</v>
       </c>
       <c r="B661" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C661" t="n">
-        <v>2.392414452347443</v>
+        <v>2.392414694476813</v>
       </c>
       <c r="D661" t="n">
-        <v>2.300751147101395</v>
+        <v>2.300751379953786</v>
       </c>
       <c r="E661" t="n">
-        <v>2.337416469199814</v>
+        <v>2.337416705762997</v>
       </c>
       <c r="F661" t="n">
         <v>2762300</v>
@@ -13652,16 +13652,16 @@
         <v>44750</v>
       </c>
       <c r="B662" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="C662" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="D662" t="n">
-        <v>2.300751402022951</v>
+        <v>2.300751173614302</v>
       </c>
       <c r="E662" t="n">
-        <v>2.337416728183861</v>
+        <v>2.337416496135238</v>
       </c>
       <c r="F662" t="n">
         <v>2746100</v>
@@ -13672,16 +13672,16 @@
         <v>44753</v>
       </c>
       <c r="B663" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C663" t="n">
-        <v>2.383248305010609</v>
+        <v>2.38324806191716</v>
       </c>
       <c r="D663" t="n">
-        <v>2.273252330260538</v>
+        <v>2.273252098386777</v>
       </c>
       <c r="E663" t="n">
-        <v>2.346582980093919</v>
+        <v>2.346582740740366</v>
       </c>
       <c r="F663" t="n">
         <v>1807800</v>
@@ -13692,16 +13692,16 @@
         <v>44754</v>
       </c>
       <c r="B664" t="n">
-        <v>2.401581048965454</v>
+        <v>2.401580810546875</v>
       </c>
       <c r="C664" t="n">
-        <v>2.447412925209175</v>
+        <v>2.447412682240605</v>
       </c>
       <c r="D664" t="n">
-        <v>2.254919744321813</v>
+        <v>2.254919520463134</v>
       </c>
       <c r="E664" t="n">
-        <v>2.355749391264316</v>
+        <v>2.355749157395706</v>
       </c>
       <c r="F664" t="n">
         <v>5712200</v>
@@ -13752,16 +13752,16 @@
         <v>44757</v>
       </c>
       <c r="B667" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C667" t="n">
-        <v>2.245753121657145</v>
+        <v>2.245753369167974</v>
       </c>
       <c r="D667" t="n">
-        <v>2.135756938891002</v>
+        <v>2.135757174278839</v>
       </c>
       <c r="E667" t="n">
-        <v>2.227420460953214</v>
+        <v>2.227420706443548</v>
       </c>
       <c r="F667" t="n">
         <v>2806200</v>
@@ -13772,16 +13772,16 @@
         <v>44760</v>
       </c>
       <c r="B668" t="n">
-        <v>2.254919767379761</v>
+        <v>2.254919528961182</v>
       </c>
       <c r="C668" t="n">
-        <v>2.346583083719351</v>
+        <v>2.346582835608969</v>
       </c>
       <c r="D668" t="n">
-        <v>2.199921777576007</v>
+        <v>2.19992154497251</v>
       </c>
       <c r="E668" t="n">
-        <v>2.199921777576007</v>
+        <v>2.19992154497251</v>
       </c>
       <c r="F668" t="n">
         <v>4381400</v>
@@ -13832,16 +13832,16 @@
         <v>44763</v>
       </c>
       <c r="B671" t="n">
-        <v>2.383248090744019</v>
+        <v>2.383248329162598</v>
       </c>
       <c r="C671" t="n">
-        <v>2.474911613337284</v>
+        <v>2.474911860925822</v>
       </c>
       <c r="D671" t="n">
-        <v>2.346582769123735</v>
+        <v>2.346583003874339</v>
       </c>
       <c r="E671" t="n">
-        <v>2.364915429933876</v>
+        <v>2.364915666518468</v>
       </c>
       <c r="F671" t="n">
         <v>3831200</v>
@@ -13872,16 +13872,16 @@
         <v>44767</v>
       </c>
       <c r="B673" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C673" t="n">
-        <v>2.392414452347443</v>
+        <v>2.392414694476813</v>
       </c>
       <c r="D673" t="n">
-        <v>2.25491949447837</v>
+        <v>2.254919722692273</v>
       </c>
       <c r="E673" t="n">
-        <v>2.300751147101395</v>
+        <v>2.300751379953786</v>
       </c>
       <c r="F673" t="n">
         <v>3311300</v>
@@ -13892,16 +13892,16 @@
         <v>44768</v>
       </c>
       <c r="B674" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C674" t="n">
-        <v>2.520743493812202</v>
+        <v>2.520743251874533</v>
       </c>
       <c r="D674" t="n">
-        <v>2.300751325610525</v>
+        <v>2.300751104787417</v>
       </c>
       <c r="E674" t="n">
-        <v>2.374081975496892</v>
+        <v>2.374081747635604</v>
       </c>
       <c r="F674" t="n">
         <v>4848400</v>
@@ -13912,16 +13912,16 @@
         <v>44769</v>
       </c>
       <c r="B675" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C675" t="n">
-        <v>2.603240801706716</v>
+        <v>2.603240558142417</v>
       </c>
       <c r="D675" t="n">
-        <v>2.419914153978682</v>
+        <v>2.419913927566782</v>
       </c>
       <c r="E675" t="n">
-        <v>2.502411145456297</v>
+        <v>2.502410911325818</v>
       </c>
       <c r="F675" t="n">
         <v>5961800</v>
@@ -13952,16 +13952,16 @@
         <v>44771</v>
       </c>
       <c r="B677" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C677" t="n">
-        <v>2.603240523687103</v>
+        <v>2.603240282723132</v>
       </c>
       <c r="D677" t="n">
-        <v>2.493244546797579</v>
+        <v>2.493244316015175</v>
       </c>
       <c r="E677" t="n">
-        <v>2.566575198057261</v>
+        <v>2.566574960487146</v>
       </c>
       <c r="F677" t="n">
         <v>2895400</v>
@@ -13972,16 +13972,16 @@
         <v>44774</v>
       </c>
       <c r="B678" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C678" t="n">
-        <v>2.749902171081845</v>
+        <v>2.749901926967264</v>
       </c>
       <c r="D678" t="n">
-        <v>2.520743656825025</v>
+        <v>2.520743433053326</v>
       </c>
       <c r="E678" t="n">
-        <v>2.57574164779644</v>
+        <v>2.575741419142454</v>
       </c>
       <c r="F678" t="n">
         <v>6003000</v>
@@ -13992,16 +13992,16 @@
         <v>44775</v>
       </c>
       <c r="B679" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C679" t="n">
-        <v>2.740735713341587</v>
+        <v>2.740735459650637</v>
       </c>
       <c r="D679" t="n">
-        <v>2.548242535242341</v>
+        <v>2.548242299369153</v>
       </c>
       <c r="E679" t="n">
-        <v>2.676571393489365</v>
+        <v>2.676571145737662</v>
       </c>
       <c r="F679" t="n">
         <v>4865400</v>
@@ -14032,16 +14032,16 @@
         <v>44777</v>
       </c>
       <c r="B681" t="n">
-        <v>2.85989785194397</v>
+        <v>2.859898090362549</v>
       </c>
       <c r="C681" t="n">
-        <v>2.878230732213672</v>
+        <v>2.878230972160592</v>
       </c>
       <c r="D681" t="n">
-        <v>2.704070227263316</v>
+        <v>2.704070452691151</v>
       </c>
       <c r="E681" t="n">
-        <v>2.722402888990452</v>
+        <v>2.72240311594661</v>
       </c>
       <c r="F681" t="n">
         <v>7566500</v>
@@ -14052,16 +14052,16 @@
         <v>44778</v>
       </c>
       <c r="B682" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C682" t="n">
-        <v>2.969894420271998</v>
+        <v>2.969894169468031</v>
       </c>
       <c r="D682" t="n">
-        <v>2.731569568829172</v>
+        <v>2.731569338151449</v>
       </c>
       <c r="E682" t="n">
-        <v>2.869064767891131</v>
+        <v>2.869064525602105</v>
       </c>
       <c r="F682" t="n">
         <v>6497600</v>
@@ -14072,16 +14072,16 @@
         <v>44781</v>
       </c>
       <c r="B683" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="C683" t="n">
-        <v>2.924062679704158</v>
+        <v>2.924062427027984</v>
       </c>
       <c r="D683" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="E683" t="n">
-        <v>2.850731806900742</v>
+        <v>2.850731560561287</v>
       </c>
       <c r="F683" t="n">
         <v>8446700</v>
@@ -14132,16 +14132,16 @@
         <v>44784</v>
       </c>
       <c r="B686" t="n">
-        <v>3.034058570861816</v>
+        <v>3.034058332443237</v>
       </c>
       <c r="C686" t="n">
-        <v>3.153221099034329</v>
+        <v>3.15322085125187</v>
       </c>
       <c r="D686" t="n">
-        <v>2.887397266701901</v>
+        <v>2.887397039808076</v>
       </c>
       <c r="E686" t="n">
-        <v>2.896563598211896</v>
+        <v>2.896563370597774</v>
       </c>
       <c r="F686" t="n">
         <v>13306300</v>
@@ -14232,16 +14232,16 @@
         <v>44791</v>
       </c>
       <c r="B691" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="C691" t="n">
-        <v>3.272383248987116</v>
+        <v>3.272383506912668</v>
       </c>
       <c r="D691" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="E691" t="n">
-        <v>3.263216917924395</v>
+        <v>3.263217175127469</v>
       </c>
       <c r="F691" t="n">
         <v>6872400</v>
@@ -14392,16 +14392,16 @@
         <v>44803</v>
       </c>
       <c r="B699" t="n">
-        <v>3.024892091751099</v>
+        <v>3.024892330169678</v>
       </c>
       <c r="C699" t="n">
-        <v>3.162387276234473</v>
+        <v>3.162387525490268</v>
       </c>
       <c r="D699" t="n">
-        <v>2.951561443249337</v>
+        <v>2.951561675888077</v>
       </c>
       <c r="E699" t="n">
-        <v>3.07989007812742</v>
+        <v>3.079890320880878</v>
       </c>
       <c r="F699" t="n">
         <v>4644000</v>
@@ -14432,16 +14432,16 @@
         <v>44805</v>
       </c>
       <c r="B701" t="n">
-        <v>3.125722169876099</v>
+        <v>3.12572193145752</v>
       </c>
       <c r="C701" t="n">
-        <v>3.134888501577799</v>
+        <v>3.134888262460046</v>
       </c>
       <c r="D701" t="n">
-        <v>2.942395317299501</v>
+        <v>2.94239509286442</v>
       </c>
       <c r="E701" t="n">
-        <v>2.951561649001202</v>
+        <v>2.951561423866946</v>
       </c>
       <c r="F701" t="n">
         <v>5408300</v>
@@ -14552,16 +14552,16 @@
         <v>44816</v>
       </c>
       <c r="B707" t="n">
-        <v>3.39154577255249</v>
+        <v>3.391546010971069</v>
       </c>
       <c r="C707" t="n">
-        <v>3.437377427882408</v>
+        <v>3.437377669522857</v>
       </c>
       <c r="D707" t="n">
-        <v>3.327381455090605</v>
+        <v>3.327381688998567</v>
       </c>
       <c r="E707" t="n">
-        <v>3.327381455090605</v>
+        <v>3.327381688998567</v>
       </c>
       <c r="F707" t="n">
         <v>4227100</v>
@@ -14732,16 +14732,16 @@
         <v>44827</v>
       </c>
       <c r="B716" t="n">
-        <v>3.134888172149658</v>
+        <v>3.134888410568237</v>
       </c>
       <c r="C716" t="n">
-        <v>3.254050471749655</v>
+        <v>3.25405071923092</v>
       </c>
       <c r="D716" t="n">
-        <v>3.098222849195813</v>
+        <v>3.098223084825873</v>
       </c>
       <c r="E716" t="n">
-        <v>3.098222849195813</v>
+        <v>3.098223084825873</v>
       </c>
       <c r="F716" t="n">
         <v>4782400</v>
@@ -14792,16 +14792,16 @@
         <v>44832</v>
       </c>
       <c r="B719" t="n">
-        <v>2.942394971847534</v>
+        <v>2.942395210266113</v>
       </c>
       <c r="C719" t="n">
-        <v>2.960727633098589</v>
+        <v>2.96072787300264</v>
       </c>
       <c r="D719" t="n">
-        <v>2.841565116424174</v>
+        <v>2.841565346672636</v>
       </c>
       <c r="E719" t="n">
-        <v>2.896563318719898</v>
+        <v>2.896563553424795</v>
       </c>
       <c r="F719" t="n">
         <v>3561500</v>
@@ -14812,16 +14812,16 @@
         <v>44833</v>
       </c>
       <c r="B720" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C720" t="n">
-        <v>2.905730096029628</v>
+        <v>2.90572985064426</v>
       </c>
       <c r="D720" t="n">
-        <v>2.795733893071542</v>
+        <v>2.79573365697522</v>
       </c>
       <c r="E720" t="n">
-        <v>2.896563763995004</v>
+        <v>2.896563519383722</v>
       </c>
       <c r="F720" t="n">
         <v>3966200</v>
@@ -14932,16 +14932,16 @@
         <v>44841</v>
       </c>
       <c r="B726" t="n">
-        <v>3.44654369354248</v>
+        <v>3.44654393196106</v>
       </c>
       <c r="C726" t="n">
-        <v>3.602371537249589</v>
+        <v>3.602371786447736</v>
       </c>
       <c r="D726" t="n">
-        <v>3.419044700866385</v>
+        <v>3.41904493738269</v>
       </c>
       <c r="E726" t="n">
-        <v>3.464876355326544</v>
+        <v>3.464876595013306</v>
       </c>
       <c r="F726" t="n">
         <v>4739800</v>
@@ -15012,16 +15012,16 @@
         <v>44848</v>
       </c>
       <c r="B730" t="n">
-        <v>3.052391052246094</v>
+        <v>3.052391290664673</v>
       </c>
       <c r="C730" t="n">
-        <v>3.199052566221344</v>
+        <v>3.199052816095478</v>
       </c>
       <c r="D730" t="n">
-        <v>2.997393066458838</v>
+        <v>2.997393300581591</v>
       </c>
       <c r="E730" t="n">
-        <v>3.153220911398631</v>
+        <v>3.153221157692909</v>
       </c>
       <c r="F730" t="n">
         <v>2652600</v>
@@ -15032,16 +15032,16 @@
         <v>44851</v>
       </c>
       <c r="B731" t="n">
-        <v>3.034058570861816</v>
+        <v>3.034058332443237</v>
       </c>
       <c r="C731" t="n">
-        <v>3.116555772994351</v>
+        <v>3.11655552809308</v>
       </c>
       <c r="D731" t="n">
-        <v>3.024892239351822</v>
+        <v>3.02489200165354</v>
       </c>
       <c r="E731" t="n">
-        <v>3.07989022841179</v>
+        <v>3.079889986391725</v>
       </c>
       <c r="F731" t="n">
         <v>3944900</v>
@@ -15092,16 +15092,16 @@
         <v>44854</v>
       </c>
       <c r="B734" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C734" t="n">
-        <v>2.95156135187282</v>
+        <v>2.951561601940523</v>
       </c>
       <c r="D734" t="n">
-        <v>2.795733510088233</v>
+        <v>2.795733746953598</v>
       </c>
       <c r="E734" t="n">
-        <v>2.942395021093878</v>
+        <v>2.942395270384973</v>
       </c>
       <c r="F734" t="n">
         <v>4518300</v>
@@ -15112,16 +15112,16 @@
         <v>44855</v>
       </c>
       <c r="B735" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C735" t="n">
-        <v>2.869064374862337</v>
+        <v>2.869064617940577</v>
       </c>
       <c r="D735" t="n">
-        <v>2.685737540740923</v>
+        <v>2.685737768287004</v>
       </c>
       <c r="E735" t="n">
-        <v>2.804899840867176</v>
+        <v>2.804900078509148</v>
       </c>
       <c r="F735" t="n">
         <v>6831600</v>
@@ -15132,16 +15132,16 @@
         <v>44858</v>
       </c>
       <c r="B736" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C736" t="n">
-        <v>2.814066387171744</v>
+        <v>2.814066144805841</v>
       </c>
       <c r="D736" t="n">
-        <v>2.704070409399987</v>
+        <v>2.704070176507662</v>
       </c>
       <c r="E736" t="n">
-        <v>2.795733724209785</v>
+        <v>2.795733483422811</v>
       </c>
       <c r="F736" t="n">
         <v>4201100</v>
@@ -15172,16 +15172,16 @@
         <v>44860</v>
       </c>
       <c r="B738" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C738" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="D738" t="n">
-        <v>2.438246512690039</v>
+        <v>2.438246278670322</v>
       </c>
       <c r="E738" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="F738" t="n">
         <v>9447400</v>
@@ -15232,16 +15232,16 @@
         <v>44865</v>
       </c>
       <c r="B741" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C741" t="n">
-        <v>2.832399050133704</v>
+        <v>2.832398806188871</v>
       </c>
       <c r="D741" t="n">
-        <v>2.557408887161731</v>
+        <v>2.55740866690086</v>
       </c>
       <c r="E741" t="n">
-        <v>2.59407421308565</v>
+        <v>2.59407398966692</v>
       </c>
       <c r="F741" t="n">
         <v>6603200</v>
@@ -15292,16 +15292,16 @@
         <v>44869</v>
       </c>
       <c r="B744" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="C744" t="n">
-        <v>2.933228914967061</v>
+        <v>2.933228662338098</v>
       </c>
       <c r="D744" t="n">
-        <v>2.768234729766846</v>
+        <v>2.768234491348267</v>
       </c>
       <c r="E744" t="n">
-        <v>2.924062583486082</v>
+        <v>2.924062331646583</v>
       </c>
       <c r="F744" t="n">
         <v>7869400</v>
@@ -15392,16 +15392,16 @@
         <v>44876</v>
       </c>
       <c r="B749" t="n">
-        <v>2.245753049850464</v>
+        <v>2.245753288269043</v>
       </c>
       <c r="C749" t="n">
-        <v>2.429079869570562</v>
+        <v>2.429080127451886</v>
       </c>
       <c r="D749" t="n">
-        <v>2.227420389732709</v>
+        <v>2.227420626205016</v>
       </c>
       <c r="E749" t="n">
-        <v>2.319083690321484</v>
+        <v>2.319083936525152</v>
       </c>
       <c r="F749" t="n">
         <v>8256600</v>
@@ -15512,16 +15512,16 @@
         <v>44887</v>
       </c>
       <c r="B755" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C755" t="n">
-        <v>2.209087984933213</v>
+        <v>2.209088230483989</v>
       </c>
       <c r="D755" t="n">
-        <v>2.108258124089469</v>
+        <v>2.10825835843252</v>
       </c>
       <c r="E755" t="n">
-        <v>2.181588991578348</v>
+        <v>2.181589234072479</v>
       </c>
       <c r="F755" t="n">
         <v>3236000</v>
@@ -15572,16 +15572,16 @@
         <v>44890</v>
       </c>
       <c r="B758" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C758" t="n">
-        <v>2.254919640524655</v>
+        <v>2.25491989116984</v>
       </c>
       <c r="D758" t="n">
-        <v>2.117424455207757</v>
+        <v>2.117424690569691</v>
       </c>
       <c r="E758" t="n">
-        <v>2.22742064716979</v>
+        <v>2.22742089475833</v>
       </c>
       <c r="F758" t="n">
         <v>2578200</v>
@@ -15592,16 +15592,16 @@
         <v>44893</v>
       </c>
       <c r="B759" t="n">
-        <v>2.044094085693359</v>
+        <v>2.04409384727478</v>
       </c>
       <c r="C759" t="n">
-        <v>2.144923741778154</v>
+        <v>2.144923491599029</v>
       </c>
       <c r="D759" t="n">
-        <v>2.034927753322014</v>
+        <v>2.034927515972576</v>
       </c>
       <c r="E759" t="n">
-        <v>2.135757409406809</v>
+        <v>2.135757160296825</v>
       </c>
       <c r="F759" t="n">
         <v>2781000</v>
@@ -15672,16 +15672,16 @@
         <v>44897</v>
       </c>
       <c r="B763" t="n">
-        <v>2.181589126586914</v>
+        <v>2.181588888168335</v>
       </c>
       <c r="C763" t="n">
-        <v>2.199921789958015</v>
+        <v>2.199921549535921</v>
       </c>
       <c r="D763" t="n">
-        <v>2.099091922874372</v>
+        <v>2.099091693471637</v>
       </c>
       <c r="E763" t="n">
-        <v>2.154089912987676</v>
+        <v>2.154089677574394</v>
       </c>
       <c r="F763" t="n">
         <v>2941200</v>
@@ -15772,16 +15772,16 @@
         <v>44904</v>
       </c>
       <c r="B768" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C768" t="n">
-        <v>2.172422626667462</v>
+        <v>2.172422383110556</v>
       </c>
       <c r="D768" t="n">
-        <v>2.071592975791404</v>
+        <v>2.071592743538817</v>
       </c>
       <c r="E768" t="n">
-        <v>2.135757299076168</v>
+        <v>2.135757059629924</v>
       </c>
       <c r="F768" t="n">
         <v>2468100</v>
@@ -15792,16 +15792,16 @@
         <v>44907</v>
       </c>
       <c r="B769" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="C769" t="n">
-        <v>2.135757299076168</v>
+        <v>2.135757059629924</v>
       </c>
       <c r="D769" t="n">
-        <v>2.034927648200111</v>
+        <v>2.034927420058185</v>
       </c>
       <c r="E769" t="n">
-        <v>2.126590967178345</v>
+        <v>2.126590728759766</v>
       </c>
       <c r="F769" t="n">
         <v>2948100</v>
@@ -15812,16 +15812,16 @@
         <v>44908</v>
       </c>
       <c r="B770" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C770" t="n">
-        <v>2.190755340574407</v>
+        <v>2.190755471267162</v>
       </c>
       <c r="D770" t="n">
-        <v>1.989095835783838</v>
+        <v>1.989095954446297</v>
       </c>
       <c r="E770" t="n">
-        <v>2.144923466066379</v>
+        <v>2.144923594024966</v>
       </c>
       <c r="F770" t="n">
         <v>3298100</v>
@@ -15832,16 +15832,16 @@
         <v>44909</v>
       </c>
       <c r="B771" t="n">
-        <v>1.979929566383362</v>
+        <v>1.979929685592651</v>
       </c>
       <c r="C771" t="n">
-        <v>2.007428560820864</v>
+        <v>2.007428681685836</v>
       </c>
       <c r="D771" t="n">
-        <v>1.888266033049108</v>
+        <v>1.888266146739441</v>
       </c>
       <c r="E771" t="n">
-        <v>1.970763234904195</v>
+        <v>1.97076335356159</v>
       </c>
       <c r="F771" t="n">
         <v>6743600</v>
@@ -15852,16 +15852,16 @@
         <v>44910</v>
       </c>
       <c r="B772" t="n">
-        <v>1.906598567962646</v>
+        <v>1.906598687171936</v>
       </c>
       <c r="C772" t="n">
-        <v>2.044093749458731</v>
+        <v>2.04409387726485</v>
       </c>
       <c r="D772" t="n">
-        <v>1.897432237099079</v>
+        <v>1.897432355735247</v>
       </c>
       <c r="E772" t="n">
-        <v>1.952430440823052</v>
+        <v>1.952430562897961</v>
       </c>
       <c r="F772" t="n">
         <v>3868500</v>
@@ -15912,16 +15912,16 @@
         <v>44915</v>
       </c>
       <c r="B775" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C775" t="n">
-        <v>2.108258224859735</v>
+        <v>2.10825798114297</v>
       </c>
       <c r="D775" t="n">
-        <v>1.879099717406664</v>
+        <v>1.879099500180852</v>
       </c>
       <c r="E775" t="n">
-        <v>1.924931375188761</v>
+        <v>1.924931152664764</v>
       </c>
       <c r="F775" t="n">
         <v>8464700</v>
@@ -15932,16 +15932,16 @@
         <v>44916</v>
       </c>
       <c r="B776" t="n">
-        <v>1.970763087272644</v>
+        <v>1.970763206481934</v>
       </c>
       <c r="C776" t="n">
-        <v>2.108258049160288</v>
+        <v>2.108258176686496</v>
       </c>
       <c r="D776" t="n">
-        <v>1.961596756480134</v>
+        <v>1.961596875134963</v>
       </c>
       <c r="E776" t="n">
-        <v>2.05326006440523</v>
+        <v>2.053260188604671</v>
       </c>
       <c r="F776" t="n">
         <v>5125400</v>
@@ -15952,16 +15952,16 @@
         <v>44917</v>
       </c>
       <c r="B777" t="n">
-        <v>1.906598567962646</v>
+        <v>1.906598687171936</v>
       </c>
       <c r="C777" t="n">
-        <v>1.989095764277324</v>
+        <v>1.989095888644717</v>
       </c>
       <c r="D777" t="n">
-        <v>1.869933244508375</v>
+        <v>1.869933361425181</v>
       </c>
       <c r="E777" t="n">
-        <v>1.952430440823052</v>
+        <v>1.952430562897961</v>
       </c>
       <c r="F777" t="n">
         <v>5426000</v>
@@ -15972,16 +15972,16 @@
         <v>44918</v>
       </c>
       <c r="B778" t="n">
-        <v>1.98909592628479</v>
+        <v>1.9890958070755</v>
       </c>
       <c r="C778" t="n">
-        <v>2.016594921115226</v>
+        <v>2.016594800257883</v>
       </c>
       <c r="D778" t="n">
-        <v>1.906598723250898</v>
+        <v>1.906598608985781</v>
       </c>
       <c r="E778" t="n">
-        <v>1.915765054861043</v>
+        <v>1.915764940046575</v>
       </c>
       <c r="F778" t="n">
         <v>4257800</v>
@@ -15992,16 +15992,16 @@
         <v>44921</v>
       </c>
       <c r="B779" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C779" t="n">
-        <v>2.044093822942382</v>
+        <v>2.044093944885827</v>
       </c>
       <c r="D779" t="n">
-        <v>1.952430511011476</v>
+        <v>1.95243062748661</v>
       </c>
       <c r="E779" t="n">
-        <v>1.989095835783838</v>
+        <v>1.989095954446297</v>
       </c>
       <c r="F779" t="n">
         <v>2247800</v>
@@ -16012,16 +16012,16 @@
         <v>44922</v>
       </c>
       <c r="B780" t="n">
-        <v>1.970763087272644</v>
+        <v>1.970763206481934</v>
       </c>
       <c r="C780" t="n">
-        <v>2.06242639519774</v>
+        <v>2.062426519951642</v>
       </c>
       <c r="D780" t="n">
-        <v>1.934097545560041</v>
+        <v>1.934097662551472</v>
       </c>
       <c r="E780" t="n">
-        <v>2.007428410442682</v>
+        <v>2.007428531869817</v>
       </c>
       <c r="F780" t="n">
         <v>3370000</v>
@@ -16032,16 +16032,16 @@
         <v>44923</v>
       </c>
       <c r="B781" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="C781" t="n">
-        <v>2.144923448562622</v>
+        <v>2.144923686981201</v>
       </c>
       <c r="D781" t="n">
-        <v>1.952430495078567</v>
+        <v>1.952430712100627</v>
       </c>
       <c r="E781" t="n">
-        <v>1.970763157315144</v>
+        <v>1.970763376374967</v>
       </c>
       <c r="F781" t="n">
         <v>4579800</v>
@@ -16112,16 +16112,16 @@
         <v>44930</v>
       </c>
       <c r="B785" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C785" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="D785" t="n">
-        <v>1.952430588400603</v>
+        <v>1.952430362697669</v>
       </c>
       <c r="E785" t="n">
-        <v>1.961596919957022</v>
+        <v>1.961596693194451</v>
       </c>
       <c r="F785" t="n">
         <v>2931500</v>
@@ -16172,16 +16172,16 @@
         <v>44935</v>
       </c>
       <c r="B788" t="n">
-        <v>2.163255929946899</v>
+        <v>2.163256168365479</v>
       </c>
       <c r="C788" t="n">
-        <v>2.190755139545351</v>
+        <v>2.190755380994696</v>
       </c>
       <c r="D788" t="n">
-        <v>2.071592626427242</v>
+        <v>2.071592854743348</v>
       </c>
       <c r="E788" t="n">
-        <v>2.135756938891002</v>
+        <v>2.135757174278839</v>
       </c>
       <c r="F788" t="n">
         <v>5355300</v>
@@ -16232,16 +16232,16 @@
         <v>44938</v>
       </c>
       <c r="B791" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C791" t="n">
-        <v>2.410747517240701</v>
+        <v>2.410747271342309</v>
       </c>
       <c r="D791" t="n">
-        <v>2.190755349197985</v>
+        <v>2.19075512573899</v>
       </c>
       <c r="E791" t="n">
-        <v>2.282418661489711</v>
+        <v>2.282418428680975</v>
       </c>
       <c r="F791" t="n">
         <v>7447800</v>
@@ -16252,16 +16252,16 @@
         <v>44939</v>
       </c>
       <c r="B792" t="n">
-        <v>2.227420568466187</v>
+        <v>2.227420806884766</v>
       </c>
       <c r="C792" t="n">
-        <v>2.392414522765486</v>
+        <v>2.392414778844683</v>
       </c>
       <c r="D792" t="n">
-        <v>2.19992157608297</v>
+        <v>2.199921811558113</v>
       </c>
       <c r="E792" t="n">
-        <v>2.319083876410242</v>
+        <v>2.319084124640275</v>
       </c>
       <c r="F792" t="n">
         <v>4284200</v>
@@ -16272,16 +16272,16 @@
         <v>44942</v>
       </c>
       <c r="B793" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C793" t="n">
-        <v>2.869064517857597</v>
+        <v>2.869064242488531</v>
       </c>
       <c r="D793" t="n">
-        <v>2.29158499437473</v>
+        <v>2.291584774431394</v>
       </c>
       <c r="E793" t="n">
-        <v>2.749901993249675</v>
+        <v>2.749901729317672</v>
       </c>
       <c r="F793" t="n">
         <v>29414600</v>
@@ -16312,16 +16312,16 @@
         <v>44944</v>
       </c>
       <c r="B795" t="n">
-        <v>2.337416648864746</v>
+        <v>2.337416410446167</v>
       </c>
       <c r="C795" t="n">
-        <v>2.493244498303254</v>
+        <v>2.493244243990096</v>
       </c>
       <c r="D795" t="n">
-        <v>2.319083986406401</v>
+        <v>2.31908374985777</v>
       </c>
       <c r="E795" t="n">
-        <v>2.429080179699046</v>
+        <v>2.429079931930706</v>
       </c>
       <c r="F795" t="n">
         <v>5215700</v>
@@ -16352,16 +16352,16 @@
         <v>44946</v>
       </c>
       <c r="B797" t="n">
-        <v>2.814066171646118</v>
+        <v>2.814066410064697</v>
       </c>
       <c r="C797" t="n">
-        <v>2.823232502425061</v>
+        <v>2.823232741620247</v>
       </c>
       <c r="D797" t="n">
-        <v>2.291584880161267</v>
+        <v>2.291585074313209</v>
       </c>
       <c r="E797" t="n">
-        <v>2.30075121094021</v>
+        <v>2.300751405868758</v>
       </c>
       <c r="F797" t="n">
         <v>16674600</v>
@@ -16392,16 +16392,16 @@
         <v>44950</v>
       </c>
       <c r="B799" t="n">
-        <v>2.58490777015686</v>
+        <v>2.584908008575439</v>
       </c>
       <c r="C799" t="n">
-        <v>2.704070292814508</v>
+        <v>2.704070542224025</v>
       </c>
       <c r="D799" t="n">
-        <v>2.54824244581376</v>
+        <v>2.548242680850518</v>
       </c>
       <c r="E799" t="n">
-        <v>2.575741439071086</v>
+        <v>2.575741676644209</v>
       </c>
       <c r="F799" t="n">
         <v>6059800</v>
@@ -16452,16 +16452,16 @@
         <v>44953</v>
       </c>
       <c r="B802" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C802" t="n">
-        <v>2.933229055494139</v>
+        <v>2.933228810175975</v>
       </c>
       <c r="D802" t="n">
-        <v>2.704070538948388</v>
+        <v>2.704070312795705</v>
       </c>
       <c r="E802" t="n">
-        <v>2.731569534708767</v>
+        <v>2.731569306256229</v>
       </c>
       <c r="F802" t="n">
         <v>5877300</v>
@@ -16572,16 +16572,16 @@
         <v>44963</v>
       </c>
       <c r="B808" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C808" t="n">
-        <v>2.676571343363308</v>
+        <v>2.676571086469485</v>
       </c>
       <c r="D808" t="n">
-        <v>2.465745506397427</v>
+        <v>2.465745269738393</v>
       </c>
       <c r="E808" t="n">
-        <v>2.658238680891716</v>
+        <v>2.658238425757438</v>
       </c>
       <c r="F808" t="n">
         <v>3450900</v>
@@ -16692,16 +16692,16 @@
         <v>44971</v>
       </c>
       <c r="B814" t="n">
-        <v>2.034927368164062</v>
+        <v>2.034927606582642</v>
       </c>
       <c r="C814" t="n">
-        <v>2.172422327710077</v>
+        <v>2.172422582238004</v>
       </c>
       <c r="D814" t="n">
-        <v>2.00742837625486</v>
+        <v>2.007428611451569</v>
       </c>
       <c r="E814" t="n">
-        <v>2.099091682618869</v>
+        <v>2.099091928555144</v>
       </c>
       <c r="F814" t="n">
         <v>2996200</v>
@@ -16732,16 +16732,16 @@
         <v>44973</v>
       </c>
       <c r="B816" t="n">
-        <v>2.062426567077637</v>
+        <v>2.062426328659058</v>
       </c>
       <c r="C816" t="n">
-        <v>2.144923551085412</v>
+        <v>2.144923303130099</v>
       </c>
       <c r="D816" t="n">
-        <v>2.044093903964798</v>
+        <v>2.044093667665493</v>
       </c>
       <c r="E816" t="n">
-        <v>2.099091893303315</v>
+        <v>2.099091650646187</v>
       </c>
       <c r="F816" t="n">
         <v>2969500</v>
@@ -16752,16 +16752,16 @@
         <v>44974</v>
       </c>
       <c r="B817" t="n">
-        <v>1.961597084999084</v>
+        <v>1.961596965789795</v>
       </c>
       <c r="C817" t="n">
-        <v>2.099092069913735</v>
+        <v>2.099091942348662</v>
       </c>
       <c r="D817" t="n">
-        <v>1.961597084999084</v>
+        <v>1.961596965789795</v>
       </c>
       <c r="E817" t="n">
-        <v>2.053260408275518</v>
+        <v>2.053260283495706</v>
       </c>
       <c r="F817" t="n">
         <v>5027900</v>
@@ -16832,16 +16832,16 @@
         <v>44984</v>
       </c>
       <c r="B821" t="n">
-        <v>1.860766887664795</v>
+        <v>1.860767006874084</v>
       </c>
       <c r="C821" t="n">
-        <v>1.897432210607146</v>
+        <v>1.897432332165384</v>
       </c>
       <c r="D821" t="n">
-        <v>1.814935233986857</v>
+        <v>1.81493535025996</v>
       </c>
       <c r="E821" t="n">
-        <v>1.824101564722445</v>
+        <v>1.824101681582785</v>
       </c>
       <c r="F821" t="n">
         <v>2628700</v>
@@ -16892,16 +16892,16 @@
         <v>44987</v>
       </c>
       <c r="B824" t="n">
-        <v>1.998262166976929</v>
+        <v>1.998262286186218</v>
       </c>
       <c r="C824" t="n">
-        <v>2.144923466066379</v>
+        <v>2.144923594024966</v>
       </c>
       <c r="D824" t="n">
-        <v>1.970763173397657</v>
+        <v>1.970763290966453</v>
       </c>
       <c r="E824" t="n">
-        <v>2.126590803680198</v>
+        <v>2.126590930545122</v>
       </c>
       <c r="F824" t="n">
         <v>10060700</v>
@@ -16912,16 +16912,16 @@
         <v>44988</v>
       </c>
       <c r="B825" t="n">
-        <v>2.493244647979736</v>
+        <v>2.493244409561157</v>
       </c>
       <c r="C825" t="n">
-        <v>2.566575302215361</v>
+        <v>2.566575056784478</v>
       </c>
       <c r="D825" t="n">
-        <v>1.998262294804088</v>
+        <v>1.998262103718605</v>
       </c>
       <c r="E825" t="n">
-        <v>2.025761290142448</v>
+        <v>2.025761096427351</v>
       </c>
       <c r="F825" t="n">
         <v>20771000</v>
@@ -16972,16 +16972,16 @@
         <v>44993</v>
       </c>
       <c r="B828" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C828" t="n">
-        <v>2.90573005973376</v>
+        <v>2.905729816715452</v>
       </c>
       <c r="D828" t="n">
-        <v>2.694904207028261</v>
+        <v>2.694903981642197</v>
       </c>
       <c r="E828" t="n">
-        <v>2.704070538948388</v>
+        <v>2.704070312795705</v>
       </c>
       <c r="F828" t="n">
         <v>7104000</v>
@@ -17132,16 +17132,16 @@
         <v>45005</v>
       </c>
       <c r="B836" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C836" t="n">
-        <v>2.621573197467279</v>
+        <v>2.621573447239113</v>
       </c>
       <c r="D836" t="n">
-        <v>2.484078225780274</v>
+        <v>2.484078462452199</v>
       </c>
       <c r="E836" t="n">
-        <v>2.584907871684078</v>
+        <v>2.584908117962603</v>
       </c>
       <c r="F836" t="n">
         <v>2571800</v>
@@ -17152,16 +17152,16 @@
         <v>45006</v>
       </c>
       <c r="B837" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C837" t="n">
-        <v>2.539076214455076</v>
+        <v>2.539076456366965</v>
       </c>
       <c r="D837" t="n">
-        <v>2.474911894334474</v>
+        <v>2.474912130133071</v>
       </c>
       <c r="E837" t="n">
-        <v>2.520743551563476</v>
+        <v>2.52074379172871</v>
       </c>
       <c r="F837" t="n">
         <v>2400000</v>
@@ -17172,16 +17172,16 @@
         <v>45007</v>
       </c>
       <c r="B838" t="n">
-        <v>2.484078168869019</v>
+        <v>2.484077930450439</v>
       </c>
       <c r="C838" t="n">
-        <v>2.621573137405957</v>
+        <v>2.621572885790791</v>
       </c>
       <c r="D838" t="n">
-        <v>2.419913850218447</v>
+        <v>2.419913617958275</v>
       </c>
       <c r="E838" t="n">
-        <v>2.493244500104815</v>
+        <v>2.493244260806463</v>
       </c>
       <c r="F838" t="n">
         <v>4450900</v>
@@ -17192,16 +17192,16 @@
         <v>45008</v>
       </c>
       <c r="B839" t="n">
-        <v>2.383248090744019</v>
+        <v>2.383248329162598</v>
       </c>
       <c r="C839" t="n">
-        <v>2.493244274147426</v>
+        <v>2.493244523569952</v>
       </c>
       <c r="D839" t="n">
-        <v>2.300751117098379</v>
+        <v>2.300751347264015</v>
       </c>
       <c r="E839" t="n">
-        <v>2.484077943742355</v>
+        <v>2.484078192247887</v>
       </c>
       <c r="F839" t="n">
         <v>5291300</v>
@@ -17212,16 +17212,16 @@
         <v>45009</v>
       </c>
       <c r="B840" t="n">
-        <v>2.355749130249023</v>
+        <v>2.355749368667603</v>
       </c>
       <c r="C840" t="n">
-        <v>2.42907999298842</v>
+        <v>2.429080238828605</v>
       </c>
       <c r="D840" t="n">
-        <v>2.209087841855346</v>
+        <v>2.209088065430759</v>
       </c>
       <c r="E840" t="n">
-        <v>2.383248121822838</v>
+        <v>2.38324836302451</v>
       </c>
       <c r="F840" t="n">
         <v>8035300</v>
@@ -17232,16 +17232,16 @@
         <v>45012</v>
       </c>
       <c r="B841" t="n">
-        <v>2.502410888671875</v>
+        <v>2.502411127090454</v>
       </c>
       <c r="C841" t="n">
-        <v>2.557408877346677</v>
+        <v>2.55740912100522</v>
       </c>
       <c r="D841" t="n">
-        <v>2.36491569844229</v>
+        <v>2.364915923760939</v>
       </c>
       <c r="E841" t="n">
-        <v>2.36491569844229</v>
+        <v>2.364915923760939</v>
       </c>
       <c r="F841" t="n">
         <v>3948600</v>
@@ -17272,16 +17272,16 @@
         <v>45014</v>
       </c>
       <c r="B843" t="n">
-        <v>2.575741529464722</v>
+        <v>2.575741291046143</v>
       </c>
       <c r="C843" t="n">
-        <v>2.676571393489365</v>
+        <v>2.676571145737662</v>
       </c>
       <c r="D843" t="n">
-        <v>2.511577209612499</v>
+        <v>2.511576977133168</v>
       </c>
       <c r="E843" t="n">
-        <v>2.658238730674444</v>
+        <v>2.658238484619669</v>
       </c>
       <c r="F843" t="n">
         <v>3021100</v>
@@ -17472,16 +17472,16 @@
         <v>45029</v>
       </c>
       <c r="B853" t="n">
-        <v>2.85073184967041</v>
+        <v>2.850731611251831</v>
       </c>
       <c r="C853" t="n">
-        <v>2.960728051254518</v>
+        <v>2.960727803636499</v>
       </c>
       <c r="D853" t="n">
-        <v>2.740735866628893</v>
+        <v>2.740735637409736</v>
       </c>
       <c r="E853" t="n">
-        <v>2.804900190069778</v>
+        <v>2.804899955484291</v>
       </c>
       <c r="F853" t="n">
         <v>4826100</v>
@@ -17512,16 +17512,16 @@
         <v>45033</v>
       </c>
       <c r="B855" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="C855" t="n">
-        <v>2.841565475118138</v>
+        <v>2.841565229570771</v>
       </c>
       <c r="D855" t="n">
-        <v>2.759068489074707</v>
+        <v>2.759068250656128</v>
       </c>
       <c r="E855" t="n">
-        <v>2.777401152639914</v>
+        <v>2.77740091263716</v>
       </c>
       <c r="F855" t="n">
         <v>2017100</v>
@@ -17532,16 +17532,16 @@
         <v>45034</v>
       </c>
       <c r="B856" t="n">
-        <v>2.667404890060425</v>
+        <v>2.667405128479004</v>
       </c>
       <c r="C856" t="n">
-        <v>2.823232513937895</v>
+        <v>2.823232766284694</v>
       </c>
       <c r="D856" t="n">
-        <v>2.612406686619929</v>
+        <v>2.612406920122646</v>
       </c>
       <c r="E856" t="n">
-        <v>2.804899852305252</v>
+        <v>2.804900103013436</v>
       </c>
       <c r="F856" t="n">
         <v>3770500</v>
@@ -17572,16 +17572,16 @@
         <v>45036</v>
       </c>
       <c r="B858" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C858" t="n">
-        <v>2.603240801706716</v>
+        <v>2.603240558142417</v>
       </c>
       <c r="D858" t="n">
-        <v>2.419914153978682</v>
+        <v>2.419913927566782</v>
       </c>
       <c r="E858" t="n">
-        <v>2.484078480683494</v>
+        <v>2.484078248268254</v>
       </c>
       <c r="F858" t="n">
         <v>4312900</v>
@@ -17672,16 +17672,16 @@
         <v>45044</v>
       </c>
       <c r="B863" t="n">
-        <v>2.548242807388306</v>
+        <v>2.548242568969727</v>
       </c>
       <c r="C863" t="n">
-        <v>2.62157346647952</v>
+        <v>2.62157322119998</v>
       </c>
       <c r="D863" t="n">
-        <v>2.438246818751485</v>
+        <v>2.438246590624346</v>
       </c>
       <c r="E863" t="n">
-        <v>2.46574581591069</v>
+        <v>2.465745585210691</v>
       </c>
       <c r="F863" t="n">
         <v>4247000</v>
@@ -17692,16 +17692,16 @@
         <v>45048</v>
       </c>
       <c r="B864" t="n">
-        <v>2.68573784828186</v>
+        <v>2.685737609863281</v>
       </c>
       <c r="C864" t="n">
-        <v>2.749902171081845</v>
+        <v>2.749901926967264</v>
       </c>
       <c r="D864" t="n">
-        <v>2.419914006710763</v>
+        <v>2.419913791889924</v>
       </c>
       <c r="E864" t="n">
-        <v>2.548242652310732</v>
+        <v>2.54824242609789</v>
       </c>
       <c r="F864" t="n">
         <v>8626200</v>
@@ -17732,16 +17732,16 @@
         <v>45050</v>
       </c>
       <c r="B866" t="n">
-        <v>2.823232889175415</v>
+        <v>2.823232650756836</v>
       </c>
       <c r="C866" t="n">
-        <v>2.869064767891131</v>
+        <v>2.869064525602105</v>
       </c>
       <c r="D866" t="n">
-        <v>2.704070572725299</v>
+        <v>2.704070344369832</v>
       </c>
       <c r="E866" t="n">
-        <v>2.722403236794548</v>
+        <v>2.72240300689091</v>
       </c>
       <c r="F866" t="n">
         <v>5400200</v>
@@ -17772,16 +17772,16 @@
         <v>45054</v>
       </c>
       <c r="B868" t="n">
-        <v>3.125722169876099</v>
+        <v>3.12572193145752</v>
       </c>
       <c r="C868" t="n">
-        <v>3.199052823489703</v>
+        <v>3.199052579477732</v>
       </c>
       <c r="D868" t="n">
-        <v>3.015725970913106</v>
+        <v>3.015725740884632</v>
       </c>
       <c r="E868" t="n">
-        <v>3.024892302614806</v>
+        <v>3.024892071887158</v>
       </c>
       <c r="F868" t="n">
         <v>6228600</v>
@@ -17892,16 +17892,16 @@
         <v>45062</v>
       </c>
       <c r="B874" t="n">
-        <v>3.602371692657471</v>
+        <v>3.60237193107605</v>
       </c>
       <c r="C874" t="n">
-        <v>3.675702561499818</v>
+        <v>3.675702804771711</v>
       </c>
       <c r="D874" t="n">
-        <v>3.529040823815123</v>
+        <v>3.529041057380388</v>
       </c>
       <c r="E874" t="n">
-        <v>3.657369680382299</v>
+        <v>3.657369922440853</v>
       </c>
       <c r="F874" t="n">
         <v>5715400</v>
@@ -17912,16 +17912,16 @@
         <v>45063</v>
       </c>
       <c r="B875" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="C875" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="D875" t="n">
-        <v>3.62987109842838</v>
+        <v>3.629870877835498</v>
       </c>
       <c r="E875" t="n">
-        <v>3.648203763083666</v>
+        <v>3.64820354137668</v>
       </c>
       <c r="F875" t="n">
         <v>6160500</v>
@@ -17972,16 +17972,16 @@
         <v>45068</v>
       </c>
       <c r="B878" t="n">
-        <v>3.923194169998169</v>
+        <v>3.92319393157959</v>
       </c>
       <c r="C878" t="n">
-        <v>3.996524828619315</v>
+        <v>3.996524585744319</v>
       </c>
       <c r="D878" t="n">
-        <v>3.859029625162064</v>
+        <v>3.859029390642864</v>
       </c>
       <c r="E878" t="n">
-        <v>3.904861505342882</v>
+        <v>3.904861268038407</v>
       </c>
       <c r="F878" t="n">
         <v>3483600</v>
@@ -17992,16 +17992,16 @@
         <v>45069</v>
       </c>
       <c r="B879" t="n">
-        <v>3.941526174545288</v>
+        <v>3.941526412963867</v>
       </c>
       <c r="C879" t="n">
-        <v>4.134019339730554</v>
+        <v>4.134019589792833</v>
       </c>
       <c r="D879" t="n">
-        <v>3.877361640455157</v>
+        <v>3.877361874992493</v>
       </c>
       <c r="E879" t="n">
-        <v>3.886527752705101</v>
+        <v>3.886527987796886</v>
       </c>
       <c r="F879" t="n">
         <v>4348000</v>
@@ -18092,16 +18092,16 @@
         <v>45076</v>
       </c>
       <c r="B884" t="n">
-        <v>3.996524333953857</v>
+        <v>3.996524572372437</v>
       </c>
       <c r="C884" t="n">
-        <v>4.244015494709879</v>
+        <v>4.24401574789291</v>
       </c>
       <c r="D884" t="n">
-        <v>3.969025121832011</v>
+        <v>3.969025358610084</v>
       </c>
       <c r="E884" t="n">
-        <v>4.225682832323698</v>
+        <v>4.225683084413067</v>
       </c>
       <c r="F884" t="n">
         <v>3937000</v>
@@ -18172,16 +18172,16 @@
         <v>45082</v>
       </c>
       <c r="B888" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C888" t="n">
-        <v>4.72066517241793</v>
+        <v>4.72066469090588</v>
       </c>
       <c r="D888" t="n">
-        <v>4.399843360854316</v>
+        <v>4.399842912066377</v>
       </c>
       <c r="E888" t="n">
-        <v>4.64733452258455</v>
+        <v>4.647334048552291</v>
       </c>
       <c r="F888" t="n">
         <v>6247400</v>
@@ -18232,16 +18232,16 @@
         <v>45086</v>
       </c>
       <c r="B891" t="n">
-        <v>4.354011535644531</v>
+        <v>4.354012012481689</v>
       </c>
       <c r="C891" t="n">
-        <v>4.500672836977939</v>
+        <v>4.500673329876966</v>
       </c>
       <c r="D891" t="n">
-        <v>4.289846997768588</v>
+        <v>4.289847467578654</v>
       </c>
       <c r="E891" t="n">
-        <v>4.454841398853827</v>
+        <v>4.454841886733544</v>
       </c>
       <c r="F891" t="n">
         <v>5651200</v>
@@ -18252,16 +18252,16 @@
         <v>45089</v>
       </c>
       <c r="B892" t="n">
-        <v>4.491506099700928</v>
+        <v>4.491506576538086</v>
       </c>
       <c r="C892" t="n">
-        <v>4.647333929244392</v>
+        <v>4.647334422624888</v>
       </c>
       <c r="D892" t="n">
-        <v>4.271513741202773</v>
+        <v>4.271514194684618</v>
       </c>
       <c r="E892" t="n">
-        <v>4.363177478876643</v>
+        <v>4.363177942089895</v>
       </c>
       <c r="F892" t="n">
         <v>6649300</v>
@@ -18272,16 +18272,16 @@
         <v>45090</v>
       </c>
       <c r="B893" t="n">
-        <v>4.289846897125244</v>
+        <v>4.289847373962402</v>
       </c>
       <c r="C893" t="n">
-        <v>4.592336479656477</v>
+        <v>4.592336990116809</v>
       </c>
       <c r="D893" t="n">
-        <v>4.234848910415514</v>
+        <v>4.234849381139381</v>
       </c>
       <c r="E893" t="n">
-        <v>4.537338055861602</v>
+        <v>4.537338560208595</v>
       </c>
       <c r="F893" t="n">
         <v>4358900</v>
@@ -18392,16 +18392,16 @@
         <v>45098</v>
       </c>
       <c r="B899" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C899" t="n">
-        <v>4.986488897178933</v>
+        <v>4.986489382037665</v>
       </c>
       <c r="D899" t="n">
-        <v>4.748163852887355</v>
+        <v>4.748164314572671</v>
       </c>
       <c r="E899" t="n">
-        <v>4.821494938343708</v>
+        <v>4.821495407159335</v>
       </c>
       <c r="F899" t="n">
         <v>4163100</v>
@@ -18412,16 +18412,16 @@
         <v>45099</v>
       </c>
       <c r="B900" t="n">
-        <v>4.766496181488037</v>
+        <v>4.766496658325195</v>
       </c>
       <c r="C900" t="n">
-        <v>4.858159922623858</v>
+        <v>4.858160408630997</v>
       </c>
       <c r="D900" t="n">
-        <v>4.592336122334244</v>
+        <v>4.592336581748543</v>
       </c>
       <c r="E900" t="n">
-        <v>4.757330069625522</v>
+        <v>4.757330545545708</v>
       </c>
       <c r="F900" t="n">
         <v>4737400</v>
@@ -18572,16 +18572,16 @@
         <v>45111</v>
       </c>
       <c r="B908" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C908" t="n">
-        <v>5.087318782005757</v>
+        <v>5.087319262304525</v>
       </c>
       <c r="D908" t="n">
-        <v>4.87649294836929</v>
+        <v>4.876493408763784</v>
       </c>
       <c r="E908" t="n">
-        <v>4.940657047463991</v>
+        <v>4.94065751391628</v>
       </c>
       <c r="F908" t="n">
         <v>2828200</v>
@@ -18612,16 +18612,16 @@
         <v>45113</v>
       </c>
       <c r="B910" t="n">
-        <v>5.087319374084473</v>
+        <v>5.087318897247314</v>
       </c>
       <c r="C910" t="n">
-        <v>5.22481413790957</v>
+        <v>5.224813648184956</v>
       </c>
       <c r="D910" t="n">
-        <v>5.041487494752643</v>
+        <v>5.041487022211331</v>
       </c>
       <c r="E910" t="n">
-        <v>5.206481473593878</v>
+        <v>5.206480985587593</v>
       </c>
       <c r="F910" t="n">
         <v>3192100</v>
@@ -18672,16 +18672,16 @@
         <v>45118</v>
       </c>
       <c r="B913" t="n">
-        <v>5.096485614776611</v>
+        <v>5.096485137939453</v>
       </c>
       <c r="C913" t="n">
-        <v>5.114818279549415</v>
+        <v>5.114817800997017</v>
       </c>
       <c r="D913" t="n">
-        <v>4.858160972730167</v>
+        <v>4.858160518191128</v>
       </c>
       <c r="E913" t="n">
-        <v>5.105652165705616</v>
+        <v>5.105651688010817</v>
       </c>
       <c r="F913" t="n">
         <v>3857700</v>
@@ -18692,16 +18692,16 @@
         <v>45119</v>
       </c>
       <c r="B914" t="n">
-        <v>5.325643062591553</v>
+        <v>5.325643539428711</v>
       </c>
       <c r="C914" t="n">
-        <v>5.573134205359659</v>
+        <v>5.573134704356201</v>
       </c>
       <c r="D914" t="n">
-        <v>5.178981774161598</v>
+        <v>5.178982237867281</v>
       </c>
       <c r="E914" t="n">
-        <v>5.178981774161598</v>
+        <v>5.178982237867281</v>
       </c>
       <c r="F914" t="n">
         <v>7685700</v>
@@ -18712,16 +18712,16 @@
         <v>45120</v>
       </c>
       <c r="B915" t="n">
-        <v>5.096485614776611</v>
+        <v>5.096485137939453</v>
       </c>
       <c r="C915" t="n">
-        <v>5.453972796388881</v>
+        <v>5.453972286104523</v>
       </c>
       <c r="D915" t="n">
-        <v>4.99565573998359</v>
+        <v>4.995655272580271</v>
       </c>
       <c r="E915" t="n">
-        <v>5.334810693908262</v>
+        <v>5.334810194772943</v>
       </c>
       <c r="F915" t="n">
         <v>4692200</v>
@@ -18732,16 +18732,16 @@
         <v>45121</v>
       </c>
       <c r="B916" t="n">
-        <v>4.482340335845947</v>
+        <v>4.482339859008789</v>
       </c>
       <c r="C916" t="n">
-        <v>4.903992029460144</v>
+        <v>4.903991507767135</v>
       </c>
       <c r="D916" t="n">
-        <v>4.381510906088113</v>
+        <v>4.381510439977321</v>
       </c>
       <c r="E916" t="n">
-        <v>4.858160589684357</v>
+        <v>4.858160072866955</v>
       </c>
       <c r="F916" t="n">
         <v>15771400</v>
@@ -18772,16 +18772,16 @@
         <v>45125</v>
       </c>
       <c r="B918" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C918" t="n">
-        <v>5.041486987624404</v>
+        <v>5.041486503749065</v>
       </c>
       <c r="D918" t="n">
-        <v>4.711498626050601</v>
+        <v>4.711498173847115</v>
       </c>
       <c r="E918" t="n">
-        <v>4.720665175828972</v>
+        <v>4.720664722745693</v>
       </c>
       <c r="F918" t="n">
         <v>5384000</v>
@@ -18812,16 +18812,16 @@
         <v>45127</v>
       </c>
       <c r="B920" t="n">
-        <v>4.876492977142334</v>
+        <v>4.876493453979492</v>
       </c>
       <c r="C920" t="n">
-        <v>5.004821613174064</v>
+        <v>5.004822102559555</v>
       </c>
       <c r="D920" t="n">
-        <v>4.784829228605952</v>
+        <v>4.784829696479972</v>
       </c>
       <c r="E920" t="n">
-        <v>4.958989738905873</v>
+        <v>4.958990223809796</v>
       </c>
       <c r="F920" t="n">
         <v>2200400</v>
@@ -18832,16 +18832,16 @@
         <v>45128</v>
       </c>
       <c r="B921" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C921" t="n">
-        <v>5.169815688182035</v>
+        <v>5.169815198316529</v>
       </c>
       <c r="D921" t="n">
-        <v>4.858160422351643</v>
+        <v>4.85815996201701</v>
       </c>
       <c r="E921" t="n">
-        <v>4.858160422351643</v>
+        <v>4.85815996201701</v>
       </c>
       <c r="F921" t="n">
         <v>3946200</v>
@@ -18852,16 +18852,16 @@
         <v>45131</v>
       </c>
       <c r="B922" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C922" t="n">
-        <v>5.105651587288944</v>
+        <v>5.105651103503303</v>
       </c>
       <c r="D922" t="n">
-        <v>4.885659197852923</v>
+        <v>4.885658734912646</v>
       </c>
       <c r="E922" t="n">
-        <v>5.068986261897133</v>
+        <v>5.068985781585712</v>
       </c>
       <c r="F922" t="n">
         <v>2320000</v>
@@ -18872,16 +18872,16 @@
         <v>45132</v>
       </c>
       <c r="B923" t="n">
-        <v>5.032320499420166</v>
+        <v>5.032320022583008</v>
       </c>
       <c r="C923" t="n">
-        <v>5.270645551552092</v>
+        <v>5.270645052132461</v>
       </c>
       <c r="D923" t="n">
-        <v>4.995655174028355</v>
+        <v>4.995654700665417</v>
       </c>
       <c r="E923" t="n">
-        <v>5.096485037398413</v>
+        <v>5.096484554481348</v>
       </c>
       <c r="F923" t="n">
         <v>3865600</v>
@@ -18952,16 +18952,16 @@
         <v>45138</v>
       </c>
       <c r="B927" t="n">
-        <v>5.224813938140869</v>
+        <v>5.224813461303711</v>
       </c>
       <c r="C927" t="n">
-        <v>5.389808347758803</v>
+        <v>5.389807855863602</v>
       </c>
       <c r="D927" t="n">
-        <v>5.087319179572829</v>
+        <v>5.087318715283986</v>
       </c>
       <c r="E927" t="n">
-        <v>5.087319179572829</v>
+        <v>5.087318715283986</v>
       </c>
       <c r="F927" t="n">
         <v>3571100</v>
@@ -18972,16 +18972,16 @@
         <v>45139</v>
       </c>
       <c r="B928" t="n">
-        <v>5.417306900024414</v>
+        <v>5.417306423187256</v>
       </c>
       <c r="C928" t="n">
-        <v>5.426473449994312</v>
+        <v>5.426472972350305</v>
       </c>
       <c r="D928" t="n">
-        <v>4.995655217282615</v>
+        <v>4.99565477755969</v>
       </c>
       <c r="E928" t="n">
-        <v>5.17898228291414</v>
+        <v>5.17898182705457</v>
       </c>
       <c r="F928" t="n">
         <v>5677300</v>
@@ -18992,16 +18992,16 @@
         <v>45140</v>
       </c>
       <c r="B929" t="n">
-        <v>5.33480978012085</v>
+        <v>5.334810256958008</v>
       </c>
       <c r="C929" t="n">
-        <v>5.518136396447286</v>
+        <v>5.518136889670584</v>
       </c>
       <c r="D929" t="n">
-        <v>5.215647260966101</v>
+        <v>5.215647727152248</v>
       </c>
       <c r="E929" t="n">
-        <v>5.472304523823111</v>
+        <v>5.472305012949855</v>
       </c>
       <c r="F929" t="n">
         <v>6874400</v>
@@ -19032,16 +19032,16 @@
         <v>45142</v>
       </c>
       <c r="B931" t="n">
-        <v>5.628132343292236</v>
+        <v>5.628132820129395</v>
       </c>
       <c r="C931" t="n">
-        <v>5.655631554171628</v>
+        <v>5.655632033338626</v>
       </c>
       <c r="D931" t="n">
-        <v>5.316477096808192</v>
+        <v>5.31647754724071</v>
       </c>
       <c r="E931" t="n">
-        <v>5.32564320904457</v>
+        <v>5.325643660253677</v>
       </c>
       <c r="F931" t="n">
         <v>4666200</v>
@@ -19092,16 +19092,16 @@
         <v>45147</v>
       </c>
       <c r="B934" t="n">
-        <v>5.224813938140869</v>
+        <v>5.224813461303711</v>
       </c>
       <c r="C934" t="n">
-        <v>5.45397245186784</v>
+        <v>5.453971954116771</v>
       </c>
       <c r="D934" t="n">
-        <v>5.197315161261333</v>
+        <v>5.197314686933821</v>
       </c>
       <c r="E934" t="n">
-        <v>5.261479265370371</v>
+        <v>5.26147878518699</v>
       </c>
       <c r="F934" t="n">
         <v>3345000</v>
@@ -19152,16 +19152,16 @@
         <v>45152</v>
       </c>
       <c r="B937" t="n">
-        <v>6.068117141723633</v>
+        <v>6.068116664886475</v>
       </c>
       <c r="C937" t="n">
-        <v>6.28810953504867</v>
+        <v>6.288109040924345</v>
       </c>
       <c r="D937" t="n">
-        <v>5.985620376676263</v>
+        <v>5.985619906321761</v>
       </c>
       <c r="E937" t="n">
-        <v>6.14144779380359</v>
+        <v>6.141447311204055</v>
       </c>
       <c r="F937" t="n">
         <v>5683800</v>
@@ -19232,16 +19232,16 @@
         <v>45156</v>
       </c>
       <c r="B941" t="n">
-        <v>5.710629940032959</v>
+        <v>5.710629463195801</v>
       </c>
       <c r="C941" t="n">
-        <v>5.838958579953599</v>
+        <v>5.838958092401009</v>
       </c>
       <c r="D941" t="n">
-        <v>5.334810133151363</v>
+        <v>5.33480968769513</v>
       </c>
       <c r="E941" t="n">
-        <v>5.609800075838448</v>
+        <v>5.609799607420576</v>
       </c>
       <c r="F941" t="n">
         <v>5405200</v>
@@ -19252,16 +19252,16 @@
         <v>45159</v>
       </c>
       <c r="B942" t="n">
-        <v>5.490636825561523</v>
+        <v>5.490637302398682</v>
       </c>
       <c r="C942" t="n">
-        <v>5.701462639060511</v>
+        <v>5.701463134206945</v>
       </c>
       <c r="D942" t="n">
-        <v>5.463138053457582</v>
+        <v>5.463138527906596</v>
       </c>
       <c r="E942" t="n">
-        <v>5.67396386695657</v>
+        <v>5.673964359714859</v>
       </c>
       <c r="F942" t="n">
         <v>3510600</v>
@@ -19272,16 +19272,16 @@
         <v>45160</v>
       </c>
       <c r="B943" t="n">
-        <v>5.628132343292236</v>
+        <v>5.628132820129395</v>
       </c>
       <c r="C943" t="n">
-        <v>5.646465004850121</v>
+        <v>5.646465483240493</v>
       </c>
       <c r="D943" t="n">
-        <v>5.408140404597616</v>
+        <v>5.408140862796206</v>
       </c>
       <c r="E943" t="n">
-        <v>5.563968246382204</v>
+        <v>5.563968717783131</v>
       </c>
       <c r="F943" t="n">
         <v>4158800</v>
@@ -19412,16 +19412,16 @@
         <v>45169</v>
       </c>
       <c r="B950" t="n">
-        <v>4.90399169921875</v>
+        <v>4.903992176055908</v>
       </c>
       <c r="C950" t="n">
-        <v>5.03232033386837</v>
+        <v>5.032320823183499</v>
       </c>
       <c r="D950" t="n">
-        <v>4.858160262529314</v>
+        <v>4.858160734910076</v>
       </c>
       <c r="E950" t="n">
-        <v>5.03232033386837</v>
+        <v>5.032320823183499</v>
       </c>
       <c r="F950" t="n">
         <v>3681000</v>
@@ -19432,16 +19432,16 @@
         <v>45170</v>
       </c>
       <c r="B951" t="n">
-        <v>5.151483058929443</v>
+        <v>5.151482582092285</v>
       </c>
       <c r="C951" t="n">
-        <v>5.169815721744364</v>
+        <v>5.169815243210278</v>
       </c>
       <c r="D951" t="n">
-        <v>4.876493116705634</v>
+        <v>4.876492665322393</v>
       </c>
       <c r="E951" t="n">
-        <v>4.949823767965317</v>
+        <v>4.949823309794364</v>
       </c>
       <c r="F951" t="n">
         <v>4962000</v>
@@ -19472,16 +19472,16 @@
         <v>45174</v>
       </c>
       <c r="B953" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C953" t="n">
-        <v>5.032320437846034</v>
+        <v>5.032319954850488</v>
       </c>
       <c r="D953" t="n">
-        <v>4.858160362908486</v>
+        <v>4.858159896628598</v>
       </c>
       <c r="E953" t="n">
-        <v>4.99565511290285</v>
+        <v>4.995654633426395</v>
       </c>
       <c r="F953" t="n">
         <v>3096400</v>
@@ -19492,16 +19492,16 @@
         <v>45175</v>
       </c>
       <c r="B954" t="n">
-        <v>4.986489295959473</v>
+        <v>4.986488819122314</v>
       </c>
       <c r="C954" t="n">
-        <v>5.105651827634952</v>
+        <v>5.105651339402779</v>
       </c>
       <c r="D954" t="n">
-        <v>4.94982396884166</v>
+        <v>4.949823495510654</v>
       </c>
       <c r="E954" t="n">
-        <v>4.94982396884166</v>
+        <v>4.949823495510654</v>
       </c>
       <c r="F954" t="n">
         <v>4361600</v>
@@ -19512,16 +19512,16 @@
         <v>45177</v>
       </c>
       <c r="B955" t="n">
-        <v>4.876492977142334</v>
+        <v>4.876493453979492</v>
       </c>
       <c r="C955" t="n">
-        <v>5.004821613174064</v>
+        <v>5.004822102559555</v>
       </c>
       <c r="D955" t="n">
-        <v>4.867326427454637</v>
+        <v>4.867326903395464</v>
       </c>
       <c r="E955" t="n">
-        <v>4.97732240119612</v>
+        <v>4.977322887892662</v>
       </c>
       <c r="F955" t="n">
         <v>2168000</v>
@@ -19552,16 +19552,16 @@
         <v>45181</v>
       </c>
       <c r="B957" t="n">
-        <v>5.050653457641602</v>
+        <v>5.05065393447876</v>
       </c>
       <c r="C957" t="n">
-        <v>5.105651444187835</v>
+        <v>5.105651926217408</v>
       </c>
       <c r="D957" t="n">
-        <v>4.913158272733446</v>
+        <v>4.913158736589549</v>
       </c>
       <c r="E957" t="n">
-        <v>4.913158272733446</v>
+        <v>4.913158736589549</v>
       </c>
       <c r="F957" t="n">
         <v>2356100</v>
@@ -19672,16 +19672,16 @@
         <v>45189</v>
       </c>
       <c r="B963" t="n">
-        <v>4.968156337738037</v>
+        <v>4.968155860900879</v>
       </c>
       <c r="C963" t="n">
-        <v>5.114817637510772</v>
+        <v>5.114817146597253</v>
       </c>
       <c r="D963" t="n">
-        <v>4.711498626050601</v>
+        <v>4.711498173847115</v>
       </c>
       <c r="E963" t="n">
-        <v>4.720665175828972</v>
+        <v>4.720664722745693</v>
       </c>
       <c r="F963" t="n">
         <v>5388800</v>
@@ -19712,16 +19712,16 @@
         <v>45191</v>
       </c>
       <c r="B965" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C965" t="n">
-        <v>4.86732647208469</v>
+        <v>4.867325975613057</v>
       </c>
       <c r="D965" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="E965" t="n">
-        <v>4.812328484709655</v>
+        <v>4.812327993847866</v>
       </c>
       <c r="F965" t="n">
         <v>2426200</v>
@@ -19752,16 +19752,16 @@
         <v>45195</v>
       </c>
       <c r="B967" t="n">
-        <v>4.491506099700928</v>
+        <v>4.491506576538086</v>
       </c>
       <c r="C967" t="n">
-        <v>4.784828661585008</v>
+        <v>4.784829169562522</v>
       </c>
       <c r="D967" t="n">
-        <v>4.418175459229907</v>
+        <v>4.418175928281977</v>
       </c>
       <c r="E967" t="n">
-        <v>4.574002851688278</v>
+        <v>4.574003337283638</v>
       </c>
       <c r="F967" t="n">
         <v>4192900</v>
@@ -19852,16 +19852,16 @@
         <v>45202</v>
       </c>
       <c r="B972" t="n">
-        <v>4.317346096038818</v>
+        <v>4.31734561920166</v>
       </c>
       <c r="C972" t="n">
-        <v>4.674833227119539</v>
+        <v>4.674832710799063</v>
       </c>
       <c r="D972" t="n">
-        <v>4.308179546405524</v>
+        <v>4.308179070580783</v>
       </c>
       <c r="E972" t="n">
-        <v>4.619835240575209</v>
+        <v>4.619834730329086</v>
       </c>
       <c r="F972" t="n">
         <v>3808300</v>
@@ -19892,16 +19892,16 @@
         <v>45204</v>
       </c>
       <c r="B974" t="n">
-        <v>4.537338256835938</v>
+        <v>4.537337779998779</v>
       </c>
       <c r="C974" t="n">
-        <v>4.79399597660141</v>
+        <v>4.793995472791623</v>
       </c>
       <c r="D974" t="n">
-        <v>4.528172143854223</v>
+        <v>4.528171667980348</v>
       </c>
       <c r="E974" t="n">
-        <v>4.67483344824297</v>
+        <v>4.674832956956192</v>
       </c>
       <c r="F974" t="n">
         <v>3401000</v>
@@ -20032,16 +20032,16 @@
         <v>45216</v>
       </c>
       <c r="B981" t="n">
-        <v>4.674833297729492</v>
+        <v>4.674832820892334</v>
       </c>
       <c r="C981" t="n">
-        <v>4.812328484709655</v>
+        <v>4.812327993847866</v>
       </c>
       <c r="D981" t="n">
-        <v>4.601502647896112</v>
+        <v>4.601502178538746</v>
       </c>
       <c r="E981" t="n">
-        <v>4.656500635271147</v>
+        <v>4.656500160303938</v>
       </c>
       <c r="F981" t="n">
         <v>2762000</v>
@@ -20052,16 +20052,16 @@
         <v>45217</v>
       </c>
       <c r="B982" t="n">
-        <v>4.509839534759521</v>
+        <v>4.509839057922363</v>
       </c>
       <c r="C982" t="n">
-        <v>4.674833504170784</v>
+        <v>4.67483300988838</v>
       </c>
       <c r="D982" t="n">
-        <v>4.418176218419932</v>
+        <v>4.418175751274577</v>
       </c>
       <c r="E982" t="n">
-        <v>4.647334727811492</v>
+        <v>4.647334236436606</v>
       </c>
       <c r="F982" t="n">
         <v>3515800</v>
@@ -20132,16 +20132,16 @@
         <v>45223</v>
       </c>
       <c r="B986" t="n">
-        <v>4.711498260498047</v>
+        <v>4.711498737335205</v>
       </c>
       <c r="C986" t="n">
-        <v>4.793995453762048</v>
+        <v>4.79399593894851</v>
       </c>
       <c r="D986" t="n">
-        <v>4.619834955251998</v>
+        <v>4.619835422812178</v>
       </c>
       <c r="E986" t="n">
-        <v>4.683999487466791</v>
+        <v>4.683999961520877</v>
       </c>
       <c r="F986" t="n">
         <v>2628000</v>
@@ -20172,16 +20172,16 @@
         <v>45225</v>
       </c>
       <c r="B988" t="n">
-        <v>4.793996334075928</v>
+        <v>4.79399585723877</v>
       </c>
       <c r="C988" t="n">
-        <v>4.858160878073153</v>
+        <v>4.858160394853837</v>
       </c>
       <c r="D988" t="n">
-        <v>4.60150313916945</v>
+        <v>4.601502681478721</v>
       </c>
       <c r="E988" t="n">
-        <v>4.60150313916945</v>
+        <v>4.601502681478721</v>
       </c>
       <c r="F988" t="n">
         <v>4908400</v>
@@ -20192,16 +20192,16 @@
         <v>45226</v>
       </c>
       <c r="B989" t="n">
-        <v>4.766496181488037</v>
+        <v>4.766496658325195</v>
       </c>
       <c r="C989" t="n">
-        <v>4.977321999347226</v>
+        <v>4.977322497275261</v>
       </c>
       <c r="D989" t="n">
-        <v>4.720664748005237</v>
+        <v>4.720665220257449</v>
       </c>
       <c r="E989" t="n">
-        <v>4.803161503108321</v>
+        <v>4.803161983613454</v>
       </c>
       <c r="F989" t="n">
         <v>2912800</v>
@@ -20252,16 +20252,16 @@
         <v>45231</v>
       </c>
       <c r="B992" t="n">
-        <v>4.803162097930908</v>
+        <v>4.80316162109375</v>
       </c>
       <c r="C992" t="n">
-        <v>4.848993974174629</v>
+        <v>4.848993492787479</v>
       </c>
       <c r="D992" t="n">
-        <v>4.656500793287267</v>
+        <v>4.656500331010008</v>
       </c>
       <c r="E992" t="n">
-        <v>4.729831445609087</v>
+        <v>4.729830976051879</v>
       </c>
       <c r="F992" t="n">
         <v>2720700</v>
@@ -20332,16 +20332,16 @@
         <v>45238</v>
       </c>
       <c r="B996" t="n">
-        <v>5.518136978149414</v>
+        <v>5.518136501312256</v>
       </c>
       <c r="C996" t="n">
-        <v>5.573134968845035</v>
+        <v>5.573134487255351</v>
       </c>
       <c r="D996" t="n">
-        <v>5.316477678932137</v>
+        <v>5.316477219520905</v>
       </c>
       <c r="E996" t="n">
-        <v>5.316477678932137</v>
+        <v>5.316477219520905</v>
       </c>
       <c r="F996" t="n">
         <v>4022900</v>
@@ -20352,16 +20352,16 @@
         <v>45239</v>
       </c>
       <c r="B997" t="n">
-        <v>5.618966102600098</v>
+        <v>5.618966579437256</v>
       </c>
       <c r="C997" t="n">
-        <v>5.728962069432778</v>
+        <v>5.728962555604424</v>
       </c>
       <c r="D997" t="n">
-        <v>5.417306392988397</v>
+        <v>5.417306852712293</v>
       </c>
       <c r="E997" t="n">
-        <v>5.582300780322537</v>
+        <v>5.5823012540482</v>
       </c>
       <c r="F997" t="n">
         <v>3100500</v>
@@ -20392,16 +20392,16 @@
         <v>45243</v>
       </c>
       <c r="B999" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C999" t="n">
-        <v>7.140579120035365</v>
+        <v>7.140578620094379</v>
       </c>
       <c r="D999" t="n">
-        <v>6.544766908003258</v>
+        <v>6.544766449777509</v>
       </c>
       <c r="E999" t="n">
-        <v>6.608931448004774</v>
+        <v>6.608930985286603</v>
       </c>
       <c r="F999" t="n">
         <v>8835300</v>
@@ -20432,16 +20432,16 @@
         <v>45246</v>
       </c>
       <c r="B1001" t="n">
-        <v>7.360570907592773</v>
+        <v>7.360570430755615</v>
       </c>
       <c r="C1001" t="n">
-        <v>7.562230635986777</v>
+        <v>7.562230146085571</v>
       </c>
       <c r="D1001" t="n">
-        <v>6.627263956657273</v>
+        <v>6.627263527325669</v>
       </c>
       <c r="E1001" t="n">
-        <v>6.78309180939305</v>
+        <v>6.783091369966508</v>
       </c>
       <c r="F1001" t="n">
         <v>9976600</v>
@@ -20452,16 +20452,16 @@
         <v>45247</v>
       </c>
       <c r="B1002" t="n">
-        <v>7.635560989379883</v>
+        <v>7.635561466217041</v>
       </c>
       <c r="C1002" t="n">
-        <v>7.699725088295085</v>
+        <v>7.699725569139261</v>
       </c>
       <c r="D1002" t="n">
-        <v>7.333071845679237</v>
+        <v>7.333072303626092</v>
       </c>
       <c r="E1002" t="n">
-        <v>7.415569043810375</v>
+        <v>7.41556950690914</v>
       </c>
       <c r="F1002" t="n">
         <v>5823800</v>
@@ -20492,16 +20492,16 @@
         <v>45251</v>
       </c>
       <c r="B1004" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1004" t="n">
-        <v>7.543897678065316</v>
+        <v>7.543897193575265</v>
       </c>
       <c r="D1004" t="n">
-        <v>7.287240393386257</v>
+        <v>7.287239925379449</v>
       </c>
       <c r="E1004" t="n">
-        <v>7.543897678065316</v>
+        <v>7.543897193575265</v>
       </c>
       <c r="F1004" t="n">
         <v>4025000</v>
@@ -20532,16 +20532,16 @@
         <v>45253</v>
       </c>
       <c r="B1006" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="C1006" t="n">
-        <v>7.323906062493096</v>
+        <v>7.32390557025422</v>
       </c>
       <c r="D1006" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="E1006" t="n">
-        <v>7.314739949011068</v>
+        <v>7.314739457388246</v>
       </c>
       <c r="F1006" t="n">
         <v>2414400</v>
@@ -20612,16 +20612,16 @@
         <v>45259</v>
       </c>
       <c r="B1010" t="n">
-        <v>7.44306755065918</v>
+        <v>7.443068027496338</v>
       </c>
       <c r="C1010" t="n">
-        <v>7.763889782032437</v>
+        <v>7.763890279422943</v>
       </c>
       <c r="D1010" t="n">
-        <v>7.168077628591552</v>
+        <v>7.16807808781159</v>
       </c>
       <c r="E1010" t="n">
-        <v>7.213909063726926</v>
+        <v>7.213909525883136</v>
       </c>
       <c r="F1010" t="n">
         <v>6571400</v>
@@ -20752,16 +20752,16 @@
         <v>45268</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.718058586120605</v>
+        <v>7.718058109283447</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.800555788512423</v>
+        <v>7.800555306578421</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.580563831581132</v>
+        <v>7.580563363238674</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.699725485957833</v>
+        <v>7.69972501025333</v>
       </c>
       <c r="F1017" t="n">
         <v>1787800</v>
@@ -20772,16 +20772,16 @@
         <v>45271</v>
       </c>
       <c r="B1018" t="n">
-        <v>7.672226905822754</v>
+        <v>7.672226428985596</v>
       </c>
       <c r="C1018" t="n">
-        <v>7.892218868372355</v>
+        <v>7.892218377862459</v>
       </c>
       <c r="D1018" t="n">
-        <v>7.626395028415665</v>
+        <v>7.626394554427008</v>
       </c>
       <c r="E1018" t="n">
-        <v>7.699725682598865</v>
+        <v>7.699725204052629</v>
       </c>
       <c r="F1018" t="n">
         <v>2800600</v>
@@ -20872,16 +20872,16 @@
         <v>45278</v>
       </c>
       <c r="B1023" t="n">
-        <v>7.44306755065918</v>
+        <v>7.443068027496338</v>
       </c>
       <c r="C1023" t="n">
-        <v>7.681392586869585</v>
+        <v>7.681393078974941</v>
       </c>
       <c r="D1023" t="n">
-        <v>7.415568776994981</v>
+        <v>7.415569252070441</v>
       </c>
       <c r="E1023" t="n">
-        <v>7.516398196543881</v>
+        <v>7.516398678078938</v>
       </c>
       <c r="F1023" t="n">
         <v>2448800</v>
@@ -20932,16 +20932,16 @@
         <v>45281</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.498065948486328</v>
+        <v>7.498066425323486</v>
       </c>
       <c r="C1026" t="n">
-        <v>7.653893789041931</v>
+        <v>7.653894275788911</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.406402204334709</v>
+        <v>7.40640267534254</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.461400625659731</v>
+        <v>7.461401100165169</v>
       </c>
       <c r="F1026" t="n">
         <v>2110700</v>
@@ -20972,16 +20972,16 @@
         <v>45286</v>
       </c>
       <c r="B1028" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C1028" t="n">
-        <v>7.433901462933017</v>
+        <v>7.433901956821806</v>
       </c>
       <c r="D1028" t="n">
-        <v>7.168078073639243</v>
+        <v>7.168078549867428</v>
       </c>
       <c r="E1028" t="n">
-        <v>7.37890391218996</v>
+        <v>7.378904402424857</v>
       </c>
       <c r="F1028" t="n">
         <v>1748700</v>
@@ -20992,16 +20992,16 @@
         <v>45287</v>
       </c>
       <c r="B1029" t="n">
-        <v>7.232242107391357</v>
+        <v>7.232241630554199</v>
       </c>
       <c r="C1029" t="n">
-        <v>7.333071969353814</v>
+        <v>7.333071485868728</v>
       </c>
       <c r="D1029" t="n">
-        <v>7.140578795191465</v>
+        <v>7.140578324397864</v>
       </c>
       <c r="E1029" t="n">
-        <v>7.195576782511401</v>
+        <v>7.195576308091665</v>
       </c>
       <c r="F1029" t="n">
         <v>1937700</v>
@@ -21012,16 +21012,16 @@
         <v>45288</v>
       </c>
       <c r="B1030" t="n">
-        <v>7.177244186401367</v>
+        <v>7.177244663238525</v>
       </c>
       <c r="C1030" t="n">
-        <v>7.31473937451447</v>
+        <v>7.314739860486446</v>
       </c>
       <c r="D1030" t="n">
-        <v>7.103913535963753</v>
+        <v>7.103914007929016</v>
       </c>
       <c r="E1030" t="n">
-        <v>7.223076061467453</v>
+        <v>7.22307654134956</v>
       </c>
       <c r="F1030" t="n">
         <v>1438100</v>
@@ -21032,16 +21032,16 @@
         <v>45293</v>
       </c>
       <c r="B1031" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1031" t="n">
-        <v>7.204743074499178</v>
+        <v>7.204743572895473</v>
       </c>
       <c r="D1031" t="n">
-        <v>6.828922852298171</v>
+        <v>6.828923324696675</v>
       </c>
       <c r="E1031" t="n">
-        <v>7.195576525064578</v>
+        <v>7.195577022826767</v>
       </c>
       <c r="F1031" t="n">
         <v>2422400</v>
@@ -21052,16 +21052,16 @@
         <v>45294</v>
       </c>
       <c r="B1032" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1032" t="n">
-        <v>7.03974868135747</v>
+        <v>7.039749168340091</v>
       </c>
       <c r="D1032" t="n">
-        <v>6.764758754596515</v>
+        <v>6.764759222556394</v>
       </c>
       <c r="E1032" t="n">
-        <v>6.874754725300897</v>
+        <v>6.874755200869873</v>
       </c>
       <c r="F1032" t="n">
         <v>2218000</v>
@@ -21172,16 +21172,16 @@
         <v>45302</v>
       </c>
       <c r="B1038" t="n">
-        <v>6.847255706787109</v>
+        <v>6.847256183624268</v>
       </c>
       <c r="C1038" t="n">
-        <v>7.213909389872389</v>
+        <v>7.213909892243003</v>
       </c>
       <c r="D1038" t="n">
-        <v>6.819756931879673</v>
+        <v>6.819757406801839</v>
       </c>
       <c r="E1038" t="n">
-        <v>6.993917442272309</v>
+        <v>6.993917929322868</v>
       </c>
       <c r="F1038" t="n">
         <v>2188900</v>
@@ -21192,16 +21192,16 @@
         <v>45303</v>
       </c>
       <c r="B1039" t="n">
-        <v>6.810590744018555</v>
+        <v>6.810590267181396</v>
       </c>
       <c r="C1039" t="n">
-        <v>7.085581130213425</v>
+        <v>7.085580634123072</v>
       </c>
       <c r="D1039" t="n">
-        <v>6.792258080744574</v>
+        <v>6.792257605190961</v>
       </c>
       <c r="E1039" t="n">
-        <v>6.83808995747211</v>
+        <v>6.83808947870962</v>
       </c>
       <c r="F1039" t="n">
         <v>1935400</v>
@@ -21212,16 +21212,16 @@
         <v>45306</v>
       </c>
       <c r="B1040" t="n">
-        <v>6.929753303527832</v>
+        <v>6.929752826690674</v>
       </c>
       <c r="C1040" t="n">
-        <v>7.003083956937887</v>
+        <v>7.003083475054838</v>
       </c>
       <c r="D1040" t="n">
-        <v>6.700594793078822</v>
+        <v>6.700594332010089</v>
       </c>
       <c r="E1040" t="n">
-        <v>6.746426670002693</v>
+        <v>6.746426205780263</v>
       </c>
       <c r="F1040" t="n">
         <v>1399400</v>
@@ -21232,16 +21232,16 @@
         <v>45307</v>
       </c>
       <c r="B1041" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C1041" t="n">
-        <v>6.911420074576932</v>
+        <v>6.911420565075185</v>
       </c>
       <c r="D1041" t="n">
-        <v>6.654762808645371</v>
+        <v>6.654763280928852</v>
       </c>
       <c r="E1041" t="n">
-        <v>6.911420074576932</v>
+        <v>6.911420565075185</v>
       </c>
       <c r="F1041" t="n">
         <v>2256200</v>
@@ -21332,16 +21332,16 @@
         <v>45314</v>
       </c>
       <c r="B1046" t="n">
-        <v>6.718926906585693</v>
+        <v>6.718927383422852</v>
       </c>
       <c r="C1046" t="n">
-        <v>6.801424103463406</v>
+        <v>6.801424586155328</v>
       </c>
       <c r="D1046" t="n">
-        <v>6.526433738594455</v>
+        <v>6.526434201770518</v>
       </c>
       <c r="E1046" t="n">
-        <v>6.608930935472167</v>
+        <v>6.608931404502994</v>
       </c>
       <c r="F1046" t="n">
         <v>2038100</v>
@@ -21352,16 +21352,16 @@
         <v>45315</v>
       </c>
       <c r="B1047" t="n">
-        <v>6.874755382537842</v>
+        <v>6.874754905700684</v>
       </c>
       <c r="C1047" t="n">
-        <v>6.957252586995552</v>
+        <v>6.957252104436338</v>
       </c>
       <c r="D1047" t="n">
-        <v>6.755592851006743</v>
+        <v>6.75559238243477</v>
       </c>
       <c r="E1047" t="n">
-        <v>6.801424728391066</v>
+        <v>6.801424256640167</v>
       </c>
       <c r="F1047" t="n">
         <v>1933800</v>
@@ -21372,16 +21372,16 @@
         <v>45316</v>
       </c>
       <c r="B1048" t="n">
-        <v>6.893087387084961</v>
+        <v>6.893087863922119</v>
       </c>
       <c r="C1048" t="n">
-        <v>7.149745089146987</v>
+        <v>7.149745583738733</v>
       </c>
       <c r="D1048" t="n">
-        <v>6.83808940173277</v>
+        <v>6.83808987476538</v>
       </c>
       <c r="E1048" t="n">
-        <v>6.883921274735496</v>
+        <v>6.883921750938578</v>
       </c>
       <c r="F1048" t="n">
         <v>2213100</v>
@@ -21392,16 +21392,16 @@
         <v>45317</v>
       </c>
       <c r="B1049" t="n">
-        <v>7.094747543334961</v>
+        <v>7.094747066497803</v>
       </c>
       <c r="C1049" t="n">
-        <v>7.17724475009915</v>
+        <v>7.177244267717364</v>
       </c>
       <c r="D1049" t="n">
-        <v>6.718927711782881</v>
+        <v>6.718927260204529</v>
       </c>
       <c r="E1049" t="n">
-        <v>6.957252781508231</v>
+        <v>6.957252313912079</v>
       </c>
       <c r="F1049" t="n">
         <v>2582000</v>
@@ -21572,16 +21572,16 @@
         <v>45330</v>
       </c>
       <c r="B1058" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1058" t="n">
-        <v>7.617229205001097</v>
+        <v>7.617228715801493</v>
       </c>
       <c r="D1058" t="n">
-        <v>7.103913761472643</v>
+        <v>7.103913305239581</v>
       </c>
       <c r="E1058" t="n">
-        <v>7.131412974802268</v>
+        <v>7.13141251680313</v>
       </c>
       <c r="F1058" t="n">
         <v>7472200</v>
@@ -21652,16 +21652,16 @@
         <v>45338</v>
       </c>
       <c r="B1062" t="n">
-        <v>7.424736022949219</v>
+        <v>7.424735546112061</v>
       </c>
       <c r="C1062" t="n">
-        <v>7.443068249055412</v>
+        <v>7.443067771040908</v>
       </c>
       <c r="D1062" t="n">
-        <v>7.158911751046727</v>
+        <v>7.158911291281541</v>
       </c>
       <c r="E1062" t="n">
-        <v>7.333072269907244</v>
+        <v>7.333071798956986</v>
       </c>
       <c r="F1062" t="n">
         <v>2565400</v>
@@ -21692,16 +21692,16 @@
         <v>45342</v>
       </c>
       <c r="B1064" t="n">
-        <v>7.204743385314941</v>
+        <v>7.2047438621521</v>
       </c>
       <c r="C1064" t="n">
-        <v>7.314739360764598</v>
+        <v>7.314739844881705</v>
       </c>
       <c r="D1064" t="n">
-        <v>6.920586896860753</v>
+        <v>6.92058735489136</v>
       </c>
       <c r="E1064" t="n">
-        <v>7.241408710464827</v>
+        <v>7.241409189728635</v>
       </c>
       <c r="F1064" t="n">
         <v>5572100</v>
@@ -21752,16 +21752,16 @@
         <v>45345</v>
       </c>
       <c r="B1067" t="n">
-        <v>7.91055154800415</v>
+        <v>7.910551071166992</v>
       </c>
       <c r="C1067" t="n">
-        <v>8.249706024094255</v>
+        <v>8.249705526813331</v>
       </c>
       <c r="D1067" t="n">
-        <v>7.754723697615412</v>
+        <v>7.754723230171342</v>
       </c>
       <c r="E1067" t="n">
-        <v>8.075545948220533</v>
+        <v>8.07554546143774</v>
       </c>
       <c r="F1067" t="n">
         <v>3191100</v>
@@ -21772,16 +21772,16 @@
         <v>45348</v>
       </c>
       <c r="B1068" t="n">
-        <v>8.084711074829102</v>
+        <v>8.084712028503418</v>
       </c>
       <c r="C1068" t="n">
-        <v>8.11221072244448</v>
+        <v>8.112211679362662</v>
       </c>
       <c r="D1068" t="n">
-        <v>7.828053816277292</v>
+        <v>7.828054739676261</v>
       </c>
       <c r="E1068" t="n">
-        <v>7.910551010782934</v>
+        <v>7.910551943913292</v>
       </c>
       <c r="F1068" t="n">
         <v>1473000</v>
@@ -21892,16 +21892,16 @@
         <v>45356</v>
       </c>
       <c r="B1074" t="n">
-        <v>8.790520668029785</v>
+        <v>8.790519714355469</v>
       </c>
       <c r="C1074" t="n">
-        <v>8.90968319927654</v>
+        <v>8.909682232674404</v>
       </c>
       <c r="D1074" t="n">
-        <v>8.61635970921901</v>
+        <v>8.616358774439233</v>
       </c>
       <c r="E1074" t="n">
-        <v>8.763021891332949</v>
+        <v>8.763020940641946</v>
       </c>
       <c r="F1074" t="n">
         <v>2317900</v>
@@ -22112,16 +22112,16 @@
         <v>45371</v>
       </c>
       <c r="B1085" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1085" t="n">
-        <v>9.193838844589299</v>
+        <v>9.193837883247255</v>
       </c>
       <c r="D1085" t="n">
-        <v>8.341369812594202</v>
+        <v>8.341368940389497</v>
       </c>
       <c r="E1085" t="n">
-        <v>8.387200813603702</v>
+        <v>8.387199936606738</v>
       </c>
       <c r="F1085" t="n">
         <v>3946300</v>
@@ -22172,16 +22172,16 @@
         <v>45376</v>
       </c>
       <c r="B1088" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1088" t="n">
-        <v>8.634692952368088</v>
+        <v>8.634691984306407</v>
       </c>
       <c r="D1088" t="n">
-        <v>8.378035659229033</v>
+        <v>8.378034719941983</v>
       </c>
       <c r="E1088" t="n">
-        <v>8.433033213530791</v>
+        <v>8.433032268077797</v>
       </c>
       <c r="F1088" t="n">
         <v>2424700</v>
@@ -22232,16 +22232,16 @@
         <v>45379</v>
       </c>
       <c r="B1091" t="n">
-        <v>9.752985954284668</v>
+        <v>9.752986907958984</v>
       </c>
       <c r="C1091" t="n">
-        <v>9.881314153231251</v>
+        <v>9.881315119453859</v>
       </c>
       <c r="D1091" t="n">
-        <v>9.340499960041242</v>
+        <v>9.340500873381522</v>
       </c>
       <c r="E1091" t="n">
-        <v>9.386331834309434</v>
+        <v>9.386332752131281</v>
       </c>
       <c r="F1091" t="n">
         <v>5263200</v>
@@ -22312,16 +22312,16 @@
         <v>45386</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.98127365112305</v>
+        <v>10.98127460479736</v>
       </c>
       <c r="C1095" t="n">
-        <v>11.18293335294909</v>
+        <v>11.18293432413664</v>
       </c>
       <c r="D1095" t="n">
-        <v>10.43129383819321</v>
+        <v>10.43129474410425</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.43129383819321</v>
+        <v>10.43129474410425</v>
       </c>
       <c r="F1095" t="n">
         <v>7684100</v>
@@ -22372,16 +22372,16 @@
         <v>45391</v>
       </c>
       <c r="B1098" t="n">
-        <v>11.40292739868164</v>
+        <v>11.40292644500732</v>
       </c>
       <c r="C1098" t="n">
-        <v>11.73291622197656</v>
+        <v>11.7329152407039</v>
       </c>
       <c r="D1098" t="n">
-        <v>11.28376573934777</v>
+        <v>11.28376479563944</v>
       </c>
       <c r="E1098" t="n">
-        <v>11.29293141564012</v>
+        <v>11.29293047116523</v>
       </c>
       <c r="F1098" t="n">
         <v>4003300</v>
@@ -22392,16 +22392,16 @@
         <v>45392</v>
       </c>
       <c r="B1099" t="n">
-        <v>10.58712196350098</v>
+        <v>10.58712291717529</v>
       </c>
       <c r="C1099" t="n">
-        <v>11.36626027193104</v>
+        <v>11.36626129578913</v>
       </c>
       <c r="D1099" t="n">
-        <v>10.44962635083433</v>
+        <v>10.44962729212322</v>
       </c>
       <c r="E1099" t="n">
-        <v>11.36626027193104</v>
+        <v>11.36626129578913</v>
       </c>
       <c r="F1099" t="n">
         <v>6473200</v>
@@ -22412,16 +22412,16 @@
         <v>45393</v>
       </c>
       <c r="B1100" t="n">
-        <v>10.50462627410889</v>
+        <v>10.50462532043457</v>
       </c>
       <c r="C1100" t="n">
-        <v>10.94461019960207</v>
+        <v>10.94460920598332</v>
       </c>
       <c r="D1100" t="n">
-        <v>10.31213308816303</v>
+        <v>10.31213215196442</v>
       </c>
       <c r="E1100" t="n">
-        <v>10.66045413293031</v>
+        <v>10.66045316510899</v>
       </c>
       <c r="F1100" t="n">
         <v>3334800</v>
@@ -22492,16 +22492,16 @@
         <v>45399</v>
       </c>
       <c r="B1104" t="n">
-        <v>9.193839073181152</v>
+        <v>9.193840026855469</v>
       </c>
       <c r="C1104" t="n">
-        <v>9.707154514451329</v>
+        <v>9.707155521371709</v>
       </c>
       <c r="D1104" t="n">
-        <v>9.129674970836255</v>
+        <v>9.129675917854847</v>
       </c>
       <c r="E1104" t="n">
-        <v>9.395498804484115</v>
+        <v>9.395499779076538</v>
       </c>
       <c r="F1104" t="n">
         <v>2870900</v>
@@ -22612,16 +22612,16 @@
         <v>45407</v>
       </c>
       <c r="B1110" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C1110" t="n">
-        <v>10.00964332536244</v>
+        <v>10.00964236464995</v>
       </c>
       <c r="D1110" t="n">
-        <v>9.505494451765941</v>
+        <v>9.505493539440995</v>
       </c>
       <c r="E1110" t="n">
-        <v>9.670488851095419</v>
+        <v>9.670487922934525</v>
       </c>
       <c r="F1110" t="n">
         <v>2344600</v>
@@ -22672,16 +22672,16 @@
         <v>45412</v>
       </c>
       <c r="B1113" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C1113" t="n">
-        <v>10.89877837583131</v>
+        <v>10.89877940479569</v>
       </c>
       <c r="D1113" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="E1113" t="n">
-        <v>10.86211305146715</v>
+        <v>10.86211407696992</v>
       </c>
       <c r="F1113" t="n">
         <v>3726700</v>
@@ -22712,16 +22712,16 @@
         <v>45415</v>
       </c>
       <c r="B1115" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="C1115" t="n">
-        <v>11.01794147491455</v>
+        <v>11.01794052124023</v>
       </c>
       <c r="D1115" t="n">
-        <v>10.41296228000361</v>
+        <v>10.41296137869417</v>
       </c>
       <c r="E1115" t="n">
-        <v>10.48629293256791</v>
+        <v>10.48629202491122</v>
       </c>
       <c r="F1115" t="n">
         <v>3177300</v>
@@ -22792,16 +22792,16 @@
         <v>45421</v>
       </c>
       <c r="B1119" t="n">
-        <v>11.2379322052002</v>
+        <v>11.23793315887451</v>
       </c>
       <c r="C1119" t="n">
-        <v>11.33876162292093</v>
+        <v>11.33876258515184</v>
       </c>
       <c r="D1119" t="n">
-        <v>10.56878898092192</v>
+        <v>10.56878987781135</v>
       </c>
       <c r="E1119" t="n">
-        <v>11.30209630064337</v>
+        <v>11.30209725976278</v>
       </c>
       <c r="F1119" t="n">
         <v>4225100</v>
@@ -22832,16 +22832,16 @@
         <v>45425</v>
       </c>
       <c r="B1121" t="n">
-        <v>9.303834915161133</v>
+        <v>9.303833961486816</v>
       </c>
       <c r="C1121" t="n">
-        <v>9.569658744903728</v>
+        <v>9.569657763981576</v>
       </c>
       <c r="D1121" t="n">
-        <v>9.184673262319901</v>
+        <v>9.184672320860052</v>
       </c>
       <c r="E1121" t="n">
-        <v>9.395498666453195</v>
+        <v>9.395497703383034</v>
       </c>
       <c r="F1121" t="n">
         <v>4893500</v>
@@ -22872,16 +22872,16 @@
         <v>45427</v>
       </c>
       <c r="B1123" t="n">
-        <v>9.52382755279541</v>
+        <v>9.523828506469727</v>
       </c>
       <c r="C1123" t="n">
-        <v>9.835482377775513</v>
+        <v>9.835483362657577</v>
       </c>
       <c r="D1123" t="n">
-        <v>9.395498478389273</v>
+        <v>9.395499419213278</v>
       </c>
       <c r="E1123" t="n">
-        <v>9.597158202693118</v>
+        <v>9.597159163710444</v>
       </c>
       <c r="F1123" t="n">
         <v>4359100</v>
@@ -23012,16 +23012,16 @@
         <v>45436</v>
       </c>
       <c r="B1130" t="n">
-        <v>8.708023071289062</v>
+        <v>8.708024024963379</v>
       </c>
       <c r="C1130" t="n">
-        <v>9.083842874498499</v>
+        <v>9.083843869331375</v>
       </c>
       <c r="D1130" t="n">
-        <v>8.67135774595571</v>
+        <v>8.671358695614559</v>
       </c>
       <c r="E1130" t="n">
-        <v>8.882183148079907</v>
+        <v>8.882184120827667</v>
       </c>
       <c r="F1130" t="n">
         <v>2233000</v>
@@ -23032,16 +23032,16 @@
         <v>45439</v>
       </c>
       <c r="B1131" t="n">
-        <v>8.808852195739746</v>
+        <v>8.808853149414062</v>
       </c>
       <c r="C1131" t="n">
-        <v>8.836351844425723</v>
+        <v>8.836352801077238</v>
       </c>
       <c r="D1131" t="n">
-        <v>8.625525575351304</v>
+        <v>8.625526509178098</v>
       </c>
       <c r="E1131" t="n">
-        <v>8.680523998552976</v>
+        <v>8.680524938334075</v>
       </c>
       <c r="F1131" t="n">
         <v>1394600</v>
@@ -23092,16 +23092,16 @@
         <v>45443</v>
       </c>
       <c r="B1134" t="n">
-        <v>8.808852195739746</v>
+        <v>8.808853149414062</v>
       </c>
       <c r="C1134" t="n">
-        <v>9.395498255153042</v>
+        <v>9.395499272339524</v>
       </c>
       <c r="D1134" t="n">
-        <v>8.717189322630665</v>
+        <v>8.717190266381268</v>
       </c>
       <c r="E1134" t="n">
-        <v>9.074676013845558</v>
+        <v>9.074676996298805</v>
       </c>
       <c r="F1134" t="n">
         <v>8270300</v>
@@ -23172,16 +23172,16 @@
         <v>45449</v>
       </c>
       <c r="B1138" t="n">
-        <v>9.074676513671875</v>
+        <v>9.074675559997559</v>
       </c>
       <c r="C1138" t="n">
-        <v>9.239670918194381</v>
+        <v>9.2396699471805</v>
       </c>
       <c r="D1138" t="n">
-        <v>8.772187354827501</v>
+        <v>8.772186432942322</v>
       </c>
       <c r="E1138" t="n">
-        <v>8.937181759350008</v>
+        <v>8.937180820125265</v>
       </c>
       <c r="F1138" t="n">
         <v>3356600</v>
@@ -23252,16 +23252,16 @@
         <v>45455</v>
       </c>
       <c r="B1142" t="n">
-        <v>8.909682273864746</v>
+        <v>8.909683227539062</v>
       </c>
       <c r="C1142" t="n">
-        <v>9.661321836091128</v>
+        <v>9.661322870219418</v>
       </c>
       <c r="D1142" t="n">
-        <v>8.882182625853835</v>
+        <v>8.882183576584646</v>
       </c>
       <c r="E1142" t="n">
-        <v>9.395498024510802</v>
+        <v>9.395499030185853</v>
       </c>
       <c r="F1142" t="n">
         <v>3064700</v>
@@ -23272,16 +23272,16 @@
         <v>45456</v>
       </c>
       <c r="B1143" t="n">
-        <v>8.62552547454834</v>
+        <v>8.625526428222656</v>
       </c>
       <c r="C1143" t="n">
-        <v>8.891349289547579</v>
+        <v>8.891350272612492</v>
       </c>
       <c r="D1143" t="n">
-        <v>8.59802670035401</v>
+        <v>8.598027650987946</v>
       </c>
       <c r="E1143" t="n">
-        <v>8.891349289547579</v>
+        <v>8.891350272612492</v>
       </c>
       <c r="F1143" t="n">
         <v>2367500</v>
@@ -23452,16 +23452,16 @@
         <v>45469</v>
       </c>
       <c r="B1152" t="n">
-        <v>8.735522270202637</v>
+        <v>8.73552131652832</v>
       </c>
       <c r="C1152" t="n">
-        <v>9.01967921093841</v>
+        <v>9.019678226242117</v>
       </c>
       <c r="D1152" t="n">
-        <v>8.735522270202637</v>
+        <v>8.73552131652832</v>
       </c>
       <c r="E1152" t="n">
-        <v>9.01967921093841</v>
+        <v>9.019678226242117</v>
       </c>
       <c r="F1152" t="n">
         <v>1529900</v>
@@ -23512,16 +23512,16 @@
         <v>45474</v>
       </c>
       <c r="B1155" t="n">
-        <v>8.579693794250488</v>
+        <v>8.579694747924805</v>
       </c>
       <c r="C1155" t="n">
-        <v>8.689689767669948</v>
+        <v>8.689690733570847</v>
       </c>
       <c r="D1155" t="n">
-        <v>8.414700271206444</v>
+        <v>8.414701206540935</v>
       </c>
       <c r="E1155" t="n">
-        <v>8.579693794250488</v>
+        <v>8.579694747924805</v>
       </c>
       <c r="F1155" t="n">
         <v>1954600</v>
@@ -23532,16 +23532,16 @@
         <v>45475</v>
       </c>
       <c r="B1156" t="n">
-        <v>8.414699554443359</v>
+        <v>8.414700508117676</v>
       </c>
       <c r="C1156" t="n">
-        <v>8.836351187053534</v>
+        <v>8.836352188515454</v>
       </c>
       <c r="D1156" t="n">
-        <v>8.387199907803193</v>
+        <v>8.387200858360856</v>
       </c>
       <c r="E1156" t="n">
-        <v>8.588859612313334</v>
+        <v>8.588860585725962</v>
       </c>
       <c r="F1156" t="n">
         <v>3229800</v>
@@ -23732,16 +23732,16 @@
         <v>45489</v>
       </c>
       <c r="B1166" t="n">
-        <v>9.303834915161133</v>
+        <v>9.303833961486816</v>
       </c>
       <c r="C1166" t="n">
-        <v>9.789651573170611</v>
+        <v>9.789650569698455</v>
       </c>
       <c r="D1166" t="n">
-        <v>9.258003913685421</v>
+        <v>9.258002964708936</v>
       </c>
       <c r="E1166" t="n">
-        <v>9.743819697524581</v>
+        <v>9.743818698750346</v>
       </c>
       <c r="F1166" t="n">
         <v>1952400</v>
@@ -23832,16 +23832,16 @@
         <v>45496</v>
       </c>
       <c r="B1171" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="C1171" t="n">
-        <v>8.607194619854459</v>
+        <v>8.607193615930459</v>
       </c>
       <c r="D1171" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="E1171" t="n">
-        <v>8.607194619854459</v>
+        <v>8.607193615930459</v>
       </c>
       <c r="F1171" t="n">
         <v>3005900</v>
@@ -23892,16 +23892,16 @@
         <v>45499</v>
       </c>
       <c r="B1174" t="n">
-        <v>7.818887233734131</v>
+        <v>7.818887710571289</v>
       </c>
       <c r="C1174" t="n">
-        <v>7.883052203726183</v>
+        <v>7.883052684476461</v>
       </c>
       <c r="D1174" t="n">
-        <v>7.653893719596588</v>
+        <v>7.653894186371567</v>
       </c>
       <c r="E1174" t="n">
-        <v>7.718057815418397</v>
+        <v>7.718058286106443</v>
       </c>
       <c r="F1174" t="n">
         <v>2119900</v>
@@ -23952,16 +23952,16 @@
         <v>45504</v>
       </c>
       <c r="B1177" t="n">
-        <v>7.736391067504883</v>
+        <v>7.736390590667725</v>
       </c>
       <c r="C1177" t="n">
-        <v>7.873886700753659</v>
+        <v>7.873886215441875</v>
       </c>
       <c r="D1177" t="n">
-        <v>7.617229409194445</v>
+        <v>7.617228939701889</v>
       </c>
       <c r="E1177" t="n">
-        <v>7.718058840907261</v>
+        <v>7.718058365200021</v>
       </c>
       <c r="F1177" t="n">
         <v>1863600</v>
@@ -23972,16 +23972,16 @@
         <v>45505</v>
       </c>
       <c r="B1178" t="n">
-        <v>7.727224349975586</v>
+        <v>7.727224826812744</v>
       </c>
       <c r="C1178" t="n">
-        <v>7.965548508650412</v>
+        <v>7.965549000194251</v>
       </c>
       <c r="D1178" t="n">
-        <v>7.663059380104842</v>
+        <v>7.663059852982463</v>
       </c>
       <c r="E1178" t="n">
-        <v>7.828053768100695</v>
+        <v>7.828054251159909</v>
       </c>
       <c r="F1178" t="n">
         <v>2732500</v>
@@ -24032,16 +24032,16 @@
         <v>45510</v>
       </c>
       <c r="B1181" t="n">
-        <v>7.95638370513916</v>
+        <v>7.956383228302002</v>
       </c>
       <c r="C1181" t="n">
-        <v>8.176375663782647</v>
+        <v>8.176375173761064</v>
       </c>
       <c r="D1181" t="n">
-        <v>7.782222748918646</v>
+        <v>7.782222282519196</v>
       </c>
       <c r="E1181" t="n">
-        <v>7.993049031579741</v>
+        <v>7.993048552545178</v>
       </c>
       <c r="F1181" t="n">
         <v>1835500</v>
@@ -24052,16 +24052,16 @@
         <v>45511</v>
       </c>
       <c r="B1182" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1182" t="n">
-        <v>8.543029196304673</v>
+        <v>8.543028238519694</v>
       </c>
       <c r="D1182" t="n">
-        <v>8.020548059586147</v>
+        <v>8.020547160378118</v>
       </c>
       <c r="E1182" t="n">
-        <v>8.158042819510907</v>
+        <v>8.158041904887924</v>
       </c>
       <c r="F1182" t="n">
         <v>2816900</v>
@@ -24092,16 +24092,16 @@
         <v>45513</v>
       </c>
       <c r="B1184" t="n">
-        <v>7.846388339996338</v>
+        <v>7.84638786315918</v>
       </c>
       <c r="C1184" t="n">
-        <v>8.103045645170351</v>
+        <v>8.103045152735731</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.653895142573226</v>
+        <v>7.653894677434178</v>
       </c>
       <c r="E1184" t="n">
-        <v>8.103045645170351</v>
+        <v>8.103045152735731</v>
       </c>
       <c r="F1184" t="n">
         <v>6458600</v>
@@ -24132,16 +24132,16 @@
         <v>45517</v>
       </c>
       <c r="B1186" t="n">
-        <v>8.176376342773438</v>
+        <v>8.176375389099121</v>
       </c>
       <c r="C1186" t="n">
-        <v>8.497198631398319</v>
+        <v>8.497197640304007</v>
       </c>
       <c r="D1186" t="n">
-        <v>8.103045683802677</v>
+        <v>8.103044738681486</v>
       </c>
       <c r="E1186" t="n">
-        <v>8.497198631398319</v>
+        <v>8.497197640304007</v>
       </c>
       <c r="F1186" t="n">
         <v>4500900</v>
@@ -24192,16 +24192,16 @@
         <v>45520</v>
       </c>
       <c r="B1189" t="n">
-        <v>8.506363868713379</v>
+        <v>8.506362915039062</v>
       </c>
       <c r="C1189" t="n">
-        <v>8.598027624776794</v>
+        <v>8.598026660825775</v>
       </c>
       <c r="D1189" t="n">
-        <v>8.304705004046447</v>
+        <v>8.304704072980718</v>
       </c>
       <c r="E1189" t="n">
-        <v>8.387201335499084</v>
+        <v>8.387200395184442</v>
       </c>
       <c r="F1189" t="n">
         <v>3088500</v>
@@ -24212,16 +24212,16 @@
         <v>45523</v>
       </c>
       <c r="B1190" t="n">
-        <v>8.744688987731934</v>
+        <v>8.744688034057617</v>
       </c>
       <c r="C1190" t="n">
-        <v>8.827186193851068</v>
+        <v>8.82718523117981</v>
       </c>
       <c r="D1190" t="n">
-        <v>8.442199814742022</v>
+        <v>8.442198894056432</v>
       </c>
       <c r="E1190" t="n">
-        <v>8.478865142553818</v>
+        <v>8.478864217869598</v>
       </c>
       <c r="F1190" t="n">
         <v>2333900</v>
@@ -24272,16 +24272,16 @@
         <v>45526</v>
       </c>
       <c r="B1193" t="n">
-        <v>8.653023719787598</v>
+        <v>8.653024673461914</v>
       </c>
       <c r="C1193" t="n">
-        <v>9.093008450852169</v>
+        <v>9.093009453018452</v>
       </c>
       <c r="D1193" t="n">
-        <v>8.616358398379734</v>
+        <v>8.616359348013061</v>
       </c>
       <c r="E1193" t="n">
-        <v>9.038010031655267</v>
+        <v>9.038011027760017</v>
       </c>
       <c r="F1193" t="n">
         <v>2148900</v>
@@ -24412,16 +24412,16 @@
         <v>45537</v>
       </c>
       <c r="B1200" t="n">
-        <v>8.93718147277832</v>
+        <v>8.937182426452637</v>
       </c>
       <c r="C1200" t="n">
-        <v>9.2488371716963</v>
+        <v>9.248838158626967</v>
       </c>
       <c r="D1200" t="n">
-        <v>8.918848373232414</v>
+        <v>8.918849324950433</v>
       </c>
       <c r="E1200" t="n">
-        <v>9.120508097385867</v>
+        <v>9.120509070622715</v>
       </c>
       <c r="F1200" t="n">
         <v>2102800</v>
@@ -24452,16 +24452,16 @@
         <v>45539</v>
       </c>
       <c r="B1202" t="n">
-        <v>9.294669151306152</v>
+        <v>9.294670104980469</v>
       </c>
       <c r="C1202" t="n">
-        <v>9.468829228106612</v>
+        <v>9.468830199650526</v>
       </c>
       <c r="D1202" t="n">
-        <v>9.184673175300023</v>
+        <v>9.184674117688264</v>
       </c>
       <c r="E1202" t="n">
-        <v>9.212171950758979</v>
+        <v>9.212172895968715</v>
       </c>
       <c r="F1202" t="n">
         <v>2019900</v>
@@ -24572,16 +24572,16 @@
         <v>45547</v>
       </c>
       <c r="B1208" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1208" t="n">
-        <v>9.212171944329347</v>
+        <v>9.212170981070326</v>
       </c>
       <c r="D1208" t="n">
-        <v>8.955514667160847</v>
+        <v>8.955513730738867</v>
       </c>
       <c r="E1208" t="n">
-        <v>9.175506619019561</v>
+        <v>9.175505659594403</v>
       </c>
       <c r="F1208" t="n">
         <v>1127400</v>
@@ -24612,16 +24612,16 @@
         <v>45551</v>
       </c>
       <c r="B1210" t="n">
-        <v>9.936312675476074</v>
+        <v>9.936311721801758</v>
       </c>
       <c r="C1210" t="n">
-        <v>10.17463772469192</v>
+        <v>10.17463674814347</v>
       </c>
       <c r="D1210" t="n">
-        <v>9.569658551873937</v>
+        <v>9.569657633390603</v>
       </c>
       <c r="E1210" t="n">
-        <v>9.707154176038602</v>
+        <v>9.707153244358619</v>
       </c>
       <c r="F1210" t="n">
         <v>2756600</v>
@@ -24652,16 +24652,16 @@
         <v>45553</v>
       </c>
       <c r="B1212" t="n">
-        <v>9.890481948852539</v>
+        <v>9.890480995178223</v>
       </c>
       <c r="C1212" t="n">
-        <v>10.26630179168833</v>
+        <v>10.26630080177617</v>
       </c>
       <c r="D1212" t="n">
-        <v>9.606324991929888</v>
+        <v>9.606324065654963</v>
       </c>
       <c r="E1212" t="n">
-        <v>9.697988752013428</v>
+        <v>9.697987816899968</v>
       </c>
       <c r="F1212" t="n">
         <v>2495300</v>
@@ -24672,16 +24672,16 @@
         <v>45554</v>
       </c>
       <c r="B1213" t="n">
-        <v>9.853815078735352</v>
+        <v>9.853816032409668</v>
       </c>
       <c r="C1213" t="n">
-        <v>10.15630421586989</v>
+        <v>10.15630519881978</v>
       </c>
       <c r="D1213" t="n">
-        <v>9.798816656451679</v>
+        <v>9.798817604803125</v>
       </c>
       <c r="E1213" t="n">
-        <v>10.00047637259812</v>
+        <v>10.00047734046665</v>
       </c>
       <c r="F1213" t="n">
         <v>3128500</v>
@@ -24732,16 +24732,16 @@
         <v>45559</v>
       </c>
       <c r="B1216" t="n">
-        <v>9.487161636352539</v>
+        <v>9.487162590026855</v>
       </c>
       <c r="C1216" t="n">
-        <v>9.615489828587524</v>
+        <v>9.615490795161728</v>
       </c>
       <c r="D1216" t="n">
-        <v>9.28550192462153</v>
+        <v>9.285502858024484</v>
       </c>
       <c r="E1216" t="n">
-        <v>9.514660409807144</v>
+        <v>9.51466136624571</v>
       </c>
       <c r="F1216" t="n">
         <v>1652000</v>
@@ -24772,16 +24772,16 @@
         <v>45561</v>
       </c>
       <c r="B1218" t="n">
-        <v>9.551325798034668</v>
+        <v>9.551326751708984</v>
       </c>
       <c r="C1218" t="n">
-        <v>9.789650834064538</v>
+        <v>9.78965181153497</v>
       </c>
       <c r="D1218" t="n">
-        <v>9.450496378562148</v>
+        <v>9.450497322168916</v>
       </c>
       <c r="E1218" t="n">
-        <v>9.450496378562148</v>
+        <v>9.450497322168916</v>
       </c>
       <c r="F1218" t="n">
         <v>1643400</v>
@@ -24792,16 +24792,16 @@
         <v>45562</v>
       </c>
       <c r="B1219" t="n">
-        <v>9.587992668151855</v>
+        <v>9.587991714477539</v>
       </c>
       <c r="C1219" t="n">
-        <v>9.752987084977519</v>
+        <v>9.752986114891955</v>
       </c>
       <c r="D1219" t="n">
-        <v>9.450497903577398</v>
+        <v>9.450496963579065</v>
       </c>
       <c r="E1219" t="n">
-        <v>9.532994237819837</v>
+        <v>9.532993289615966</v>
       </c>
       <c r="F1219" t="n">
         <v>1380700</v>
@@ -24892,16 +24892,16 @@
         <v>45569</v>
       </c>
       <c r="B1224" t="n">
-        <v>9.120508193969727</v>
+        <v>9.12050724029541</v>
       </c>
       <c r="C1224" t="n">
-        <v>9.258003819509156</v>
+        <v>9.258002851457784</v>
       </c>
       <c r="D1224" t="n">
-        <v>9.038010993480132</v>
+        <v>9.03801004843203</v>
       </c>
       <c r="E1224" t="n">
-        <v>9.166340069149538</v>
+        <v>9.166339110682868</v>
       </c>
       <c r="F1224" t="n">
         <v>1258700</v>
@@ -24972,16 +24972,16 @@
         <v>45575</v>
       </c>
       <c r="B1228" t="n">
-        <v>9.422996520996094</v>
+        <v>9.42299747467041</v>
       </c>
       <c r="C1228" t="n">
-        <v>9.441329619130419</v>
+        <v>9.441330574660176</v>
       </c>
       <c r="D1228" t="n">
-        <v>8.946347333716643</v>
+        <v>8.946348239150669</v>
       </c>
       <c r="E1228" t="n">
-        <v>9.065509849079064</v>
+        <v>9.065510766573185</v>
       </c>
       <c r="F1228" t="n">
         <v>2116800</v>
@@ -24992,16 +24992,16 @@
         <v>45576</v>
       </c>
       <c r="B1229" t="n">
-        <v>10.1013069152832</v>
+        <v>10.10130786895752</v>
       </c>
       <c r="C1229" t="n">
-        <v>10.3671307354659</v>
+        <v>10.36713171423691</v>
       </c>
       <c r="D1229" t="n">
-        <v>9.432163652924501</v>
+        <v>9.432164543424346</v>
       </c>
       <c r="E1229" t="n">
-        <v>9.432163652924501</v>
+        <v>9.432164543424346</v>
       </c>
       <c r="F1229" t="n">
         <v>6482800</v>
@@ -25112,16 +25112,16 @@
         <v>45586</v>
       </c>
       <c r="B1235" t="n">
-        <v>10.95377540588379</v>
+        <v>10.95377635955811</v>
       </c>
       <c r="C1235" t="n">
-        <v>11.2654310852861</v>
+        <v>11.26543206609426</v>
       </c>
       <c r="D1235" t="n">
-        <v>10.89877785903058</v>
+        <v>10.89877880791662</v>
       </c>
       <c r="E1235" t="n">
-        <v>11.07293792295939</v>
+        <v>11.07293888700842</v>
       </c>
       <c r="F1235" t="n">
         <v>2389000</v>
@@ -25132,16 +25132,16 @@
         <v>45587</v>
       </c>
       <c r="B1236" t="n">
-        <v>10.65128612518311</v>
+        <v>10.65128707885742</v>
       </c>
       <c r="C1236" t="n">
-        <v>11.00877367135879</v>
+        <v>11.00877465704114</v>
       </c>
       <c r="D1236" t="n">
-        <v>10.62378735214505</v>
+        <v>10.62378830335723</v>
       </c>
       <c r="E1236" t="n">
-        <v>10.86211238292884</v>
+        <v>10.86211335547971</v>
       </c>
       <c r="F1236" t="n">
         <v>2418100</v>
@@ -25232,16 +25232,16 @@
         <v>45594</v>
       </c>
       <c r="B1241" t="n">
-        <v>11.42125988006592</v>
+        <v>11.4212589263916</v>
       </c>
       <c r="C1241" t="n">
-        <v>11.62291960845494</v>
+        <v>11.62291863794205</v>
       </c>
       <c r="D1241" t="n">
-        <v>11.25626547736851</v>
+        <v>11.25626453747121</v>
       </c>
       <c r="E1241" t="n">
-        <v>11.47625830568849</v>
+        <v>11.47625734742181</v>
       </c>
       <c r="F1241" t="n">
         <v>2046100</v>
@@ -25252,16 +25252,16 @@
         <v>45595</v>
       </c>
       <c r="B1242" t="n">
-        <v>12.09956836700439</v>
+        <v>12.09956932067871</v>
       </c>
       <c r="C1242" t="n">
-        <v>12.35622563676056</v>
+        <v>12.35622661066431</v>
       </c>
       <c r="D1242" t="n">
-        <v>11.3204300081306</v>
+        <v>11.32043090039411</v>
       </c>
       <c r="E1242" t="n">
-        <v>11.3204300081306</v>
+        <v>11.32043090039411</v>
       </c>
       <c r="F1242" t="n">
         <v>5623200</v>
@@ -25412,16 +25412,16 @@
         <v>45607</v>
       </c>
       <c r="B1250" t="n">
-        <v>12.33789348602295</v>
+        <v>12.33789443969727</v>
       </c>
       <c r="C1250" t="n">
-        <v>12.47538823424922</v>
+        <v>12.47538919855138</v>
       </c>
       <c r="D1250" t="n">
-        <v>11.64125144689053</v>
+        <v>11.64125234671695</v>
       </c>
       <c r="E1250" t="n">
-        <v>11.69624987068321</v>
+        <v>11.69625077476081</v>
       </c>
       <c r="F1250" t="n">
         <v>4291300</v>
@@ -25432,16 +25432,16 @@
         <v>45608</v>
       </c>
       <c r="B1251" t="n">
-        <v>11.86124420166016</v>
+        <v>11.86124324798584</v>
       </c>
       <c r="C1251" t="n">
-        <v>12.37455965339907</v>
+        <v>12.37455865845288</v>
       </c>
       <c r="D1251" t="n">
-        <v>11.77874787160726</v>
+        <v>11.77874692456585</v>
       </c>
       <c r="E1251" t="n">
-        <v>12.28289589889094</v>
+        <v>12.28289491131475</v>
       </c>
       <c r="F1251" t="n">
         <v>1595200</v>
@@ -25472,16 +25472,16 @@
         <v>45610</v>
       </c>
       <c r="B1253" t="n">
-        <v>10.58712196350098</v>
+        <v>10.58712291717529</v>
       </c>
       <c r="C1253" t="n">
-        <v>10.99960705316045</v>
+        <v>10.99960804399089</v>
       </c>
       <c r="D1253" t="n">
-        <v>10.40379535411568</v>
+        <v>10.40379629127617</v>
       </c>
       <c r="E1253" t="n">
-        <v>10.55962319063574</v>
+        <v>10.559624141833</v>
       </c>
       <c r="F1253" t="n">
         <v>63226600</v>
@@ -25512,16 +25512,16 @@
         <v>45615</v>
       </c>
       <c r="B1255" t="n">
-        <v>11.35709667205811</v>
+        <v>11.35709571838379</v>
       </c>
       <c r="C1255" t="n">
-        <v>11.46709265778581</v>
+        <v>11.46709169487495</v>
       </c>
       <c r="D1255" t="n">
-        <v>10.91711185497689</v>
+        <v>10.91711093824883</v>
       </c>
       <c r="E1255" t="n">
-        <v>11.00877561350184</v>
+        <v>11.00877468907663</v>
       </c>
       <c r="F1255" t="n">
         <v>7243900</v>
@@ -25532,16 +25532,16 @@
         <v>45617</v>
       </c>
       <c r="B1256" t="n">
-        <v>11.2379322052002</v>
+        <v>11.23793315887451</v>
       </c>
       <c r="C1256" t="n">
-        <v>11.32959507380898</v>
+        <v>11.329596035262</v>
       </c>
       <c r="D1256" t="n">
-        <v>10.94460875280948</v>
+        <v>10.94460968159175</v>
       </c>
       <c r="E1256" t="n">
-        <v>11.30209630064337</v>
+        <v>11.30209725976278</v>
       </c>
       <c r="F1256" t="n">
         <v>3263500</v>
@@ -25592,16 +25592,16 @@
         <v>45622</v>
       </c>
       <c r="B1259" t="n">
-        <v>11.57708835601807</v>
+        <v>11.57708740234375</v>
       </c>
       <c r="C1259" t="n">
-        <v>11.66875123809635</v>
+        <v>11.66875027687121</v>
       </c>
       <c r="D1259" t="n">
-        <v>11.31126451190142</v>
+        <v>11.31126358012461</v>
       </c>
       <c r="E1259" t="n">
-        <v>11.63208591043096</v>
+        <v>11.63208495222617</v>
       </c>
       <c r="F1259" t="n">
         <v>7231300</v>
@@ -25652,16 +25652,16 @@
         <v>45625</v>
       </c>
       <c r="B1262" t="n">
-        <v>9.688821792602539</v>
+        <v>9.688820838928223</v>
       </c>
       <c r="C1262" t="n">
-        <v>9.697988343058428</v>
+        <v>9.697987388481845</v>
       </c>
       <c r="D1262" t="n">
-        <v>9.001346243477393</v>
+        <v>9.00134535747155</v>
       </c>
       <c r="E1262" t="n">
-        <v>9.532993931533877</v>
+        <v>9.532992993197755</v>
       </c>
       <c r="F1262" t="n">
         <v>14865400</v>
@@ -25732,16 +25732,16 @@
         <v>45631</v>
       </c>
       <c r="B1266" t="n">
-        <v>9.404665946960449</v>
+        <v>9.404664993286133</v>
       </c>
       <c r="C1266" t="n">
-        <v>9.835483338655724</v>
+        <v>9.835482341294636</v>
       </c>
       <c r="D1266" t="n">
-        <v>9.294669961367802</v>
+        <v>9.294669018847561</v>
       </c>
       <c r="E1266" t="n">
-        <v>9.624657918145745</v>
+        <v>9.624656942163279</v>
       </c>
       <c r="F1266" t="n">
         <v>7256000</v>
@@ -25952,16 +25952,16 @@
         <v>45646</v>
       </c>
       <c r="B1277" t="n">
-        <v>8.93718147277832</v>
+        <v>8.937182426452637</v>
       </c>
       <c r="C1277" t="n">
-        <v>9.138841196931772</v>
+        <v>9.138842172124919</v>
       </c>
       <c r="D1277" t="n">
-        <v>8.588860448938831</v>
+        <v>8.588861365444293</v>
       </c>
       <c r="E1277" t="n">
-        <v>8.799686722865236</v>
+        <v>8.799687661867678</v>
       </c>
       <c r="F1277" t="n">
         <v>5127000</v>
@@ -26032,16 +26032,16 @@
         <v>45656</v>
       </c>
       <c r="B1281" t="n">
-        <v>7.378904342651367</v>
+        <v>7.378903865814209</v>
       </c>
       <c r="C1281" t="n">
-        <v>7.86472014868406</v>
+        <v>7.86471964045267</v>
       </c>
       <c r="D1281" t="n">
-        <v>7.314739801232726</v>
+        <v>7.314739328541989</v>
       </c>
       <c r="E1281" t="n">
-        <v>7.809722594732624</v>
+        <v>7.809722090055269</v>
       </c>
       <c r="F1281" t="n">
         <v>5347400</v>
@@ -34472,19 +34472,39 @@
         <v>46274</v>
       </c>
       <c r="B1703" t="n">
-        <v>9.08</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="C1703" t="n">
-        <v>9.33</v>
+        <v>9.329999923706055</v>
       </c>
       <c r="D1703" t="n">
-        <v>8.98</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="E1703" t="n">
-        <v>9.279999999999999</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="F1703" t="n">
         <v>6444200</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1704" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="C1704" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="D1704" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>10259400</v>
       </c>
     </row>
   </sheetData>
